--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -802,7 +802,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -937,7 +937,7 @@
         <v>86</v>
       </c>
       <c r="AY2" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -945,7 +945,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1092,7 +1092,7 @@
         <v>87</v>
       </c>
       <c r="AY3" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1100,7 +1100,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1247,7 +1247,7 @@
         <v>87</v>
       </c>
       <c r="AY4" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1255,7 +1255,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1402,7 +1402,7 @@
         <v>87</v>
       </c>
       <c r="AY5" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1410,7 +1410,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1557,7 +1557,7 @@
         <v>87</v>
       </c>
       <c r="AY6" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1565,7 +1565,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1712,7 +1712,7 @@
         <v>87</v>
       </c>
       <c r="AY7" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1720,7 +1720,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1867,7 +1867,7 @@
         <v>87</v>
       </c>
       <c r="AY8" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1875,7 +1875,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2022,7 +2022,7 @@
         <v>87</v>
       </c>
       <c r="AY9" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2030,7 +2030,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2177,7 +2177,7 @@
         <v>87</v>
       </c>
       <c r="AY10" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2185,7 +2185,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2332,7 +2332,7 @@
         <v>87</v>
       </c>
       <c r="AY11" s="2">
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
   </si>
   <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
@@ -223,49 +223,55 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4791,naive=0.1153,drift4=0.1952; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04107,naive=0.01437,drift4=0.0194; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1142,naive=0.03522,drift4=0.05413; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=4.789,naive=1.898,drift4=2.937; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05562,naive=0.01749,drift4=0.03119; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1895,naive=0.09846,drift4=0.1253; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3301,naive=0.09697,drift4=0.118; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.0302,naive=0.01494,drift4=0.01988; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04626,naive=0.01468,drift4=0.02121; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=762,naive=264.7,drift4=326.6; naive_cap_applied</t>
+    <t>REDUCE_CONFLICT</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=5.203,naive=1.806,drift4=2.731; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03978,naive=0.01375,drift4=0.01995; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1094,naive=0.03241,drift4=0.05479; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05574,naive=0.01743,drift4=0.03289; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4524,naive=0.1124,drift4=0.1962; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.331,naive=0.09223,drift4=0.1138; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04916,naive=0.01362,drift4=0.0213; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1819,naive=0.09163,drift4=0.1303; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02889,naive=0.01385,drift4=0.02136; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=712.1,naive=251.1,drift4=317.6; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -802,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,61 +832,61 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1691622367477087</v>
       </c>
       <c r="L2">
-        <v>0.01320757137988905</v>
+        <v>1.667529779394976</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>9.09033</v>
+        <v>162.403</v>
       </c>
       <c r="S2">
-        <v>9.083476397497975</v>
+        <v>162.3010553653823</v>
       </c>
       <c r="T2">
-        <v>9.052515088843235</v>
+        <v>161.1869684427783</v>
       </c>
       <c r="U2">
-        <v>9.09033</v>
+        <v>162.403</v>
       </c>
       <c r="V2">
-        <v>9.11378</v>
+        <v>163.526</v>
       </c>
       <c r="Y2">
-        <v>-0.0007539443014747225</v>
+        <v>-0.0006277263019629864</v>
       </c>
       <c r="AA2">
-        <v>0.0007539443014747225</v>
+        <v>0.0006277263019629864</v>
       </c>
       <c r="AB2">
-        <v>0.4180794849515861</v>
+        <v>0.4276747064524046</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3819205150484139</v>
+        <v>0.3723252935475955</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -913,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.5025795624796461</v>
+        <v>4.714049707656474</v>
       </c>
       <c r="AR2">
-        <v>0.116203463621939</v>
+        <v>2.049990708944266</v>
       </c>
       <c r="AS2">
-        <v>0.2435028625503056</v>
+        <v>3.964277884836795</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -945,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -957,7 +963,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
         <v>67</v>
@@ -966,73 +972,73 @@
         <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K3">
-        <v>0.7614406039998592</v>
+        <v>0.9944810556946149</v>
       </c>
       <c r="L3">
-        <v>1.580300249130866</v>
+        <v>1.74281019230603</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" t="s">
         <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0.9403601509999648</v>
+        <v>0.9986202639236537</v>
       </c>
       <c r="R3">
-        <v>0.8084</v>
+        <v>0.814715</v>
       </c>
       <c r="S3">
-        <v>0.8155751968832385</v>
+        <v>0.8224709972108237</v>
       </c>
       <c r="T3">
-        <v>0.8150604544486763</v>
+        <v>0.8261669757900578</v>
       </c>
       <c r="U3">
-        <v>0.8084</v>
+        <v>0.814715</v>
       </c>
       <c r="V3">
-        <v>0.8199</v>
+        <v>0.8224299999999999</v>
       </c>
       <c r="W3">
-        <v>0.8155751968832385</v>
+        <v>0.8224709972108237</v>
       </c>
       <c r="X3">
-        <v>0.798725</v>
+        <v>0.80504</v>
       </c>
       <c r="Y3">
-        <v>0.008875800201927922</v>
+        <v>0.009519890036176776</v>
       </c>
       <c r="Z3">
-        <v>0.7416224168721984</v>
+        <v>0.8016534584830748</v>
       </c>
       <c r="AA3">
-        <v>0.008875800201927922</v>
+        <v>0.009519890036176776</v>
       </c>
       <c r="AB3">
-        <v>0.4183870355776679</v>
+        <v>0.4238714136275828</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3816129644223321</v>
+        <v>0.3761285863724171</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1041,58 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>470.1800754999824</v>
+        <v>499.3101319618268</v>
       </c>
       <c r="AI3">
-        <v>0.011968085106383</v>
+        <v>0.01187531836286311</v>
       </c>
       <c r="AJ3">
-        <v>41777.77777777771</v>
+        <v>42104.13436692499</v>
       </c>
       <c r="AK3">
-        <v>39286.15741955402</v>
+        <v>42046.04177377561</v>
       </c>
       <c r="AL3">
-        <v>48597.42382428751</v>
+        <v>51608.28237331535</v>
       </c>
       <c r="AM3">
-        <v>392.8615741955402</v>
+        <v>420.4604177377561</v>
       </c>
       <c r="AN3">
-        <v>0.003928615741955402</v>
+        <v>0.00420460417737756</v>
       </c>
       <c r="AO3">
-        <v>470.1800754999825</v>
+        <v>499.3101319618269</v>
       </c>
       <c r="AP3">
-        <v>0.004701800754999825</v>
+        <v>0.004993101319618269</v>
       </c>
       <c r="AQ3">
-        <v>0.03775763864887026</v>
+        <v>0.03914827944028984</v>
       </c>
       <c r="AR3">
-        <v>0.01462854974211326</v>
+        <v>0.0155265768355269</v>
       </c>
       <c r="AS3">
-        <v>0.02829434496287172</v>
+        <v>0.02759320396020567</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
         <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1100,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1112,7 +1118,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>67</v>
@@ -1121,73 +1127,73 @@
         <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.2304796023442486</v>
+        <v>0.349964848679059</v>
       </c>
       <c r="M4">
         <v>1</v>
       </c>
       <c r="N4">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>6.7813</v>
+        <v>6.78471</v>
       </c>
       <c r="S4">
-        <v>6.83411087457003</v>
+        <v>6.829498327365241</v>
       </c>
       <c r="T4">
-        <v>6.890211897225512</v>
+        <v>6.887526430890647</v>
       </c>
       <c r="U4">
-        <v>6.7813</v>
+        <v>6.78471</v>
       </c>
       <c r="V4">
-        <v>6.7993</v>
+        <v>6.786719999999999</v>
       </c>
       <c r="W4">
-        <v>6.83411087457003</v>
+        <v>6.829498327365241</v>
       </c>
       <c r="X4">
-        <v>6.746092750286647</v>
+        <v>6.754851115089838</v>
       </c>
       <c r="Y4">
-        <v>0.007787721317450895</v>
+        <v>0.00660136208699284</v>
       </c>
       <c r="Z4">
         <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.007787721317450895</v>
+        <v>0.00660136208699284</v>
       </c>
       <c r="AB4">
-        <v>0.4225065777117103</v>
+        <v>0.4283489355166407</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3774934222882897</v>
+        <v>0.3716510644833593</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1199,55 +1205,55 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.00519181421163393</v>
+        <v>0.004400908057995227</v>
       </c>
       <c r="AJ4">
-        <v>96305.44923575831</v>
+        <v>113612.916564262</v>
       </c>
       <c r="AK4">
-        <v>72229.08692681874</v>
+        <v>85209.68742319649</v>
       </c>
       <c r="AL4">
-        <v>10651.21539038514</v>
+        <v>12559.07583716865</v>
       </c>
       <c r="AM4">
-        <v>722.2908692681874</v>
+        <v>852.0968742319649</v>
       </c>
       <c r="AN4">
-        <v>0.007222908692681874</v>
+        <v>0.008520968742319649</v>
       </c>
       <c r="AO4">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.1212587712243107</v>
+        <v>0.1238580141273271</v>
       </c>
       <c r="AR4">
-        <v>0.03883075594620033</v>
+        <v>0.03360236117180146</v>
       </c>
       <c r="AS4">
-        <v>0.07324930562112672</v>
+        <v>0.0689724191017307</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
         <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1255,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1267,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1279,70 +1285,70 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K5">
-        <v>0.1828580646515154</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.674548379147616</v>
+        <v>0.006632915408631916</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q5">
-        <v>0.7957145161628789</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>161.69</v>
+        <v>1.335085</v>
       </c>
       <c r="S5">
-        <v>162.6761351883347</v>
+        <v>1.340402553044849</v>
       </c>
       <c r="T5">
-        <v>162.7177781191311</v>
+        <v>1.337455457151159</v>
       </c>
       <c r="U5">
-        <v>161.69</v>
+        <v>1.335085</v>
       </c>
       <c r="V5">
-        <v>163.17</v>
+        <v>1.34697</v>
       </c>
       <c r="W5">
-        <v>162.6761351883347</v>
+        <v>1.340402553044849</v>
       </c>
       <c r="X5">
-        <v>159.815</v>
+        <v>1.320835</v>
       </c>
       <c r="Y5">
-        <v>0.006098925031447476</v>
+        <v>0.003982932206450226</v>
       </c>
       <c r="Z5">
-        <v>0.5259387671118606</v>
+        <v>0.3731616171823597</v>
       </c>
       <c r="AA5">
-        <v>0.006098925031447476</v>
+        <v>0.003982932206450226</v>
       </c>
       <c r="AB5">
-        <v>0.4375392258443707</v>
+        <v>0.4404254646519279</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3624607741556293</v>
+        <v>0.3595745353480721</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1351,58 +1357,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>397.8572580814395</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.0115962644566764</v>
+        <v>0.01067347771864707</v>
       </c>
       <c r="AJ5">
-        <v>43117.33333333317</v>
+        <v>46845.08771929848</v>
       </c>
       <c r="AK5">
-        <v>34309.08803156677</v>
+        <v>46845.08771929848</v>
       </c>
       <c r="AL5">
-        <v>212.1905376434336</v>
+        <v>35087.71929824579</v>
       </c>
       <c r="AM5">
-        <v>343.0908803156677</v>
+        <v>468.4508771929848</v>
       </c>
       <c r="AN5">
-        <v>0.003430908803156677</v>
+        <v>0.004684508771929849</v>
       </c>
       <c r="AO5">
-        <v>397.8572580814395</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0.003978572580814395</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>4.461251821490215</v>
+        <v>0.05502011473270348</v>
       </c>
       <c r="AR5">
-        <v>1.968786022706826</v>
+        <v>0.01610451818681127</v>
       </c>
       <c r="AS5">
-        <v>4.238092640281098</v>
+        <v>0.04306081693986744</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1410,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1422,82 +1428,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.01892761058849605</v>
+        <v>0.0917218933108295</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>1.3405</v>
+        <v>9.053789999999999</v>
       </c>
       <c r="S6">
-        <v>1.332260503155429</v>
+        <v>9.063783526442268</v>
       </c>
       <c r="T6">
-        <v>1.321686708528823</v>
+        <v>9.006812235229912</v>
       </c>
       <c r="U6">
-        <v>1.3405</v>
+        <v>9.053789999999999</v>
       </c>
       <c r="V6">
-        <v>1.3404</v>
+        <v>9.132709999999999</v>
       </c>
       <c r="W6">
-        <v>1.332260503155429</v>
+        <v>9.067370685</v>
       </c>
       <c r="X6">
-        <v>1.35475</v>
+        <v>8.962444999999999</v>
       </c>
       <c r="Y6">
-        <v>-0.00614658474044812</v>
+        <v>0.001103794813251581</v>
       </c>
       <c r="Z6">
-        <v>0.5782103048821575</v>
+        <v>0.148674640100717</v>
       </c>
       <c r="AA6">
-        <v>0.00614658474044812</v>
+        <v>0.001103794813251581</v>
       </c>
       <c r="AB6">
-        <v>0.4360268131952313</v>
+        <v>0.4221081577959771</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3639731868047687</v>
+        <v>0.3778918422040229</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1506,58 +1512,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.01063036180529648</v>
+        <v>0.0100891449879001</v>
       </c>
       <c r="AJ6">
-        <v>47035.08771929848</v>
+        <v>49558.21336690568</v>
       </c>
       <c r="AK6">
-        <v>35276.31578947385</v>
+        <v>49558.21336690568</v>
       </c>
       <c r="AL6">
-        <v>26315.78947368434</v>
+        <v>5473.753352673928</v>
       </c>
       <c r="AM6">
-        <v>352.7631578947385</v>
+        <v>495.5821336690568</v>
       </c>
       <c r="AN6">
-        <v>0.003527631578947385</v>
+        <v>0.004955821336690568</v>
       </c>
       <c r="AO6">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.05571813102099527</v>
+        <v>0.5211345406879005</v>
       </c>
       <c r="AR6">
-        <v>0.01709384460671275</v>
+        <v>0.1108530166897102</v>
       </c>
       <c r="AS6">
-        <v>0.04409015815685147</v>
+        <v>0.242584250763116</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1565,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1586,73 +1592,73 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K7">
-        <v>0.8095472615621123</v>
+        <v>0.5316513436573271</v>
       </c>
       <c r="L7">
-        <v>1.119724379993362</v>
+        <v>2.028489328445747</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>31</v>
+        <v>104</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.9523868153905281</v>
+        <v>0.8829128359143318</v>
       </c>
       <c r="R7">
-        <v>4.713</v>
+        <v>7.7208</v>
       </c>
       <c r="S7">
-        <v>4.670529366153491</v>
+        <v>7.677218248069876</v>
       </c>
       <c r="T7">
-        <v>4.65768168626357</v>
+        <v>7.66946659399335</v>
       </c>
       <c r="U7">
-        <v>4.713</v>
+        <v>7.7208</v>
       </c>
       <c r="V7">
-        <v>4.66261</v>
+        <v>7.663199999999999</v>
       </c>
       <c r="W7">
-        <v>4.670529366153491</v>
+        <v>7.677218248069876</v>
       </c>
       <c r="X7">
-        <v>4.766025</v>
+        <v>7.783725</v>
       </c>
       <c r="Y7">
-        <v>-0.009011379980163227</v>
+        <v>-0.005644719709113569</v>
       </c>
       <c r="Z7">
-        <v>0.8009549051675542</v>
+        <v>0.6925983620202456</v>
       </c>
       <c r="AA7">
-        <v>0.009011379980163227</v>
+        <v>0.005644719709113569</v>
       </c>
       <c r="AB7">
-        <v>0.4380065803345791</v>
+        <v>0.3986612300920681</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3619934196654209</v>
+        <v>0.4013387699079319</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1661,58 +1667,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>476.193407695264</v>
+        <v>441.4564179571659</v>
       </c>
       <c r="AI7">
-        <v>0.01125079567154671</v>
+        <v>0.00815006216972336</v>
       </c>
       <c r="AJ7">
-        <v>44441.30127298473</v>
+        <v>61349.22526817628</v>
       </c>
       <c r="AK7">
-        <v>42325.30939118895</v>
+        <v>54166.01846267271</v>
       </c>
       <c r="AL7">
-        <v>8980.545171056428</v>
+        <v>7015.596630229084</v>
       </c>
       <c r="AM7">
-        <v>423.2530939118895</v>
+        <v>541.6601846267271</v>
       </c>
       <c r="AN7">
-        <v>0.004232530939118895</v>
+        <v>0.005416601846267271</v>
       </c>
       <c r="AO7">
-        <v>476.1934076952641</v>
+        <v>441.4564179571659</v>
       </c>
       <c r="AP7">
-        <v>0.004761934076952641</v>
+        <v>0.004414564179571659</v>
       </c>
       <c r="AQ7">
-        <v>0.1937515325565687</v>
+        <v>0.3303417984186599</v>
       </c>
       <c r="AR7">
-        <v>0.09833204775404814</v>
+        <v>0.1157293391435874</v>
       </c>
       <c r="AS7">
-        <v>0.1886898387678253</v>
+        <v>0.1594821746275255</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
         <v>68</v>
       </c>
       <c r="AX7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1720,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1732,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1741,73 +1747,73 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K8">
-        <v>0.4306304101394878</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>1.92666694182994</v>
+        <v>1.678908595448022</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.857657602534872</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>7.7395</v>
+        <v>1.138205</v>
       </c>
       <c r="S8">
-        <v>7.649469136906649</v>
+        <v>1.12557489358866</v>
       </c>
       <c r="T8">
-        <v>7.598740140926337</v>
+        <v>1.115855435996774</v>
       </c>
       <c r="U8">
-        <v>7.7395</v>
+        <v>1.138205</v>
       </c>
       <c r="V8">
-        <v>7.655199999999999</v>
+        <v>1.12961</v>
       </c>
       <c r="W8">
-        <v>7.649469136906649</v>
+        <v>1.12557489358866</v>
       </c>
       <c r="X8">
-        <v>7.802424999999999</v>
+        <v>1.151205</v>
       </c>
       <c r="Y8">
-        <v>-0.01163264591941988</v>
+        <v>-0.01109651285255321</v>
       </c>
       <c r="Z8">
-        <v>1.430764610144617</v>
+        <v>0.971546647026178</v>
       </c>
       <c r="AA8">
-        <v>0.01163264591941988</v>
+        <v>0.01109651285255321</v>
       </c>
       <c r="AB8">
-        <v>0.4001225554579798</v>
+        <v>0.4183416071924016</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3998774445420203</v>
+        <v>0.3816583928075984</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1816,58 +1822,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>428.828801267436</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.008130370178952144</v>
+        <v>0.01142149261336931</v>
       </c>
       <c r="AJ8">
-        <v>61497.81485895896</v>
+        <v>43777.11538461535</v>
       </c>
       <c r="AK8">
-        <v>52744.06845306817</v>
+        <v>43777.11538461535</v>
       </c>
       <c r="AL8">
-        <v>6814.919368572669</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM8">
-        <v>527.4406845306817</v>
+        <v>437.7711538461535</v>
       </c>
       <c r="AN8">
-        <v>0.005274406845306816</v>
+        <v>0.004377711538461535</v>
       </c>
       <c r="AO8">
-        <v>428.828801267436</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>0.00428828801267436</v>
+        <v>0.005</v>
       </c>
       <c r="AQ8">
-        <v>0.3228958749537663</v>
+        <v>0.04782710656256262</v>
       </c>
       <c r="AR8">
-        <v>0.1146782077071728</v>
+        <v>0.01599855892161834</v>
       </c>
       <c r="AS8">
-        <v>0.1724192152158853</v>
+        <v>0.03159032711410843</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
         <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1875,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1887,7 +1893,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1896,73 +1902,73 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K9">
-        <v>0.096826474372876</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1.4406523881995</v>
+        <v>1.262735121503479</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.774206618593219</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>0.695</v>
+        <v>4.69175</v>
       </c>
       <c r="S9">
-        <v>0.6849328448882432</v>
+        <v>4.638430345536857</v>
       </c>
       <c r="T9">
-        <v>0.6797108621522074</v>
+        <v>4.622676531550846</v>
       </c>
       <c r="U9">
-        <v>0.695</v>
+        <v>4.69175</v>
       </c>
       <c r="V9">
-        <v>0.6856999999999999</v>
+        <v>4.62815</v>
       </c>
       <c r="W9">
-        <v>0.6849328448882432</v>
+        <v>4.638430345536857</v>
       </c>
       <c r="X9">
-        <v>0.704275</v>
+        <v>4.744775</v>
       </c>
       <c r="Y9">
-        <v>-0.01448511526871469</v>
+        <v>-0.01136455575491927</v>
       </c>
       <c r="Z9">
-        <v>1.085407559219045</v>
+        <v>1.005556896994678</v>
       </c>
       <c r="AA9">
-        <v>0.01448511526871469</v>
+        <v>0.01136455575491927</v>
       </c>
       <c r="AB9">
-        <v>0.4386533051205504</v>
+        <v>0.4457236733537884</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3613466948794496</v>
+        <v>0.3542763266462116</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1971,58 +1977,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>387.1033092966095</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.01334532374100728</v>
+        <v>0.01130175307720992</v>
       </c>
       <c r="AJ9">
-        <v>37466.30727762778</v>
+        <v>44240.92409240953</v>
       </c>
       <c r="AK9">
-        <v>29006.66306858672</v>
+        <v>44240.92409240953</v>
       </c>
       <c r="AL9">
-        <v>41736.20585408161</v>
+        <v>9429.51438000949</v>
       </c>
       <c r="AM9">
-        <v>290.0666306858672</v>
+        <v>442.4092409240953</v>
       </c>
       <c r="AN9">
-        <v>0.002900666306858672</v>
+        <v>0.004424092409240953</v>
       </c>
       <c r="AO9">
-        <v>387.1033092966095</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP9">
-        <v>0.003871033092966095</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ9">
-        <v>0.03016306890096576</v>
+        <v>0.1924677845227944</v>
       </c>
       <c r="AR9">
-        <v>0.01479589192625276</v>
+        <v>0.09944254259270892</v>
       </c>
       <c r="AS9">
-        <v>0.03243147834682247</v>
+        <v>0.1895671244776326</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
         <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2030,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2042,7 +2048,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2051,73 +2057,73 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K10">
-        <v>0.8754661615499069</v>
+        <v>0.324162191047089</v>
       </c>
       <c r="L10">
-        <v>1.540624850535451</v>
+        <v>1.640007613092572</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q10">
-        <v>0.9688665403874768</v>
+        <v>0.8310405477617723</v>
       </c>
       <c r="R10">
-        <v>1.1413</v>
+        <v>0.691625</v>
       </c>
       <c r="S10">
-        <v>1.12267681316296</v>
+        <v>0.681082946713269</v>
       </c>
       <c r="T10">
-        <v>1.1109395813678</v>
+        <v>0.6755594628739823</v>
       </c>
       <c r="U10">
-        <v>1.1413</v>
+        <v>0.691625</v>
       </c>
       <c r="V10">
-        <v>1.1258</v>
+        <v>0.6821500000000001</v>
       </c>
       <c r="W10">
-        <v>1.12267681316296</v>
+        <v>0.681082946713269</v>
       </c>
       <c r="X10">
-        <v>1.1543</v>
+        <v>0.7009000000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.01631752110491574</v>
+        <v>-0.01524244104352948</v>
       </c>
       <c r="Z10">
-        <v>1.432552833618487</v>
+        <v>1.136609518785014</v>
       </c>
       <c r="AA10">
-        <v>0.01631752110491574</v>
+        <v>0.01524244104352948</v>
       </c>
       <c r="AB10">
-        <v>0.4187760110307887</v>
+        <v>0.4494403460740298</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3812239889692113</v>
+        <v>0.3505596539259703</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2126,58 +2132,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>484.4332701937384</v>
+        <v>415.5202738808861</v>
       </c>
       <c r="AI10">
-        <v>0.01139051958293175</v>
+        <v>0.01341044641243457</v>
       </c>
       <c r="AJ10">
-        <v>43896.15384615381</v>
+        <v>37284.36657681916</v>
       </c>
       <c r="AK10">
-        <v>42529.51471323947</v>
+        <v>30984.82042295051</v>
       </c>
       <c r="AL10">
-        <v>37264.09770721061</v>
+        <v>44800.02952893622</v>
       </c>
       <c r="AM10">
-        <v>425.2951471323947</v>
+        <v>309.8482042295051</v>
       </c>
       <c r="AN10">
-        <v>0.004252951471323946</v>
+        <v>0.003098482042295051</v>
       </c>
       <c r="AO10">
-        <v>484.4332701937384</v>
+        <v>415.5202738808862</v>
       </c>
       <c r="AP10">
-        <v>0.004844332701937384</v>
+        <v>0.004155202738808862</v>
       </c>
       <c r="AQ10">
-        <v>0.04626933416451879</v>
+        <v>0.03097697848846228</v>
       </c>
       <c r="AR10">
-        <v>0.01600890444415493</v>
+        <v>0.01464117461699301</v>
       </c>
       <c r="AS10">
-        <v>0.03465548428545468</v>
+        <v>0.03219924351504305</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
         <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2185,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2206,73 +2212,73 @@
         <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.370828324607074</v>
+        <v>1.52672893408051</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4121.08</v>
+        <v>3992.86</v>
       </c>
       <c r="S11">
-        <v>4017.65405096534</v>
+        <v>3817.326102609168</v>
       </c>
       <c r="T11">
-        <v>3962.302172363497</v>
+        <v>3724.746116701021</v>
       </c>
       <c r="U11">
-        <v>4121.08</v>
+        <v>3992.86</v>
       </c>
       <c r="V11">
-        <v>4022.84</v>
+        <v>3825.46</v>
       </c>
       <c r="W11">
-        <v>4017.65405096534</v>
+        <v>3817.326102609168</v>
       </c>
       <c r="X11">
-        <v>4265.2775</v>
+        <v>4138.8175</v>
       </c>
       <c r="Y11">
-        <v>-0.02509680691339657</v>
+        <v>-0.0439619464220715</v>
       </c>
       <c r="Z11">
-        <v>0.7172520261076673</v>
+        <v>1.202637051133601</v>
       </c>
       <c r="AA11">
-        <v>0.02509680691339657</v>
+        <v>0.0439619464220715</v>
       </c>
       <c r="AB11">
-        <v>0.4102220050540104</v>
+        <v>0.4131892846123006</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3897779949459895</v>
+        <v>0.3868107153876993</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2284,22 +2290,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.0349902210100265</v>
+        <v>0.03655462500563503</v>
       </c>
       <c r="AJ11">
-        <v>14289.7068257078</v>
+        <v>13678.15973827999</v>
       </c>
       <c r="AK11">
-        <v>10717.28011928085</v>
+        <v>10258.61980370999</v>
       </c>
       <c r="AL11">
-        <v>2.60059987170374</v>
+        <v>2.569241046194956</v>
       </c>
       <c r="AM11">
-        <v>107.1728011928085</v>
+        <v>102.5861980370999</v>
       </c>
       <c r="AN11">
-        <v>0.001071728011928085</v>
+        <v>0.001025861980370999</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2308,31 +2314,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>586.1797895357679</v>
+        <v>548.2303773026795</v>
       </c>
       <c r="AR11">
-        <v>293.4996349044342</v>
+        <v>299.913713421236</v>
       </c>
       <c r="AS11">
-        <v>463.0307683878226</v>
+        <v>412.3776775534004</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03584234839127775</v>
+        <v>0.04070865284495344</v>
       </c>
       <c r="AV11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
         <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
   <si>
     <t>Pair</t>
   </si>
@@ -169,30 +169,30 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -214,9 +214,6 @@
     <t>LOW</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -235,52 +232,43 @@
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=5.203,naive=1.806,drift4=2.731; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03978,naive=0.01375,drift4=0.01995; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1094,naive=0.03241,drift4=0.05479; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05574,naive=0.01743,drift4=0.03289; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4524,naive=0.1124,drift4=0.1962; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.331,naive=0.09223,drift4=0.1138; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.04916,naive=0.01362,drift4=0.0213; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1819,naive=0.09163,drift4=0.1303; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02889,naive=0.01385,drift4=0.02136; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=712.1,naive=251.1,drift4=317.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03919,naive=0.0135,drift4=0.01999; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05637,naive=0.01759,drift4=0.03266; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1068,naive=0.02967,drift4=0.05316; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4383,naive=0.1127,drift4=0.195; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.171,naive=1.753,drift4=2.566; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3316,naive=0.09121,drift4=0.11; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.177,naive=0.08997,drift4=0.128; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05119,naive=0.0133,drift4=0.02026; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02941,naive=0.01354,drift4=0.02117; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=721.4,naive=246.2,drift4=285.9; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -808,7 +796,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -829,64 +817,73 @@
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K2">
-        <v>0.1691622367477087</v>
+        <v>0.8177768968945478</v>
       </c>
       <c r="L2">
-        <v>1.667529779394976</v>
+        <v>1.614412087797669</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.954444224223637</v>
       </c>
       <c r="R2">
-        <v>162.403</v>
+        <v>0.80901</v>
       </c>
       <c r="S2">
-        <v>162.3010553653823</v>
+        <v>0.814484119192829</v>
       </c>
       <c r="T2">
-        <v>161.1869684427783</v>
+        <v>0.8201073531217524</v>
       </c>
       <c r="U2">
-        <v>162.403</v>
+        <v>0.80901</v>
       </c>
       <c r="V2">
-        <v>163.526</v>
+        <v>0.81102</v>
+      </c>
+      <c r="W2">
+        <v>0.814484119192829</v>
+      </c>
+      <c r="X2">
+        <v>0.799335</v>
       </c>
       <c r="Y2">
-        <v>-0.0006277263019629864</v>
+        <v>0.00676644193870166</v>
+      </c>
+      <c r="Z2">
+        <v>0.5658004333673406</v>
       </c>
       <c r="AA2">
-        <v>0.0006277263019629864</v>
+        <v>0.00676644193870166</v>
       </c>
       <c r="AB2">
-        <v>0.4276747064524046</v>
+        <v>0.4254395246922723</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3723252935475955</v>
+        <v>0.3745604753077277</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -895,55 +892,58 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>477.2221121118185</v>
+      </c>
+      <c r="AI2">
+        <v>0.01195906107464681</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>41809.30232558132</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>39904.64712347097</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>49325.28290561423</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>399.0464712347097</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.003990464712347097</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>477.2221121118185</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.004772221121118185</v>
       </c>
       <c r="AQ2">
-        <v>4.714049707656474</v>
+        <v>0.03799304440561113</v>
       </c>
       <c r="AR2">
-        <v>2.049990708944266</v>
+        <v>0.01452322446874832</v>
       </c>
       <c r="AS2">
-        <v>3.964277884836795</v>
+        <v>0.02457009560752225</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AY2" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,79 +966,79 @@
         <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K3">
-        <v>0.9944810556946149</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1.74281019230603</v>
+        <v>0.015584986259377</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
         <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>0.9986202639236537</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.814715</v>
+        <v>1.33951</v>
       </c>
       <c r="S3">
-        <v>0.8224709972108237</v>
+        <v>1.346717449414908</v>
       </c>
       <c r="T3">
-        <v>0.8261669757900578</v>
+        <v>1.342514775958193</v>
       </c>
       <c r="U3">
-        <v>0.814715</v>
+        <v>1.33951</v>
       </c>
       <c r="V3">
-        <v>0.8224299999999999</v>
+        <v>1.35582</v>
       </c>
       <c r="W3">
-        <v>0.8224709972108237</v>
+        <v>1.346717449414908</v>
       </c>
       <c r="X3">
-        <v>0.80504</v>
+        <v>1.32526</v>
       </c>
       <c r="Y3">
-        <v>0.009519890036176776</v>
+        <v>0.005380661148410925</v>
       </c>
       <c r="Z3">
-        <v>0.8016534584830748</v>
+        <v>0.5057859238531898</v>
       </c>
       <c r="AA3">
-        <v>0.009519890036176776</v>
+        <v>0.005380661148410925</v>
       </c>
       <c r="AB3">
-        <v>0.4238714136275828</v>
+        <v>0.4389667221491461</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3761285863724171</v>
+        <v>0.3610332778508539</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1047,58 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>499.3101319618268</v>
+        <v>500</v>
       </c>
       <c r="AI3">
-        <v>0.01187531836286311</v>
+        <v>0.01063821845301635</v>
       </c>
       <c r="AJ3">
-        <v>42104.13436692499</v>
+        <v>47000.35087719321</v>
       </c>
       <c r="AK3">
-        <v>42046.04177377561</v>
+        <v>47000.35087719321</v>
       </c>
       <c r="AL3">
-        <v>51608.28237331535</v>
+        <v>35087.71929824579</v>
       </c>
       <c r="AM3">
-        <v>420.4604177377561</v>
+        <v>470.0035087719321</v>
       </c>
       <c r="AN3">
-        <v>0.00420460417737756</v>
+        <v>0.004700035087719321</v>
       </c>
       <c r="AO3">
-        <v>499.3101319618269</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0.004993101319618269</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.03914827944028984</v>
+        <v>0.0535667053939405</v>
       </c>
       <c r="AR3">
-        <v>0.0155265768355269</v>
+        <v>0.01537450901426796</v>
       </c>
       <c r="AS3">
-        <v>0.02759320396020567</v>
+        <v>0.0400915936294372</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY3" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1121,79 +1121,79 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.349964848679059</v>
+        <v>0.6163803082298828</v>
       </c>
       <c r="M4">
+        <v>6</v>
+      </c>
+      <c r="N4">
         <v>1</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>6.78471</v>
+        <v>6.7719</v>
       </c>
       <c r="S4">
-        <v>6.829498327365241</v>
+        <v>6.799173143544933</v>
       </c>
       <c r="T4">
-        <v>6.887526430890647</v>
+        <v>6.844652671650291</v>
       </c>
       <c r="U4">
-        <v>6.78471</v>
+        <v>6.7719</v>
       </c>
       <c r="V4">
-        <v>6.786719999999999</v>
+        <v>6.761099999999999</v>
       </c>
       <c r="W4">
-        <v>6.829498327365241</v>
+        <v>6.799173143544933</v>
       </c>
       <c r="X4">
-        <v>6.754851115089838</v>
+        <v>6.7421</v>
       </c>
       <c r="Y4">
-        <v>0.00660136208699284</v>
+        <v>0.004027399037926339</v>
       </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>0.9152061592259507</v>
       </c>
       <c r="AA4">
-        <v>0.00660136208699284</v>
+        <v>0.004027399037926339</v>
       </c>
       <c r="AB4">
-        <v>0.4283489355166407</v>
+        <v>0.4298263937656794</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3716510644833593</v>
+        <v>0.3701736062343207</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1202,58 +1202,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.004400908057995227</v>
+        <v>0.004400537515320671</v>
       </c>
       <c r="AJ4">
-        <v>113612.916564262</v>
+        <v>113622.4832214763</v>
       </c>
       <c r="AK4">
-        <v>85209.68742319649</v>
+        <v>113622.4832214763</v>
       </c>
       <c r="AL4">
-        <v>12559.07583716865</v>
+        <v>16778.52348993286</v>
       </c>
       <c r="AM4">
-        <v>852.0968742319649</v>
+        <v>1136.224832214763</v>
       </c>
       <c r="AN4">
-        <v>0.008520968742319649</v>
+        <v>0.01136224832214763</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.1238580141273271</v>
+        <v>0.1170480546303424</v>
       </c>
       <c r="AR4">
-        <v>0.03360236117180146</v>
+        <v>0.02728800437534951</v>
       </c>
       <c r="AS4">
-        <v>0.0689724191017307</v>
+        <v>0.05836718356271586</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY4" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,82 +1273,82 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.006632915408631916</v>
+        <v>0.1053328644719332</v>
       </c>
       <c r="M5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>1.335085</v>
+        <v>9.068239999999999</v>
       </c>
       <c r="S5">
-        <v>1.340402553044849</v>
+        <v>9.083790868978152</v>
       </c>
       <c r="T5">
-        <v>1.337455457151159</v>
+        <v>9.021801501209344</v>
       </c>
       <c r="U5">
-        <v>1.335085</v>
+        <v>9.068239999999999</v>
       </c>
       <c r="V5">
-        <v>1.34697</v>
+        <v>9.16161</v>
       </c>
       <c r="W5">
-        <v>1.340402553044849</v>
+        <v>9.083790868978152</v>
       </c>
       <c r="X5">
-        <v>1.320835</v>
+        <v>8.976894999999999</v>
       </c>
       <c r="Y5">
-        <v>0.003982932206450226</v>
+        <v>0.001714871791897074</v>
       </c>
       <c r="Z5">
-        <v>0.3731616171823597</v>
+        <v>0.1702432424123129</v>
       </c>
       <c r="AA5">
-        <v>0.003982932206450226</v>
+        <v>0.001714871791897074</v>
       </c>
       <c r="AB5">
-        <v>0.4404254646519279</v>
+        <v>0.4230438888440519</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3595745353480721</v>
+        <v>0.3769561111559481</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1360,22 +1360,22 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01067347771864707</v>
+        <v>0.01007306820287068</v>
       </c>
       <c r="AJ5">
-        <v>46845.08771929848</v>
+        <v>49637.30910285182</v>
       </c>
       <c r="AK5">
-        <v>46845.08771929848</v>
+        <v>49637.30910285182</v>
       </c>
       <c r="AL5">
-        <v>35087.71929824579</v>
+        <v>5473.753352673928</v>
       </c>
       <c r="AM5">
-        <v>468.4508771929848</v>
+        <v>496.3730910285182</v>
       </c>
       <c r="AN5">
-        <v>0.004684508771929849</v>
+        <v>0.004963730910285182</v>
       </c>
       <c r="AO5">
         <v>500</v>
@@ -1384,31 +1384,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.05502011473270348</v>
+        <v>0.5080854227947751</v>
       </c>
       <c r="AR5">
-        <v>0.01610451818681127</v>
+        <v>0.1058910979362605</v>
       </c>
       <c r="AS5">
-        <v>0.04306081693986744</v>
+        <v>0.234780307217255</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY5" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,82 +1428,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J6" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.1367858210383857</v>
       </c>
       <c r="L6">
-        <v>0.0917218933108295</v>
+        <v>1.64378184550154</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
         <v>72</v>
       </c>
-      <c r="P6" t="s">
-        <v>75</v>
-      </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.7841964552595965</v>
       </c>
       <c r="R6">
-        <v>9.053789999999999</v>
+        <v>162.2315</v>
       </c>
       <c r="S6">
-        <v>9.063783526442268</v>
+        <v>162.4473488363326</v>
       </c>
       <c r="T6">
-        <v>9.006812235229912</v>
+        <v>161.8954372764127</v>
       </c>
       <c r="U6">
-        <v>9.053789999999999</v>
+        <v>162.2315</v>
       </c>
       <c r="V6">
-        <v>9.132709999999999</v>
+        <v>163.183</v>
       </c>
       <c r="W6">
-        <v>9.067370685</v>
+        <v>162.47484725</v>
       </c>
       <c r="X6">
-        <v>8.962444999999999</v>
+        <v>160.3565</v>
       </c>
       <c r="Y6">
-        <v>0.001103794813251581</v>
+        <v>0.00133049892488563</v>
       </c>
       <c r="Z6">
-        <v>0.148674640100717</v>
+        <v>0.1297851999999995</v>
       </c>
       <c r="AA6">
-        <v>0.001103794813251581</v>
+        <v>0.00133049892488563</v>
       </c>
       <c r="AB6">
-        <v>0.4221081577959771</v>
+        <v>0.4235530849697329</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3778918422040229</v>
+        <v>0.3764469150302671</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,58 +1512,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>392.0982276297983</v>
       </c>
       <c r="AI6">
-        <v>0.0100891449879001</v>
+        <v>0.01155755818074792</v>
       </c>
       <c r="AJ6">
-        <v>49558.21336690568</v>
+        <v>43261.73333333318</v>
       </c>
       <c r="AK6">
-        <v>49558.21336690568</v>
+        <v>33925.6979283858</v>
       </c>
       <c r="AL6">
-        <v>5473.753352673928</v>
+        <v>209.1190547358916</v>
       </c>
       <c r="AM6">
-        <v>495.5821336690568</v>
+        <v>339.256979283858</v>
       </c>
       <c r="AN6">
-        <v>0.004955821336690568</v>
+        <v>0.00339256979283858</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>392.0982276297983</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.003920982276297984</v>
       </c>
       <c r="AQ6">
-        <v>0.5211345406879005</v>
+        <v>4.596803088712453</v>
       </c>
       <c r="AR6">
-        <v>0.1108530166897102</v>
+        <v>1.969724287287069</v>
       </c>
       <c r="AS6">
-        <v>0.242584250763116</v>
+        <v>3.565161506553571</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY6" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1586,79 +1586,79 @@
         <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K7">
-        <v>0.5316513436573271</v>
+        <v>0.4204862932025254</v>
       </c>
       <c r="L7">
-        <v>2.028489328445747</v>
+        <v>1.92283086552391</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q7">
-        <v>0.8829128359143318</v>
+        <v>0.8551215733006313</v>
       </c>
       <c r="R7">
-        <v>7.7208</v>
+        <v>7.734</v>
       </c>
       <c r="S7">
-        <v>7.677218248069876</v>
+        <v>7.698164867752628</v>
       </c>
       <c r="T7">
-        <v>7.66946659399335</v>
+        <v>7.688804536966142</v>
       </c>
       <c r="U7">
-        <v>7.7208</v>
+        <v>7.734</v>
       </c>
       <c r="V7">
-        <v>7.663199999999999</v>
+        <v>7.6896</v>
       </c>
       <c r="W7">
-        <v>7.677218248069876</v>
+        <v>7.698164867752628</v>
       </c>
       <c r="X7">
-        <v>7.783725</v>
+        <v>7.796925</v>
       </c>
       <c r="Y7">
-        <v>-0.005644719709113569</v>
+        <v>-0.004633453872171163</v>
       </c>
       <c r="Z7">
-        <v>0.6925983620202456</v>
+        <v>0.5694895867679255</v>
       </c>
       <c r="AA7">
-        <v>0.005644719709113569</v>
+        <v>0.004633453872171163</v>
       </c>
       <c r="AB7">
-        <v>0.3986612300920681</v>
+        <v>0.3961620263400052</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.4013387699079319</v>
+        <v>0.4038379736599947</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,58 +1667,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>441.4564179571659</v>
+        <v>427.5607866503157</v>
       </c>
       <c r="AI7">
-        <v>0.00815006216972336</v>
+        <v>0.008136152055857269</v>
       </c>
       <c r="AJ7">
-        <v>61349.22526817628</v>
+        <v>61454.11203814053</v>
       </c>
       <c r="AK7">
-        <v>54166.01846267271</v>
+        <v>52550.736971848</v>
       </c>
       <c r="AL7">
-        <v>7015.596630229084</v>
+        <v>6794.768162897336</v>
       </c>
       <c r="AM7">
-        <v>541.6601846267271</v>
+        <v>525.5073697184799</v>
       </c>
       <c r="AN7">
-        <v>0.005416601846267271</v>
+        <v>0.005255073697184799</v>
       </c>
       <c r="AO7">
-        <v>441.4564179571659</v>
+        <v>427.5607866503157</v>
       </c>
       <c r="AP7">
-        <v>0.004414564179571659</v>
+        <v>0.004275607866503157</v>
       </c>
       <c r="AQ7">
-        <v>0.3303417984186599</v>
+        <v>0.3235471939611005</v>
       </c>
       <c r="AR7">
-        <v>0.1157293391435874</v>
+        <v>0.1094781003496964</v>
       </c>
       <c r="AS7">
-        <v>0.1594821746275255</v>
+        <v>0.1464069388144718</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY7" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1741,79 +1741,79 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.6913151086580912</v>
       </c>
       <c r="L8">
-        <v>1.678908595448022</v>
+        <v>1.080685084071596</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.9228287771645228</v>
       </c>
       <c r="R8">
-        <v>1.138205</v>
+        <v>4.72342</v>
       </c>
       <c r="S8">
-        <v>1.12557489358866</v>
+        <v>4.682026549676137</v>
       </c>
       <c r="T8">
-        <v>1.115855435996774</v>
+        <v>4.655984014274864</v>
       </c>
       <c r="U8">
-        <v>1.138205</v>
+        <v>4.72342</v>
       </c>
       <c r="V8">
-        <v>1.12961</v>
+        <v>4.69149</v>
       </c>
       <c r="W8">
-        <v>1.12557489358866</v>
+        <v>4.682026549676137</v>
       </c>
       <c r="X8">
-        <v>1.151205</v>
+        <v>4.776445</v>
       </c>
       <c r="Y8">
-        <v>-0.01109651285255321</v>
+        <v>-0.008763449010222017</v>
       </c>
       <c r="Z8">
-        <v>0.971546647026178</v>
+        <v>0.7806402701341471</v>
       </c>
       <c r="AA8">
-        <v>0.01109651285255321</v>
+        <v>0.008763449010222017</v>
       </c>
       <c r="AB8">
-        <v>0.4183416071924016</v>
+        <v>0.4463881230212595</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3816583928075984</v>
+        <v>0.3536118769787406</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,58 +1822,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>461.4143885822614</v>
       </c>
       <c r="AI8">
-        <v>0.01142149261336931</v>
+        <v>0.01122597609359313</v>
       </c>
       <c r="AJ8">
-        <v>43777.11538461535</v>
+        <v>44539.55681282443</v>
       </c>
       <c r="AK8">
-        <v>43777.11538461535</v>
+        <v>41102.38474902856</v>
       </c>
       <c r="AL8">
-        <v>38461.53846153843</v>
+        <v>8701.827224559442</v>
       </c>
       <c r="AM8">
-        <v>437.7711538461535</v>
+        <v>411.0238474902856</v>
       </c>
       <c r="AN8">
-        <v>0.004377711538461535</v>
+        <v>0.004110238474902856</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>461.4143885822614</v>
       </c>
       <c r="AP8">
-        <v>0.005</v>
+        <v>0.004614143885822613</v>
       </c>
       <c r="AQ8">
-        <v>0.04782710656256262</v>
+        <v>0.1839974079376004</v>
       </c>
       <c r="AR8">
-        <v>0.01599855892161834</v>
+        <v>0.09306750440257795</v>
       </c>
       <c r="AS8">
-        <v>0.03159032711410843</v>
+        <v>0.175609089366169</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY8" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1896,79 +1896,79 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.926654347584107</v>
       </c>
       <c r="L9">
-        <v>1.262735121503479</v>
+        <v>1.567338617969237</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.9816635868960267</v>
       </c>
       <c r="R9">
-        <v>4.69175</v>
+        <v>1.14252</v>
       </c>
       <c r="S9">
-        <v>4.638430345536857</v>
+        <v>1.13226781225161</v>
       </c>
       <c r="T9">
-        <v>4.622676531550846</v>
+        <v>1.121705262977535</v>
       </c>
       <c r="U9">
-        <v>4.69175</v>
+        <v>1.14252</v>
       </c>
       <c r="V9">
-        <v>4.62815</v>
+        <v>1.13824</v>
       </c>
       <c r="W9">
-        <v>4.638430345536857</v>
+        <v>1.13226781225161</v>
       </c>
       <c r="X9">
-        <v>4.744775</v>
+        <v>1.15552</v>
       </c>
       <c r="Y9">
-        <v>-0.01136455575491927</v>
+        <v>-0.008973311406706506</v>
       </c>
       <c r="Z9">
-        <v>1.005556896994678</v>
+        <v>0.7886298267992545</v>
       </c>
       <c r="AA9">
-        <v>0.01136455575491927</v>
+        <v>0.008973311406706506</v>
       </c>
       <c r="AB9">
-        <v>0.4457236733537884</v>
+        <v>0.4129601661709609</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3542763266462116</v>
+        <v>0.3870398338290392</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1977,58 +1977,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>490.8317934480133</v>
       </c>
       <c r="AI9">
-        <v>0.01130175307720992</v>
+        <v>0.01137835661520149</v>
       </c>
       <c r="AJ9">
-        <v>44240.92409240953</v>
+        <v>43943.07692307689</v>
       </c>
       <c r="AK9">
-        <v>44240.92409240953</v>
+        <v>43137.31851155567</v>
       </c>
       <c r="AL9">
-        <v>9429.51438000949</v>
+        <v>37756.2918036933</v>
       </c>
       <c r="AM9">
-        <v>442.4092409240953</v>
+        <v>431.3731851155567</v>
       </c>
       <c r="AN9">
-        <v>0.004424092409240953</v>
+        <v>0.004313731851155567</v>
       </c>
       <c r="AO9">
-        <v>500.0000000000001</v>
+        <v>490.8317934480133</v>
       </c>
       <c r="AP9">
-        <v>0.005000000000000001</v>
+        <v>0.004908317934480133</v>
       </c>
       <c r="AQ9">
-        <v>0.1924677845227944</v>
+        <v>0.04737871158390136</v>
       </c>
       <c r="AR9">
-        <v>0.09944254259270892</v>
+        <v>0.01494999740709829</v>
       </c>
       <c r="AS9">
-        <v>0.1895671244776326</v>
+        <v>0.02771872273946265</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY9" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2051,79 +2051,79 @@
         <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K10">
-        <v>0.324162191047089</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1.640007613092572</v>
+        <v>1.286430796385193</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q10">
-        <v>0.8310405477617723</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>0.691625</v>
+        <v>0.69797</v>
       </c>
       <c r="S10">
-        <v>0.681082946713269</v>
+        <v>0.6903856822235885</v>
       </c>
       <c r="T10">
-        <v>0.6755594628739823</v>
+        <v>0.6834983353737917</v>
       </c>
       <c r="U10">
-        <v>0.691625</v>
+        <v>0.69797</v>
       </c>
       <c r="V10">
-        <v>0.6821500000000001</v>
+        <v>0.69484</v>
       </c>
       <c r="W10">
-        <v>0.681082946713269</v>
+        <v>0.6903856822235885</v>
       </c>
       <c r="X10">
-        <v>0.7009000000000001</v>
+        <v>0.707245</v>
       </c>
       <c r="Y10">
-        <v>-0.01524244104352948</v>
+        <v>-0.01086625181083921</v>
       </c>
       <c r="Z10">
-        <v>1.136609518785014</v>
+        <v>0.8177162023085059</v>
       </c>
       <c r="AA10">
-        <v>0.01524244104352948</v>
+        <v>0.01086625181083921</v>
       </c>
       <c r="AB10">
-        <v>0.4494403460740298</v>
+        <v>0.4479340505865345</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3505596539259703</v>
+        <v>0.3520659494134656</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2132,58 +2132,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>415.5202738808861</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01341044641243457</v>
+        <v>0.01328853675659421</v>
       </c>
       <c r="AJ10">
-        <v>37284.36657681916</v>
+        <v>37626.41509433938</v>
       </c>
       <c r="AK10">
-        <v>30984.82042295051</v>
+        <v>28219.81132075453</v>
       </c>
       <c r="AL10">
-        <v>44800.02952893622</v>
+        <v>40431.26684636092</v>
       </c>
       <c r="AM10">
-        <v>309.8482042295051</v>
+        <v>282.1981132075453</v>
       </c>
       <c r="AN10">
-        <v>0.003098482042295051</v>
+        <v>0.002821981132075453</v>
       </c>
       <c r="AO10">
-        <v>415.5202738808862</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.004155202738808862</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.03097697848846228</v>
+        <v>0.03053222523278472</v>
       </c>
       <c r="AR10">
-        <v>0.01464117461699301</v>
+        <v>0.01329104206107144</v>
       </c>
       <c r="AS10">
-        <v>0.03219924351504305</v>
+        <v>0.02918164497882425</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY10" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2206,79 +2206,79 @@
         <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.52672893408051</v>
+        <v>1.601694257357708</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>3992.86</v>
+        <v>4052.81</v>
       </c>
       <c r="S11">
-        <v>3817.326102609168</v>
+        <v>3893.615226325778</v>
       </c>
       <c r="T11">
-        <v>3724.746116701021</v>
+        <v>3764.089093326046</v>
       </c>
       <c r="U11">
-        <v>3992.86</v>
+        <v>4052.81</v>
       </c>
       <c r="V11">
-        <v>3825.46</v>
+        <v>3945.36</v>
       </c>
       <c r="W11">
-        <v>3817.326102609168</v>
+        <v>3893.615226325778</v>
       </c>
       <c r="X11">
-        <v>4138.8175</v>
+        <v>4197.0075</v>
       </c>
       <c r="Y11">
-        <v>-0.0439619464220715</v>
+        <v>-0.03928009792569161</v>
       </c>
       <c r="Z11">
-        <v>1.202637051133601</v>
+        <v>1.104005087981569</v>
       </c>
       <c r="AA11">
-        <v>0.0439619464220715</v>
+        <v>0.03928009792569161</v>
       </c>
       <c r="AB11">
-        <v>0.4131892846123006</v>
+        <v>0.4040073226198792</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3868107153876993</v>
+        <v>0.3959926773801208</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2290,22 +2290,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03655462500563503</v>
+        <v>0.03557963487062063</v>
       </c>
       <c r="AJ11">
-        <v>13678.15973827999</v>
+        <v>14052.98288805284</v>
       </c>
       <c r="AK11">
-        <v>10258.61980370999</v>
+        <v>10539.73716603963</v>
       </c>
       <c r="AL11">
-        <v>2.569241046194956</v>
+        <v>2.60059987170374</v>
       </c>
       <c r="AM11">
-        <v>102.5861980370999</v>
+        <v>105.3973716603963</v>
       </c>
       <c r="AN11">
-        <v>0.001025861980370999</v>
+        <v>0.001053973716603963</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2314,31 +2314,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>548.2303773026795</v>
+        <v>545.3442646528041</v>
       </c>
       <c r="AR11">
-        <v>299.913713421236</v>
+        <v>281.6278273267829</v>
       </c>
       <c r="AS11">
-        <v>412.3776775534004</v>
+        <v>320.6668007000793</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04070865284495344</v>
+        <v>0.04596404769726044</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY11" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,18 +169,18 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
@@ -238,34 +238,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03919,naive=0.0135,drift4=0.01999; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05637,naive=0.01759,drift4=0.03266; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1068,naive=0.02967,drift4=0.05316; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4383,naive=0.1127,drift4=0.195; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.171,naive=1.753,drift4=2.566; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3316,naive=0.09121,drift4=0.11; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.177,naive=0.08997,drift4=0.128; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05119,naive=0.0133,drift4=0.02026; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02941,naive=0.01354,drift4=0.02117; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=721.4,naive=246.2,drift4=285.9; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05862,naive=0.02092,drift4=0.03593; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4467,naive=0.1313,drift4=0.2132; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03892,naive=0.01369,drift4=0.02088; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1075,naive=0.03096,drift4=0.0545; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.141,naive=1.744,drift4=2.585; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3408,naive=0.09123,drift4=0.1147; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1762,naive=0.09161,drift4=0.1324; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.05212,naive=0.01371,drift4=0.02134; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02934,naive=0.01383,drift4=0.02175; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=721.2,naive=245.9,drift4=287.3; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -796,7 +796,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -820,19 +820,19 @@
         <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K2">
-        <v>0.8177768968945478</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.614412087797669</v>
+        <v>0.4344475741781855</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="O2" t="s">
         <v>70</v>
@@ -841,46 +841,46 @@
         <v>72</v>
       </c>
       <c r="Q2">
-        <v>0.954444224223637</v>
+        <v>0.75</v>
       </c>
       <c r="R2">
-        <v>0.80901</v>
+        <v>1.35335</v>
       </c>
       <c r="S2">
-        <v>0.814484119192829</v>
+        <v>1.365857882169107</v>
       </c>
       <c r="T2">
-        <v>0.8201073531217524</v>
+        <v>1.357114450792559</v>
       </c>
       <c r="U2">
-        <v>0.80901</v>
+        <v>1.35335</v>
       </c>
       <c r="V2">
-        <v>0.81102</v>
+        <v>1.3835</v>
       </c>
       <c r="W2">
-        <v>0.814484119192829</v>
+        <v>1.365857882169107</v>
       </c>
       <c r="X2">
-        <v>0.799335</v>
+        <v>1.3388875</v>
       </c>
       <c r="Y2">
-        <v>0.00676644193870166</v>
+        <v>0.009242163645107842</v>
       </c>
       <c r="Z2">
-        <v>0.5658004333673406</v>
+        <v>0.8648492424620056</v>
       </c>
       <c r="AA2">
-        <v>0.00676644193870166</v>
+        <v>0.009242163645107842</v>
       </c>
       <c r="AB2">
-        <v>0.4254395246922723</v>
+        <v>0.440093846051868</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3745604753077277</v>
+        <v>0.3599061539481321</v>
       </c>
       <c r="AE2" t="s">
         <v>74</v>
@@ -892,46 +892,46 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>477.2221121118185</v>
+        <v>375</v>
       </c>
       <c r="AI2">
-        <v>0.01195906107464681</v>
+        <v>0.01068644474821734</v>
       </c>
       <c r="AJ2">
-        <v>41809.30232558132</v>
+        <v>46788.24546240299</v>
       </c>
       <c r="AK2">
-        <v>39904.64712347097</v>
+        <v>35091.18409680224</v>
       </c>
       <c r="AL2">
-        <v>49325.28290561423</v>
+        <v>25929.12705272268</v>
       </c>
       <c r="AM2">
-        <v>399.0464712347097</v>
+        <v>350.9118409680224</v>
       </c>
       <c r="AN2">
-        <v>0.003990464712347097</v>
+        <v>0.003509118409680224</v>
       </c>
       <c r="AO2">
-        <v>477.2221121118185</v>
+        <v>375</v>
       </c>
       <c r="AP2">
-        <v>0.004772221121118185</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ2">
-        <v>0.03799304440561113</v>
+        <v>0.0540008446956466</v>
       </c>
       <c r="AR2">
-        <v>0.01452322446874832</v>
+        <v>0.01672460925464242</v>
       </c>
       <c r="AS2">
-        <v>0.02457009560752225</v>
+        <v>0.04122718831694158</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV2" t="s">
         <v>84</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="AY2" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -972,70 +972,70 @@
         <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J3" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.015584986259377</v>
+        <v>0.04639021614399383</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R3">
-        <v>1.33951</v>
+        <v>9.16333</v>
       </c>
       <c r="S3">
-        <v>1.346717449414908</v>
+        <v>9.242223453490938</v>
       </c>
       <c r="T3">
-        <v>1.342514775958193</v>
+        <v>9.182501753348673</v>
       </c>
       <c r="U3">
-        <v>1.33951</v>
+        <v>9.16333</v>
       </c>
       <c r="V3">
-        <v>1.35582</v>
+        <v>9.351790000000001</v>
       </c>
       <c r="W3">
-        <v>1.346717449414908</v>
+        <v>9.242223453490938</v>
       </c>
       <c r="X3">
-        <v>1.32526</v>
+        <v>9.071985</v>
       </c>
       <c r="Y3">
-        <v>0.005380661148410925</v>
+        <v>0.008609692490714404</v>
       </c>
       <c r="Z3">
-        <v>0.5057859238531898</v>
+        <v>0.8636866111000931</v>
       </c>
       <c r="AA3">
-        <v>0.005380661148410925</v>
+        <v>0.008609692490714404</v>
       </c>
       <c r="AB3">
-        <v>0.4389667221491461</v>
+        <v>0.4245690290425134</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3610332778508539</v>
+        <v>0.3754309709574867</v>
       </c>
       <c r="AE3" t="s">
         <v>75</v>
@@ -1047,46 +1047,46 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI3">
-        <v>0.01063821845301635</v>
+        <v>0.009968537638609545</v>
       </c>
       <c r="AJ3">
-        <v>47000.35087719321</v>
+        <v>50157.80830915759</v>
       </c>
       <c r="AK3">
-        <v>47000.35087719321</v>
+        <v>37618.35623186819</v>
       </c>
       <c r="AL3">
-        <v>35087.71929824579</v>
+        <v>4105.315014505447</v>
       </c>
       <c r="AM3">
-        <v>470.0035087719321</v>
+        <v>376.1835623186819</v>
       </c>
       <c r="AN3">
-        <v>0.004700035087719321</v>
+        <v>0.003761835623186819</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ3">
-        <v>0.0535667053939405</v>
+        <v>0.5140703124509063</v>
       </c>
       <c r="AR3">
-        <v>0.01537450901426796</v>
+        <v>0.1120035233849842</v>
       </c>
       <c r="AS3">
-        <v>0.0400915936294372</v>
+        <v>0.2446796971992862</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV3" t="s">
         <v>84</v>
@@ -1098,7 +1098,7 @@
         <v>85</v>
       </c>
       <c r="AY3" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1127,70 +1127,70 @@
         <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.48575500316923</v>
       </c>
       <c r="L4">
-        <v>0.6163803082298828</v>
+        <v>1.378364710260847</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.8714387507923075</v>
       </c>
       <c r="R4">
-        <v>6.7719</v>
+        <v>0.8051649999999999</v>
       </c>
       <c r="S4">
-        <v>6.799173143544933</v>
+        <v>0.8096024233132023</v>
       </c>
       <c r="T4">
-        <v>6.844652671650291</v>
+        <v>0.8170893540256168</v>
       </c>
       <c r="U4">
-        <v>6.7719</v>
+        <v>0.8051649999999999</v>
       </c>
       <c r="V4">
-        <v>6.761099999999999</v>
+        <v>0.8033299999999998</v>
       </c>
       <c r="W4">
-        <v>6.799173143544933</v>
+        <v>0.8096024233132023</v>
       </c>
       <c r="X4">
-        <v>6.7421</v>
+        <v>0.7954899999999999</v>
       </c>
       <c r="Y4">
-        <v>0.004027399037926339</v>
+        <v>0.005511197472819118</v>
       </c>
       <c r="Z4">
-        <v>0.9152061592259507</v>
+        <v>0.458648404465364</v>
       </c>
       <c r="AA4">
-        <v>0.004027399037926339</v>
+        <v>0.005511197472819118</v>
       </c>
       <c r="AB4">
-        <v>0.4298263937656794</v>
+        <v>0.4291933547321977</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3701736062343207</v>
+        <v>0.3708066452678023</v>
       </c>
       <c r="AE4" t="s">
         <v>76</v>
@@ -1202,46 +1202,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
+        <v>435.7193753961537</v>
       </c>
       <c r="AI4">
-        <v>0.004400537515320671</v>
+        <v>0.01201617059857299</v>
       </c>
       <c r="AJ4">
-        <v>113622.4832214763</v>
+        <v>41610.5943152454</v>
       </c>
       <c r="AK4">
-        <v>113622.4832214763</v>
+        <v>36261.08432980294</v>
       </c>
       <c r="AL4">
-        <v>16778.52348993286</v>
+        <v>45035.59435619152</v>
       </c>
       <c r="AM4">
-        <v>1136.224832214763</v>
+        <v>362.6108432980294</v>
       </c>
       <c r="AN4">
-        <v>0.01136224832214763</v>
+        <v>0.003626108432980294</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>435.7193753961537</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0.004357193753961537</v>
       </c>
       <c r="AQ4">
-        <v>0.1170480546303424</v>
+        <v>0.03759572170604478</v>
       </c>
       <c r="AR4">
-        <v>0.02728800437534951</v>
+        <v>0.014156168893699</v>
       </c>
       <c r="AS4">
-        <v>0.05836718356271586</v>
+        <v>0.02463648767176508</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV4" t="s">
         <v>84</v>
@@ -1253,7 +1253,7 @@
         <v>85</v>
       </c>
       <c r="AY4" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1285,19 +1285,19 @@
         <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.1053328644719332</v>
+        <v>0.9012854344525589</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1309,43 +1309,43 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>9.068239999999999</v>
+        <v>6.76585</v>
       </c>
       <c r="S5">
-        <v>9.083790868978152</v>
+        <v>6.790799325916677</v>
       </c>
       <c r="T5">
-        <v>9.021801501209344</v>
+        <v>6.838323896533075</v>
       </c>
       <c r="U5">
-        <v>9.068239999999999</v>
+        <v>6.76585</v>
       </c>
       <c r="V5">
-        <v>9.16161</v>
+        <v>6.749000000000001</v>
       </c>
       <c r="W5">
-        <v>9.083790868978152</v>
+        <v>6.790799325916677</v>
       </c>
       <c r="X5">
-        <v>8.976894999999999</v>
+        <v>6.736050000000001</v>
       </c>
       <c r="Y5">
-        <v>0.001714871791897074</v>
+        <v>0.003687537547636469</v>
       </c>
       <c r="Z5">
-        <v>0.1702432424123129</v>
+        <v>0.8372257019018846</v>
       </c>
       <c r="AA5">
-        <v>0.001714871791897074</v>
+        <v>0.003687537547636469</v>
       </c>
       <c r="AB5">
-        <v>0.4230438888440519</v>
+        <v>0.4302244685714747</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3769561111559481</v>
+        <v>0.3697755314285254</v>
       </c>
       <c r="AE5" t="s">
         <v>77</v>
@@ -1360,43 +1360,43 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01007306820287068</v>
+        <v>0.004404472460962044</v>
       </c>
       <c r="AJ5">
-        <v>49637.30910285182</v>
+        <v>113520.9731543622</v>
       </c>
       <c r="AK5">
-        <v>49637.30910285182</v>
+        <v>113520.9731543622</v>
       </c>
       <c r="AL5">
-        <v>5473.753352673928</v>
+        <v>16778.52348993286</v>
       </c>
       <c r="AM5">
-        <v>496.3730910285182</v>
+        <v>1135.209731543622</v>
       </c>
       <c r="AN5">
-        <v>0.004963730910285182</v>
+        <v>0.01135209731543622</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.5080854227947751</v>
+        <v>0.1170197463626841</v>
       </c>
       <c r="AR5">
-        <v>0.1058910979362605</v>
+        <v>0.02796284556767449</v>
       </c>
       <c r="AS5">
-        <v>0.234780307217255</v>
+        <v>0.05829205110668501</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV5" t="s">
         <v>84</v>
@@ -1408,7 +1408,7 @@
         <v>85</v>
       </c>
       <c r="AY5" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1440,19 +1440,19 @@
         <v>68</v>
       </c>
       <c r="J6" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K6">
-        <v>0.1367858210383857</v>
+        <v>0.06538241125378751</v>
       </c>
       <c r="L6">
-        <v>1.64378184550154</v>
+        <v>1.585584343636076</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
@@ -1461,46 +1461,46 @@
         <v>72</v>
       </c>
       <c r="Q6">
-        <v>0.7841964552595965</v>
+        <v>0.7663456028134469</v>
       </c>
       <c r="R6">
-        <v>162.2315</v>
+        <v>162.0845</v>
       </c>
       <c r="S6">
-        <v>162.4473488363326</v>
+        <v>162.2723456427186</v>
       </c>
       <c r="T6">
-        <v>161.8954372764127</v>
+        <v>161.8157631141572</v>
       </c>
       <c r="U6">
-        <v>162.2315</v>
+        <v>162.0845</v>
       </c>
       <c r="V6">
-        <v>163.183</v>
+        <v>162.889</v>
       </c>
       <c r="W6">
-        <v>162.47484725</v>
+        <v>162.32762675</v>
       </c>
       <c r="X6">
-        <v>160.3565</v>
+        <v>160.2095</v>
       </c>
       <c r="Y6">
-        <v>0.00133049892488563</v>
+        <v>0.001158936497435769</v>
       </c>
       <c r="Z6">
-        <v>0.1297851999999995</v>
+        <v>0.1296675999999995</v>
       </c>
       <c r="AA6">
-        <v>0.00133049892488563</v>
+        <v>0.001158936497435769</v>
       </c>
       <c r="AB6">
-        <v>0.4235530849697329</v>
+        <v>0.4246540193439942</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3764469150302671</v>
+        <v>0.3753459806560059</v>
       </c>
       <c r="AE6" t="s">
         <v>78</v>
@@ -1512,46 +1512,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>392.0982276297983</v>
+        <v>383.1728014067235</v>
       </c>
       <c r="AI6">
-        <v>0.01155755818074792</v>
+        <v>0.01156804012721764</v>
       </c>
       <c r="AJ6">
-        <v>43261.73333333318</v>
+        <v>43222.53333333317</v>
       </c>
       <c r="AK6">
-        <v>33925.6979283858</v>
+        <v>33123.3983624575</v>
       </c>
       <c r="AL6">
-        <v>209.1190547358916</v>
+        <v>204.3588274169184</v>
       </c>
       <c r="AM6">
-        <v>339.256979283858</v>
+        <v>331.233983624575</v>
       </c>
       <c r="AN6">
-        <v>0.00339256979283858</v>
+        <v>0.00331233983624575</v>
       </c>
       <c r="AO6">
-        <v>392.0982276297983</v>
+        <v>383.1728014067234</v>
       </c>
       <c r="AP6">
-        <v>0.003920982276297984</v>
+        <v>0.003831728014067234</v>
       </c>
       <c r="AQ6">
-        <v>4.596803088712453</v>
+        <v>4.589856188488345</v>
       </c>
       <c r="AR6">
-        <v>1.969724287287069</v>
+        <v>1.950206266075283</v>
       </c>
       <c r="AS6">
-        <v>3.565161506553571</v>
+        <v>3.563854679376535</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV6" t="s">
         <v>84</v>
@@ -1563,7 +1563,7 @@
         <v>85</v>
       </c>
       <c r="AY6" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1595,19 +1595,19 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K7">
-        <v>0.4204862932025254</v>
+        <v>0.2028434314198591</v>
       </c>
       <c r="L7">
-        <v>1.92283086552391</v>
+        <v>1.712397308278712</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
         <v>70</v>
@@ -1616,46 +1616,46 @@
         <v>72</v>
       </c>
       <c r="Q7">
-        <v>0.8551215733006313</v>
+        <v>0.8007108578549648</v>
       </c>
       <c r="R7">
-        <v>7.734</v>
+        <v>7.7583</v>
       </c>
       <c r="S7">
-        <v>7.698164867752628</v>
+        <v>7.736578998765781</v>
       </c>
       <c r="T7">
-        <v>7.688804536966142</v>
+        <v>7.72403883265658</v>
       </c>
       <c r="U7">
-        <v>7.734</v>
+        <v>7.7583</v>
       </c>
       <c r="V7">
-        <v>7.6896</v>
+        <v>7.7382</v>
       </c>
       <c r="W7">
-        <v>7.698164867752628</v>
+        <v>7.736578998765781</v>
       </c>
       <c r="X7">
-        <v>7.796925</v>
+        <v>7.821225</v>
       </c>
       <c r="Y7">
-        <v>-0.004633453872171163</v>
+        <v>-0.002799711436038729</v>
       </c>
       <c r="Z7">
-        <v>0.5694895867679255</v>
+        <v>0.345188736340393</v>
       </c>
       <c r="AA7">
-        <v>0.004633453872171163</v>
+        <v>0.002799711436038729</v>
       </c>
       <c r="AB7">
-        <v>0.3961620263400052</v>
+        <v>0.3983429541803013</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.4038379736599947</v>
+        <v>0.4016570458196987</v>
       </c>
       <c r="AE7" t="s">
         <v>79</v>
@@ -1667,46 +1667,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>427.5607866503157</v>
+        <v>400.3554289274824</v>
       </c>
       <c r="AI7">
-        <v>0.008136152055857269</v>
+        <v>0.008110668574301086</v>
       </c>
       <c r="AJ7">
-        <v>61454.11203814053</v>
+        <v>61647.1990464838</v>
       </c>
       <c r="AK7">
-        <v>52550.736971848</v>
+        <v>49361.58163286581</v>
       </c>
       <c r="AL7">
-        <v>6794.768162897336</v>
+        <v>6362.422390583737</v>
       </c>
       <c r="AM7">
-        <v>525.5073697184799</v>
+        <v>493.6158163286581</v>
       </c>
       <c r="AN7">
-        <v>0.005255073697184799</v>
+        <v>0.004936158163286582</v>
       </c>
       <c r="AO7">
-        <v>427.5607866503157</v>
+        <v>400.3554289274824</v>
       </c>
       <c r="AP7">
-        <v>0.004275607866503157</v>
+        <v>0.004003554289274824</v>
       </c>
       <c r="AQ7">
-        <v>0.3235471939611005</v>
+        <v>0.3261854711446734</v>
       </c>
       <c r="AR7">
-        <v>0.1094781003496964</v>
+        <v>0.1070503099844104</v>
       </c>
       <c r="AS7">
-        <v>0.1464069388144718</v>
+        <v>0.14792738469878</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV7" t="s">
         <v>84</v>
@@ -1718,7 +1718,7 @@
         <v>85</v>
       </c>
       <c r="AY7" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1750,19 +1750,19 @@
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K8">
-        <v>0.6913151086580912</v>
+        <v>0.2825536779918912</v>
       </c>
       <c r="L8">
-        <v>1.080685084071596</v>
+        <v>0.8838316310306225</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O8" t="s">
         <v>70</v>
@@ -1771,46 +1771,46 @@
         <v>72</v>
       </c>
       <c r="Q8">
-        <v>0.9228287771645228</v>
+        <v>0.8206384194979728</v>
       </c>
       <c r="R8">
-        <v>4.72342</v>
+        <v>4.74173</v>
       </c>
       <c r="S8">
-        <v>4.682026549676137</v>
+        <v>4.708758686664174</v>
       </c>
       <c r="T8">
-        <v>4.655984014274864</v>
+        <v>4.678971324910421</v>
       </c>
       <c r="U8">
-        <v>4.72342</v>
+        <v>4.74173</v>
       </c>
       <c r="V8">
-        <v>4.69149</v>
+        <v>4.728109999999999</v>
       </c>
       <c r="W8">
-        <v>4.682026549676137</v>
+        <v>4.708758686664174</v>
       </c>
       <c r="X8">
-        <v>4.776445</v>
+        <v>4.794754999999999</v>
       </c>
       <c r="Y8">
-        <v>-0.008763449010222017</v>
+        <v>-0.006953435420368852</v>
       </c>
       <c r="Z8">
-        <v>0.7806402701341471</v>
+        <v>0.6218069464559323</v>
       </c>
       <c r="AA8">
-        <v>0.008763449010222017</v>
+        <v>0.006953435420368852</v>
       </c>
       <c r="AB8">
-        <v>0.4463881230212595</v>
+        <v>0.4492451881452436</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3536118769787406</v>
+        <v>0.3507548118547564</v>
       </c>
       <c r="AE8" t="s">
         <v>80</v>
@@ -1822,46 +1822,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>461.4143885822614</v>
+        <v>410.3192097489864</v>
       </c>
       <c r="AI8">
-        <v>0.01122597609359313</v>
+        <v>0.01118262743766509</v>
       </c>
       <c r="AJ8">
-        <v>44539.55681282443</v>
+        <v>44712.21122112239</v>
       </c>
       <c r="AK8">
-        <v>41102.38474902856</v>
+        <v>36692.55834876141</v>
       </c>
       <c r="AL8">
-        <v>8701.827224559442</v>
+        <v>7738.221777444394</v>
       </c>
       <c r="AM8">
-        <v>411.0238474902856</v>
+        <v>366.9255834876141</v>
       </c>
       <c r="AN8">
-        <v>0.004110238474902856</v>
+        <v>0.003669255834876141</v>
       </c>
       <c r="AO8">
-        <v>461.4143885822614</v>
+        <v>410.3192097489864</v>
       </c>
       <c r="AP8">
-        <v>0.004614143885822613</v>
+        <v>0.004103192097489864</v>
       </c>
       <c r="AQ8">
-        <v>0.1839974079376004</v>
+        <v>0.183125462414879</v>
       </c>
       <c r="AR8">
-        <v>0.09306750440257795</v>
+        <v>0.09196486962675031</v>
       </c>
       <c r="AS8">
-        <v>0.175609089366169</v>
+        <v>0.176106761471167</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV8" t="s">
         <v>84</v>
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="AY8" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1905,19 +1905,19 @@
         <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K9">
-        <v>0.926654347584107</v>
+        <v>0.4732606909828342</v>
       </c>
       <c r="L9">
-        <v>1.567338617969237</v>
+        <v>1.296853484456645</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
@@ -1926,46 +1926,46 @@
         <v>72</v>
       </c>
       <c r="Q9">
-        <v>0.9816635868960267</v>
+        <v>0.8683151727457086</v>
       </c>
       <c r="R9">
-        <v>1.14252</v>
+        <v>1.14685</v>
       </c>
       <c r="S9">
-        <v>1.13226781225161</v>
+        <v>1.137962682327056</v>
       </c>
       <c r="T9">
-        <v>1.121705262977535</v>
+        <v>1.125406198847424</v>
       </c>
       <c r="U9">
-        <v>1.14252</v>
+        <v>1.14685</v>
       </c>
       <c r="V9">
-        <v>1.13824</v>
+        <v>1.1469</v>
       </c>
       <c r="W9">
-        <v>1.13226781225161</v>
+        <v>1.137962682327056</v>
       </c>
       <c r="X9">
-        <v>1.15552</v>
+        <v>1.15985</v>
       </c>
       <c r="Y9">
-        <v>-0.008973311406706506</v>
+        <v>-0.007749328746518081</v>
       </c>
       <c r="Z9">
-        <v>0.7886298267992545</v>
+        <v>0.6836398209957119</v>
       </c>
       <c r="AA9">
-        <v>0.008973311406706506</v>
+        <v>0.007749328746518081</v>
       </c>
       <c r="AB9">
-        <v>0.4129601661709609</v>
+        <v>0.4153438291148594</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3870398338290392</v>
+        <v>0.3846561708851406</v>
       </c>
       <c r="AE9" t="s">
         <v>81</v>
@@ -1977,46 +1977,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>490.8317934480133</v>
+        <v>434.1575863728543</v>
       </c>
       <c r="AI9">
-        <v>0.01137835661520149</v>
+        <v>0.0113353969568819</v>
       </c>
       <c r="AJ9">
-        <v>43943.07692307689</v>
+        <v>44109.61538461534</v>
       </c>
       <c r="AK9">
-        <v>43137.31851155567</v>
+        <v>38301.04830243903</v>
       </c>
       <c r="AL9">
-        <v>37756.2918036933</v>
+        <v>33396.73741329645</v>
       </c>
       <c r="AM9">
-        <v>431.3731851155567</v>
+        <v>383.0104830243903</v>
       </c>
       <c r="AN9">
-        <v>0.004313731851155567</v>
+        <v>0.003830104830243903</v>
       </c>
       <c r="AO9">
-        <v>490.8317934480133</v>
+        <v>434.1575863728543</v>
       </c>
       <c r="AP9">
-        <v>0.004908317934480133</v>
+        <v>0.004341575863728543</v>
       </c>
       <c r="AQ9">
-        <v>0.04737871158390136</v>
+        <v>0.04783364549062673</v>
       </c>
       <c r="AR9">
-        <v>0.01494999740709829</v>
+        <v>0.01466577280167936</v>
       </c>
       <c r="AS9">
-        <v>0.02771872273946265</v>
+        <v>0.02801268259515465</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV9" t="s">
         <v>84</v>
@@ -2028,7 +2028,7 @@
         <v>85</v>
       </c>
       <c r="AY9" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2060,19 +2060,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.286430796385193</v>
+        <v>0.9997032835319883</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O10" t="s">
         <v>70</v>
@@ -2084,43 +2084,43 @@
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>0.69797</v>
+        <v>0.7001500000000001</v>
       </c>
       <c r="S10">
-        <v>0.6903856822235885</v>
+        <v>0.6932314819995591</v>
       </c>
       <c r="T10">
-        <v>0.6834983353737917</v>
+        <v>0.6855141179171849</v>
       </c>
       <c r="U10">
-        <v>0.69797</v>
+        <v>0.7001500000000001</v>
       </c>
       <c r="V10">
-        <v>0.69484</v>
+        <v>0.6992000000000002</v>
       </c>
       <c r="W10">
-        <v>0.6903856822235885</v>
+        <v>0.6932314819995591</v>
       </c>
       <c r="X10">
-        <v>0.707245</v>
+        <v>0.7094250000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.01086625181083921</v>
+        <v>-0.009881479683554902</v>
       </c>
       <c r="Z10">
-        <v>0.8177162023085059</v>
+        <v>0.7459318598858135</v>
       </c>
       <c r="AA10">
-        <v>0.01086625181083921</v>
+        <v>0.009881479683554902</v>
       </c>
       <c r="AB10">
-        <v>0.4479340505865345</v>
+        <v>0.449990578844313</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3520659494134656</v>
+        <v>0.3500094211556871</v>
       </c>
       <c r="AE10" t="s">
         <v>82</v>
@@ -2135,43 +2135,43 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01328853675659421</v>
+        <v>0.01324716132257382</v>
       </c>
       <c r="AJ10">
-        <v>37626.41509433938</v>
+        <v>37743.9353099728</v>
       </c>
       <c r="AK10">
-        <v>28219.81132075453</v>
+        <v>28307.9514824796</v>
       </c>
       <c r="AL10">
         <v>40431.26684636092</v>
       </c>
       <c r="AM10">
-        <v>282.1981132075453</v>
+        <v>283.079514824796</v>
       </c>
       <c r="AN10">
-        <v>0.002821981132075453</v>
+        <v>0.00283079514824796</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ10">
-        <v>0.03053222523278472</v>
+        <v>0.03038856311542163</v>
       </c>
       <c r="AR10">
-        <v>0.01329104206107144</v>
+        <v>0.01320095170365907</v>
       </c>
       <c r="AS10">
-        <v>0.02918164497882425</v>
+        <v>0.02922594202116263</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV10" t="s">
         <v>84</v>
@@ -2183,7 +2183,7 @@
         <v>85</v>
       </c>
       <c r="AY10" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2215,19 +2215,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.601694257357708</v>
+        <v>1.634135471833873</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O11" t="s">
         <v>70</v>
@@ -2239,43 +2239,43 @@
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4052.81</v>
+        <v>4059.21</v>
       </c>
       <c r="S11">
-        <v>3893.615226325778</v>
+        <v>3902.871674423247</v>
       </c>
       <c r="T11">
-        <v>3764.089093326046</v>
+        <v>3771.50619247565</v>
       </c>
       <c r="U11">
-        <v>4052.81</v>
+        <v>4059.21</v>
       </c>
       <c r="V11">
-        <v>3945.36</v>
+        <v>3958.16</v>
       </c>
       <c r="W11">
-        <v>3893.615226325778</v>
+        <v>3902.871674423247</v>
       </c>
       <c r="X11">
-        <v>4197.0075</v>
+        <v>4203.4075</v>
       </c>
       <c r="Y11">
-        <v>-0.03928009792569161</v>
+        <v>-0.03851447093812664</v>
       </c>
       <c r="Z11">
-        <v>1.104005087981569</v>
+        <v>1.084195811832751</v>
       </c>
       <c r="AA11">
-        <v>0.03928009792569161</v>
+        <v>0.03851447093812664</v>
       </c>
       <c r="AB11">
-        <v>0.4040073226198792</v>
+        <v>0.4044831797331777</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3959926773801208</v>
+        <v>0.3955168202668224</v>
       </c>
       <c r="AE11" t="s">
         <v>83</v>
@@ -2290,22 +2290,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03557963487062063</v>
+        <v>0.03552353783125288</v>
       </c>
       <c r="AJ11">
-        <v>14052.98288805284</v>
+        <v>14075.17467362472</v>
       </c>
       <c r="AK11">
-        <v>10539.73716603963</v>
+        <v>10556.38100521854</v>
       </c>
       <c r="AL11">
-        <v>2.60059987170374</v>
+        <v>2.600599871703739</v>
       </c>
       <c r="AM11">
-        <v>105.3973716603963</v>
+        <v>105.5638100521854</v>
       </c>
       <c r="AN11">
-        <v>0.001053973716603963</v>
+        <v>0.001055638100521854</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2314,19 +2314,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>545.3442646528041</v>
+        <v>545.1828031561096</v>
       </c>
       <c r="AR11">
-        <v>281.6278273267829</v>
+        <v>280.8282397589354</v>
       </c>
       <c r="AS11">
-        <v>320.6668007000793</v>
+        <v>320.9517304827621</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04596404769726044</v>
+        <v>0.04188345169470575</v>
       </c>
       <c r="AV11" t="s">
         <v>84</v>
@@ -2338,7 +2338,7 @@
         <v>85</v>
       </c>
       <c r="AY11" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,6 +169,15 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
@@ -178,21 +187,12 @@
     <t>USDCHF</t>
   </si>
   <si>
-    <t>USDCNH</t>
+    <t>AUDCNH</t>
   </si>
   <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -205,70 +205,82 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05862,naive=0.02092,drift4=0.03593; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.4467,naive=0.1313,drift4=0.2132; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03892,naive=0.01369,drift4=0.02088; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1075,naive=0.03096,drift4=0.0545; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.141,naive=1.744,drift4=2.585; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3408,naive=0.09123,drift4=0.1147; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1762,naive=0.09161,drift4=0.1324; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.05212,naive=0.01371,drift4=0.02134; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02934,naive=0.01383,drift4=0.02175; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=721.2,naive=245.9,drift4=287.3; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05125,naive=0.01349,drift4=0.01994; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1045,naive=0.0286,drift4=0.05282; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3303,naive=0.0892,drift4=0.1091; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05646,naive=0.01952,drift4=0.03423; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.4115,naive=0.122,drift4=0.2029; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03929,naive=0.01365,drift4=0.02012; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.171,naive=0.08865,drift4=0.1234; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.12,naive=1.682,drift4=2.405; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03,naive=0.01361,drift4=0.02098; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=732.4,naive=252.3,drift4=271.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -796,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -817,73 +829,64 @@
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.461548057468464</v>
       </c>
       <c r="L2">
-        <v>0.4344475741781855</v>
+        <v>1.289547499566908</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.35335</v>
+        <v>1.144395</v>
       </c>
       <c r="S2">
-        <v>1.365857882169107</v>
+        <v>1.145293198657527</v>
       </c>
       <c r="T2">
-        <v>1.357114450792559</v>
+        <v>1.148856031324252</v>
       </c>
       <c r="U2">
-        <v>1.35335</v>
+        <v>1.144395</v>
       </c>
       <c r="V2">
-        <v>1.3835</v>
-      </c>
-      <c r="W2">
-        <v>1.365857882169107</v>
-      </c>
-      <c r="X2">
-        <v>1.3388875</v>
+        <v>1.14199</v>
       </c>
       <c r="Y2">
-        <v>0.009242163645107842</v>
-      </c>
-      <c r="Z2">
-        <v>0.8648492424620056</v>
+        <v>0.0007848676877539316</v>
       </c>
       <c r="AA2">
-        <v>0.009242163645107842</v>
+        <v>0.0007848676877539316</v>
       </c>
       <c r="AB2">
-        <v>0.440093846051868</v>
+        <v>0.4110378360143142</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3599061539481321</v>
+        <v>0.3889621639856858</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -892,58 +895,55 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>375</v>
-      </c>
-      <c r="AI2">
-        <v>0.01068644474821734</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>46788.24546240299</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>35091.18409680224</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>25929.12705272268</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>350.9118409680224</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.003509118409680224</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.0540008446956466</v>
+        <v>0.04540466663796382</v>
       </c>
       <c r="AR2">
-        <v>0.01672460925464242</v>
+        <v>0.01383051365861976</v>
       </c>
       <c r="AS2">
-        <v>0.04122718831694158</v>
+        <v>0.02291455803527424</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -972,73 +972,64 @@
         <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.04639021614399383</v>
+        <v>0.9445277784560701</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>9.16333</v>
+        <v>6.77381</v>
       </c>
       <c r="S3">
-        <v>9.242223453490938</v>
+        <v>6.775192700263536</v>
       </c>
       <c r="T3">
-        <v>9.182501753348673</v>
+        <v>6.784603189579009</v>
       </c>
       <c r="U3">
-        <v>9.16333</v>
+        <v>6.77381</v>
       </c>
       <c r="V3">
-        <v>9.351790000000001</v>
-      </c>
-      <c r="W3">
-        <v>9.242223453490938</v>
-      </c>
-      <c r="X3">
-        <v>9.071985</v>
+        <v>6.76492</v>
       </c>
       <c r="Y3">
-        <v>0.008609692490714404</v>
-      </c>
-      <c r="Z3">
-        <v>0.8636866111000931</v>
+        <v>0.000204124453377877</v>
       </c>
       <c r="AA3">
-        <v>0.008609692490714404</v>
+        <v>0.000204124453377877</v>
       </c>
       <c r="AB3">
-        <v>0.4245690290425134</v>
+        <v>0.4315713278804829</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3754309709574867</v>
+        <v>0.3684286721195171</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1047,58 +1038,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>375</v>
-      </c>
-      <c r="AI3">
-        <v>0.009968537638609545</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>50157.80830915759</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>37618.35623186819</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>4105.315014505447</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>376.1835623186819</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.003761835623186819</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>375.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.003750000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.5140703124509063</v>
+        <v>0.1094098622636678</v>
       </c>
       <c r="AR3">
-        <v>0.1120035233849842</v>
+        <v>0.02409428221325506</v>
       </c>
       <c r="AS3">
-        <v>0.2446796971992862</v>
+        <v>0.05157521569961097</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1127,73 +1115,64 @@
         <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K4">
-        <v>0.48575500316923</v>
+        <v>0.2273763052166383</v>
       </c>
       <c r="L4">
-        <v>1.378364710260847</v>
+        <v>1.738524582408123</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.8714387507923075</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>0.8051649999999999</v>
+        <v>7.7489</v>
       </c>
       <c r="S4">
-        <v>0.8096024233132023</v>
+        <v>7.744505401938935</v>
       </c>
       <c r="T4">
-        <v>0.8170893540256168</v>
+        <v>7.767848520540613</v>
       </c>
       <c r="U4">
-        <v>0.8051649999999999</v>
+        <v>7.7489</v>
       </c>
       <c r="V4">
-        <v>0.8033299999999998</v>
-      </c>
-      <c r="W4">
-        <v>0.8096024233132023</v>
-      </c>
-      <c r="X4">
-        <v>0.7954899999999999</v>
+        <v>7.719399999999999</v>
       </c>
       <c r="Y4">
-        <v>0.005511197472819118</v>
-      </c>
-      <c r="Z4">
-        <v>0.458648404465364</v>
+        <v>-0.0005671254063241395</v>
       </c>
       <c r="AA4">
-        <v>0.005511197472819118</v>
+        <v>0.0005671254063241395</v>
       </c>
       <c r="AB4">
-        <v>0.4291933547321977</v>
+        <v>0.3964084294965211</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3708066452678023</v>
+        <v>0.4035915705034788</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1202,58 +1181,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>435.7193753961537</v>
-      </c>
-      <c r="AI4">
-        <v>0.01201617059857299</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>41610.5943152454</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>36261.08432980294</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>45035.59435619152</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>362.6108432980294</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.003626108432980294</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>435.7193753961537</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.004357193753961537</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0.03759572170604478</v>
+        <v>0.3050850196490743</v>
       </c>
       <c r="AR4">
-        <v>0.014156168893699</v>
+        <v>0.09813461755882155</v>
       </c>
       <c r="AS4">
-        <v>0.02463648767176508</v>
+        <v>0.1263181950911947</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW4" t="s">
         <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AY4" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1237,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,25 +1249,25 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.9012854344525589</v>
+        <v>0.5881446195461555</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1303,52 +1279,52 @@
         <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>6.76585</v>
+        <v>1.34744</v>
       </c>
       <c r="S5">
-        <v>6.790799325916677</v>
+        <v>1.359618703437023</v>
       </c>
       <c r="T5">
-        <v>6.838323896533075</v>
+        <v>1.355285981034613</v>
       </c>
       <c r="U5">
-        <v>6.76585</v>
+        <v>1.34744</v>
       </c>
       <c r="V5">
-        <v>6.749000000000001</v>
+        <v>1.37168</v>
       </c>
       <c r="W5">
-        <v>6.790799325916677</v>
+        <v>1.359618703437023</v>
       </c>
       <c r="X5">
-        <v>6.736050000000001</v>
+        <v>1.33319</v>
       </c>
       <c r="Y5">
-        <v>0.003687537547636469</v>
+        <v>0.009038401292096938</v>
       </c>
       <c r="Z5">
-        <v>0.8372257019018846</v>
+        <v>0.8546458552296953</v>
       </c>
       <c r="AA5">
-        <v>0.003687537547636469</v>
+        <v>0.009038401292096938</v>
       </c>
       <c r="AB5">
-        <v>0.4302244685714747</v>
+        <v>0.4399956214645614</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3697755314285254</v>
+        <v>0.3600043785354387</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1357,58 +1333,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.004404472460962044</v>
+        <v>0.01057561004571627</v>
       </c>
       <c r="AJ5">
-        <v>113520.9731543622</v>
+        <v>47278.59649122831</v>
       </c>
       <c r="AK5">
-        <v>113520.9731543622</v>
+        <v>35458.94736842123</v>
       </c>
       <c r="AL5">
-        <v>16778.52348993286</v>
+        <v>26315.78947368434</v>
       </c>
       <c r="AM5">
-        <v>1135.209731543622</v>
+        <v>354.5894736842123</v>
       </c>
       <c r="AN5">
-        <v>0.01135209731543622</v>
+        <v>0.003545894736842123</v>
       </c>
       <c r="AO5">
-        <v>499.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.004999999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.1170197463626841</v>
+        <v>0.04959118807570365</v>
       </c>
       <c r="AR5">
-        <v>0.02796284556767449</v>
+        <v>0.01527610689714574</v>
       </c>
       <c r="AS5">
-        <v>0.05829205110668501</v>
+        <v>0.03669449956205958</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1392,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1431,79 +1407,79 @@
         <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K6">
-        <v>0.06538241125378751</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1.585584343636076</v>
+        <v>0.09442998547464578</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q6">
-        <v>0.7663456028134469</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>162.0845</v>
+        <v>9.1273</v>
       </c>
       <c r="S6">
-        <v>162.2723456427186</v>
+        <v>9.183442158443132</v>
       </c>
       <c r="T6">
-        <v>161.8157631141572</v>
+        <v>9.125633101608129</v>
       </c>
       <c r="U6">
-        <v>162.0845</v>
+        <v>9.1273</v>
       </c>
       <c r="V6">
-        <v>162.889</v>
+        <v>9.279730000000001</v>
       </c>
       <c r="W6">
-        <v>162.32762675</v>
+        <v>9.183442158443132</v>
       </c>
       <c r="X6">
-        <v>160.2095</v>
+        <v>9.035955</v>
       </c>
       <c r="Y6">
-        <v>0.001158936497435769</v>
+        <v>0.006151014916035614</v>
       </c>
       <c r="Z6">
-        <v>0.1296675999999995</v>
+        <v>0.6146166560088878</v>
       </c>
       <c r="AA6">
-        <v>0.001158936497435769</v>
+        <v>0.006151014916035614</v>
       </c>
       <c r="AB6">
-        <v>0.4246540193439942</v>
+        <v>0.4270160025514099</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3753459806560059</v>
+        <v>0.37298399744859</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,58 +1488,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>383.1728014067235</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01156804012721764</v>
+        <v>0.01000788842264416</v>
       </c>
       <c r="AJ6">
-        <v>43222.53333333317</v>
+        <v>49960.58897586074</v>
       </c>
       <c r="AK6">
-        <v>33123.3983624575</v>
+        <v>37470.44173189555</v>
       </c>
       <c r="AL6">
-        <v>204.3588274169184</v>
+        <v>4105.315014505445</v>
       </c>
       <c r="AM6">
-        <v>331.233983624575</v>
+        <v>374.7044173189555</v>
       </c>
       <c r="AN6">
-        <v>0.00331233983624575</v>
+        <v>0.003747044173189555</v>
       </c>
       <c r="AO6">
-        <v>383.1728014067234</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.003831728014067234</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>4.589856188488345</v>
+        <v>0.4830909789212179</v>
       </c>
       <c r="AR6">
-        <v>1.950206266075283</v>
+        <v>0.1007624574630314</v>
       </c>
       <c r="AS6">
-        <v>3.563854679376535</v>
+        <v>0.2235709236814991</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1547,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,7 +1559,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
@@ -1592,73 +1568,73 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K7">
-        <v>0.2028434314198591</v>
+        <v>0.4621772135232619</v>
       </c>
       <c r="L7">
-        <v>1.712397308278712</v>
+        <v>1.360413208425827</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.8007108578549648</v>
+        <v>0.8655443033808154</v>
       </c>
       <c r="R7">
-        <v>7.7583</v>
+        <v>0.8084899999999999</v>
       </c>
       <c r="S7">
-        <v>7.736578998765781</v>
+        <v>0.8119967991693238</v>
       </c>
       <c r="T7">
-        <v>7.72403883265658</v>
+        <v>0.8154198103899284</v>
       </c>
       <c r="U7">
-        <v>7.7583</v>
+        <v>0.8084899999999999</v>
       </c>
       <c r="V7">
-        <v>7.7382</v>
+        <v>0.8099799999999998</v>
       </c>
       <c r="W7">
-        <v>7.736578998765781</v>
+        <v>0.8119967991693238</v>
       </c>
       <c r="X7">
-        <v>7.821225</v>
+        <v>0.7988149999999999</v>
       </c>
       <c r="Y7">
-        <v>-0.002799711436038729</v>
+        <v>0.004337467586888939</v>
       </c>
       <c r="Z7">
-        <v>0.345188736340393</v>
+        <v>0.3624598624624115</v>
       </c>
       <c r="AA7">
-        <v>0.002799711436038729</v>
+        <v>0.004337467586888939</v>
       </c>
       <c r="AB7">
-        <v>0.3983429541803013</v>
+        <v>0.4255293849229868</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.4016570458196987</v>
+        <v>0.3744706150770132</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,58 +1643,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>400.3554289274824</v>
+        <v>432.7721516904077</v>
       </c>
       <c r="AI7">
-        <v>0.008110668574301086</v>
+        <v>0.01196675283553293</v>
       </c>
       <c r="AJ7">
-        <v>61647.1990464838</v>
+        <v>41782.4289405684</v>
       </c>
       <c r="AK7">
-        <v>49361.58163286581</v>
+        <v>36164.5433509227</v>
       </c>
       <c r="AL7">
-        <v>6362.422390583737</v>
+        <v>44730.97175094646</v>
       </c>
       <c r="AM7">
-        <v>493.6158163286581</v>
+        <v>361.645433509227</v>
       </c>
       <c r="AN7">
-        <v>0.004936158163286582</v>
+        <v>0.00361645433509227</v>
       </c>
       <c r="AO7">
-        <v>400.3554289274824</v>
+        <v>432.7721516904077</v>
       </c>
       <c r="AP7">
-        <v>0.004003554289274824</v>
+        <v>0.004327721516904077</v>
       </c>
       <c r="AQ7">
-        <v>0.3261854711446734</v>
+        <v>0.03661710140431752</v>
       </c>
       <c r="AR7">
-        <v>0.1070503099844104</v>
+        <v>0.01395770328773555</v>
       </c>
       <c r="AS7">
-        <v>0.14792738469878</v>
+        <v>0.02224381623116381</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
         <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1702,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1741,79 +1717,79 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="K8">
-        <v>0.2825536779918912</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>0.8838316310306225</v>
+        <v>0.7226452061373857</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.8206384194979728</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>4.74173</v>
+        <v>4.73111</v>
       </c>
       <c r="S8">
-        <v>4.708758686664174</v>
+        <v>4.7014358038852</v>
       </c>
       <c r="T8">
-        <v>4.678971324910421</v>
+        <v>4.683806247838432</v>
       </c>
       <c r="U8">
-        <v>4.74173</v>
+        <v>4.73111</v>
       </c>
       <c r="V8">
-        <v>4.728109999999999</v>
+        <v>4.70687</v>
       </c>
       <c r="W8">
-        <v>4.708758686664174</v>
+        <v>4.7014358038852</v>
       </c>
       <c r="X8">
-        <v>4.794754999999999</v>
+        <v>4.784135</v>
       </c>
       <c r="Y8">
-        <v>-0.006953435420368852</v>
+        <v>-0.006272142502457126</v>
       </c>
       <c r="Z8">
-        <v>0.6218069464559323</v>
+        <v>0.5596265179594555</v>
       </c>
       <c r="AA8">
-        <v>0.006953435420368852</v>
+        <v>0.006272142502457126</v>
       </c>
       <c r="AB8">
-        <v>0.4492451881452436</v>
+        <v>0.4458162766739177</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3507548118547564</v>
+        <v>0.3541837233260823</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,58 +1798,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>410.3192097489864</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01118262743766509</v>
+        <v>0.01120772926437975</v>
       </c>
       <c r="AJ8">
-        <v>44712.21122112239</v>
+        <v>44612.0697784067</v>
       </c>
       <c r="AK8">
-        <v>36692.55834876141</v>
+        <v>33459.05233380503</v>
       </c>
       <c r="AL8">
-        <v>7738.221777444394</v>
+        <v>7072.135785007118</v>
       </c>
       <c r="AM8">
-        <v>366.9255834876141</v>
+        <v>334.5905233380503</v>
       </c>
       <c r="AN8">
-        <v>0.003669255834876141</v>
+        <v>0.003345905233380503</v>
       </c>
       <c r="AO8">
-        <v>410.3192097489864</v>
+        <v>375</v>
       </c>
       <c r="AP8">
-        <v>0.004103192097489864</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.183125462414879</v>
+        <v>0.1696836470694267</v>
       </c>
       <c r="AR8">
-        <v>0.09196486962675031</v>
+        <v>0.087041213406612</v>
       </c>
       <c r="AS8">
-        <v>0.176106761471167</v>
+        <v>0.156590104085051</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1857,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,82 +1869,82 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K9">
-        <v>0.4732606909828342</v>
+        <v>0.07588101400851993</v>
       </c>
       <c r="L9">
-        <v>1.296853484456645</v>
+        <v>1.59810554341032</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.8683151727457086</v>
+        <v>0.94308923949361</v>
       </c>
       <c r="R9">
-        <v>1.14685</v>
+        <v>162.4215</v>
       </c>
       <c r="S9">
-        <v>1.137962682327056</v>
+        <v>160.9475192514668</v>
       </c>
       <c r="T9">
-        <v>1.125406198847424</v>
+        <v>157.876568445119</v>
       </c>
       <c r="U9">
-        <v>1.14685</v>
+        <v>162.4215</v>
       </c>
       <c r="V9">
-        <v>1.1469</v>
+        <v>163.563</v>
       </c>
       <c r="W9">
-        <v>1.137962682327056</v>
+        <v>160.9475192514668</v>
       </c>
       <c r="X9">
-        <v>1.15985</v>
+        <v>164.2965</v>
       </c>
       <c r="Y9">
-        <v>-0.007749328746518081</v>
+        <v>-0.009075034700044332</v>
       </c>
       <c r="Z9">
-        <v>0.6836398209957119</v>
+        <v>0.7861230658843973</v>
       </c>
       <c r="AA9">
-        <v>0.007749328746518081</v>
+        <v>0.009075034700044332</v>
       </c>
       <c r="AB9">
-        <v>0.4153438291148594</v>
+        <v>0.4198029511995399</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3846561708851406</v>
+        <v>0.3801970488004601</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1977,58 +1953,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>434.1575863728543</v>
+        <v>471.544619746805</v>
       </c>
       <c r="AI9">
-        <v>0.0113353969568819</v>
+        <v>0.01154403819691363</v>
       </c>
       <c r="AJ9">
-        <v>44109.61538461534</v>
+        <v>43312.39999999984</v>
       </c>
       <c r="AK9">
-        <v>38301.04830243903</v>
+        <v>40847.45837664288</v>
       </c>
       <c r="AL9">
-        <v>33396.73741329645</v>
+        <v>251.4904638649617</v>
       </c>
       <c r="AM9">
-        <v>383.0104830243903</v>
+        <v>408.4745837664289</v>
       </c>
       <c r="AN9">
-        <v>0.003830104830243903</v>
+        <v>0.004084745837664289</v>
       </c>
       <c r="AO9">
-        <v>434.1575863728543</v>
+        <v>471.544619746805</v>
       </c>
       <c r="AP9">
-        <v>0.004341575863728543</v>
+        <v>0.00471544619746805</v>
       </c>
       <c r="AQ9">
-        <v>0.04783364549062673</v>
+        <v>4.323167120146226</v>
       </c>
       <c r="AR9">
-        <v>0.01466577280167936</v>
+        <v>1.87367454634048</v>
       </c>
       <c r="AS9">
-        <v>0.02801268259515465</v>
+        <v>3.257601245699296</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2012,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,82 +2024,82 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.9997032835319883</v>
+        <v>0.819862375895185</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>0.7001500000000001</v>
+        <v>0.699605</v>
       </c>
       <c r="S10">
-        <v>0.6932314819995591</v>
+        <v>0.6912531132119483</v>
       </c>
       <c r="T10">
-        <v>0.6855141179171849</v>
+        <v>0.6820568012426382</v>
       </c>
       <c r="U10">
-        <v>0.7001500000000001</v>
+        <v>0.699605</v>
       </c>
       <c r="V10">
-        <v>0.6992000000000002</v>
+        <v>0.6981100000000001</v>
       </c>
       <c r="W10">
-        <v>0.6932314819995591</v>
+        <v>0.6912531132119483</v>
       </c>
       <c r="X10">
-        <v>0.7094250000000001</v>
+        <v>0.7088800000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.009881479683554902</v>
+        <v>-0.01193800328478465</v>
       </c>
       <c r="Z10">
-        <v>0.7459318598858135</v>
+        <v>0.900472969062179</v>
       </c>
       <c r="AA10">
-        <v>0.009881479683554902</v>
+        <v>0.01193800328478465</v>
       </c>
       <c r="AB10">
-        <v>0.449990578844313</v>
+        <v>0.4457608041992391</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3500094211556871</v>
+        <v>0.3542391958007609</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2135,55 +2111,55 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01324716132257382</v>
+        <v>0.01325748100713983</v>
       </c>
       <c r="AJ10">
-        <v>37743.9353099728</v>
+        <v>37714.55525606444</v>
       </c>
       <c r="AK10">
-        <v>28307.9514824796</v>
+        <v>28285.91644204833</v>
       </c>
       <c r="AL10">
         <v>40431.26684636092</v>
       </c>
       <c r="AM10">
-        <v>283.079514824796</v>
+        <v>282.8591644204833</v>
       </c>
       <c r="AN10">
-        <v>0.00283079514824796</v>
+        <v>0.002828591644204833</v>
       </c>
       <c r="AO10">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.03038856311542163</v>
+        <v>0.02956930420277445</v>
       </c>
       <c r="AR10">
-        <v>0.01320095170365907</v>
+        <v>0.01251428572245282</v>
       </c>
       <c r="AS10">
-        <v>0.02922594202116263</v>
+        <v>0.02590870807622483</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2167,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46219</v>
+        <v>46221</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2206,79 +2182,79 @@
         <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.634135471833873</v>
+        <v>1.776246315865284</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4059.21</v>
+        <v>3988.32</v>
       </c>
       <c r="S11">
-        <v>3902.871674423247</v>
+        <v>3774.557199536824</v>
       </c>
       <c r="T11">
-        <v>3771.50619247565</v>
+        <v>3624.88918016857</v>
       </c>
       <c r="U11">
-        <v>4059.21</v>
+        <v>3988.32</v>
       </c>
       <c r="V11">
-        <v>3958.16</v>
+        <v>3816.38</v>
       </c>
       <c r="W11">
-        <v>3902.871674423247</v>
+        <v>3774.557199536824</v>
       </c>
       <c r="X11">
-        <v>4203.4075</v>
+        <v>4135.4125</v>
       </c>
       <c r="Y11">
-        <v>-0.03851447093812664</v>
+        <v>-0.05359720395133202</v>
       </c>
       <c r="Z11">
-        <v>1.084195811832751</v>
+        <v>1.453254247926826</v>
       </c>
       <c r="AA11">
-        <v>0.03851447093812664</v>
+        <v>0.05359720395133202</v>
       </c>
       <c r="AB11">
-        <v>0.4044831797331777</v>
+        <v>0.3979867052126335</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3955168202668224</v>
+        <v>0.4020132947873666</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2290,22 +2266,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03552353783125288</v>
+        <v>0.03688081698559791</v>
       </c>
       <c r="AJ11">
-        <v>14075.17467362472</v>
+        <v>13557.18340500027</v>
       </c>
       <c r="AK11">
-        <v>10556.38100521854</v>
+        <v>10167.8875537502</v>
       </c>
       <c r="AL11">
-        <v>2.600599871703739</v>
+        <v>2.549416183693936</v>
       </c>
       <c r="AM11">
-        <v>105.5638100521854</v>
+        <v>101.678875537502</v>
       </c>
       <c r="AN11">
-        <v>0.001055638100521854</v>
+        <v>0.00101678875537502</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2314,31 +2290,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>545.1828031561096</v>
+        <v>552.0505702810731</v>
       </c>
       <c r="AR11">
-        <v>280.8282397589354</v>
+        <v>270.3482840688273</v>
       </c>
       <c r="AS11">
-        <v>320.9517304827621</v>
+        <v>270.9071435162136</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04188345169470575</v>
+        <v>0.02218542471574859</v>
       </c>
       <c r="AV11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46247</v>
+        <v>46249</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,12 +169,12 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05125,naive=0.01349,drift4=0.01994; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1045,naive=0.0286,drift4=0.05282; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3303,naive=0.0892,drift4=0.1091; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05646,naive=0.01952,drift4=0.03423; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.4115,naive=0.122,drift4=0.2029; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03929,naive=0.01365,drift4=0.02012; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.171,naive=0.08865,drift4=0.1234; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.12,naive=1.682,drift4=2.405; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03,naive=0.01361,drift4=0.02098; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=732.4,naive=252.3,drift4=271.6; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.102,naive=0.02744,drift4=0.05269; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05092,naive=0.01339,drift4=0.01927; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3294,naive=0.08744,drift4=0.1083; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05643,naive=0.01877,drift4=0.03307; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3941,naive=0.1192,drift4=0.1988; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03951,naive=0.01374,drift4=0.02026; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1646,naive=0.08841,drift4=0.1199; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.176,naive=1.629,drift4=2.287; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03042,naive=0.0133,drift4=0.01963; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=736.1,naive=252.1,drift4=273.2; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K2">
-        <v>0.461548057468464</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.289547499566908</v>
+        <v>0.9616218022766068</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.144395</v>
+        <v>6.77712</v>
       </c>
       <c r="S2">
-        <v>1.145293198657527</v>
+        <v>6.777862916361046</v>
       </c>
       <c r="T2">
-        <v>1.148856031324252</v>
+        <v>6.783541088320776</v>
       </c>
       <c r="U2">
-        <v>1.144395</v>
+        <v>6.77712</v>
       </c>
       <c r="V2">
-        <v>1.14199</v>
+        <v>6.77154</v>
       </c>
       <c r="Y2">
-        <v>0.0007848676877539316</v>
+        <v>0.0001096212492985807</v>
       </c>
       <c r="AA2">
-        <v>0.0007848676877539316</v>
+        <v>0.0001096212492985807</v>
       </c>
       <c r="AB2">
-        <v>0.4110378360143142</v>
+        <v>0.4338703475776942</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3889621639856858</v>
+        <v>0.3661296524223058</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.04540466663796382</v>
+        <v>0.1023629249995831</v>
       </c>
       <c r="AR2">
-        <v>0.01383051365861976</v>
+        <v>0.0227401843517806</v>
       </c>
       <c r="AS2">
-        <v>0.02291455803527424</v>
+        <v>0.04794001805420357</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -975,19 +975,19 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.5201522974967753</v>
       </c>
       <c r="L3">
-        <v>0.9445277784560701</v>
+        <v>1.324320737734512</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>6.77381</v>
+        <v>1.143045</v>
       </c>
       <c r="S3">
-        <v>6.775192700263536</v>
+        <v>1.143072115092425</v>
       </c>
       <c r="T3">
-        <v>6.784603189579009</v>
+        <v>1.146704996146448</v>
       </c>
       <c r="U3">
-        <v>6.77381</v>
+        <v>1.143045</v>
       </c>
       <c r="V3">
-        <v>6.76492</v>
+        <v>1.13929</v>
       </c>
       <c r="Y3">
-        <v>0.000204124453377877</v>
+        <v>2.37218065994593E-05</v>
       </c>
       <c r="AA3">
-        <v>0.000204124453377877</v>
+        <v>2.37218065994593E-05</v>
       </c>
       <c r="AB3">
-        <v>0.4315713278804829</v>
+        <v>0.4087817488450641</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3684286721195171</v>
+        <v>0.3912182511549359</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.1094098622636678</v>
+        <v>0.04398223880807571</v>
       </c>
       <c r="AR3">
-        <v>0.02409428221325506</v>
+        <v>0.01323706652284412</v>
       </c>
       <c r="AS3">
-        <v>0.05157521569961097</v>
+        <v>0.02025665950607181</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1086,7 +1086,7 @@
         <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,19 +1118,19 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K4">
-        <v>0.2273763052166383</v>
+        <v>0.1918544247572201</v>
       </c>
       <c r="L4">
-        <v>1.738524582408123</v>
+        <v>1.705645373883409</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O4" t="s">
         <v>66</v>
@@ -1142,34 +1142,34 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>7.7489</v>
+        <v>7.7535</v>
       </c>
       <c r="S4">
-        <v>7.744505401938935</v>
+        <v>7.751781178997026</v>
       </c>
       <c r="T4">
-        <v>7.767848520540613</v>
+        <v>7.774487244517255</v>
       </c>
       <c r="U4">
-        <v>7.7489</v>
+        <v>7.7535</v>
       </c>
       <c r="V4">
-        <v>7.719399999999999</v>
+        <v>7.728599999999999</v>
       </c>
       <c r="Y4">
-        <v>-0.0005671254063241395</v>
+        <v>-0.000221683240210678</v>
       </c>
       <c r="AA4">
-        <v>0.0005671254063241395</v>
+        <v>0.000221683240210678</v>
       </c>
       <c r="AB4">
-        <v>0.3964084294965211</v>
+        <v>0.3966500753860352</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4035915705034788</v>
+        <v>0.4033499246139648</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1205,19 +1205,19 @@
         <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0.3050850196490743</v>
+        <v>0.2982602459625821</v>
       </c>
       <c r="AR4">
-        <v>0.09813461755882155</v>
+        <v>0.09043007224362766</v>
       </c>
       <c r="AS4">
-        <v>0.1263181950911947</v>
+        <v>0.1163029290353617</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV4" t="s">
         <v>86</v>
@@ -1229,7 +1229,7 @@
         <v>88</v>
       </c>
       <c r="AY4" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1237,7 +1237,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,19 +1261,19 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.5881446195461555</v>
+        <v>0.5906059774087326</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1285,43 +1285,43 @@
         <v>0.75</v>
       </c>
       <c r="R5">
-        <v>1.34744</v>
+        <v>1.343895</v>
       </c>
       <c r="S5">
-        <v>1.359618703437023</v>
+        <v>1.355625860530824</v>
       </c>
       <c r="T5">
-        <v>1.355285981034613</v>
+        <v>1.353578196836661</v>
       </c>
       <c r="U5">
-        <v>1.34744</v>
+        <v>1.343895</v>
       </c>
       <c r="V5">
-        <v>1.37168</v>
+        <v>1.36459</v>
       </c>
       <c r="W5">
-        <v>1.359618703437023</v>
+        <v>1.355625860530824</v>
       </c>
       <c r="X5">
-        <v>1.33319</v>
+        <v>1.329645</v>
       </c>
       <c r="Y5">
-        <v>0.009038401292096938</v>
+        <v>0.008729000800527119</v>
       </c>
       <c r="Z5">
-        <v>0.8546458552296953</v>
+        <v>0.8232182828648739</v>
       </c>
       <c r="AA5">
-        <v>0.009038401292096938</v>
+        <v>0.008729000800527119</v>
       </c>
       <c r="AB5">
-        <v>0.4399956214645614</v>
+        <v>0.4381788702180791</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3600043785354387</v>
+        <v>0.3618211297819209</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1336,43 +1336,43 @@
         <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01057561004571627</v>
+        <v>0.01060350697041058</v>
       </c>
       <c r="AJ5">
-        <v>47278.59649122831</v>
+        <v>47154.21052631603</v>
       </c>
       <c r="AK5">
-        <v>35458.94736842123</v>
+        <v>35365.65789473702</v>
       </c>
       <c r="AL5">
         <v>26315.78947368434</v>
       </c>
       <c r="AM5">
-        <v>354.5894736842123</v>
+        <v>353.6565789473702</v>
       </c>
       <c r="AN5">
-        <v>0.003545894736842123</v>
+        <v>0.003536565789473702</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ5">
-        <v>0.04959118807570365</v>
+        <v>0.0492498826065657</v>
       </c>
       <c r="AR5">
-        <v>0.01527610689714574</v>
+        <v>0.01442723972287493</v>
       </c>
       <c r="AS5">
-        <v>0.03669449956205958</v>
+        <v>0.03359970812581044</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1384,7 +1384,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1392,7 +1392,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,19 +1416,19 @@
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.09442998547464578</v>
+        <v>0.1161808050671752</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1440,43 +1440,43 @@
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>9.1273</v>
+        <v>9.11858</v>
       </c>
       <c r="S6">
-        <v>9.183442158443132</v>
+        <v>9.176838855063767</v>
       </c>
       <c r="T6">
-        <v>9.125633101608129</v>
+        <v>9.129886112095239</v>
       </c>
       <c r="U6">
-        <v>9.1273</v>
+        <v>9.11858</v>
       </c>
       <c r="V6">
-        <v>9.279730000000001</v>
+        <v>9.26229</v>
       </c>
       <c r="W6">
-        <v>9.183442158443132</v>
+        <v>9.176838855063767</v>
       </c>
       <c r="X6">
-        <v>9.035955</v>
+        <v>9.027234999999999</v>
       </c>
       <c r="Y6">
-        <v>0.006151014916035614</v>
+        <v>0.00638902713621723</v>
       </c>
       <c r="Z6">
-        <v>0.6146166560088878</v>
+        <v>0.637789206456486</v>
       </c>
       <c r="AA6">
-        <v>0.006151014916035614</v>
+        <v>0.00638902713621723</v>
       </c>
       <c r="AB6">
-        <v>0.4270160025514099</v>
+        <v>0.4283042275693946</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.37298399744859</v>
+        <v>0.3716957724306055</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1491,22 +1491,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01000788842264416</v>
+        <v>0.01001745885872581</v>
       </c>
       <c r="AJ6">
-        <v>49960.58897586074</v>
+        <v>49912.85784662542</v>
       </c>
       <c r="AK6">
-        <v>37470.44173189555</v>
+        <v>37434.64338496907</v>
       </c>
       <c r="AL6">
-        <v>4105.315014505445</v>
+        <v>4105.315014505446</v>
       </c>
       <c r="AM6">
-        <v>374.7044173189555</v>
+        <v>374.3464338496906</v>
       </c>
       <c r="AN6">
-        <v>0.003747044173189555</v>
+        <v>0.003743464338496906</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1515,19 +1515,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.4830909789212179</v>
+        <v>0.4660948779410808</v>
       </c>
       <c r="AR6">
-        <v>0.1007624574630314</v>
+        <v>0.09407454098995205</v>
       </c>
       <c r="AS6">
-        <v>0.2235709236814991</v>
+        <v>0.209539390007527</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1539,7 +1539,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1547,7 +1547,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1559,7 +1559,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
@@ -1571,19 +1571,19 @@
         <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K7">
-        <v>0.4621772135232619</v>
+        <v>0.4719928589526362</v>
       </c>
       <c r="L7">
-        <v>1.360413208425827</v>
+        <v>1.365993379372389</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1592,46 +1592,46 @@
         <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.8655443033808154</v>
+        <v>0.8679982147381591</v>
       </c>
       <c r="R7">
-        <v>0.8084899999999999</v>
+        <v>0.8085450000000001</v>
       </c>
       <c r="S7">
-        <v>0.8119967991693238</v>
+        <v>0.8132050904392021</v>
       </c>
       <c r="T7">
-        <v>0.8154198103899284</v>
+        <v>0.8181345486206881</v>
       </c>
       <c r="U7">
-        <v>0.8084899999999999</v>
+        <v>0.8085450000000001</v>
       </c>
       <c r="V7">
-        <v>0.8099799999999998</v>
+        <v>0.8100900000000001</v>
       </c>
       <c r="W7">
-        <v>0.8119967991693238</v>
+        <v>0.8132050904392021</v>
       </c>
       <c r="X7">
-        <v>0.7988149999999999</v>
+        <v>0.7988700000000001</v>
       </c>
       <c r="Y7">
-        <v>0.004337467586888939</v>
+        <v>0.005763551118616791</v>
       </c>
       <c r="Z7">
-        <v>0.3624598624624115</v>
+        <v>0.4816630944911633</v>
       </c>
       <c r="AA7">
-        <v>0.004337467586888939</v>
+        <v>0.005763551118616791</v>
       </c>
       <c r="AB7">
-        <v>0.4255293849229868</v>
+        <v>0.4256410894697438</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3744706150770132</v>
+        <v>0.3743589105302562</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1643,46 +1643,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>432.7721516904077</v>
+        <v>433.9991073690795</v>
       </c>
       <c r="AI7">
-        <v>0.01196675283553293</v>
+        <v>0.01196593881602139</v>
       </c>
       <c r="AJ7">
-        <v>41782.4289405684</v>
+        <v>41785.27131782939</v>
       </c>
       <c r="AK7">
-        <v>36164.5433509227</v>
+        <v>36269.54090622551</v>
       </c>
       <c r="AL7">
-        <v>44730.97175094646</v>
+        <v>44857.78887535698</v>
       </c>
       <c r="AM7">
-        <v>361.645433509227</v>
+        <v>362.6954090622551</v>
       </c>
       <c r="AN7">
-        <v>0.00361645433509227</v>
+        <v>0.003626954090622551</v>
       </c>
       <c r="AO7">
-        <v>432.7721516904077</v>
+        <v>433.9991073690795</v>
       </c>
       <c r="AP7">
-        <v>0.004327721516904077</v>
+        <v>0.004339991073690795</v>
       </c>
       <c r="AQ7">
-        <v>0.03661710140431752</v>
+        <v>0.03596062066777696</v>
       </c>
       <c r="AR7">
-        <v>0.01395770328773555</v>
+        <v>0.01354330327990906</v>
       </c>
       <c r="AS7">
-        <v>0.02224381623116381</v>
+        <v>0.02071324192712968</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1694,7 +1694,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1702,7 +1702,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1753,10 +1753,10 @@
         <v>4.73111</v>
       </c>
       <c r="S8">
-        <v>4.7014358038852</v>
+        <v>4.702356796724415</v>
       </c>
       <c r="T8">
-        <v>4.683806247838432</v>
+        <v>4.685875717614749</v>
       </c>
       <c r="U8">
         <v>4.73111</v>
@@ -1765,28 +1765,28 @@
         <v>4.70687</v>
       </c>
       <c r="W8">
-        <v>4.7014358038852</v>
+        <v>4.702356796724415</v>
       </c>
       <c r="X8">
         <v>4.784135</v>
       </c>
       <c r="Y8">
-        <v>-0.006272142502457126</v>
+        <v>-0.00607747511167249</v>
       </c>
       <c r="Z8">
-        <v>0.5596265179594555</v>
+        <v>0.5422574875169265</v>
       </c>
       <c r="AA8">
-        <v>0.006272142502457126</v>
+        <v>0.00607747511167249</v>
       </c>
       <c r="AB8">
-        <v>0.4458162766739177</v>
+        <v>0.4458929866619997</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3541837233260823</v>
+        <v>0.3541070133380003</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1825,19 +1825,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1696836470694267</v>
+        <v>0.1576945006622805</v>
       </c>
       <c r="AR8">
-        <v>0.087041213406612</v>
+        <v>0.08287876447076031</v>
       </c>
       <c r="AS8">
-        <v>0.156590104085051</v>
+        <v>0.140898912737831</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1849,7 +1849,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1857,7 +1857,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1881,19 +1881,19 @@
         <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K9">
-        <v>0.07588101400851993</v>
+        <v>0.1045663857225371</v>
       </c>
       <c r="L9">
-        <v>1.59810554341032</v>
+        <v>1.626162787168392</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" t="s">
         <v>72</v>
@@ -1902,46 +1902,46 @@
         <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.94308923949361</v>
+        <v>0.9215752107080972</v>
       </c>
       <c r="R9">
-        <v>162.4215</v>
+        <v>162.444</v>
       </c>
       <c r="S9">
-        <v>160.9475192514668</v>
+        <v>160.9896839612005</v>
       </c>
       <c r="T9">
-        <v>157.876568445119</v>
+        <v>157.8716282226711</v>
       </c>
       <c r="U9">
-        <v>162.4215</v>
+        <v>162.444</v>
       </c>
       <c r="V9">
-        <v>163.563</v>
+        <v>163.608</v>
       </c>
       <c r="W9">
-        <v>160.9475192514668</v>
+        <v>160.9896839612005</v>
       </c>
       <c r="X9">
-        <v>164.2965</v>
+        <v>164.319</v>
       </c>
       <c r="Y9">
-        <v>-0.009075034700044332</v>
+        <v>-0.00895272240771882</v>
       </c>
       <c r="Z9">
-        <v>0.7861230658843973</v>
+        <v>0.7756352206930509</v>
       </c>
       <c r="AA9">
-        <v>0.009075034700044332</v>
+        <v>0.00895272240771882</v>
       </c>
       <c r="AB9">
-        <v>0.4198029511995399</v>
+        <v>0.4158579902766131</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3801970488004601</v>
+        <v>0.384142009723387</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1953,46 +1953,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>471.544619746805</v>
+        <v>460.7876053540486</v>
       </c>
       <c r="AI9">
-        <v>0.01154403819691363</v>
+        <v>0.01154243924059988</v>
       </c>
       <c r="AJ9">
-        <v>43312.39999999984</v>
+        <v>43318.39999999983</v>
       </c>
       <c r="AK9">
-        <v>40847.45837664288</v>
+        <v>39921.16360753748</v>
       </c>
       <c r="AL9">
-        <v>251.4904638649617</v>
+        <v>245.7533895221583</v>
       </c>
       <c r="AM9">
-        <v>408.4745837664289</v>
+        <v>399.2116360753748</v>
       </c>
       <c r="AN9">
-        <v>0.004084745837664289</v>
+        <v>0.003992116360753748</v>
       </c>
       <c r="AO9">
-        <v>471.544619746805</v>
+        <v>460.7876053540486</v>
       </c>
       <c r="AP9">
-        <v>0.00471544619746805</v>
+        <v>0.004607876053540486</v>
       </c>
       <c r="AQ9">
-        <v>4.323167120146226</v>
+        <v>4.299419128950889</v>
       </c>
       <c r="AR9">
-        <v>1.87367454634048</v>
+        <v>1.768968739459159</v>
       </c>
       <c r="AS9">
-        <v>3.257601245699296</v>
+        <v>2.981066461994629</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2004,7 +2004,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2012,7 +2012,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,19 +2036,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.819862375895185</v>
+        <v>0.850549069690636</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
@@ -2060,43 +2060,43 @@
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>0.699605</v>
+        <v>0.6966950000000001</v>
       </c>
       <c r="S10">
-        <v>0.6912531132119483</v>
+        <v>0.6875141377034354</v>
       </c>
       <c r="T10">
-        <v>0.6820568012426382</v>
+        <v>0.6794209281319635</v>
       </c>
       <c r="U10">
-        <v>0.699605</v>
+        <v>0.6966950000000001</v>
       </c>
       <c r="V10">
-        <v>0.6981100000000001</v>
+        <v>0.6922900000000002</v>
       </c>
       <c r="W10">
-        <v>0.6912531132119483</v>
+        <v>0.6875141377034354</v>
       </c>
       <c r="X10">
-        <v>0.7088800000000001</v>
+        <v>0.7059700000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.01193800328478465</v>
+        <v>-0.01317773530248484</v>
       </c>
       <c r="Z10">
-        <v>0.900472969062179</v>
+        <v>0.9898503823789341</v>
       </c>
       <c r="AA10">
-        <v>0.01193800328478465</v>
+        <v>0.01317773530248484</v>
       </c>
       <c r="AB10">
-        <v>0.4457608041992391</v>
+        <v>0.4395703400036883</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3542391958007609</v>
+        <v>0.3604296599963117</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2111,22 +2111,22 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01325748100713983</v>
+        <v>0.01331285569725642</v>
       </c>
       <c r="AJ10">
-        <v>37714.55525606444</v>
+        <v>37557.68194070057</v>
       </c>
       <c r="AK10">
-        <v>28285.91644204833</v>
+        <v>28168.26145552543</v>
       </c>
       <c r="AL10">
         <v>40431.26684636092</v>
       </c>
       <c r="AM10">
-        <v>282.8591644204833</v>
+        <v>281.6826145552542</v>
       </c>
       <c r="AN10">
-        <v>0.002828591644204833</v>
+        <v>0.002816826145552542</v>
       </c>
       <c r="AO10">
         <v>375</v>
@@ -2135,19 +2135,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.02956930420277445</v>
+        <v>0.02896720922803718</v>
       </c>
       <c r="AR10">
-        <v>0.01251428572245282</v>
+        <v>0.01223005364037288</v>
       </c>
       <c r="AS10">
-        <v>0.02590870807622483</v>
+        <v>0.023078654805039</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2159,7 +2159,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2167,7 +2167,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46221</v>
+        <v>46223</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2218,10 +2218,10 @@
         <v>3988.32</v>
       </c>
       <c r="S11">
-        <v>3774.557199536824</v>
+        <v>3774.105012850006</v>
       </c>
       <c r="T11">
-        <v>3624.88918016857</v>
+        <v>3623.878659437742</v>
       </c>
       <c r="U11">
         <v>3988.32</v>
@@ -2230,28 +2230,28 @@
         <v>3816.38</v>
       </c>
       <c r="W11">
-        <v>3774.557199536824</v>
+        <v>3774.105012850006</v>
       </c>
       <c r="X11">
         <v>4135.4125</v>
       </c>
       <c r="Y11">
-        <v>-0.05359720395133202</v>
+        <v>-0.05371058168602161</v>
       </c>
       <c r="Z11">
-        <v>1.453254247926826</v>
+        <v>1.456328413413287</v>
       </c>
       <c r="AA11">
-        <v>0.05359720395133202</v>
+        <v>0.05371058168602161</v>
       </c>
       <c r="AB11">
-        <v>0.3979867052126335</v>
+        <v>0.3982465105233899</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4020132947873666</v>
+        <v>0.4017534894766102</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2290,19 +2290,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>552.0505702810731</v>
+        <v>551.6399570454053</v>
       </c>
       <c r="AR11">
-        <v>270.3482840688273</v>
+        <v>255.8839031689911</v>
       </c>
       <c r="AS11">
-        <v>270.9071435162136</v>
+        <v>234.7852721118961</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.02218542471574859</v>
+        <v>0.02207862071365497</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2314,7 +2314,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>Pair</t>
   </si>
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>LOW</t>
   </si>
   <si>
@@ -229,10 +229,13 @@
     <t>UP</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>NO_SIGNAL</t>
@@ -244,34 +247,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.102,naive=0.02744,drift4=0.05269; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.05092,naive=0.01339,drift4=0.01927; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3294,naive=0.08744,drift4=0.1083; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05643,naive=0.01877,drift4=0.03307; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3941,naive=0.1192,drift4=0.1988; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03951,naive=0.01374,drift4=0.02026; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1646,naive=0.08841,drift4=0.1199; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=5.176,naive=1.629,drift4=2.287; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03042,naive=0.0133,drift4=0.01963; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=736.1,naive=252.1,drift4=273.2; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05944,naive=0.01208,drift4=0.0174; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.338,naive=0.07493,drift4=0.09517; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.06157,naive=0.01801,drift4=0.02937; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03738,naive=0.01302,drift4=0.01854; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3453,naive=0.1073,drift4=0.1757; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1407,naive=0.07977,drift4=0.1112; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02998,naive=0.01262,drift4=0.01851; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=6.038,naive=1.477,drift4=1.749; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09504,naive=0.02508,drift4=0.05013; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=669.1,naive=240.2,drift4=260.7; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +811,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,28 +829,28 @@
         <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.6882994163513212</v>
       </c>
       <c r="L2">
-        <v>0.9616218022766068</v>
+        <v>1.423627092272378</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P2" t="s">
         <v>73</v>
@@ -856,37 +859,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>6.77712</v>
+        <v>1.141505</v>
       </c>
       <c r="S2">
-        <v>6.777862916361046</v>
+        <v>1.150782554601837</v>
       </c>
       <c r="T2">
-        <v>6.783541088320776</v>
+        <v>1.161606595196639</v>
       </c>
       <c r="U2">
-        <v>6.77712</v>
+        <v>1.141505</v>
       </c>
       <c r="V2">
-        <v>6.77154</v>
+        <v>1.14471</v>
       </c>
       <c r="Y2">
-        <v>0.0001096212492985807</v>
+        <v>0.008127476096764058</v>
       </c>
       <c r="AA2">
-        <v>0.0001096212492985807</v>
+        <v>0.008127476096764058</v>
       </c>
       <c r="AB2">
-        <v>0.4338703475776942</v>
+        <v>0.3973318010939917</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3661296524223058</v>
+        <v>0.4026681989060083</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -919,31 +922,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.1023629249995831</v>
+        <v>0.04128718059009557</v>
       </c>
       <c r="AR2">
-        <v>0.0227401843517806</v>
+        <v>0.01004184426961693</v>
       </c>
       <c r="AS2">
-        <v>0.04794001805420357</v>
+        <v>0.0148217063138117</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +954,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,7 +966,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -975,61 +978,61 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K3">
-        <v>0.5201522974967753</v>
+        <v>0.2983132593948509</v>
       </c>
       <c r="L3">
-        <v>1.324320737734512</v>
+        <v>1.811908380628527</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>42</v>
+        <v>109</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>1.143045</v>
+        <v>7.7264</v>
       </c>
       <c r="S3">
-        <v>1.143072115092425</v>
+        <v>7.731954897738209</v>
       </c>
       <c r="T3">
-        <v>1.146704996146448</v>
+        <v>7.761050764821054</v>
       </c>
       <c r="U3">
-        <v>1.143045</v>
+        <v>7.7264</v>
       </c>
       <c r="V3">
-        <v>1.13929</v>
+        <v>7.7069</v>
       </c>
       <c r="Y3">
-        <v>2.37218065994593E-05</v>
+        <v>0.0007189503181571189</v>
       </c>
       <c r="AA3">
-        <v>2.37218065994593E-05</v>
+        <v>0.0007189503181571189</v>
       </c>
       <c r="AB3">
-        <v>0.4087817488450641</v>
+        <v>0.3906666472415808</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3912182511549359</v>
+        <v>0.4093333527584192</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1062,31 +1065,31 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.04398223880807571</v>
+        <v>0.256222125751404</v>
       </c>
       <c r="AR3">
-        <v>0.01323706652284412</v>
+        <v>0.06601860447056108</v>
       </c>
       <c r="AS3">
-        <v>0.02025665950607181</v>
+        <v>0.0875753592692303</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1097,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1109,70 +1112,79 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K4">
-        <v>0.1918544247572201</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.705645373883409</v>
+        <v>0.5791583796555356</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="O4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>7.7535</v>
+        <v>1.343005</v>
       </c>
       <c r="S4">
-        <v>7.751781178997026</v>
+        <v>1.366353347309209</v>
       </c>
       <c r="T4">
-        <v>7.774487244517255</v>
+        <v>1.377741759125278</v>
       </c>
       <c r="U4">
-        <v>7.7535</v>
+        <v>1.343005</v>
       </c>
       <c r="V4">
-        <v>7.728599999999999</v>
+        <v>1.36591</v>
+      </c>
+      <c r="W4">
+        <v>1.366353347309209</v>
+      </c>
+      <c r="X4">
+        <v>1.327439435127194</v>
       </c>
       <c r="Y4">
-        <v>-0.000221683240210678</v>
+        <v>0.01738515292884885</v>
+      </c>
+      <c r="Z4">
+        <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.000221683240210678</v>
+        <v>0.01738515292884885</v>
       </c>
       <c r="AB4">
-        <v>0.3966500753860352</v>
+        <v>0.4246492221494385</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4033499246139648</v>
+        <v>0.3753507778505615</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1181,55 +1193,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI4">
+        <v>0.0115901019525659</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>43140.25899395185</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>32355.19424546389</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>24091.64094360326</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>323.5519424546389</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.003235519424546389</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.2982602459625821</v>
+        <v>0.0439207561070098</v>
       </c>
       <c r="AR4">
-        <v>0.09043007224362766</v>
+        <v>0.01132704751140213</v>
       </c>
       <c r="AS4">
-        <v>0.1163029290353617</v>
+        <v>0.02613520469750388</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY4" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1237,7 +1252,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1249,7 +1264,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1261,70 +1276,70 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.5585486117996296</v>
       </c>
       <c r="L5">
-        <v>0.5906059774087326</v>
+        <v>1.425604946971071</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>0.8896371529499074</v>
       </c>
       <c r="R5">
-        <v>1.343895</v>
+        <v>0.8101700000000001</v>
       </c>
       <c r="S5">
-        <v>1.355625860530824</v>
+        <v>0.8172471288364973</v>
       </c>
       <c r="T5">
-        <v>1.353578196836661</v>
+        <v>0.8264028056305028</v>
       </c>
       <c r="U5">
-        <v>1.343895</v>
+        <v>0.8101700000000001</v>
       </c>
       <c r="V5">
-        <v>1.36459</v>
+        <v>0.8107400000000001</v>
       </c>
       <c r="W5">
-        <v>1.355625860530824</v>
+        <v>0.8172471288364973</v>
       </c>
       <c r="X5">
-        <v>1.329645</v>
+        <v>0.801795</v>
       </c>
       <c r="Y5">
-        <v>0.008729000800527119</v>
+        <v>0.008735362746704084</v>
       </c>
       <c r="Z5">
-        <v>0.8232182828648739</v>
+        <v>0.8450303088354874</v>
       </c>
       <c r="AA5">
-        <v>0.008729000800527119</v>
+        <v>0.008735362746704084</v>
       </c>
       <c r="AB5">
-        <v>0.4381788702180791</v>
+        <v>0.4227294261765532</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3618211297819209</v>
+        <v>0.3772705738234468</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1333,58 +1348,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>444.8185764749537</v>
       </c>
       <c r="AI5">
-        <v>0.01060350697041058</v>
+        <v>0.01033733660836621</v>
       </c>
       <c r="AJ5">
-        <v>47154.21052631603</v>
+        <v>48368.35820895495</v>
       </c>
       <c r="AK5">
-        <v>35365.65789473702</v>
+        <v>43030.28848987596</v>
       </c>
       <c r="AL5">
-        <v>26315.78947368434</v>
+        <v>53112.66584775536</v>
       </c>
       <c r="AM5">
-        <v>353.6565789473702</v>
+        <v>430.3028848987596</v>
       </c>
       <c r="AN5">
-        <v>0.003536565789473702</v>
+        <v>0.004303028848987596</v>
       </c>
       <c r="AO5">
-        <v>375.0000000000001</v>
+        <v>444.8185764749537</v>
       </c>
       <c r="AP5">
-        <v>0.003750000000000001</v>
+        <v>0.004448185764749537</v>
       </c>
       <c r="AQ5">
-        <v>0.0492498826065657</v>
+        <v>0.031288216814724</v>
       </c>
       <c r="AR5">
-        <v>0.01442723972287493</v>
+        <v>0.01086625281332157</v>
       </c>
       <c r="AS5">
-        <v>0.03359970812581044</v>
+        <v>0.01540151984546945</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY5" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1392,7 +1407,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,70 +1431,70 @@
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.1161808050671752</v>
+        <v>0.05138742086143865</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>9.11858</v>
+        <v>9.088609999999999</v>
       </c>
       <c r="S6">
-        <v>9.176838855063767</v>
+        <v>9.142937643996792</v>
       </c>
       <c r="T6">
-        <v>9.129886112095239</v>
+        <v>9.123811610440452</v>
       </c>
       <c r="U6">
-        <v>9.11858</v>
+        <v>9.088609999999999</v>
       </c>
       <c r="V6">
-        <v>9.26229</v>
+        <v>9.194199999999999</v>
       </c>
       <c r="W6">
-        <v>9.176838855063767</v>
+        <v>9.142937643996792</v>
       </c>
       <c r="X6">
-        <v>9.027234999999999</v>
+        <v>9.001267499999999</v>
       </c>
       <c r="Y6">
-        <v>0.00638902713621723</v>
+        <v>0.005977552562690288</v>
       </c>
       <c r="Z6">
-        <v>0.637789206456486</v>
+        <v>0.6220069725138712</v>
       </c>
       <c r="AA6">
-        <v>0.00638902713621723</v>
+        <v>0.005977552562690288</v>
       </c>
       <c r="AB6">
-        <v>0.4283042275693946</v>
+        <v>0.4282575037138154</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3716957724306055</v>
+        <v>0.3717424962861847</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1491,22 +1506,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01001745885872581</v>
+        <v>0.009610105395654524</v>
       </c>
       <c r="AJ6">
-        <v>49912.85784662542</v>
+        <v>52028.56570398165</v>
       </c>
       <c r="AK6">
-        <v>37434.64338496907</v>
+        <v>39021.42427798624</v>
       </c>
       <c r="AL6">
-        <v>4105.315014505446</v>
+        <v>4293.44248218223</v>
       </c>
       <c r="AM6">
-        <v>374.3464338496906</v>
+        <v>390.2142427798624</v>
       </c>
       <c r="AN6">
-        <v>0.003743464338496906</v>
+        <v>0.003902142427798624</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1515,31 +1530,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.4660948779410808</v>
+        <v>0.4033883530590582</v>
       </c>
       <c r="AR6">
-        <v>0.09407454098995205</v>
+        <v>0.06719336682309301</v>
       </c>
       <c r="AS6">
-        <v>0.209539390007527</v>
+        <v>0.1700399202598371</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW6" t="s">
         <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY6" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1547,7 +1562,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1568,73 +1583,73 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K7">
-        <v>0.4719928589526362</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.365993379372389</v>
+        <v>0.6710355043976531</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q7">
-        <v>0.8679982147381591</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>0.8085450000000001</v>
+        <v>4.73382</v>
       </c>
       <c r="S7">
-        <v>0.8132050904392021</v>
+        <v>4.741179356582096</v>
       </c>
       <c r="T7">
-        <v>0.8181345486206881</v>
+        <v>4.718901026373057</v>
       </c>
       <c r="U7">
-        <v>0.8085450000000001</v>
+        <v>4.73382</v>
       </c>
       <c r="V7">
-        <v>0.8100900000000001</v>
+        <v>4.774369999999999</v>
       </c>
       <c r="W7">
-        <v>0.8132050904392021</v>
+        <v>4.741179356582096</v>
       </c>
       <c r="X7">
-        <v>0.7988700000000001</v>
+        <v>4.685605</v>
       </c>
       <c r="Y7">
-        <v>0.005763551118616791</v>
+        <v>0.001554633801474583</v>
       </c>
       <c r="Z7">
-        <v>0.4816630944911633</v>
+        <v>0.1526362456102131</v>
       </c>
       <c r="AA7">
-        <v>0.005763551118616791</v>
+        <v>0.001554633801474583</v>
       </c>
       <c r="AB7">
-        <v>0.4256410894697438</v>
+        <v>0.4521562556138915</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3743589105302562</v>
+        <v>0.3478437443861085</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1643,58 +1658,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>433.9991073690795</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01196593881602139</v>
+        <v>0.01018522039283283</v>
       </c>
       <c r="AJ7">
-        <v>41785.27131782939</v>
+        <v>49090.73939645349</v>
       </c>
       <c r="AK7">
-        <v>36269.54090622551</v>
+        <v>49090.73939645349</v>
       </c>
       <c r="AL7">
-        <v>44857.78887535698</v>
+        <v>10370.21673752984</v>
       </c>
       <c r="AM7">
-        <v>362.6954090622551</v>
+        <v>490.9073939645348</v>
       </c>
       <c r="AN7">
-        <v>0.003626954090622551</v>
+        <v>0.004909073939645348</v>
       </c>
       <c r="AO7">
-        <v>433.9991073690795</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.004339991073690795</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.03596062066777696</v>
+        <v>0.129231400511493</v>
       </c>
       <c r="AR7">
-        <v>0.01354330327990906</v>
+        <v>0.06052145342805362</v>
       </c>
       <c r="AS7">
-        <v>0.02071324192712968</v>
+        <v>0.09210243007359289</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW7" t="s">
         <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY7" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1702,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,70 +1741,70 @@
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.7226452061373857</v>
+        <v>0.6470560086710306</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>4.73111</v>
+        <v>0.699945</v>
       </c>
       <c r="S8">
-        <v>4.702356796724415</v>
+        <v>0.6984410886178472</v>
       </c>
       <c r="T8">
-        <v>4.685875717614749</v>
+        <v>0.6879766175609653</v>
       </c>
       <c r="U8">
-        <v>4.73111</v>
+        <v>0.699945</v>
       </c>
       <c r="V8">
-        <v>4.70687</v>
+        <v>0.7101900000000001</v>
       </c>
       <c r="W8">
-        <v>4.702356796724415</v>
+        <v>0.6984410886178472</v>
       </c>
       <c r="X8">
-        <v>4.784135</v>
+        <v>0.7078200000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.00607747511167249</v>
+        <v>-0.002148613651291015</v>
       </c>
       <c r="Z8">
-        <v>0.5422574875169265</v>
+        <v>0.1909728739241753</v>
       </c>
       <c r="AA8">
-        <v>0.00607747511167249</v>
+        <v>0.002148613651291015</v>
       </c>
       <c r="AB8">
-        <v>0.4458929866619997</v>
+        <v>0.4366697151491715</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3541070133380003</v>
+        <v>0.3633302848508286</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1801,22 +1816,22 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01120772926437975</v>
+        <v>0.01125088399802849</v>
       </c>
       <c r="AJ8">
-        <v>44612.0697784067</v>
+        <v>44440.95238095211</v>
       </c>
       <c r="AK8">
-        <v>33459.05233380503</v>
+        <v>33330.71428571408</v>
       </c>
       <c r="AL8">
-        <v>7072.135785007118</v>
+        <v>47619.04761904732</v>
       </c>
       <c r="AM8">
-        <v>334.5905233380503</v>
+        <v>333.3071428571408</v>
       </c>
       <c r="AN8">
-        <v>0.003345905233380503</v>
+        <v>0.003333071428571408</v>
       </c>
       <c r="AO8">
         <v>375</v>
@@ -1825,31 +1840,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1576945006622805</v>
+        <v>0.02615412222150581</v>
       </c>
       <c r="AR8">
-        <v>0.08287876447076031</v>
+        <v>0.009318327365775959</v>
       </c>
       <c r="AS8">
-        <v>0.140898912737831</v>
+        <v>0.01546589341353431</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW8" t="s">
         <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY8" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1857,7 +1872,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1869,7 +1884,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1881,70 +1896,70 @@
         <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K9">
-        <v>0.1045663857225371</v>
+        <v>0.2357537202218213</v>
       </c>
       <c r="L9">
-        <v>1.626162787168392</v>
+        <v>1.743477961427452</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q9">
-        <v>0.9215752107080972</v>
+        <v>0.823184709833634</v>
       </c>
       <c r="R9">
-        <v>162.444</v>
+        <v>162.4865</v>
       </c>
       <c r="S9">
-        <v>160.9896839612005</v>
+        <v>161.5238313118946</v>
       </c>
       <c r="T9">
-        <v>157.8716282226711</v>
+        <v>159.2145259793521</v>
       </c>
       <c r="U9">
-        <v>162.444</v>
+        <v>162.4865</v>
       </c>
       <c r="V9">
-        <v>163.608</v>
+        <v>163.243</v>
       </c>
       <c r="W9">
-        <v>160.9896839612005</v>
+        <v>161.5238313118946</v>
       </c>
       <c r="X9">
-        <v>164.319</v>
+        <v>164.064</v>
       </c>
       <c r="Y9">
-        <v>-0.00895272240771882</v>
+        <v>-0.005924607201862457</v>
       </c>
       <c r="Z9">
-        <v>0.7756352206930509</v>
+        <v>0.6102495645676275</v>
       </c>
       <c r="AA9">
-        <v>0.00895272240771882</v>
+        <v>0.005924607201862457</v>
       </c>
       <c r="AB9">
-        <v>0.4158579902766131</v>
+        <v>0.3891966734970436</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.384142009723387</v>
+        <v>0.4108033265029565</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1953,58 +1968,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>460.7876053540486</v>
+        <v>411.592354916817</v>
       </c>
       <c r="AI9">
-        <v>0.01154243924059988</v>
+        <v>0.0097084988599052</v>
       </c>
       <c r="AJ9">
-        <v>43318.39999999983</v>
+        <v>51501.26782884355</v>
       </c>
       <c r="AK9">
-        <v>39921.16360753748</v>
+        <v>42395.05621375085</v>
       </c>
       <c r="AL9">
-        <v>245.7533895221583</v>
+        <v>260.9143295827705</v>
       </c>
       <c r="AM9">
-        <v>399.2116360753748</v>
+        <v>423.9505621375085</v>
       </c>
       <c r="AN9">
-        <v>0.003992116360753748</v>
+        <v>0.004239505621375085</v>
       </c>
       <c r="AO9">
-        <v>460.7876053540486</v>
+        <v>411.592354916817</v>
       </c>
       <c r="AP9">
-        <v>0.004607876053540486</v>
+        <v>0.00411592354916817</v>
       </c>
       <c r="AQ9">
-        <v>4.299419128950889</v>
+        <v>4.363485639693498</v>
       </c>
       <c r="AR9">
-        <v>1.768968739459159</v>
+        <v>1.33216590990505</v>
       </c>
       <c r="AS9">
-        <v>2.981066461994629</v>
+        <v>1.982915173165015</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW9" t="s">
         <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY9" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2012,7 +2027,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,70 +2051,70 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.850549069690636</v>
+        <v>1.128653120691019</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>0.6966950000000001</v>
+        <v>6.76801</v>
       </c>
       <c r="S10">
-        <v>0.6875141377034354</v>
+        <v>6.718901372271469</v>
       </c>
       <c r="T10">
-        <v>0.6794209281319635</v>
+        <v>6.686105841683576</v>
       </c>
       <c r="U10">
-        <v>0.6966950000000001</v>
+        <v>6.76801</v>
       </c>
       <c r="V10">
-        <v>0.6922900000000002</v>
+        <v>6.73122</v>
       </c>
       <c r="W10">
-        <v>0.6875141377034354</v>
+        <v>6.718901372271469</v>
       </c>
       <c r="X10">
-        <v>0.7059700000000001</v>
+        <v>6.800749085152354</v>
       </c>
       <c r="Y10">
-        <v>-0.01317773530248484</v>
+        <v>-0.007255992193943399</v>
       </c>
       <c r="Z10">
-        <v>0.9898503823789341</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.01317773530248484</v>
+        <v>0.007255992193943399</v>
       </c>
       <c r="AB10">
-        <v>0.4395703400036883</v>
+        <v>0.4361519412713491</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3604296599963117</v>
+        <v>0.3638480587286509</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2111,22 +2126,22 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01331285569725642</v>
+        <v>0.004837328129295599</v>
       </c>
       <c r="AJ10">
-        <v>37557.68194070057</v>
+        <v>103362.8454873515</v>
       </c>
       <c r="AK10">
-        <v>28168.26145552543</v>
+        <v>77522.13411551362</v>
       </c>
       <c r="AL10">
-        <v>40431.26684636092</v>
+        <v>11454.19910956302</v>
       </c>
       <c r="AM10">
-        <v>281.6826145552542</v>
+        <v>775.2213411551362</v>
       </c>
       <c r="AN10">
-        <v>0.002816826145552542</v>
+        <v>0.007752213411551362</v>
       </c>
       <c r="AO10">
         <v>375</v>
@@ -2135,31 +2150,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.02896720922803718</v>
+        <v>0.08698928368690512</v>
       </c>
       <c r="AR10">
-        <v>0.01223005364037288</v>
+        <v>0.01789265732926622</v>
       </c>
       <c r="AS10">
-        <v>0.023078654805039</v>
+        <v>0.0433557201078804</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW10" t="s">
         <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY10" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2167,7 +2182,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2191,70 +2206,70 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.776246315865284</v>
+        <v>1.879864558389473</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>3988.32</v>
+        <v>4007.2</v>
       </c>
       <c r="S11">
-        <v>3774.105012850006</v>
+        <v>3863.232468543733</v>
       </c>
       <c r="T11">
-        <v>3623.878659437742</v>
+        <v>3729.799310204706</v>
       </c>
       <c r="U11">
-        <v>3988.32</v>
+        <v>4007.2</v>
       </c>
       <c r="V11">
-        <v>3816.38</v>
+        <v>3925.139999999999</v>
       </c>
       <c r="W11">
-        <v>3774.105012850006</v>
+        <v>3863.232468543733</v>
       </c>
       <c r="X11">
-        <v>4135.4125</v>
+        <v>4137.065</v>
       </c>
       <c r="Y11">
-        <v>-0.05371058168602161</v>
+        <v>-0.03592721387908426</v>
       </c>
       <c r="Z11">
-        <v>1.456328413413287</v>
+        <v>1.108593781667628</v>
       </c>
       <c r="AA11">
-        <v>0.05371058168602161</v>
+        <v>0.03592721387908426</v>
       </c>
       <c r="AB11">
-        <v>0.3982465105233899</v>
+        <v>0.4009381329529487</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4017534894766102</v>
+        <v>0.3990618670470513</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2266,22 +2281,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03688081698559791</v>
+        <v>0.03240791575164701</v>
       </c>
       <c r="AJ11">
-        <v>13557.18340500027</v>
+        <v>15428.32941901206</v>
       </c>
       <c r="AK11">
-        <v>10167.8875537502</v>
+        <v>11571.24706425905</v>
       </c>
       <c r="AL11">
-        <v>2.549416183693936</v>
+        <v>2.887614060755402</v>
       </c>
       <c r="AM11">
-        <v>101.678875537502</v>
+        <v>115.7124706425905</v>
       </c>
       <c r="AN11">
-        <v>0.00101678875537502</v>
+        <v>0.001157124706425905</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2290,31 +2305,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>551.6399570454053</v>
+        <v>476.7432013754182</v>
       </c>
       <c r="AR11">
-        <v>255.8839031689911</v>
+        <v>201.9691121176079</v>
       </c>
       <c r="AS11">
-        <v>234.7852721118961</v>
+        <v>210.7592443949108</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.02207862071365497</v>
+        <v>0.03283167980890172</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW11" t="s">
         <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY11" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -247,34 +247,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05944,naive=0.01208,drift4=0.0174; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.338,naive=0.07493,drift4=0.09517; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.06157,naive=0.01801,drift4=0.02937; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03738,naive=0.01302,drift4=0.01854; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3453,naive=0.1073,drift4=0.1757; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1407,naive=0.07977,drift4=0.1112; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02998,naive=0.01262,drift4=0.01851; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=6.038,naive=1.477,drift4=1.749; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09504,naive=0.02508,drift4=0.05013; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=669.1,naive=240.2,drift4=260.7; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05902,naive=0.01219,drift4=0.01726; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3354,naive=0.07652,drift4=0.0942; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06025,naive=0.01753,drift4=0.02909; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03712,naive=0.01346,drift4=0.01863; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3372,naive=0.1057,drift4=0.1745; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1409,naive=0.07999,drift4=0.1116; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02996,naive=0.0126,drift4=0.01848; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=6.237,naive=1.643,drift4=1.798; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09497,naive=0.02501,drift4=0.0501; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=675,naive=229.4,drift4=263; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -811,7 +811,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -835,19 +835,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K2">
-        <v>0.6882994163513212</v>
+        <v>0.9997503834852586</v>
       </c>
       <c r="L2">
-        <v>1.423627092272378</v>
+        <v>1.607081868208929</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
         <v>71</v>
@@ -859,34 +859,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.141505</v>
+        <v>1.139965</v>
       </c>
       <c r="S2">
-        <v>1.150782554601837</v>
+        <v>1.148061020733432</v>
       </c>
       <c r="T2">
-        <v>1.161606595196639</v>
+        <v>1.158684387466788</v>
       </c>
       <c r="U2">
-        <v>1.141505</v>
+        <v>1.139965</v>
       </c>
       <c r="V2">
-        <v>1.14471</v>
+        <v>1.14163</v>
       </c>
       <c r="Y2">
-        <v>0.008127476096764058</v>
+        <v>0.007101990616757695</v>
       </c>
       <c r="AA2">
-        <v>0.008127476096764058</v>
+        <v>0.007101990616757695</v>
       </c>
       <c r="AB2">
-        <v>0.3973318010939917</v>
+        <v>0.3966146979247819</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4026681989060083</v>
+        <v>0.4033853020752182</v>
       </c>
       <c r="AE2" t="s">
         <v>77</v>
@@ -922,19 +922,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.04128718059009557</v>
+        <v>0.04102685232194606</v>
       </c>
       <c r="AR2">
-        <v>0.01004184426961693</v>
+        <v>0.01020629360982728</v>
       </c>
       <c r="AS2">
-        <v>0.0148217063138117</v>
+        <v>0.01468021656113982</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV2" t="s">
         <v>87</v>
@@ -946,7 +946,7 @@
         <v>89</v>
       </c>
       <c r="AY2" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -954,7 +954,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -978,19 +978,19 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K3">
-        <v>0.2983132593948509</v>
+        <v>0.4634407824260308</v>
       </c>
       <c r="L3">
-        <v>1.811908380628527</v>
+        <v>1.975753434410489</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -1002,34 +1002,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>7.7264</v>
+        <v>7.7143</v>
       </c>
       <c r="S3">
-        <v>7.731954897738209</v>
+        <v>7.711414336314913</v>
       </c>
       <c r="T3">
-        <v>7.761050764821054</v>
+        <v>7.740221465541575</v>
       </c>
       <c r="U3">
-        <v>7.7264</v>
+        <v>7.7143</v>
       </c>
       <c r="V3">
-        <v>7.7069</v>
+        <v>7.6827</v>
       </c>
       <c r="Y3">
-        <v>0.0007189503181571189</v>
+        <v>-0.0003740668220170943</v>
       </c>
       <c r="AA3">
-        <v>0.0007189503181571189</v>
+        <v>0.0003740668220170943</v>
       </c>
       <c r="AB3">
-        <v>0.3906666472415808</v>
+        <v>0.3893213794896733</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4093333527584192</v>
+        <v>0.4106786205103267</v>
       </c>
       <c r="AE3" t="s">
         <v>78</v>
@@ -1065,19 +1065,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.256222125751404</v>
+        <v>0.2556828910679363</v>
       </c>
       <c r="AR3">
-        <v>0.06601860447056108</v>
+        <v>0.06787504703317963</v>
       </c>
       <c r="AS3">
-        <v>0.0875753592692303</v>
+        <v>0.08657656526006254</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV3" t="s">
         <v>87</v>
@@ -1089,7 +1089,7 @@
         <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1097,7 +1097,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1121,19 +1121,19 @@
         <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.5791583796555356</v>
+        <v>0.393898797014347</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" t="s">
         <v>72</v>
@@ -1145,43 +1145,43 @@
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>1.343005</v>
+        <v>1.33748</v>
       </c>
       <c r="S4">
-        <v>1.366353347309209</v>
+        <v>1.356860523446636</v>
       </c>
       <c r="T4">
-        <v>1.377741759125278</v>
+        <v>1.367720457281338</v>
       </c>
       <c r="U4">
-        <v>1.343005</v>
+        <v>1.33748</v>
       </c>
       <c r="V4">
-        <v>1.36591</v>
+        <v>1.35486</v>
       </c>
       <c r="W4">
-        <v>1.366353347309209</v>
+        <v>1.356860523446636</v>
       </c>
       <c r="X4">
-        <v>1.327439435127194</v>
+        <v>1.324559651035576</v>
       </c>
       <c r="Y4">
-        <v>0.01738515292884885</v>
+        <v>0.0144903276659356</v>
       </c>
       <c r="Z4">
         <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.01738515292884885</v>
+        <v>0.0144903276659356</v>
       </c>
       <c r="AB4">
-        <v>0.4246492221494385</v>
+        <v>0.4258420464241907</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3753507778505615</v>
+        <v>0.3741579535758094</v>
       </c>
       <c r="AE4" t="s">
         <v>79</v>
@@ -1196,22 +1196,22 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.0115901019525659</v>
+        <v>0.009660218443957065</v>
       </c>
       <c r="AJ4">
-        <v>43140.25899395185</v>
+        <v>51758.663937126</v>
       </c>
       <c r="AK4">
-        <v>32355.19424546389</v>
+        <v>38818.9979528445</v>
       </c>
       <c r="AL4">
-        <v>24091.64094360326</v>
+        <v>29023.9838747828</v>
       </c>
       <c r="AM4">
-        <v>323.5519424546389</v>
+        <v>388.1899795284451</v>
       </c>
       <c r="AN4">
-        <v>0.003235519424546389</v>
+        <v>0.003881899795284451</v>
       </c>
       <c r="AO4">
         <v>375.0000000000001</v>
@@ -1220,19 +1220,19 @@
         <v>0.003750000000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.0439207561070098</v>
+        <v>0.04402149597091368</v>
       </c>
       <c r="AR4">
-        <v>0.01132704751140213</v>
+        <v>0.0111604827681831</v>
       </c>
       <c r="AS4">
-        <v>0.02613520469750388</v>
+        <v>0.02569067717172626</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV4" t="s">
         <v>88</v>
@@ -1244,7 +1244,7 @@
         <v>90</v>
       </c>
       <c r="AY4" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1252,7 +1252,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1276,19 +1276,19 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K5">
-        <v>0.5585486117996296</v>
+        <v>0.7682790670394533</v>
       </c>
       <c r="L5">
-        <v>1.425604946971071</v>
+        <v>1.570669371859712</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" t="s">
         <v>72</v>
@@ -1297,46 +1297,46 @@
         <v>75</v>
       </c>
       <c r="Q5">
-        <v>0.8896371529499074</v>
+        <v>0.9420697667598633</v>
       </c>
       <c r="R5">
-        <v>0.8101700000000001</v>
+        <v>0.8129150000000001</v>
       </c>
       <c r="S5">
-        <v>0.8172471288364973</v>
+        <v>0.8215925756239335</v>
       </c>
       <c r="T5">
-        <v>0.8264028056305028</v>
+        <v>0.8304885971089975</v>
       </c>
       <c r="U5">
-        <v>0.8101700000000001</v>
+        <v>0.8129150000000001</v>
       </c>
       <c r="V5">
-        <v>0.8107400000000001</v>
+        <v>0.8162300000000001</v>
       </c>
       <c r="W5">
-        <v>0.8172471288364973</v>
+        <v>0.8215925756239335</v>
       </c>
       <c r="X5">
-        <v>0.801795</v>
+        <v>0.80454</v>
       </c>
       <c r="Y5">
-        <v>0.008735362746704084</v>
+        <v>0.01067464079754151</v>
       </c>
       <c r="Z5">
-        <v>0.8450303088354874</v>
+        <v>1.036128432708466</v>
       </c>
       <c r="AA5">
-        <v>0.008735362746704084</v>
+        <v>0.01067464079754151</v>
       </c>
       <c r="AB5">
-        <v>0.4227294261765532</v>
+        <v>0.4225924596839347</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3772705738234468</v>
+        <v>0.3774075403160653</v>
       </c>
       <c r="AE5" t="s">
         <v>80</v>
@@ -1348,46 +1348,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>444.8185764749537</v>
+        <v>471.0348833799317</v>
       </c>
       <c r="AI5">
-        <v>0.01033733660836621</v>
+        <v>0.01030243014337298</v>
       </c>
       <c r="AJ5">
-        <v>48368.35820895495</v>
+        <v>48532.23880596986</v>
       </c>
       <c r="AK5">
-        <v>43030.28848987596</v>
+        <v>45720.75489227402</v>
       </c>
       <c r="AL5">
-        <v>53112.66584775536</v>
+        <v>56242.97114984225</v>
       </c>
       <c r="AM5">
-        <v>430.3028848987596</v>
+        <v>457.2075489227402</v>
       </c>
       <c r="AN5">
-        <v>0.004303028848987596</v>
+        <v>0.004572075489227402</v>
       </c>
       <c r="AO5">
-        <v>444.8185764749537</v>
+        <v>471.0348833799316</v>
       </c>
       <c r="AP5">
-        <v>0.004448185764749537</v>
+        <v>0.004710348833799317</v>
       </c>
       <c r="AQ5">
-        <v>0.031288216814724</v>
+        <v>0.03159627679497913</v>
       </c>
       <c r="AR5">
-        <v>0.01086625281332157</v>
+        <v>0.01123233260874431</v>
       </c>
       <c r="AS5">
-        <v>0.01540151984546945</v>
+        <v>0.01537168837488112</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV5" t="s">
         <v>88</v>
@@ -1399,7 +1399,7 @@
         <v>90</v>
       </c>
       <c r="AY5" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1407,7 +1407,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1431,19 +1431,19 @@
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.05138742086143865</v>
+        <v>0.004995935529032214</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
         <v>72</v>
@@ -1455,43 +1455,43 @@
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>9.088609999999999</v>
+        <v>9.05043</v>
       </c>
       <c r="S6">
-        <v>9.142937643996792</v>
+        <v>9.082081725141387</v>
       </c>
       <c r="T6">
-        <v>9.123811610440452</v>
+        <v>9.065963463423355</v>
       </c>
       <c r="U6">
-        <v>9.088609999999999</v>
+        <v>9.05043</v>
       </c>
       <c r="V6">
-        <v>9.194199999999999</v>
+        <v>9.117840000000001</v>
       </c>
       <c r="W6">
-        <v>9.142937643996792</v>
+        <v>9.082081725141387</v>
       </c>
       <c r="X6">
-        <v>9.001267499999999</v>
+        <v>8.9630875</v>
       </c>
       <c r="Y6">
-        <v>0.005977552562690288</v>
+        <v>0.003497262024167584</v>
       </c>
       <c r="Z6">
-        <v>0.6220069725138712</v>
+        <v>0.3623862969503639</v>
       </c>
       <c r="AA6">
-        <v>0.005977552562690288</v>
+        <v>0.003497262024167584</v>
       </c>
       <c r="AB6">
-        <v>0.4282575037138154</v>
+        <v>0.4294094465173351</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3717424962861847</v>
+        <v>0.370590553482665</v>
       </c>
       <c r="AE6" t="s">
         <v>81</v>
@@ -1506,22 +1506,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.009610105395654524</v>
+        <v>0.009650646433373846</v>
       </c>
       <c r="AJ6">
-        <v>52028.56570398165</v>
+        <v>51810.0008586887</v>
       </c>
       <c r="AK6">
-        <v>39021.42427798624</v>
+        <v>38857.50064401652</v>
       </c>
       <c r="AL6">
         <v>4293.44248218223</v>
       </c>
       <c r="AM6">
-        <v>390.2142427798624</v>
+        <v>388.5750064401652</v>
       </c>
       <c r="AN6">
-        <v>0.003902142427798624</v>
+        <v>0.003885750064401652</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1530,19 +1530,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.4033883530590582</v>
+        <v>0.401188963578697</v>
       </c>
       <c r="AR6">
-        <v>0.06719336682309301</v>
+        <v>0.06799663463507193</v>
       </c>
       <c r="AS6">
-        <v>0.1700399202598371</v>
+        <v>0.1660935844288943</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV6" t="s">
         <v>88</v>
@@ -1554,7 +1554,7 @@
         <v>90</v>
       </c>
       <c r="AY6" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1562,7 +1562,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1574,7 +1574,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
@@ -1586,19 +1586,19 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.6710355043976531</v>
+        <v>0.6146742369239991</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1610,43 +1610,43 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>4.73382</v>
+        <v>4.73606</v>
       </c>
       <c r="S7">
-        <v>4.741179356582096</v>
+        <v>4.74405080313015</v>
       </c>
       <c r="T7">
-        <v>4.718901026373057</v>
+        <v>4.720838753610576</v>
       </c>
       <c r="U7">
-        <v>4.73382</v>
+        <v>4.73606</v>
       </c>
       <c r="V7">
-        <v>4.774369999999999</v>
+        <v>4.77885</v>
       </c>
       <c r="W7">
-        <v>4.741179356582096</v>
+        <v>4.74405080313015</v>
       </c>
       <c r="X7">
-        <v>4.685605</v>
+        <v>4.687845</v>
       </c>
       <c r="Y7">
-        <v>0.001554633801474583</v>
+        <v>0.001687225907220417</v>
       </c>
       <c r="Z7">
-        <v>0.1526362456102131</v>
+        <v>0.1657327207331814</v>
       </c>
       <c r="AA7">
-        <v>0.001554633801474583</v>
+        <v>0.001687225907220417</v>
       </c>
       <c r="AB7">
-        <v>0.4521562556138915</v>
+        <v>0.4523467172846918</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3478437443861085</v>
+        <v>0.3476532827153082</v>
       </c>
       <c r="AE7" t="s">
         <v>82</v>
@@ -1661,22 +1661,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01018522039283283</v>
+        <v>0.01018040311989288</v>
       </c>
       <c r="AJ7">
-        <v>49090.73939645349</v>
+        <v>49113.96868194556</v>
       </c>
       <c r="AK7">
-        <v>49090.73939645349</v>
+        <v>49113.96868194556</v>
       </c>
       <c r="AL7">
         <v>10370.21673752984</v>
       </c>
       <c r="AM7">
-        <v>490.9073939645348</v>
+        <v>491.1396868194556</v>
       </c>
       <c r="AN7">
-        <v>0.004909073939645348</v>
+        <v>0.004911396868194556</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1685,19 +1685,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.129231400511493</v>
+        <v>0.1291663425073252</v>
       </c>
       <c r="AR7">
-        <v>0.06052145342805362</v>
+        <v>0.06046424246938382</v>
       </c>
       <c r="AS7">
-        <v>0.09210243007359289</v>
+        <v>0.09243970005290998</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV7" t="s">
         <v>88</v>
@@ -1709,7 +1709,7 @@
         <v>90</v>
       </c>
       <c r="AY7" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1717,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1741,19 +1741,19 @@
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.6470560086710306</v>
+        <v>0.5011456292692775</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" t="s">
         <v>72</v>
@@ -1765,43 +1765,43 @@
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>0.699945</v>
+        <v>0.699785</v>
       </c>
       <c r="S8">
-        <v>0.6984410886178472</v>
+        <v>0.6983230211354452</v>
       </c>
       <c r="T8">
-        <v>0.6879766175609653</v>
+        <v>0.6880434635351704</v>
       </c>
       <c r="U8">
-        <v>0.699945</v>
+        <v>0.699785</v>
       </c>
       <c r="V8">
-        <v>0.7101900000000001</v>
+        <v>0.70987</v>
       </c>
       <c r="W8">
-        <v>0.6984410886178472</v>
+        <v>0.6983230211354452</v>
       </c>
       <c r="X8">
-        <v>0.7078200000000001</v>
+        <v>0.7076600000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.002148613651291015</v>
+        <v>-0.00208918291268717</v>
       </c>
       <c r="Z8">
-        <v>0.1909728739241753</v>
+        <v>0.1856481097847343</v>
       </c>
       <c r="AA8">
-        <v>0.002148613651291015</v>
+        <v>0.00208918291268717</v>
       </c>
       <c r="AB8">
-        <v>0.4366697151491715</v>
+        <v>0.4366235055163742</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3633302848508286</v>
+        <v>0.3633764944836258</v>
       </c>
       <c r="AE8" t="s">
         <v>83</v>
@@ -1816,43 +1816,43 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01125088399802849</v>
+        <v>0.01125345641875726</v>
       </c>
       <c r="AJ8">
-        <v>44440.95238095211</v>
+        <v>44430.79365079337</v>
       </c>
       <c r="AK8">
-        <v>33330.71428571408</v>
+        <v>33323.09523809503</v>
       </c>
       <c r="AL8">
-        <v>47619.04761904732</v>
+        <v>47619.04761904731</v>
       </c>
       <c r="AM8">
-        <v>333.3071428571408</v>
+        <v>333.2309523809503</v>
       </c>
       <c r="AN8">
-        <v>0.003333071428571408</v>
+        <v>0.003332309523809503</v>
       </c>
       <c r="AO8">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP8">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ8">
-        <v>0.02615412222150581</v>
+        <v>0.02614638757860162</v>
       </c>
       <c r="AR8">
-        <v>0.009318327365775959</v>
+        <v>0.009316531771876156</v>
       </c>
       <c r="AS8">
-        <v>0.01546589341353431</v>
+        <v>0.01544275938196698</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV8" t="s">
         <v>88</v>
@@ -1864,7 +1864,7 @@
         <v>90</v>
       </c>
       <c r="AY8" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1872,7 +1872,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1896,19 +1896,19 @@
         <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K9">
-        <v>0.2357537202218213</v>
+        <v>0.409297788694392</v>
       </c>
       <c r="L9">
-        <v>1.743477961427452</v>
+        <v>1.897848379278704</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
@@ -1917,46 +1917,46 @@
         <v>76</v>
       </c>
       <c r="Q9">
-        <v>0.823184709833634</v>
+        <v>0.693026658479206</v>
       </c>
       <c r="R9">
-        <v>162.4865</v>
+        <v>163.206</v>
       </c>
       <c r="S9">
-        <v>161.5238313118946</v>
+        <v>162.443203519255</v>
       </c>
       <c r="T9">
-        <v>159.2145259793521</v>
+        <v>159.6462308358749</v>
       </c>
       <c r="U9">
-        <v>162.4865</v>
+        <v>163.206</v>
       </c>
       <c r="V9">
-        <v>163.243</v>
+        <v>164.682</v>
       </c>
       <c r="W9">
-        <v>161.5238313118946</v>
+        <v>162.443203519255</v>
       </c>
       <c r="X9">
-        <v>164.064</v>
+        <v>164.7835</v>
       </c>
       <c r="Y9">
-        <v>-0.005924607201862457</v>
+        <v>-0.004673826211934322</v>
       </c>
       <c r="Z9">
-        <v>0.6102495645676275</v>
+        <v>0.4835476898541741</v>
       </c>
       <c r="AA9">
-        <v>0.005924607201862457</v>
+        <v>0.004673826211934322</v>
       </c>
       <c r="AB9">
-        <v>0.3891966734970436</v>
+        <v>0.3859582155971711</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4108033265029565</v>
+        <v>0.4140417844028289</v>
       </c>
       <c r="AE9" t="s">
         <v>84</v>
@@ -1968,46 +1968,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>411.592354916817</v>
+        <v>346.513329239603</v>
       </c>
       <c r="AI9">
-        <v>0.0097084988599052</v>
+        <v>0.009665698565003655</v>
       </c>
       <c r="AJ9">
-        <v>51501.26782884355</v>
+        <v>51729.31854199727</v>
       </c>
       <c r="AK9">
-        <v>42395.05621375085</v>
+        <v>35849.7967745668</v>
       </c>
       <c r="AL9">
-        <v>260.9143295827705</v>
+        <v>219.6597966653603</v>
       </c>
       <c r="AM9">
-        <v>423.9505621375085</v>
+        <v>358.497967745668</v>
       </c>
       <c r="AN9">
-        <v>0.004239505621375085</v>
+        <v>0.00358497967745668</v>
       </c>
       <c r="AO9">
-        <v>411.592354916817</v>
+        <v>346.513329239603</v>
       </c>
       <c r="AP9">
-        <v>0.00411592354916817</v>
+        <v>0.00346513329239603</v>
       </c>
       <c r="AQ9">
-        <v>4.363485639693498</v>
+        <v>4.495278224983198</v>
       </c>
       <c r="AR9">
-        <v>1.33216590990505</v>
+        <v>1.45528937192282</v>
       </c>
       <c r="AS9">
-        <v>1.982915173165015</v>
+        <v>1.970200100303549</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV9" t="s">
         <v>88</v>
@@ -2019,7 +2019,7 @@
         <v>90</v>
       </c>
       <c r="AY9" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2027,7 +2027,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2051,19 +2051,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.128653120691019</v>
+        <v>1.277602445120374</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2075,43 +2075,43 @@
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.76801</v>
+        <v>6.76844</v>
       </c>
       <c r="S10">
-        <v>6.718901372271469</v>
+        <v>6.722895575319953</v>
       </c>
       <c r="T10">
-        <v>6.686105841683576</v>
+        <v>6.694356193145873</v>
       </c>
       <c r="U10">
-        <v>6.76801</v>
+        <v>6.76844</v>
       </c>
       <c r="V10">
-        <v>6.73122</v>
+        <v>6.73208</v>
       </c>
       <c r="W10">
-        <v>6.718901372271469</v>
+        <v>6.722895575319953</v>
       </c>
       <c r="X10">
-        <v>6.800749085152354</v>
+        <v>6.798802949786698</v>
       </c>
       <c r="Y10">
-        <v>-0.007255992193943399</v>
+        <v>-0.006728939708418359</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.007255992193943399</v>
+        <v>0.006728939708418359</v>
       </c>
       <c r="AB10">
-        <v>0.4361519412713491</v>
+        <v>0.4362344644505542</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3638480587286509</v>
+        <v>0.3637655355494457</v>
       </c>
       <c r="AE10" t="s">
         <v>85</v>
@@ -2126,22 +2126,22 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004837328129295599</v>
+        <v>0.00448595980561224</v>
       </c>
       <c r="AJ10">
-        <v>103362.8454873515</v>
+        <v>111458.8675927203</v>
       </c>
       <c r="AK10">
-        <v>77522.13411551362</v>
+        <v>83594.15069454024</v>
       </c>
       <c r="AL10">
-        <v>11454.19910956302</v>
+        <v>12350.57867020174</v>
       </c>
       <c r="AM10">
-        <v>775.2213411551362</v>
+        <v>835.9415069454024</v>
       </c>
       <c r="AN10">
-        <v>0.007752213411551362</v>
+        <v>0.008359415069454024</v>
       </c>
       <c r="AO10">
         <v>375</v>
@@ -2150,19 +2150,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08698928368690512</v>
+        <v>0.08692657779506123</v>
       </c>
       <c r="AR10">
-        <v>0.01789265732926622</v>
+        <v>0.01783652976415892</v>
       </c>
       <c r="AS10">
-        <v>0.0433557201078804</v>
+        <v>0.04334763115332989</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV10" t="s">
         <v>88</v>
@@ -2174,7 +2174,7 @@
         <v>90</v>
       </c>
       <c r="AY10" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2182,7 +2182,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2206,19 +2206,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.879864558389473</v>
+        <v>1.744476749522717</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2230,43 +2230,43 @@
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4007.2</v>
+        <v>4081.49</v>
       </c>
       <c r="S11">
-        <v>3863.232468543733</v>
+        <v>3983.539041439973</v>
       </c>
       <c r="T11">
-        <v>3729.799310204706</v>
+        <v>3845.896387619497</v>
       </c>
       <c r="U11">
-        <v>4007.2</v>
+        <v>4081.49</v>
       </c>
       <c r="V11">
-        <v>3925.139999999999</v>
+        <v>4073.719999999999</v>
       </c>
       <c r="W11">
-        <v>3863.232468543733</v>
+        <v>3983.539041439973</v>
       </c>
       <c r="X11">
-        <v>4137.065</v>
+        <v>4211.355</v>
       </c>
       <c r="Y11">
-        <v>-0.03592721387908426</v>
+        <v>-0.02399882360609158</v>
       </c>
       <c r="Z11">
-        <v>1.108593781667628</v>
+        <v>0.7542521738730743</v>
       </c>
       <c r="AA11">
-        <v>0.03592721387908426</v>
+        <v>0.02399882360609158</v>
       </c>
       <c r="AB11">
-        <v>0.4009381329529487</v>
+        <v>0.4026578176050248</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3990618670470513</v>
+        <v>0.3973421823949752</v>
       </c>
       <c r="AE11" t="s">
         <v>86</v>
@@ -2281,22 +2281,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03240791575164701</v>
+        <v>0.03181803704039454</v>
       </c>
       <c r="AJ11">
-        <v>15428.32941901206</v>
+        <v>15714.35721711009</v>
       </c>
       <c r="AK11">
-        <v>11571.24706425905</v>
+        <v>11785.76791283257</v>
       </c>
       <c r="AL11">
-        <v>2.887614060755402</v>
+        <v>2.887614060755403</v>
       </c>
       <c r="AM11">
-        <v>115.7124706425905</v>
+        <v>117.8576791283257</v>
       </c>
       <c r="AN11">
-        <v>0.001157124706425905</v>
+        <v>0.001178576791283257</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2305,19 +2305,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>476.7432013754182</v>
+        <v>487.8722143808304</v>
       </c>
       <c r="AR11">
-        <v>201.9691121176079</v>
+        <v>195.7947646370976</v>
       </c>
       <c r="AS11">
-        <v>210.7592443949108</v>
+        <v>220.380007460656</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03283167980890172</v>
+        <v>0.03370640327911153</v>
       </c>
       <c r="AV11" t="s">
         <v>88</v>
@@ -2329,7 +2329,7 @@
         <v>90</v>
       </c>
       <c r="AY11" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -247,34 +247,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.05902,naive=0.01219,drift4=0.01726; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3354,naive=0.07652,drift4=0.0942; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06025,naive=0.01753,drift4=0.02909; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03712,naive=0.01346,drift4=0.01863; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.3372,naive=0.1057,drift4=0.1745; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1409,naive=0.07999,drift4=0.1116; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02996,naive=0.0126,drift4=0.01848; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=6.237,naive=1.643,drift4=1.798; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09497,naive=0.02501,drift4=0.0501; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=675,naive=229.4,drift4=263; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06021,naive=0.01203,drift4=0.01752; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3316,naive=0.07315,drift4=0.09446; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06016,naive=0.01771,drift4=0.02947; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03691,naive=0.01326,drift4=0.01881; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.3001,naive=0.1048,drift4=0.1758; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1384,naive=0.07819,drift4=0.1127; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02967,naive=0.01254,drift4=0.01876; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=6.341,naive=1.604,drift4=1.666; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09487,naive=0.02431,drift4=0.0511; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=667.3,naive=221.9,drift4=268.2; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -862,10 +862,10 @@
         <v>1.139965</v>
       </c>
       <c r="S2">
-        <v>1.148061020733432</v>
+        <v>1.150234658322407</v>
       </c>
       <c r="T2">
-        <v>1.158684387466788</v>
+        <v>1.164111956419289</v>
       </c>
       <c r="U2">
         <v>1.139965</v>
@@ -874,19 +874,19 @@
         <v>1.14163</v>
       </c>
       <c r="Y2">
-        <v>0.007101990616757695</v>
+        <v>0.009008748797030324</v>
       </c>
       <c r="AA2">
-        <v>0.007101990616757695</v>
+        <v>0.009008748797030324</v>
       </c>
       <c r="AB2">
-        <v>0.3966146979247819</v>
+        <v>0.39754806724643</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4033853020752182</v>
+        <v>0.4024519327535699</v>
       </c>
       <c r="AE2" t="s">
         <v>77</v>
@@ -922,19 +922,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.04102685232194606</v>
+        <v>0.03962226699693155</v>
       </c>
       <c r="AR2">
-        <v>0.01020629360982728</v>
+        <v>0.009168895477324714</v>
       </c>
       <c r="AS2">
-        <v>0.01468021656113982</v>
+        <v>0.01387909606604269</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV2" t="s">
         <v>87</v>
@@ -1005,10 +1005,10 @@
         <v>7.7143</v>
       </c>
       <c r="S3">
-        <v>7.711414336314913</v>
+        <v>7.71855139035652</v>
       </c>
       <c r="T3">
-        <v>7.740221465541575</v>
+        <v>7.758071358375172</v>
       </c>
       <c r="U3">
         <v>7.7143</v>
@@ -1017,19 +1017,19 @@
         <v>7.6827</v>
       </c>
       <c r="Y3">
-        <v>-0.0003740668220170943</v>
+        <v>0.0005511051367616564</v>
       </c>
       <c r="AA3">
-        <v>0.0003740668220170943</v>
+        <v>0.0005511051367616564</v>
       </c>
       <c r="AB3">
-        <v>0.3893213794896733</v>
+        <v>0.3918118366597881</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4106786205103267</v>
+        <v>0.4081881633402119</v>
       </c>
       <c r="AE3" t="s">
         <v>78</v>
@@ -1065,19 +1065,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.2556828910679363</v>
+        <v>0.2345120998901604</v>
       </c>
       <c r="AR3">
-        <v>0.06787504703317963</v>
+        <v>0.0592829258594492</v>
       </c>
       <c r="AS3">
-        <v>0.08657656526006254</v>
+        <v>0.08187448218279181</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV3" t="s">
         <v>87</v>
@@ -1148,10 +1148,10 @@
         <v>1.33748</v>
       </c>
       <c r="S4">
-        <v>1.356860523446636</v>
+        <v>1.358300890006599</v>
       </c>
       <c r="T4">
-        <v>1.367720457281338</v>
+        <v>1.371070226252353</v>
       </c>
       <c r="U4">
         <v>1.33748</v>
@@ -1160,28 +1160,28 @@
         <v>1.35486</v>
       </c>
       <c r="W4">
-        <v>1.356860523446636</v>
+        <v>1.358300890006599</v>
       </c>
       <c r="X4">
-        <v>1.324559651035576</v>
+        <v>1.323599406662267</v>
       </c>
       <c r="Y4">
-        <v>0.0144903276659356</v>
+        <v>0.01556725334704023</v>
       </c>
       <c r="Z4">
         <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.0144903276659356</v>
+        <v>0.01556725334704023</v>
       </c>
       <c r="AB4">
-        <v>0.4258420464241907</v>
+        <v>0.4266991650160204</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3741579535758094</v>
+        <v>0.3733008349839796</v>
       </c>
       <c r="AE4" t="s">
         <v>79</v>
@@ -1196,43 +1196,43 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.009660218443957065</v>
+        <v>0.01037816889802682</v>
       </c>
       <c r="AJ4">
-        <v>51758.663937126</v>
+        <v>48178.05577389128</v>
       </c>
       <c r="AK4">
-        <v>38818.9979528445</v>
+        <v>36133.54183041846</v>
       </c>
       <c r="AL4">
-        <v>29023.9838747828</v>
+        <v>27016.13618926523</v>
       </c>
       <c r="AM4">
-        <v>388.1899795284451</v>
+        <v>361.3354183041845</v>
       </c>
       <c r="AN4">
-        <v>0.003881899795284451</v>
+        <v>0.003613354183041845</v>
       </c>
       <c r="AO4">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.04402149597091368</v>
+        <v>0.04199832943042445</v>
       </c>
       <c r="AR4">
-        <v>0.0111604827681831</v>
+        <v>0.01052943014006013</v>
       </c>
       <c r="AS4">
-        <v>0.02569067717172626</v>
+        <v>0.02451992046474581</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV4" t="s">
         <v>88</v>
@@ -1303,10 +1303,10 @@
         <v>0.8129150000000001</v>
       </c>
       <c r="S5">
-        <v>0.8215925756239335</v>
+        <v>0.8211217177270498</v>
       </c>
       <c r="T5">
-        <v>0.8304885971089975</v>
+        <v>0.8293253068076452</v>
       </c>
       <c r="U5">
         <v>0.8129150000000001</v>
@@ -1315,28 +1315,28 @@
         <v>0.8162300000000001</v>
       </c>
       <c r="W5">
-        <v>0.8215925756239335</v>
+        <v>0.8211217177270498</v>
       </c>
       <c r="X5">
         <v>0.80454</v>
       </c>
       <c r="Y5">
-        <v>0.01067464079754151</v>
+        <v>0.01009541923454448</v>
       </c>
       <c r="Z5">
-        <v>1.036128432708466</v>
+        <v>0.9799065942745887</v>
       </c>
       <c r="AA5">
-        <v>0.01067464079754151</v>
+        <v>0.01009541923454448</v>
       </c>
       <c r="AB5">
-        <v>0.4225924596839347</v>
+        <v>0.4241762189036206</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3774075403160653</v>
+        <v>0.3758237810963794</v>
       </c>
       <c r="AE5" t="s">
         <v>80</v>
@@ -1375,19 +1375,19 @@
         <v>0.004710348833799317</v>
       </c>
       <c r="AQ5">
-        <v>0.03159627679497913</v>
+        <v>0.03012084761519061</v>
       </c>
       <c r="AR5">
-        <v>0.01123233260874431</v>
+        <v>0.01030037366274189</v>
       </c>
       <c r="AS5">
-        <v>0.01537168837488112</v>
+        <v>0.01412362109971092</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV5" t="s">
         <v>88</v>
@@ -1458,10 +1458,10 @@
         <v>9.05043</v>
       </c>
       <c r="S6">
-        <v>9.082081725141387</v>
+        <v>9.085626668010763</v>
       </c>
       <c r="T6">
-        <v>9.065963463423355</v>
+        <v>9.074961750611848</v>
       </c>
       <c r="U6">
         <v>9.05043</v>
@@ -1470,28 +1470,28 @@
         <v>9.117840000000001</v>
       </c>
       <c r="W6">
-        <v>9.082081725141387</v>
+        <v>9.085626668010763</v>
       </c>
       <c r="X6">
         <v>8.9630875</v>
       </c>
       <c r="Y6">
-        <v>0.003497262024167584</v>
+        <v>0.003888949807993904</v>
       </c>
       <c r="Z6">
-        <v>0.3623862969503639</v>
+        <v>0.4029729857831228</v>
       </c>
       <c r="AA6">
-        <v>0.003497262024167584</v>
+        <v>0.003888949807993904</v>
       </c>
       <c r="AB6">
-        <v>0.4294094465173351</v>
+        <v>0.4368492710528975</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.370590553482665</v>
+        <v>0.3631507289471026</v>
       </c>
       <c r="AE6" t="s">
         <v>81</v>
@@ -1530,19 +1530,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.401188963578697</v>
+        <v>0.3427106174777593</v>
       </c>
       <c r="AR6">
-        <v>0.06799663463507193</v>
+        <v>0.06264082979442238</v>
       </c>
       <c r="AS6">
-        <v>0.1660935844288943</v>
+        <v>0.1593728395024146</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV6" t="s">
         <v>88</v>
@@ -1574,7 +1574,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
@@ -1613,10 +1613,10 @@
         <v>4.73606</v>
       </c>
       <c r="S7">
-        <v>4.74405080313015</v>
+        <v>4.747009217733437</v>
       </c>
       <c r="T7">
-        <v>4.720838753610576</v>
+        <v>4.727661203922364</v>
       </c>
       <c r="U7">
         <v>4.73606</v>
@@ -1625,28 +1625,28 @@
         <v>4.77885</v>
       </c>
       <c r="W7">
-        <v>4.74405080313015</v>
+        <v>4.747009217733437</v>
       </c>
       <c r="X7">
         <v>4.687845</v>
       </c>
       <c r="Y7">
-        <v>0.001687225907220417</v>
+        <v>0.002311883239113675</v>
       </c>
       <c r="Z7">
-        <v>0.1657327207331814</v>
+        <v>0.2270915220042878</v>
       </c>
       <c r="AA7">
-        <v>0.001687225907220417</v>
+        <v>0.002311883239113675</v>
       </c>
       <c r="AB7">
-        <v>0.4523467172846918</v>
+        <v>0.4548413725388539</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3476532827153082</v>
+        <v>0.3451586274611462</v>
       </c>
       <c r="AE7" t="s">
         <v>82</v>
@@ -1685,19 +1685,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.1291663425073252</v>
+        <v>0.1193955459506451</v>
       </c>
       <c r="AR7">
-        <v>0.06046424246938382</v>
+        <v>0.05396774815989491</v>
       </c>
       <c r="AS7">
-        <v>0.09243970005290998</v>
+        <v>0.08289768105804476</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV7" t="s">
         <v>88</v>
@@ -1768,10 +1768,10 @@
         <v>0.699785</v>
       </c>
       <c r="S8">
-        <v>0.6983230211354452</v>
+        <v>0.6988379516944501</v>
       </c>
       <c r="T8">
-        <v>0.6880434635351704</v>
+        <v>0.6893163884710802</v>
       </c>
       <c r="U8">
         <v>0.699785</v>
@@ -1780,28 +1780,28 @@
         <v>0.70987</v>
       </c>
       <c r="W8">
-        <v>0.6983230211354452</v>
+        <v>0.6987353225</v>
       </c>
       <c r="X8">
         <v>0.7076600000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.00208918291268717</v>
+        <v>-0.00135334182005891</v>
       </c>
       <c r="Z8">
-        <v>0.1856481097847343</v>
+        <v>0.1332923809523801</v>
       </c>
       <c r="AA8">
-        <v>0.00208918291268717</v>
+        <v>0.00135334182005891</v>
       </c>
       <c r="AB8">
-        <v>0.4366235055163742</v>
+        <v>0.4386113989196185</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3633764944836258</v>
+        <v>0.3613886010803815</v>
       </c>
       <c r="AE8" t="s">
         <v>83</v>
@@ -1840,19 +1840,19 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="AQ8">
-        <v>0.02614638757860162</v>
+        <v>0.02482735900452658</v>
       </c>
       <c r="AR8">
-        <v>0.009316531771876156</v>
+        <v>0.008516252452704919</v>
       </c>
       <c r="AS8">
-        <v>0.01544275938196698</v>
+        <v>0.01396386687521369</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV8" t="s">
         <v>88</v>
@@ -1923,10 +1923,10 @@
         <v>163.206</v>
       </c>
       <c r="S9">
-        <v>162.443203519255</v>
+        <v>162.5092159817407</v>
       </c>
       <c r="T9">
-        <v>159.6462308358749</v>
+        <v>159.7395076927804</v>
       </c>
       <c r="U9">
         <v>163.206</v>
@@ -1935,28 +1935,28 @@
         <v>164.682</v>
       </c>
       <c r="W9">
-        <v>162.443203519255</v>
+        <v>162.5092159817407</v>
       </c>
       <c r="X9">
         <v>164.7835</v>
       </c>
       <c r="Y9">
-        <v>-0.004673826211934322</v>
+        <v>-0.00426935295429891</v>
       </c>
       <c r="Z9">
-        <v>0.4835476898541741</v>
+        <v>0.4417014378822909</v>
       </c>
       <c r="AA9">
-        <v>0.004673826211934322</v>
+        <v>0.00426935295429891</v>
       </c>
       <c r="AB9">
-        <v>0.3859582155971711</v>
+        <v>0.3798860780251876</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4140417844028289</v>
+        <v>0.4201139219748123</v>
       </c>
       <c r="AE9" t="s">
         <v>84</v>
@@ -1995,19 +1995,19 @@
         <v>0.00346513329239603</v>
       </c>
       <c r="AQ9">
-        <v>4.495278224983198</v>
+        <v>4.35632839558128</v>
       </c>
       <c r="AR9">
-        <v>1.45528937192282</v>
+        <v>1.297656849764627</v>
       </c>
       <c r="AS9">
-        <v>1.970200100303549</v>
+        <v>1.59678822025513</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV9" t="s">
         <v>88</v>
@@ -2078,10 +2078,10 @@
         <v>6.76844</v>
       </c>
       <c r="S10">
-        <v>6.722895575319953</v>
+        <v>6.722623968421908</v>
       </c>
       <c r="T10">
-        <v>6.694356193145873</v>
+        <v>6.693952186231321</v>
       </c>
       <c r="U10">
         <v>6.76844</v>
@@ -2090,28 +2090,28 @@
         <v>6.73208</v>
       </c>
       <c r="W10">
-        <v>6.722895575319953</v>
+        <v>6.722623968421908</v>
       </c>
       <c r="X10">
-        <v>6.798802949786698</v>
+        <v>6.798984021052061</v>
       </c>
       <c r="Y10">
-        <v>-0.006728939708418359</v>
+        <v>-0.006769068142451075</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.006728939708418359</v>
+        <v>0.006769068142451075</v>
       </c>
       <c r="AB10">
-        <v>0.4362344644505542</v>
+        <v>0.438735661047352</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3637655355494457</v>
+        <v>0.3612643389526481</v>
       </c>
       <c r="AE10" t="s">
         <v>85</v>
@@ -2126,22 +2126,22 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.00448595980561224</v>
+        <v>0.004512712094967383</v>
       </c>
       <c r="AJ10">
-        <v>111458.8675927203</v>
+        <v>110798.1164049008</v>
       </c>
       <c r="AK10">
-        <v>83594.15069454024</v>
+        <v>83098.58730367562</v>
       </c>
       <c r="AL10">
-        <v>12350.57867020174</v>
+        <v>12277.36188895456</v>
       </c>
       <c r="AM10">
-        <v>835.9415069454024</v>
+        <v>830.9858730367563</v>
       </c>
       <c r="AN10">
-        <v>0.008359415069454024</v>
+        <v>0.008309858730367563</v>
       </c>
       <c r="AO10">
         <v>375</v>
@@ -2150,19 +2150,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08692657779506123</v>
+        <v>0.08289262945967629</v>
       </c>
       <c r="AR10">
-        <v>0.01783652976415892</v>
+        <v>0.01702914884780859</v>
       </c>
       <c r="AS10">
-        <v>0.04334763115332989</v>
+        <v>0.04250318700793362</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV10" t="s">
         <v>88</v>
@@ -2233,10 +2233,10 @@
         <v>4081.49</v>
       </c>
       <c r="S11">
-        <v>3983.539041439973</v>
+        <v>3994.775050915919</v>
       </c>
       <c r="T11">
-        <v>3845.896387619497</v>
+        <v>3875.466065930238</v>
       </c>
       <c r="U11">
         <v>4081.49</v>
@@ -2245,28 +2245,28 @@
         <v>4073.719999999999</v>
       </c>
       <c r="W11">
-        <v>3983.539041439973</v>
+        <v>3994.775050915919</v>
       </c>
       <c r="X11">
         <v>4211.355</v>
       </c>
       <c r="Y11">
-        <v>-0.02399882360609158</v>
+        <v>-0.02124590506998207</v>
       </c>
       <c r="Z11">
-        <v>0.7542521738730743</v>
+        <v>0.6677314833410172</v>
       </c>
       <c r="AA11">
-        <v>0.02399882360609158</v>
+        <v>0.02124590506998207</v>
       </c>
       <c r="AB11">
-        <v>0.4026578176050248</v>
+        <v>0.4060396050237004</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3973421823949752</v>
+        <v>0.3939603949762996</v>
       </c>
       <c r="AE11" t="s">
         <v>86</v>
@@ -2305,19 +2305,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>487.8722143808304</v>
+        <v>479.5640542692452</v>
       </c>
       <c r="AR11">
-        <v>195.7947646370976</v>
+        <v>176.4777570938011</v>
       </c>
       <c r="AS11">
-        <v>220.380007460656</v>
+        <v>216.2568490306786</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03370640327911153</v>
+        <v>0.03338830132778246</v>
       </c>
       <c r="AV11" t="s">
         <v>88</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -172,27 +172,27 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -238,43 +238,40 @@
     <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06021,naive=0.01203,drift4=0.01752; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3316,naive=0.07315,drift4=0.09446; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06016,naive=0.01771,drift4=0.02947; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03691,naive=0.01326,drift4=0.01881; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.3001,naive=0.1048,drift4=0.1758; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1384,naive=0.07819,drift4=0.1127; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02967,naive=0.01254,drift4=0.01876; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=6.341,naive=1.604,drift4=1.666; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09487,naive=0.02431,drift4=0.0511; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=667.3,naive=221.9,drift4=268.2; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06058,naive=0.01192,drift4=0.01764; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=6.297,naive=1.563,drift4=1.65; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06019,naive=0.01772,drift4=0.02948; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0368,naive=0.01353,drift4=0.01889; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.304,naive=0.1046,drift4=0.1759; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.1388,naive=0.07863,drift4=0.1135; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3354,naive=0.07086,drift4=0.09592; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02953,naive=0.01244,drift4=0.01861; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09405,naive=0.02358,drift4=0.05085; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=672.5,naive=216.9,drift4=272.7; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -811,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -835,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K2">
-        <v>0.9997503834852586</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1.607081868208929</v>
+        <v>1.842751679610346</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
         <v>71</v>
@@ -859,37 +856,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.139965</v>
+        <v>1.14124</v>
       </c>
       <c r="S2">
-        <v>1.150234658322407</v>
+        <v>1.152592064868947</v>
       </c>
       <c r="T2">
-        <v>1.164111956419289</v>
+        <v>1.166781380602185</v>
       </c>
       <c r="U2">
-        <v>1.139965</v>
+        <v>1.14124</v>
       </c>
       <c r="V2">
-        <v>1.14163</v>
+        <v>1.14418</v>
       </c>
       <c r="Y2">
-        <v>0.009008748797030324</v>
+        <v>0.009947131952040878</v>
       </c>
       <c r="AA2">
-        <v>0.009008748797030324</v>
+        <v>0.009947131952040878</v>
       </c>
       <c r="AB2">
-        <v>0.39754806724643</v>
+        <v>0.3982086327981558</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4024519327535699</v>
+        <v>0.4017913672018444</v>
       </c>
       <c r="AE2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -922,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03962226699693155</v>
+        <v>0.03986427651647348</v>
       </c>
       <c r="AR2">
-        <v>0.009168895477324714</v>
+        <v>0.009027634381983908</v>
       </c>
       <c r="AS2">
-        <v>0.01387909606604269</v>
+        <v>0.01400523421017505</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -954,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,73 +963,73 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K3">
-        <v>0.4634407824260308</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1.975753434410489</v>
+        <v>2.42202431667825</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>7.7143</v>
+        <v>163.0645</v>
       </c>
       <c r="S3">
-        <v>7.71855139035652</v>
+        <v>162.3710182522998</v>
       </c>
       <c r="T3">
-        <v>7.758071358375172</v>
+        <v>159.7694156623443</v>
       </c>
       <c r="U3">
-        <v>7.7143</v>
+        <v>163.0645</v>
       </c>
       <c r="V3">
-        <v>7.6827</v>
+        <v>164.399</v>
       </c>
       <c r="Y3">
-        <v>0.0005511051367616564</v>
+        <v>-0.004252806390724029</v>
       </c>
       <c r="AA3">
-        <v>0.0005511051367616564</v>
+        <v>0.004252806390724029</v>
       </c>
       <c r="AB3">
-        <v>0.3918118366597881</v>
+        <v>0.3803973789560492</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4081881633402119</v>
+        <v>0.4196026210439507</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1065,31 +1062,31 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.2345120998901604</v>
+        <v>4.322987783340024</v>
       </c>
       <c r="AR3">
-        <v>0.0592829258594492</v>
+        <v>1.268066795129204</v>
       </c>
       <c r="AS3">
-        <v>0.08187448218279181</v>
+        <v>1.596215101082956</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1097,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1121,70 +1118,70 @@
         <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.393898797014347</v>
+        <v>0.3098825048213359</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" t="s">
         <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>1.33748</v>
+        <v>1.337615</v>
       </c>
       <c r="S4">
-        <v>1.358300890006599</v>
+        <v>1.357987898235275</v>
       </c>
       <c r="T4">
-        <v>1.371070226252353</v>
+        <v>1.370038281627247</v>
       </c>
       <c r="U4">
-        <v>1.33748</v>
+        <v>1.337615</v>
       </c>
       <c r="V4">
-        <v>1.35486</v>
+        <v>1.35513</v>
       </c>
       <c r="W4">
-        <v>1.358300890006599</v>
+        <v>1.357987898235275</v>
       </c>
       <c r="X4">
-        <v>1.323599406662267</v>
+        <v>1.32403306784315</v>
       </c>
       <c r="Y4">
-        <v>0.01556725334704023</v>
+        <v>0.01523076388592731</v>
       </c>
       <c r="Z4">
         <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.01556725334704023</v>
+        <v>0.01523076388592731</v>
       </c>
       <c r="AB4">
-        <v>0.4266991650160204</v>
+        <v>0.4266687733916356</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3733008349839796</v>
+        <v>0.3733312266083645</v>
       </c>
       <c r="AE4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1196,55 +1193,55 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.01037816889802682</v>
+        <v>0.01015384259061821</v>
       </c>
       <c r="AJ4">
-        <v>48178.05577389128</v>
+        <v>49242.44152277704</v>
       </c>
       <c r="AK4">
-        <v>36133.54183041846</v>
+        <v>36931.83114208278</v>
       </c>
       <c r="AL4">
-        <v>27016.13618926523</v>
+        <v>27610.21006947648</v>
       </c>
       <c r="AM4">
-        <v>361.3354183041845</v>
+        <v>369.3183114208278</v>
       </c>
       <c r="AN4">
-        <v>0.003613354183041845</v>
+        <v>0.003693183114208278</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.04199832943042445</v>
+        <v>0.04199378495487448</v>
       </c>
       <c r="AR4">
-        <v>0.01052943014006013</v>
+        <v>0.01052902137473537</v>
       </c>
       <c r="AS4">
-        <v>0.02451992046474581</v>
+        <v>0.02452905588349166</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
         <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1252,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1276,70 +1273,70 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K5">
-        <v>0.7682790670394533</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.570669371859712</v>
+        <v>1.881072780285014</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
         <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.9420697667598633</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0.8129150000000001</v>
+        <v>0.81419</v>
       </c>
       <c r="S5">
-        <v>0.8211217177270498</v>
+        <v>0.823105140285445</v>
       </c>
       <c r="T5">
-        <v>0.8293253068076452</v>
+        <v>0.8311410786398341</v>
       </c>
       <c r="U5">
-        <v>0.8129150000000001</v>
+        <v>0.81419</v>
       </c>
       <c r="V5">
-        <v>0.8162300000000001</v>
+        <v>0.81878</v>
       </c>
       <c r="W5">
-        <v>0.8211217177270498</v>
+        <v>0.823105140285445</v>
       </c>
       <c r="X5">
-        <v>0.80454</v>
+        <v>0.8058149999999999</v>
       </c>
       <c r="Y5">
-        <v>0.01009541923454448</v>
+        <v>0.0109497049649898</v>
       </c>
       <c r="Z5">
-        <v>0.9799065942745887</v>
+        <v>1.064494362441193</v>
       </c>
       <c r="AA5">
-        <v>0.01009541923454448</v>
+        <v>0.0109497049649898</v>
       </c>
       <c r="AB5">
-        <v>0.4241762189036206</v>
+        <v>0.4241652721590743</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3758237810963794</v>
+        <v>0.3758347278409258</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1348,58 +1345,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>471.0348833799317</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01030243014337298</v>
+        <v>0.01028629681032689</v>
       </c>
       <c r="AJ5">
-        <v>48532.23880596986</v>
+        <v>48608.35820895493</v>
       </c>
       <c r="AK5">
-        <v>45720.75489227402</v>
+        <v>48608.35820895493</v>
       </c>
       <c r="AL5">
-        <v>56242.97114984225</v>
+        <v>59701.49253731308</v>
       </c>
       <c r="AM5">
-        <v>457.2075489227402</v>
+        <v>486.0835820895493</v>
       </c>
       <c r="AN5">
-        <v>0.004572075489227402</v>
+        <v>0.004860835820895493</v>
       </c>
       <c r="AO5">
-        <v>471.0348833799316</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.004710348833799317</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.03012084761519061</v>
+        <v>0.03030521311426044</v>
       </c>
       <c r="AR5">
-        <v>0.01030037366274189</v>
+        <v>0.01050639352901101</v>
       </c>
       <c r="AS5">
-        <v>0.01412362109971092</v>
+        <v>0.01412372403828651</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1407,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1431,70 +1428,70 @@
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.004995935529032214</v>
+        <v>0.0594261786988079</v>
       </c>
       <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
         <v>4</v>
-      </c>
-      <c r="N6">
-        <v>3</v>
       </c>
       <c r="O6" t="s">
         <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q6">
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>9.05043</v>
+        <v>9.05885</v>
       </c>
       <c r="S6">
-        <v>9.085626668010763</v>
+        <v>9.101985662069314</v>
       </c>
       <c r="T6">
-        <v>9.074961750611848</v>
+        <v>9.094497980085102</v>
       </c>
       <c r="U6">
-        <v>9.05043</v>
+        <v>9.05885</v>
       </c>
       <c r="V6">
-        <v>9.117840000000001</v>
+        <v>9.134679999999999</v>
       </c>
       <c r="W6">
-        <v>9.085626668010763</v>
+        <v>9.101985662069314</v>
       </c>
       <c r="X6">
-        <v>8.9630875</v>
+        <v>8.9715075</v>
       </c>
       <c r="Y6">
-        <v>0.003888949807993904</v>
+        <v>0.004761715015627195</v>
       </c>
       <c r="Z6">
-        <v>0.4029729857831228</v>
+        <v>0.493867957401203</v>
       </c>
       <c r="AA6">
-        <v>0.003888949807993904</v>
+        <v>0.004761715015627195</v>
       </c>
       <c r="AB6">
-        <v>0.4368492710528975</v>
+        <v>0.4362234145473332</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3631507289471026</v>
+        <v>0.3637765854526669</v>
       </c>
       <c r="AE6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1506,22 +1503,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.009650646433373846</v>
+        <v>0.009641676371724851</v>
       </c>
       <c r="AJ6">
-        <v>51810.0008586887</v>
+        <v>51858.20190628866</v>
       </c>
       <c r="AK6">
-        <v>38857.50064401652</v>
+        <v>38893.6514297165</v>
       </c>
       <c r="AL6">
         <v>4293.44248218223</v>
       </c>
       <c r="AM6">
-        <v>388.5750064401652</v>
+        <v>388.936514297165</v>
       </c>
       <c r="AN6">
-        <v>0.003885750064401652</v>
+        <v>0.00388936514297165</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1530,31 +1527,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.3427106174777593</v>
+        <v>0.3433413971581619</v>
       </c>
       <c r="AR6">
-        <v>0.06264082979442238</v>
+        <v>0.06211157860645996</v>
       </c>
       <c r="AS6">
-        <v>0.1593728395024146</v>
+        <v>0.1606263036626226</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
         <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1562,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1586,70 +1583,70 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.6146742369239991</v>
+        <v>0.5645803466869699</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>4.73606</v>
+        <v>4.73979</v>
       </c>
       <c r="S7">
-        <v>4.747009217733437</v>
+        <v>4.753167566706827</v>
       </c>
       <c r="T7">
-        <v>4.727661203922364</v>
+        <v>4.733936258112715</v>
       </c>
       <c r="U7">
-        <v>4.73606</v>
+        <v>4.73979</v>
       </c>
       <c r="V7">
-        <v>4.77885</v>
+        <v>4.78631</v>
       </c>
       <c r="W7">
-        <v>4.747009217733437</v>
+        <v>4.753167566706827</v>
       </c>
       <c r="X7">
-        <v>4.687845</v>
+        <v>4.691575</v>
       </c>
       <c r="Y7">
-        <v>0.002311883239113675</v>
+        <v>0.002822396500019315</v>
       </c>
       <c r="Z7">
-        <v>0.2270915220042878</v>
+        <v>0.2774565323411092</v>
       </c>
       <c r="AA7">
-        <v>0.002311883239113675</v>
+        <v>0.002822396500019315</v>
       </c>
       <c r="AB7">
-        <v>0.4548413725388539</v>
+        <v>0.455160017866904</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3451586274611462</v>
+        <v>0.344839982133096</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1661,22 +1658,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01018040311989288</v>
+        <v>0.01017239160384741</v>
       </c>
       <c r="AJ7">
-        <v>49113.96868194556</v>
+        <v>49152.64959037655</v>
       </c>
       <c r="AK7">
-        <v>49113.96868194556</v>
+        <v>49152.64959037655</v>
       </c>
       <c r="AL7">
         <v>10370.21673752984</v>
       </c>
       <c r="AM7">
-        <v>491.1396868194556</v>
+        <v>491.5264959037655</v>
       </c>
       <c r="AN7">
-        <v>0.004911396868194556</v>
+        <v>0.004915264959037656</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1685,31 +1682,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.1193955459506451</v>
+        <v>0.1194148283922898</v>
       </c>
       <c r="AR7">
-        <v>0.05396774815989491</v>
+        <v>0.05393427881986854</v>
       </c>
       <c r="AS7">
-        <v>0.08289768105804476</v>
+        <v>0.08360500250308057</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
         <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1717,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1729,82 +1726,82 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.5769827144540528</v>
       </c>
       <c r="L8">
-        <v>0.5011456292692775</v>
+        <v>2.089533310047968</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
         <v>75</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>0.5672629641594604</v>
       </c>
       <c r="R8">
-        <v>0.699785</v>
+        <v>7.7303</v>
       </c>
       <c r="S8">
-        <v>0.6988379516944501</v>
+        <v>7.742872688816446</v>
       </c>
       <c r="T8">
-        <v>0.6893163884710802</v>
+        <v>7.778306164432515</v>
       </c>
       <c r="U8">
-        <v>0.699785</v>
+        <v>7.7303</v>
       </c>
       <c r="V8">
-        <v>0.70987</v>
+        <v>7.7147</v>
       </c>
       <c r="W8">
-        <v>0.6987353225</v>
+        <v>7.742872688816446</v>
       </c>
       <c r="X8">
-        <v>0.7076600000000001</v>
+        <v>7.6694</v>
       </c>
       <c r="Y8">
-        <v>-0.00135334182005891</v>
+        <v>0.001626416674184201</v>
       </c>
       <c r="Z8">
-        <v>0.1332923809523801</v>
+        <v>0.2064480922240761</v>
       </c>
       <c r="AA8">
-        <v>0.00135334182005891</v>
+        <v>0.001626416674184201</v>
       </c>
       <c r="AB8">
-        <v>0.4386113989196185</v>
+        <v>0.3938720254548191</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3613886010803815</v>
+        <v>0.4061279745451808</v>
       </c>
       <c r="AE8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1813,58 +1810,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>283.6314820797302</v>
       </c>
       <c r="AI8">
-        <v>0.01125345641875726</v>
+        <v>0.007878090112932164</v>
       </c>
       <c r="AJ8">
-        <v>44430.79365079337</v>
+        <v>63467.15927750462</v>
       </c>
       <c r="AK8">
-        <v>33323.09523809503</v>
+        <v>36002.56889853787</v>
       </c>
       <c r="AL8">
-        <v>47619.04761904731</v>
+        <v>4657.331397039942</v>
       </c>
       <c r="AM8">
-        <v>333.2309523809503</v>
+        <v>360.0256889853787</v>
       </c>
       <c r="AN8">
-        <v>0.003332309523809503</v>
+        <v>0.003600256889853787</v>
       </c>
       <c r="AO8">
-        <v>374.9999999999999</v>
+        <v>283.6314820797302</v>
       </c>
       <c r="AP8">
-        <v>0.003749999999999999</v>
+        <v>0.002836314820797302</v>
       </c>
       <c r="AQ8">
-        <v>0.02482735900452658</v>
+        <v>0.2355448672541067</v>
       </c>
       <c r="AR8">
-        <v>0.008516252452704919</v>
+        <v>0.05671041630417055</v>
       </c>
       <c r="AS8">
-        <v>0.01396386687521369</v>
+        <v>0.08333685902443488</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1872,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,73 +1890,73 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K9">
-        <v>0.409297788694392</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1.897848379278704</v>
+        <v>0.517013818993594</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.693026658479206</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>163.206</v>
+        <v>0.69902</v>
       </c>
       <c r="S9">
-        <v>162.5092159817407</v>
+        <v>0.6976119791031391</v>
       </c>
       <c r="T9">
-        <v>159.7395076927804</v>
+        <v>0.6881206601853984</v>
       </c>
       <c r="U9">
-        <v>163.206</v>
+        <v>0.69902</v>
       </c>
       <c r="V9">
-        <v>164.682</v>
+        <v>0.70834</v>
       </c>
       <c r="W9">
-        <v>162.5092159817407</v>
+        <v>0.6976119791031391</v>
       </c>
       <c r="X9">
-        <v>164.7835</v>
+        <v>0.7068950000000001</v>
       </c>
       <c r="Y9">
-        <v>-0.00426935295429891</v>
+        <v>-0.002014278413866375</v>
       </c>
       <c r="Z9">
-        <v>0.4417014378822909</v>
+        <v>0.1787963043632844</v>
       </c>
       <c r="AA9">
-        <v>0.00426935295429891</v>
+        <v>0.002014278413866375</v>
       </c>
       <c r="AB9">
-        <v>0.3798860780251876</v>
+        <v>0.4383931907835943</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4201139219748123</v>
+        <v>0.3616068092164058</v>
       </c>
       <c r="AE9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1968,58 +1965,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>346.513329239603</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.009665698565003655</v>
+        <v>0.01126577208091335</v>
       </c>
       <c r="AJ9">
-        <v>51729.31854199727</v>
+        <v>44382.22222222194</v>
       </c>
       <c r="AK9">
-        <v>35849.7967745668</v>
+        <v>33286.66666666645</v>
       </c>
       <c r="AL9">
-        <v>219.6597966653603</v>
+        <v>47619.04761904731</v>
       </c>
       <c r="AM9">
-        <v>358.497967745668</v>
+        <v>332.8666666666645</v>
       </c>
       <c r="AN9">
-        <v>0.00358497967745668</v>
+        <v>0.003328666666666645</v>
       </c>
       <c r="AO9">
-        <v>346.513329239603</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP9">
-        <v>0.00346513329239603</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ9">
-        <v>4.35632839558128</v>
+        <v>0.02478071637225347</v>
       </c>
       <c r="AR9">
-        <v>1.297656849764627</v>
+        <v>0.008504010781145887</v>
       </c>
       <c r="AS9">
-        <v>1.59678822025513</v>
+        <v>0.01383211838362513</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
         <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2027,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2039,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2051,70 +2048,70 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.277602445120374</v>
+        <v>1.280426642031332</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.76844</v>
+        <v>6.773065000000001</v>
       </c>
       <c r="S10">
-        <v>6.722623968421908</v>
+        <v>6.724088244609129</v>
       </c>
       <c r="T10">
-        <v>6.693952186231321</v>
+        <v>6.687684289137645</v>
       </c>
       <c r="U10">
-        <v>6.76844</v>
+        <v>6.773065000000001</v>
       </c>
       <c r="V10">
-        <v>6.73208</v>
+        <v>6.741330000000001</v>
       </c>
       <c r="W10">
-        <v>6.722623968421908</v>
+        <v>6.724088244609129</v>
       </c>
       <c r="X10">
-        <v>6.798984021052061</v>
+        <v>6.805716170260582</v>
       </c>
       <c r="Y10">
-        <v>-0.006769068142451075</v>
+        <v>-0.00723110665420636</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.006769068142451075</v>
+        <v>0.00723110665420636</v>
       </c>
       <c r="AB10">
-        <v>0.438735661047352</v>
+        <v>0.4397137256955553</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3612643389526481</v>
+        <v>0.3602862743044447</v>
       </c>
       <c r="AE10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2126,55 +2123,55 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004512712094967383</v>
+        <v>0.004820737769470907</v>
       </c>
       <c r="AJ10">
-        <v>110798.1164049008</v>
+        <v>103718.5642343862</v>
       </c>
       <c r="AK10">
-        <v>83098.58730367562</v>
+        <v>77788.92317578966</v>
       </c>
       <c r="AL10">
-        <v>12277.36188895456</v>
+        <v>11485.04010751257</v>
       </c>
       <c r="AM10">
-        <v>830.9858730367563</v>
+        <v>777.8892317578966</v>
       </c>
       <c r="AN10">
-        <v>0.008309858730367563</v>
+        <v>0.007778892317578966</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ10">
-        <v>0.08289262945967629</v>
+        <v>0.08215449696218889</v>
       </c>
       <c r="AR10">
-        <v>0.01702914884780859</v>
+        <v>0.01649605142704881</v>
       </c>
       <c r="AS10">
-        <v>0.04250318700793362</v>
+        <v>0.04242070303057858</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
         <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2182,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2206,70 +2203,70 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.744476749522717</v>
+        <v>1.6162473010679</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4081.49</v>
+        <v>4130.68</v>
       </c>
       <c r="S11">
-        <v>3994.775050915919</v>
+        <v>4075.017895985588</v>
       </c>
       <c r="T11">
-        <v>3875.466065930238</v>
+        <v>3954.335547244615</v>
       </c>
       <c r="U11">
-        <v>4081.49</v>
+        <v>4130.68</v>
       </c>
       <c r="V11">
-        <v>4073.719999999999</v>
+        <v>4172.1</v>
       </c>
       <c r="W11">
-        <v>3994.775050915919</v>
+        <v>4075.017895985588</v>
       </c>
       <c r="X11">
-        <v>4211.355</v>
+        <v>4270.64</v>
       </c>
       <c r="Y11">
-        <v>-0.02124590506998207</v>
+        <v>-0.01347528833373969</v>
       </c>
       <c r="Z11">
-        <v>0.6677314833410172</v>
+        <v>0.3977000858417536</v>
       </c>
       <c r="AA11">
-        <v>0.02124590506998207</v>
+        <v>0.01347528833373969</v>
       </c>
       <c r="AB11">
-        <v>0.4060396050237004</v>
+        <v>0.4077713460155915</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3939603949762996</v>
+        <v>0.3922286539844085</v>
       </c>
       <c r="AE11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2281,22 +2278,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03181803704039454</v>
+        <v>0.03388304104893142</v>
       </c>
       <c r="AJ11">
-        <v>15714.35721711009</v>
+        <v>14756.64475564447</v>
       </c>
       <c r="AK11">
-        <v>11785.76791283257</v>
+        <v>11067.48356673335</v>
       </c>
       <c r="AL11">
-        <v>2.887614060755403</v>
+        <v>2.679336953415261</v>
       </c>
       <c r="AM11">
-        <v>117.8576791283257</v>
+        <v>110.6748356673335</v>
       </c>
       <c r="AN11">
-        <v>0.001178576791283257</v>
+        <v>0.001106748356673335</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2305,31 +2302,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>479.5640542692452</v>
+        <v>491.3608737453328</v>
       </c>
       <c r="AR11">
-        <v>176.4777570938011</v>
+        <v>175.0944694009438</v>
       </c>
       <c r="AS11">
-        <v>216.2568490306786</v>
+        <v>226.1283078639245</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03338830132778246</v>
+        <v>0.0331732132678858</v>
       </c>
       <c r="AV11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
         <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>Pair</t>
   </si>
@@ -172,6 +172,9 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
@@ -187,9 +190,6 @@
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
@@ -238,40 +238,43 @@
     <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06058,naive=0.01192,drift4=0.01764; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=6.297,naive=1.563,drift4=1.65; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06019,naive=0.01772,drift4=0.02948; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.0368,naive=0.01353,drift4=0.01889; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.304,naive=0.1046,drift4=0.1759; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.1388,naive=0.07863,drift4=0.1135; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3354,naive=0.07086,drift4=0.09592; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02953,naive=0.01244,drift4=0.01861; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09405,naive=0.02358,drift4=0.05085; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=672.5,naive=216.9,drift4=272.7; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06042,naive=0.01217,drift4=0.01781; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3256,naive=0.07134,drift4=0.09604; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.617,naive=1.817,drift4=1.776; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05656,naive=0.01815,drift4=0.03124; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03582,naive=0.01381,drift4=0.01942; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.255,naive=0.1084,drift4=0.1817; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.1312,naive=0.07405,drift4=0.1133; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02833,naive=0.012,drift4=0.0188; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09412,naive=0.02235,drift4=0.05142; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=647.6,naive=216.3,drift4=271.7; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +811,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +835,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>1.842751679610346</v>
+        <v>2.019393163375722</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
         <v>71</v>
@@ -856,37 +859,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.14124</v>
+        <v>1.137675</v>
       </c>
       <c r="S2">
-        <v>1.152592064868947</v>
+        <v>1.147552693993932</v>
       </c>
       <c r="T2">
-        <v>1.166781380602185</v>
+        <v>1.16310567387802</v>
       </c>
       <c r="U2">
-        <v>1.14124</v>
+        <v>1.137675</v>
       </c>
       <c r="V2">
-        <v>1.14418</v>
+        <v>1.13705</v>
       </c>
       <c r="Y2">
-        <v>0.009947131952040878</v>
+        <v>0.008682351281281378</v>
       </c>
       <c r="AA2">
-        <v>0.009947131952040878</v>
+        <v>0.008682351281281378</v>
       </c>
       <c r="AB2">
-        <v>0.3982086327981558</v>
+        <v>0.3982892187903161</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4017913672018444</v>
+        <v>0.4017107812096839</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -919,31 +922,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03986427651647348</v>
+        <v>0.03771048971631439</v>
       </c>
       <c r="AR2">
-        <v>0.009027634381983908</v>
+        <v>0.008822693316030753</v>
       </c>
       <c r="AS2">
-        <v>0.01400523421017505</v>
+        <v>0.01363574682142654</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY2" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +954,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,73 +966,73 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.5599390518113131</v>
       </c>
       <c r="L3">
-        <v>2.42202431667825</v>
+        <v>2.076735691128985</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>163.0645</v>
+        <v>7.7102</v>
       </c>
       <c r="S3">
-        <v>162.3710182522998</v>
+        <v>7.714633524250251</v>
       </c>
       <c r="T3">
-        <v>159.7694156623443</v>
+        <v>7.758038419689299</v>
       </c>
       <c r="U3">
-        <v>163.0645</v>
+        <v>7.7102</v>
       </c>
       <c r="V3">
-        <v>164.399</v>
+        <v>7.674500000000001</v>
       </c>
       <c r="Y3">
-        <v>-0.004252806390724029</v>
+        <v>0.0005750206544902723</v>
       </c>
       <c r="AA3">
-        <v>0.004252806390724029</v>
+        <v>0.0005750206544902723</v>
       </c>
       <c r="AB3">
-        <v>0.3803973789560492</v>
+        <v>0.394950303979426</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4196026210439507</v>
+        <v>0.4050496960205741</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1062,31 +1065,31 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>4.322987783340024</v>
+        <v>0.2170692225964442</v>
       </c>
       <c r="AR3">
-        <v>1.268066795129204</v>
+        <v>0.05413327404276985</v>
       </c>
       <c r="AS3">
-        <v>1.596215101082956</v>
+        <v>0.08037315899415744</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1097,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1109,79 +1112,70 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
         <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>0.3098825048213359</v>
+        <v>2.778900950289698</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.337615</v>
+        <v>163.8215</v>
       </c>
       <c r="S4">
-        <v>1.357987898235275</v>
+        <v>163.3539978929823</v>
       </c>
       <c r="T4">
-        <v>1.370038281627247</v>
+        <v>160.2580387565872</v>
       </c>
       <c r="U4">
-        <v>1.337615</v>
+        <v>163.8215</v>
       </c>
       <c r="V4">
-        <v>1.35513</v>
-      </c>
-      <c r="W4">
-        <v>1.357987898235275</v>
-      </c>
-      <c r="X4">
-        <v>1.32403306784315</v>
+        <v>165.913</v>
       </c>
       <c r="Y4">
-        <v>0.01523076388592731</v>
-      </c>
-      <c r="Z4">
-        <v>1.5</v>
+        <v>-0.002853728643784117</v>
       </c>
       <c r="AA4">
-        <v>0.01523076388592731</v>
+        <v>0.002853728643784117</v>
       </c>
       <c r="AB4">
-        <v>0.4266687733916356</v>
+        <v>0.3785529228005374</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3733312266083645</v>
+        <v>0.4214470771994626</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1190,58 +1184,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
-      </c>
-      <c r="AI4">
-        <v>0.01015384259061821</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>49242.44152277704</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>36931.83114208278</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>27610.21006947648</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>369.3183114208278</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.003693183114208278</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>375.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.003750000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0.04199378495487448</v>
+        <v>4.334028565242894</v>
       </c>
       <c r="AR4">
-        <v>0.01052902137473537</v>
+        <v>1.351815728900176</v>
       </c>
       <c r="AS4">
-        <v>0.02452905588349166</v>
+        <v>1.547485761136729</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1240,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,70 +1264,70 @@
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.881072780285014</v>
+        <v>0.006122699155397303</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="O5" t="s">
         <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>0.81419</v>
+        <v>1.331435</v>
       </c>
       <c r="S5">
-        <v>0.823105140285445</v>
+        <v>1.349377301264372</v>
       </c>
       <c r="T5">
-        <v>0.8311410786398341</v>
+        <v>1.363208406729081</v>
       </c>
       <c r="U5">
-        <v>0.81419</v>
+        <v>1.331435</v>
       </c>
       <c r="V5">
-        <v>0.81878</v>
+        <v>1.34277</v>
       </c>
       <c r="W5">
-        <v>0.823105140285445</v>
+        <v>1.349377301264372</v>
       </c>
       <c r="X5">
-        <v>0.8058149999999999</v>
+        <v>1.31909</v>
       </c>
       <c r="Y5">
-        <v>0.0109497049649898</v>
+        <v>0.01347591227838536</v>
       </c>
       <c r="Z5">
-        <v>1.064494362441193</v>
+        <v>1.453406339762808</v>
       </c>
       <c r="AA5">
-        <v>0.0109497049649898</v>
+        <v>0.01347591227838536</v>
       </c>
       <c r="AB5">
-        <v>0.4241652721590743</v>
+        <v>0.4341973120509994</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3758347278409258</v>
+        <v>0.3658026879490006</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1345,58 +1336,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01028629681032689</v>
+        <v>0.009271950940151119</v>
       </c>
       <c r="AJ5">
-        <v>48608.35820895493</v>
+        <v>53926.08343458844</v>
       </c>
       <c r="AK5">
-        <v>48608.35820895493</v>
+        <v>40444.56257594133</v>
       </c>
       <c r="AL5">
-        <v>59701.49253731308</v>
+        <v>30376.67071688917</v>
       </c>
       <c r="AM5">
-        <v>486.0835820895493</v>
+        <v>404.4456257594133</v>
       </c>
       <c r="AN5">
-        <v>0.004860835820895493</v>
+        <v>0.004044456257594133</v>
       </c>
       <c r="AO5">
-        <v>499.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.004999999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.03030521311426044</v>
+        <v>0.03994361970720553</v>
       </c>
       <c r="AR5">
-        <v>0.01050639352901101</v>
+        <v>0.01069045830781607</v>
       </c>
       <c r="AS5">
-        <v>0.01412372403828651</v>
+        <v>0.02399750893892211</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY5" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1395,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,7 +1407,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1428,70 +1419,70 @@
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0.0594261786988079</v>
+        <v>2.077023474180427</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="O6" t="s">
         <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>9.05885</v>
+        <v>0.816755</v>
       </c>
       <c r="S6">
-        <v>9.101985662069314</v>
+        <v>0.8258748342911921</v>
       </c>
       <c r="T6">
-        <v>9.094497980085102</v>
+        <v>0.8318521859791179</v>
       </c>
       <c r="U6">
-        <v>9.05885</v>
+        <v>0.816755</v>
       </c>
       <c r="V6">
-        <v>9.134679999999999</v>
+        <v>0.82391</v>
       </c>
       <c r="W6">
-        <v>9.101985662069314</v>
+        <v>0.8258748342911921</v>
       </c>
       <c r="X6">
-        <v>8.9715075</v>
+        <v>0.80838</v>
       </c>
       <c r="Y6">
-        <v>0.004761715015627195</v>
+        <v>0.01116593628590228</v>
       </c>
       <c r="Z6">
-        <v>0.493867957401203</v>
+        <v>1.088935437754277</v>
       </c>
       <c r="AA6">
-        <v>0.004761715015627195</v>
+        <v>0.01116593628590228</v>
       </c>
       <c r="AB6">
-        <v>0.4362234145473332</v>
+        <v>0.4275692234002926</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3637765854526669</v>
+        <v>0.3724307765997074</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1500,58 +1491,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.009641676371724851</v>
+        <v>0.01025399293545806</v>
       </c>
       <c r="AJ6">
-        <v>51858.20190628866</v>
+        <v>48761.49253731315</v>
       </c>
       <c r="AK6">
-        <v>38893.6514297165</v>
+        <v>48761.49253731315</v>
       </c>
       <c r="AL6">
-        <v>4293.44248218223</v>
+        <v>59701.49253731308</v>
       </c>
       <c r="AM6">
-        <v>388.936514297165</v>
+        <v>487.6149253731315</v>
       </c>
       <c r="AN6">
-        <v>0.00388936514297165</v>
+        <v>0.004876149253731315</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.3433413971581619</v>
+        <v>0.02904960493074168</v>
       </c>
       <c r="AR6">
-        <v>0.06211157860645996</v>
+        <v>0.01012901925524903</v>
       </c>
       <c r="AS6">
-        <v>0.1606263036626226</v>
+        <v>0.01385692835528336</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW6" t="s">
         <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY6" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1550,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1580,73 +1571,73 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5645803466869699</v>
+        <v>0.2169207677842748</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>4.73979</v>
+        <v>9.023020000000001</v>
       </c>
       <c r="S7">
-        <v>4.753167566706827</v>
+        <v>9.046422426282696</v>
       </c>
       <c r="T7">
-        <v>4.733936258112715</v>
+        <v>9.043861637992112</v>
       </c>
       <c r="U7">
-        <v>4.73979</v>
+        <v>9.023020000000001</v>
       </c>
       <c r="V7">
-        <v>4.78631</v>
+        <v>9.063020000000002</v>
       </c>
       <c r="W7">
-        <v>4.753167566706827</v>
+        <v>9.046422426282696</v>
       </c>
       <c r="X7">
-        <v>4.691575</v>
+        <v>8.931675</v>
       </c>
       <c r="Y7">
-        <v>0.002822396500019315</v>
+        <v>0.00259363564335392</v>
       </c>
       <c r="Z7">
-        <v>0.2774565323411092</v>
+        <v>0.2561982186512156</v>
       </c>
       <c r="AA7">
-        <v>0.002822396500019315</v>
+        <v>0.00259363564335392</v>
       </c>
       <c r="AB7">
-        <v>0.455160017866904</v>
+        <v>0.448763506700894</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.344839982133096</v>
+        <v>0.3512364932991061</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1655,58 +1646,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.01017239160384741</v>
+        <v>0.01012355065155569</v>
       </c>
       <c r="AJ7">
-        <v>49152.64959037655</v>
+        <v>49389.78597624391</v>
       </c>
       <c r="AK7">
-        <v>49152.64959037655</v>
+        <v>37042.33948218294</v>
       </c>
       <c r="AL7">
-        <v>10370.21673752984</v>
+        <v>4105.315014505446</v>
       </c>
       <c r="AM7">
-        <v>491.5264959037655</v>
+        <v>370.4233948218293</v>
       </c>
       <c r="AN7">
-        <v>0.004915264959037656</v>
+        <v>0.003704233948218293</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ7">
-        <v>0.1194148283922898</v>
+        <v>0.2765920394353519</v>
       </c>
       <c r="AR7">
-        <v>0.05393427881986854</v>
+        <v>0.06440023431951196</v>
       </c>
       <c r="AS7">
-        <v>0.08360500250308057</v>
+        <v>0.1554740610040493</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW7" t="s">
         <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY7" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1705,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,70 +1729,70 @@
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K8">
-        <v>0.5769827144540528</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>2.089533310047968</v>
+        <v>0.5862595877272422</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q8">
-        <v>0.5672629641594604</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>7.7303</v>
+        <v>4.72195</v>
       </c>
       <c r="S8">
-        <v>7.742872688816446</v>
+        <v>4.730670853721815</v>
       </c>
       <c r="T8">
-        <v>7.778306164432515</v>
+        <v>4.719712417646137</v>
       </c>
       <c r="U8">
-        <v>7.7303</v>
+        <v>4.72195</v>
       </c>
       <c r="V8">
-        <v>7.7147</v>
+        <v>4.750629999999999</v>
       </c>
       <c r="W8">
-        <v>7.742872688816446</v>
+        <v>4.730670853721815</v>
       </c>
       <c r="X8">
-        <v>7.6694</v>
+        <v>4.673735</v>
       </c>
       <c r="Y8">
-        <v>0.001626416674184201</v>
+        <v>0.001846875490383275</v>
       </c>
       <c r="Z8">
-        <v>0.2064480922240761</v>
+        <v>0.1808742864630369</v>
       </c>
       <c r="AA8">
-        <v>0.001626416674184201</v>
+        <v>0.001846875490383275</v>
       </c>
       <c r="AB8">
-        <v>0.3938720254548191</v>
+        <v>0.4600342327998223</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.4061279745451808</v>
+        <v>0.3399657672001777</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1810,58 +1801,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>283.6314820797302</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.007878090112932164</v>
+        <v>0.01021082391808467</v>
       </c>
       <c r="AJ8">
-        <v>63467.15927750462</v>
+        <v>48967.64492377901</v>
       </c>
       <c r="AK8">
-        <v>36002.56889853787</v>
+        <v>48967.64492377901</v>
       </c>
       <c r="AL8">
-        <v>4657.331397039942</v>
+        <v>10370.21673752984</v>
       </c>
       <c r="AM8">
-        <v>360.0256889853787</v>
+        <v>489.6764492377901</v>
       </c>
       <c r="AN8">
-        <v>0.003600256889853787</v>
+        <v>0.004896764492377901</v>
       </c>
       <c r="AO8">
-        <v>283.6314820797302</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>0.002836314820797302</v>
+        <v>0.005</v>
       </c>
       <c r="AQ8">
-        <v>0.2355448672541067</v>
+        <v>0.1069903650488819</v>
       </c>
       <c r="AR8">
-        <v>0.05671041630417055</v>
+        <v>0.0490083111201273</v>
       </c>
       <c r="AS8">
-        <v>0.08333685902443488</v>
+        <v>0.07967664338601504</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW8" t="s">
         <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY8" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1860,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,70 +1884,70 @@
         <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.517013818993594</v>
+        <v>0.7086979502669031</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" t="s">
         <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
         <v>0.75</v>
       </c>
       <c r="R9">
-        <v>0.69902</v>
+        <v>0.6968300000000001</v>
       </c>
       <c r="S9">
-        <v>0.6976119791031391</v>
+        <v>0.694886449949119</v>
       </c>
       <c r="T9">
-        <v>0.6881206601853984</v>
+        <v>0.6866870261906244</v>
       </c>
       <c r="U9">
-        <v>0.69902</v>
+        <v>0.6968300000000001</v>
       </c>
       <c r="V9">
-        <v>0.70834</v>
+        <v>0.7039600000000001</v>
       </c>
       <c r="W9">
-        <v>0.6976119791031391</v>
+        <v>0.694886449949119</v>
       </c>
       <c r="X9">
-        <v>0.7068950000000001</v>
+        <v>0.7047050000000001</v>
       </c>
       <c r="Y9">
-        <v>-0.002014278413866375</v>
+        <v>-0.002789130850969523</v>
       </c>
       <c r="Z9">
-        <v>0.1787963043632844</v>
+        <v>0.2468000064610897</v>
       </c>
       <c r="AA9">
-        <v>0.002014278413866375</v>
+        <v>0.002789130850969523</v>
       </c>
       <c r="AB9">
-        <v>0.4383931907835943</v>
+        <v>0.4427465782834746</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3616068092164058</v>
+        <v>0.3572534217165254</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1968,55 +1959,55 @@
         <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.01126577208091335</v>
+        <v>0.0113011781926726</v>
       </c>
       <c r="AJ9">
-        <v>44382.22222222194</v>
+        <v>44243.17460317433</v>
       </c>
       <c r="AK9">
-        <v>33286.66666666645</v>
+        <v>33182.38095238075</v>
       </c>
       <c r="AL9">
-        <v>47619.04761904731</v>
+        <v>47619.04761904733</v>
       </c>
       <c r="AM9">
-        <v>332.8666666666645</v>
+        <v>331.8238095238075</v>
       </c>
       <c r="AN9">
-        <v>0.003328666666666645</v>
+        <v>0.003318238095238075</v>
       </c>
       <c r="AO9">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP9">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.02478071637225347</v>
+        <v>0.02288013110467144</v>
       </c>
       <c r="AR9">
-        <v>0.008504010781145887</v>
+        <v>0.007844703524473881</v>
       </c>
       <c r="AS9">
-        <v>0.01383211838362513</v>
+        <v>0.01343749175863589</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW9" t="s">
         <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY9" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2015,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,7 +2027,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2048,70 +2039,70 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.280426642031332</v>
+        <v>1.201166085349996</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.773065000000001</v>
+        <v>6.77675</v>
       </c>
       <c r="S10">
-        <v>6.724088244609129</v>
+        <v>6.734875423863052</v>
       </c>
       <c r="T10">
-        <v>6.687684289137645</v>
+        <v>6.704749770457378</v>
       </c>
       <c r="U10">
-        <v>6.773065000000001</v>
+        <v>6.77675</v>
       </c>
       <c r="V10">
-        <v>6.741330000000001</v>
+        <v>6.748699999999999</v>
       </c>
       <c r="W10">
-        <v>6.724088244609129</v>
+        <v>6.734875423863052</v>
       </c>
       <c r="X10">
-        <v>6.805716170260582</v>
+        <v>6.80655</v>
       </c>
       <c r="Y10">
-        <v>-0.00723110665420636</v>
+        <v>-0.00617915315408535</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>1.405187118689524</v>
       </c>
       <c r="AA10">
-        <v>0.00723110665420636</v>
+        <v>0.00617915315408535</v>
       </c>
       <c r="AB10">
-        <v>0.4397137256955553</v>
+        <v>0.4421950997571019</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3602862743044447</v>
+        <v>0.3578049002428981</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2123,55 +2114,55 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004820737769470907</v>
+        <v>0.004397388128527694</v>
       </c>
       <c r="AJ10">
-        <v>103718.5642343862</v>
+        <v>113703.8590604025</v>
       </c>
       <c r="AK10">
-        <v>77788.92317578966</v>
+        <v>85277.89429530187</v>
       </c>
       <c r="AL10">
-        <v>11485.04010751257</v>
+        <v>12583.89261744964</v>
       </c>
       <c r="AM10">
-        <v>777.8892317578966</v>
+        <v>852.7789429530187</v>
       </c>
       <c r="AN10">
-        <v>0.007778892317578966</v>
+        <v>0.008527789429530187</v>
       </c>
       <c r="AO10">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08215449696218889</v>
+        <v>0.0781814767500027</v>
       </c>
       <c r="AR10">
-        <v>0.01649605142704881</v>
+        <v>0.01509575995489133</v>
       </c>
       <c r="AS10">
-        <v>0.04242070303057858</v>
+        <v>0.04124627195558649</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW10" t="s">
         <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY10" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2170,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,70 +2194,70 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.6162473010679</v>
+        <v>1.679542508140375</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4130.68</v>
+        <v>4045.89</v>
       </c>
       <c r="S11">
-        <v>4075.017895985588</v>
+        <v>3948.672403070427</v>
       </c>
       <c r="T11">
-        <v>3954.335547244615</v>
+        <v>3849.867213019518</v>
       </c>
       <c r="U11">
-        <v>4130.68</v>
+        <v>4045.89</v>
       </c>
       <c r="V11">
-        <v>4172.1</v>
+        <v>4002.52</v>
       </c>
       <c r="W11">
-        <v>4075.017895985588</v>
+        <v>3948.672403070427</v>
       </c>
       <c r="X11">
-        <v>4270.64</v>
+        <v>4175.755</v>
       </c>
       <c r="Y11">
-        <v>-0.01347528833373969</v>
+        <v>-0.02402872963169356</v>
       </c>
       <c r="Z11">
-        <v>0.3977000858417536</v>
+        <v>0.7486050662578273</v>
       </c>
       <c r="AA11">
-        <v>0.01347528833373969</v>
+        <v>0.02402872963169356</v>
       </c>
       <c r="AB11">
-        <v>0.4077713460155915</v>
+        <v>0.4095673466974834</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3922286539844085</v>
+        <v>0.3904326533025166</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2278,22 +2269,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03388304104893142</v>
+        <v>0.03209800563040515</v>
       </c>
       <c r="AJ11">
-        <v>14756.64475564447</v>
+        <v>15577.29180302623</v>
       </c>
       <c r="AK11">
-        <v>11067.48356673335</v>
+        <v>11682.96885226967</v>
       </c>
       <c r="AL11">
-        <v>2.679336953415261</v>
+        <v>2.887614060755402</v>
       </c>
       <c r="AM11">
-        <v>110.6748356673335</v>
+        <v>116.8296885226967</v>
       </c>
       <c r="AN11">
-        <v>0.001106748356673335</v>
+        <v>0.001168296885226967</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2302,31 +2293,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>491.3608737453328</v>
+        <v>457.5576281083092</v>
       </c>
       <c r="AR11">
-        <v>175.0944694009438</v>
+        <v>161.5656106266083</v>
       </c>
       <c r="AS11">
-        <v>226.1283078639245</v>
+        <v>210.6508695646872</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.0331732132678858</v>
+        <v>0.03053592836191687</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AW11" t="s">
         <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY11" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -172,27 +172,27 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -205,15 +205,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -247,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06042,naive=0.01217,drift4=0.01781; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3256,naive=0.07134,drift4=0.09604; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.617,naive=1.817,drift4=1.776; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.05656,naive=0.01815,drift4=0.03124; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03582,naive=0.01381,drift4=0.01942; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.255,naive=0.1084,drift4=0.1817; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.1312,naive=0.07405,drift4=0.1133; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02833,naive=0.012,drift4=0.0188; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09412,naive=0.02235,drift4=0.05142; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=647.6,naive=216.3,drift4=271.7; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06205,naive=0.01199,drift4=0.01825; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.651,naive=1.838,drift4=1.792; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03434,naive=0.01326,drift4=0.01963; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05644,naive=0.01842,drift4=0.03257; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.2344,naive=0.1097,drift4=0.1877; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1239,naive=0.07093,drift4=0.1188; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02693,naive=0.01167,drift4=0.0195; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3212,naive=0.07231,drift4=0.09659; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09535,naive=0.02125,drift4=0.05183; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=610.2,naive=200.2,drift4=276.5; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -811,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,13 +823,13 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" t="s">
         <v>66</v>
       </c>
-      <c r="H2" t="s">
-        <v>67</v>
-      </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
         <v>46226</v>
@@ -850,10 +847,10 @@
         <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -862,10 +859,10 @@
         <v>1.137675</v>
       </c>
       <c r="S2">
-        <v>1.147552693993932</v>
+        <v>1.14147308816307</v>
       </c>
       <c r="T2">
-        <v>1.16310567387802</v>
+        <v>1.147801345084798</v>
       </c>
       <c r="U2">
         <v>1.137675</v>
@@ -874,22 +871,22 @@
         <v>1.13705</v>
       </c>
       <c r="Y2">
-        <v>0.008682351281281378</v>
+        <v>0.003338464994897421</v>
       </c>
       <c r="AA2">
-        <v>0.008682351281281378</v>
+        <v>0.003338464994897421</v>
       </c>
       <c r="AB2">
-        <v>0.3982892187903161</v>
+        <v>0.3997721335488879</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4017107812096839</v>
+        <v>0.4002278664511121</v>
       </c>
       <c r="AE2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -922,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03771048971631439</v>
+        <v>0.03701207565653994</v>
       </c>
       <c r="AR2">
-        <v>0.008822693316030753</v>
+        <v>0.008068516096769939</v>
       </c>
       <c r="AS2">
-        <v>0.01363574682142654</v>
+        <v>0.0134665992798199</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AX2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -954,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -969,10 +966,10 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
@@ -981,58 +978,58 @@
         <v>46226</v>
       </c>
       <c r="K3">
-        <v>0.5599390518113131</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2.076735691128985</v>
+        <v>2.778900950289698</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>7.7102</v>
+        <v>163.8215</v>
       </c>
       <c r="S3">
-        <v>7.714633524250251</v>
+        <v>163.936866221097</v>
       </c>
       <c r="T3">
-        <v>7.758038419689299</v>
+        <v>161.798829241327</v>
       </c>
       <c r="U3">
-        <v>7.7102</v>
+        <v>163.8215</v>
       </c>
       <c r="V3">
-        <v>7.674500000000001</v>
+        <v>165.913</v>
       </c>
       <c r="Y3">
-        <v>0.0005750206544902723</v>
+        <v>0.0007042190499844018</v>
       </c>
       <c r="AA3">
-        <v>0.0005750206544902723</v>
+        <v>0.0007042190499844018</v>
       </c>
       <c r="AB3">
-        <v>0.394950303979426</v>
+        <v>0.3786507343232977</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4050496960205741</v>
+        <v>0.4213492656767022</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1065,31 +1062,31 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.2170692225964442</v>
+        <v>4.007246171393907</v>
       </c>
       <c r="AR3">
-        <v>0.05413327404276985</v>
+        <v>1.258008626180795</v>
       </c>
       <c r="AS3">
-        <v>0.08037315899415744</v>
+        <v>1.455954520829094</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1097,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1109,16 +1106,16 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
         <v>46226</v>
@@ -1127,55 +1124,64 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.778900950289698</v>
+        <v>2.077023474180427</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>163.8215</v>
+        <v>0.816755</v>
       </c>
       <c r="S4">
-        <v>163.3539978929823</v>
+        <v>0.8237601199010242</v>
       </c>
       <c r="T4">
-        <v>160.2580387565872</v>
+        <v>0.8268747801644387</v>
       </c>
       <c r="U4">
-        <v>163.8215</v>
+        <v>0.816755</v>
       </c>
       <c r="V4">
-        <v>165.913</v>
+        <v>0.82391</v>
+      </c>
+      <c r="W4">
+        <v>0.8237601199010242</v>
+      </c>
+      <c r="X4">
+        <v>0.80838</v>
       </c>
       <c r="Y4">
-        <v>-0.002853728643784117</v>
+        <v>0.008576770146523924</v>
+      </c>
+      <c r="Z4">
+        <v>0.8364322269879531</v>
       </c>
       <c r="AA4">
-        <v>0.002853728643784117</v>
+        <v>0.008576770146523924</v>
       </c>
       <c r="AB4">
-        <v>0.3785529228005374</v>
+        <v>0.4321129493480312</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4214470771994626</v>
+        <v>0.3678870506519688</v>
       </c>
       <c r="AE4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1184,43 +1190,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI4">
+        <v>0.01025399293545806</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>48761.49253731315</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>48761.49253731315</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>59701.49253731308</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>487.6149253731315</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.004876149253731315</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>4.334028565242894</v>
+        <v>0.02710175958981609</v>
       </c>
       <c r="AR4">
-        <v>1.351815728900176</v>
+        <v>0.009069273085628427</v>
       </c>
       <c r="AS4">
-        <v>1.547485761136729</v>
+        <v>0.01327908264551326</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1232,7 +1241,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1240,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1255,13 +1264,13 @@
         <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
         <v>46226</v>
@@ -1279,10 +1288,10 @@
         <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q5">
         <v>0.75</v>
@@ -1291,10 +1300,10 @@
         <v>1.331435</v>
       </c>
       <c r="S5">
-        <v>1.349377301264372</v>
+        <v>1.34050626882868</v>
       </c>
       <c r="T5">
-        <v>1.363208406729081</v>
+        <v>1.342777473049589</v>
       </c>
       <c r="U5">
         <v>1.331435</v>
@@ -1303,31 +1312,31 @@
         <v>1.34277</v>
       </c>
       <c r="W5">
-        <v>1.349377301264372</v>
+        <v>1.34050626882868</v>
       </c>
       <c r="X5">
         <v>1.31909</v>
       </c>
       <c r="Y5">
-        <v>0.01347591227838536</v>
+        <v>0.006813151846451578</v>
       </c>
       <c r="Z5">
-        <v>1.453406339762808</v>
+        <v>0.7348131898485362</v>
       </c>
       <c r="AA5">
-        <v>0.01347591227838536</v>
+        <v>0.006813151846451578</v>
       </c>
       <c r="AB5">
-        <v>0.4341973120509994</v>
+        <v>0.4374156281611774</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3658026879490006</v>
+        <v>0.3625843718388226</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1363,31 +1372,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.03994361970720553</v>
+        <v>0.03855670908636545</v>
       </c>
       <c r="AR5">
-        <v>0.01069045830781607</v>
+        <v>0.01046911245293445</v>
       </c>
       <c r="AS5">
-        <v>0.02399750893892211</v>
+        <v>0.02400559289635933</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1395,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1410,31 +1419,31 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J6" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2.077023474180427</v>
+        <v>0.3302812254125366</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P6" t="s">
         <v>75</v>
@@ -1443,46 +1452,46 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>0.816755</v>
+        <v>9.01909</v>
       </c>
       <c r="S6">
-        <v>0.8258748342911921</v>
+        <v>9.047600489652496</v>
       </c>
       <c r="T6">
-        <v>0.8318521859791179</v>
+        <v>9.05440351587689</v>
       </c>
       <c r="U6">
-        <v>0.816755</v>
+        <v>9.01909</v>
       </c>
       <c r="V6">
-        <v>0.82391</v>
+        <v>9.055160000000001</v>
       </c>
       <c r="W6">
-        <v>0.8258748342911921</v>
+        <v>9.047600489652496</v>
       </c>
       <c r="X6">
-        <v>0.80838</v>
+        <v>8.927745</v>
       </c>
       <c r="Y6">
-        <v>0.01116593628590228</v>
+        <v>0.003161127081833672</v>
       </c>
       <c r="Z6">
-        <v>1.088935437754277</v>
+        <v>0.3121187766434425</v>
       </c>
       <c r="AA6">
-        <v>0.01116593628590228</v>
+        <v>0.003161127081833672</v>
       </c>
       <c r="AB6">
-        <v>0.4275692234002926</v>
+        <v>0.4567317898030007</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3724307765997074</v>
+        <v>0.3432682101969994</v>
       </c>
       <c r="AE6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1494,55 +1503,55 @@
         <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.01025399293545806</v>
+        <v>0.0101279619119002</v>
       </c>
       <c r="AJ6">
-        <v>48761.49253731315</v>
+        <v>49368.27412556789</v>
       </c>
       <c r="AK6">
-        <v>48761.49253731315</v>
+        <v>49368.27412556789</v>
       </c>
       <c r="AL6">
-        <v>59701.49253731308</v>
+        <v>5473.753352673927</v>
       </c>
       <c r="AM6">
-        <v>487.6149253731315</v>
+        <v>493.6827412556789</v>
       </c>
       <c r="AN6">
-        <v>0.004876149253731315</v>
+        <v>0.004936827412556789</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.02904960493074168</v>
+        <v>0.2068138444937041</v>
       </c>
       <c r="AR6">
-        <v>0.01012901925524903</v>
+        <v>0.06318251588168093</v>
       </c>
       <c r="AS6">
-        <v>0.01385692835528336</v>
+        <v>0.1530582066562891</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1550,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1562,82 +1571,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="2">
+        <v>46227</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0.5841023495793738</v>
+      </c>
+      <c r="M7">
+        <v>6</v>
+      </c>
+      <c r="N7">
+        <v>41</v>
+      </c>
+      <c r="O7" t="s">
         <v>70</v>
-      </c>
-      <c r="J7" s="2">
-        <v>46226</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0.2169207677842748</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7" t="s">
-        <v>72</v>
       </c>
       <c r="P7" t="s">
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>9.023020000000001</v>
+        <v>4.7259</v>
       </c>
       <c r="S7">
-        <v>9.046422426282696</v>
+        <v>4.731982382835215</v>
       </c>
       <c r="T7">
-        <v>9.043861637992112</v>
+        <v>4.715816001790408</v>
       </c>
       <c r="U7">
-        <v>9.023020000000001</v>
+        <v>4.7259</v>
       </c>
       <c r="V7">
-        <v>9.063020000000002</v>
+        <v>4.75853</v>
       </c>
       <c r="W7">
-        <v>9.046422426282696</v>
+        <v>4.73298885</v>
       </c>
       <c r="X7">
-        <v>8.931675</v>
+        <v>4.677685</v>
       </c>
       <c r="Y7">
-        <v>0.00259363564335392</v>
+        <v>0.00128703164163762</v>
       </c>
       <c r="Z7">
-        <v>0.2561982186512156</v>
+        <v>0.1470258218396768</v>
       </c>
       <c r="AA7">
-        <v>0.00259363564335392</v>
+        <v>0.00128703164163762</v>
       </c>
       <c r="AB7">
-        <v>0.448763506700894</v>
+        <v>0.4687366672288881</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3512364932991061</v>
+        <v>0.3312633327711119</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1646,58 +1655,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01012355065155569</v>
+        <v>0.01020228951099259</v>
       </c>
       <c r="AJ7">
-        <v>49389.78597624391</v>
+        <v>49008.60727989225</v>
       </c>
       <c r="AK7">
-        <v>37042.33948218294</v>
+        <v>49008.60727989225</v>
       </c>
       <c r="AL7">
-        <v>4105.315014505446</v>
+        <v>10370.21673752984</v>
       </c>
       <c r="AM7">
-        <v>370.4233948218293</v>
+        <v>490.0860727989225</v>
       </c>
       <c r="AN7">
-        <v>0.003704233948218293</v>
+        <v>0.004900860727989225</v>
       </c>
       <c r="AO7">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.2765920394353519</v>
+        <v>0.09593575045248391</v>
       </c>
       <c r="AR7">
-        <v>0.06440023431951196</v>
+        <v>0.04301638947497143</v>
       </c>
       <c r="AS7">
-        <v>0.1554740610040493</v>
+        <v>0.08046618905239736</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1705,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,7 +1735,7 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J8" s="2">
         <v>46226</v>
@@ -1735,64 +1744,64 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.5862595877272422</v>
+        <v>0.7086979502669031</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>4.72195</v>
+        <v>0.6968300000000001</v>
       </c>
       <c r="S8">
-        <v>4.730670853721815</v>
+        <v>0.6955316417411134</v>
       </c>
       <c r="T8">
-        <v>4.719712417646137</v>
+        <v>0.6883888725301739</v>
       </c>
       <c r="U8">
-        <v>4.72195</v>
+        <v>0.6968300000000001</v>
       </c>
       <c r="V8">
-        <v>4.750629999999999</v>
+        <v>0.7039600000000001</v>
       </c>
       <c r="W8">
-        <v>4.730670853721815</v>
+        <v>0.6955316417411134</v>
       </c>
       <c r="X8">
-        <v>4.673735</v>
+        <v>0.7047050000000001</v>
       </c>
       <c r="Y8">
-        <v>0.001846875490383275</v>
+        <v>-0.00186323530687067</v>
       </c>
       <c r="Z8">
-        <v>0.1808742864630369</v>
+        <v>0.1648708900173564</v>
       </c>
       <c r="AA8">
-        <v>0.001846875490383275</v>
+        <v>0.00186323530687067</v>
       </c>
       <c r="AB8">
-        <v>0.4600342327998223</v>
+        <v>0.4497014280087273</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3399657672001777</v>
+        <v>0.3502985719912728</v>
       </c>
       <c r="AE8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1801,58 +1810,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01021082391808467</v>
+        <v>0.0113011781926726</v>
       </c>
       <c r="AJ8">
-        <v>48967.64492377901</v>
+        <v>44243.17460317433</v>
       </c>
       <c r="AK8">
-        <v>48967.64492377901</v>
+        <v>33182.38095238075</v>
       </c>
       <c r="AL8">
-        <v>10370.21673752984</v>
+        <v>47619.04761904733</v>
       </c>
       <c r="AM8">
-        <v>489.6764492377901</v>
+        <v>331.8238095238075</v>
       </c>
       <c r="AN8">
-        <v>0.004896764492377901</v>
+        <v>0.003318238095238075</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP8">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1069903650488819</v>
+        <v>0.02053014561963781</v>
       </c>
       <c r="AR8">
-        <v>0.0490083111201273</v>
+        <v>0.007068557220834136</v>
       </c>
       <c r="AS8">
-        <v>0.07967664338601504</v>
+        <v>0.01332213805329264</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
         <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1860,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1875,79 +1884,79 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" t="s">
         <v>68</v>
       </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" t="s">
-        <v>69</v>
-      </c>
       <c r="J9" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.6464114921989814</v>
       </c>
       <c r="L9">
-        <v>0.7086979502669031</v>
+        <v>2.167074898742928</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>0.9116028730497454</v>
       </c>
       <c r="R9">
-        <v>0.6968300000000001</v>
+        <v>7.6973</v>
       </c>
       <c r="S9">
-        <v>0.694886449949119</v>
+        <v>7.680242310117044</v>
       </c>
       <c r="T9">
-        <v>0.6866870261906244</v>
+        <v>7.703881093056516</v>
       </c>
       <c r="U9">
-        <v>0.6968300000000001</v>
+        <v>7.6973</v>
       </c>
       <c r="V9">
-        <v>0.7039600000000001</v>
+        <v>7.648700000000001</v>
       </c>
       <c r="W9">
-        <v>0.694886449949119</v>
+        <v>7.680242310117044</v>
       </c>
       <c r="X9">
-        <v>0.7047050000000001</v>
+        <v>7.7582</v>
       </c>
       <c r="Y9">
-        <v>-0.002789130850969523</v>
+        <v>-0.002216061460896212</v>
       </c>
       <c r="Z9">
-        <v>0.2468000064610897</v>
+        <v>0.2800934299336051</v>
       </c>
       <c r="AA9">
-        <v>0.002789130850969523</v>
+        <v>0.002216061460896212</v>
       </c>
       <c r="AB9">
-        <v>0.4427465782834746</v>
+        <v>0.395467159280301</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3572534217165254</v>
+        <v>0.4045328407196991</v>
       </c>
       <c r="AE9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1956,58 +1965,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>455.8014365248727</v>
       </c>
       <c r="AI9">
-        <v>0.0113011781926726</v>
+        <v>0.00791186519948547</v>
       </c>
       <c r="AJ9">
-        <v>44243.17460317433</v>
+        <v>63196.22331691348</v>
       </c>
       <c r="AK9">
-        <v>33182.38095238075</v>
+        <v>57609.85874159164</v>
       </c>
       <c r="AL9">
-        <v>47619.04761904733</v>
+        <v>7484.424245071861</v>
       </c>
       <c r="AM9">
-        <v>331.8238095238075</v>
+        <v>576.0985874159164</v>
       </c>
       <c r="AN9">
-        <v>0.003318238095238075</v>
+        <v>0.005760985874159164</v>
       </c>
       <c r="AO9">
-        <v>375</v>
+        <v>455.8014365248727</v>
       </c>
       <c r="AP9">
-        <v>0.00375</v>
+        <v>0.004558014365248727</v>
       </c>
       <c r="AQ9">
-        <v>0.02288013110467144</v>
+        <v>0.2026219426992898</v>
       </c>
       <c r="AR9">
-        <v>0.007844703524473881</v>
+        <v>0.05124940838468305</v>
       </c>
       <c r="AS9">
-        <v>0.01343749175863589</v>
+        <v>0.07744466255743465</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2015,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2027,16 +2036,16 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
         <v>68</v>
-      </c>
-      <c r="H10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>69</v>
       </c>
       <c r="J10" s="2">
         <v>46226</v>
@@ -2054,10 +2063,10 @@
         <v>6</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
@@ -2066,10 +2075,10 @@
         <v>6.77675</v>
       </c>
       <c r="S10">
-        <v>6.734875423863052</v>
+        <v>6.74432770688502</v>
       </c>
       <c r="T10">
-        <v>6.704749770457378</v>
+        <v>6.726205120274524</v>
       </c>
       <c r="U10">
         <v>6.77675</v>
@@ -2078,31 +2087,31 @@
         <v>6.748699999999999</v>
       </c>
       <c r="W10">
-        <v>6.734875423863052</v>
+        <v>6.74432770688502</v>
       </c>
       <c r="X10">
         <v>6.80655</v>
       </c>
       <c r="Y10">
-        <v>-0.00617915315408535</v>
+        <v>-0.004784342511525406</v>
       </c>
       <c r="Z10">
-        <v>1.405187118689524</v>
+        <v>1.087996413254354</v>
       </c>
       <c r="AA10">
-        <v>0.00617915315408535</v>
+        <v>0.004784342511525406</v>
       </c>
       <c r="AB10">
-        <v>0.4421950997571019</v>
+        <v>0.443758456893348</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3578049002428981</v>
+        <v>0.3562415431066519</v>
       </c>
       <c r="AE10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2138,31 +2147,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.0781814767500027</v>
+        <v>0.07417494839447768</v>
       </c>
       <c r="AR10">
-        <v>0.01509575995489133</v>
+        <v>0.01423679563669163</v>
       </c>
       <c r="AS10">
-        <v>0.04124627195558649</v>
+        <v>0.03919898447370633</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2170,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2182,16 +2191,16 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>69</v>
       </c>
       <c r="J11" s="2">
         <v>46226</v>
@@ -2209,10 +2218,10 @@
         <v>101</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
@@ -2221,10 +2230,10 @@
         <v>4045.89</v>
       </c>
       <c r="S11">
-        <v>3948.672403070427</v>
+        <v>4010.949822587927</v>
       </c>
       <c r="T11">
-        <v>3849.867213019518</v>
+        <v>4001.93408917002</v>
       </c>
       <c r="U11">
         <v>4045.89</v>
@@ -2233,31 +2242,31 @@
         <v>4002.52</v>
       </c>
       <c r="W11">
-        <v>3948.672403070427</v>
+        <v>4010.949822587927</v>
       </c>
       <c r="X11">
         <v>4175.755</v>
       </c>
       <c r="Y11">
-        <v>-0.02402872963169356</v>
+        <v>-0.008635968207754646</v>
       </c>
       <c r="Z11">
-        <v>0.7486050662578273</v>
+        <v>0.2690499935477031</v>
       </c>
       <c r="AA11">
-        <v>0.02402872963169356</v>
+        <v>0.008635968207754646</v>
       </c>
       <c r="AB11">
-        <v>0.4095673466974834</v>
+        <v>0.4167484190059697</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3904326533025166</v>
+        <v>0.3832515809940303</v>
       </c>
       <c r="AE11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2293,31 +2302,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>457.5576281083092</v>
+        <v>427.5046275165506</v>
       </c>
       <c r="AR11">
-        <v>161.5656106266083</v>
+        <v>141.8296742070548</v>
       </c>
       <c r="AS11">
-        <v>210.6508695646872</v>
+        <v>209.534736970985</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03053592836191687</v>
+        <v>0.03753360393602585</v>
       </c>
       <c r="AV11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
   <si>
     <t>Pair</t>
   </si>
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
+    <t>AUDUSD</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
+    <t>USDCNH</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -220,21 +220,18 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
+    <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
-  </si>
-  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
@@ -244,34 +241,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06205,naive=0.01199,drift4=0.01825; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.651,naive=1.838,drift4=1.792; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03434,naive=0.01326,drift4=0.01963; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05644,naive=0.01842,drift4=0.03257; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.2344,naive=0.1097,drift4=0.1877; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1239,naive=0.07093,drift4=0.1188; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02693,naive=0.01167,drift4=0.0195; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3212,naive=0.07231,drift4=0.09659; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09535,naive=0.02125,drift4=0.05183; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=610.2,naive=200.2,drift4=276.5; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05516,naive=0.01789,drift4=0.03534; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.1029,naive=0.05916,drift4=0.1309; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.06529,naive=0.009961,drift4=0.01927; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02989,naive=0.01067,drift4=0.01974; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=7.249,naive=1.753,drift4=1.756; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.02457,naive=0.01063,drift4=0.02213; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2107,naive=0.109,drift4=0.1994; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1053,naive=0.02133,drift4=0.04922; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3066,naive=0.06415,drift4=0.09864; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=454.8,naive=152.9,drift4=279.3; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +805,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,28 +823,28 @@
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" t="s">
         <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0.3302513599941327</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="L2">
-        <v>2.019393163375722</v>
-      </c>
-      <c r="M2">
-        <v>6</v>
-      </c>
       <c r="N2">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P2" t="s">
         <v>72</v>
@@ -856,37 +853,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.137675</v>
+        <v>1.32899</v>
       </c>
       <c r="S2">
-        <v>1.14147308816307</v>
+        <v>1.33007637047654</v>
       </c>
       <c r="T2">
-        <v>1.147801345084798</v>
+        <v>1.336268638642645</v>
       </c>
       <c r="U2">
-        <v>1.137675</v>
+        <v>1.32899</v>
       </c>
       <c r="V2">
-        <v>1.13705</v>
+        <v>1.32288</v>
       </c>
       <c r="Y2">
-        <v>0.003338464994897421</v>
+        <v>0.0008174406703886492</v>
       </c>
       <c r="AA2">
-        <v>0.003338464994897421</v>
+        <v>0.0008174406703886492</v>
       </c>
       <c r="AB2">
-        <v>0.3997721335488879</v>
+        <v>0.446226882060304</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4002278664511121</v>
+        <v>0.3537731179396961</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -919,31 +916,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03701207565653994</v>
+        <v>0.02894378866935051</v>
       </c>
       <c r="AR2">
-        <v>0.008068516096769939</v>
+        <v>0.007910404308249398</v>
       </c>
       <c r="AS2">
-        <v>0.0134665992798199</v>
+        <v>0.02015211190068665</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AW2" t="s">
         <v>65</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AY2" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +948,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,7 +960,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
         <v>65</v>
@@ -975,61 +972,61 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.778900950289698</v>
+        <v>0.571803579797887</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
         <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>163.8215</v>
+        <v>4.7282</v>
       </c>
       <c r="S3">
-        <v>163.936866221097</v>
+        <v>4.730020532728285</v>
       </c>
       <c r="T3">
-        <v>161.798829241327</v>
+        <v>4.719335059181186</v>
       </c>
       <c r="U3">
-        <v>163.8215</v>
+        <v>4.7282</v>
       </c>
       <c r="V3">
-        <v>165.913</v>
+        <v>4.74823</v>
       </c>
       <c r="Y3">
-        <v>0.0007042190499844018</v>
+        <v>0.0003850371660007981</v>
       </c>
       <c r="AA3">
-        <v>0.0007042190499844018</v>
+        <v>0.0003850371660007981</v>
       </c>
       <c r="AB3">
-        <v>0.3786507343232977</v>
+        <v>0.4915555065773776</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4213492656767022</v>
+        <v>0.3084444934226225</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1062,31 +1059,31 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>4.007246171393907</v>
+        <v>0.06581591397506598</v>
       </c>
       <c r="AR3">
-        <v>1.258008626180795</v>
+        <v>0.02076782850486351</v>
       </c>
       <c r="AS3">
-        <v>1.455954520829094</v>
+        <v>0.06462657404606476</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AW3" t="s">
         <v>65</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AY3" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1091,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1106,82 +1103,73 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.077023474180427</v>
+        <v>2.184951219045213</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>0.816755</v>
+        <v>1.137055</v>
       </c>
       <c r="S4">
-        <v>0.8237601199010242</v>
+        <v>1.135990868807647</v>
       </c>
       <c r="T4">
-        <v>0.8268747801644387</v>
+        <v>1.140586839891603</v>
       </c>
       <c r="U4">
-        <v>0.816755</v>
+        <v>1.137055</v>
       </c>
       <c r="V4">
-        <v>0.82391</v>
-      </c>
-      <c r="W4">
-        <v>0.8237601199010242</v>
-      </c>
-      <c r="X4">
-        <v>0.80838</v>
+        <v>1.13061</v>
       </c>
       <c r="Y4">
-        <v>0.008576770146523924</v>
-      </c>
-      <c r="Z4">
-        <v>0.8364322269879531</v>
+        <v>-0.0009358660683547913</v>
       </c>
       <c r="AA4">
-        <v>0.008576770146523924</v>
+        <v>0.0009358660683547913</v>
       </c>
       <c r="AB4">
-        <v>0.4321129493480312</v>
+        <v>0.4101367619511154</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3678870506519688</v>
+        <v>0.3898632380488847</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1190,58 +1178,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
-      </c>
-      <c r="AI4">
-        <v>0.01025399293545806</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>48761.49253731315</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>48761.49253731315</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>59701.49253731308</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>487.6149253731315</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.004876149253731315</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0.02710175958981609</v>
+        <v>0.03142481209583413</v>
       </c>
       <c r="AR4">
-        <v>0.009069273085628427</v>
+        <v>0.004722854615872598</v>
       </c>
       <c r="AS4">
-        <v>0.01327908264551326</v>
+        <v>0.01023653121682599</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX4" t="s">
         <v>87</v>
       </c>
-      <c r="AW4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>89</v>
-      </c>
       <c r="AY4" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1234,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,7 +1246,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
         <v>66</v>
@@ -1270,73 +1255,73 @@
         <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J5" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0.006122699155397303</v>
+        <v>2.475696314671024</v>
       </c>
       <c r="M5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>1.331435</v>
+        <v>0.81914</v>
       </c>
       <c r="S5">
-        <v>1.34050626882868</v>
+        <v>0.8256868673158919</v>
       </c>
       <c r="T5">
-        <v>1.342777473049589</v>
+        <v>0.8212566808462807</v>
       </c>
       <c r="U5">
-        <v>1.331435</v>
+        <v>0.81914</v>
       </c>
       <c r="V5">
-        <v>1.34277</v>
+        <v>0.8349799999999999</v>
       </c>
       <c r="W5">
-        <v>1.34050626882868</v>
+        <v>0.8256868673158919</v>
       </c>
       <c r="X5">
-        <v>1.31909</v>
+        <v>0.810765</v>
       </c>
       <c r="Y5">
-        <v>0.006813151846451578</v>
+        <v>0.007992366769895178</v>
       </c>
       <c r="Z5">
-        <v>0.7348131898485362</v>
+        <v>0.7817155004050026</v>
       </c>
       <c r="AA5">
-        <v>0.006813151846451578</v>
+        <v>0.007992366769895178</v>
       </c>
       <c r="AB5">
-        <v>0.4374156281611774</v>
+        <v>0.4463302656958154</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3625843718388226</v>
+        <v>0.3536697343041846</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1345,58 +1330,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.009271950940151119</v>
+        <v>0.0102241375100716</v>
       </c>
       <c r="AJ5">
-        <v>53926.08343458844</v>
+        <v>48903.88059701463</v>
       </c>
       <c r="AK5">
-        <v>40444.56257594133</v>
+        <v>48903.88059701463</v>
       </c>
       <c r="AL5">
-        <v>30376.67071688917</v>
+        <v>59701.49253731308</v>
       </c>
       <c r="AM5">
-        <v>404.4456257594133</v>
+        <v>489.0388059701464</v>
       </c>
       <c r="AN5">
-        <v>0.004044456257594133</v>
+        <v>0.004890388059701464</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.03855670908636545</v>
+        <v>0.01813720641789505</v>
       </c>
       <c r="AR5">
-        <v>0.01046911245293445</v>
+        <v>0.005873662465091974</v>
       </c>
       <c r="AS5">
-        <v>0.02400559289635933</v>
+        <v>0.009591186222923896</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW5" t="s">
         <v>66</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY5" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1389,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,7 +1401,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>66</v>
@@ -1428,70 +1413,70 @@
         <v>68</v>
       </c>
       <c r="J6" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0.3302812254125366</v>
+        <v>3.569077241700109</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>9.01909</v>
+        <v>163.777</v>
       </c>
       <c r="S6">
-        <v>9.047600489652496</v>
+        <v>164.5744310447378</v>
       </c>
       <c r="T6">
-        <v>9.05440351587689</v>
+        <v>163.1753964993488</v>
       </c>
       <c r="U6">
-        <v>9.01909</v>
+        <v>163.777</v>
       </c>
       <c r="V6">
-        <v>9.055160000000001</v>
+        <v>166.184</v>
       </c>
       <c r="W6">
-        <v>9.047600489652496</v>
+        <v>164.5744310447378</v>
       </c>
       <c r="X6">
-        <v>8.927745</v>
+        <v>162.175</v>
       </c>
       <c r="Y6">
-        <v>0.003161127081833672</v>
+        <v>0.004869005078477305</v>
       </c>
       <c r="Z6">
-        <v>0.3121187766434425</v>
+        <v>0.4977721877264561</v>
       </c>
       <c r="AA6">
-        <v>0.003161127081833672</v>
+        <v>0.004869005078477305</v>
       </c>
       <c r="AB6">
-        <v>0.4567317898030007</v>
+        <v>0.374980935513116</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3432682101969994</v>
+        <v>0.425019064486884</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1503,55 +1488,55 @@
         <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.0101279619119002</v>
+        <v>0.009781593264011368</v>
       </c>
       <c r="AJ6">
-        <v>49368.27412556789</v>
+        <v>51116.41697877686</v>
       </c>
       <c r="AK6">
-        <v>49368.27412556789</v>
+        <v>51116.41697877686</v>
       </c>
       <c r="AL6">
-        <v>5473.753352673927</v>
+        <v>312.1098626716624</v>
       </c>
       <c r="AM6">
-        <v>493.6827412556789</v>
+        <v>511.1641697877686</v>
       </c>
       <c r="AN6">
-        <v>0.004936827412556789</v>
+        <v>0.005111641697877686</v>
       </c>
       <c r="AO6">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.2068138444937041</v>
+        <v>4.460949069773671</v>
       </c>
       <c r="AR6">
-        <v>0.06318251588168093</v>
+        <v>0.8868603636992575</v>
       </c>
       <c r="AS6">
-        <v>0.1530582066562891</v>
+        <v>1.096912678803801</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW6" t="s">
         <v>66</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY6" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1544,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1580,73 +1565,73 @@
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5841023495793738</v>
+        <v>0.5147098189776956</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>4.7259</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="S7">
-        <v>4.731982382835215</v>
+        <v>0.6999043977076645</v>
       </c>
       <c r="T7">
-        <v>4.715816001790408</v>
+        <v>0.6985100089625437</v>
       </c>
       <c r="U7">
-        <v>4.7259</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="V7">
-        <v>4.75853</v>
+        <v>0.7027800000000002</v>
       </c>
       <c r="W7">
-        <v>4.73298885</v>
+        <v>0.6999043977076645</v>
       </c>
       <c r="X7">
-        <v>4.677685</v>
+        <v>0.69069</v>
       </c>
       <c r="Y7">
-        <v>0.00128703164163762</v>
+        <v>0.002168412645748769</v>
       </c>
       <c r="Z7">
-        <v>0.1470258218396768</v>
+        <v>0.1966750269694117</v>
       </c>
       <c r="AA7">
-        <v>0.00128703164163762</v>
+        <v>0.002168412645748769</v>
       </c>
       <c r="AB7">
-        <v>0.4687366672288881</v>
+        <v>0.4678235328394243</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3312633327711119</v>
+        <v>0.3321764671605756</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1658,55 +1643,55 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01020228951099259</v>
+        <v>0.01102535832414563</v>
       </c>
       <c r="AJ7">
-        <v>49008.60727989225</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AK7">
-        <v>49008.60727989225</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AL7">
-        <v>10370.21673752984</v>
+        <v>64935.06493506436</v>
       </c>
       <c r="AM7">
-        <v>490.0860727989225</v>
+        <v>453.499999999996</v>
       </c>
       <c r="AN7">
-        <v>0.004900860727989225</v>
+        <v>0.00453499999999996</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ7">
-        <v>0.09593575045248391</v>
+        <v>0.01574553543626426</v>
       </c>
       <c r="AR7">
-        <v>0.04301638947497143</v>
+        <v>0.003857914142786858</v>
       </c>
       <c r="AS7">
-        <v>0.08046618905239736</v>
+        <v>0.01176138579718845</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW7" t="s">
         <v>66</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY7" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1699,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,7 +1711,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -1735,73 +1720,73 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.7086979502669031</v>
+        <v>0.4771409674339303</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q8">
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>0.6968300000000001</v>
+        <v>8.98892</v>
       </c>
       <c r="S8">
-        <v>0.6955316417411134</v>
+        <v>8.958343372547338</v>
       </c>
       <c r="T8">
-        <v>0.6883888725301739</v>
+        <v>8.972081485565283</v>
       </c>
       <c r="U8">
-        <v>0.6968300000000001</v>
+        <v>8.98892</v>
       </c>
       <c r="V8">
-        <v>0.7039600000000001</v>
+        <v>8.920390000000001</v>
       </c>
       <c r="W8">
-        <v>0.6955316417411134</v>
+        <v>8.958343372547338</v>
       </c>
       <c r="X8">
-        <v>0.7047050000000001</v>
+        <v>9.080265000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.00186323530687067</v>
+        <v>-0.003401590786508525</v>
       </c>
       <c r="Z8">
-        <v>0.1648708900173564</v>
+        <v>0.3347378340649428</v>
       </c>
       <c r="AA8">
-        <v>0.00186323530687067</v>
+        <v>0.003401590786508525</v>
       </c>
       <c r="AB8">
-        <v>0.4497014280087273</v>
+        <v>0.469078655453103</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3502985719912728</v>
+        <v>0.3309213445468971</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1813,22 +1798,22 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.0113011781926726</v>
+        <v>0.01016195494008179</v>
       </c>
       <c r="AJ8">
-        <v>44243.17460317433</v>
+        <v>49203.13098691772</v>
       </c>
       <c r="AK8">
-        <v>33182.38095238075</v>
+        <v>36902.34824018829</v>
       </c>
       <c r="AL8">
-        <v>47619.04761904733</v>
+        <v>4105.315014505446</v>
       </c>
       <c r="AM8">
-        <v>331.8238095238075</v>
+        <v>369.0234824018829</v>
       </c>
       <c r="AN8">
-        <v>0.003318238095238075</v>
+        <v>0.003690234824018829</v>
       </c>
       <c r="AO8">
         <v>375</v>
@@ -1837,31 +1822,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.02053014561963781</v>
+        <v>0.1189312624929517</v>
       </c>
       <c r="AR8">
-        <v>0.007068557220834136</v>
+        <v>0.05270686126380056</v>
       </c>
       <c r="AS8">
-        <v>0.01332213805329264</v>
+        <v>0.1224847325722459</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW8" t="s">
         <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY8" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1854,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1881,7 +1866,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
@@ -1890,73 +1875,73 @@
         <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="K9">
-        <v>0.6464114921989814</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.167074898742928</v>
+        <v>1.517345620394397</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>113</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q9">
-        <v>0.9116028730497454</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>7.6973</v>
+        <v>6.765079999999999</v>
       </c>
       <c r="S9">
-        <v>7.680242310117044</v>
+        <v>6.713330141793496</v>
       </c>
       <c r="T9">
-        <v>7.703881093056516</v>
+        <v>6.662110613676987</v>
       </c>
       <c r="U9">
-        <v>7.6973</v>
+        <v>6.765079999999999</v>
       </c>
       <c r="V9">
-        <v>7.648700000000001</v>
+        <v>6.746059999999999</v>
       </c>
       <c r="W9">
-        <v>7.680242310117044</v>
+        <v>6.713330141793496</v>
       </c>
       <c r="X9">
-        <v>7.7582</v>
+        <v>6.799579905471002</v>
       </c>
       <c r="Y9">
-        <v>-0.002216061460896212</v>
+        <v>-0.007649555985517281</v>
       </c>
       <c r="Z9">
-        <v>0.2800934299336051</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>0.002216061460896212</v>
+        <v>0.007649555985517281</v>
       </c>
       <c r="AB9">
-        <v>0.395467159280301</v>
+        <v>0.4351891038956787</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4045328407196991</v>
+        <v>0.3648108961043214</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1965,58 +1950,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>455.8014365248727</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.00791186519948547</v>
+        <v>0.005099703990344854</v>
       </c>
       <c r="AJ9">
-        <v>63196.22331691348</v>
+        <v>98044.90632135472</v>
       </c>
       <c r="AK9">
-        <v>57609.85874159164</v>
+        <v>73533.67974101604</v>
       </c>
       <c r="AL9">
-        <v>7484.424245071861</v>
+        <v>10869.59499976586</v>
       </c>
       <c r="AM9">
-        <v>576.0985874159164</v>
+        <v>735.3367974101603</v>
       </c>
       <c r="AN9">
-        <v>0.005760985874159164</v>
+        <v>0.007353367974101604</v>
       </c>
       <c r="AO9">
-        <v>455.8014365248727</v>
+        <v>375</v>
       </c>
       <c r="AP9">
-        <v>0.004558014365248727</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.2026219426992898</v>
+        <v>0.07759003437314589</v>
       </c>
       <c r="AR9">
-        <v>0.05124940838468305</v>
+        <v>0.01085239139770276</v>
       </c>
       <c r="AS9">
-        <v>0.07744466255743465</v>
+        <v>0.02507470802710865</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW9" t="s">
         <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY9" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2009,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,7 +2021,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
         <v>67</v>
@@ -2045,73 +2030,73 @@
         <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.6317203254759612</v>
       </c>
       <c r="L10">
-        <v>1.201166085349996</v>
+        <v>2.158244697090097</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.9079300813689903</v>
       </c>
       <c r="R10">
-        <v>6.77675</v>
+        <v>7.69</v>
       </c>
       <c r="S10">
-        <v>6.74432770688502</v>
+        <v>7.622919799747425</v>
       </c>
       <c r="T10">
-        <v>6.726205120274524</v>
+        <v>7.590213959429482</v>
       </c>
       <c r="U10">
-        <v>6.77675</v>
+        <v>7.69</v>
       </c>
       <c r="V10">
-        <v>6.748699999999999</v>
+        <v>7.622400000000001</v>
       </c>
       <c r="W10">
-        <v>6.74432770688502</v>
+        <v>7.622919799747425</v>
       </c>
       <c r="X10">
-        <v>6.80655</v>
+        <v>7.7509</v>
       </c>
       <c r="Y10">
-        <v>-0.004784342511525406</v>
+        <v>-0.008723042945718493</v>
       </c>
       <c r="Z10">
-        <v>1.087996413254354</v>
+        <v>1.10148112073195</v>
       </c>
       <c r="AA10">
-        <v>0.004784342511525406</v>
+        <v>0.008723042945718493</v>
       </c>
       <c r="AB10">
-        <v>0.443758456893348</v>
+        <v>0.4039080303802292</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3562415431066519</v>
+        <v>0.3960919696197709</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2120,58 +2105,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>453.9650406844952</v>
       </c>
       <c r="AI10">
-        <v>0.004397388128527694</v>
+        <v>0.007919375812743759</v>
       </c>
       <c r="AJ10">
-        <v>113703.8590604025</v>
+        <v>63136.28899835848</v>
       </c>
       <c r="AK10">
-        <v>85277.89429530187</v>
+        <v>57323.3360076157</v>
       </c>
       <c r="AL10">
-        <v>12583.89261744964</v>
+        <v>7454.269961978634</v>
       </c>
       <c r="AM10">
-        <v>852.7789429530187</v>
+        <v>573.2333600761569</v>
       </c>
       <c r="AN10">
-        <v>0.008527789429530187</v>
+        <v>0.005732333600761569</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>453.9650406844951</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.004539650406844951</v>
       </c>
       <c r="AQ10">
-        <v>0.07417494839447768</v>
+        <v>0.1406778286801442</v>
       </c>
       <c r="AR10">
-        <v>0.01423679563669163</v>
+        <v>0.03443688981687151</v>
       </c>
       <c r="AS10">
-        <v>0.03919898447370633</v>
+        <v>0.05638783433245466</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW10" t="s">
         <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY10" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2164,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2200,73 +2185,73 @@
         <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.679542508140375</v>
+        <v>1.67225064054127</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4045.89</v>
+        <v>4065.63</v>
       </c>
       <c r="S11">
-        <v>4010.949822587927</v>
+        <v>4015.627815695351</v>
       </c>
       <c r="T11">
-        <v>4001.93408917002</v>
+        <v>4041.690618351678</v>
       </c>
       <c r="U11">
-        <v>4045.89</v>
+        <v>4065.63</v>
       </c>
       <c r="V11">
-        <v>4002.52</v>
+        <v>3955.56</v>
       </c>
       <c r="W11">
-        <v>4010.949822587927</v>
+        <v>4015.627815695351</v>
       </c>
       <c r="X11">
-        <v>4175.755</v>
+        <v>4195.495</v>
       </c>
       <c r="Y11">
-        <v>-0.008635968207754646</v>
+        <v>-0.01229875426555019</v>
       </c>
       <c r="Z11">
-        <v>0.2690499935477031</v>
+        <v>0.3850320279108988</v>
       </c>
       <c r="AA11">
-        <v>0.008635968207754646</v>
+        <v>0.01229875426555019</v>
       </c>
       <c r="AB11">
-        <v>0.4167484190059697</v>
+        <v>0.44181519213033</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3832515809940303</v>
+        <v>0.3581848078696699</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2278,22 +2263,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03209800563040515</v>
+        <v>0.03194215902578441</v>
       </c>
       <c r="AJ11">
-        <v>15577.29180302623</v>
+        <v>15653.29380510532</v>
       </c>
       <c r="AK11">
-        <v>11682.96885226967</v>
+        <v>11739.97035382899</v>
       </c>
       <c r="AL11">
         <v>2.887614060755402</v>
       </c>
       <c r="AM11">
-        <v>116.8296885226967</v>
+        <v>117.3997035382899</v>
       </c>
       <c r="AN11">
-        <v>0.001168296885226967</v>
+        <v>0.001173997035382899</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2302,31 +2287,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>427.5046275165506</v>
+        <v>333.1887310792765</v>
       </c>
       <c r="AR11">
-        <v>141.8296742070548</v>
+        <v>72.20478098504081</v>
       </c>
       <c r="AS11">
-        <v>209.534736970985</v>
+        <v>173.8010623834666</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03753360393602585</v>
+        <v>0.03248696319184401</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW11" t="s">
         <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY11" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -220,19 +220,19 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
-    <t>NO_SIGNAL</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -241,34 +241,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05516,naive=0.01789,drift4=0.03534; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.1029,naive=0.05916,drift4=0.1309; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.06529,naive=0.009961,drift4=0.01927; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02989,naive=0.01067,drift4=0.01974; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=7.249,naive=1.753,drift4=1.756; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.02457,naive=0.01063,drift4=0.02213; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2107,naive=0.109,drift4=0.1994; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1053,naive=0.02133,drift4=0.04922; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3066,naive=0.06415,drift4=0.09864; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=454.8,naive=152.9,drift4=279.3; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.0626,naive=0.01174,drift4=0.01838; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0344,naive=0.01308,drift4=0.01957; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.578,naive=1.76,drift4=1.751; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05735,naive=0.01821,drift4=0.03238; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.0277,naive=0.01216,drift4=0.02024; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1239,naive=0.07093,drift4=0.1188; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.2344,naive=0.1097,drift4=0.1877; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3212,naive=0.07231,drift4=0.09659; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09628,naive=0.02199,drift4=0.05204; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=610.2,naive=200.2,drift4=276.5; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -823,7 +823,7 @@
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
         <v>68</v>
@@ -832,19 +832,19 @@
         <v>46230</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0.3302513599941327</v>
+        <v>2.184951219045213</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
         <v>72</v>
@@ -853,34 +853,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.32899</v>
+        <v>1.137055</v>
       </c>
       <c r="S2">
-        <v>1.33007637047654</v>
+        <v>1.139434610215785</v>
       </c>
       <c r="T2">
-        <v>1.336268638642645</v>
+        <v>1.14940716860582</v>
       </c>
       <c r="U2">
-        <v>1.32899</v>
+        <v>1.137055</v>
       </c>
       <c r="V2">
-        <v>1.32288</v>
+        <v>1.13061</v>
       </c>
       <c r="Y2">
-        <v>0.0008174406703886492</v>
+        <v>0.00209278374026296</v>
       </c>
       <c r="AA2">
-        <v>0.0008174406703886492</v>
+        <v>0.00209278374026296</v>
       </c>
       <c r="AB2">
-        <v>0.446226882060304</v>
+        <v>0.4008907072021103</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3537731179396961</v>
+        <v>0.3991092927978898</v>
       </c>
       <c r="AE2" t="s">
         <v>75</v>
@@ -916,19 +916,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.02894378866935051</v>
+        <v>0.03477187396859784</v>
       </c>
       <c r="AR2">
-        <v>0.007910404308249398</v>
+        <v>0.006942598925878485</v>
       </c>
       <c r="AS2">
-        <v>0.02015211190068665</v>
+        <v>0.01229401656257361</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV2" t="s">
         <v>85</v>
@@ -963,10 +963,10 @@
         <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
@@ -975,55 +975,64 @@
         <v>46230</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.571803579797887</v>
+        <v>2.475696314671024</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>4.7282</v>
+        <v>0.81914</v>
       </c>
       <c r="S3">
-        <v>4.730020532728285</v>
+        <v>0.8303893931979528</v>
       </c>
       <c r="T3">
-        <v>4.719335059181186</v>
+        <v>0.8316876878036235</v>
       </c>
       <c r="U3">
-        <v>4.7282</v>
+        <v>0.81914</v>
       </c>
       <c r="V3">
-        <v>4.74823</v>
+        <v>0.8349799999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.8303893931979528</v>
+      </c>
+      <c r="X3">
+        <v>0.810765</v>
       </c>
       <c r="Y3">
-        <v>0.0003850371660007981</v>
+        <v>0.0137331752788935</v>
+      </c>
+      <c r="Z3">
+        <v>1.343211128113761</v>
       </c>
       <c r="AA3">
-        <v>0.0003850371660007981</v>
+        <v>0.0137331752788935</v>
       </c>
       <c r="AB3">
-        <v>0.4915555065773776</v>
+        <v>0.4320996057460227</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3084444934226225</v>
+        <v>0.3679003942539772</v>
       </c>
       <c r="AE3" t="s">
         <v>76</v>
@@ -1035,52 +1044,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI3">
+        <v>0.0102241375100716</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>48903.88059701463</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>48903.88059701463</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>59701.49253731308</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>489.0388059701464</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.004890388059701464</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.06581591397506598</v>
+        <v>0.02372418581813656</v>
       </c>
       <c r="AR3">
-        <v>0.02076782850486351</v>
+        <v>0.008542612881181456</v>
       </c>
       <c r="AS3">
-        <v>0.06462657404606476</v>
+        <v>0.01164349356653238</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
         <v>46259</v>
@@ -1106,10 +1118,10 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
@@ -1121,52 +1133,61 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.184951219045213</v>
+        <v>3.569077241700109</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>1.137055</v>
+        <v>163.777</v>
       </c>
       <c r="S4">
-        <v>1.135990868807647</v>
+        <v>164.9328392614813</v>
       </c>
       <c r="T4">
-        <v>1.140586839891603</v>
+        <v>164.152228284504</v>
       </c>
       <c r="U4">
-        <v>1.137055</v>
+        <v>163.777</v>
       </c>
       <c r="V4">
-        <v>1.13061</v>
+        <v>166.184</v>
+      </c>
+      <c r="W4">
+        <v>164.9328392614813</v>
+      </c>
+      <c r="X4">
+        <v>162.175</v>
       </c>
       <c r="Y4">
-        <v>-0.0009358660683547913</v>
+        <v>0.007057396713099373</v>
+      </c>
+      <c r="Z4">
+        <v>0.7214976663428736</v>
       </c>
       <c r="AA4">
-        <v>0.0009358660683547913</v>
+        <v>0.007057396713099373</v>
       </c>
       <c r="AB4">
-        <v>0.4101367619511154</v>
+        <v>0.3788618242137581</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3898632380488847</v>
+        <v>0.4211381757862419</v>
       </c>
       <c r="AE4" t="s">
         <v>77</v>
@@ -1178,52 +1199,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI4">
+        <v>0.009781593264011368</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>51116.41697877686</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>51116.41697877686</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>312.1098626716624</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>511.1641697877686</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.005111641697877686</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.03142481209583413</v>
+        <v>4.646015501811858</v>
       </c>
       <c r="AR4">
-        <v>0.004722854615872598</v>
+        <v>1.167271601239547</v>
       </c>
       <c r="AS4">
-        <v>0.01023653121682599</v>
+        <v>1.321028066049352</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY4" s="2">
         <v>46259</v>
@@ -1246,7 +1270,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>66</v>
@@ -1255,70 +1279,70 @@
         <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
         <v>46230</v>
       </c>
       <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0.3302513599941327</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
-      <c r="L5">
-        <v>2.475696314671024</v>
-      </c>
-      <c r="M5">
-        <v>6</v>
-      </c>
       <c r="N5">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
         <v>73</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>0.81914</v>
+        <v>1.32899</v>
       </c>
       <c r="S5">
-        <v>0.8256868673158919</v>
+        <v>1.33502722857898</v>
       </c>
       <c r="T5">
-        <v>0.8212566808462807</v>
+        <v>1.347917714716592</v>
       </c>
       <c r="U5">
-        <v>0.81914</v>
+        <v>1.32899</v>
       </c>
       <c r="V5">
-        <v>0.8349799999999999</v>
+        <v>1.32288</v>
       </c>
       <c r="W5">
-        <v>0.8256868673158919</v>
+        <v>1.33502722857898</v>
       </c>
       <c r="X5">
-        <v>0.810765</v>
+        <v>1.317065</v>
       </c>
       <c r="Y5">
-        <v>0.007992366769895178</v>
+        <v>0.004542719342493533</v>
       </c>
       <c r="Z5">
-        <v>0.7817155004050026</v>
+        <v>0.5062665475036034</v>
       </c>
       <c r="AA5">
-        <v>0.007992366769895178</v>
+        <v>0.004542719342493533</v>
       </c>
       <c r="AB5">
-        <v>0.4463302656958154</v>
+        <v>0.4363508691845883</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3536697343041846</v>
+        <v>0.3636491308154117</v>
       </c>
       <c r="AE5" t="s">
         <v>78</v>
@@ -1330,46 +1354,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.0102241375100716</v>
+        <v>0.008972979480658259</v>
       </c>
       <c r="AJ5">
-        <v>48903.88059701463</v>
+        <v>55722.85115303974</v>
       </c>
       <c r="AK5">
-        <v>48903.88059701463</v>
+        <v>41792.13836477981</v>
       </c>
       <c r="AL5">
-        <v>59701.49253731308</v>
+        <v>31446.5408805031</v>
       </c>
       <c r="AM5">
-        <v>489.0388059701464</v>
+        <v>417.9213836477981</v>
       </c>
       <c r="AN5">
-        <v>0.004890388059701464</v>
+        <v>0.004179213836477981</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.01813720641789505</v>
+        <v>0.03466893976698469</v>
       </c>
       <c r="AR5">
-        <v>0.005873662465091974</v>
+        <v>0.009201015222123844</v>
       </c>
       <c r="AS5">
-        <v>0.009591186222923896</v>
+        <v>0.02286274114115988</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV5" t="s">
         <v>86</v>
@@ -1416,64 +1440,64 @@
         <v>46230</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>3.569077241700109</v>
+        <v>0.5147098189776956</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>163.777</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="S6">
-        <v>164.5744310447378</v>
+        <v>0.6999681198381074</v>
       </c>
       <c r="T6">
-        <v>163.1753964993488</v>
+        <v>0.698484453906832</v>
       </c>
       <c r="U6">
-        <v>163.777</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="V6">
-        <v>166.184</v>
+        <v>0.7027800000000002</v>
       </c>
       <c r="W6">
-        <v>164.5744310447378</v>
+        <v>0.6999681198381074</v>
       </c>
       <c r="X6">
-        <v>162.175</v>
+        <v>0.69069</v>
       </c>
       <c r="Y6">
-        <v>0.004869005078477305</v>
+        <v>0.002259654116048762</v>
       </c>
       <c r="Z6">
-        <v>0.4977721877264561</v>
+        <v>0.2049506283256209</v>
       </c>
       <c r="AA6">
-        <v>0.004869005078477305</v>
+        <v>0.002259654116048762</v>
       </c>
       <c r="AB6">
-        <v>0.374980935513116</v>
+        <v>0.4502058923237894</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.425019064486884</v>
+        <v>0.3497941076762106</v>
       </c>
       <c r="AE6" t="s">
         <v>79</v>
@@ -1488,43 +1512,43 @@
         <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.009781593264011368</v>
+        <v>0.01102535832414563</v>
       </c>
       <c r="AJ6">
-        <v>51116.41697877686</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AK6">
-        <v>51116.41697877686</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AL6">
-        <v>312.1098626716624</v>
+        <v>64935.06493506436</v>
       </c>
       <c r="AM6">
-        <v>511.1641697877686</v>
+        <v>453.499999999996</v>
       </c>
       <c r="AN6">
-        <v>0.005111641697877686</v>
+        <v>0.00453499999999996</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ6">
-        <v>4.460949069773671</v>
+        <v>0.02005757543837777</v>
       </c>
       <c r="AR6">
-        <v>0.8868603636992575</v>
+        <v>0.005878894069939932</v>
       </c>
       <c r="AS6">
-        <v>1.096912678803801</v>
+        <v>0.01340922205233603</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV6" t="s">
         <v>86</v>
@@ -1556,7 +1580,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>66</v>
@@ -1565,7 +1589,7 @@
         <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J7" s="2">
         <v>46230</v>
@@ -1574,16 +1598,16 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5147098189776956</v>
+        <v>0.571803579797887</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" t="s">
         <v>74</v>
@@ -1592,43 +1616,43 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>0.6983900000000001</v>
+        <v>4.7282</v>
       </c>
       <c r="S7">
-        <v>0.6999043977076645</v>
+        <v>4.73390884487149</v>
       </c>
       <c r="T7">
-        <v>0.6985100089625437</v>
+        <v>4.726223709795539</v>
       </c>
       <c r="U7">
-        <v>0.6983900000000001</v>
+        <v>4.7282</v>
       </c>
       <c r="V7">
-        <v>0.7027800000000002</v>
+        <v>4.74823</v>
       </c>
       <c r="W7">
-        <v>0.6999043977076645</v>
+        <v>4.7352923</v>
       </c>
       <c r="X7">
-        <v>0.69069</v>
+        <v>4.6933525</v>
       </c>
       <c r="Y7">
-        <v>0.002168412645748769</v>
+        <v>0.001207403424451056</v>
       </c>
       <c r="Z7">
-        <v>0.1966750269694117</v>
+        <v>0.2035239256761609</v>
       </c>
       <c r="AA7">
-        <v>0.002168412645748769</v>
+        <v>0.001207403424451056</v>
       </c>
       <c r="AB7">
-        <v>0.4678235328394243</v>
+        <v>0.4687366672288881</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3321764671605756</v>
+        <v>0.3312633327711119</v>
       </c>
       <c r="AE7" t="s">
         <v>80</v>
@@ -1643,43 +1667,43 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01102535832414563</v>
+        <v>0.007370140856985728</v>
       </c>
       <c r="AJ7">
-        <v>45349.9999999996</v>
+        <v>67841.30855872029</v>
       </c>
       <c r="AK7">
-        <v>45349.9999999996</v>
+        <v>67841.30855872029</v>
       </c>
       <c r="AL7">
-        <v>64935.06493506436</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM7">
-        <v>453.499999999996</v>
+        <v>678.413085587203</v>
       </c>
       <c r="AN7">
-        <v>0.00453499999999996</v>
+        <v>0.00678413085587203</v>
       </c>
       <c r="AO7">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.01574553543626426</v>
+        <v>0.08793385602186127</v>
       </c>
       <c r="AR7">
-        <v>0.003857914142786858</v>
+        <v>0.03498250304000233</v>
       </c>
       <c r="AS7">
-        <v>0.01176138579718845</v>
+        <v>0.07422223568030864</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV7" t="s">
         <v>86</v>
@@ -1711,7 +1735,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -1720,7 +1744,7 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J8" s="2">
         <v>46230</v>
@@ -1738,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
         <v>73</v>
@@ -1750,10 +1774,10 @@
         <v>8.98892</v>
       </c>
       <c r="S8">
-        <v>8.958343372547338</v>
+        <v>8.955020099515837</v>
       </c>
       <c r="T8">
-        <v>8.972081485565283</v>
+        <v>8.966202662886595</v>
       </c>
       <c r="U8">
         <v>8.98892</v>
@@ -1762,28 +1786,28 @@
         <v>8.920390000000001</v>
       </c>
       <c r="W8">
-        <v>8.958343372547338</v>
+        <v>8.955020099515837</v>
       </c>
       <c r="X8">
         <v>9.080265000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.003401590786508525</v>
+        <v>-0.003771298496834278</v>
       </c>
       <c r="Z8">
-        <v>0.3347378340649428</v>
+        <v>0.3711193878610058</v>
       </c>
       <c r="AA8">
-        <v>0.003401590786508525</v>
+        <v>0.003771298496834278</v>
       </c>
       <c r="AB8">
-        <v>0.469078655453103</v>
+        <v>0.4567317898030007</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3309213445468971</v>
+        <v>0.3432682101969994</v>
       </c>
       <c r="AE8" t="s">
         <v>81</v>
@@ -1822,19 +1846,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1189312624929517</v>
+        <v>0.1898762217228014</v>
       </c>
       <c r="AR8">
-        <v>0.05270686126380056</v>
+        <v>0.0601156273185434</v>
       </c>
       <c r="AS8">
-        <v>0.1224847325722459</v>
+        <v>0.1438490349360235</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV8" t="s">
         <v>86</v>
@@ -1875,70 +1899,70 @@
         <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J9" s="2">
         <v>46230</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.6317203254759612</v>
       </c>
       <c r="L9">
-        <v>1.517345620394397</v>
+        <v>2.158244697090097</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
         <v>73</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>0.9079300813689903</v>
       </c>
       <c r="R9">
-        <v>6.765079999999999</v>
+        <v>7.69</v>
       </c>
       <c r="S9">
-        <v>6.713330141793496</v>
+        <v>7.64852009530019</v>
       </c>
       <c r="T9">
-        <v>6.662110613676987</v>
+        <v>7.654261293673839</v>
       </c>
       <c r="U9">
-        <v>6.765079999999999</v>
+        <v>7.69</v>
       </c>
       <c r="V9">
-        <v>6.746059999999999</v>
+        <v>7.622400000000001</v>
       </c>
       <c r="W9">
-        <v>6.713330141793496</v>
+        <v>7.64852009530019</v>
       </c>
       <c r="X9">
-        <v>6.799579905471002</v>
+        <v>7.7509</v>
       </c>
       <c r="Y9">
-        <v>-0.007649555985517281</v>
+        <v>-0.005394005812719115</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>0.681115019701319</v>
       </c>
       <c r="AA9">
-        <v>0.007649555985517281</v>
+        <v>0.005394005812719115</v>
       </c>
       <c r="AB9">
-        <v>0.4351891038956787</v>
+        <v>0.395467159280301</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3648108961043214</v>
+        <v>0.4045328407196991</v>
       </c>
       <c r="AE9" t="s">
         <v>82</v>
@@ -1950,46 +1974,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>453.9650406844952</v>
       </c>
       <c r="AI9">
-        <v>0.005099703990344854</v>
+        <v>0.007919375812743759</v>
       </c>
       <c r="AJ9">
-        <v>98044.90632135472</v>
+        <v>63136.28899835848</v>
       </c>
       <c r="AK9">
-        <v>73533.67974101604</v>
+        <v>57323.3360076157</v>
       </c>
       <c r="AL9">
-        <v>10869.59499976586</v>
+        <v>7454.269961978634</v>
       </c>
       <c r="AM9">
-        <v>735.3367974101603</v>
+        <v>573.2333600761569</v>
       </c>
       <c r="AN9">
-        <v>0.007353367974101604</v>
+        <v>0.005732333600761569</v>
       </c>
       <c r="AO9">
-        <v>375</v>
+        <v>453.9650406844951</v>
       </c>
       <c r="AP9">
-        <v>0.00375</v>
+        <v>0.004539650406844951</v>
       </c>
       <c r="AQ9">
-        <v>0.07759003437314589</v>
+        <v>0.1756726213336506</v>
       </c>
       <c r="AR9">
-        <v>0.01085239139770276</v>
+        <v>0.0481885022448811</v>
       </c>
       <c r="AS9">
-        <v>0.02507470802710865</v>
+        <v>0.06936487115316818</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV9" t="s">
         <v>86</v>
@@ -2021,7 +2045,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>67</v>
@@ -2030,70 +2054,70 @@
         <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J10" s="2">
         <v>46230</v>
       </c>
       <c r="K10">
-        <v>0.6317203254759612</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.158244697090097</v>
+        <v>1.517345620394397</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
         <v>73</v>
       </c>
       <c r="Q10">
-        <v>0.9079300813689903</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>7.69</v>
+        <v>6.765079999999999</v>
       </c>
       <c r="S10">
-        <v>7.622919799747425</v>
+        <v>6.695637122918773</v>
       </c>
       <c r="T10">
-        <v>7.590213959429482</v>
+        <v>6.623530889754512</v>
       </c>
       <c r="U10">
-        <v>7.69</v>
+        <v>6.765079999999999</v>
       </c>
       <c r="V10">
-        <v>7.622400000000001</v>
+        <v>6.746059999999999</v>
       </c>
       <c r="W10">
-        <v>7.622919799747425</v>
+        <v>6.695637122918773</v>
       </c>
       <c r="X10">
-        <v>7.7509</v>
+        <v>6.811375251387483</v>
       </c>
       <c r="Y10">
-        <v>-0.008723042945718493</v>
+        <v>-0.01026490109225994</v>
       </c>
       <c r="Z10">
-        <v>1.10148112073195</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.008723042945718493</v>
+        <v>0.01026490109225994</v>
       </c>
       <c r="AB10">
-        <v>0.4039080303802292</v>
+        <v>0.442563215978486</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3960919696197709</v>
+        <v>0.357436784021514</v>
       </c>
       <c r="AE10" t="s">
         <v>83</v>
@@ -2105,46 +2129,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>453.9650406844952</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.007919375812743759</v>
+        <v>0.00684326739483996</v>
       </c>
       <c r="AJ10">
-        <v>63136.28899835848</v>
+        <v>73064.51306827727</v>
       </c>
       <c r="AK10">
-        <v>57323.3360076157</v>
+        <v>54798.38480120795</v>
       </c>
       <c r="AL10">
-        <v>7454.269961978634</v>
+        <v>8100.182821372099</v>
       </c>
       <c r="AM10">
-        <v>573.2333600761569</v>
+        <v>547.9838480120795</v>
       </c>
       <c r="AN10">
-        <v>0.005732333600761569</v>
+        <v>0.005479838480120795</v>
       </c>
       <c r="AO10">
-        <v>453.9650406844951</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP10">
-        <v>0.004539650406844951</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ10">
-        <v>0.1406778286801442</v>
+        <v>0.08395425167743545</v>
       </c>
       <c r="AR10">
-        <v>0.03443688981687151</v>
+        <v>0.01326239124582115</v>
       </c>
       <c r="AS10">
-        <v>0.05638783433245466</v>
+        <v>0.03403914978955434</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV10" t="s">
         <v>86</v>
@@ -2176,7 +2200,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>67</v>
@@ -2185,7 +2209,7 @@
         <v>67</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J11" s="2">
         <v>46230</v>
@@ -2203,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
         <v>73</v>
@@ -2215,10 +2239,10 @@
         <v>4065.63</v>
       </c>
       <c r="S11">
-        <v>4015.627815695351</v>
+        <v>3996.438679093746</v>
       </c>
       <c r="T11">
-        <v>4041.690618351678</v>
+        <v>4000.826348313311</v>
       </c>
       <c r="U11">
         <v>4065.63</v>
@@ -2227,28 +2251,28 @@
         <v>3955.56</v>
       </c>
       <c r="W11">
-        <v>4015.627815695351</v>
+        <v>3996.438679093746</v>
       </c>
       <c r="X11">
         <v>4195.495</v>
       </c>
       <c r="Y11">
-        <v>-0.01229875426555019</v>
+        <v>-0.01701859758666039</v>
       </c>
       <c r="Z11">
-        <v>0.3850320279108988</v>
+        <v>0.5327942163497026</v>
       </c>
       <c r="AA11">
-        <v>0.01229875426555019</v>
+        <v>0.01701859758666039</v>
       </c>
       <c r="AB11">
-        <v>0.44181519213033</v>
+        <v>0.4167484190059697</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3581848078696699</v>
+        <v>0.3832515809940303</v>
       </c>
       <c r="AE11" t="s">
         <v>84</v>
@@ -2287,19 +2311,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>333.1887310792765</v>
+        <v>407.3438223348643</v>
       </c>
       <c r="AR11">
-        <v>72.20478098504081</v>
+        <v>119.4163711026086</v>
       </c>
       <c r="AS11">
-        <v>173.8010623834666</v>
+        <v>202.3847869453769</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03248696319184401</v>
+        <v>0.04157677839021321</v>
       </c>
       <c r="AV11" t="s">
         <v>86</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -178,12 +178,12 @@
     <t>USDJPY</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>AUDCNH</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -226,13 +226,13 @@
     <t>UP</t>
   </si>
   <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
+    <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -241,34 +241,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.0626,naive=0.01174,drift4=0.01838; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0344,naive=0.01308,drift4=0.01957; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.578,naive=1.76,drift4=1.751; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05735,naive=0.01821,drift4=0.03238; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.0277,naive=0.01216,drift4=0.02024; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1239,naive=0.07093,drift4=0.1188; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.2344,naive=0.1097,drift4=0.1877; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3212,naive=0.07231,drift4=0.09659; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09628,naive=0.02199,drift4=0.05204; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=610.2,naive=200.2,drift4=276.5; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06409,naive=0.0112,drift4=0.01883; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03308,naive=0.01219,drift4=0.01972; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.866,naive=1.765,drift4=1.759; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.02649,naive=0.01164,drift4=0.02107; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05677,naive=0.01826,drift4=0.03383; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1162,naive=0.06618,drift4=0.1241; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2145,naive=0.11,drift4=0.1936; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3138,naive=0.06927,drift4=0.09777; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1004,naive=0.02126,drift4=0.05157; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=534,naive=179.8,drift4=279.8; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -823,7 +823,7 @@
         <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" t="s">
         <v>68</v>
@@ -844,7 +844,7 @@
         <v>48</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P2" t="s">
         <v>72</v>
@@ -856,10 +856,10 @@
         <v>1.137055</v>
       </c>
       <c r="S2">
-        <v>1.139434610215785</v>
+        <v>1.137274646540839</v>
       </c>
       <c r="T2">
-        <v>1.14940716860582</v>
+        <v>1.143918300710949</v>
       </c>
       <c r="U2">
         <v>1.137055</v>
@@ -868,19 +868,19 @@
         <v>1.13061</v>
       </c>
       <c r="Y2">
-        <v>0.00209278374026296</v>
+        <v>0.0001931714304402866</v>
       </c>
       <c r="AA2">
-        <v>0.00209278374026296</v>
+        <v>0.0001931714304402866</v>
       </c>
       <c r="AB2">
-        <v>0.4008907072021103</v>
+        <v>0.4039318510752031</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3991092927978898</v>
+        <v>0.396068148924797</v>
       </c>
       <c r="AE2" t="s">
         <v>75</v>
@@ -916,19 +916,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03477187396859784</v>
+        <v>0.03410286274290813</v>
       </c>
       <c r="AR2">
-        <v>0.006942598925878485</v>
+        <v>0.006057540283555759</v>
       </c>
       <c r="AS2">
-        <v>0.01229401656257361</v>
+        <v>0.01169669202322499</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV2" t="s">
         <v>85</v>
@@ -960,7 +960,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -987,7 +987,7 @@
         <v>38</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
         <v>73</v>
@@ -999,10 +999,10 @@
         <v>0.81914</v>
       </c>
       <c r="S3">
-        <v>0.8303893931979528</v>
+        <v>0.8296859223041861</v>
       </c>
       <c r="T3">
-        <v>0.8316876878036235</v>
+        <v>0.8301141275518287</v>
       </c>
       <c r="U3">
         <v>0.81914</v>
@@ -1011,28 +1011,28 @@
         <v>0.8349799999999999</v>
       </c>
       <c r="W3">
-        <v>0.8303893931979528</v>
+        <v>0.8296859223041861</v>
       </c>
       <c r="X3">
         <v>0.810765</v>
       </c>
       <c r="Y3">
-        <v>0.0137331752788935</v>
+        <v>0.01287438326071998</v>
       </c>
       <c r="Z3">
-        <v>1.343211128113761</v>
+        <v>1.259214603484907</v>
       </c>
       <c r="AA3">
-        <v>0.0137331752788935</v>
+        <v>0.01287438326071998</v>
       </c>
       <c r="AB3">
-        <v>0.4320996057460227</v>
+        <v>0.4369365860818993</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3679003942539772</v>
+        <v>0.3630634139181007</v>
       </c>
       <c r="AE3" t="s">
         <v>76</v>
@@ -1071,19 +1071,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.02372418581813656</v>
+        <v>0.02187751235752217</v>
       </c>
       <c r="AR3">
-        <v>0.008542612881181456</v>
+        <v>0.007425613824641858</v>
       </c>
       <c r="AS3">
-        <v>0.01164349356653238</v>
+        <v>0.0108300515262109</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1115,7 +1115,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>66</v>
@@ -1142,7 +1142,7 @@
         <v>46</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
         <v>73</v>
@@ -1154,10 +1154,10 @@
         <v>163.777</v>
       </c>
       <c r="S4">
-        <v>164.9328392614813</v>
+        <v>164.5872570149775</v>
       </c>
       <c r="T4">
-        <v>164.152228284504</v>
+        <v>163.2270877366064</v>
       </c>
       <c r="U4">
         <v>163.777</v>
@@ -1166,28 +1166,28 @@
         <v>166.184</v>
       </c>
       <c r="W4">
-        <v>164.9328392614813</v>
+        <v>164.5872570149775</v>
       </c>
       <c r="X4">
         <v>162.175</v>
       </c>
       <c r="Y4">
-        <v>0.007057396713099373</v>
+        <v>0.004947318701512041</v>
       </c>
       <c r="Z4">
-        <v>0.7214976663428736</v>
+        <v>0.5057784113467807</v>
       </c>
       <c r="AA4">
-        <v>0.007057396713099373</v>
+        <v>0.004947318701512041</v>
       </c>
       <c r="AB4">
-        <v>0.3788618242137581</v>
+        <v>0.3771985387697701</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4211381757862419</v>
+        <v>0.4228014612302299</v>
       </c>
       <c r="AE4" t="s">
         <v>77</v>
@@ -1226,19 +1226,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>4.646015501811858</v>
+        <v>4.652503752042117</v>
       </c>
       <c r="AR4">
-        <v>1.167271601239547</v>
+        <v>1.055753157355829</v>
       </c>
       <c r="AS4">
-        <v>1.321028066049352</v>
+        <v>1.218966494801571</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV4" t="s">
         <v>86</v>
@@ -1279,7 +1279,7 @@
         <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J5" s="2">
         <v>46230</v>
@@ -1288,61 +1288,61 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.3302513599941327</v>
+        <v>0.5147098189776956</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>1.32899</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="S5">
-        <v>1.33502722857898</v>
+        <v>0.700449939029405</v>
       </c>
       <c r="T5">
-        <v>1.347917714716592</v>
+        <v>0.6996050882059283</v>
       </c>
       <c r="U5">
-        <v>1.32899</v>
+        <v>0.6983900000000001</v>
       </c>
       <c r="V5">
-        <v>1.32288</v>
+        <v>0.7027800000000002</v>
       </c>
       <c r="W5">
-        <v>1.33502722857898</v>
+        <v>0.700449939029405</v>
       </c>
       <c r="X5">
-        <v>1.317065</v>
+        <v>0.69069</v>
       </c>
       <c r="Y5">
-        <v>0.004542719342493533</v>
+        <v>0.00294955401624441</v>
       </c>
       <c r="Z5">
-        <v>0.5062665475036034</v>
+        <v>0.2675245492733657</v>
       </c>
       <c r="AA5">
-        <v>0.004542719342493533</v>
+        <v>0.00294955401624441</v>
       </c>
       <c r="AB5">
-        <v>0.4363508691845883</v>
+        <v>0.4573547439353595</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3636491308154117</v>
+        <v>0.3426452560646405</v>
       </c>
       <c r="AE5" t="s">
         <v>78</v>
@@ -1354,46 +1354,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.008972979480658259</v>
+        <v>0.01102535832414563</v>
       </c>
       <c r="AJ5">
-        <v>55722.85115303974</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AK5">
-        <v>41792.13836477981</v>
+        <v>45349.9999999996</v>
       </c>
       <c r="AL5">
-        <v>31446.5408805031</v>
+        <v>64935.06493506436</v>
       </c>
       <c r="AM5">
-        <v>417.9213836477981</v>
+        <v>453.499999999996</v>
       </c>
       <c r="AN5">
-        <v>0.004179213836477981</v>
+        <v>0.00453499999999996</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.03466893976698469</v>
+        <v>0.0182942622354148</v>
       </c>
       <c r="AR5">
-        <v>0.009201015222123844</v>
+        <v>0.005062342938969245</v>
       </c>
       <c r="AS5">
-        <v>0.02286274114115988</v>
+        <v>0.01301792497067794</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV5" t="s">
         <v>86</v>
@@ -1434,7 +1434,7 @@
         <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2">
         <v>46230</v>
@@ -1443,61 +1443,61 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.5147098189776956</v>
+        <v>0.3302513599941327</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N6">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>0.6983900000000001</v>
+        <v>1.32899</v>
       </c>
       <c r="S6">
-        <v>0.6999681198381074</v>
+        <v>1.332295544255687</v>
       </c>
       <c r="T6">
-        <v>0.698484453906832</v>
+        <v>1.341482295123377</v>
       </c>
       <c r="U6">
-        <v>0.6983900000000001</v>
+        <v>1.32899</v>
       </c>
       <c r="V6">
-        <v>0.7027800000000002</v>
+        <v>1.32288</v>
       </c>
       <c r="W6">
-        <v>0.6999681198381074</v>
+        <v>1.332295544255687</v>
       </c>
       <c r="X6">
-        <v>0.69069</v>
+        <v>1.317065</v>
       </c>
       <c r="Y6">
-        <v>0.002259654116048762</v>
+        <v>0.002487260442657597</v>
       </c>
       <c r="Z6">
-        <v>0.2049506283256209</v>
+        <v>0.2771944868501061</v>
       </c>
       <c r="AA6">
-        <v>0.002259654116048762</v>
+        <v>0.002487260442657597</v>
       </c>
       <c r="AB6">
-        <v>0.4502058923237894</v>
+        <v>0.4404587821741963</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3497941076762106</v>
+        <v>0.3595412178258037</v>
       </c>
       <c r="AE6" t="s">
         <v>79</v>
@@ -1509,46 +1509,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01102535832414563</v>
+        <v>0.008972979480658259</v>
       </c>
       <c r="AJ6">
-        <v>45349.9999999996</v>
+        <v>55722.85115303974</v>
       </c>
       <c r="AK6">
-        <v>45349.9999999996</v>
+        <v>41792.13836477981</v>
       </c>
       <c r="AL6">
-        <v>64935.06493506436</v>
+        <v>31446.5408805031</v>
       </c>
       <c r="AM6">
-        <v>453.499999999996</v>
+        <v>417.9213836477981</v>
       </c>
       <c r="AN6">
-        <v>0.00453499999999996</v>
+        <v>0.004179213836477981</v>
       </c>
       <c r="AO6">
-        <v>499.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.004999999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.02005757543837777</v>
+        <v>0.03257514271135253</v>
       </c>
       <c r="AR6">
-        <v>0.005878894069939932</v>
+        <v>0.008852851225212881</v>
       </c>
       <c r="AS6">
-        <v>0.01340922205233603</v>
+        <v>0.02227902076576797</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV6" t="s">
         <v>86</v>
@@ -1580,7 +1580,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
         <v>66</v>
@@ -1607,7 +1607,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
         <v>74</v>
@@ -1619,10 +1619,10 @@
         <v>4.7282</v>
       </c>
       <c r="S7">
-        <v>4.73390884487149</v>
+        <v>4.735220002101462</v>
       </c>
       <c r="T7">
-        <v>4.726223709795539</v>
+        <v>4.72938274620225</v>
       </c>
       <c r="U7">
         <v>4.7282</v>
@@ -1637,22 +1637,22 @@
         <v>4.6933525</v>
       </c>
       <c r="Y7">
-        <v>0.001207403424451056</v>
+        <v>0.001484709213117448</v>
       </c>
       <c r="Z7">
         <v>0.2035239256761609</v>
       </c>
       <c r="AA7">
-        <v>0.001207403424451056</v>
+        <v>0.001484709213117448</v>
       </c>
       <c r="AB7">
-        <v>0.4687366672288881</v>
+        <v>0.4777352708867221</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3312633327711119</v>
+        <v>0.322264729113278</v>
       </c>
       <c r="AE7" t="s">
         <v>80</v>
@@ -1691,19 +1691,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.08793385602186127</v>
+        <v>0.07944011823896788</v>
       </c>
       <c r="AR7">
-        <v>0.03498250304000233</v>
+        <v>0.02881286505271276</v>
       </c>
       <c r="AS7">
-        <v>0.07422223568030864</v>
+        <v>0.07181990051288577</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV7" t="s">
         <v>86</v>
@@ -1735,7 +1735,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" t="s">
         <v>73</v>
@@ -1774,10 +1774,10 @@
         <v>8.98892</v>
       </c>
       <c r="S8">
-        <v>8.955020099515837</v>
+        <v>8.93854440299466</v>
       </c>
       <c r="T8">
-        <v>8.966202662886595</v>
+        <v>8.929950939173487</v>
       </c>
       <c r="U8">
         <v>8.98892</v>
@@ -1786,28 +1786,28 @@
         <v>8.920390000000001</v>
       </c>
       <c r="W8">
-        <v>8.955020099515837</v>
+        <v>8.93854440299466</v>
       </c>
       <c r="X8">
         <v>9.080265000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.003771298496834278</v>
+        <v>-0.005604187934183429</v>
       </c>
       <c r="Z8">
-        <v>0.3711193878610058</v>
+        <v>0.5514871860018622</v>
       </c>
       <c r="AA8">
-        <v>0.003771298496834278</v>
+        <v>0.005604187934183429</v>
       </c>
       <c r="AB8">
-        <v>0.4567317898030007</v>
+        <v>0.4652684128559521</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3432682101969994</v>
+        <v>0.3347315871440479</v>
       </c>
       <c r="AE8" t="s">
         <v>81</v>
@@ -1846,19 +1846,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1898762217228014</v>
+        <v>0.1281194839938811</v>
       </c>
       <c r="AR8">
-        <v>0.0601156273185434</v>
+        <v>0.0580494970510118</v>
       </c>
       <c r="AS8">
-        <v>0.1438490349360235</v>
+        <v>0.1378740427859807</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV8" t="s">
         <v>86</v>
@@ -1890,7 +1890,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
@@ -1917,7 +1917,7 @@
         <v>114</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
         <v>73</v>
@@ -1929,10 +1929,10 @@
         <v>7.69</v>
       </c>
       <c r="S9">
-        <v>7.64852009530019</v>
+        <v>7.634521808826518</v>
       </c>
       <c r="T9">
-        <v>7.654261293673839</v>
+        <v>7.618897113873745</v>
       </c>
       <c r="U9">
         <v>7.69</v>
@@ -1941,28 +1941,28 @@
         <v>7.622400000000001</v>
       </c>
       <c r="W9">
-        <v>7.64852009530019</v>
+        <v>7.634521808826518</v>
       </c>
       <c r="X9">
         <v>7.7509</v>
       </c>
       <c r="Y9">
-        <v>-0.005394005812719115</v>
+        <v>-0.007214329151298087</v>
       </c>
       <c r="Z9">
-        <v>0.681115019701319</v>
+        <v>0.9109719404512765</v>
       </c>
       <c r="AA9">
-        <v>0.005394005812719115</v>
+        <v>0.007214329151298087</v>
       </c>
       <c r="AB9">
-        <v>0.395467159280301</v>
+        <v>0.3991540470024339</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4045328407196991</v>
+        <v>0.4008459529975662</v>
       </c>
       <c r="AE9" t="s">
         <v>82</v>
@@ -2001,19 +2001,19 @@
         <v>0.004539650406844951</v>
       </c>
       <c r="AQ9">
-        <v>0.1756726213336506</v>
+        <v>0.161085189550867</v>
       </c>
       <c r="AR9">
-        <v>0.0481885022448811</v>
+        <v>0.04235574752521119</v>
       </c>
       <c r="AS9">
-        <v>0.06936487115316818</v>
+        <v>0.06479048516709381</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV9" t="s">
         <v>86</v>
@@ -2045,7 +2045,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
         <v>67</v>
@@ -2072,7 +2072,7 @@
         <v>8</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
         <v>73</v>
@@ -2084,10 +2084,10 @@
         <v>6.765079999999999</v>
       </c>
       <c r="S10">
-        <v>6.695637122918773</v>
+        <v>6.701191225012574</v>
       </c>
       <c r="T10">
-        <v>6.623530889754512</v>
+        <v>6.63569298014601</v>
       </c>
       <c r="U10">
         <v>6.765079999999999</v>
@@ -2096,28 +2096,28 @@
         <v>6.746059999999999</v>
       </c>
       <c r="W10">
-        <v>6.695637122918773</v>
+        <v>6.701191225012574</v>
       </c>
       <c r="X10">
-        <v>6.811375251387483</v>
+        <v>6.807672516658283</v>
       </c>
       <c r="Y10">
-        <v>-0.01026490109225994</v>
+        <v>-0.009443905317812315</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.01026490109225994</v>
+        <v>0.009443905317812315</v>
       </c>
       <c r="AB10">
-        <v>0.442563215978486</v>
+        <v>0.441008328863268</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.357436784021514</v>
+        <v>0.3589916711367321</v>
       </c>
       <c r="AE10" t="s">
         <v>83</v>
@@ -2132,43 +2132,43 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.00684326739483996</v>
+        <v>0.006295936878541544</v>
       </c>
       <c r="AJ10">
-        <v>73064.51306827727</v>
+        <v>79416.298105553</v>
       </c>
       <c r="AK10">
-        <v>54798.38480120795</v>
+        <v>59562.22357916475</v>
       </c>
       <c r="AL10">
-        <v>8100.182821372099</v>
+        <v>8804.36352255476</v>
       </c>
       <c r="AM10">
-        <v>547.9838480120795</v>
+        <v>595.6222357916474</v>
       </c>
       <c r="AN10">
-        <v>0.005479838480120795</v>
+        <v>0.005956222357916474</v>
       </c>
       <c r="AO10">
-        <v>375.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.003750000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08395425167743545</v>
+        <v>0.0823400346706033</v>
       </c>
       <c r="AR10">
-        <v>0.01326239124582115</v>
+        <v>0.01239582451374733</v>
       </c>
       <c r="AS10">
-        <v>0.03403914978955434</v>
+        <v>0.03082934280351164</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV10" t="s">
         <v>86</v>
@@ -2200,7 +2200,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
         <v>67</v>
@@ -2227,7 +2227,7 @@
         <v>102</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P11" t="s">
         <v>73</v>
@@ -2239,10 +2239,10 @@
         <v>4065.63</v>
       </c>
       <c r="S11">
-        <v>3996.438679093746</v>
+        <v>4006.60665761875</v>
       </c>
       <c r="T11">
-        <v>4000.826348313311</v>
+        <v>4023.333057983934</v>
       </c>
       <c r="U11">
         <v>4065.63</v>
@@ -2251,28 +2251,28 @@
         <v>3955.56</v>
       </c>
       <c r="W11">
-        <v>3996.438679093746</v>
+        <v>4006.60665761875</v>
       </c>
       <c r="X11">
         <v>4195.495</v>
       </c>
       <c r="Y11">
-        <v>-0.01701859758666039</v>
+        <v>-0.01451763745870866</v>
       </c>
       <c r="Z11">
-        <v>0.5327942163497026</v>
+        <v>0.4544976889943382</v>
       </c>
       <c r="AA11">
-        <v>0.01701859758666039</v>
+        <v>0.01451763745870866</v>
       </c>
       <c r="AB11">
-        <v>0.4167484190059697</v>
+        <v>0.4283805170135917</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3832515809940303</v>
+        <v>0.3716194829864083</v>
       </c>
       <c r="AE11" t="s">
         <v>84</v>
@@ -2311,19 +2311,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>407.3438223348643</v>
+        <v>370.3792360780287</v>
       </c>
       <c r="AR11">
-        <v>119.4163711026086</v>
+        <v>98.66483913672732</v>
       </c>
       <c r="AS11">
-        <v>202.3847869453769</v>
+        <v>195.0715376148925</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04157677839021321</v>
+        <v>0.04205316226800889</v>
       </c>
       <c r="AV11" t="s">
         <v>86</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>Pair</t>
   </si>
@@ -172,6 +172,9 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
@@ -184,9 +187,6 @@
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
@@ -211,6 +211,9 @@
     <t>MEDIUM</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -226,10 +229,13 @@
     <t>UP</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>NO_SIGNAL</t>
@@ -244,6 +250,9 @@
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06409,naive=0.0112,drift4=0.01883; naive_cap_applied</t>
   </si>
   <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1162,naive=0.06618,drift4=0.1241; naive_cap_applied</t>
+  </si>
+  <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03308,naive=0.01219,drift4=0.01972; naive_cap_applied</t>
   </si>
   <si>
@@ -254,9 +263,6 @@
   </si>
   <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05677,naive=0.01826,drift4=0.03383; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1162,naive=0.06618,drift4=0.1241; naive_cap_applied</t>
   </si>
   <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2145,naive=0.11,drift4=0.1936; naive_cap_applied</t>
@@ -805,7 +811,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -820,58 +826,58 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>2.184951219045213</v>
+        <v>2.229848045867981</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.137055</v>
+        <v>1.138385</v>
       </c>
       <c r="S2">
-        <v>1.137274646540839</v>
+        <v>1.139620716129513</v>
       </c>
       <c r="T2">
-        <v>1.143918300710949</v>
+        <v>1.146459641062795</v>
       </c>
       <c r="U2">
-        <v>1.137055</v>
+        <v>1.138385</v>
       </c>
       <c r="V2">
-        <v>1.13061</v>
+        <v>1.13327</v>
       </c>
       <c r="Y2">
-        <v>0.0001931714304402866</v>
+        <v>0.001085499307802436</v>
       </c>
       <c r="AA2">
-        <v>0.0001931714304402866</v>
+        <v>0.001085499307802436</v>
       </c>
       <c r="AB2">
         <v>0.4039318510752031</v>
@@ -883,7 +889,7 @@
         <v>0.396068148924797</v>
       </c>
       <c r="AE2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -916,31 +922,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03410286274290813</v>
+        <v>0.03429148452102111</v>
       </c>
       <c r="AR2">
-        <v>0.006057540283555759</v>
+        <v>0.005808073985073037</v>
       </c>
       <c r="AS2">
-        <v>0.01169669202322499</v>
+        <v>0.01167334852651093</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY2" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -948,7 +954,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -960,7 +966,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -972,70 +978,61 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.475696314671024</v>
+        <v>0.5921660548914897</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0.81914</v>
+        <v>4.72079</v>
       </c>
       <c r="S3">
-        <v>0.8296859223041861</v>
+        <v>4.725396004536346</v>
       </c>
       <c r="T3">
-        <v>0.8301141275518287</v>
+        <v>4.721918289426771</v>
       </c>
       <c r="U3">
-        <v>0.81914</v>
+        <v>4.72079</v>
       </c>
       <c r="V3">
-        <v>0.8349799999999999</v>
-      </c>
-      <c r="W3">
-        <v>0.8296859223041861</v>
-      </c>
-      <c r="X3">
-        <v>0.810765</v>
+        <v>4.73341</v>
       </c>
       <c r="Y3">
-        <v>0.01287438326071998</v>
-      </c>
-      <c r="Z3">
-        <v>1.259214603484907</v>
+        <v>0.0009756851154883605</v>
       </c>
       <c r="AA3">
-        <v>0.01287438326071998</v>
+        <v>0.0009756851154883605</v>
       </c>
       <c r="AB3">
-        <v>0.4369365860818993</v>
+        <v>0.4777352708867221</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3630634139181007</v>
+        <v>0.322264729113278</v>
       </c>
       <c r="AE3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1044,58 +1041,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.0102241375100716</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>48903.88059701463</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>48903.88059701463</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>59701.49253731308</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>489.0388059701464</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.004890388059701464</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.02187751235752217</v>
+        <v>0.07689499151171393</v>
       </c>
       <c r="AR3">
-        <v>0.007425613824641858</v>
+        <v>0.02922396999107149</v>
       </c>
       <c r="AS3">
-        <v>0.0108300515262109</v>
+        <v>0.07322722909943137</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1103,7 +1097,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,79 +1112,79 @@
         <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>3.569077241700109</v>
+        <v>2.744246931337766</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>163.777</v>
+        <v>0.8197099999999999</v>
       </c>
       <c r="S4">
-        <v>164.5872570149775</v>
+        <v>0.8305939770959434</v>
       </c>
       <c r="T4">
-        <v>163.2270877366064</v>
+        <v>0.8309841908790948</v>
       </c>
       <c r="U4">
-        <v>163.777</v>
+        <v>0.8197099999999999</v>
       </c>
       <c r="V4">
-        <v>166.184</v>
+        <v>0.8361199999999999</v>
       </c>
       <c r="W4">
-        <v>164.5872570149775</v>
+        <v>0.8305939770959434</v>
       </c>
       <c r="X4">
-        <v>162.175</v>
+        <v>0.8113349999999999</v>
       </c>
       <c r="Y4">
-        <v>0.004947318701512041</v>
+        <v>0.01327783862090674</v>
       </c>
       <c r="Z4">
-        <v>0.5057784113467807</v>
+        <v>1.29957935473951</v>
       </c>
       <c r="AA4">
-        <v>0.004947318701512041</v>
+        <v>0.01327783862090674</v>
       </c>
       <c r="AB4">
-        <v>0.3771985387697701</v>
+        <v>0.4369365860818993</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4228014612302299</v>
+        <v>0.3630634139181007</v>
       </c>
       <c r="AE4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1202,22 +1196,22 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.009781593264011368</v>
+        <v>0.01021702797330769</v>
       </c>
       <c r="AJ4">
-        <v>51116.41697877686</v>
+        <v>48937.91044776091</v>
       </c>
       <c r="AK4">
-        <v>51116.41697877686</v>
+        <v>48937.91044776091</v>
       </c>
       <c r="AL4">
-        <v>312.1098626716624</v>
+        <v>59701.49253731309</v>
       </c>
       <c r="AM4">
-        <v>511.1641697877686</v>
+        <v>489.3791044776091</v>
       </c>
       <c r="AN4">
-        <v>0.005111641697877686</v>
+        <v>0.004893791044776091</v>
       </c>
       <c r="AO4">
         <v>500</v>
@@ -1226,31 +1220,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>4.652503752042117</v>
+        <v>0.02195212107845924</v>
       </c>
       <c r="AR4">
-        <v>1.055753157355829</v>
+        <v>0.007579817798880702</v>
       </c>
       <c r="AS4">
-        <v>1.218966494801571</v>
+        <v>0.01084228149189176</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY4" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1258,7 +1252,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1270,82 +1264,82 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0.5147098189776956</v>
+        <v>3.990078193416717</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>0.6983900000000001</v>
+        <v>163.876</v>
       </c>
       <c r="S5">
-        <v>0.700449939029405</v>
+        <v>164.7767066864221</v>
       </c>
       <c r="T5">
-        <v>0.6996050882059283</v>
+        <v>163.4549120076157</v>
       </c>
       <c r="U5">
-        <v>0.6983900000000001</v>
+        <v>163.876</v>
       </c>
       <c r="V5">
-        <v>0.7027800000000002</v>
+        <v>166.382</v>
       </c>
       <c r="W5">
-        <v>0.700449939029405</v>
+        <v>164.7767066864221</v>
       </c>
       <c r="X5">
-        <v>0.69069</v>
+        <v>162.274</v>
       </c>
       <c r="Y5">
-        <v>0.00294955401624441</v>
+        <v>0.005496269657680618</v>
       </c>
       <c r="Z5">
-        <v>0.2675245492733657</v>
+        <v>0.5622388804132802</v>
       </c>
       <c r="AA5">
-        <v>0.00294955401624441</v>
+        <v>0.005496269657680618</v>
       </c>
       <c r="AB5">
-        <v>0.4573547439353595</v>
+        <v>0.3771985387697701</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3426452560646405</v>
+        <v>0.4228014612302299</v>
       </c>
       <c r="AE5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1357,55 +1351,55 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01102535832414563</v>
+        <v>0.00977568405379671</v>
       </c>
       <c r="AJ5">
-        <v>45349.9999999996</v>
+        <v>51147.31585518135</v>
       </c>
       <c r="AK5">
-        <v>45349.9999999996</v>
+        <v>51147.31585518135</v>
       </c>
       <c r="AL5">
-        <v>64935.06493506436</v>
+        <v>312.1098626716624</v>
       </c>
       <c r="AM5">
-        <v>453.499999999996</v>
+        <v>511.4731585518135</v>
       </c>
       <c r="AN5">
-        <v>0.00453499999999996</v>
+        <v>0.005114731585518136</v>
       </c>
       <c r="AO5">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.0182942622354148</v>
+        <v>4.701049774548353</v>
       </c>
       <c r="AR5">
-        <v>0.005062342938969245</v>
+        <v>1.07824629880137</v>
       </c>
       <c r="AS5">
-        <v>0.01301792497067794</v>
+        <v>1.206300865993987</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY5" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1413,7 +1407,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1425,82 +1419,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.3302513599941327</v>
+        <v>0.650343444575059</v>
       </c>
       <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6">
         <v>1</v>
       </c>
-      <c r="N6">
-        <v>7</v>
-      </c>
-      <c r="O6" t="s">
-        <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q6">
-        <v>0.75</v>
-      </c>
       <c r="R6">
-        <v>1.32899</v>
+        <v>0.697225</v>
       </c>
       <c r="S6">
-        <v>1.332295544255687</v>
+        <v>0.6988185905988538</v>
       </c>
       <c r="T6">
-        <v>1.341482295123377</v>
+        <v>0.6982932291033901</v>
       </c>
       <c r="U6">
-        <v>1.32899</v>
+        <v>0.697225</v>
       </c>
       <c r="V6">
-        <v>1.32288</v>
+        <v>0.70045</v>
       </c>
       <c r="W6">
-        <v>1.332295544255687</v>
+        <v>0.6988185905988538</v>
       </c>
       <c r="X6">
-        <v>1.317065</v>
+        <v>0.6895249999999999</v>
       </c>
       <c r="Y6">
-        <v>0.002487260442657597</v>
+        <v>0.002285618844496078</v>
       </c>
       <c r="Z6">
-        <v>0.2771944868501061</v>
+        <v>0.2069598180329563</v>
       </c>
       <c r="AA6">
-        <v>0.002487260442657597</v>
+        <v>0.002285618844496078</v>
       </c>
       <c r="AB6">
-        <v>0.4404587821741963</v>
+        <v>0.4573547439353595</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3595412178258037</v>
+        <v>0.3426452560646405</v>
       </c>
       <c r="AE6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1509,58 +1503,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.008972979480658259</v>
+        <v>0.01104378070206901</v>
       </c>
       <c r="AJ6">
-        <v>55722.85115303974</v>
+        <v>45274.35064935025</v>
       </c>
       <c r="AK6">
-        <v>41792.13836477981</v>
+        <v>45274.35064935025</v>
       </c>
       <c r="AL6">
-        <v>31446.5408805031</v>
+        <v>64935.06493506437</v>
       </c>
       <c r="AM6">
-        <v>417.9213836477981</v>
+        <v>452.7435064935025</v>
       </c>
       <c r="AN6">
-        <v>0.004179213836477981</v>
+        <v>0.004527435064935025</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.03257514271135253</v>
+        <v>0.01798890136541919</v>
       </c>
       <c r="AR6">
-        <v>0.008852851225212881</v>
+        <v>0.005187602927600872</v>
       </c>
       <c r="AS6">
-        <v>0.02227902076576797</v>
+        <v>0.01305718737096484</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY6" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1568,7 +1562,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1580,82 +1574,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.571803579797887</v>
+        <v>0.5577364673232961</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>4.7282</v>
+        <v>1.3286</v>
       </c>
       <c r="S7">
-        <v>4.735220002101462</v>
+        <v>1.33142218384049</v>
       </c>
       <c r="T7">
-        <v>4.72938274620225</v>
+        <v>1.340313245291399</v>
       </c>
       <c r="U7">
-        <v>4.7282</v>
+        <v>1.3286</v>
       </c>
       <c r="V7">
-        <v>4.74823</v>
+        <v>1.3221</v>
       </c>
       <c r="W7">
-        <v>4.7352923</v>
+        <v>1.33142218384049</v>
       </c>
       <c r="X7">
-        <v>4.6933525</v>
+        <v>1.316675</v>
       </c>
       <c r="Y7">
-        <v>0.001484709213117448</v>
+        <v>0.002124178714804757</v>
       </c>
       <c r="Z7">
-        <v>0.2035239256761609</v>
+        <v>0.2366611186993372</v>
       </c>
       <c r="AA7">
-        <v>0.001484709213117448</v>
+        <v>0.002124178714804757</v>
       </c>
       <c r="AB7">
-        <v>0.4777352708867221</v>
+        <v>0.4404587821741963</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.322264729113278</v>
+        <v>0.3595412178258037</v>
       </c>
       <c r="AE7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,22 +1661,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.007370140856985728</v>
+        <v>0.008975613427668236</v>
       </c>
       <c r="AJ7">
-        <v>67841.30855872029</v>
+        <v>55706.49895178188</v>
       </c>
       <c r="AK7">
-        <v>67841.30855872029</v>
+        <v>55706.49895178188</v>
       </c>
       <c r="AL7">
-        <v>14348.23158045774</v>
+        <v>41928.72117400412</v>
       </c>
       <c r="AM7">
-        <v>678.413085587203</v>
+        <v>557.0649895178188</v>
       </c>
       <c r="AN7">
-        <v>0.00678413085587203</v>
+        <v>0.005570649895178188</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1691,31 +1685,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.07944011823896788</v>
+        <v>0.03266911923915516</v>
       </c>
       <c r="AR7">
-        <v>0.02881286505271276</v>
+        <v>0.008948852626565829</v>
       </c>
       <c r="AS7">
-        <v>0.07181990051288577</v>
+        <v>0.02235570907751056</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY7" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1723,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,67 +1732,67 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.4771409674339303</v>
+        <v>0.5766398971767849</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q8">
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>8.98892</v>
+        <v>8.99408</v>
       </c>
       <c r="S8">
-        <v>8.93854440299466</v>
+        <v>8.949121299943343</v>
       </c>
       <c r="T8">
-        <v>8.929950939173487</v>
+        <v>8.943041161507667</v>
       </c>
       <c r="U8">
-        <v>8.98892</v>
+        <v>8.99408</v>
       </c>
       <c r="V8">
-        <v>8.920390000000001</v>
+        <v>8.930710000000001</v>
       </c>
       <c r="W8">
-        <v>8.93854440299466</v>
+        <v>8.949121299943343</v>
       </c>
       <c r="X8">
-        <v>9.080265000000001</v>
+        <v>9.085425000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.005604187934183429</v>
+        <v>-0.004998699150625452</v>
       </c>
       <c r="Z8">
-        <v>0.5514871860018622</v>
+        <v>0.4921856703339795</v>
       </c>
       <c r="AA8">
-        <v>0.005604187934183429</v>
+        <v>0.004998699150625452</v>
       </c>
       <c r="AB8">
         <v>0.4652684128559521</v>
@@ -1810,7 +1804,7 @@
         <v>0.3347315871440479</v>
       </c>
       <c r="AE8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,22 +1816,22 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01016195494008179</v>
+        <v>0.01015612491772366</v>
       </c>
       <c r="AJ8">
-        <v>49203.13098691772</v>
+        <v>49231.37555421753</v>
       </c>
       <c r="AK8">
-        <v>36902.34824018829</v>
+        <v>36923.53166566315</v>
       </c>
       <c r="AL8">
-        <v>4105.315014505446</v>
+        <v>4105.315014505447</v>
       </c>
       <c r="AM8">
-        <v>369.0234824018829</v>
+        <v>369.2353166566315</v>
       </c>
       <c r="AN8">
-        <v>0.003690234824018829</v>
+        <v>0.003692353166566315</v>
       </c>
       <c r="AO8">
         <v>375</v>
@@ -1846,31 +1840,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1281194839938811</v>
+        <v>0.127528881617951</v>
       </c>
       <c r="AR8">
-        <v>0.0580494970510118</v>
+        <v>0.05674798598225635</v>
       </c>
       <c r="AS8">
-        <v>0.1378740427859807</v>
+        <v>0.137065787778261</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY8" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1878,7 +1872,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,67 +1887,67 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K9">
-        <v>0.6317203254759612</v>
+        <v>0.4909375551523664</v>
       </c>
       <c r="L9">
-        <v>2.158244697090097</v>
+        <v>2.024715989915113</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.9079300813689903</v>
+        <v>0.8727343887880916</v>
       </c>
       <c r="R9">
-        <v>7.69</v>
+        <v>7.7078</v>
       </c>
       <c r="S9">
-        <v>7.634521808826518</v>
+        <v>7.661650494909875</v>
       </c>
       <c r="T9">
-        <v>7.618897113873745</v>
+        <v>7.642192806918759</v>
       </c>
       <c r="U9">
-        <v>7.69</v>
+        <v>7.7078</v>
       </c>
       <c r="V9">
-        <v>7.622400000000001</v>
+        <v>7.657999999999999</v>
       </c>
       <c r="W9">
-        <v>7.634521808826518</v>
+        <v>7.661650494909875</v>
       </c>
       <c r="X9">
-        <v>7.7509</v>
+        <v>7.768699999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.007214329151298087</v>
+        <v>-0.00598737708426854</v>
       </c>
       <c r="Z9">
-        <v>0.9109719404512765</v>
+        <v>0.7577915449938494</v>
       </c>
       <c r="AA9">
-        <v>0.007214329151298087</v>
+        <v>0.00598737708426854</v>
       </c>
       <c r="AB9">
         <v>0.3991540470024339</v>
@@ -1965,7 +1959,7 @@
         <v>0.4008459529975662</v>
       </c>
       <c r="AE9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1974,58 +1968,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>453.9650406844952</v>
+        <v>436.3671943940458</v>
       </c>
       <c r="AI9">
-        <v>0.007919375812743759</v>
+        <v>0.007901087210358275</v>
       </c>
       <c r="AJ9">
-        <v>63136.28899835848</v>
+        <v>63282.4302134652</v>
       </c>
       <c r="AK9">
-        <v>57323.3360076157</v>
+        <v>55228.75305337361</v>
       </c>
       <c r="AL9">
-        <v>7454.269961978634</v>
+        <v>7165.306968703601</v>
       </c>
       <c r="AM9">
-        <v>573.2333600761569</v>
+        <v>552.2875305337361</v>
       </c>
       <c r="AN9">
-        <v>0.005732333600761569</v>
+        <v>0.005522875305337361</v>
       </c>
       <c r="AO9">
-        <v>453.9650406844951</v>
+        <v>436.3671943940458</v>
       </c>
       <c r="AP9">
-        <v>0.004539650406844951</v>
+        <v>0.004363671943940457</v>
       </c>
       <c r="AQ9">
-        <v>0.161085189550867</v>
+        <v>0.1607775114376505</v>
       </c>
       <c r="AR9">
-        <v>0.04235574752521119</v>
+        <v>0.03998387220664849</v>
       </c>
       <c r="AS9">
-        <v>0.06479048516709381</v>
+        <v>0.0687331662048644</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY9" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2033,7 +2027,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,67 +2042,67 @@
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.517345620394397</v>
+        <v>1.509101234576306</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q10">
         <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.765079999999999</v>
+        <v>6.771725</v>
       </c>
       <c r="S10">
-        <v>6.701191225012574</v>
+        <v>6.71388374939349</v>
       </c>
       <c r="T10">
-        <v>6.63569298014601</v>
+        <v>6.650641734262518</v>
       </c>
       <c r="U10">
-        <v>6.765079999999999</v>
+        <v>6.771725</v>
       </c>
       <c r="V10">
-        <v>6.746059999999999</v>
+        <v>6.75935</v>
       </c>
       <c r="W10">
-        <v>6.701191225012574</v>
+        <v>6.71388374939349</v>
       </c>
       <c r="X10">
-        <v>6.807672516658283</v>
+        <v>6.810285833737674</v>
       </c>
       <c r="Y10">
-        <v>-0.009443905317812315</v>
+        <v>-0.008541582921118396</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.009443905317812315</v>
+        <v>0.008541582921118396</v>
       </c>
       <c r="AB10">
         <v>0.441008328863268</v>
@@ -2120,7 +2114,7 @@
         <v>0.3589916711367321</v>
       </c>
       <c r="AE10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2132,22 +2126,22 @@
         <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.006295936878541544</v>
+        <v>0.00569438861407893</v>
       </c>
       <c r="AJ10">
-        <v>79416.298105553</v>
+        <v>87805.73892758024</v>
       </c>
       <c r="AK10">
-        <v>59562.22357916475</v>
+        <v>65854.30419568518</v>
       </c>
       <c r="AL10">
-        <v>8804.36352255476</v>
+        <v>9724.893464469567</v>
       </c>
       <c r="AM10">
-        <v>595.6222357916474</v>
+        <v>658.5430419568518</v>
       </c>
       <c r="AN10">
-        <v>0.005956222357916474</v>
+        <v>0.006585430419568518</v>
       </c>
       <c r="AO10">
         <v>375</v>
@@ -2156,31 +2150,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.0823400346706033</v>
+        <v>0.08101466956292436</v>
       </c>
       <c r="AR10">
-        <v>0.01239582451374733</v>
+        <v>0.01116238358085309</v>
       </c>
       <c r="AS10">
-        <v>0.03082934280351164</v>
+        <v>0.031342469828863</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY10" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2188,7 +2182,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2200,70 +2194,70 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.67225064054127</v>
+        <v>1.777723893238875</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4065.63</v>
+        <v>4018.51</v>
       </c>
       <c r="S11">
-        <v>4006.60665761875</v>
+        <v>3931.926781600814</v>
       </c>
       <c r="T11">
-        <v>4023.333057983934</v>
+        <v>3952.754554199324</v>
       </c>
       <c r="U11">
-        <v>4065.63</v>
+        <v>4018.51</v>
       </c>
       <c r="V11">
-        <v>3955.56</v>
+        <v>3861.320000000001</v>
       </c>
       <c r="W11">
-        <v>4006.60665761875</v>
+        <v>3931.926781600814</v>
       </c>
       <c r="X11">
-        <v>4195.495</v>
+        <v>4148.375</v>
       </c>
       <c r="Y11">
-        <v>-0.01451763745870866</v>
+        <v>-0.02154610002194497</v>
       </c>
       <c r="Z11">
-        <v>0.4544976889943382</v>
+        <v>0.6667171169998548</v>
       </c>
       <c r="AA11">
-        <v>0.01451763745870866</v>
+        <v>0.02154610002194497</v>
       </c>
       <c r="AB11">
         <v>0.4283805170135917</v>
@@ -2275,7 +2269,7 @@
         <v>0.3716194829864083</v>
       </c>
       <c r="AE11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2287,22 +2281,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03194215902578441</v>
+        <v>0.03231670445015687</v>
       </c>
       <c r="AJ11">
-        <v>15653.29380510532</v>
+        <v>15471.87463904826</v>
       </c>
       <c r="AK11">
-        <v>11739.97035382899</v>
+        <v>11603.90597928619</v>
       </c>
       <c r="AL11">
         <v>2.887614060755402</v>
       </c>
       <c r="AM11">
-        <v>117.3997035382899</v>
+        <v>116.0390597928619</v>
       </c>
       <c r="AN11">
-        <v>0.001173997035382899</v>
+        <v>0.001160390597928619</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2311,31 +2305,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>370.3792360780287</v>
+        <v>350.326371947099</v>
       </c>
       <c r="AR11">
-        <v>98.66483913672732</v>
+        <v>100.781622999516</v>
       </c>
       <c r="AS11">
-        <v>195.0715376148925</v>
+        <v>183.0665714465729</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04205316226800889</v>
+        <v>0.03706765707980825</v>
       </c>
       <c r="AV11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AW11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AY11" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="88">
   <si>
     <t>Pair</t>
   </si>
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -229,52 +229,43 @@
     <t>UP</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
-  </si>
-  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>REDUCE_CONFLICT</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.06409,naive=0.0112,drift4=0.01883; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1162,naive=0.06618,drift4=0.1241; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.03308,naive=0.01219,drift4=0.01972; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=6.866,naive=1.765,drift4=1.759; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.02649,naive=0.01164,drift4=0.02107; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.05677,naive=0.01826,drift4=0.03383; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2145,naive=0.11,drift4=0.1936; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3138,naive=0.06927,drift4=0.09777; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1004,naive=0.02126,drift4=0.05157; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=534,naive=179.8,drift4=279.8; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.02089,naive=0.009614,drift4=0.02377; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.0231,naive=0.01023,drift4=0.02062; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=7.765,naive=1.788,drift4=1.686; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05309,naive=0.01801,drift4=0.03687; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.08179,naive=0.05147,drift4=0.1393; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.06614,naive=0.008875,drift4=0.0198; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2097,naive=0.1108,drift4=0.2034; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1099,naive=0.02165,drift4=0.04977; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3098,naive=0.06055,drift4=0.0968; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=385.8,naive=136.6,drift4=283.5; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -829,7 +820,7 @@
         <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
         <v>69</v>
@@ -838,58 +829,58 @@
         <v>46231</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>2.229848045867981</v>
+        <v>0.650343444575059</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.138385</v>
+        <v>0.697225</v>
       </c>
       <c r="S2">
-        <v>1.139620716129513</v>
+        <v>0.6968724729802317</v>
       </c>
       <c r="T2">
-        <v>1.146459641062795</v>
+        <v>0.6944064107302118</v>
       </c>
       <c r="U2">
-        <v>1.138385</v>
+        <v>0.697225</v>
       </c>
       <c r="V2">
-        <v>1.13327</v>
+        <v>0.70045</v>
       </c>
       <c r="Y2">
-        <v>0.001085499307802436</v>
+        <v>-0.0005056144282954419</v>
       </c>
       <c r="AA2">
-        <v>0.001085499307802436</v>
+        <v>0.0005056144282954419</v>
       </c>
       <c r="AB2">
-        <v>0.4039318510752031</v>
+        <v>0.4852293709680197</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.396068148924797</v>
+        <v>0.3147706290319803</v>
       </c>
       <c r="AE2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -922,28 +913,28 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03429148452102111</v>
+        <v>0.01330904581758576</v>
       </c>
       <c r="AR2">
-        <v>0.005808073985073037</v>
+        <v>0.003541404853203574</v>
       </c>
       <c r="AS2">
-        <v>0.01167334852651093</v>
+        <v>0.01101439379419384</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AY2" s="2">
         <v>46260</v>
@@ -966,73 +957,82 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
         <v>46231</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>0.5921660548914897</v>
+        <v>2.744246931337766</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>4.72079</v>
+        <v>0.8197099999999999</v>
       </c>
       <c r="S3">
-        <v>4.725396004536346</v>
+        <v>0.8261288545914537</v>
       </c>
       <c r="T3">
-        <v>4.721918289426771</v>
+        <v>0.8217445155246574</v>
       </c>
       <c r="U3">
-        <v>4.72079</v>
+        <v>0.8197099999999999</v>
       </c>
       <c r="V3">
-        <v>4.73341</v>
+        <v>0.8361199999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.8261288545914537</v>
+      </c>
+      <c r="X3">
+        <v>0.8113349999999999</v>
       </c>
       <c r="Y3">
-        <v>0.0009756851154883605</v>
+        <v>0.007830640825967414</v>
+      </c>
+      <c r="Z3">
+        <v>0.7664303989795476</v>
       </c>
       <c r="AA3">
-        <v>0.0009756851154883605</v>
+        <v>0.007830640825967414</v>
       </c>
       <c r="AB3">
-        <v>0.4777352708867221</v>
+        <v>0.4667074295864012</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.322264729113278</v>
+        <v>0.3332925704135988</v>
       </c>
       <c r="AE3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1041,52 +1041,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI3">
+        <v>0.01021702797330769</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>48937.91044776091</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>48937.91044776091</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>59701.49253731309</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>489.3791044776091</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.004893791044776091</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.07689499151171393</v>
+        <v>0.01384096809741641</v>
       </c>
       <c r="AR3">
-        <v>0.02922396999107149</v>
+        <v>0.005414667434928152</v>
       </c>
       <c r="AS3">
-        <v>0.07322722909943137</v>
+        <v>0.009004862801618415</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AX3" t="s">
         <v>87</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>89</v>
       </c>
       <c r="AY3" s="2">
         <v>46260</v>
@@ -1127,64 +1130,64 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.744246931337766</v>
+        <v>3.990078193416717</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4">
-        <v>0.8197099999999999</v>
+        <v>163.876</v>
       </c>
       <c r="S4">
-        <v>0.8305939770959434</v>
+        <v>164.5698850396152</v>
       </c>
       <c r="T4">
-        <v>0.8309841908790948</v>
+        <v>162.8216138619726</v>
       </c>
       <c r="U4">
-        <v>0.8197099999999999</v>
+        <v>163.876</v>
       </c>
       <c r="V4">
-        <v>0.8361199999999999</v>
+        <v>166.382</v>
       </c>
       <c r="W4">
-        <v>0.8305939770959434</v>
+        <v>164.5698850396152</v>
       </c>
       <c r="X4">
-        <v>0.8113349999999999</v>
+        <v>162.274</v>
       </c>
       <c r="Y4">
-        <v>0.01327783862090674</v>
+        <v>0.004234207813317537</v>
       </c>
       <c r="Z4">
-        <v>1.29957935473951</v>
+        <v>0.4331367288484577</v>
       </c>
       <c r="AA4">
-        <v>0.01327783862090674</v>
+        <v>0.004234207813317537</v>
       </c>
       <c r="AB4">
-        <v>0.4369365860818993</v>
+        <v>0.3681946029345791</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3630634139181007</v>
+        <v>0.4318053970654209</v>
       </c>
       <c r="AE4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1196,22 +1199,22 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.01021702797330769</v>
+        <v>0.00977568405379671</v>
       </c>
       <c r="AJ4">
-        <v>48937.91044776091</v>
+        <v>51147.31585518135</v>
       </c>
       <c r="AK4">
-        <v>48937.91044776091</v>
+        <v>51147.31585518135</v>
       </c>
       <c r="AL4">
-        <v>59701.49253731309</v>
+        <v>312.1098626716624</v>
       </c>
       <c r="AM4">
-        <v>489.3791044776091</v>
+        <v>511.4731585518135</v>
       </c>
       <c r="AN4">
-        <v>0.004893791044776091</v>
+        <v>0.005114731585518136</v>
       </c>
       <c r="AO4">
         <v>500</v>
@@ -1220,28 +1223,28 @@
         <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.02195212107845924</v>
+        <v>4.478746127092077</v>
       </c>
       <c r="AR4">
-        <v>0.007579817798880702</v>
+        <v>0.8160126957203453</v>
       </c>
       <c r="AS4">
-        <v>0.01084228149189176</v>
+        <v>0.9387081756962979</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW4" t="s">
         <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY4" s="2">
         <v>46260</v>
@@ -1264,82 +1267,82 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
         <v>46231</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>3.990078193416717</v>
+        <v>0.5577364673232961</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>163.876</v>
+        <v>1.3286</v>
       </c>
       <c r="S5">
-        <v>164.7767066864221</v>
+        <v>1.327198765156653</v>
       </c>
       <c r="T5">
-        <v>163.4549120076157</v>
+        <v>1.330510266285098</v>
       </c>
       <c r="U5">
-        <v>163.876</v>
+        <v>1.3286</v>
       </c>
       <c r="V5">
-        <v>166.382</v>
+        <v>1.3221</v>
       </c>
       <c r="W5">
-        <v>164.7767066864221</v>
+        <v>1.3266071</v>
       </c>
       <c r="X5">
-        <v>162.274</v>
+        <v>1.340525</v>
       </c>
       <c r="Y5">
-        <v>0.005496269657680618</v>
+        <v>-0.001054670211762322</v>
       </c>
       <c r="Z5">
-        <v>0.5622388804132802</v>
+        <v>0.1671194968553457</v>
       </c>
       <c r="AA5">
-        <v>0.005496269657680618</v>
+        <v>0.001054670211762322</v>
       </c>
       <c r="AB5">
-        <v>0.3771985387697701</v>
+        <v>0.4516819120678047</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4228014612302299</v>
+        <v>0.3483180879321953</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1348,55 +1351,55 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.00977568405379671</v>
+        <v>0.008975613427668236</v>
       </c>
       <c r="AJ5">
-        <v>51147.31585518135</v>
+        <v>55706.49895178188</v>
       </c>
       <c r="AK5">
-        <v>51147.31585518135</v>
+        <v>41779.87421383641</v>
       </c>
       <c r="AL5">
-        <v>312.1098626716624</v>
+        <v>31446.54088050309</v>
       </c>
       <c r="AM5">
-        <v>511.4731585518135</v>
+        <v>417.7987421383641</v>
       </c>
       <c r="AN5">
-        <v>0.005114731585518136</v>
+        <v>0.004177987421383641</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>4.701049774548353</v>
+        <v>0.02646200766391234</v>
       </c>
       <c r="AR5">
-        <v>1.07824629880137</v>
+        <v>0.007620212408046843</v>
       </c>
       <c r="AS5">
-        <v>1.206300865993987</v>
+        <v>0.01849042754036804</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY5" s="2">
         <v>46260</v>
@@ -1422,10 +1425,10 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
@@ -1437,64 +1440,64 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.650343444575059</v>
+        <v>0.5921660548914897</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>0.697225</v>
+        <v>4.72079</v>
       </c>
       <c r="S6">
-        <v>0.6988185905988538</v>
+        <v>4.713783111856818</v>
       </c>
       <c r="T6">
-        <v>0.6982932291033901</v>
+        <v>4.700044136299765</v>
       </c>
       <c r="U6">
-        <v>0.697225</v>
+        <v>4.72079</v>
       </c>
       <c r="V6">
-        <v>0.70045</v>
+        <v>4.73341</v>
       </c>
       <c r="W6">
-        <v>0.6988185905988538</v>
+        <v>4.713708815</v>
       </c>
       <c r="X6">
-        <v>0.6895249999999999</v>
+        <v>4.7556375</v>
       </c>
       <c r="Y6">
-        <v>0.002285618844496078</v>
+        <v>-0.001484261774656728</v>
       </c>
       <c r="Z6">
-        <v>0.2069598180329563</v>
+        <v>0.2032049644881273</v>
       </c>
       <c r="AA6">
-        <v>0.002285618844496078</v>
+        <v>0.001484261774656728</v>
       </c>
       <c r="AB6">
-        <v>0.4573547439353595</v>
+        <v>0.512586405580199</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3426452560646405</v>
+        <v>0.2874135944198011</v>
       </c>
       <c r="AE6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1503,55 +1506,55 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01104378070206901</v>
+        <v>0.007381709417279718</v>
       </c>
       <c r="AJ6">
-        <v>45274.35064935025</v>
+        <v>67734.98816270911</v>
       </c>
       <c r="AK6">
-        <v>45274.35064935025</v>
+        <v>50801.24112203183</v>
       </c>
       <c r="AL6">
-        <v>64935.06493506437</v>
+        <v>10761.17368534331</v>
       </c>
       <c r="AM6">
-        <v>452.7435064935025</v>
+        <v>508.0124112203183</v>
       </c>
       <c r="AN6">
-        <v>0.004527435064935025</v>
+        <v>0.005080124112203183</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ6">
-        <v>0.01798890136541919</v>
+        <v>0.05292515803974524</v>
       </c>
       <c r="AR6">
-        <v>0.005187602927600872</v>
+        <v>0.01738119786205442</v>
       </c>
       <c r="AS6">
-        <v>0.01305718737096484</v>
+        <v>0.05939798223802774</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY6" s="2">
         <v>46260</v>
@@ -1574,13 +1577,13 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
         <v>69</v>
@@ -1589,67 +1592,67 @@
         <v>46231</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0.5577364673232961</v>
+        <v>2.229848045867981</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1.3286</v>
+        <v>1.138385</v>
       </c>
       <c r="S7">
-        <v>1.33142218384049</v>
+        <v>1.136136195394441</v>
       </c>
       <c r="T7">
-        <v>1.340313245291399</v>
+        <v>1.137690792442758</v>
       </c>
       <c r="U7">
-        <v>1.3286</v>
+        <v>1.138385</v>
       </c>
       <c r="V7">
-        <v>1.3221</v>
+        <v>1.13327</v>
       </c>
       <c r="W7">
-        <v>1.33142218384049</v>
+        <v>1.136136195394441</v>
       </c>
       <c r="X7">
-        <v>1.316675</v>
+        <v>1.14806</v>
       </c>
       <c r="Y7">
-        <v>0.002124178714804757</v>
+        <v>-0.001975434150625068</v>
       </c>
       <c r="Z7">
-        <v>0.2366611186993372</v>
+        <v>0.2324345845539336</v>
       </c>
       <c r="AA7">
-        <v>0.002124178714804757</v>
+        <v>0.001975434150625068</v>
       </c>
       <c r="AB7">
-        <v>0.4404587821741963</v>
+        <v>0.4169377817002493</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3595412178258037</v>
+        <v>0.3830622182997508</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1661,22 +1664,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008975613427668236</v>
+        <v>0.008498882188363378</v>
       </c>
       <c r="AJ7">
-        <v>55706.49895178188</v>
+        <v>58831.26614987053</v>
       </c>
       <c r="AK7">
-        <v>55706.49895178188</v>
+        <v>58831.26614987053</v>
       </c>
       <c r="AL7">
-        <v>41928.72117400412</v>
+        <v>51679.58656330726</v>
       </c>
       <c r="AM7">
-        <v>557.0649895178188</v>
+        <v>588.3126614987053</v>
       </c>
       <c r="AN7">
-        <v>0.005570649895178188</v>
+        <v>0.005883126614987053</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1685,28 +1688,28 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.03266911923915516</v>
+        <v>0.02986735863666825</v>
       </c>
       <c r="AR7">
-        <v>0.008948852626565829</v>
+        <v>0.003803203169038076</v>
       </c>
       <c r="AS7">
-        <v>0.02235570907751056</v>
+        <v>0.00871865385343152</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY7" s="2">
         <v>46260</v>
@@ -1756,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q8">
         <v>0.75</v>
@@ -1768,10 +1771,10 @@
         <v>8.99408</v>
       </c>
       <c r="S8">
-        <v>8.949121299943343</v>
+        <v>8.963750763619577</v>
       </c>
       <c r="T8">
-        <v>8.943041161507667</v>
+        <v>8.973969062407297</v>
       </c>
       <c r="U8">
         <v>8.99408</v>
@@ -1780,31 +1783,31 @@
         <v>8.930710000000001</v>
       </c>
       <c r="W8">
-        <v>8.949121299943343</v>
+        <v>8.963750763619577</v>
       </c>
       <c r="X8">
         <v>9.085425000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.004998699150625452</v>
+        <v>-0.003372133267707519</v>
       </c>
       <c r="Z8">
-        <v>0.4921856703339795</v>
+        <v>0.3320295186427592</v>
       </c>
       <c r="AA8">
-        <v>0.004998699150625452</v>
+        <v>0.003372133267707519</v>
       </c>
       <c r="AB8">
-        <v>0.4652684128559521</v>
+        <v>0.4708091781513171</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3347315871440479</v>
+        <v>0.3291908218486829</v>
       </c>
       <c r="AE8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1840,28 +1843,28 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.127528881617951</v>
+        <v>0.1111450723883654</v>
       </c>
       <c r="AR8">
-        <v>0.05674798598225635</v>
+        <v>0.04932233769722467</v>
       </c>
       <c r="AS8">
-        <v>0.137065787778261</v>
+        <v>0.1099223072541505</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW8" t="s">
         <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY8" s="2">
         <v>46260</v>
@@ -1884,7 +1887,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1899,67 +1902,67 @@
         <v>46231</v>
       </c>
       <c r="K9">
-        <v>0.4909375551523664</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.024715989915113</v>
+        <v>1.509101234576306</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q9">
-        <v>0.8727343887880916</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>7.7078</v>
+        <v>6.771725</v>
       </c>
       <c r="S9">
-        <v>7.661650494909875</v>
+        <v>6.722106772273616</v>
       </c>
       <c r="T9">
-        <v>7.642192806918759</v>
+        <v>6.667764095847414</v>
       </c>
       <c r="U9">
-        <v>7.7078</v>
+        <v>6.771725</v>
       </c>
       <c r="V9">
-        <v>7.657999999999999</v>
+        <v>6.75935</v>
       </c>
       <c r="W9">
-        <v>7.661650494909875</v>
+        <v>6.722106772273616</v>
       </c>
       <c r="X9">
-        <v>7.768699999999999</v>
+        <v>6.804803818484256</v>
       </c>
       <c r="Y9">
-        <v>-0.00598737708426854</v>
+        <v>-0.0073272656119946</v>
       </c>
       <c r="Z9">
-        <v>0.7577915449938494</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>0.00598737708426854</v>
+        <v>0.0073272656119946</v>
       </c>
       <c r="AB9">
-        <v>0.3991540470024339</v>
+        <v>0.4336718416865972</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4008459529975662</v>
+        <v>0.3663281583134028</v>
       </c>
       <c r="AE9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1968,55 +1971,55 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>436.3671943940458</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.007901087210358275</v>
+        <v>0.004884843741329734</v>
       </c>
       <c r="AJ9">
-        <v>63282.4302134652</v>
+        <v>102357.419495243</v>
       </c>
       <c r="AK9">
-        <v>55228.75305337361</v>
+        <v>76768.06462143228</v>
       </c>
       <c r="AL9">
-        <v>7165.306968703601</v>
+        <v>11336.55968330555</v>
       </c>
       <c r="AM9">
-        <v>552.2875305337361</v>
+        <v>767.6806462143228</v>
       </c>
       <c r="AN9">
-        <v>0.005522875305337361</v>
+        <v>0.007676806462143228</v>
       </c>
       <c r="AO9">
-        <v>436.3671943940458</v>
+        <v>375</v>
       </c>
       <c r="AP9">
-        <v>0.004363671943940457</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.1607775114376505</v>
+        <v>0.07438053045563454</v>
       </c>
       <c r="AR9">
-        <v>0.03998387220664849</v>
+        <v>0.008621618107857399</v>
       </c>
       <c r="AS9">
-        <v>0.0687331662048644</v>
+        <v>0.02392010291959705</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW9" t="s">
         <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY9" s="2">
         <v>46260</v>
@@ -2054,67 +2057,67 @@
         <v>46231</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.4909375551523664</v>
       </c>
       <c r="L10">
-        <v>1.509101234576306</v>
+        <v>2.024715989915113</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.8727343887880916</v>
       </c>
       <c r="R10">
-        <v>6.771725</v>
+        <v>7.7078</v>
       </c>
       <c r="S10">
-        <v>6.71388374939349</v>
+        <v>7.639586468932697</v>
       </c>
       <c r="T10">
-        <v>6.650641734262518</v>
+        <v>7.587811870346156</v>
       </c>
       <c r="U10">
-        <v>6.771725</v>
+        <v>7.7078</v>
       </c>
       <c r="V10">
-        <v>6.75935</v>
+        <v>7.657999999999999</v>
       </c>
       <c r="W10">
-        <v>6.71388374939349</v>
+        <v>7.639586468932697</v>
       </c>
       <c r="X10">
-        <v>6.810285833737674</v>
+        <v>7.768699999999999</v>
       </c>
       <c r="Y10">
-        <v>-0.008541582921118396</v>
+        <v>-0.008849935269117402</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>1.120090822123213</v>
       </c>
       <c r="AA10">
-        <v>0.008541582921118396</v>
+        <v>0.008849935269117402</v>
       </c>
       <c r="AB10">
-        <v>0.441008328863268</v>
+        <v>0.4042497101324258</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3589916711367321</v>
+        <v>0.3957502898675742</v>
       </c>
       <c r="AE10" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2123,55 +2126,55 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>436.3671943940458</v>
       </c>
       <c r="AI10">
-        <v>0.00569438861407893</v>
+        <v>0.007901087210358275</v>
       </c>
       <c r="AJ10">
-        <v>87805.73892758024</v>
+        <v>63282.4302134652</v>
       </c>
       <c r="AK10">
-        <v>65854.30419568518</v>
+        <v>55228.75305337361</v>
       </c>
       <c r="AL10">
-        <v>9724.893464469567</v>
+        <v>7165.306968703601</v>
       </c>
       <c r="AM10">
-        <v>658.5430419568518</v>
+        <v>552.2875305337361</v>
       </c>
       <c r="AN10">
-        <v>0.006585430419568518</v>
+        <v>0.005522875305337361</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>436.3671943940458</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.004363671943940457</v>
       </c>
       <c r="AQ10">
-        <v>0.08101466956292436</v>
+        <v>0.1302012529690851</v>
       </c>
       <c r="AR10">
-        <v>0.01116238358085309</v>
+        <v>0.02813157518684083</v>
       </c>
       <c r="AS10">
-        <v>0.031342469828863</v>
+        <v>0.05020827767135409</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW10" t="s">
         <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY10" s="2">
         <v>46260</v>
@@ -2221,10 +2224,10 @@
         <v>103</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
@@ -2233,10 +2236,10 @@
         <v>4018.51</v>
       </c>
       <c r="S11">
-        <v>3931.926781600814</v>
+        <v>3928.405586607313</v>
       </c>
       <c r="T11">
-        <v>3952.754554199324</v>
+        <v>3939.61710940436</v>
       </c>
       <c r="U11">
         <v>4018.51</v>
@@ -2245,31 +2248,31 @@
         <v>3861.320000000001</v>
       </c>
       <c r="W11">
-        <v>3931.926781600814</v>
+        <v>3928.405586607313</v>
       </c>
       <c r="X11">
         <v>4148.375</v>
       </c>
       <c r="Y11">
-        <v>-0.02154610002194497</v>
+        <v>-0.02242234395153604</v>
       </c>
       <c r="Z11">
-        <v>0.6667171169998548</v>
+        <v>0.693831389463575</v>
       </c>
       <c r="AA11">
-        <v>0.02154610002194497</v>
+        <v>0.02242234395153604</v>
       </c>
       <c r="AB11">
-        <v>0.4283805170135917</v>
+        <v>0.4552861130953555</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3716194829864083</v>
+        <v>0.3447138869046446</v>
       </c>
       <c r="AE11" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2305,28 +2308,28 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>350.326371947099</v>
+        <v>296.1922221126541</v>
       </c>
       <c r="AR11">
-        <v>100.781622999516</v>
+        <v>60.91350680697661</v>
       </c>
       <c r="AS11">
-        <v>183.0665714465729</v>
+        <v>147.7330148679231</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03706765707980825</v>
+        <v>0.04320218631084363</v>
       </c>
       <c r="AV11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AW11" t="s">
         <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AY11" s="2">
         <v>46260</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,33 +169,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -211,9 +211,6 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -229,43 +226,52 @@
     <t>UP</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>BLOCK_STRONG_CONFLICT</t>
+  </si>
+  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.02089,naive=0.009614,drift4=0.02377; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.0231,naive=0.01023,drift4=0.02062; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=7.765,naive=1.788,drift4=1.686; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05309,naive=0.01801,drift4=0.03687; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.08179,naive=0.05147,drift4=0.1393; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.06614,naive=0.008875,drift4=0.0198; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2097,naive=0.1108,drift4=0.2034; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1099,naive=0.02165,drift4=0.04977; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3098,naive=0.06055,drift4=0.0968; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=385.8,naive=136.6,drift4=283.5; naive_cap_applied</t>
+    <t>REDUCE_CONFLICT</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.06529,naive=0.009961,drift4=0.01927; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.02457,naive=0.01063,drift4=0.02213; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.1029,naive=0.05916,drift4=0.1309; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2107,naive=0.109,drift4=0.1994; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02989,naive=0.01067,drift4=0.01974; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05516,naive=0.01789,drift4=0.03534; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=7.249,naive=1.753,drift4=1.756; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3066,naive=0.06415,drift4=0.09864; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1053,naive=0.02133,drift4=0.04922; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=454.8,naive=152.9,drift4=279.3; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -802,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -817,31 +823,31 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.7433162552396745</v>
       </c>
       <c r="L2">
-        <v>0.650343444575059</v>
+        <v>1.50386669438296</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
         <v>72</v>
@@ -850,37 +856,37 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0.697225</v>
+        <v>1.145695</v>
       </c>
       <c r="S2">
-        <v>0.6968724729802317</v>
+        <v>1.149710226291426</v>
       </c>
       <c r="T2">
-        <v>0.6944064107302118</v>
+        <v>1.153398470590829</v>
       </c>
       <c r="U2">
-        <v>0.697225</v>
+        <v>1.145695</v>
       </c>
       <c r="V2">
-        <v>0.70045</v>
+        <v>1.14789</v>
       </c>
       <c r="Y2">
-        <v>-0.0005056144282954419</v>
+        <v>0.003504620593985049</v>
       </c>
       <c r="AA2">
-        <v>0.0005056144282954419</v>
+        <v>0.003504620593985049</v>
       </c>
       <c r="AB2">
-        <v>0.4852293709680197</v>
+        <v>0.4101367619511154</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3147706290319803</v>
+        <v>0.3898632380488847</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -913,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01330904581758576</v>
+        <v>0.03563344242463792</v>
       </c>
       <c r="AR2">
-        <v>0.003541404853203574</v>
+        <v>0.005451556598451002</v>
       </c>
       <c r="AS2">
-        <v>0.01101439379419384</v>
+        <v>0.01150498468291821</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AX2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -945,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -957,82 +963,73 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J3" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.744246931337766</v>
+        <v>0.8276575547104769</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
         <v>73</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>0.8197099999999999</v>
+        <v>0.695295</v>
       </c>
       <c r="S3">
-        <v>0.8261288545914537</v>
+        <v>0.6958396126752528</v>
       </c>
       <c r="T3">
-        <v>0.8217445155246574</v>
+        <v>0.6955396310248338</v>
       </c>
       <c r="U3">
-        <v>0.8197099999999999</v>
+        <v>0.695295</v>
       </c>
       <c r="V3">
-        <v>0.8361199999999999</v>
-      </c>
-      <c r="W3">
-        <v>0.8261288545914537</v>
-      </c>
-      <c r="X3">
-        <v>0.8113349999999999</v>
+        <v>0.69659</v>
       </c>
       <c r="Y3">
-        <v>0.007830640825967414</v>
-      </c>
-      <c r="Z3">
-        <v>0.7664303989795476</v>
+        <v>0.0007832828874835192</v>
       </c>
       <c r="AA3">
-        <v>0.007830640825967414</v>
+        <v>0.0007832828874835192</v>
       </c>
       <c r="AB3">
-        <v>0.4667074295864012</v>
+        <v>0.4678235328394243</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3332925704135988</v>
+        <v>0.3321764671605756</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1041,58 +1038,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.01021702797330769</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>48937.91044776091</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>48937.91044776091</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>59701.49253731309</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>489.3791044776091</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.004893791044776091</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.01384096809741641</v>
+        <v>0.01558731385190217</v>
       </c>
       <c r="AR3">
-        <v>0.005414667434928152</v>
+        <v>0.004691670301962474</v>
       </c>
       <c r="AS3">
-        <v>0.009004862801618415</v>
+        <v>0.0125607870297175</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AX3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1100,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1112,82 +1106,73 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>3.990078193416717</v>
+        <v>0.6632591236562488</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P4" t="s">
         <v>73</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>163.876</v>
+        <v>4.70125</v>
       </c>
       <c r="S4">
-        <v>164.5698850396152</v>
+        <v>4.698277272336779</v>
       </c>
       <c r="T4">
-        <v>162.8216138619726</v>
+        <v>4.6995446142246</v>
       </c>
       <c r="U4">
-        <v>163.876</v>
+        <v>4.70125</v>
       </c>
       <c r="V4">
-        <v>166.382</v>
-      </c>
-      <c r="W4">
-        <v>164.5698850396152</v>
-      </c>
-      <c r="X4">
-        <v>162.274</v>
+        <v>4.69433</v>
       </c>
       <c r="Y4">
-        <v>0.004234207813317537</v>
-      </c>
-      <c r="Z4">
-        <v>0.4331367288484577</v>
+        <v>-0.0006323270753993059</v>
       </c>
       <c r="AA4">
-        <v>0.004234207813317537</v>
+        <v>0.0006323270753993059</v>
       </c>
       <c r="AB4">
-        <v>0.3681946029345791</v>
+        <v>0.4915555065773776</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4318053970654209</v>
+        <v>0.3084444934226225</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1196,58 +1181,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
-      </c>
-      <c r="AI4">
-        <v>0.00977568405379671</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>51147.31585518135</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>51147.31585518135</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>312.1098626716624</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>511.4731585518135</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.005114731585518136</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>4.478746127092077</v>
+        <v>0.06618614085935499</v>
       </c>
       <c r="AR4">
-        <v>0.8160126957203453</v>
+        <v>0.0269174720769299</v>
       </c>
       <c r="AS4">
-        <v>0.9387081756962979</v>
+        <v>0.07009747241415941</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AX4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY4" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1255,7 +1237,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1270,79 +1252,70 @@
         <v>63</v>
       </c>
       <c r="G5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I5" t="s">
         <v>68</v>
       </c>
-      <c r="H5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I5" t="s">
-        <v>69</v>
-      </c>
       <c r="J5" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.5577364673232961</v>
+        <v>0.4792599117402066</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P5" t="s">
         <v>73</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.3286</v>
+        <v>9.03811</v>
       </c>
       <c r="S5">
-        <v>1.327198765156653</v>
+        <v>9.029781068240107</v>
       </c>
       <c r="T5">
-        <v>1.330510266285098</v>
+        <v>9.033997868838341</v>
       </c>
       <c r="U5">
-        <v>1.3286</v>
+        <v>9.03811</v>
       </c>
       <c r="V5">
-        <v>1.3221</v>
-      </c>
-      <c r="W5">
-        <v>1.3266071</v>
-      </c>
-      <c r="X5">
-        <v>1.340525</v>
+        <v>9.01877</v>
       </c>
       <c r="Y5">
-        <v>-0.001054670211762322</v>
-      </c>
-      <c r="Z5">
-        <v>0.1671194968553457</v>
+        <v>-0.0009215346748261429</v>
       </c>
       <c r="AA5">
-        <v>0.001054670211762322</v>
+        <v>0.0009215346748261429</v>
       </c>
       <c r="AB5">
-        <v>0.4516819120678047</v>
+        <v>0.469078655453103</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3483180879321953</v>
+        <v>0.3309213445468971</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1351,58 +1324,55 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
-      </c>
-      <c r="AI5">
-        <v>0.008975613427668236</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>55706.49895178188</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>41779.87421383641</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>31446.54088050309</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>417.7987421383641</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.004177987421383641</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>0.02646200766391234</v>
+        <v>0.1203477534295891</v>
       </c>
       <c r="AR5">
-        <v>0.007620212408046843</v>
+        <v>0.04945355180574008</v>
       </c>
       <c r="AS5">
-        <v>0.01849042754036804</v>
+        <v>0.1192958788948709</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AW5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AX5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY5" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1410,7 +1380,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1422,82 +1392,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0.5921660548914897</v>
+        <v>2.371049492894731</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>4.72079</v>
+        <v>0.81491</v>
       </c>
       <c r="S6">
-        <v>4.713783111856818</v>
+        <v>0.8233600982040008</v>
       </c>
       <c r="T6">
-        <v>4.700044136299765</v>
+        <v>0.8246426865834584</v>
       </c>
       <c r="U6">
-        <v>4.72079</v>
+        <v>0.81491</v>
       </c>
       <c r="V6">
-        <v>4.73341</v>
+        <v>0.82652</v>
       </c>
       <c r="W6">
-        <v>4.713708815</v>
+        <v>0.8233600982040008</v>
       </c>
       <c r="X6">
-        <v>4.7556375</v>
+        <v>0.806535</v>
       </c>
       <c r="Y6">
-        <v>-0.001484261774656728</v>
+        <v>0.01036936373832789</v>
       </c>
       <c r="Z6">
-        <v>0.2032049644881273</v>
+        <v>1.00896694973143</v>
       </c>
       <c r="AA6">
-        <v>0.001484261774656728</v>
+        <v>0.01036936373832789</v>
       </c>
       <c r="AB6">
-        <v>0.512586405580199</v>
+        <v>0.4463302656958154</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.2874135944198011</v>
+        <v>0.3536697343041846</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1506,58 +1476,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.007381709417279718</v>
+        <v>0.01027720852609497</v>
       </c>
       <c r="AJ6">
-        <v>67734.98816270911</v>
+        <v>48651.34328358181</v>
       </c>
       <c r="AK6">
-        <v>50801.24112203183</v>
+        <v>48651.34328358181</v>
       </c>
       <c r="AL6">
-        <v>10761.17368534331</v>
+        <v>59701.49253731309</v>
       </c>
       <c r="AM6">
-        <v>508.0124112203183</v>
+        <v>486.5134328358181</v>
       </c>
       <c r="AN6">
-        <v>0.005080124112203183</v>
+        <v>0.004865134328358181</v>
       </c>
       <c r="AO6">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.05292515803974524</v>
+        <v>0.01831786488098754</v>
       </c>
       <c r="AR6">
-        <v>0.01738119786205442</v>
+        <v>0.005433831140914195</v>
       </c>
       <c r="AS6">
-        <v>0.05939798223802774</v>
+        <v>0.01047754010096085</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1565,7 +1535,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1577,82 +1547,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" t="s">
         <v>68</v>
       </c>
-      <c r="H7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" t="s">
-        <v>69</v>
-      </c>
       <c r="J7" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2.229848045867981</v>
+        <v>0.4014999642724688</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1.138385</v>
+        <v>1.335485</v>
       </c>
       <c r="S7">
-        <v>1.136136195394441</v>
+        <v>1.343388652074018</v>
       </c>
       <c r="T7">
-        <v>1.137690792442758</v>
+        <v>1.35289195089401</v>
       </c>
       <c r="U7">
-        <v>1.138385</v>
+        <v>1.335485</v>
       </c>
       <c r="V7">
-        <v>1.13327</v>
+        <v>1.33587</v>
       </c>
       <c r="W7">
-        <v>1.136136195394441</v>
+        <v>1.343388652074018</v>
       </c>
       <c r="X7">
-        <v>1.14806</v>
+        <v>1.32356</v>
       </c>
       <c r="Y7">
-        <v>-0.001975434150625068</v>
+        <v>0.00591818857869438</v>
       </c>
       <c r="Z7">
-        <v>0.2324345845539336</v>
+        <v>0.6627800481356522</v>
       </c>
       <c r="AA7">
-        <v>0.001975434150625068</v>
+        <v>0.00591818857869438</v>
       </c>
       <c r="AB7">
-        <v>0.4169377817002493</v>
+        <v>0.446226882060304</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3830622182997508</v>
+        <v>0.3537731179396961</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1664,22 +1634,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008498882188363378</v>
+        <v>0.008929340277127799</v>
       </c>
       <c r="AJ7">
-        <v>58831.26614987053</v>
+        <v>55995.1781970649</v>
       </c>
       <c r="AK7">
-        <v>58831.26614987053</v>
+        <v>55995.1781970649</v>
       </c>
       <c r="AL7">
-        <v>51679.58656330726</v>
+        <v>41928.72117400412</v>
       </c>
       <c r="AM7">
-        <v>588.3126614987053</v>
+        <v>559.951781970649</v>
       </c>
       <c r="AN7">
-        <v>0.005883126614987053</v>
+        <v>0.00559951781970649</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1688,31 +1658,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.02986735863666825</v>
+        <v>0.02825156533075833</v>
       </c>
       <c r="AR7">
-        <v>0.003803203169038076</v>
+        <v>0.007463401528883317</v>
       </c>
       <c r="AS7">
-        <v>0.00871865385343152</v>
+        <v>0.01959731900980129</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1720,7 +1690,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1732,82 +1702,82 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0.5766398971767849</v>
+        <v>3.623420612403818</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>8.99408</v>
+        <v>163.4765</v>
       </c>
       <c r="S8">
-        <v>8.963750763619577</v>
+        <v>164.2119082658437</v>
       </c>
       <c r="T8">
-        <v>8.973969062407297</v>
+        <v>163.0500932727376</v>
       </c>
       <c r="U8">
-        <v>8.99408</v>
+        <v>163.4765</v>
       </c>
       <c r="V8">
-        <v>8.930710000000001</v>
+        <v>165.583</v>
       </c>
       <c r="W8">
-        <v>8.963750763619577</v>
+        <v>164.2119082658437</v>
       </c>
       <c r="X8">
-        <v>9.085425000000001</v>
+        <v>161.8745</v>
       </c>
       <c r="Y8">
-        <v>-0.003372133267707519</v>
+        <v>0.004498556464346352</v>
       </c>
       <c r="Z8">
-        <v>0.3320295186427592</v>
+        <v>0.4590563457201755</v>
       </c>
       <c r="AA8">
-        <v>0.003372133267707519</v>
+        <v>0.004498556464346352</v>
       </c>
       <c r="AB8">
-        <v>0.4708091781513171</v>
+        <v>0.374980935513116</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3291908218486829</v>
+        <v>0.425019064486884</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1816,58 +1786,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.01015612491772366</v>
+        <v>0.009799573639024508</v>
       </c>
       <c r="AJ8">
-        <v>49231.37555421753</v>
+        <v>51022.62796504402</v>
       </c>
       <c r="AK8">
-        <v>36923.53166566315</v>
+        <v>51022.62796504402</v>
       </c>
       <c r="AL8">
-        <v>4105.315014505447</v>
+        <v>312.1098626716624</v>
       </c>
       <c r="AM8">
-        <v>369.2353166566315</v>
+        <v>510.2262796504402</v>
       </c>
       <c r="AN8">
-        <v>0.003692353166566315</v>
+        <v>0.005102262796504402</v>
       </c>
       <c r="AO8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ8">
-        <v>0.1111450723883654</v>
+        <v>4.381727609634654</v>
       </c>
       <c r="AR8">
-        <v>0.04932233769722467</v>
+        <v>0.8967873162908504</v>
       </c>
       <c r="AS8">
-        <v>0.1099223072541505</v>
+        <v>1.210946305072705</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1875,7 +1845,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1887,82 +1857,82 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" t="s">
         <v>68</v>
       </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" t="s">
-        <v>69</v>
-      </c>
       <c r="J9" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>1.509101234576306</v>
+        <v>1.541116014666038</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q9">
         <v>0.75</v>
       </c>
       <c r="R9">
-        <v>6.771725</v>
+        <v>7.7509</v>
       </c>
       <c r="S9">
-        <v>6.722106772273616</v>
+        <v>7.730435384960498</v>
       </c>
       <c r="T9">
-        <v>6.667764095847414</v>
+        <v>7.706803825862826</v>
       </c>
       <c r="U9">
-        <v>6.771725</v>
+        <v>7.7509</v>
       </c>
       <c r="V9">
-        <v>6.75935</v>
+        <v>7.744199999999999</v>
       </c>
       <c r="W9">
-        <v>6.722106772273616</v>
+        <v>7.730435384960498</v>
       </c>
       <c r="X9">
-        <v>6.804803818484256</v>
+        <v>7.811799999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.0073272656119946</v>
+        <v>-0.002640288874776037</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>0.3360363717487972</v>
       </c>
       <c r="AA9">
-        <v>0.0073272656119946</v>
+        <v>0.002640288874776037</v>
       </c>
       <c r="AB9">
-        <v>0.4336718416865972</v>
+        <v>0.4039080303802292</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3663281583134028</v>
+        <v>0.3960919696197709</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1974,22 +1944,22 @@
         <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.004884843741329734</v>
+        <v>0.007857152072662467</v>
       </c>
       <c r="AJ9">
-        <v>102357.419495243</v>
+        <v>63636.28899835847</v>
       </c>
       <c r="AK9">
-        <v>76768.06462143228</v>
+        <v>47727.21674876885</v>
       </c>
       <c r="AL9">
-        <v>11336.55968330555</v>
+        <v>6157.635467980344</v>
       </c>
       <c r="AM9">
-        <v>767.6806462143228</v>
+        <v>477.2721674876885</v>
       </c>
       <c r="AN9">
-        <v>0.007676806462143228</v>
+        <v>0.004772721674876885</v>
       </c>
       <c r="AO9">
         <v>375</v>
@@ -1998,31 +1968,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.07438053045563454</v>
+        <v>0.151979607683341</v>
       </c>
       <c r="AR9">
-        <v>0.008621618107857399</v>
+        <v>0.03975604121482933</v>
       </c>
       <c r="AS9">
-        <v>0.02392010291959705</v>
+        <v>0.07444920743117162</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2030,7 +2000,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2045,79 +2015,79 @@
         <v>64</v>
       </c>
       <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
         <v>68</v>
       </c>
-      <c r="H10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>69</v>
-      </c>
       <c r="J10" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K10">
-        <v>0.4909375551523664</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.024715989915113</v>
+        <v>1.699149591905781</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>115</v>
+        <v>10</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q10">
-        <v>0.8727343887880916</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>7.7078</v>
+        <v>6.76172</v>
       </c>
       <c r="S10">
-        <v>7.639586468932697</v>
+        <v>6.698425946268422</v>
       </c>
       <c r="T10">
-        <v>7.587811870346156</v>
+        <v>6.635040390186102</v>
       </c>
       <c r="U10">
-        <v>7.7078</v>
+        <v>6.76172</v>
       </c>
       <c r="V10">
-        <v>7.657999999999999</v>
+        <v>6.739340000000001</v>
       </c>
       <c r="W10">
-        <v>7.639586468932697</v>
+        <v>6.698425946268422</v>
       </c>
       <c r="X10">
-        <v>7.768699999999999</v>
+        <v>6.803916035821053</v>
       </c>
       <c r="Y10">
-        <v>-0.008849935269117402</v>
+        <v>-0.009360643997618691</v>
       </c>
       <c r="Z10">
-        <v>1.120090822123213</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.008849935269117402</v>
+        <v>0.009360643997618691</v>
       </c>
       <c r="AB10">
-        <v>0.4042497101324258</v>
+        <v>0.4351891038956787</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3957502898675742</v>
+        <v>0.3648108961043214</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2126,58 +2096,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>436.3671943940458</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.007901087210358275</v>
+        <v>0.006240429331745794</v>
       </c>
       <c r="AJ10">
-        <v>63282.4302134652</v>
+        <v>80122.69243342626</v>
       </c>
       <c r="AK10">
-        <v>55228.75305337361</v>
+        <v>60092.01932506969</v>
       </c>
       <c r="AL10">
-        <v>7165.306968703601</v>
+        <v>8887.090758722587</v>
       </c>
       <c r="AM10">
-        <v>552.2875305337361</v>
+        <v>600.9201932506969</v>
       </c>
       <c r="AN10">
-        <v>0.005522875305337361</v>
+        <v>0.006009201932506969</v>
       </c>
       <c r="AO10">
-        <v>436.3671943940458</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP10">
-        <v>0.004363671943940457</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ10">
-        <v>0.1302012529690851</v>
+        <v>0.08258509318226688</v>
       </c>
       <c r="AR10">
-        <v>0.02813157518684083</v>
+        <v>0.0125756225978196</v>
       </c>
       <c r="AS10">
-        <v>0.05020827767135409</v>
+        <v>0.02611929683362362</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2185,7 +2155,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2197,82 +2167,82 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>69</v>
-      </c>
       <c r="J11" s="2">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1.777723893238875</v>
+        <v>1.653939172377564</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q11">
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>4018.51</v>
+        <v>4071.67</v>
       </c>
       <c r="S11">
-        <v>3928.405586607313</v>
+        <v>4021.233480858235</v>
       </c>
       <c r="T11">
-        <v>3939.61710940436</v>
+        <v>4041.85084979025</v>
       </c>
       <c r="U11">
-        <v>4018.51</v>
+        <v>4071.67</v>
       </c>
       <c r="V11">
-        <v>3861.320000000001</v>
+        <v>3967.64</v>
       </c>
       <c r="W11">
-        <v>3928.405586607313</v>
+        <v>4021.233480858235</v>
       </c>
       <c r="X11">
-        <v>4148.375</v>
+        <v>4201.535</v>
       </c>
       <c r="Y11">
-        <v>-0.02242234395153604</v>
+        <v>-0.01238718244400099</v>
       </c>
       <c r="Z11">
-        <v>0.693831389463575</v>
+        <v>0.3883765382648564</v>
       </c>
       <c r="AA11">
-        <v>0.02242234395153604</v>
+        <v>0.01238718244400099</v>
       </c>
       <c r="AB11">
-        <v>0.4552861130953555</v>
+        <v>0.44181519213033</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3447138869046446</v>
+        <v>0.3581848078696699</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2284,22 +2254,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.03231670445015687</v>
+        <v>0.03189477536244339</v>
       </c>
       <c r="AJ11">
-        <v>15471.87463904826</v>
+        <v>15676.5487236746</v>
       </c>
       <c r="AK11">
-        <v>11603.90597928619</v>
+        <v>11757.41154275595</v>
       </c>
       <c r="AL11">
         <v>2.887614060755402</v>
       </c>
       <c r="AM11">
-        <v>116.0390597928619</v>
+        <v>117.5741154275595</v>
       </c>
       <c r="AN11">
-        <v>0.001160390597928619</v>
+        <v>0.001175741154275595</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2308,31 +2278,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>296.1922221126541</v>
+        <v>349.3732816645701</v>
       </c>
       <c r="AR11">
-        <v>60.91350680697661</v>
+        <v>77.3434283375251</v>
       </c>
       <c r="AS11">
-        <v>147.7330148679231</v>
+        <v>183.8208029293828</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04320218631084363</v>
+        <v>0.02752457970622852</v>
       </c>
       <c r="AV11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,6 +169,15 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -178,27 +187,18 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -208,6 +208,9 @@
     <t>HIGH</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
@@ -232,46 +235,43 @@
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
-  </si>
-  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
+    <t>REDUCE_CONFLICT</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>REDUCE_CONFLICT</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.06529,naive=0.009961,drift4=0.01927; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.02457,naive=0.01063,drift4=0.02213; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.1029,naive=0.05916,drift4=0.1309; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.2107,naive=0.109,drift4=0.1994; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02989,naive=0.01067,drift4=0.01974; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05516,naive=0.01789,drift4=0.03534; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=7.249,naive=1.753,drift4=1.756; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3066,naive=0.06415,drift4=0.09864; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1053,naive=0.02133,drift4=0.04922; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=454.8,naive=152.9,drift4=279.3; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.3082,naive=0.05683,drift4=0.09587; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=312.4,naive=123.5,drift4=282.9; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05342,naive=0.01815,drift4=0.03824; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06671,naive=0.007432,drift4=0.02048; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=0.01798,naive=0.008494,drift4=0.02579; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.54,naive=0.20,drift4=0.26); metric_best=naive; scores=model=0.05531,naive=0.0425,drift4=0.1494; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.01771,naive=0.01006,drift4=0.0215; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1955,naive=0.113,drift4=0.2074; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=8.502,naive=1.856,drift4=1.639; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1128,naive=0.0219,drift4=0.04939; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -823,67 +823,67 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="K2">
-        <v>0.7433162552396745</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.50386669438296</v>
+        <v>0.6626148758334846</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.145695</v>
+        <v>7.7836</v>
       </c>
       <c r="S2">
-        <v>1.149710226291426</v>
+        <v>7.779117209658365</v>
       </c>
       <c r="T2">
-        <v>1.153398470590829</v>
+        <v>7.747369111776692</v>
       </c>
       <c r="U2">
-        <v>1.145695</v>
+        <v>7.7836</v>
       </c>
       <c r="V2">
-        <v>1.14789</v>
+        <v>7.8096</v>
       </c>
       <c r="Y2">
-        <v>0.003504620593985049</v>
+        <v>-0.0005759276352375666</v>
       </c>
       <c r="AA2">
-        <v>0.003504620593985049</v>
+        <v>0.0005759276352375666</v>
       </c>
       <c r="AB2">
-        <v>0.4101367619511154</v>
+        <v>0.4062739752469927</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3898632380488847</v>
+        <v>0.3937260247530073</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,31 +919,31 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.03563344242463792</v>
+        <v>0.1419415044979198</v>
       </c>
       <c r="AR2">
-        <v>0.005451556598451002</v>
+        <v>0.04656328055806756</v>
       </c>
       <c r="AS2">
-        <v>0.01150498468291821</v>
+        <v>0.07157380200628763</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
       </c>
       <c r="AW2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AX2" t="s">
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,70 +963,79 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.8276575547104769</v>
+        <v>1.525260554991763</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="O3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.695295</v>
+        <v>4101.35</v>
       </c>
       <c r="S3">
-        <v>0.6958396126752528</v>
+        <v>4221.809502454055</v>
       </c>
       <c r="T3">
-        <v>0.6955396310248338</v>
+        <v>4410.024026916818</v>
       </c>
       <c r="U3">
-        <v>0.695295</v>
+        <v>4101.35</v>
       </c>
       <c r="V3">
-        <v>0.69659</v>
+        <v>4027.000000000001</v>
+      </c>
+      <c r="W3">
+        <v>4221.809502454055</v>
+      </c>
+      <c r="X3">
+        <v>3971.485000000001</v>
       </c>
       <c r="Y3">
-        <v>0.0007832828874835192</v>
+        <v>0.02937069561340898</v>
+      </c>
+      <c r="Z3">
+        <v>0.9275748081011437</v>
       </c>
       <c r="AA3">
-        <v>0.0007832828874835192</v>
+        <v>0.02937069561340898</v>
       </c>
       <c r="AB3">
-        <v>0.4678235328394243</v>
+        <v>0.4697864619681752</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3321764671605756</v>
+        <v>0.3302135380318248</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1038,55 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI3">
+        <v>0.03166396430443632</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>15790.82123743889</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>15790.82123743889</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.850152081007202</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>157.9082123743889</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.001579082123743889</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.01558731385190217</v>
+        <v>310.1834114627783</v>
       </c>
       <c r="AR3">
-        <v>0.004691670301962474</v>
+        <v>56.21196884314294</v>
       </c>
       <c r="AS3">
-        <v>0.0125607870297175</v>
+        <v>148.757328754384</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1109,67 +1121,76 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.6632591236562488</v>
+        <v>0.274677165007067</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="O4" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4.70125</v>
+        <v>1.34587</v>
       </c>
       <c r="S4">
-        <v>4.698277272336779</v>
+        <v>1.354355625286461</v>
       </c>
       <c r="T4">
-        <v>4.6995446142246</v>
+        <v>1.356352886994835</v>
       </c>
       <c r="U4">
-        <v>4.70125</v>
+        <v>1.34587</v>
       </c>
       <c r="V4">
-        <v>4.69433</v>
+        <v>1.35664</v>
+      </c>
+      <c r="W4">
+        <v>1.354355625286461</v>
+      </c>
+      <c r="X4">
+        <v>1.333945</v>
       </c>
       <c r="Y4">
-        <v>-0.0006323270753993059</v>
+        <v>0.006304936796615503</v>
+      </c>
+      <c r="Z4">
+        <v>0.7115828332461965</v>
       </c>
       <c r="AA4">
-        <v>0.0006323270753993059</v>
+        <v>0.006304936796615503</v>
       </c>
       <c r="AB4">
-        <v>0.4915555065773776</v>
+        <v>0.4540884989317808</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3084444934226225</v>
+        <v>0.3459115010682193</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1181,55 +1202,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI4">
+        <v>0.008860439715574327</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>56430.60796645693</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>42322.9559748427</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>31446.5408805031</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>423.229559748427</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.00423229559748427</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.06618614085935499</v>
+        <v>0.02399865417781481</v>
       </c>
       <c r="AR4">
-        <v>0.0269174720769299</v>
+        <v>0.008223303508879716</v>
       </c>
       <c r="AS4">
-        <v>0.07009747241415941</v>
+        <v>0.01420877241398586</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1237,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1252,67 +1276,76 @@
         <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.4792599117402066</v>
+        <v>0.1854587861281391</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>9.03811</v>
+        <v>1.152235</v>
       </c>
       <c r="S5">
-        <v>9.029781068240107</v>
+        <v>1.158810997915091</v>
       </c>
       <c r="T5">
-        <v>9.033997868838341</v>
+        <v>1.160005345909411</v>
       </c>
       <c r="U5">
-        <v>9.03811</v>
+        <v>1.152235</v>
       </c>
       <c r="V5">
-        <v>9.01877</v>
+        <v>1.16097</v>
+      </c>
+      <c r="W5">
+        <v>1.158810997915091</v>
+      </c>
+      <c r="X5">
+        <v>1.14004125</v>
       </c>
       <c r="Y5">
-        <v>-0.0009215346748261429</v>
+        <v>0.005707167301020194</v>
+      </c>
+      <c r="Z5">
+        <v>0.5392924994436544</v>
       </c>
       <c r="AA5">
-        <v>0.0009215346748261429</v>
+        <v>0.005707167301020194</v>
       </c>
       <c r="AB5">
-        <v>0.469078655453103</v>
+        <v>0.4270982613647548</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3309213445468971</v>
+        <v>0.3729017386352452</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1324,55 +1357,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI5">
+        <v>0.01058269363454494</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>47246.95028190713</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>47246.95028190713</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>41004.61301896499</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>472.4695028190713</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.004724695028190713</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.1203477534295891</v>
+        <v>0.0324557127811792</v>
       </c>
       <c r="AR5">
-        <v>0.04945355180574008</v>
+        <v>0.007172852111003474</v>
       </c>
       <c r="AS5">
-        <v>0.1192958788948709</v>
+        <v>0.01067209875013536</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1380,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1392,31 +1428,31 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2.371049492894731</v>
+        <v>0.005696016308642093</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1428,43 +1464,43 @@
         <v>1</v>
       </c>
       <c r="R6">
-        <v>0.81491</v>
+        <v>0.702775</v>
       </c>
       <c r="S6">
-        <v>0.8233600982040008</v>
+        <v>0.7060557610269981</v>
       </c>
       <c r="T6">
-        <v>0.8246426865834584</v>
+        <v>0.7040974628160568</v>
       </c>
       <c r="U6">
-        <v>0.81491</v>
+        <v>0.702775</v>
       </c>
       <c r="V6">
-        <v>0.82652</v>
+        <v>0.7115500000000001</v>
       </c>
       <c r="W6">
-        <v>0.8233600982040008</v>
+        <v>0.7060557610269981</v>
       </c>
       <c r="X6">
-        <v>0.806535</v>
+        <v>0.695075</v>
       </c>
       <c r="Y6">
-        <v>0.01036936373832789</v>
+        <v>0.004668295011914248</v>
       </c>
       <c r="Z6">
-        <v>1.00896694973143</v>
+        <v>0.4260728606490918</v>
       </c>
       <c r="AA6">
-        <v>0.01036936373832789</v>
+        <v>0.004668295011914248</v>
       </c>
       <c r="AB6">
-        <v>0.4463302656958154</v>
+        <v>0.5017403980295896</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3536697343041846</v>
+        <v>0.2982596019704105</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1479,55 +1515,55 @@
         <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.01027720852609497</v>
+        <v>0.01095656504571174</v>
       </c>
       <c r="AJ6">
-        <v>48651.34328358181</v>
+        <v>45634.74025973985</v>
       </c>
       <c r="AK6">
-        <v>48651.34328358181</v>
+        <v>45634.74025973985</v>
       </c>
       <c r="AL6">
-        <v>59701.49253731309</v>
+        <v>64935.06493506435</v>
       </c>
       <c r="AM6">
-        <v>486.5134328358181</v>
+        <v>456.3474025973985</v>
       </c>
       <c r="AN6">
-        <v>0.004865134328358181</v>
+        <v>0.004563474025973985</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.01831786488098754</v>
+        <v>0.01537437814657642</v>
       </c>
       <c r="AR6">
-        <v>0.005433831140914195</v>
+        <v>0.003383404294725531</v>
       </c>
       <c r="AS6">
-        <v>0.01047754010096085</v>
+        <v>0.0097293746228147</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1535,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1547,79 +1583,79 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.4014999642724688</v>
+        <v>0.3886497203685205</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1.335485</v>
+        <v>4.74093</v>
       </c>
       <c r="S7">
-        <v>1.343388652074018</v>
+        <v>4.762312929414509</v>
       </c>
       <c r="T7">
-        <v>1.35289195089401</v>
+        <v>4.764796924542508</v>
       </c>
       <c r="U7">
-        <v>1.335485</v>
+        <v>4.74093</v>
       </c>
       <c r="V7">
-        <v>1.33587</v>
+        <v>4.773689999999999</v>
       </c>
       <c r="W7">
-        <v>1.343388652074018</v>
+        <v>4.762312929414509</v>
       </c>
       <c r="X7">
-        <v>1.32356</v>
+        <v>4.7060825</v>
       </c>
       <c r="Y7">
-        <v>0.00591818857869438</v>
+        <v>0.004510281614474336</v>
       </c>
       <c r="Z7">
-        <v>0.6627800481356522</v>
+        <v>0.6136144462159369</v>
       </c>
       <c r="AA7">
-        <v>0.00591818857869438</v>
+        <v>0.004510281614474336</v>
       </c>
       <c r="AB7">
-        <v>0.446226882060304</v>
+        <v>0.5425648987860212</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3537731179396961</v>
+        <v>0.2574351012139788</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1634,55 +1670,55 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008929340277127799</v>
+        <v>0.007350351091452505</v>
       </c>
       <c r="AJ7">
-        <v>55995.1781970649</v>
+        <v>68023.96154673951</v>
       </c>
       <c r="AK7">
-        <v>55995.1781970649</v>
+        <v>68023.96154673951</v>
       </c>
       <c r="AL7">
-        <v>41928.72117400412</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM7">
-        <v>559.951781970649</v>
+        <v>680.2396154673951</v>
       </c>
       <c r="AN7">
-        <v>0.00559951781970649</v>
+        <v>0.006802396154673951</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ7">
-        <v>0.02825156533075833</v>
+        <v>0.05120374807396562</v>
       </c>
       <c r="AR7">
-        <v>0.007463401528883317</v>
+        <v>0.01541190539792375</v>
       </c>
       <c r="AS7">
-        <v>0.01959731900980129</v>
+        <v>0.05195662929419464</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1690,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1702,79 +1738,79 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.3762123956723264</v>
       </c>
       <c r="L8">
-        <v>3.623420612403818</v>
+        <v>1.3177803820073</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.8440530989180817</v>
       </c>
       <c r="R8">
-        <v>163.4765</v>
+        <v>0.8059350000000001</v>
       </c>
       <c r="S8">
-        <v>164.2119082658437</v>
+        <v>0.8071393008624872</v>
       </c>
       <c r="T8">
-        <v>163.0500932727376</v>
+        <v>0.8067184405901684</v>
       </c>
       <c r="U8">
-        <v>163.4765</v>
+        <v>0.8059350000000001</v>
       </c>
       <c r="V8">
-        <v>165.583</v>
+        <v>0.8085700000000001</v>
       </c>
       <c r="W8">
-        <v>164.2119082658437</v>
+        <v>0.8071439025000001</v>
       </c>
       <c r="X8">
-        <v>161.8745</v>
+        <v>0.7962600000000001</v>
       </c>
       <c r="Y8">
-        <v>0.004498556464346352</v>
+        <v>0.001494290311857816</v>
       </c>
       <c r="Z8">
-        <v>0.4590563457201755</v>
+        <v>0.1249511627906975</v>
       </c>
       <c r="AA8">
-        <v>0.004498556464346352</v>
+        <v>0.001494290311857816</v>
       </c>
       <c r="AB8">
-        <v>0.374980935513116</v>
+        <v>0.4880746103604971</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.425019064486884</v>
+        <v>0.3119253896395029</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1786,58 +1822,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>422.0265494590408</v>
       </c>
       <c r="AI8">
-        <v>0.009799573639024508</v>
+        <v>0.01200469020454505</v>
       </c>
       <c r="AJ8">
-        <v>51022.62796504402</v>
+        <v>41650.38759689916</v>
       </c>
       <c r="AK8">
-        <v>51022.62796504402</v>
+        <v>35155.13872230196</v>
       </c>
       <c r="AL8">
-        <v>312.1098626716624</v>
+        <v>43620.31518956486</v>
       </c>
       <c r="AM8">
-        <v>510.2262796504402</v>
+        <v>351.5513872230196</v>
       </c>
       <c r="AN8">
-        <v>0.005102262796504402</v>
+        <v>0.003515513872230196</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>422.0265494590408</v>
       </c>
       <c r="AP8">
-        <v>0.005</v>
+        <v>0.004220265494590408</v>
       </c>
       <c r="AQ8">
-        <v>4.381727609634654</v>
+        <v>0.01487235947255213</v>
       </c>
       <c r="AR8">
-        <v>0.8967873162908504</v>
+        <v>0.005922949823206417</v>
       </c>
       <c r="AS8">
-        <v>1.210946305072705</v>
+        <v>0.01101442357319184</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX8" t="s">
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1845,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1860,76 +1896,76 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>1.541116014666038</v>
+        <v>0.05823076207883358</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
         <v>0.75</v>
       </c>
       <c r="R9">
-        <v>7.7509</v>
+        <v>9.102370000000001</v>
       </c>
       <c r="S9">
-        <v>7.730435384960498</v>
+        <v>9.090258842451778</v>
       </c>
       <c r="T9">
-        <v>7.706803825862826</v>
+        <v>9.046575857738972</v>
       </c>
       <c r="U9">
-        <v>7.7509</v>
+        <v>9.102370000000001</v>
       </c>
       <c r="V9">
-        <v>7.744199999999999</v>
+        <v>9.147290000000002</v>
       </c>
       <c r="W9">
-        <v>7.730435384960498</v>
+        <v>9.088716445000001</v>
       </c>
       <c r="X9">
-        <v>7.811799999999999</v>
+        <v>9.193715000000001</v>
       </c>
       <c r="Y9">
-        <v>-0.002640288874776037</v>
+        <v>-0.001330549906037928</v>
       </c>
       <c r="Z9">
-        <v>0.3360363717487972</v>
+        <v>0.1494723849143358</v>
       </c>
       <c r="AA9">
-        <v>0.002640288874776037</v>
+        <v>0.001330549906037928</v>
       </c>
       <c r="AB9">
-        <v>0.4039080303802292</v>
+        <v>0.4770646551672466</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3960919696197709</v>
+        <v>0.3229353448327534</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1944,22 +1980,22 @@
         <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.007857152072662467</v>
+        <v>0.01003529849918208</v>
       </c>
       <c r="AJ9">
-        <v>63636.28899835847</v>
+        <v>49824.12830477859</v>
       </c>
       <c r="AK9">
-        <v>47727.21674876885</v>
+        <v>37368.09622858394</v>
       </c>
       <c r="AL9">
-        <v>6157.635467980344</v>
+        <v>4105.315014505446</v>
       </c>
       <c r="AM9">
-        <v>477.2721674876885</v>
+        <v>373.6809622858394</v>
       </c>
       <c r="AN9">
-        <v>0.004772721674876885</v>
+        <v>0.003736809622858394</v>
       </c>
       <c r="AO9">
         <v>375</v>
@@ -1968,31 +2004,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.151979607683341</v>
+        <v>0.1388715895500769</v>
       </c>
       <c r="AR9">
-        <v>0.03975604121482933</v>
+        <v>0.05589321206718759</v>
       </c>
       <c r="AS9">
-        <v>0.07444920743117162</v>
+        <v>0.09296816979976469</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2000,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2012,31 +2048,31 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.699149591905781</v>
+        <v>0.1235639613455076</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
@@ -2045,46 +2081,46 @@
         <v>74</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>6.76172</v>
+        <v>160.29</v>
       </c>
       <c r="S10">
-        <v>6.698425946268422</v>
+        <v>159.6375242695781</v>
       </c>
       <c r="T10">
-        <v>6.635040390186102</v>
+        <v>159.7959446250085</v>
       </c>
       <c r="U10">
-        <v>6.76172</v>
+        <v>160.29</v>
       </c>
       <c r="V10">
-        <v>6.739340000000001</v>
+        <v>159.21</v>
       </c>
       <c r="W10">
-        <v>6.698425946268422</v>
+        <v>159.6375242695781</v>
       </c>
       <c r="X10">
-        <v>6.803916035821053</v>
+        <v>162.165</v>
       </c>
       <c r="Y10">
-        <v>-0.009360643997618691</v>
+        <v>-0.00407059536104488</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>0.3479870562250034</v>
       </c>
       <c r="AA10">
-        <v>0.009360643997618691</v>
+        <v>0.00407059536104488</v>
       </c>
       <c r="AB10">
-        <v>0.4351891038956787</v>
+        <v>0.3609970303508924</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3648108961043214</v>
+        <v>0.4390029696491076</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2096,58 +2132,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.006240429331745794</v>
+        <v>0.0116975481938986</v>
       </c>
       <c r="AJ10">
-        <v>80122.69243342626</v>
+        <v>42743.99999999983</v>
       </c>
       <c r="AK10">
-        <v>60092.01932506969</v>
+        <v>42743.99999999983</v>
       </c>
       <c r="AL10">
-        <v>8887.090758722587</v>
+        <v>266.6666666666657</v>
       </c>
       <c r="AM10">
-        <v>600.9201932506969</v>
+        <v>427.4399999999983</v>
       </c>
       <c r="AN10">
-        <v>0.006009201932506969</v>
+        <v>0.004274399999999983</v>
       </c>
       <c r="AO10">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.08258509318226688</v>
+        <v>3.199524838974722</v>
       </c>
       <c r="AR10">
-        <v>0.0125756225978196</v>
+        <v>1.761148429142851</v>
       </c>
       <c r="AS10">
-        <v>0.02611929683362362</v>
+        <v>2.448724403490512</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2155,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46233</v>
+        <v>46235</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2167,79 +2203,79 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.02462895362935497</v>
       </c>
       <c r="L11">
-        <v>1.653939172377564</v>
+        <v>2.350152272313951</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
+        <v>0.7561572384073387</v>
       </c>
       <c r="R11">
-        <v>4071.67</v>
+        <v>6.74808</v>
       </c>
       <c r="S11">
-        <v>4021.233480858235</v>
+        <v>6.6660428198669</v>
       </c>
       <c r="T11">
-        <v>4041.85084979025</v>
+        <v>6.588738809647995</v>
       </c>
       <c r="U11">
-        <v>4071.67</v>
+        <v>6.74808</v>
       </c>
       <c r="V11">
-        <v>3967.64</v>
+        <v>6.71206</v>
       </c>
       <c r="W11">
-        <v>4021.233480858235</v>
+        <v>6.6660428198669</v>
       </c>
       <c r="X11">
-        <v>4201.535</v>
+        <v>6.802771453422067</v>
       </c>
       <c r="Y11">
-        <v>-0.01238718244400099</v>
+        <v>-0.01215711433964922</v>
       </c>
       <c r="Z11">
-        <v>0.3883765382648564</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.01238718244400099</v>
+        <v>0.01215711433964922</v>
       </c>
       <c r="AB11">
-        <v>0.44181519213033</v>
+        <v>0.431565572641554</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3581848078696699</v>
+        <v>0.3684344273584461</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2251,58 +2287,58 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>375</v>
+        <v>378.0786192036693</v>
       </c>
       <c r="AI11">
-        <v>0.03189477536244339</v>
+        <v>0.008104742893099481</v>
       </c>
       <c r="AJ11">
-        <v>15676.5487236746</v>
+        <v>61692.271623534</v>
       </c>
       <c r="AK11">
-        <v>11757.41154275595</v>
+        <v>46649.0577419269</v>
       </c>
       <c r="AL11">
-        <v>2.887614060755402</v>
+        <v>6912.937864092734</v>
       </c>
       <c r="AM11">
-        <v>117.5741154275595</v>
+        <v>466.490577419269</v>
       </c>
       <c r="AN11">
-        <v>0.001175741154275595</v>
+        <v>0.00466490577419269</v>
       </c>
       <c r="AO11">
-        <v>375</v>
+        <v>378.0786192036693</v>
       </c>
       <c r="AP11">
-        <v>0.00375</v>
+        <v>0.003780786192036693</v>
       </c>
       <c r="AQ11">
-        <v>349.3732816645701</v>
+        <v>0.07844947523881489</v>
       </c>
       <c r="AR11">
-        <v>77.3434283375251</v>
+        <v>0.01601756636834938</v>
       </c>
       <c r="AS11">
-        <v>183.8208029293828</v>
+        <v>0.02230717168301981</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.02752457970622852</v>
+        <v>0.03809357219934806</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -172,33 +172,33 @@
     <t>EURCNH</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>AUDCNH</t>
   </si>
   <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>GBPCNH</t>
+    <t>USDCNH</t>
   </si>
   <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.3082,naive=0.05683,drift4=0.09587; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=312.4,naive=123.5,drift4=282.9; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.05342,naive=0.01815,drift4=0.03824; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.06671,naive=0.007432,drift4=0.02048; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.50,naive=0.20,drift4=0.30); metric_best=naive; scores=model=0.01798,naive=0.008494,drift4=0.02579; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.54,naive=0.20,drift4=0.26); metric_best=naive; scores=model=0.05531,naive=0.0425,drift4=0.1494; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=0.01771,naive=0.01006,drift4=0.0215; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1955,naive=0.113,drift4=0.2074; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=8.502,naive=1.856,drift4=1.639; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1128,naive=0.0219,drift4=0.04939; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1366,naive=0.04591,drift4=0.06992; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1374,naive=0.05343,drift4=0.08357; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=302.3,naive=51.03,drift4=128.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.02423,naive=0.009183,drift4=0.01297; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01682,naive=0.00373,drift4=0.008922; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03224,naive=0.008309,drift4=0.01127; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.04815,naive=0.01252,drift4=0.04475; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01447,naive=0.005536,drift4=0.0101; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.07393,naive=0.01436,drift4=0.01742; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.397,naive=3.436,drift4=4.346; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -859,10 +859,10 @@
         <v>7.7836</v>
       </c>
       <c r="S2">
-        <v>7.779117209658365</v>
+        <v>7.777681409236244</v>
       </c>
       <c r="T2">
-        <v>7.747369111776692</v>
+        <v>7.746944271471207</v>
       </c>
       <c r="U2">
         <v>7.7836</v>
@@ -871,19 +871,19 @@
         <v>7.8096</v>
       </c>
       <c r="Y2">
-        <v>-0.0005759276352375666</v>
+        <v>-0.0007603924615544941</v>
       </c>
       <c r="AA2">
-        <v>0.0005759276352375666</v>
+        <v>0.0007603924615544941</v>
       </c>
       <c r="AB2">
-        <v>0.4062739752469927</v>
+        <v>0.4264349228894188</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3937260247530073</v>
+        <v>0.3735650771105812</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.1419415044979198</v>
+        <v>0.1366464391619375</v>
       </c>
       <c r="AR2">
-        <v>0.04656328055806756</v>
+        <v>0.04591007142001213</v>
       </c>
       <c r="AS2">
-        <v>0.07157380200628763</v>
+        <v>0.06992174843283862</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,79 +963,70 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.525260554991763</v>
+        <v>0.05823076207883358</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>4101.35</v>
+        <v>9.102370000000001</v>
       </c>
       <c r="S3">
-        <v>4221.809502454055</v>
+        <v>9.094629115587862</v>
       </c>
       <c r="T3">
-        <v>4410.024026916818</v>
+        <v>9.047407266769415</v>
       </c>
       <c r="U3">
-        <v>4101.35</v>
+        <v>9.102370000000001</v>
       </c>
       <c r="V3">
-        <v>4027.000000000001</v>
-      </c>
-      <c r="W3">
-        <v>4221.809502454055</v>
-      </c>
-      <c r="X3">
-        <v>3971.485000000001</v>
+        <v>9.147290000000002</v>
       </c>
       <c r="Y3">
-        <v>0.02937069561340898</v>
-      </c>
-      <c r="Z3">
-        <v>0.9275748081011437</v>
+        <v>-0.0008504251543431295</v>
       </c>
       <c r="AA3">
-        <v>0.02937069561340898</v>
+        <v>0.0008504251543431295</v>
       </c>
       <c r="AB3">
-        <v>0.4697864619681752</v>
+        <v>0.43728163016232</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3302135380318248</v>
+        <v>0.36271836983768</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1047,58 +1038,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.03166396430443632</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>15790.82123743889</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>15790.82123743889</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.850152081007202</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>157.9082123743889</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.001579082123743889</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>310.1834114627783</v>
+        <v>0.1374064622571514</v>
       </c>
       <c r="AR3">
-        <v>56.21196884314294</v>
+        <v>0.05343121999263051</v>
       </c>
       <c r="AS3">
-        <v>148.757328754384</v>
+        <v>0.08356518379825222</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,7 +1106,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
         <v>67</v>
@@ -1127,7 +1115,7 @@
         <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
         <v>46233</v>
@@ -1136,61 +1124,61 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.274677165007067</v>
+        <v>1.525260554991763</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>1.34587</v>
+        <v>4101.35</v>
       </c>
       <c r="S4">
-        <v>1.354355625286461</v>
+        <v>4208.183078883262</v>
       </c>
       <c r="T4">
-        <v>1.356352886994835</v>
+        <v>4409.778127988468</v>
       </c>
       <c r="U4">
-        <v>1.34587</v>
+        <v>4101.35</v>
       </c>
       <c r="V4">
-        <v>1.35664</v>
+        <v>4027.000000000001</v>
       </c>
       <c r="W4">
-        <v>1.354355625286461</v>
+        <v>4208.183078883262</v>
       </c>
       <c r="X4">
-        <v>1.333945</v>
+        <v>3971.485000000001</v>
       </c>
       <c r="Y4">
-        <v>0.006304936796615503</v>
+        <v>0.02604827163818299</v>
       </c>
       <c r="Z4">
-        <v>0.7115828332461965</v>
+        <v>0.8226472019655942</v>
       </c>
       <c r="AA4">
-        <v>0.006304936796615503</v>
+        <v>0.02604827163818299</v>
       </c>
       <c r="AB4">
-        <v>0.4540884989317808</v>
+        <v>0.4344895037688049</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3459115010682193</v>
+        <v>0.3655104962311952</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1202,46 +1190,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.008860439715574327</v>
+        <v>0.03166396430443632</v>
       </c>
       <c r="AJ4">
-        <v>56430.60796645693</v>
+        <v>15790.82123743889</v>
       </c>
       <c r="AK4">
-        <v>42322.9559748427</v>
+        <v>15790.82123743889</v>
       </c>
       <c r="AL4">
-        <v>31446.5408805031</v>
+        <v>3.850152081007202</v>
       </c>
       <c r="AM4">
-        <v>423.229559748427</v>
+        <v>157.9082123743889</v>
       </c>
       <c r="AN4">
-        <v>0.00423229559748427</v>
+        <v>0.001579082123743889</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.02399865417781481</v>
+        <v>302.3256723747335</v>
       </c>
       <c r="AR4">
-        <v>0.008223303508879716</v>
+        <v>51.031275208787</v>
       </c>
       <c r="AS4">
-        <v>0.01420877241398586</v>
+        <v>128.6483847079737</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1253,7 +1241,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1282,70 +1270,70 @@
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.1854587861281391</v>
+        <v>0.5977178050946401</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>1.152235</v>
+        <v>1.349445</v>
       </c>
       <c r="S5">
-        <v>1.158810997915091</v>
+        <v>1.360052436520948</v>
       </c>
       <c r="T5">
-        <v>1.160005345909411</v>
+        <v>1.361755472624392</v>
       </c>
       <c r="U5">
-        <v>1.152235</v>
+        <v>1.349445</v>
       </c>
       <c r="V5">
-        <v>1.16097</v>
+        <v>1.36379</v>
       </c>
       <c r="W5">
-        <v>1.158810997915091</v>
+        <v>1.360052436520948</v>
       </c>
       <c r="X5">
-        <v>1.14004125</v>
+        <v>1.33528875</v>
       </c>
       <c r="Y5">
-        <v>0.005707167301020194</v>
+        <v>0.007860591962583366</v>
       </c>
       <c r="Z5">
-        <v>0.5392924994436544</v>
+        <v>0.7493111891177624</v>
       </c>
       <c r="AA5">
-        <v>0.005707167301020194</v>
+        <v>0.007860591962583366</v>
       </c>
       <c r="AB5">
-        <v>0.4270982613647548</v>
+        <v>0.4269116697396151</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3729017386352452</v>
+        <v>0.3730883302603848</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1357,46 +1345,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01058269363454494</v>
+        <v>0.01049042384091236</v>
       </c>
       <c r="AJ5">
-        <v>47246.95028190713</v>
+        <v>47662.51655629146</v>
       </c>
       <c r="AK5">
-        <v>47246.95028190713</v>
+        <v>35746.88741721859</v>
       </c>
       <c r="AL5">
-        <v>41004.61301896499</v>
+        <v>26490.0662251656</v>
       </c>
       <c r="AM5">
-        <v>472.4695028190713</v>
+        <v>357.4688741721859</v>
       </c>
       <c r="AN5">
-        <v>0.004724695028190713</v>
+        <v>0.003574688741721859</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.0324557127811792</v>
+        <v>0.0242332598811832</v>
       </c>
       <c r="AR5">
-        <v>0.007172852111003474</v>
+        <v>0.009182931635909787</v>
       </c>
       <c r="AS5">
-        <v>0.01067209875013536</v>
+        <v>0.01296607082127836</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1408,7 +1396,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1437,70 +1425,70 @@
         <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.005696016308642093</v>
+        <v>0.1551900343993899</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>0.702775</v>
+        <v>0.7048449999999999</v>
       </c>
       <c r="S6">
-        <v>0.7060557610269981</v>
+        <v>0.7100601426739257</v>
       </c>
       <c r="T6">
-        <v>0.7040974628160568</v>
+        <v>0.7078605582895873</v>
       </c>
       <c r="U6">
-        <v>0.702775</v>
+        <v>0.7048449999999999</v>
       </c>
       <c r="V6">
-        <v>0.7115500000000001</v>
+        <v>0.7156899999999999</v>
       </c>
       <c r="W6">
-        <v>0.7060557610269981</v>
+        <v>0.7100601426739257</v>
       </c>
       <c r="X6">
-        <v>0.695075</v>
+        <v>0.6971449999999999</v>
       </c>
       <c r="Y6">
-        <v>0.004668295011914248</v>
+        <v>0.007398992223716924</v>
       </c>
       <c r="Z6">
-        <v>0.4260728606490918</v>
+        <v>0.6772912563539881</v>
       </c>
       <c r="AA6">
-        <v>0.004668295011914248</v>
+        <v>0.007398992223716924</v>
       </c>
       <c r="AB6">
-        <v>0.5017403980295896</v>
+        <v>0.4420311759230134</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.2982596019704105</v>
+        <v>0.3579688240769866</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1512,46 +1500,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01095656504571174</v>
+        <v>0.0109243876313233</v>
       </c>
       <c r="AJ6">
-        <v>45634.74025973985</v>
+        <v>45769.15584415544</v>
       </c>
       <c r="AK6">
-        <v>45634.74025973985</v>
+        <v>34326.86688311658</v>
       </c>
       <c r="AL6">
-        <v>64935.06493506435</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM6">
-        <v>456.3474025973985</v>
+        <v>343.2686688311658</v>
       </c>
       <c r="AN6">
-        <v>0.004563474025973985</v>
+        <v>0.003432686688311658</v>
       </c>
       <c r="AO6">
-        <v>499.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.004999999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.01537437814657642</v>
+        <v>0.01681882597198171</v>
       </c>
       <c r="AR6">
-        <v>0.003383404294725531</v>
+        <v>0.003729641222699242</v>
       </c>
       <c r="AS6">
-        <v>0.0097293746228147</v>
+        <v>0.008922321156931307</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1563,7 +1551,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1601,13 +1589,13 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.3886497203685205</v>
+        <v>0.008413607076037008</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N7">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1619,43 +1607,43 @@
         <v>1</v>
       </c>
       <c r="R7">
-        <v>4.74093</v>
+        <v>1.154795</v>
       </c>
       <c r="S7">
-        <v>4.762312929414509</v>
+        <v>1.16301057602103</v>
       </c>
       <c r="T7">
-        <v>4.764796924542508</v>
+        <v>1.164053466470201</v>
       </c>
       <c r="U7">
-        <v>4.74093</v>
+        <v>1.154795</v>
       </c>
       <c r="V7">
-        <v>4.773689999999999</v>
+        <v>1.16609</v>
       </c>
       <c r="W7">
-        <v>4.762312929414509</v>
+        <v>1.16301057602103</v>
       </c>
       <c r="X7">
-        <v>4.7060825</v>
+        <v>1.141795</v>
       </c>
       <c r="Y7">
-        <v>0.004510281614474336</v>
+        <v>0.007114315546075529</v>
       </c>
       <c r="Z7">
-        <v>0.6136144462159369</v>
+        <v>0.6319673862330988</v>
       </c>
       <c r="AA7">
-        <v>0.004510281614474336</v>
+        <v>0.007114315546075529</v>
       </c>
       <c r="AB7">
-        <v>0.5425648987860212</v>
+        <v>0.4028531654231196</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.2574351012139788</v>
+        <v>0.3971468345768805</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1670,43 +1658,43 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.007350351091452505</v>
+        <v>0.01125740932373279</v>
       </c>
       <c r="AJ7">
-        <v>68023.96154673951</v>
+        <v>44415.19230769227</v>
       </c>
       <c r="AK7">
-        <v>68023.96154673951</v>
+        <v>44415.19230769227</v>
       </c>
       <c r="AL7">
-        <v>14348.23158045774</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM7">
-        <v>680.2396154673951</v>
+        <v>444.1519230769227</v>
       </c>
       <c r="AN7">
-        <v>0.006802396154673951</v>
+        <v>0.004441519230769227</v>
       </c>
       <c r="AO7">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.05120374807396562</v>
+        <v>0.0322368627435243</v>
       </c>
       <c r="AR7">
-        <v>0.01541190539792375</v>
+        <v>0.008308535227457951</v>
       </c>
       <c r="AS7">
-        <v>0.05195662929419464</v>
+        <v>0.01126888345265342</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1718,7 +1706,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1747,70 +1735,70 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K8">
-        <v>0.3762123956723264</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.3177803820073</v>
+        <v>0.3886497203685205</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.8440530989180817</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>0.8059350000000001</v>
+        <v>4.74093</v>
       </c>
       <c r="S8">
-        <v>0.8071393008624872</v>
+        <v>4.762884081452667</v>
       </c>
       <c r="T8">
-        <v>0.8067184405901684</v>
+        <v>4.764809699013573</v>
       </c>
       <c r="U8">
-        <v>0.8059350000000001</v>
+        <v>4.74093</v>
       </c>
       <c r="V8">
-        <v>0.8085700000000001</v>
+        <v>4.773689999999999</v>
       </c>
       <c r="W8">
-        <v>0.8071439025000001</v>
+        <v>4.762884081452667</v>
       </c>
       <c r="X8">
-        <v>0.7962600000000001</v>
+        <v>4.7060825</v>
       </c>
       <c r="Y8">
-        <v>0.001494290311857816</v>
+        <v>0.004630754188032066</v>
       </c>
       <c r="Z8">
-        <v>0.1249511627906975</v>
+        <v>0.6300044896381924</v>
       </c>
       <c r="AA8">
-        <v>0.001494290311857816</v>
+        <v>0.004630754188032066</v>
       </c>
       <c r="AB8">
-        <v>0.4880746103604971</v>
+        <v>0.4790286448438341</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3119253896395029</v>
+        <v>0.3209713551561659</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1822,46 +1810,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>422.0265494590408</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.01200469020454505</v>
+        <v>0.007350351091452505</v>
       </c>
       <c r="AJ8">
-        <v>41650.38759689916</v>
+        <v>68023.96154673951</v>
       </c>
       <c r="AK8">
-        <v>35155.13872230196</v>
+        <v>68023.96154673951</v>
       </c>
       <c r="AL8">
-        <v>43620.31518956486</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM8">
-        <v>351.5513872230196</v>
+        <v>680.2396154673951</v>
       </c>
       <c r="AN8">
-        <v>0.003515513872230196</v>
+        <v>0.006802396154673951</v>
       </c>
       <c r="AO8">
-        <v>422.0265494590408</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP8">
-        <v>0.004220265494590408</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ8">
-        <v>0.01487235947255213</v>
+        <v>0.04814737867715133</v>
       </c>
       <c r="AR8">
-        <v>0.005922949823206417</v>
+        <v>0.01251643941727024</v>
       </c>
       <c r="AS8">
-        <v>0.01101442357319184</v>
+        <v>0.04475091762952476</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1873,7 +1861,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1896,28 +1884,28 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
         <v>46234</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.08687051514847721</v>
       </c>
       <c r="L9">
-        <v>0.05823076207883358</v>
+        <v>1.118438100924791</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="O9" t="s">
         <v>72</v>
@@ -1926,46 +1914,46 @@
         <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>0.7717176287871192</v>
       </c>
       <c r="R9">
-        <v>9.102370000000001</v>
+        <v>0.806345</v>
       </c>
       <c r="S9">
-        <v>9.090258842451778</v>
+        <v>0.8077972074805991</v>
       </c>
       <c r="T9">
-        <v>9.046575857738972</v>
+        <v>0.8072005817649544</v>
       </c>
       <c r="U9">
-        <v>9.102370000000001</v>
+        <v>0.806345</v>
       </c>
       <c r="V9">
-        <v>9.147290000000002</v>
+        <v>0.8093899999999999</v>
       </c>
       <c r="W9">
-        <v>9.088716445000001</v>
+        <v>0.8077972074805991</v>
       </c>
       <c r="X9">
-        <v>9.193715000000001</v>
+        <v>0.7968649999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.001330549906037928</v>
+        <v>0.00180097536488619</v>
       </c>
       <c r="Z9">
-        <v>0.1494723849143358</v>
+        <v>0.1531864431011769</v>
       </c>
       <c r="AA9">
-        <v>0.001330549906037928</v>
+        <v>0.00180097536488619</v>
       </c>
       <c r="AB9">
-        <v>0.4770646551672466</v>
+        <v>0.4493396938298393</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3229353448327534</v>
+        <v>0.3506603061701606</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1977,58 +1965,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>385.8588143935596</v>
       </c>
       <c r="AI9">
-        <v>0.01003529849918208</v>
+        <v>0.0117567542429109</v>
       </c>
       <c r="AJ9">
-        <v>49824.12830477859</v>
+        <v>42528.74472573845</v>
       </c>
       <c r="AK9">
-        <v>37368.09622858394</v>
+        <v>32820.18203503958</v>
       </c>
       <c r="AL9">
-        <v>4105.315014505446</v>
+        <v>40702.40658159916</v>
       </c>
       <c r="AM9">
-        <v>373.6809622858394</v>
+        <v>328.2018203503958</v>
       </c>
       <c r="AN9">
-        <v>0.003736809622858394</v>
+        <v>0.003282018203503958</v>
       </c>
       <c r="AO9">
-        <v>375</v>
+        <v>385.8588143935597</v>
       </c>
       <c r="AP9">
-        <v>0.00375</v>
+        <v>0.003858588143935597</v>
       </c>
       <c r="AQ9">
-        <v>0.1388715895500769</v>
+        <v>0.01446895913836966</v>
       </c>
       <c r="AR9">
-        <v>0.05589321206718759</v>
+        <v>0.0055362417048328</v>
       </c>
       <c r="AS9">
-        <v>0.09296816979976469</v>
+        <v>0.01010124790407258</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2057,70 +2045,70 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.08643744362619533</v>
       </c>
       <c r="L10">
-        <v>0.1235639613455076</v>
+        <v>2.427643560125567</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.7716093609065489</v>
       </c>
       <c r="R10">
-        <v>160.29</v>
+        <v>6.749995</v>
       </c>
       <c r="S10">
-        <v>159.6375242695781</v>
+        <v>6.671275066009981</v>
       </c>
       <c r="T10">
-        <v>159.7959446250085</v>
+        <v>6.581118725286884</v>
       </c>
       <c r="U10">
-        <v>160.29</v>
+        <v>6.749995</v>
       </c>
       <c r="V10">
-        <v>159.21</v>
+        <v>6.715890000000001</v>
       </c>
       <c r="W10">
-        <v>159.6375242695781</v>
+        <v>6.671275066009981</v>
       </c>
       <c r="X10">
-        <v>162.165</v>
+        <v>6.802474955993346</v>
       </c>
       <c r="Y10">
-        <v>-0.00407059536104488</v>
+        <v>-0.01166222108164807</v>
       </c>
       <c r="Z10">
-        <v>0.3479870562250034</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.00407059536104488</v>
+        <v>0.01166222108164807</v>
       </c>
       <c r="AB10">
-        <v>0.3609970303508924</v>
+        <v>0.3816535392984095</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4390029696491076</v>
+        <v>0.4183464607015905</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2132,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>385.8046804532744</v>
       </c>
       <c r="AI10">
-        <v>0.0116975481938986</v>
+        <v>0.007774814054432049</v>
       </c>
       <c r="AJ10">
-        <v>42743.99999999983</v>
+        <v>64310.21970422225</v>
       </c>
       <c r="AK10">
-        <v>42743.99999999983</v>
+        <v>49622.36752573468</v>
       </c>
       <c r="AL10">
-        <v>266.6666666666657</v>
+        <v>7351.46730119573</v>
       </c>
       <c r="AM10">
-        <v>427.4399999999983</v>
+        <v>496.2236752573468</v>
       </c>
       <c r="AN10">
-        <v>0.004274399999999983</v>
+        <v>0.004962236752573468</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>385.8046804532744</v>
       </c>
       <c r="AP10">
-        <v>0.005</v>
+        <v>0.003858046804532744</v>
       </c>
       <c r="AQ10">
-        <v>3.199524838974722</v>
+        <v>0.07392821752644813</v>
       </c>
       <c r="AR10">
-        <v>1.761148429142851</v>
+        <v>0.01435819842779663</v>
       </c>
       <c r="AS10">
-        <v>2.448724403490512</v>
+        <v>0.01742000512362011</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2183,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2215,19 +2203,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="K11">
-        <v>0.02462895362935497</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.350152272313951</v>
+        <v>0.4670013583701229</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2236,46 +2224,46 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.7561572384073387</v>
+        <v>0.75</v>
       </c>
       <c r="R11">
-        <v>6.74808</v>
+        <v>157.169</v>
       </c>
       <c r="S11">
-        <v>6.6660428198669</v>
+        <v>154.9024054285153</v>
       </c>
       <c r="T11">
-        <v>6.588738809647995</v>
+        <v>155.3087750096255</v>
       </c>
       <c r="U11">
-        <v>6.74808</v>
+        <v>157.169</v>
       </c>
       <c r="V11">
-        <v>6.71206</v>
+        <v>152.968</v>
       </c>
       <c r="W11">
-        <v>6.6660428198669</v>
+        <v>154.9024054285153</v>
       </c>
       <c r="X11">
-        <v>6.802771453422067</v>
+        <v>159.044</v>
       </c>
       <c r="Y11">
-        <v>-0.01215711433964922</v>
+        <v>-0.01442138444276345</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>1.208850438125163</v>
       </c>
       <c r="AA11">
-        <v>0.01215711433964922</v>
+        <v>0.01442138444276345</v>
       </c>
       <c r="AB11">
-        <v>0.431565572641554</v>
+        <v>0.4674543362842704</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3684344273584461</v>
+        <v>0.3325456637157296</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2287,46 +2275,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>378.0786192036693</v>
+        <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.008104742893099481</v>
+        <v>0.0119298334913374</v>
       </c>
       <c r="AJ11">
-        <v>61692.271623534</v>
+        <v>41911.73333333318</v>
       </c>
       <c r="AK11">
-        <v>46649.0577419269</v>
+        <v>31433.79999999988</v>
       </c>
       <c r="AL11">
-        <v>6912.937864092734</v>
+        <v>199.9999999999992</v>
       </c>
       <c r="AM11">
-        <v>466.490577419269</v>
+        <v>314.3379999999988</v>
       </c>
       <c r="AN11">
-        <v>0.00466490577419269</v>
+        <v>0.003143379999999988</v>
       </c>
       <c r="AO11">
-        <v>378.0786192036693</v>
+        <v>375</v>
       </c>
       <c r="AP11">
-        <v>0.003780786192036693</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>0.07844947523881489</v>
+        <v>4.397239606930601</v>
       </c>
       <c r="AR11">
-        <v>0.01601756636834938</v>
+        <v>3.435872843204334</v>
       </c>
       <c r="AS11">
-        <v>0.02230717168301981</v>
+        <v>4.345879499608788</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03809357219934806</v>
+        <v>0.031218007895298</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2338,7 +2326,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,51 +169,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1366,naive=0.04591,drift4=0.06992; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1374,naive=0.05343,drift4=0.08357; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=302.3,naive=51.03,drift4=128.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.02423,naive=0.009183,drift4=0.01297; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01682,naive=0.00373,drift4=0.008922; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03224,naive=0.008309,drift4=0.01127; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.04815,naive=0.01252,drift4=0.04475; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.01447,naive=0.005536,drift4=0.0101; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.07393,naive=0.01436,drift4=0.01742; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.397,naive=3.436,drift4=4.346; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=304.7,naive=110.6,drift4=280.9; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1117,naive=0.02276,drift4=0.09684; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03464,naive=0.005901,drift4=0.01927; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04849,naive=0.01135,drift4=0.03203; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.07234,naive=0.008419,drift4=0.01768; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3375,naive=0.04103,drift4=0.07819; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=7.625,naive=4.873,drift4=5.606; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02117,naive=0.006905,drift4=0.01336; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.2224,naive=0.02317,drift4=0.03081; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1311,naive=0.08352,drift4=0.2212; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.6626148758334846</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>7.7836</v>
+        <v>4063.2</v>
       </c>
       <c r="S2">
-        <v>7.777681409236244</v>
+        <v>4066.014869965415</v>
       </c>
       <c r="T2">
-        <v>7.746944271471207</v>
+        <v>4109.25094127953</v>
       </c>
       <c r="U2">
-        <v>7.7836</v>
+        <v>4063.2</v>
       </c>
       <c r="V2">
-        <v>7.8096</v>
+        <v>4005.32</v>
       </c>
       <c r="Y2">
-        <v>-0.0007603924615544941</v>
+        <v>0.0006927716985171295</v>
       </c>
       <c r="AA2">
-        <v>0.0007603924615544941</v>
+        <v>0.0006927716985171295</v>
       </c>
       <c r="AB2">
-        <v>0.4264349228894188</v>
+        <v>0.4726106524264579</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3735650771105812</v>
+        <v>0.3273893475735422</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.1366464391619375</v>
+        <v>338.391731753559</v>
       </c>
       <c r="AR2">
-        <v>0.04591007142001213</v>
+        <v>45.02772599570812</v>
       </c>
       <c r="AS2">
-        <v>0.06992174843283862</v>
+        <v>117.1280743403066</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,7 +963,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -975,19 +975,19 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.05823076207883358</v>
+        <v>0.3849949008583666</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>9.102370000000001</v>
+        <v>4.72932</v>
       </c>
       <c r="S3">
-        <v>9.094629115587862</v>
+        <v>4.730218011817866</v>
       </c>
       <c r="T3">
-        <v>9.047407266769415</v>
+        <v>4.720260610812169</v>
       </c>
       <c r="U3">
-        <v>9.102370000000001</v>
+        <v>4.72932</v>
       </c>
       <c r="V3">
-        <v>9.147290000000002</v>
+        <v>4.745640000000001</v>
       </c>
       <c r="Y3">
-        <v>-0.0008504251543431295</v>
+        <v>0.0001898818049669053</v>
       </c>
       <c r="AA3">
-        <v>0.0008504251543431295</v>
+        <v>0.0001898818049669053</v>
       </c>
       <c r="AB3">
-        <v>0.43728163016232</v>
+        <v>0.4790496765762571</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.36271836983768</v>
+        <v>0.320950323423743</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.1374064622571514</v>
+        <v>0.0558315596963822</v>
       </c>
       <c r="AR3">
-        <v>0.05343121999263051</v>
+        <v>0.01103767580687245</v>
       </c>
       <c r="AS3">
-        <v>0.08356518379825222</v>
+        <v>0.04237614601251664</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1086,7 +1086,7 @@
         <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,19 +1118,19 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.525260554991763</v>
+        <v>0.0007555498663784668</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N4">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -1142,43 +1142,43 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>4101.35</v>
+        <v>0.700045</v>
       </c>
       <c r="S4">
-        <v>4208.183078883262</v>
+        <v>0.7028455477295454</v>
       </c>
       <c r="T4">
-        <v>4409.778127988468</v>
+        <v>0.7023679313895593</v>
       </c>
       <c r="U4">
-        <v>4101.35</v>
+        <v>0.700045</v>
       </c>
       <c r="V4">
-        <v>4027.000000000001</v>
+        <v>0.7050900000000001</v>
       </c>
       <c r="W4">
-        <v>4208.183078883262</v>
+        <v>0.7028455477295454</v>
       </c>
       <c r="X4">
-        <v>3971.485000000001</v>
+        <v>0.692345</v>
       </c>
       <c r="Y4">
-        <v>0.02604827163818299</v>
+        <v>0.004000525294153105</v>
       </c>
       <c r="Z4">
-        <v>0.8226472019655942</v>
+        <v>0.3637074973435566</v>
       </c>
       <c r="AA4">
-        <v>0.02604827163818299</v>
+        <v>0.004000525294153105</v>
       </c>
       <c r="AB4">
-        <v>0.4344895037688049</v>
+        <v>0.4538652206325554</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3655104962311952</v>
+        <v>0.3461347793674446</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1193,22 +1193,22 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.03166396430443632</v>
+        <v>0.01099929290259921</v>
       </c>
       <c r="AJ4">
-        <v>15790.82123743889</v>
+        <v>45457.46753246713</v>
       </c>
       <c r="AK4">
-        <v>15790.82123743889</v>
+        <v>45457.46753246713</v>
       </c>
       <c r="AL4">
-        <v>3.850152081007202</v>
+        <v>64935.06493506437</v>
       </c>
       <c r="AM4">
-        <v>157.9082123743889</v>
+        <v>454.5746753246713</v>
       </c>
       <c r="AN4">
-        <v>0.001579082123743889</v>
+        <v>0.004545746753246713</v>
       </c>
       <c r="AO4">
         <v>500</v>
@@ -1217,19 +1217,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>302.3256723747335</v>
+        <v>0.01706206060231391</v>
       </c>
       <c r="AR4">
-        <v>51.031275208787</v>
+        <v>0.003535137156057618</v>
       </c>
       <c r="AS4">
-        <v>128.6483847079737</v>
+        <v>0.00964506877919202</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1241,7 +1241,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,79 +1261,79 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
         <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.5977178050946401</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>1.349445</v>
+        <v>1.342705</v>
       </c>
       <c r="S5">
-        <v>1.360052436520948</v>
+        <v>1.338934801231477</v>
       </c>
       <c r="T5">
-        <v>1.361755472624392</v>
+        <v>1.332803089970653</v>
       </c>
       <c r="U5">
-        <v>1.349445</v>
+        <v>1.342705</v>
       </c>
       <c r="V5">
-        <v>1.36379</v>
+        <v>1.34491</v>
       </c>
       <c r="W5">
-        <v>1.360052436520948</v>
+        <v>1.338934801231477</v>
       </c>
       <c r="X5">
-        <v>1.33528875</v>
+        <v>1.35686125</v>
       </c>
       <c r="Y5">
-        <v>0.007860591962583366</v>
+        <v>-0.002807912958187575</v>
       </c>
       <c r="Z5">
-        <v>0.7493111891177624</v>
+        <v>0.2663275068272496</v>
       </c>
       <c r="AA5">
-        <v>0.007860591962583366</v>
+        <v>0.002807912958187575</v>
       </c>
       <c r="AB5">
-        <v>0.4269116697396151</v>
+        <v>0.4571107537024985</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3730883302603848</v>
+        <v>0.3428892462975014</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1345,58 +1345,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01049042384091236</v>
+        <v>0.01054308280672224</v>
       </c>
       <c r="AJ5">
-        <v>47662.51655629146</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AK5">
-        <v>35746.88741721859</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AL5">
-        <v>26490.0662251656</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM5">
-        <v>357.4688741721859</v>
+        <v>474.2445916114797</v>
       </c>
       <c r="AN5">
-        <v>0.003574688741721859</v>
+        <v>0.004742445916114797</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.0242332598811832</v>
+        <v>0.0237466901187499</v>
       </c>
       <c r="AR5">
-        <v>0.009182931635909787</v>
+        <v>0.00833652750156021</v>
       </c>
       <c r="AS5">
-        <v>0.01296607082127836</v>
+        <v>0.01270803268709513</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX5" t="s">
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,31 +1416,31 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.1551900343993899</v>
+        <v>9.410748419536978E-05</v>
       </c>
       <c r="M6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O6" t="s">
         <v>72</v>
@@ -1452,43 +1452,43 @@
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>0.7048449999999999</v>
+        <v>1.15109</v>
       </c>
       <c r="S6">
-        <v>0.7100601426739257</v>
+        <v>1.146681949911661</v>
       </c>
       <c r="T6">
-        <v>0.7078605582895873</v>
+        <v>1.13087179095705</v>
       </c>
       <c r="U6">
-        <v>0.7048449999999999</v>
+        <v>1.15109</v>
       </c>
       <c r="V6">
-        <v>0.7156899999999999</v>
+        <v>1.16088</v>
       </c>
       <c r="W6">
-        <v>0.7100601426739257</v>
+        <v>1.146681949911661</v>
       </c>
       <c r="X6">
-        <v>0.6971449999999999</v>
+        <v>1.16409</v>
       </c>
       <c r="Y6">
-        <v>0.007398992223716924</v>
+        <v>-0.003829457373740734</v>
       </c>
       <c r="Z6">
-        <v>0.6772912563539881</v>
+        <v>0.3390807760260937</v>
       </c>
       <c r="AA6">
-        <v>0.007398992223716924</v>
+        <v>0.003829457373740734</v>
       </c>
       <c r="AB6">
-        <v>0.4420311759230134</v>
+        <v>0.4078900567114984</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3579688240769866</v>
+        <v>0.3921099432885016</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1503,22 +1503,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.0109243876313233</v>
+        <v>0.01129364341624027</v>
       </c>
       <c r="AJ6">
-        <v>45769.15584415544</v>
+        <v>44272.69230769226</v>
       </c>
       <c r="AK6">
-        <v>34326.86688311658</v>
+        <v>33204.5192307692</v>
       </c>
       <c r="AL6">
-        <v>48701.29870129827</v>
+        <v>28846.15384615382</v>
       </c>
       <c r="AM6">
-        <v>343.2686688311658</v>
+        <v>332.045192307692</v>
       </c>
       <c r="AN6">
-        <v>0.003432686688311658</v>
+        <v>0.00332045192307692</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1527,31 +1527,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.01681882597198171</v>
+        <v>0.03083654624303067</v>
       </c>
       <c r="AR6">
-        <v>0.003729641222699242</v>
+        <v>0.008137163237798757</v>
       </c>
       <c r="AS6">
-        <v>0.008922321156931307</v>
+        <v>0.01137174250253028</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX6" t="s">
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1574,76 +1574,76 @@
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.008413607076037008</v>
+        <v>0.5106728317218918</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>1.154795</v>
+        <v>7.7765</v>
       </c>
       <c r="S7">
-        <v>1.16301057602103</v>
+        <v>7.745942888098668</v>
       </c>
       <c r="T7">
-        <v>1.164053466470201</v>
+        <v>7.663723439086237</v>
       </c>
       <c r="U7">
-        <v>1.154795</v>
+        <v>7.7765</v>
       </c>
       <c r="V7">
-        <v>1.16609</v>
+        <v>7.813500000000001</v>
       </c>
       <c r="W7">
-        <v>1.16301057602103</v>
+        <v>7.745942888098668</v>
       </c>
       <c r="X7">
-        <v>1.141795</v>
+        <v>7.839425</v>
       </c>
       <c r="Y7">
-        <v>0.007114315546075529</v>
+        <v>-0.003929417077262598</v>
       </c>
       <c r="Z7">
-        <v>0.6319673862330988</v>
+        <v>0.4856116313282882</v>
       </c>
       <c r="AA7">
-        <v>0.007114315546075529</v>
+        <v>0.003929417077262598</v>
       </c>
       <c r="AB7">
-        <v>0.4028531654231196</v>
+        <v>0.4016457016660354</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3971468345768805</v>
+        <v>0.3983542983339646</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,58 +1655,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.01125740932373279</v>
+        <v>0.008091686491352166</v>
       </c>
       <c r="AJ7">
-        <v>44415.19230769227</v>
+        <v>61791.8156535557</v>
       </c>
       <c r="AK7">
-        <v>44415.19230769227</v>
+        <v>46343.86174016677</v>
       </c>
       <c r="AL7">
-        <v>38461.53846153842</v>
+        <v>5959.475566150167</v>
       </c>
       <c r="AM7">
-        <v>444.1519230769227</v>
+        <v>463.4386174016677</v>
       </c>
       <c r="AN7">
-        <v>0.004441519230769227</v>
+        <v>0.004634386174016678</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ7">
-        <v>0.0322368627435243</v>
+        <v>0.1209565048745219</v>
       </c>
       <c r="AR7">
-        <v>0.008308535227457951</v>
+        <v>0.04670154912417359</v>
       </c>
       <c r="AS7">
-        <v>0.01126888345265342</v>
+        <v>0.07536691564671884</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX7" t="s">
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,79 +1726,79 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.3886497203685205</v>
+        <v>0.9663643811290482</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>4.74093</v>
+        <v>157.4315</v>
       </c>
       <c r="S8">
-        <v>4.762884081452667</v>
+        <v>156.708604425747</v>
       </c>
       <c r="T8">
-        <v>4.764809699013573</v>
+        <v>159.2230258079342</v>
       </c>
       <c r="U8">
-        <v>4.74093</v>
+        <v>157.4315</v>
       </c>
       <c r="V8">
-        <v>4.773689999999999</v>
+        <v>153.173</v>
       </c>
       <c r="W8">
-        <v>4.762884081452667</v>
+        <v>156.708604425747</v>
       </c>
       <c r="X8">
-        <v>4.7060825</v>
+        <v>159.0335</v>
       </c>
       <c r="Y8">
-        <v>0.004630754188032066</v>
+        <v>-0.004591810242886871</v>
       </c>
       <c r="Z8">
-        <v>0.6300044896381924</v>
+        <v>0.4512456768121406</v>
       </c>
       <c r="AA8">
-        <v>0.004630754188032066</v>
+        <v>0.004591810242886871</v>
       </c>
       <c r="AB8">
-        <v>0.4790286448438341</v>
+        <v>0.4436186738620447</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3209713551561659</v>
+        <v>0.3563813261379555</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1810,58 +1810,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.007350351091452505</v>
+        <v>0.01017585426042431</v>
       </c>
       <c r="AJ8">
-        <v>68023.96154673951</v>
+        <v>49135.92384519383</v>
       </c>
       <c r="AK8">
-        <v>68023.96154673951</v>
+        <v>36851.94288389538</v>
       </c>
       <c r="AL8">
-        <v>14348.23158045774</v>
+        <v>234.0823970037469</v>
       </c>
       <c r="AM8">
-        <v>680.2396154673951</v>
+        <v>368.5194288389537</v>
       </c>
       <c r="AN8">
-        <v>0.006802396154673951</v>
+        <v>0.003685194288389537</v>
       </c>
       <c r="AO8">
-        <v>499.9999999999999</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP8">
-        <v>0.004999999999999999</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.04814737867715133</v>
+        <v>4.531661960821052</v>
       </c>
       <c r="AR8">
-        <v>0.01251643941727024</v>
+        <v>3.653227493631338</v>
       </c>
       <c r="AS8">
-        <v>0.04475091762952476</v>
+        <v>4.900329354763137</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1884,76 +1884,76 @@
         <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
         <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K9">
-        <v>0.08687051514847721</v>
+        <v>0.3801480452828046</v>
       </c>
       <c r="L9">
-        <v>1.118438100924791</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.7717176287871192</v>
+        <v>0.7148889660378965</v>
       </c>
       <c r="R9">
-        <v>0.806345</v>
+        <v>0.80999</v>
       </c>
       <c r="S9">
-        <v>0.8077972074805991</v>
+        <v>0.8054362345988628</v>
       </c>
       <c r="T9">
-        <v>0.8072005817649544</v>
+        <v>0.7984826919702883</v>
       </c>
       <c r="U9">
-        <v>0.806345</v>
+        <v>0.80999</v>
       </c>
       <c r="V9">
-        <v>0.8093899999999999</v>
+        <v>0.81158</v>
       </c>
       <c r="W9">
-        <v>0.8077972074805991</v>
+        <v>0.8054362345988628</v>
       </c>
       <c r="X9">
-        <v>0.7968649999999999</v>
+        <v>0.8194699999999999</v>
       </c>
       <c r="Y9">
-        <v>0.00180097536488619</v>
+        <v>-0.005622002001428619</v>
       </c>
       <c r="Z9">
-        <v>0.1531864431011769</v>
+        <v>0.4803550001199549</v>
       </c>
       <c r="AA9">
-        <v>0.00180097536488619</v>
+        <v>0.005622002001428619</v>
       </c>
       <c r="AB9">
-        <v>0.4493396938298393</v>
+        <v>0.4448063211097453</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3506603061701606</v>
+        <v>0.3551936788902547</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1965,58 +1965,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>385.8588143935596</v>
+        <v>357.4444830189483</v>
       </c>
       <c r="AI9">
-        <v>0.0117567542429109</v>
+        <v>0.01170384819565672</v>
       </c>
       <c r="AJ9">
-        <v>42528.74472573845</v>
+        <v>42720.99156118149</v>
       </c>
       <c r="AK9">
-        <v>32820.18203503958</v>
+        <v>30540.76548528674</v>
       </c>
       <c r="AL9">
-        <v>40702.40658159916</v>
+        <v>37705.11424250514</v>
       </c>
       <c r="AM9">
-        <v>328.2018203503958</v>
+        <v>305.4076548528674</v>
       </c>
       <c r="AN9">
-        <v>0.003282018203503958</v>
+        <v>0.003054076548528674</v>
       </c>
       <c r="AO9">
-        <v>385.8588143935597</v>
+        <v>357.4444830189483</v>
       </c>
       <c r="AP9">
-        <v>0.003858588143935597</v>
+        <v>0.003574444830189483</v>
       </c>
       <c r="AQ9">
-        <v>0.01446895913836966</v>
+        <v>0.01666352473563732</v>
       </c>
       <c r="AR9">
-        <v>0.0055362417048328</v>
+        <v>0.005130953894725698</v>
       </c>
       <c r="AS9">
-        <v>0.01010124790407258</v>
+        <v>0.009393234093968637</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2048,19 +2048,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K10">
-        <v>0.08643744362619533</v>
+        <v>0.06116447076549618</v>
       </c>
       <c r="L10">
-        <v>2.427643560125567</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2069,46 +2069,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.7716093609065489</v>
+        <v>0.765291117691374</v>
       </c>
       <c r="R10">
-        <v>6.749995</v>
+        <v>6.75752</v>
       </c>
       <c r="S10">
-        <v>6.671275066009981</v>
+        <v>6.716661561932174</v>
       </c>
       <c r="T10">
-        <v>6.581118725286884</v>
+        <v>6.674694860484208</v>
       </c>
       <c r="U10">
-        <v>6.749995</v>
+        <v>6.75752</v>
       </c>
       <c r="V10">
-        <v>6.715890000000001</v>
+        <v>6.733740000000001</v>
       </c>
       <c r="W10">
-        <v>6.671275066009981</v>
+        <v>6.716661561932174</v>
       </c>
       <c r="X10">
-        <v>6.802474955993346</v>
+        <v>6.787095000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.01166222108164807</v>
+        <v>-0.006046365836553427</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>1.381519461295903</v>
       </c>
       <c r="AA10">
-        <v>0.01166222108164807</v>
+        <v>0.006046365836553427</v>
       </c>
       <c r="AB10">
-        <v>0.3816535392984095</v>
+        <v>0.3697923020740288</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4183464607015905</v>
+        <v>0.4302076979259712</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2120,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>385.8046804532744</v>
+        <v>382.645558845687</v>
       </c>
       <c r="AI10">
-        <v>0.007774814054432049</v>
+        <v>0.004376605618629338</v>
       </c>
       <c r="AJ10">
-        <v>64310.21970422225</v>
+        <v>114243.786982248</v>
       </c>
       <c r="AK10">
-        <v>49622.36752573468</v>
+        <v>87429.75542893984</v>
       </c>
       <c r="AL10">
-        <v>7351.46730119573</v>
+        <v>12938.14231092765</v>
       </c>
       <c r="AM10">
-        <v>496.2236752573468</v>
+        <v>874.2975542893984</v>
       </c>
       <c r="AN10">
-        <v>0.004962236752573468</v>
+        <v>0.008742975542893983</v>
       </c>
       <c r="AO10">
-        <v>385.8046804532744</v>
+        <v>382.645558845687</v>
       </c>
       <c r="AP10">
-        <v>0.003858046804532744</v>
+        <v>0.00382645558845687</v>
       </c>
       <c r="AQ10">
-        <v>0.07392821752644813</v>
+        <v>0.08648349179784395</v>
       </c>
       <c r="AR10">
-        <v>0.01435819842779663</v>
+        <v>0.01356666131240972</v>
       </c>
       <c r="AS10">
-        <v>0.01742000512362011</v>
+        <v>0.01862810839268989</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2171,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2191,7 +2191,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2203,19 +2203,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.4670013583701229</v>
+        <v>0.04823018825873739</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2227,43 +2227,43 @@
         <v>0.75</v>
       </c>
       <c r="R11">
-        <v>157.169</v>
+        <v>9.074780000000001</v>
       </c>
       <c r="S11">
-        <v>154.9024054285153</v>
+        <v>8.99934930593551</v>
       </c>
       <c r="T11">
-        <v>155.3087750096255</v>
+        <v>8.936181613393581</v>
       </c>
       <c r="U11">
-        <v>157.169</v>
+        <v>9.074780000000001</v>
       </c>
       <c r="V11">
-        <v>152.968</v>
+        <v>9.059230000000001</v>
       </c>
       <c r="W11">
-        <v>154.9024054285153</v>
+        <v>8.99934930593551</v>
       </c>
       <c r="X11">
-        <v>159.044</v>
+        <v>9.1626125</v>
       </c>
       <c r="Y11">
-        <v>-0.01442138444276345</v>
+        <v>-0.008312123716992611</v>
       </c>
       <c r="Z11">
-        <v>1.208850438125163</v>
+        <v>0.8588016288331816</v>
       </c>
       <c r="AA11">
-        <v>0.01442138444276345</v>
+        <v>0.008312123716992611</v>
       </c>
       <c r="AB11">
-        <v>0.4674543362842704</v>
+        <v>0.5119180819978749</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3325456637157296</v>
+        <v>0.2880819180021251</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2278,22 +2278,22 @@
         <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.0119298334913374</v>
+        <v>0.009678747032985897</v>
       </c>
       <c r="AJ11">
-        <v>41911.73333333318</v>
+        <v>51659.57931289685</v>
       </c>
       <c r="AK11">
-        <v>31433.79999999988</v>
+        <v>38744.68448467264</v>
       </c>
       <c r="AL11">
-        <v>199.9999999999992</v>
+        <v>4269.490222867401</v>
       </c>
       <c r="AM11">
-        <v>314.3379999999988</v>
+        <v>387.4468448467264</v>
       </c>
       <c r="AN11">
-        <v>0.003143379999999988</v>
+        <v>0.003874468448467264</v>
       </c>
       <c r="AO11">
         <v>375</v>
@@ -2302,19 +2302,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>4.397239606930601</v>
+        <v>0.1100741291881027</v>
       </c>
       <c r="AR11">
-        <v>3.435872843204334</v>
+        <v>0.04868229603111702</v>
       </c>
       <c r="AS11">
-        <v>4.345879499608788</v>
+        <v>0.07786363029865694</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.031218007895298</v>
+        <v>0.03659974559473456</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2326,7 +2326,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46265</v>
+        <v>46266</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,51 +169,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>AUDUSD</t>
+    <t>EURUSD</t>
   </si>
   <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=304.7,naive=110.6,drift4=280.9; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1117,naive=0.02276,drift4=0.09684; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03464,naive=0.005901,drift4=0.01927; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04849,naive=0.01135,drift4=0.03203; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.07234,naive=0.008419,drift4=0.01768; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.3375,naive=0.04103,drift4=0.07819; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=7.625,naive=4.873,drift4=5.606; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02117,naive=0.006905,drift4=0.01336; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.2224,naive=0.02317,drift4=0.03081; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1311,naive=0.08352,drift4=0.2212; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03715,naive=0.005511,drift4=0.018; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=7.588,naive=5.262,drift4=6.107; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=316.8,naive=111.6,drift4=274; naive_cap_applied; model_divergence_guard(abs=430.1,thr=389.6)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1206,naive=0.01685,drift4=0.08702; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.07525,naive=0.008745,drift4=0.01688; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04884,naive=0.008684,drift4=0.0291; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3487,naive=0.04014,drift4=0.07166; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02074,naive=0.006911,drift4=0.01036; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1249,naive=0.07133,drift4=0.2103; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.2341,naive=0.02367,drift4=0.02767; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.594074680822617</v>
+        <v>0.04072730525686864</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>4063.2</v>
+        <v>0.700045</v>
       </c>
       <c r="S2">
-        <v>4066.014869965415</v>
+        <v>0.7004714936248078</v>
       </c>
       <c r="T2">
-        <v>4109.25094127953</v>
+        <v>0.6970453055731572</v>
       </c>
       <c r="U2">
-        <v>4063.2</v>
+        <v>0.700045</v>
       </c>
       <c r="V2">
-        <v>4005.32</v>
+        <v>0.7050900000000001</v>
       </c>
       <c r="Y2">
-        <v>0.0006927716985171295</v>
+        <v>0.0006092374416040874</v>
       </c>
       <c r="AA2">
-        <v>0.0006927716985171295</v>
+        <v>0.0006092374416040874</v>
       </c>
       <c r="AB2">
-        <v>0.4726106524264579</v>
+        <v>0.448681601024946</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3273893475735422</v>
+        <v>0.351318398975054</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>338.391731753559</v>
+        <v>0.01604165624241019</v>
       </c>
       <c r="AR2">
-        <v>45.02772599570812</v>
+        <v>0.003410441330768114</v>
       </c>
       <c r="AS2">
-        <v>117.1280743403066</v>
+        <v>0.008646539429707396</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -972,7 +972,7 @@
         <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
         <v>46237</v>
@@ -981,13 +981,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.3849949008583666</v>
+        <v>1.064118146134086</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>4.72932</v>
+        <v>157.4315</v>
       </c>
       <c r="S3">
-        <v>4.730218011817866</v>
+        <v>157.3376530884892</v>
       </c>
       <c r="T3">
-        <v>4.720260610812169</v>
+        <v>160.5267529403962</v>
       </c>
       <c r="U3">
-        <v>4.72932</v>
+        <v>157.4315</v>
       </c>
       <c r="V3">
-        <v>4.745640000000001</v>
+        <v>153.173</v>
       </c>
       <c r="Y3">
-        <v>0.0001898818049669053</v>
+        <v>-0.0005961126681177574</v>
       </c>
       <c r="AA3">
-        <v>0.0001898818049669053</v>
+        <v>0.0005961126681177574</v>
       </c>
       <c r="AB3">
-        <v>0.4790496765762571</v>
+        <v>0.4505118835703935</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.320950323423743</v>
+        <v>0.3494881164296065</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.0558315596963822</v>
+        <v>4.287510781280591</v>
       </c>
       <c r="AR3">
-        <v>0.01103767580687245</v>
+        <v>3.388376437168119</v>
       </c>
       <c r="AS3">
-        <v>0.04237614601251664</v>
+        <v>4.643538007917752</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1115,7 +1115,7 @@
         <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" s="2">
         <v>46237</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.0007555498663784668</v>
+        <v>1.569404174446048</v>
       </c>
       <c r="M4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -1142,43 +1142,43 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>0.700045</v>
+        <v>4063.2</v>
       </c>
       <c r="S4">
-        <v>0.7028455477295454</v>
+        <v>4160.38876517188</v>
       </c>
       <c r="T4">
-        <v>0.7023679313895593</v>
+        <v>4464.335883906268</v>
       </c>
       <c r="U4">
-        <v>0.700045</v>
+        <v>4063.2</v>
       </c>
       <c r="V4">
-        <v>0.7050900000000001</v>
+        <v>4005.32</v>
       </c>
       <c r="W4">
-        <v>0.7028455477295454</v>
+        <v>4160.38876517188</v>
       </c>
       <c r="X4">
-        <v>0.692345</v>
+        <v>3933.335</v>
       </c>
       <c r="Y4">
-        <v>0.004000525294153105</v>
+        <v>0.02391926687632404</v>
       </c>
       <c r="Z4">
-        <v>0.3637074973435566</v>
+        <v>0.7483830529540669</v>
       </c>
       <c r="AA4">
-        <v>0.004000525294153105</v>
+        <v>0.02391926687632404</v>
       </c>
       <c r="AB4">
-        <v>0.4538652206325554</v>
+        <v>0.3</v>
       </c>
       <c r="AC4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD4">
-        <v>0.3461347793674446</v>
+        <v>0.4</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1193,22 +1193,22 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.01099929290259921</v>
+        <v>0.0319612620594605</v>
       </c>
       <c r="AJ4">
-        <v>45457.46753246713</v>
+        <v>15643.93793554847</v>
       </c>
       <c r="AK4">
-        <v>45457.46753246713</v>
+        <v>15643.93793554847</v>
       </c>
       <c r="AL4">
-        <v>64935.06493506437</v>
+        <v>3.850152081007203</v>
       </c>
       <c r="AM4">
-        <v>454.5746753246713</v>
+        <v>156.4393793554847</v>
       </c>
       <c r="AN4">
-        <v>0.004545746753246713</v>
+        <v>0.001564393793554847</v>
       </c>
       <c r="AO4">
         <v>500</v>
@@ -1217,19 +1217,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.01706206060231391</v>
+        <v>297.5309869638194</v>
       </c>
       <c r="AR4">
-        <v>0.003535137156057618</v>
+        <v>40.50565754130037</v>
       </c>
       <c r="AS4">
-        <v>0.00964506877919202</v>
+        <v>86.94534692098031</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1261,13 +1261,13 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
         <v>70</v>
@@ -1279,13 +1279,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.4474181392974408</v>
+        <v>0.3849949008583666</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1297,43 +1297,43 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>1.342705</v>
+        <v>4.72932</v>
       </c>
       <c r="S5">
-        <v>1.338934801231477</v>
+        <v>4.741808524060263</v>
       </c>
       <c r="T5">
-        <v>1.332803089970653</v>
+        <v>4.744448336527471</v>
       </c>
       <c r="U5">
-        <v>1.342705</v>
+        <v>4.72932</v>
       </c>
       <c r="V5">
-        <v>1.34491</v>
+        <v>4.745640000000001</v>
       </c>
       <c r="W5">
-        <v>1.338934801231477</v>
+        <v>4.741808524060263</v>
       </c>
       <c r="X5">
-        <v>1.35686125</v>
+        <v>4.694472500000001</v>
       </c>
       <c r="Y5">
-        <v>-0.002807912958187575</v>
+        <v>0.00264065955787788</v>
       </c>
       <c r="Z5">
-        <v>0.2663275068272496</v>
+        <v>0.3583764706295443</v>
       </c>
       <c r="AA5">
-        <v>0.002807912958187575</v>
+        <v>0.00264065955787788</v>
       </c>
       <c r="AB5">
-        <v>0.4571107537024985</v>
+        <v>0.4762048622104743</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3428892462975014</v>
+        <v>0.3237951377895257</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1348,22 +1348,22 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01054308280672224</v>
+        <v>0.007368395456429236</v>
       </c>
       <c r="AJ5">
-        <v>47424.45916114797</v>
+        <v>67857.37857809041</v>
       </c>
       <c r="AK5">
-        <v>47424.45916114797</v>
+        <v>67857.37857809041</v>
       </c>
       <c r="AL5">
-        <v>35320.0883002208</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM5">
-        <v>474.2445916114797</v>
+        <v>678.5737857809041</v>
       </c>
       <c r="AN5">
-        <v>0.004742445916114797</v>
+        <v>0.006785737857809042</v>
       </c>
       <c r="AO5">
         <v>500</v>
@@ -1372,25 +1372,25 @@
         <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.0237466901187499</v>
+        <v>0.05238300353681248</v>
       </c>
       <c r="AR5">
-        <v>0.00833652750156021</v>
+        <v>0.009322759434679978</v>
       </c>
       <c r="AS5">
-        <v>0.01270803268709513</v>
+        <v>0.03346931469147169</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
         <v>89</v>
@@ -1416,7 +1416,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>68</v>
@@ -1425,7 +1425,7 @@
         <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
         <v>46237</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>9.410748419536978E-05</v>
+        <v>0.02721310628042968</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -1455,10 +1455,10 @@
         <v>1.15109</v>
       </c>
       <c r="S6">
-        <v>1.146681949911661</v>
+        <v>1.149555987510801</v>
       </c>
       <c r="T6">
-        <v>1.13087179095705</v>
+        <v>1.137542076542457</v>
       </c>
       <c r="U6">
         <v>1.15109</v>
@@ -1467,28 +1467,28 @@
         <v>1.16088</v>
       </c>
       <c r="W6">
-        <v>1.146681949911661</v>
+        <v>1.149363365</v>
       </c>
       <c r="X6">
         <v>1.16409</v>
       </c>
       <c r="Y6">
-        <v>-0.003829457373740734</v>
+        <v>-0.001332660773005527</v>
       </c>
       <c r="Z6">
-        <v>0.3390807760260937</v>
+        <v>0.1328180769230768</v>
       </c>
       <c r="AA6">
-        <v>0.003829457373740734</v>
+        <v>0.001332660773005527</v>
       </c>
       <c r="AB6">
-        <v>0.4078900567114984</v>
+        <v>0.4013215874256177</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3921099432885016</v>
+        <v>0.3986784125743823</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1527,19 +1527,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.03083654624303067</v>
+        <v>0.02747164879098828</v>
       </c>
       <c r="AR6">
-        <v>0.008137163237798757</v>
+        <v>0.007624110104774627</v>
       </c>
       <c r="AS6">
-        <v>0.01137174250253028</v>
+        <v>0.01035255048397359</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1589,61 +1589,61 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5106728317218918</v>
+        <v>0.5398017231284329</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>7.7765</v>
+        <v>1.342705</v>
       </c>
       <c r="S7">
-        <v>7.745942888098668</v>
+        <v>1.34049810831042</v>
       </c>
       <c r="T7">
-        <v>7.663723439086237</v>
+        <v>1.336228511088949</v>
       </c>
       <c r="U7">
-        <v>7.7765</v>
+        <v>1.342705</v>
       </c>
       <c r="V7">
-        <v>7.813500000000001</v>
+        <v>1.34491</v>
       </c>
       <c r="W7">
-        <v>7.745942888098668</v>
+        <v>1.34049810831042</v>
       </c>
       <c r="X7">
-        <v>7.839425</v>
+        <v>1.35686125</v>
       </c>
       <c r="Y7">
-        <v>-0.003929417077262598</v>
+        <v>-0.001643616199820258</v>
       </c>
       <c r="Z7">
-        <v>0.4856116313282882</v>
+        <v>0.1558952186899541</v>
       </c>
       <c r="AA7">
-        <v>0.003929417077262598</v>
+        <v>0.001643616199820258</v>
       </c>
       <c r="AB7">
-        <v>0.4016457016660354</v>
+        <v>0.4573975420880934</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3983542983339646</v>
+        <v>0.3426024579119066</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,46 +1655,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008091686491352166</v>
+        <v>0.01054308280672224</v>
       </c>
       <c r="AJ7">
-        <v>61791.8156535557</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AK7">
-        <v>46343.86174016677</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AL7">
-        <v>5959.475566150167</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM7">
-        <v>463.4386174016677</v>
+        <v>474.2445916114797</v>
       </c>
       <c r="AN7">
-        <v>0.004634386174016678</v>
+        <v>0.004742445916114797</v>
       </c>
       <c r="AO7">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.1209565048745219</v>
+        <v>0.02363160056164271</v>
       </c>
       <c r="AR7">
-        <v>0.04670154912417359</v>
+        <v>0.007612012567133518</v>
       </c>
       <c r="AS7">
-        <v>0.07536691564671884</v>
+        <v>0.01098143227806338</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1735,7 +1735,7 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
         <v>46237</v>
@@ -1744,13 +1744,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.9663643811290482</v>
+        <v>0.5106728317218918</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="O8" t="s">
         <v>72</v>
@@ -1762,43 +1762,43 @@
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>157.4315</v>
+        <v>7.7765</v>
       </c>
       <c r="S8">
-        <v>156.708604425747</v>
+        <v>7.735202478734054</v>
       </c>
       <c r="T8">
-        <v>159.2230258079342</v>
+        <v>7.634008277911553</v>
       </c>
       <c r="U8">
-        <v>157.4315</v>
+        <v>7.7765</v>
       </c>
       <c r="V8">
-        <v>153.173</v>
+        <v>7.813500000000001</v>
       </c>
       <c r="W8">
-        <v>156.708604425747</v>
+        <v>7.735202478734054</v>
       </c>
       <c r="X8">
-        <v>159.0335</v>
+        <v>7.839425</v>
       </c>
       <c r="Y8">
-        <v>-0.004591810242886871</v>
+        <v>-0.005310553753738327</v>
       </c>
       <c r="Z8">
-        <v>0.4512456768121406</v>
+        <v>0.656297517138594</v>
       </c>
       <c r="AA8">
-        <v>0.004591810242886871</v>
+        <v>0.005310553753738327</v>
       </c>
       <c r="AB8">
-        <v>0.4436186738620447</v>
+        <v>0.3949904788980218</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3563813261379555</v>
+        <v>0.4050095211019782</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1813,43 +1813,43 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01017585426042431</v>
+        <v>0.008091686491352166</v>
       </c>
       <c r="AJ8">
-        <v>49135.92384519383</v>
+        <v>61791.8156535557</v>
       </c>
       <c r="AK8">
-        <v>36851.94288389538</v>
+        <v>46343.86174016677</v>
       </c>
       <c r="AL8">
-        <v>234.0823970037469</v>
+        <v>5959.475566150167</v>
       </c>
       <c r="AM8">
-        <v>368.5194288389537</v>
+        <v>463.4386174016677</v>
       </c>
       <c r="AN8">
-        <v>0.003685194288389537</v>
+        <v>0.004634386174016678</v>
       </c>
       <c r="AO8">
-        <v>375.0000000000001</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP8">
-        <v>0.003750000000000001</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ8">
-        <v>4.531661960821052</v>
+        <v>0.1192861068869834</v>
       </c>
       <c r="AR8">
-        <v>3.653227493631338</v>
+        <v>0.04342836478344488</v>
       </c>
       <c r="AS8">
-        <v>4.900329354763137</v>
+        <v>0.06784544432034675</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1881,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1890,16 +1890,16 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
         <v>46237</v>
       </c>
       <c r="K9">
-        <v>0.3801480452828046</v>
+        <v>0.1845477155945729</v>
       </c>
       <c r="L9">
-        <v>1.329377158473881</v>
+        <v>1.189516755040264</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1914,16 +1914,16 @@
         <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.7148889660378965</v>
+        <v>0.8615892133040703</v>
       </c>
       <c r="R9">
         <v>0.80999</v>
       </c>
       <c r="S9">
-        <v>0.8054362345988628</v>
+        <v>0.8056020841735145</v>
       </c>
       <c r="T9">
-        <v>0.7984826919702883</v>
+        <v>0.7982498530673742</v>
       </c>
       <c r="U9">
         <v>0.80999</v>
@@ -1932,28 +1932,28 @@
         <v>0.81158</v>
       </c>
       <c r="W9">
-        <v>0.8054362345988628</v>
+        <v>0.8056020841735145</v>
       </c>
       <c r="X9">
         <v>0.8194699999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.005622002001428619</v>
+        <v>-0.005417246912289603</v>
       </c>
       <c r="Z9">
-        <v>0.4803550001199549</v>
+        <v>0.4628603192495212</v>
       </c>
       <c r="AA9">
-        <v>0.005622002001428619</v>
+        <v>0.005417246912289603</v>
       </c>
       <c r="AB9">
-        <v>0.4448063211097453</v>
+        <v>0.4245951567595062</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3551936788902547</v>
+        <v>0.3754048432404938</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1965,7 +1965,7 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>357.4444830189483</v>
+        <v>430.7946066520352</v>
       </c>
       <c r="AI9">
         <v>0.01170384819565672</v>
@@ -1974,37 +1974,37 @@
         <v>42720.99156118149</v>
       </c>
       <c r="AK9">
-        <v>30540.76548528674</v>
+        <v>36807.94551076819</v>
       </c>
       <c r="AL9">
-        <v>37705.11424250514</v>
+        <v>45442.46905612191</v>
       </c>
       <c r="AM9">
-        <v>305.4076548528674</v>
+        <v>368.0794551076818</v>
       </c>
       <c r="AN9">
-        <v>0.003054076548528674</v>
+        <v>0.003680794551076818</v>
       </c>
       <c r="AO9">
-        <v>357.4444830189483</v>
+        <v>430.7946066520352</v>
       </c>
       <c r="AP9">
-        <v>0.003574444830189483</v>
+        <v>0.004307946066520352</v>
       </c>
       <c r="AQ9">
-        <v>0.01666352473563732</v>
+        <v>0.01668036818180997</v>
       </c>
       <c r="AR9">
-        <v>0.005130953894725698</v>
+        <v>0.004873063905075095</v>
       </c>
       <c r="AS9">
-        <v>0.009393234093968637</v>
+        <v>0.007652326696198588</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2036,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2045,22 +2045,22 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
         <v>46237</v>
       </c>
       <c r="K10">
-        <v>0.06116447076549618</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.397867003755076</v>
+        <v>0.04823018825873739</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2069,46 +2069,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.765291117691374</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.75752</v>
+        <v>9.074780000000001</v>
       </c>
       <c r="S10">
-        <v>6.716661561932174</v>
+        <v>9.001154940299934</v>
       </c>
       <c r="T10">
-        <v>6.674694860484208</v>
+        <v>8.939724052964618</v>
       </c>
       <c r="U10">
-        <v>6.75752</v>
+        <v>9.074780000000001</v>
       </c>
       <c r="V10">
-        <v>6.733740000000001</v>
+        <v>9.059230000000001</v>
       </c>
       <c r="W10">
-        <v>6.716661561932174</v>
+        <v>9.001154940299934</v>
       </c>
       <c r="X10">
-        <v>6.787095000000001</v>
+        <v>9.1626125</v>
       </c>
       <c r="Y10">
-        <v>-0.006046365836553427</v>
+        <v>-0.008113150919368506</v>
       </c>
       <c r="Z10">
-        <v>1.381519461295903</v>
+        <v>0.8382439267932388</v>
       </c>
       <c r="AA10">
-        <v>0.006046365836553427</v>
+        <v>0.008113150919368506</v>
       </c>
       <c r="AB10">
-        <v>0.3697923020740288</v>
+        <v>0.5119833884246214</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4302076979259712</v>
+        <v>0.2880166115753786</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2120,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>382.645558845687</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004376605618629338</v>
+        <v>0.009678747032985897</v>
       </c>
       <c r="AJ10">
-        <v>114243.786982248</v>
+        <v>51659.57931289685</v>
       </c>
       <c r="AK10">
-        <v>87429.75542893984</v>
+        <v>38744.68448467264</v>
       </c>
       <c r="AL10">
-        <v>12938.14231092765</v>
+        <v>4269.490222867401</v>
       </c>
       <c r="AM10">
-        <v>874.2975542893984</v>
+        <v>387.4468448467264</v>
       </c>
       <c r="AN10">
-        <v>0.008742975542893983</v>
+        <v>0.003874468448467264</v>
       </c>
       <c r="AO10">
-        <v>382.645558845687</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.00382645558845687</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08648349179784395</v>
+        <v>0.1210297015555979</v>
       </c>
       <c r="AR10">
-        <v>0.01356666131240972</v>
+        <v>0.0437427996913252</v>
       </c>
       <c r="AS10">
-        <v>0.01862810839268989</v>
+        <v>0.06295515583840698</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2191,7 +2191,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2200,22 +2200,22 @@
         <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2">
         <v>46237</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.08246748434534681</v>
       </c>
       <c r="L11">
-        <v>0.04823018825873739</v>
+        <v>2.42396697331862</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2224,46 +2224,46 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
+        <v>0.7706168710863367</v>
       </c>
       <c r="R11">
-        <v>9.074780000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="S11">
-        <v>8.99934930593551</v>
+        <v>6.689529260883468</v>
       </c>
       <c r="T11">
-        <v>8.936181613393581</v>
+        <v>6.597531674525678</v>
       </c>
       <c r="U11">
-        <v>9.074780000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="V11">
-        <v>9.059230000000001</v>
+        <v>6.733740000000001</v>
       </c>
       <c r="W11">
-        <v>8.99934930593551</v>
+        <v>6.689529260883468</v>
       </c>
       <c r="X11">
-        <v>9.1626125</v>
+        <v>6.802847159411022</v>
       </c>
       <c r="Y11">
-        <v>-0.008312123716992611</v>
+        <v>-0.01006149284301525</v>
       </c>
       <c r="Z11">
-        <v>0.8588016288331816</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.008312123716992611</v>
+        <v>0.01006149284301525</v>
       </c>
       <c r="AB11">
-        <v>0.5119180819978749</v>
+        <v>0.3594988701756279</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.2880819180021251</v>
+        <v>0.4405011298243722</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2275,46 +2275,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>375</v>
+        <v>385.3084355431683</v>
       </c>
       <c r="AI11">
-        <v>0.009678747032985897</v>
+        <v>0.0067076618953435</v>
       </c>
       <c r="AJ11">
-        <v>51659.57931289685</v>
+        <v>74541.62237173926</v>
       </c>
       <c r="AK11">
-        <v>38744.68448467264</v>
+        <v>57443.03179780898</v>
       </c>
       <c r="AL11">
-        <v>4269.490222867401</v>
+        <v>8500.608477342128</v>
       </c>
       <c r="AM11">
-        <v>387.4468448467264</v>
+        <v>574.4303179780898</v>
       </c>
       <c r="AN11">
-        <v>0.003874468448467264</v>
+        <v>0.005744303179780898</v>
       </c>
       <c r="AO11">
-        <v>375</v>
+        <v>385.3084355431683</v>
       </c>
       <c r="AP11">
-        <v>0.00375</v>
+        <v>0.003853084355431683</v>
       </c>
       <c r="AQ11">
-        <v>0.1100741291881027</v>
+        <v>0.07949451275789235</v>
       </c>
       <c r="AR11">
-        <v>0.04868229603111702</v>
+        <v>0.01222470433969592</v>
       </c>
       <c r="AS11">
-        <v>0.07786363029865694</v>
+        <v>0.0178227941071116</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03659974559473456</v>
+        <v>0.03434698184389726</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,51 +169,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=316.8,naive=111.6,drift4=274; naive_cap_applied</t>
+  </si>
+  <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03715,naive=0.005511,drift4=0.018; naive_cap_applied</t>
   </si>
   <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1505,naive=0.02849,drift4=0.1031; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04884,naive=0.008684,drift4=0.0291; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.07525,naive=0.008745,drift4=0.01688; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.351,naive=0.04196,drift4=0.07358; naive_cap_applied</t>
+  </si>
+  <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=7.588,naive=5.262,drift4=6.107; naive_cap_applied</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=316.8,naive=111.6,drift4=274; naive_cap_applied; model_divergence_guard(abs=430.1,thr=389.6)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=0.1206,naive=0.01685,drift4=0.08702; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.07525,naive=0.008745,drift4=0.01688; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04884,naive=0.008684,drift4=0.0291; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.3487,naive=0.04014,drift4=0.07166; naive_cap_applied</t>
-  </si>
-  <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02074,naive=0.006911,drift4=0.01036; naive_cap_applied</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1249,naive=0.07133,drift4=0.2103; naive_cap_applied</t>
-  </si>
-  <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.2341,naive=0.02367,drift4=0.02767; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1246,naive=0.07174,drift4=0.2108; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.04072730525686864</v>
+        <v>1.594074680822617</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0.700045</v>
+        <v>4063.2</v>
       </c>
       <c r="S2">
-        <v>0.7004714936248078</v>
+        <v>4065.08861591256</v>
       </c>
       <c r="T2">
-        <v>0.6970453055731572</v>
+        <v>4108.237008013593</v>
       </c>
       <c r="U2">
-        <v>0.700045</v>
+        <v>4063.2</v>
       </c>
       <c r="V2">
-        <v>0.7050900000000001</v>
+        <v>4005.32</v>
       </c>
       <c r="Y2">
-        <v>0.0006092374416040874</v>
+        <v>0.0004648099804490189</v>
       </c>
       <c r="AA2">
-        <v>0.0006092374416040874</v>
+        <v>0.0004648099804490189</v>
       </c>
       <c r="AB2">
-        <v>0.448681601024946</v>
+        <v>0.4682667796385537</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.351318398975054</v>
+        <v>0.3317332203614463</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01604165624241019</v>
+        <v>339.7893926326376</v>
       </c>
       <c r="AR2">
-        <v>0.003410441330768114</v>
+        <v>41.32982393550433</v>
       </c>
       <c r="AS2">
-        <v>0.008646539429707396</v>
+        <v>93.61548143416439</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,13 +966,13 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
         <v>46237</v>
@@ -981,52 +981,61 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.064118146134086</v>
+        <v>0.0007555498663784668</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>157.4315</v>
+        <v>0.700045</v>
       </c>
       <c r="S3">
-        <v>157.3376530884892</v>
+        <v>0.7028113384892352</v>
       </c>
       <c r="T3">
-        <v>160.5267529403962</v>
+        <v>0.7022602394128384</v>
       </c>
       <c r="U3">
-        <v>157.4315</v>
+        <v>0.700045</v>
       </c>
       <c r="V3">
-        <v>153.173</v>
+        <v>0.7050900000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.7028113384892352</v>
+      </c>
+      <c r="X3">
+        <v>0.692345</v>
       </c>
       <c r="Y3">
-        <v>-0.0005961126681177574</v>
+        <v>0.003951658092315682</v>
+      </c>
+      <c r="Z3">
+        <v>0.3592647388617022</v>
       </c>
       <c r="AA3">
-        <v>0.0005961126681177574</v>
+        <v>0.003951658092315682</v>
       </c>
       <c r="AB3">
-        <v>0.4505118835703935</v>
+        <v>0.448681601024946</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3494881164296065</v>
+        <v>0.351318398975054</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1038,55 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI3">
+        <v>0.01099929290259921</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>45457.46753246713</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>45457.46753246713</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>64935.06493506437</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>454.5746753246713</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.004545746753246713</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>4.287510781280591</v>
+        <v>0.01675139345483889</v>
       </c>
       <c r="AR3">
-        <v>3.388376437168119</v>
+        <v>0.00328516938985525</v>
       </c>
       <c r="AS3">
-        <v>4.643538007917752</v>
+        <v>0.008450633226945127</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1115,22 +1127,22 @@
         <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.569404174446048</v>
+        <v>0.1900347107390751</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -1142,43 +1154,43 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>4063.2</v>
+        <v>4.75301</v>
       </c>
       <c r="S4">
-        <v>4160.38876517188</v>
+        <v>4.76023194156474</v>
       </c>
       <c r="T4">
-        <v>4464.335883906268</v>
+        <v>4.73975183916744</v>
       </c>
       <c r="U4">
-        <v>4063.2</v>
+        <v>4.75301</v>
       </c>
       <c r="V4">
-        <v>4005.32</v>
+        <v>4.793019999999999</v>
       </c>
       <c r="W4">
-        <v>4160.38876517188</v>
+        <v>4.76023194156474</v>
       </c>
       <c r="X4">
-        <v>3933.335</v>
+        <v>4.7181625</v>
       </c>
       <c r="Y4">
-        <v>0.02391926687632404</v>
+        <v>0.001519445901595057</v>
       </c>
       <c r="Z4">
-        <v>0.7483830529540669</v>
+        <v>0.2072441800628549</v>
       </c>
       <c r="AA4">
-        <v>0.02391926687632404</v>
+        <v>0.001519445901595057</v>
       </c>
       <c r="AB4">
-        <v>0.3</v>
+        <v>0.465307193788246</v>
       </c>
       <c r="AC4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4</v>
+        <v>0.334692806211754</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1193,43 +1205,43 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.0319612620594605</v>
+        <v>0.007331669826068097</v>
       </c>
       <c r="AJ4">
-        <v>15643.93793554847</v>
+        <v>68197.28818423144</v>
       </c>
       <c r="AK4">
-        <v>15643.93793554847</v>
+        <v>68197.28818423144</v>
       </c>
       <c r="AL4">
-        <v>3.850152081007203</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM4">
-        <v>156.4393793554847</v>
+        <v>681.9728818423143</v>
       </c>
       <c r="AN4">
-        <v>0.001564393793554847</v>
+        <v>0.006819728818423143</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ4">
-        <v>297.5309869638194</v>
+        <v>0.06225131355920498</v>
       </c>
       <c r="AR4">
-        <v>40.50565754130037</v>
+        <v>0.01464567725302561</v>
       </c>
       <c r="AS4">
-        <v>86.94534692098031</v>
+        <v>0.031890671349915</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1241,7 +1253,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,13 +1273,13 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I5" t="s">
         <v>70</v>
@@ -1279,13 +1291,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.3849949008583666</v>
+        <v>0.4474181392974408</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1297,43 +1309,43 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>4.72932</v>
+        <v>1.342705</v>
       </c>
       <c r="S5">
-        <v>4.741808524060263</v>
+        <v>1.338636983380847</v>
       </c>
       <c r="T5">
-        <v>4.744448336527471</v>
+        <v>1.332159567209021</v>
       </c>
       <c r="U5">
-        <v>4.72932</v>
+        <v>1.342705</v>
       </c>
       <c r="V5">
-        <v>4.745640000000001</v>
+        <v>1.34491</v>
       </c>
       <c r="W5">
-        <v>4.741808524060263</v>
+        <v>1.338636983380847</v>
       </c>
       <c r="X5">
-        <v>4.694472500000001</v>
+        <v>1.35686125</v>
       </c>
       <c r="Y5">
-        <v>0.00264065955787788</v>
+        <v>-0.003029717338620846</v>
       </c>
       <c r="Z5">
-        <v>0.3583764706295443</v>
+        <v>0.2873654123904925</v>
       </c>
       <c r="AA5">
-        <v>0.00264065955787788</v>
+        <v>0.003029717338620846</v>
       </c>
       <c r="AB5">
-        <v>0.4762048622104743</v>
+        <v>0.4573975420880934</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3237951377895257</v>
+        <v>0.3426024579119066</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1348,22 +1360,22 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.007368395456429236</v>
+        <v>0.01054308280672224</v>
       </c>
       <c r="AJ5">
-        <v>67857.37857809041</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AK5">
-        <v>67857.37857809041</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AL5">
-        <v>14348.23158045774</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM5">
-        <v>678.5737857809041</v>
+        <v>474.2445916114797</v>
       </c>
       <c r="AN5">
-        <v>0.006785737857809042</v>
+        <v>0.004742445916114797</v>
       </c>
       <c r="AO5">
         <v>500</v>
@@ -1372,31 +1384,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.05238300353681248</v>
+        <v>0.02265873025495328</v>
       </c>
       <c r="AR5">
-        <v>0.009322759434679978</v>
+        <v>0.007809165872265232</v>
       </c>
       <c r="AS5">
-        <v>0.03346931469147169</v>
+        <v>0.01059393436516914</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX5" t="s">
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,7 +1428,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
         <v>68</v>
@@ -1425,7 +1437,7 @@
         <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2">
         <v>46237</v>
@@ -1434,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.02721310628042968</v>
+        <v>9.410748419536978E-05</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -1455,10 +1467,10 @@
         <v>1.15109</v>
       </c>
       <c r="S6">
-        <v>1.149555987510801</v>
+        <v>1.146805873170796</v>
       </c>
       <c r="T6">
-        <v>1.137542076542457</v>
+        <v>1.130689431615861</v>
       </c>
       <c r="U6">
         <v>1.15109</v>
@@ -1467,19 +1479,19 @@
         <v>1.16088</v>
       </c>
       <c r="W6">
-        <v>1.149363365</v>
+        <v>1.146805873170796</v>
       </c>
       <c r="X6">
         <v>1.16409</v>
       </c>
       <c r="Y6">
-        <v>-0.001332660773005527</v>
+        <v>-0.003721800058383102</v>
       </c>
       <c r="Z6">
-        <v>0.1328180769230768</v>
+        <v>0.3295482176310924</v>
       </c>
       <c r="AA6">
-        <v>0.001332660773005527</v>
+        <v>0.003721800058383102</v>
       </c>
       <c r="AB6">
         <v>0.4013215874256177</v>
@@ -1527,19 +1539,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.02747164879098828</v>
+        <v>0.02846851557150682</v>
       </c>
       <c r="AR6">
-        <v>0.007624110104774627</v>
+        <v>0.008046024784723884</v>
       </c>
       <c r="AS6">
-        <v>0.01035255048397359</v>
+        <v>0.01049370758527635</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1551,7 +1563,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,67 +1595,67 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5398017231284329</v>
+        <v>0.3959586949593628</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>1.342705</v>
+        <v>7.7793</v>
       </c>
       <c r="S7">
-        <v>1.34049810831042</v>
+        <v>7.749930192060869</v>
       </c>
       <c r="T7">
-        <v>1.336228511088949</v>
+        <v>7.664014079074487</v>
       </c>
       <c r="U7">
-        <v>1.342705</v>
+        <v>7.7793</v>
       </c>
       <c r="V7">
-        <v>1.34491</v>
+        <v>7.819100000000001</v>
       </c>
       <c r="W7">
-        <v>1.34049810831042</v>
+        <v>7.749930192060869</v>
       </c>
       <c r="X7">
-        <v>1.35686125</v>
+        <v>7.842225</v>
       </c>
       <c r="Y7">
-        <v>-0.001643616199820258</v>
+        <v>-0.003775379267945905</v>
       </c>
       <c r="Z7">
-        <v>0.1558952186899541</v>
+        <v>0.4667430741220742</v>
       </c>
       <c r="AA7">
-        <v>0.001643616199820258</v>
+        <v>0.003775379267945905</v>
       </c>
       <c r="AB7">
-        <v>0.4573975420880934</v>
+        <v>0.3946832025360349</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3426024579119066</v>
+        <v>0.405316797463965</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,46 +1667,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.01054308280672224</v>
+        <v>0.008088774054220833</v>
       </c>
       <c r="AJ7">
-        <v>47424.45916114797</v>
+        <v>61814.06436233599</v>
       </c>
       <c r="AK7">
-        <v>47424.45916114797</v>
+        <v>46360.54827175199</v>
       </c>
       <c r="AL7">
-        <v>35320.0883002208</v>
+        <v>5959.475566150167</v>
       </c>
       <c r="AM7">
-        <v>474.2445916114797</v>
+        <v>463.6054827175199</v>
       </c>
       <c r="AN7">
-        <v>0.004742445916114797</v>
+        <v>0.0046360548271752</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ7">
-        <v>0.02363160056164271</v>
+        <v>0.1126539624027407</v>
       </c>
       <c r="AR7">
-        <v>0.007612012567133518</v>
+        <v>0.04702533565862096</v>
       </c>
       <c r="AS7">
-        <v>0.01098143227806338</v>
+        <v>0.07292118926850866</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1706,7 +1718,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1735,7 +1747,7 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
         <v>46237</v>
@@ -1744,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.5106728317218918</v>
+        <v>0.9663643811290482</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
         <v>72</v>
@@ -1762,43 +1774,43 @@
         <v>0.75</v>
       </c>
       <c r="R8">
-        <v>7.7765</v>
+        <v>157.4315</v>
       </c>
       <c r="S8">
-        <v>7.735202478734054</v>
+        <v>156.7787452466943</v>
       </c>
       <c r="T8">
-        <v>7.634008277911553</v>
+        <v>159.2861467273804</v>
       </c>
       <c r="U8">
-        <v>7.7765</v>
+        <v>157.4315</v>
       </c>
       <c r="V8">
-        <v>7.813500000000001</v>
+        <v>153.173</v>
       </c>
       <c r="W8">
-        <v>7.735202478734054</v>
+        <v>156.7787452466943</v>
       </c>
       <c r="X8">
-        <v>7.839425</v>
+        <v>159.0335</v>
       </c>
       <c r="Y8">
-        <v>-0.005310553753738327</v>
+        <v>-0.004146277925991216</v>
       </c>
       <c r="Z8">
-        <v>0.656297517138594</v>
+        <v>0.4074623928250252</v>
       </c>
       <c r="AA8">
-        <v>0.005310553753738327</v>
+        <v>0.004146277925991216</v>
       </c>
       <c r="AB8">
-        <v>0.3949904788980218</v>
+        <v>0.4505118835703935</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.4050095211019782</v>
+        <v>0.3494881164296065</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1813,43 +1825,43 @@
         <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.008091686491352166</v>
+        <v>0.01017585426042431</v>
       </c>
       <c r="AJ8">
-        <v>61791.8156535557</v>
+        <v>49135.92384519383</v>
       </c>
       <c r="AK8">
-        <v>46343.86174016677</v>
+        <v>36851.94288389538</v>
       </c>
       <c r="AL8">
-        <v>5959.475566150167</v>
+        <v>234.0823970037469</v>
       </c>
       <c r="AM8">
-        <v>463.4386174016677</v>
+        <v>368.5194288389537</v>
       </c>
       <c r="AN8">
-        <v>0.004634386174016678</v>
+        <v>0.003685194288389537</v>
       </c>
       <c r="AO8">
-        <v>374.9999999999999</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP8">
-        <v>0.003749999999999999</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.1192861068869834</v>
+        <v>4.507903295516781</v>
       </c>
       <c r="AR8">
-        <v>0.04342836478344488</v>
+        <v>3.625516382814196</v>
       </c>
       <c r="AS8">
-        <v>0.06784544432034675</v>
+        <v>4.878560805807377</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1861,7 +1873,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1881,7 +1893,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1890,16 +1902,16 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
         <v>46237</v>
       </c>
       <c r="K9">
-        <v>0.1845477155945729</v>
+        <v>0.3801480452828046</v>
       </c>
       <c r="L9">
-        <v>1.189516755040264</v>
+        <v>1.329377158473881</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1914,16 +1926,16 @@
         <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.8615892133040703</v>
+        <v>0.7148889660378965</v>
       </c>
       <c r="R9">
         <v>0.80999</v>
       </c>
       <c r="S9">
-        <v>0.8056020841735145</v>
+        <v>0.8056397540583552</v>
       </c>
       <c r="T9">
-        <v>0.7982498530673742</v>
+        <v>0.7983385726023028</v>
       </c>
       <c r="U9">
         <v>0.80999</v>
@@ -1932,19 +1944,19 @@
         <v>0.81158</v>
       </c>
       <c r="W9">
-        <v>0.8056020841735145</v>
+        <v>0.8056397540583552</v>
       </c>
       <c r="X9">
         <v>0.8194699999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.005417246912289603</v>
+        <v>-0.005370740307466502</v>
       </c>
       <c r="Z9">
-        <v>0.4628603192495212</v>
+        <v>0.4588867027051475</v>
       </c>
       <c r="AA9">
-        <v>0.005417246912289603</v>
+        <v>0.005370740307466502</v>
       </c>
       <c r="AB9">
         <v>0.4245951567595062</v>
@@ -1965,7 +1977,7 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>430.7946066520352</v>
+        <v>357.4444830189483</v>
       </c>
       <c r="AI9">
         <v>0.01170384819565672</v>
@@ -1974,37 +1986,37 @@
         <v>42720.99156118149</v>
       </c>
       <c r="AK9">
-        <v>36807.94551076819</v>
+        <v>30540.76548528674</v>
       </c>
       <c r="AL9">
-        <v>45442.46905612191</v>
+        <v>37705.11424250514</v>
       </c>
       <c r="AM9">
-        <v>368.0794551076818</v>
+        <v>305.4076548528674</v>
       </c>
       <c r="AN9">
-        <v>0.003680794551076818</v>
+        <v>0.003054076548528674</v>
       </c>
       <c r="AO9">
-        <v>430.7946066520352</v>
+        <v>357.4444830189483</v>
       </c>
       <c r="AP9">
-        <v>0.004307946066520352</v>
+        <v>0.003574444830189483</v>
       </c>
       <c r="AQ9">
-        <v>0.01668036818180997</v>
+        <v>0.01630021285275825</v>
       </c>
       <c r="AR9">
-        <v>0.004873063905075095</v>
+        <v>0.00505715480130211</v>
       </c>
       <c r="AS9">
-        <v>0.007652326696198588</v>
+        <v>0.008203558543996467</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2016,7 +2028,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,7 +2048,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2045,22 +2057,22 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
         <v>46237</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.06116447076549618</v>
       </c>
       <c r="L10">
-        <v>0.04823018825873739</v>
+        <v>2.397867003755076</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2069,46 +2081,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.765291117691374</v>
       </c>
       <c r="R10">
-        <v>9.074780000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="S10">
-        <v>9.001154940299934</v>
+        <v>6.717657098536375</v>
       </c>
       <c r="T10">
-        <v>8.939724052964618</v>
+        <v>6.67577347161162</v>
       </c>
       <c r="U10">
-        <v>9.074780000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="V10">
-        <v>9.059230000000001</v>
+        <v>6.733740000000001</v>
       </c>
       <c r="W10">
-        <v>9.001154940299934</v>
+        <v>6.717657098536375</v>
       </c>
       <c r="X10">
-        <v>9.1626125</v>
+        <v>6.787095000000001</v>
       </c>
       <c r="Y10">
-        <v>-0.008113150919368506</v>
+        <v>-0.00589904306071235</v>
       </c>
       <c r="Z10">
-        <v>0.8382439267932388</v>
+        <v>1.34785803765426</v>
       </c>
       <c r="AA10">
-        <v>0.008113150919368506</v>
+        <v>0.00589904306071235</v>
       </c>
       <c r="AB10">
-        <v>0.5119833884246214</v>
+        <v>0.3594988701756279</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.2880166115753786</v>
+        <v>0.4405011298243722</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2120,46 +2132,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>382.645558845687</v>
       </c>
       <c r="AI10">
-        <v>0.009678747032985897</v>
+        <v>0.004376605618629338</v>
       </c>
       <c r="AJ10">
-        <v>51659.57931289685</v>
+        <v>114243.786982248</v>
       </c>
       <c r="AK10">
-        <v>38744.68448467264</v>
+        <v>87429.75542893984</v>
       </c>
       <c r="AL10">
-        <v>4269.490222867401</v>
+        <v>12938.14231092765</v>
       </c>
       <c r="AM10">
-        <v>387.4468448467264</v>
+        <v>874.2975542893984</v>
       </c>
       <c r="AN10">
-        <v>0.003874468448467264</v>
+        <v>0.008742975542893983</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>382.645558845687</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.00382645558845687</v>
       </c>
       <c r="AQ10">
-        <v>0.1210297015555979</v>
+        <v>0.08089705333325507</v>
       </c>
       <c r="AR10">
-        <v>0.0437427996913252</v>
+        <v>0.01280502105360233</v>
       </c>
       <c r="AS10">
-        <v>0.06295515583840698</v>
+        <v>0.01680307324625755</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2171,7 +2183,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2191,7 +2203,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2200,22 +2212,22 @@
         <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K11">
-        <v>0.08246748434534681</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.42396697331862</v>
+        <v>0.04421110681978428</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2224,46 +2236,46 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.7706168710863367</v>
+        <v>0.75</v>
       </c>
       <c r="R11">
-        <v>6.75752</v>
+        <v>9.074170000000001</v>
       </c>
       <c r="S11">
-        <v>6.689529260883468</v>
+        <v>8.99556451768844</v>
       </c>
       <c r="T11">
-        <v>6.597531674525678</v>
+        <v>8.929811526364528</v>
       </c>
       <c r="U11">
-        <v>6.75752</v>
+        <v>9.074170000000001</v>
       </c>
       <c r="V11">
-        <v>6.733740000000001</v>
+        <v>9.058010000000001</v>
       </c>
       <c r="W11">
-        <v>6.689529260883468</v>
+        <v>8.99556451768844</v>
       </c>
       <c r="X11">
-        <v>6.802847159411022</v>
+        <v>9.1620025</v>
       </c>
       <c r="Y11">
-        <v>-0.01006149284301525</v>
+        <v>-0.008662553413872667</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.8949475685146292</v>
       </c>
       <c r="AA11">
-        <v>0.01006149284301525</v>
+        <v>0.008662553413872667</v>
       </c>
       <c r="AB11">
-        <v>0.3594988701756279</v>
+        <v>0.5123109538598168</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4405011298243722</v>
+        <v>0.2876890461401832</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2275,46 +2287,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>385.3084355431683</v>
+        <v>375</v>
       </c>
       <c r="AI11">
-        <v>0.0067076618953435</v>
+        <v>0.009679397674938839</v>
       </c>
       <c r="AJ11">
-        <v>74541.62237173926</v>
+        <v>51656.10679418225</v>
       </c>
       <c r="AK11">
-        <v>57443.03179780898</v>
+        <v>38742.08009563669</v>
       </c>
       <c r="AL11">
-        <v>8500.608477342128</v>
+        <v>4269.490222867401</v>
       </c>
       <c r="AM11">
-        <v>574.4303179780898</v>
+        <v>387.4208009563669</v>
       </c>
       <c r="AN11">
-        <v>0.005744303179780898</v>
+        <v>0.003874208009563669</v>
       </c>
       <c r="AO11">
-        <v>385.3084355431683</v>
+        <v>375</v>
       </c>
       <c r="AP11">
-        <v>0.003853084355431683</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ11">
-        <v>0.07949451275789235</v>
+        <v>0.1083533428242224</v>
       </c>
       <c r="AR11">
-        <v>0.01222470433969592</v>
+        <v>0.04574422943305893</v>
       </c>
       <c r="AS11">
-        <v>0.0178227941071116</v>
+        <v>0.06464705930244218</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03434698184389726</v>
+        <v>0.04342088262741264</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2326,7 +2338,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,51 +169,51 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>EURUSD</t>
+    <t>USDCHF</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=316.8,naive=111.6,drift4=274; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.03715,naive=0.005511,drift4=0.018; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.1505,naive=0.02849,drift4=0.1031; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.04884,naive=0.008684,drift4=0.0291; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.07525,naive=0.008745,drift4=0.01688; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.351,naive=0.04196,drift4=0.07358; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=7.588,naive=5.262,drift4=6.107; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02074,naive=0.006911,drift4=0.01036; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.2341,naive=0.02367,drift4=0.02767; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=0.1246,naive=0.07174,drift4=0.2108; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.246,naive=3.317,drift4=4.575; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01566,naive=0.003214,drift4=0.00715; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=295.8,naive=36.85,drift4=62.53; naive_cap_applied; model_divergence_guard(abs=426.8,thr=389.6)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.05449,naive=0.01336,drift4=0.01525; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02438,naive=0.007462,drift4=0.00932; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0224,naive=0.007159,drift4=0.009352; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01682,naive=0.004755,drift4=0.006645; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1094,naive=0.04324,drift4=0.06489; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1199,naive=0.04129,drift4=0.05451; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.0758,naive=0.0113,drift4=0.01559; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.594074680822617</v>
+        <v>1.064118146134086</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>4063.2</v>
+        <v>157.4315</v>
       </c>
       <c r="S2">
-        <v>4065.08861591256</v>
+        <v>157.5587370547433</v>
       </c>
       <c r="T2">
-        <v>4108.237008013593</v>
+        <v>160.6115964456177</v>
       </c>
       <c r="U2">
-        <v>4063.2</v>
+        <v>157.4315</v>
       </c>
       <c r="V2">
-        <v>4005.32</v>
+        <v>153.173</v>
       </c>
       <c r="Y2">
-        <v>0.0004648099804490189</v>
+        <v>0.0008082058212196847</v>
       </c>
       <c r="AA2">
-        <v>0.0004648099804490189</v>
+        <v>0.0008082058212196847</v>
       </c>
       <c r="AB2">
-        <v>0.4682667796385537</v>
+        <v>0.4750946069705661</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3317332203614463</v>
+        <v>0.3249053930294338</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>339.7893926326376</v>
+        <v>4.2464036093366</v>
       </c>
       <c r="AR2">
-        <v>41.32982393550433</v>
+        <v>3.317222312751193</v>
       </c>
       <c r="AS2">
-        <v>93.61548143416439</v>
+        <v>4.575264586318733</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -966,13 +966,13 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
         <v>46237</v>
@@ -981,31 +981,31 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.0007555498663784668</v>
+        <v>0.04072730525686864</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0.700045</v>
       </c>
       <c r="S3">
-        <v>0.7028113384892352</v>
+        <v>0.7005406522799369</v>
       </c>
       <c r="T3">
-        <v>0.7022602394128384</v>
+        <v>0.6969113792643779</v>
       </c>
       <c r="U3">
         <v>0.700045</v>
@@ -1013,29 +1013,20 @@
       <c r="V3">
         <v>0.7050900000000001</v>
       </c>
-      <c r="W3">
-        <v>0.7028113384892352</v>
-      </c>
-      <c r="X3">
-        <v>0.692345</v>
-      </c>
       <c r="Y3">
-        <v>0.003951658092315682</v>
-      </c>
-      <c r="Z3">
-        <v>0.3592647388617022</v>
+        <v>0.0007080291694631981</v>
       </c>
       <c r="AA3">
-        <v>0.003951658092315682</v>
+        <v>0.0007080291694631981</v>
       </c>
       <c r="AB3">
-        <v>0.448681601024946</v>
+        <v>0.4328783341967565</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.351318398975054</v>
+        <v>0.3671216658032435</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1047,55 +1038,52 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.01099929290259921</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>45457.46753246713</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>45457.46753246713</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>64935.06493506437</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>454.5746753246713</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.004545746753246713</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.01675139345483889</v>
+        <v>0.01565676963005057</v>
       </c>
       <c r="AR3">
-        <v>0.00328516938985525</v>
+        <v>0.003214495111890641</v>
       </c>
       <c r="AS3">
-        <v>0.008450633226945127</v>
+        <v>0.007149956568681812</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
         <v>46267</v>
@@ -1118,7 +1106,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>67</v>
@@ -1130,19 +1118,19 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.1900347107390751</v>
+        <v>1.569404174446048</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -1154,43 +1142,43 @@
         <v>1</v>
       </c>
       <c r="R4">
-        <v>4.75301</v>
+        <v>4063.2</v>
       </c>
       <c r="S4">
-        <v>4.76023194156474</v>
+        <v>4159.420233759016</v>
       </c>
       <c r="T4">
-        <v>4.73975183916744</v>
+        <v>4461.107445863388</v>
       </c>
       <c r="U4">
-        <v>4.75301</v>
+        <v>4063.2</v>
       </c>
       <c r="V4">
-        <v>4.793019999999999</v>
+        <v>4005.32</v>
       </c>
       <c r="W4">
-        <v>4.76023194156474</v>
+        <v>4159.420233759016</v>
       </c>
       <c r="X4">
-        <v>4.7181625</v>
+        <v>3933.335</v>
       </c>
       <c r="Y4">
-        <v>0.001519445901595057</v>
+        <v>0.02368090021633592</v>
       </c>
       <c r="Z4">
-        <v>0.2072441800628549</v>
+        <v>0.7409250664845506</v>
       </c>
       <c r="AA4">
-        <v>0.001519445901595057</v>
+        <v>0.02368090021633592</v>
       </c>
       <c r="AB4">
-        <v>0.465307193788246</v>
+        <v>0.3</v>
       </c>
       <c r="AC4">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD4">
-        <v>0.334692806211754</v>
+        <v>0.4</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1205,43 +1193,43 @@
         <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.007331669826068097</v>
+        <v>0.0319612620594605</v>
       </c>
       <c r="AJ4">
-        <v>68197.28818423144</v>
+        <v>15643.93793554847</v>
       </c>
       <c r="AK4">
-        <v>68197.28818423144</v>
+        <v>15643.93793554847</v>
       </c>
       <c r="AL4">
-        <v>14348.23158045774</v>
+        <v>3.850152081007203</v>
       </c>
       <c r="AM4">
-        <v>681.9728818423143</v>
+        <v>156.4393793554847</v>
       </c>
       <c r="AN4">
-        <v>0.006819728818423143</v>
+        <v>0.001564393793554847</v>
       </c>
       <c r="AO4">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.06225131355920498</v>
+        <v>295.7955899974643</v>
       </c>
       <c r="AR4">
-        <v>0.01464567725302561</v>
+        <v>36.85308619283683</v>
       </c>
       <c r="AS4">
-        <v>0.031890671349915</v>
+        <v>62.52997816640261</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1276,28 +1264,28 @@
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.4474181392974408</v>
+        <v>0.1900347107390751</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1309,43 +1297,43 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>1.342705</v>
+        <v>4.75301</v>
       </c>
       <c r="S5">
-        <v>1.338636983380847</v>
+        <v>4.775407160558753</v>
       </c>
       <c r="T5">
-        <v>1.332159567209021</v>
+        <v>4.76813539669774</v>
       </c>
       <c r="U5">
-        <v>1.342705</v>
+        <v>4.75301</v>
       </c>
       <c r="V5">
-        <v>1.34491</v>
+        <v>4.793019999999999</v>
       </c>
       <c r="W5">
-        <v>1.338636983380847</v>
+        <v>4.775407160558753</v>
       </c>
       <c r="X5">
-        <v>1.35686125</v>
+        <v>4.7181625</v>
       </c>
       <c r="Y5">
-        <v>-0.003029717338620846</v>
+        <v>0.00471220564626492</v>
       </c>
       <c r="Z5">
-        <v>0.2873654123904925</v>
+        <v>0.6427192928833827</v>
       </c>
       <c r="AA5">
-        <v>0.003029717338620846</v>
+        <v>0.00471220564626492</v>
       </c>
       <c r="AB5">
-        <v>0.4573975420880934</v>
+        <v>0.3862163010801796</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3426024579119066</v>
+        <v>0.4137836989198204</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1360,49 +1348,49 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01054308280672224</v>
+        <v>0.007331669826068097</v>
       </c>
       <c r="AJ5">
-        <v>47424.45916114797</v>
+        <v>68197.28818423144</v>
       </c>
       <c r="AK5">
-        <v>47424.45916114797</v>
+        <v>68197.28818423144</v>
       </c>
       <c r="AL5">
-        <v>35320.0883002208</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM5">
-        <v>474.2445916114797</v>
+        <v>681.9728818423143</v>
       </c>
       <c r="AN5">
-        <v>0.004742445916114797</v>
+        <v>0.006819728818423143</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.02265873025495328</v>
+        <v>0.05448678485055043</v>
       </c>
       <c r="AR5">
-        <v>0.007809165872265232</v>
+        <v>0.01336325734380417</v>
       </c>
       <c r="AS5">
-        <v>0.01059393436516914</v>
+        <v>0.01524620892069136</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
         <v>89</v>
@@ -1428,7 +1416,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>68</v>
@@ -1446,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>9.410748419536978E-05</v>
+        <v>0.02721310628042968</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -1467,10 +1455,10 @@
         <v>1.15109</v>
       </c>
       <c r="S6">
-        <v>1.146805873170796</v>
+        <v>1.149611390378469</v>
       </c>
       <c r="T6">
-        <v>1.130689431615861</v>
+        <v>1.13785817211817</v>
       </c>
       <c r="U6">
         <v>1.15109</v>
@@ -1479,28 +1467,28 @@
         <v>1.16088</v>
       </c>
       <c r="W6">
-        <v>1.146805873170796</v>
+        <v>1.149363365</v>
       </c>
       <c r="X6">
         <v>1.16409</v>
       </c>
       <c r="Y6">
-        <v>-0.003721800058383102</v>
+        <v>-0.001284529985953422</v>
       </c>
       <c r="Z6">
-        <v>0.3295482176310924</v>
+        <v>0.1328180769230768</v>
       </c>
       <c r="AA6">
-        <v>0.003721800058383102</v>
+        <v>0.001284529985953422</v>
       </c>
       <c r="AB6">
-        <v>0.4013215874256177</v>
+        <v>0.4044252988651443</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3986784125743823</v>
+        <v>0.3955747011348558</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1539,19 +1527,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.02846851557150682</v>
+        <v>0.02438371221092047</v>
       </c>
       <c r="AR6">
-        <v>0.008046024784723884</v>
+        <v>0.007462467286905573</v>
       </c>
       <c r="AS6">
-        <v>0.01049370758527635</v>
+        <v>0.009320330792270175</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1583,7 +1571,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
         <v>68</v>
@@ -1592,70 +1580,70 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.3959586949593628</v>
+        <v>0.5398017231284329</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>7.7793</v>
+        <v>1.342705</v>
       </c>
       <c r="S7">
-        <v>7.749930192060869</v>
+        <v>1.340740475155892</v>
       </c>
       <c r="T7">
-        <v>7.664014079074487</v>
+        <v>1.335828040895061</v>
       </c>
       <c r="U7">
-        <v>7.7793</v>
+        <v>1.342705</v>
       </c>
       <c r="V7">
-        <v>7.819100000000001</v>
+        <v>1.34491</v>
       </c>
       <c r="W7">
-        <v>7.749930192060869</v>
+        <v>1.3406909425</v>
       </c>
       <c r="X7">
-        <v>7.842225</v>
+        <v>1.35686125</v>
       </c>
       <c r="Y7">
-        <v>-0.003775379267945905</v>
+        <v>-0.001463109800073753</v>
       </c>
       <c r="Z7">
-        <v>0.4667430741220742</v>
+        <v>0.1422733774834439</v>
       </c>
       <c r="AA7">
-        <v>0.003775379267945905</v>
+        <v>0.001463109800073753</v>
       </c>
       <c r="AB7">
-        <v>0.3946832025360349</v>
+        <v>0.4105419107294093</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.405316797463965</v>
+        <v>0.3894580892705907</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1667,46 +1655,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008088774054220833</v>
+        <v>0.01054308280672224</v>
       </c>
       <c r="AJ7">
-        <v>61814.06436233599</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AK7">
-        <v>46360.54827175199</v>
+        <v>47424.45916114797</v>
       </c>
       <c r="AL7">
-        <v>5959.475566150167</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM7">
-        <v>463.6054827175199</v>
+        <v>474.2445916114797</v>
       </c>
       <c r="AN7">
-        <v>0.0046360548271752</v>
+        <v>0.004742445916114797</v>
       </c>
       <c r="AO7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.1126539624027407</v>
+        <v>0.02240374599437471</v>
       </c>
       <c r="AR7">
-        <v>0.04702533565862096</v>
+        <v>0.007158591867835537</v>
       </c>
       <c r="AS7">
-        <v>0.07292118926850866</v>
+        <v>0.009351834528170712</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1747,70 +1735,70 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
         <v>46237</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.1845477155945729</v>
       </c>
       <c r="L8">
-        <v>0.9663643811290482</v>
+        <v>1.189516755040264</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>0.8615892133040703</v>
       </c>
       <c r="R8">
-        <v>157.4315</v>
+        <v>0.80999</v>
       </c>
       <c r="S8">
-        <v>156.7787452466943</v>
+        <v>0.8058218729698552</v>
       </c>
       <c r="T8">
-        <v>159.2861467273804</v>
+        <v>0.798307874112148</v>
       </c>
       <c r="U8">
-        <v>157.4315</v>
+        <v>0.80999</v>
       </c>
       <c r="V8">
-        <v>153.173</v>
+        <v>0.81158</v>
       </c>
       <c r="W8">
-        <v>156.7787452466943</v>
+        <v>0.8058218729698552</v>
       </c>
       <c r="X8">
-        <v>159.0335</v>
+        <v>0.8194699999999999</v>
       </c>
       <c r="Y8">
-        <v>-0.004146277925991216</v>
+        <v>-0.005145899369306778</v>
       </c>
       <c r="Z8">
-        <v>0.4074623928250252</v>
+        <v>0.439675847061688</v>
       </c>
       <c r="AA8">
-        <v>0.004146277925991216</v>
+        <v>0.005145899369306778</v>
       </c>
       <c r="AB8">
-        <v>0.4505118835703935</v>
+        <v>0.4098911565572293</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3494881164296065</v>
+        <v>0.3901088434427707</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1822,46 +1810,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>430.7946066520352</v>
       </c>
       <c r="AI8">
-        <v>0.01017585426042431</v>
+        <v>0.01170384819565672</v>
       </c>
       <c r="AJ8">
-        <v>49135.92384519383</v>
+        <v>42720.99156118149</v>
       </c>
       <c r="AK8">
-        <v>36851.94288389538</v>
+        <v>36807.94551076819</v>
       </c>
       <c r="AL8">
-        <v>234.0823970037469</v>
+        <v>45442.46905612191</v>
       </c>
       <c r="AM8">
-        <v>368.5194288389537</v>
+        <v>368.0794551076818</v>
       </c>
       <c r="AN8">
-        <v>0.003685194288389537</v>
+        <v>0.003680794551076818</v>
       </c>
       <c r="AO8">
-        <v>375.0000000000001</v>
+        <v>430.7946066520352</v>
       </c>
       <c r="AP8">
-        <v>0.003750000000000001</v>
+        <v>0.004307946066520352</v>
       </c>
       <c r="AQ8">
-        <v>4.507903295516781</v>
+        <v>0.01682063140568655</v>
       </c>
       <c r="AR8">
-        <v>3.625516382814196</v>
+        <v>0.004755045149069353</v>
       </c>
       <c r="AS8">
-        <v>4.878560805807377</v>
+        <v>0.006645106123908793</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1893,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1902,70 +1890,70 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K9">
-        <v>0.3801480452828046</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1.329377158473881</v>
+        <v>0.3959586949593628</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.7148889660378965</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>0.80999</v>
+        <v>7.7793</v>
       </c>
       <c r="S9">
-        <v>0.8056397540583552</v>
+        <v>7.731252629171177</v>
       </c>
       <c r="T9">
-        <v>0.7983385726023028</v>
+        <v>7.635331563096059</v>
       </c>
       <c r="U9">
-        <v>0.80999</v>
+        <v>7.7793</v>
       </c>
       <c r="V9">
-        <v>0.81158</v>
+        <v>7.819100000000001</v>
       </c>
       <c r="W9">
-        <v>0.8056397540583552</v>
+        <v>7.731252629171177</v>
       </c>
       <c r="X9">
-        <v>0.8194699999999999</v>
+        <v>7.842225</v>
       </c>
       <c r="Y9">
-        <v>-0.005370740307466502</v>
+        <v>-0.006176310314401444</v>
       </c>
       <c r="Z9">
-        <v>0.4588867027051475</v>
+        <v>0.7635656865923411</v>
       </c>
       <c r="AA9">
-        <v>0.005370740307466502</v>
+        <v>0.006176310314401444</v>
       </c>
       <c r="AB9">
-        <v>0.4245951567595062</v>
+        <v>0.4347175835781953</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3754048432404938</v>
+        <v>0.3652824164218047</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1977,46 +1965,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>357.4444830189483</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.01170384819565672</v>
+        <v>0.008088774054220833</v>
       </c>
       <c r="AJ9">
-        <v>42720.99156118149</v>
+        <v>61814.06436233599</v>
       </c>
       <c r="AK9">
-        <v>30540.76548528674</v>
+        <v>46360.54827175199</v>
       </c>
       <c r="AL9">
-        <v>37705.11424250514</v>
+        <v>5959.475566150167</v>
       </c>
       <c r="AM9">
-        <v>305.4076548528674</v>
+        <v>463.6054827175199</v>
       </c>
       <c r="AN9">
-        <v>0.003054076548528674</v>
+        <v>0.0046360548271752</v>
       </c>
       <c r="AO9">
-        <v>357.4444830189483</v>
+        <v>375</v>
       </c>
       <c r="AP9">
-        <v>0.003574444830189483</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ9">
-        <v>0.01630021285275825</v>
+        <v>0.1094177424511917</v>
       </c>
       <c r="AR9">
-        <v>0.00505715480130211</v>
+        <v>0.04323617273847094</v>
       </c>
       <c r="AS9">
-        <v>0.008203558543996467</v>
+        <v>0.06489001430623768</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2048,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2060,19 +2048,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K10">
-        <v>0.06116447076549618</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.397867003755076</v>
+        <v>0.04421110681978428</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2081,46 +2069,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.765291117691374</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.75752</v>
+        <v>9.074170000000001</v>
       </c>
       <c r="S10">
-        <v>6.717657098536375</v>
+        <v>9.008848588173224</v>
       </c>
       <c r="T10">
-        <v>6.67577347161162</v>
+        <v>8.931926955893184</v>
       </c>
       <c r="U10">
-        <v>6.75752</v>
+        <v>9.074170000000001</v>
       </c>
       <c r="V10">
-        <v>6.733740000000001</v>
+        <v>9.058010000000001</v>
       </c>
       <c r="W10">
-        <v>6.717657098536375</v>
+        <v>9.008848588173224</v>
       </c>
       <c r="X10">
-        <v>6.787095000000001</v>
+        <v>9.1620025</v>
       </c>
       <c r="Y10">
-        <v>-0.00589904306071235</v>
+        <v>-0.007198610101725689</v>
       </c>
       <c r="Z10">
-        <v>1.34785803765426</v>
+        <v>0.7437043443688427</v>
       </c>
       <c r="AA10">
-        <v>0.00589904306071235</v>
+        <v>0.007198610101725689</v>
       </c>
       <c r="AB10">
-        <v>0.3594988701756279</v>
+        <v>0.4155468500775573</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4405011298243722</v>
+        <v>0.3844531499224428</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2132,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>382.645558845687</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004376605618629338</v>
+        <v>0.009679397674938839</v>
       </c>
       <c r="AJ10">
-        <v>114243.786982248</v>
+        <v>51656.10679418225</v>
       </c>
       <c r="AK10">
-        <v>87429.75542893984</v>
+        <v>38742.08009563669</v>
       </c>
       <c r="AL10">
-        <v>12938.14231092765</v>
+        <v>4269.490222867401</v>
       </c>
       <c r="AM10">
-        <v>874.2975542893984</v>
+        <v>387.4208009563669</v>
       </c>
       <c r="AN10">
-        <v>0.008742975542893983</v>
+        <v>0.003874208009563669</v>
       </c>
       <c r="AO10">
-        <v>382.645558845687</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.00382645558845687</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.08089705333325507</v>
+        <v>0.1199402899413222</v>
       </c>
       <c r="AR10">
-        <v>0.01280502105360233</v>
+        <v>0.04128652506277814</v>
       </c>
       <c r="AS10">
-        <v>0.01680307324625755</v>
+        <v>0.05451230245954278</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2203,7 +2191,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2215,19 +2203,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.08246748434534681</v>
       </c>
       <c r="L11">
-        <v>0.04421110681978428</v>
+        <v>2.42396697331862</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2236,46 +2224,46 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.75</v>
+        <v>0.7706168710863367</v>
       </c>
       <c r="R11">
-        <v>9.074170000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="S11">
-        <v>8.99556451768844</v>
+        <v>6.686655613230148</v>
       </c>
       <c r="T11">
-        <v>8.929811526364528</v>
+        <v>6.598248203754721</v>
       </c>
       <c r="U11">
-        <v>9.074170000000001</v>
+        <v>6.75752</v>
       </c>
       <c r="V11">
-        <v>9.058010000000001</v>
+        <v>6.733740000000001</v>
       </c>
       <c r="W11">
-        <v>8.99556451768844</v>
+        <v>6.686655613230148</v>
       </c>
       <c r="X11">
-        <v>9.1620025</v>
+        <v>6.804762924513235</v>
       </c>
       <c r="Y11">
-        <v>-0.008662553413872667</v>
+        <v>-0.01048674465926138</v>
       </c>
       <c r="Z11">
-        <v>0.8949475685146292</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.008662553413872667</v>
+        <v>0.01048674465926138</v>
       </c>
       <c r="AB11">
-        <v>0.5123109538598168</v>
+        <v>0.3826090450229678</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.2876890461401832</v>
+        <v>0.4173909549770323</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2287,46 +2275,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>375</v>
+        <v>385.3084355431683</v>
       </c>
       <c r="AI11">
-        <v>0.009679397674938839</v>
+        <v>0.006991163106174253</v>
       </c>
       <c r="AJ11">
-        <v>51656.10679418225</v>
+        <v>71518.8577932654</v>
       </c>
       <c r="AK11">
-        <v>38742.08009563669</v>
+        <v>55113.63841631485</v>
       </c>
       <c r="AL11">
-        <v>4269.490222867401</v>
+        <v>8155.897195467397</v>
       </c>
       <c r="AM11">
-        <v>387.4208009563669</v>
+        <v>551.1363841631485</v>
       </c>
       <c r="AN11">
-        <v>0.003874208009563669</v>
+        <v>0.005511363841631485</v>
       </c>
       <c r="AO11">
-        <v>375</v>
+        <v>385.3084355431683</v>
       </c>
       <c r="AP11">
-        <v>0.00375</v>
+        <v>0.003853084355431683</v>
       </c>
       <c r="AQ11">
-        <v>0.1083533428242224</v>
+        <v>0.07580169310690178</v>
       </c>
       <c r="AR11">
-        <v>0.04574422943305893</v>
+        <v>0.01130264142775037</v>
       </c>
       <c r="AS11">
-        <v>0.06464705930244218</v>
+        <v>0.01559312349836122</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04342088262741264</v>
+        <v>0.03414944168061687</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,48 +169,48 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
   </si>
   <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>MEDIUM</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.246,naive=3.317,drift4=4.575; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01566,naive=0.003214,drift4=0.00715; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=295.8,naive=36.85,drift4=62.53; naive_cap_applied; model_divergence_guard(abs=426.8,thr=389.6)</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.05449,naive=0.01336,drift4=0.01525; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02438,naive=0.007462,drift4=0.00932; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0224,naive=0.007159,drift4=0.009352; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01682,naive=0.004755,drift4=0.006645; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.1094,naive=0.04324,drift4=0.06489; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1199,naive=0.04129,drift4=0.05451; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.0758,naive=0.0113,drift4=0.01559; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.02009,naive=0.007673,drift4=0.007264; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=413,naive=121.3,drift4=167.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01909,naive=0.003388,drift4=0.004609; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.0654,naive=0.01841,drift4=0.01815; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02542,naive=0.008919,drift4=0.009765; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.421,naive=3.519,drift4=4.777; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1011,naive=0.05124,drift4=0.07263; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1051,naive=0.04447,drift4=0.05358; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.07555,naive=0.01415,drift4=0.01092; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01879,naive=0.005414,drift4=0.008036; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.064118146134086</v>
+        <v>0.825697215621753</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>157.4315</v>
+        <v>1.34671</v>
       </c>
       <c r="S2">
-        <v>157.5587370547433</v>
+        <v>1.346158065942213</v>
       </c>
       <c r="T2">
-        <v>160.6115964456177</v>
+        <v>1.338860710523052</v>
       </c>
       <c r="U2">
-        <v>157.4315</v>
+        <v>1.34671</v>
       </c>
       <c r="V2">
-        <v>153.173</v>
+        <v>1.35292</v>
       </c>
       <c r="Y2">
-        <v>0.0008082058212196847</v>
+        <v>-0.0004098388352255797</v>
       </c>
       <c r="AA2">
-        <v>0.0008082058212196847</v>
+        <v>0.0004098388352255797</v>
       </c>
       <c r="AB2">
-        <v>0.4750946069705661</v>
+        <v>0.3926182803787752</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3249053930294338</v>
+        <v>0.4073817196212248</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>4.2464036093366</v>
+        <v>0.02008925426455093</v>
       </c>
       <c r="AR2">
-        <v>3.317222312751193</v>
+        <v>0.007673443966917455</v>
       </c>
       <c r="AS2">
-        <v>4.575264586318733</v>
+        <v>0.007264227034408257</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,67 +966,76 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
         <v>70</v>
       </c>
       <c r="J3" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.04072730525686864</v>
+        <v>0.1282376139516318</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.700045</v>
+        <v>4268.639999999999</v>
       </c>
       <c r="S3">
-        <v>0.7005406522799369</v>
+        <v>4323.168802371742</v>
       </c>
       <c r="T3">
-        <v>0.6969113792643779</v>
+        <v>4261.627291707048</v>
       </c>
       <c r="U3">
-        <v>0.700045</v>
+        <v>4268.639999999999</v>
       </c>
       <c r="V3">
-        <v>0.7050900000000001</v>
+        <v>4416.199999999999</v>
+      </c>
+      <c r="W3">
+        <v>4323.168802371742</v>
+      </c>
+      <c r="X3">
+        <v>4121.5475</v>
       </c>
       <c r="Y3">
-        <v>0.0007080291694631981</v>
+        <v>0.01277427995139954</v>
+      </c>
+      <c r="Z3">
+        <v>0.3707109633172472</v>
       </c>
       <c r="AA3">
-        <v>0.0007080291694631981</v>
+        <v>0.01277427995139954</v>
       </c>
       <c r="AB3">
-        <v>0.4328783341967565</v>
+        <v>0.4109341055723418</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3671216658032435</v>
+        <v>0.3890658944276583</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1038,55 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI3">
+        <v>0.03445886746129912</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>14510.05319781771</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>14510.05319781771</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>3.399221578258582</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>145.1005319781771</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.001451005319781771</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.01565676963005057</v>
+        <v>413.0076351112947</v>
       </c>
       <c r="AR3">
-        <v>0.003214495111890641</v>
+        <v>121.2826342395241</v>
       </c>
       <c r="AS3">
-        <v>0.007149956568681812</v>
+        <v>167.6987825565766</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1106,7 +1118,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>67</v>
@@ -1118,67 +1130,67 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.569404174446048</v>
+        <v>0.4836793528452488</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4063.2</v>
+        <v>0.705725</v>
       </c>
       <c r="S4">
-        <v>4159.420233759016</v>
+        <v>0.7113089544367487</v>
       </c>
       <c r="T4">
-        <v>4461.107445863388</v>
+        <v>0.7087176256325676</v>
       </c>
       <c r="U4">
-        <v>4063.2</v>
+        <v>0.705725</v>
       </c>
       <c r="V4">
-        <v>4005.32</v>
+        <v>0.7164500000000001</v>
       </c>
       <c r="W4">
-        <v>4159.420233759016</v>
+        <v>0.7113089544367487</v>
       </c>
       <c r="X4">
-        <v>3933.335</v>
+        <v>0.698025</v>
       </c>
       <c r="Y4">
-        <v>0.02368090021633592</v>
+        <v>0.007912365916962896</v>
       </c>
       <c r="Z4">
-        <v>0.7409250664845506</v>
+        <v>0.7251888878894273</v>
       </c>
       <c r="AA4">
-        <v>0.02368090021633592</v>
+        <v>0.007912365916962896</v>
       </c>
       <c r="AB4">
-        <v>0.3</v>
+        <v>0.3874677325337812</v>
       </c>
       <c r="AC4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4</v>
+        <v>0.4125322674662187</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1190,46 +1202,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.0319612620594605</v>
+        <v>0.010910765524815</v>
       </c>
       <c r="AJ4">
-        <v>15643.93793554847</v>
+        <v>45826.2987012983</v>
       </c>
       <c r="AK4">
-        <v>15643.93793554847</v>
+        <v>34369.72402597372</v>
       </c>
       <c r="AL4">
-        <v>3.850152081007203</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM4">
-        <v>156.4393793554847</v>
+        <v>343.6972402597372</v>
       </c>
       <c r="AN4">
-        <v>0.001564393793554847</v>
+        <v>0.003436972402597372</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ4">
-        <v>295.7955899974643</v>
+        <v>0.01909253957892934</v>
       </c>
       <c r="AR4">
-        <v>36.85308619283683</v>
+        <v>0.003387667429697142</v>
       </c>
       <c r="AS4">
-        <v>62.52997816640261</v>
+        <v>0.00460852817744393</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1241,7 +1253,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1270,22 +1282,22 @@
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.1900347107390751</v>
+        <v>0.04430240762997241</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1297,43 +1309,43 @@
         <v>1</v>
       </c>
       <c r="R5">
-        <v>4.75301</v>
+        <v>4.76213</v>
       </c>
       <c r="S5">
-        <v>4.775407160558753</v>
+        <v>4.777745807265901</v>
       </c>
       <c r="T5">
-        <v>4.76813539669774</v>
+        <v>4.748992617123906</v>
       </c>
       <c r="U5">
-        <v>4.75301</v>
+        <v>4.76213</v>
       </c>
       <c r="V5">
-        <v>4.793019999999999</v>
+        <v>4.81126</v>
       </c>
       <c r="W5">
-        <v>4.775407160558753</v>
+        <v>4.777745807265901</v>
       </c>
       <c r="X5">
-        <v>4.7181625</v>
+        <v>4.7272825</v>
       </c>
       <c r="Y5">
-        <v>0.00471220564626492</v>
+        <v>0.003279164421362022</v>
       </c>
       <c r="Z5">
-        <v>0.6427192928833827</v>
+        <v>0.4481184379338766</v>
       </c>
       <c r="AA5">
-        <v>0.00471220564626492</v>
+        <v>0.003279164421362022</v>
       </c>
       <c r="AB5">
-        <v>0.3862163010801796</v>
+        <v>0.3804269850434665</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4137836989198204</v>
+        <v>0.4195730149565335</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1348,22 +1360,22 @@
         <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.007331669826068097</v>
+        <v>0.007317628876154141</v>
       </c>
       <c r="AJ5">
-        <v>68197.28818423144</v>
+        <v>68328.14405624522</v>
       </c>
       <c r="AK5">
-        <v>68197.28818423144</v>
+        <v>68328.14405624522</v>
       </c>
       <c r="AL5">
         <v>14348.23158045774</v>
       </c>
       <c r="AM5">
-        <v>681.9728818423143</v>
+        <v>683.2814405624522</v>
       </c>
       <c r="AN5">
-        <v>0.006819728818423143</v>
+        <v>0.006832814405624522</v>
       </c>
       <c r="AO5">
         <v>499.9999999999999</v>
@@ -1372,19 +1384,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.05448678485055043</v>
+        <v>0.06539640306914768</v>
       </c>
       <c r="AR5">
-        <v>0.01336325734380417</v>
+        <v>0.01840534608361298</v>
       </c>
       <c r="AS5">
-        <v>0.01524620892069136</v>
+        <v>0.01814671454915946</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1396,7 +1408,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,67 +1440,67 @@
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.02721310628042968</v>
+        <v>0.4279558520887797</v>
       </c>
       <c r="M6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>1.15109</v>
+        <v>1.15551</v>
       </c>
       <c r="S6">
-        <v>1.149611390378469</v>
+        <v>1.152775894205479</v>
       </c>
       <c r="T6">
-        <v>1.13785817211817</v>
+        <v>1.134504156834615</v>
       </c>
       <c r="U6">
-        <v>1.15109</v>
+        <v>1.15551</v>
       </c>
       <c r="V6">
-        <v>1.16088</v>
+        <v>1.16972</v>
       </c>
       <c r="W6">
-        <v>1.149363365</v>
+        <v>1.152775894205479</v>
       </c>
       <c r="X6">
-        <v>1.16409</v>
+        <v>1.16851</v>
       </c>
       <c r="Y6">
-        <v>-0.001284529985953422</v>
+        <v>-0.002366146372182598</v>
       </c>
       <c r="Z6">
-        <v>0.1328180769230768</v>
+        <v>0.210315830347747</v>
       </c>
       <c r="AA6">
-        <v>0.001284529985953422</v>
+        <v>0.002366146372182598</v>
       </c>
       <c r="AB6">
-        <v>0.4044252988651443</v>
+        <v>0.4004477680200023</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3955747011348558</v>
+        <v>0.3995522319799977</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1500,46 +1512,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.01129364341624027</v>
+        <v>0.0112504435271006</v>
       </c>
       <c r="AJ6">
-        <v>44272.69230769226</v>
+        <v>44442.69230769228</v>
       </c>
       <c r="AK6">
-        <v>33204.5192307692</v>
+        <v>44442.69230769228</v>
       </c>
       <c r="AL6">
-        <v>28846.15384615382</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM6">
-        <v>332.045192307692</v>
+        <v>444.4269230769228</v>
       </c>
       <c r="AN6">
-        <v>0.00332045192307692</v>
+        <v>0.004444269230769227</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ6">
-        <v>0.02438371221092047</v>
+        <v>0.02542021020654428</v>
       </c>
       <c r="AR6">
-        <v>0.007462467286905573</v>
+        <v>0.008918894165058432</v>
       </c>
       <c r="AS6">
-        <v>0.009320330792270175</v>
+        <v>0.009765163708061835</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1551,7 +1563,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,13 +1595,13 @@
         <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.306561496195065</v>
       </c>
       <c r="L7">
-        <v>0.5398017231284329</v>
+        <v>1.846346534990227</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1598,52 +1610,52 @@
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.8266403740487662</v>
       </c>
       <c r="R7">
-        <v>1.342705</v>
+        <v>157.669</v>
       </c>
       <c r="S7">
-        <v>1.340740475155892</v>
+        <v>157.1407282579382</v>
       </c>
       <c r="T7">
-        <v>1.335828040895061</v>
+        <v>159.3062667943989</v>
       </c>
       <c r="U7">
-        <v>1.342705</v>
+        <v>157.669</v>
       </c>
       <c r="V7">
-        <v>1.34491</v>
+        <v>153.648</v>
       </c>
       <c r="W7">
-        <v>1.3406909425</v>
+        <v>157.1407282579382</v>
       </c>
       <c r="X7">
-        <v>1.35686125</v>
+        <v>159.271</v>
       </c>
       <c r="Y7">
-        <v>-0.001463109800073753</v>
+        <v>-0.003350511147161665</v>
       </c>
       <c r="Z7">
-        <v>0.1422733774834439</v>
+        <v>0.3297576417364769</v>
       </c>
       <c r="AA7">
-        <v>0.001463109800073753</v>
+        <v>0.003350511147161665</v>
       </c>
       <c r="AB7">
-        <v>0.4105419107294093</v>
+        <v>0.4751504931862748</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3894580892705907</v>
+        <v>0.3248495068137252</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,46 +1667,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>413.3201870243831</v>
       </c>
       <c r="AI7">
-        <v>0.01054308280672224</v>
+        <v>0.01016052616557465</v>
       </c>
       <c r="AJ7">
-        <v>47424.45916114797</v>
+        <v>49210.04993757835</v>
       </c>
       <c r="AK7">
-        <v>47424.45916114797</v>
+        <v>40679.01408735823</v>
       </c>
       <c r="AL7">
-        <v>35320.0883002208</v>
+        <v>258.0026136232121</v>
       </c>
       <c r="AM7">
-        <v>474.2445916114797</v>
+        <v>406.7901408735823</v>
       </c>
       <c r="AN7">
-        <v>0.004742445916114797</v>
+        <v>0.004067901408735823</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>413.3201870243831</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.004133201870243831</v>
       </c>
       <c r="AQ7">
-        <v>0.02240374599437471</v>
+        <v>4.421342775510393</v>
       </c>
       <c r="AR7">
-        <v>0.007158591867835537</v>
+        <v>3.51948166760813</v>
       </c>
       <c r="AS7">
-        <v>0.009351834528170712</v>
+        <v>4.776905692522635</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1706,7 +1718,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,67 +1750,67 @@
         <v>70</v>
       </c>
       <c r="J8" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K8">
-        <v>0.1845477155945729</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.189516755040264</v>
+        <v>0.189864250044427</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>0.8615892133040703</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>0.80999</v>
+        <v>7.7947</v>
       </c>
       <c r="S8">
-        <v>0.8058218729698552</v>
+        <v>7.766631252348002</v>
       </c>
       <c r="T8">
-        <v>0.798307874112148</v>
+        <v>7.687901989610495</v>
       </c>
       <c r="U8">
-        <v>0.80999</v>
+        <v>7.7947</v>
       </c>
       <c r="V8">
-        <v>0.81158</v>
+        <v>7.8499</v>
       </c>
       <c r="W8">
-        <v>0.8058218729698552</v>
+        <v>7.766631252348002</v>
       </c>
       <c r="X8">
-        <v>0.8194699999999999</v>
+        <v>7.857625</v>
       </c>
       <c r="Y8">
-        <v>-0.005145899369306778</v>
+        <v>-0.003601004227487576</v>
       </c>
       <c r="Z8">
-        <v>0.439675847061688</v>
+        <v>0.4460667088120358</v>
       </c>
       <c r="AA8">
-        <v>0.005145899369306778</v>
+        <v>0.003601004227487576</v>
       </c>
       <c r="AB8">
-        <v>0.4098911565572293</v>
+        <v>0.4458619428617201</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3901088434427707</v>
+        <v>0.3541380571382799</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1810,46 +1822,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>430.7946066520352</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01170384819565672</v>
+        <v>0.008072793051688983</v>
       </c>
       <c r="AJ8">
-        <v>42720.99156118149</v>
+        <v>61936.43226062762</v>
       </c>
       <c r="AK8">
-        <v>36807.94551076819</v>
+        <v>46452.32419547071</v>
       </c>
       <c r="AL8">
-        <v>45442.46905612191</v>
+        <v>5959.475566150168</v>
       </c>
       <c r="AM8">
-        <v>368.0794551076818</v>
+        <v>464.5232419547071</v>
       </c>
       <c r="AN8">
-        <v>0.003680794551076818</v>
+        <v>0.004645232419547071</v>
       </c>
       <c r="AO8">
-        <v>430.7946066520352</v>
+        <v>375</v>
       </c>
       <c r="AP8">
-        <v>0.004307946066520352</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.01682063140568655</v>
+        <v>0.1010586395992964</v>
       </c>
       <c r="AR8">
-        <v>0.004755045149069353</v>
+        <v>0.0512383816620252</v>
       </c>
       <c r="AS8">
-        <v>0.006645106123908793</v>
+        <v>0.0726270304249484</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1861,7 +1873,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,67 +1905,67 @@
         <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.3959586949593628</v>
+        <v>0.007589455652057173</v>
       </c>
       <c r="M9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>7.7793</v>
+        <v>9.08699</v>
       </c>
       <c r="S9">
-        <v>7.731252629171177</v>
+        <v>9.029593397027938</v>
       </c>
       <c r="T9">
-        <v>7.635331563096059</v>
+        <v>8.953269249755692</v>
       </c>
       <c r="U9">
-        <v>7.7793</v>
+        <v>9.08699</v>
       </c>
       <c r="V9">
-        <v>7.819100000000001</v>
+        <v>9.08365</v>
       </c>
       <c r="W9">
-        <v>7.731252629171177</v>
+        <v>9.029593397027938</v>
       </c>
       <c r="X9">
-        <v>7.842225</v>
+        <v>9.174822499999999</v>
       </c>
       <c r="Y9">
-        <v>-0.006176310314401444</v>
+        <v>-0.006316349305112285</v>
       </c>
       <c r="Z9">
-        <v>0.7635656865923411</v>
+        <v>0.6534779605733919</v>
       </c>
       <c r="AA9">
-        <v>0.006176310314401444</v>
+        <v>0.006316349305112285</v>
       </c>
       <c r="AB9">
-        <v>0.4347175835781953</v>
+        <v>0.4197291614714603</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3652824164218047</v>
+        <v>0.3802708385285397</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1965,46 +1977,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.008088774054220833</v>
+        <v>0.009665741901333638</v>
       </c>
       <c r="AJ9">
-        <v>61814.06436233599</v>
+        <v>51729.08661372513</v>
       </c>
       <c r="AK9">
-        <v>46360.54827175199</v>
+        <v>51729.08661372513</v>
       </c>
       <c r="AL9">
-        <v>5959.475566150167</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM9">
-        <v>463.6054827175199</v>
+        <v>517.2908661372513</v>
       </c>
       <c r="AN9">
-        <v>0.0046360548271752</v>
+        <v>0.005172908661372514</v>
       </c>
       <c r="AO9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.1094177424511917</v>
+        <v>0.1051394232482715</v>
       </c>
       <c r="AR9">
-        <v>0.04323617273847094</v>
+        <v>0.04446559150959063</v>
       </c>
       <c r="AS9">
-        <v>0.06489001430623768</v>
+        <v>0.05358066263135217</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2016,7 +2028,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2045,22 +2057,22 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.2872454174635685</v>
       </c>
       <c r="L10">
-        <v>0.04421110681978428</v>
+        <v>2.677131246811971</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2069,46 +2081,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.8218113543658921</v>
       </c>
       <c r="R10">
-        <v>9.074170000000001</v>
+        <v>6.74733</v>
       </c>
       <c r="S10">
-        <v>9.008848588173224</v>
+        <v>6.701758285646064</v>
       </c>
       <c r="T10">
-        <v>8.931926955893184</v>
+        <v>6.660151254983846</v>
       </c>
       <c r="U10">
-        <v>9.074170000000001</v>
+        <v>6.74733</v>
       </c>
       <c r="V10">
-        <v>9.058010000000001</v>
+        <v>6.71336</v>
       </c>
       <c r="W10">
-        <v>9.008848588173224</v>
+        <v>6.701758285646064</v>
       </c>
       <c r="X10">
-        <v>9.1620025</v>
+        <v>6.777711142902624</v>
       </c>
       <c r="Y10">
-        <v>-0.007198610101725689</v>
+        <v>-0.006754036686205627</v>
       </c>
       <c r="Z10">
-        <v>0.7437043443688427</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.007198610101725689</v>
+        <v>0.006754036686205627</v>
       </c>
       <c r="AB10">
-        <v>0.4155468500775573</v>
+        <v>0.3457272737470512</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3844531499224428</v>
+        <v>0.4542727262529488</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2120,46 +2132,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>410.9056771829461</v>
       </c>
       <c r="AI10">
-        <v>0.009679397674938839</v>
+        <v>0.004502691124137085</v>
       </c>
       <c r="AJ10">
-        <v>51656.10679418225</v>
+        <v>111044.7033152473</v>
       </c>
       <c r="AK10">
-        <v>38742.08009563669</v>
+        <v>91257.79802666207</v>
       </c>
       <c r="AL10">
-        <v>4269.490222867401</v>
+        <v>13525.02367998335</v>
       </c>
       <c r="AM10">
-        <v>387.4208009563669</v>
+        <v>912.5779802666207</v>
       </c>
       <c r="AN10">
-        <v>0.003874208009563669</v>
+        <v>0.009125779802666207</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>410.9056771829461</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.00410905677182946</v>
       </c>
       <c r="AQ10">
-        <v>0.1199402899413222</v>
+        <v>0.075546036782613</v>
       </c>
       <c r="AR10">
-        <v>0.04128652506277814</v>
+        <v>0.01414789751504147</v>
       </c>
       <c r="AS10">
-        <v>0.05451230245954278</v>
+        <v>0.01092093721579322</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2171,7 +2183,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,67 +2215,67 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K11">
-        <v>0.08246748434534681</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.42396697331862</v>
+        <v>0.8295875572996088</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q11">
-        <v>0.7706168710863367</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>6.75752</v>
+        <v>0.8066800000000001</v>
       </c>
       <c r="S11">
-        <v>6.686655613230148</v>
+        <v>0.8008182428182398</v>
       </c>
       <c r="T11">
-        <v>6.598248203754721</v>
+        <v>0.7941757539463682</v>
       </c>
       <c r="U11">
-        <v>6.75752</v>
+        <v>0.8066800000000001</v>
       </c>
       <c r="V11">
-        <v>6.733740000000001</v>
+        <v>0.8049600000000001</v>
       </c>
       <c r="W11">
-        <v>6.686655613230148</v>
+        <v>0.8008182428182398</v>
       </c>
       <c r="X11">
-        <v>6.804762924513235</v>
+        <v>0.81616</v>
       </c>
       <c r="Y11">
-        <v>-0.01048674465926138</v>
+        <v>-0.007266521026628026</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.6183288166413823</v>
       </c>
       <c r="AA11">
-        <v>0.01048674465926138</v>
+        <v>0.007266521026628026</v>
       </c>
       <c r="AB11">
-        <v>0.3826090450229678</v>
+        <v>0.4159546397079577</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4173909549770323</v>
+        <v>0.3840453602920423</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2275,46 +2287,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>385.3084355431683</v>
+        <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.006991163106174253</v>
+        <v>0.01175187186988643</v>
       </c>
       <c r="AJ11">
-        <v>71518.8577932654</v>
+        <v>42546.41350210976</v>
       </c>
       <c r="AK11">
-        <v>55113.63841631485</v>
+        <v>42546.41350210976</v>
       </c>
       <c r="AL11">
-        <v>8155.897195467397</v>
+        <v>52742.61603375534</v>
       </c>
       <c r="AM11">
-        <v>551.1363841631485</v>
+        <v>425.4641350210976</v>
       </c>
       <c r="AN11">
-        <v>0.005511363841631485</v>
+        <v>0.004254641350210976</v>
       </c>
       <c r="AO11">
-        <v>385.3084355431683</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>0.003853084355431683</v>
+        <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.07580169310690178</v>
+        <v>0.01878910261782699</v>
       </c>
       <c r="AR11">
-        <v>0.01130264142775037</v>
+        <v>0.00541413553711769</v>
       </c>
       <c r="AS11">
-        <v>0.01559312349836122</v>
+        <v>0.008035879580256129</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03414944168061687</v>
+        <v>0.04343152500130548</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2326,7 +2338,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -193,12 +193,12 @@
     <t>GBPCNH</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.02009,naive=0.007673,drift4=0.007264; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=413,naive=121.3,drift4=167.7; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01909,naive=0.003388,drift4=0.004609; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.0654,naive=0.01841,drift4=0.01815; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02542,naive=0.008919,drift4=0.009765; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.48,naive=0.20,drift4=0.32); metric_best=naive; scores=model=4.421,naive=3.519,drift4=4.777; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.1011,naive=0.05124,drift4=0.07263; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1051,naive=0.04447,drift4=0.05358; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.07555,naive=0.01415,drift4=0.01092; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01879,naive=0.005414,drift4=0.008036; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02049,naive=0.006978,drift4=0.0074; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=388,naive=122.5,drift4=166.4; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01764,naive=0.002899,drift4=0.004002; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.05484,naive=0.018,drift4=0.01192; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02172,naive=0.008021,drift4=0.008918; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.187,naive=3.169,drift4=4.458; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1034,naive=0.04651,drift4=0.06499; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1205,naive=0.04007,drift4=0.04734; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01884,naive=0.004834,drift4=0.007268; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.06805,naive=0.01248,drift4=0.0113; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.825697215621753</v>
+        <v>0.8655590227027731</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -859,10 +859,10 @@
         <v>1.34671</v>
       </c>
       <c r="S2">
-        <v>1.346158065942213</v>
+        <v>1.347055682500632</v>
       </c>
       <c r="T2">
-        <v>1.338860710523052</v>
+        <v>1.3412496786902</v>
       </c>
       <c r="U2">
         <v>1.34671</v>
@@ -871,19 +871,19 @@
         <v>1.35292</v>
       </c>
       <c r="Y2">
-        <v>-0.0004098388352255797</v>
+        <v>0.0002566866664924517</v>
       </c>
       <c r="AA2">
-        <v>0.0004098388352255797</v>
+        <v>0.0002566866664924517</v>
       </c>
       <c r="AB2">
-        <v>0.3926182803787752</v>
+        <v>0.3960745704136094</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4073817196212248</v>
+        <v>0.4039254295863905</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.02008925426455093</v>
+        <v>0.02049388346590836</v>
       </c>
       <c r="AR2">
-        <v>0.007673443966917455</v>
+        <v>0.00697824986102748</v>
       </c>
       <c r="AS2">
-        <v>0.007264227034408257</v>
+        <v>0.007399798417737032</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1282376139516318</v>
+        <v>0.1235224784910224</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -1002,10 +1002,10 @@
         <v>4268.639999999999</v>
       </c>
       <c r="S3">
-        <v>4323.168802371742</v>
+        <v>4503.120458064439</v>
       </c>
       <c r="T3">
-        <v>4261.627291707048</v>
+        <v>4697.952148667046</v>
       </c>
       <c r="U3">
         <v>4268.639999999999</v>
@@ -1014,28 +1014,28 @@
         <v>4416.199999999999</v>
       </c>
       <c r="W3">
-        <v>4323.168802371742</v>
+        <v>4503.120458064439</v>
       </c>
       <c r="X3">
-        <v>4121.5475</v>
+        <v>4112.319694623707</v>
       </c>
       <c r="Y3">
-        <v>0.01277427995139954</v>
+        <v>0.05493095179364846</v>
       </c>
       <c r="Z3">
-        <v>0.3707109633172472</v>
+        <v>1.5</v>
       </c>
       <c r="AA3">
-        <v>0.01277427995139954</v>
+        <v>0.05493095179364846</v>
       </c>
       <c r="AB3">
-        <v>0.4109341055723418</v>
+        <v>0.4132442595922519</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3890658944276583</v>
+        <v>0.3867557404077481</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1050,22 +1050,22 @@
         <v>500</v>
       </c>
       <c r="AI3">
-        <v>0.03445886746129912</v>
+        <v>0.03662063452909897</v>
       </c>
       <c r="AJ3">
-        <v>14510.05319781771</v>
+        <v>13653.50454544137</v>
       </c>
       <c r="AK3">
-        <v>14510.05319781771</v>
+        <v>13653.50454544137</v>
       </c>
       <c r="AL3">
-        <v>3.399221578258582</v>
+        <v>3.198560793470842</v>
       </c>
       <c r="AM3">
-        <v>145.1005319781771</v>
+        <v>136.5350454544137</v>
       </c>
       <c r="AN3">
-        <v>0.001451005319781771</v>
+        <v>0.001365350454544137</v>
       </c>
       <c r="AO3">
         <v>500</v>
@@ -1074,19 +1074,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>413.0076351112947</v>
+        <v>388.0228832822809</v>
       </c>
       <c r="AR3">
-        <v>121.2826342395241</v>
+        <v>122.5489846712669</v>
       </c>
       <c r="AS3">
-        <v>167.6987825565766</v>
+        <v>166.447380990724</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV3" t="s">
         <v>87</v>
@@ -1136,13 +1136,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.4836793528452488</v>
+        <v>0.5567459216752554</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="s">
         <v>72</v>
@@ -1157,10 +1157,10 @@
         <v>0.705725</v>
       </c>
       <c r="S4">
-        <v>0.7113089544367487</v>
+        <v>0.7115063595394642</v>
       </c>
       <c r="T4">
-        <v>0.7087176256325676</v>
+        <v>0.7091979286954787</v>
       </c>
       <c r="U4">
         <v>0.705725</v>
@@ -1169,28 +1169,28 @@
         <v>0.7164500000000001</v>
       </c>
       <c r="W4">
-        <v>0.7113089544367487</v>
+        <v>0.7115063595394642</v>
       </c>
       <c r="X4">
         <v>0.698025</v>
       </c>
       <c r="Y4">
-        <v>0.007912365916962896</v>
+        <v>0.008192085499966879</v>
       </c>
       <c r="Z4">
-        <v>0.7251888878894273</v>
+        <v>0.7508259142161137</v>
       </c>
       <c r="AA4">
-        <v>0.007912365916962896</v>
+        <v>0.008192085499966879</v>
       </c>
       <c r="AB4">
-        <v>0.3874677325337812</v>
+        <v>0.3859091207212976</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4125322674662187</v>
+        <v>0.4140908792787024</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1229,19 +1229,19 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.01909253957892934</v>
+        <v>0.01763968225699579</v>
       </c>
       <c r="AR4">
-        <v>0.003387667429697142</v>
+        <v>0.002899229413044679</v>
       </c>
       <c r="AS4">
-        <v>0.00460852817744393</v>
+        <v>0.004002154579317642</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1273,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1312,10 +1312,10 @@
         <v>4.76213</v>
       </c>
       <c r="S5">
-        <v>4.777745807265901</v>
+        <v>4.793264978878625</v>
       </c>
       <c r="T5">
-        <v>4.748992617123906</v>
+        <v>4.788284486143543</v>
       </c>
       <c r="U5">
         <v>4.76213</v>
@@ -1324,28 +1324,28 @@
         <v>4.81126</v>
       </c>
       <c r="W5">
-        <v>4.777745807265901</v>
+        <v>4.793264978878625</v>
       </c>
       <c r="X5">
         <v>4.7272825</v>
       </c>
       <c r="Y5">
-        <v>0.003279164421362022</v>
+        <v>0.006538036315393541</v>
       </c>
       <c r="Z5">
-        <v>0.4481184379338766</v>
+        <v>0.8934637744063452</v>
       </c>
       <c r="AA5">
-        <v>0.003279164421362022</v>
+        <v>0.006538036315393541</v>
       </c>
       <c r="AB5">
-        <v>0.3804269850434665</v>
+        <v>0.3555533587806834</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4195730149565335</v>
+        <v>0.4444466412193167</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1384,19 +1384,19 @@
         <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.06539640306914768</v>
+        <v>0.05484312935026162</v>
       </c>
       <c r="AR5">
-        <v>0.01840534608361298</v>
+        <v>0.0179985595282394</v>
       </c>
       <c r="AS5">
-        <v>0.01814671454915946</v>
+        <v>0.01191892848701538</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1431,10 +1431,10 @@
         <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.4279558520887797</v>
+        <v>0.468749840353423</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1455,22 +1455,22 @@
         <v>0</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
         <v>1.15551</v>
       </c>
       <c r="S6">
-        <v>1.152775894205479</v>
+        <v>1.157452282827527</v>
       </c>
       <c r="T6">
-        <v>1.134504156834615</v>
+        <v>1.146425364745148</v>
       </c>
       <c r="U6">
         <v>1.15551</v>
@@ -1479,28 +1479,28 @@
         <v>1.16972</v>
       </c>
       <c r="W6">
-        <v>1.152775894205479</v>
+        <v>1.157452282827527</v>
       </c>
       <c r="X6">
-        <v>1.16851</v>
+        <v>1.14251</v>
       </c>
       <c r="Y6">
-        <v>-0.002366146372182598</v>
+        <v>0.001680887943442537</v>
       </c>
       <c r="Z6">
-        <v>0.210315830347747</v>
+        <v>0.1494063713482527</v>
       </c>
       <c r="AA6">
-        <v>0.002366146372182598</v>
+        <v>0.001680887943442537</v>
       </c>
       <c r="AB6">
-        <v>0.4004477680200023</v>
+        <v>0.4046303824615381</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3995522319799977</v>
+        <v>0.3953696175384619</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1512,7 +1512,7 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
         <v>0.0112504435271006</v>
@@ -1521,43 +1521,43 @@
         <v>44442.69230769228</v>
       </c>
       <c r="AK6">
-        <v>44442.69230769228</v>
+        <v>33332.01923076921</v>
       </c>
       <c r="AL6">
-        <v>38461.53846153843</v>
+        <v>28846.15384615382</v>
       </c>
       <c r="AM6">
-        <v>444.4269230769228</v>
+        <v>333.320192307692</v>
       </c>
       <c r="AN6">
-        <v>0.004444269230769227</v>
+        <v>0.00333320192307692</v>
       </c>
       <c r="AO6">
-        <v>500.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.005000000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.02542021020654428</v>
+        <v>0.021719833955678</v>
       </c>
       <c r="AR6">
-        <v>0.008918894165058432</v>
+        <v>0.008021460448215166</v>
       </c>
       <c r="AS6">
-        <v>0.009765163708061835</v>
+        <v>0.008917600017036799</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
         <v>89</v>
@@ -1586,10 +1586,10 @@
         <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
         <v>70</v>
@@ -1598,34 +1598,34 @@
         <v>46239</v>
       </c>
       <c r="K7">
-        <v>0.306561496195065</v>
+        <v>0.06640297558107278</v>
       </c>
       <c r="L7">
-        <v>1.846346534990227</v>
+        <v>1.624084279917644</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.8266403740487662</v>
+        <v>0.9501977683141954</v>
       </c>
       <c r="R7">
         <v>157.669</v>
       </c>
       <c r="S7">
-        <v>157.1407282579382</v>
+        <v>157.8906338727083</v>
       </c>
       <c r="T7">
-        <v>159.3062667943989</v>
+        <v>160.8963582811799</v>
       </c>
       <c r="U7">
         <v>157.669</v>
@@ -1634,28 +1634,28 @@
         <v>153.648</v>
       </c>
       <c r="W7">
-        <v>157.1407282579382</v>
+        <v>157.9055035</v>
       </c>
       <c r="X7">
-        <v>159.271</v>
+        <v>156.067</v>
       </c>
       <c r="Y7">
-        <v>-0.003350511147161665</v>
+        <v>0.001405690863190216</v>
       </c>
       <c r="Z7">
-        <v>0.3297576417364769</v>
+        <v>0.1476301498127351</v>
       </c>
       <c r="AA7">
-        <v>0.003350511147161665</v>
+        <v>0.001405690863190216</v>
       </c>
       <c r="AB7">
-        <v>0.4751504931862748</v>
+        <v>0.4743741602337886</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3248495068137252</v>
+        <v>0.3256258397662114</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1667,7 +1667,7 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>413.3201870243831</v>
+        <v>475.0988841570977</v>
       </c>
       <c r="AI7">
         <v>0.01016052616557465</v>
@@ -1676,43 +1676,43 @@
         <v>49210.04993757835</v>
       </c>
       <c r="AK7">
-        <v>40679.01408735823</v>
+        <v>46759.27962931706</v>
       </c>
       <c r="AL7">
-        <v>258.0026136232121</v>
+        <v>296.5660949794637</v>
       </c>
       <c r="AM7">
-        <v>406.7901408735823</v>
+        <v>467.5927962931706</v>
       </c>
       <c r="AN7">
-        <v>0.004067901408735823</v>
+        <v>0.004675927962931706</v>
       </c>
       <c r="AO7">
-        <v>413.3201870243831</v>
+        <v>475.0988841570978</v>
       </c>
       <c r="AP7">
-        <v>0.004133201870243831</v>
+        <v>0.004750988841570978</v>
       </c>
       <c r="AQ7">
-        <v>4.421342775510393</v>
+        <v>4.187255394617863</v>
       </c>
       <c r="AR7">
-        <v>3.51948166760813</v>
+        <v>3.169067860778971</v>
       </c>
       <c r="AS7">
-        <v>4.776905692522635</v>
+        <v>4.458095412923126</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
         <v>89</v>
@@ -1777,10 +1777,10 @@
         <v>7.7947</v>
       </c>
       <c r="S8">
-        <v>7.766631252348002</v>
+        <v>7.751017249584336</v>
       </c>
       <c r="T8">
-        <v>7.687901989610495</v>
+        <v>7.648737367903129</v>
       </c>
       <c r="U8">
         <v>7.7947</v>
@@ -1789,28 +1789,28 @@
         <v>7.8499</v>
       </c>
       <c r="W8">
-        <v>7.766631252348002</v>
+        <v>7.751017249584336</v>
       </c>
       <c r="X8">
         <v>7.857625</v>
       </c>
       <c r="Y8">
-        <v>-0.003601004227487576</v>
+        <v>-0.005604160572653647</v>
       </c>
       <c r="Z8">
-        <v>0.4460667088120358</v>
+        <v>0.6942034233716854</v>
       </c>
       <c r="AA8">
-        <v>0.003601004227487576</v>
+        <v>0.005604160572653647</v>
       </c>
       <c r="AB8">
-        <v>0.4458619428617201</v>
+        <v>0.4366752885464417</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3541380571382799</v>
+        <v>0.3633247114535583</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1849,19 +1849,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.1010586395992964</v>
+        <v>0.1033853678495548</v>
       </c>
       <c r="AR8">
-        <v>0.0512383816620252</v>
+        <v>0.04651430074105194</v>
       </c>
       <c r="AS8">
-        <v>0.0726270304249484</v>
+        <v>0.064994795730727</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1932,10 +1932,10 @@
         <v>9.08699</v>
       </c>
       <c r="S9">
-        <v>9.029593397027938</v>
+        <v>9.033570353221139</v>
       </c>
       <c r="T9">
-        <v>8.953269249755692</v>
+        <v>8.95805394890828</v>
       </c>
       <c r="U9">
         <v>9.08699</v>
@@ -1944,28 +1944,28 @@
         <v>9.08365</v>
       </c>
       <c r="W9">
-        <v>9.029593397027938</v>
+        <v>9.033570353221139</v>
       </c>
       <c r="X9">
         <v>9.174822499999999</v>
       </c>
       <c r="Y9">
-        <v>-0.006316349305112285</v>
+        <v>-0.00587869545128381</v>
       </c>
       <c r="Z9">
-        <v>0.6534779605733919</v>
+        <v>0.6081990923503442</v>
       </c>
       <c r="AA9">
-        <v>0.006316349305112285</v>
+        <v>0.00587869545128381</v>
       </c>
       <c r="AB9">
-        <v>0.4197291614714603</v>
+        <v>0.404054477332267</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3802708385285397</v>
+        <v>0.395945522667733</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -2004,19 +2004,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.1051394232482715</v>
+        <v>0.1205436691108248</v>
       </c>
       <c r="AR9">
-        <v>0.04446559150959063</v>
+        <v>0.0400734366610779</v>
       </c>
       <c r="AS9">
-        <v>0.05358066263135217</v>
+        <v>0.04734373094329805</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2057,70 +2057,70 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
         <v>46239</v>
       </c>
       <c r="K10">
-        <v>0.2872454174635685</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.677131246811971</v>
+        <v>0.8173047550643496</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q10">
-        <v>0.8218113543658921</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>6.74733</v>
+        <v>0.8066800000000001</v>
       </c>
       <c r="S10">
-        <v>6.701758285646064</v>
+        <v>0.8003041146654499</v>
       </c>
       <c r="T10">
-        <v>6.660151254983846</v>
+        <v>0.7928026802088131</v>
       </c>
       <c r="U10">
-        <v>6.74733</v>
+        <v>0.8066800000000001</v>
       </c>
       <c r="V10">
-        <v>6.71336</v>
+        <v>0.8049600000000001</v>
       </c>
       <c r="W10">
-        <v>6.701758285646064</v>
+        <v>0.8003041146654499</v>
       </c>
       <c r="X10">
-        <v>6.777711142902624</v>
+        <v>0.81616</v>
       </c>
       <c r="Y10">
-        <v>-0.006754036686205627</v>
+        <v>-0.007903859441848236</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>0.672561744150859</v>
       </c>
       <c r="AA10">
-        <v>0.006754036686205627</v>
+        <v>0.007903859441848236</v>
       </c>
       <c r="AB10">
-        <v>0.3457272737470512</v>
+        <v>0.411265428600029</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4542727262529488</v>
+        <v>0.388734571399971</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2132,46 +2132,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>410.9056771829461</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.004502691124137085</v>
+        <v>0.01175187186988643</v>
       </c>
       <c r="AJ10">
-        <v>111044.7033152473</v>
+        <v>42546.41350210976</v>
       </c>
       <c r="AK10">
-        <v>91257.79802666207</v>
+        <v>42546.41350210976</v>
       </c>
       <c r="AL10">
-        <v>13525.02367998335</v>
+        <v>52742.61603375534</v>
       </c>
       <c r="AM10">
-        <v>912.5779802666207</v>
+        <v>425.4641350210976</v>
       </c>
       <c r="AN10">
-        <v>0.009125779802666207</v>
+        <v>0.004254641350210976</v>
       </c>
       <c r="AO10">
-        <v>410.9056771829461</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>0.00410905677182946</v>
+        <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.075546036782613</v>
+        <v>0.0188382369344123</v>
       </c>
       <c r="AR10">
-        <v>0.01414789751504147</v>
+        <v>0.004833727198490056</v>
       </c>
       <c r="AS10">
-        <v>0.01092093721579322</v>
+        <v>0.007268316473312104</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2212,70 +2212,70 @@
         <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2">
         <v>46239</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.2588874665877943</v>
       </c>
       <c r="L11">
-        <v>0.8295875572996088</v>
+        <v>2.642373204981608</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.8147218666469486</v>
       </c>
       <c r="R11">
-        <v>0.8066800000000001</v>
+        <v>6.74733</v>
       </c>
       <c r="S11">
-        <v>0.8008182428182398</v>
+        <v>6.670759159880555</v>
       </c>
       <c r="T11">
-        <v>0.7941757539463682</v>
+        <v>6.574913637424834</v>
       </c>
       <c r="U11">
-        <v>0.8066800000000001</v>
+        <v>6.74733</v>
       </c>
       <c r="V11">
-        <v>0.8049600000000001</v>
+        <v>6.71336</v>
       </c>
       <c r="W11">
-        <v>0.8008182428182398</v>
+        <v>6.670759159880555</v>
       </c>
       <c r="X11">
-        <v>0.81616</v>
+        <v>6.798377226746296</v>
       </c>
       <c r="Y11">
-        <v>-0.007266521026628026</v>
+        <v>-0.01134831705570122</v>
       </c>
       <c r="Z11">
-        <v>0.6183288166413823</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.007266521026628026</v>
+        <v>0.01134831705570122</v>
       </c>
       <c r="AB11">
-        <v>0.4159546397079577</v>
+        <v>0.3567796163126223</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3840453602920423</v>
+        <v>0.4432203836873777</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2287,46 +2287,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>500</v>
+        <v>407.3609333234743</v>
       </c>
       <c r="AI11">
-        <v>0.01175187186988643</v>
+        <v>0.007565544703800811</v>
       </c>
       <c r="AJ11">
-        <v>42546.41350210976</v>
+        <v>66089.09464890319</v>
       </c>
       <c r="AK11">
-        <v>42546.41350210976</v>
+        <v>53844.23055736127</v>
       </c>
       <c r="AL11">
-        <v>52742.61603375534</v>
+        <v>7980.079610358656</v>
       </c>
       <c r="AM11">
-        <v>425.4641350210976</v>
+        <v>538.4423055736127</v>
       </c>
       <c r="AN11">
-        <v>0.004254641350210976</v>
+        <v>0.005384423055736127</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>407.3609333234743</v>
       </c>
       <c r="AP11">
-        <v>0.005</v>
+        <v>0.004073609333234742</v>
       </c>
       <c r="AQ11">
-        <v>0.01878910261782699</v>
+        <v>0.06804728475470198</v>
       </c>
       <c r="AR11">
-        <v>0.00541413553711769</v>
+        <v>0.01247837149337394</v>
       </c>
       <c r="AS11">
-        <v>0.008035879580256129</v>
+        <v>0.0112953359115846</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04343152500130548</v>
+        <v>0.03910147263564134</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
   <si>
     <t>Pair</t>
   </si>
@@ -169,118 +169,103 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
+    <t>USDCHF</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02049,naive=0.006978,drift4=0.0074; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=388,naive=122.5,drift4=166.4; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01764,naive=0.002899,drift4=0.004002; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.05484,naive=0.018,drift4=0.01192; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02172,naive=0.008021,drift4=0.008918; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.187,naive=3.169,drift4=4.458; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.1034,naive=0.04651,drift4=0.06499; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1205,naive=0.04007,drift4=0.04734; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01884,naive=0.004834,drift4=0.007268; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.06805,naive=0.01248,drift4=0.0113; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=397.2,naive=103.6,drift4=146.2; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01679,naive=0.002541,drift4=0.004952; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05303,naive=0.009197,drift4=0.01106; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.281,naive=3.275,drift4=4.575; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01901,naive=0.007296,drift4=0.007388; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01488,naive=0.004938,drift4=0.00683; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02233,naive=0.007922,drift4=0.009213; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.08717,naive=0.04505,drift4=0.06759; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.06969,naive=0.01332,drift4=0.01084; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1049,naive=0.04212,drift4=0.04972; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -808,7 +793,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -823,70 +808,79 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J2" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.8655590227027731</v>
+        <v>0.02541797099827621</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>1.34671</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="S2">
-        <v>1.347055682500632</v>
+        <v>4340.41417539278</v>
       </c>
       <c r="T2">
-        <v>1.3412496786902</v>
+        <v>4367.531238660604</v>
       </c>
       <c r="U2">
-        <v>1.34671</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="V2">
-        <v>1.35292</v>
+        <v>4362.519999999999</v>
+      </c>
+      <c r="W2">
+        <v>4340.41417539278</v>
+      </c>
+      <c r="X2">
+        <v>4103.2725</v>
       </c>
       <c r="Y2">
-        <v>0.0002566866664924517</v>
+        <v>0.02324819071921837</v>
+      </c>
+      <c r="Z2">
+        <v>0.7118743599125161</v>
       </c>
       <c r="AA2">
-        <v>0.0002566866664924517</v>
+        <v>0.02324819071921837</v>
       </c>
       <c r="AB2">
-        <v>0.3960745704136094</v>
+        <v>0.4067208789724112</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4039254295863905</v>
+        <v>0.3932791210275888</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -895,55 +889,58 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI2">
+        <v>0.03265771606393492</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.6093916370396</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>153.1031744599457</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.001531031744599457</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ2">
-        <v>0.02049388346590836</v>
+        <v>397.1911777113008</v>
       </c>
       <c r="AR2">
-        <v>0.00697824986102748</v>
+        <v>103.6088461173436</v>
       </c>
       <c r="AS2">
-        <v>0.007399798417737032</v>
+        <v>146.1632191822883</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AW2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AY2" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +948,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,79 +963,79 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J3" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1235224784910224</v>
+        <v>0.4555109864156004</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R3">
-        <v>4268.639999999999</v>
+        <v>0.702825</v>
       </c>
       <c r="S3">
-        <v>4503.120458064439</v>
+        <v>0.7068176889676537</v>
       </c>
       <c r="T3">
-        <v>4697.952148667046</v>
+        <v>0.7051258522573058</v>
       </c>
       <c r="U3">
-        <v>4268.639999999999</v>
+        <v>0.702825</v>
       </c>
       <c r="V3">
-        <v>4416.199999999999</v>
+        <v>0.7106500000000001</v>
       </c>
       <c r="W3">
-        <v>4503.120458064439</v>
+        <v>0.7068176889676537</v>
       </c>
       <c r="X3">
-        <v>4112.319694623707</v>
+        <v>0.695125</v>
       </c>
       <c r="Y3">
-        <v>0.05493095179364846</v>
+        <v>0.005680914833214102</v>
       </c>
       <c r="Z3">
-        <v>1.5</v>
+        <v>0.5185310347602163</v>
       </c>
       <c r="AA3">
-        <v>0.05493095179364846</v>
+        <v>0.005680914833214102</v>
       </c>
       <c r="AB3">
-        <v>0.4132442595922519</v>
+        <v>0.4104363492712391</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3867557404077481</v>
+        <v>0.3895636507287609</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1047,58 +1044,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI3">
-        <v>0.03662063452909897</v>
+        <v>0.01095578557962518</v>
       </c>
       <c r="AJ3">
-        <v>13653.50454544137</v>
+        <v>45637.98701298661</v>
       </c>
       <c r="AK3">
-        <v>13653.50454544137</v>
+        <v>34228.49025973996</v>
       </c>
       <c r="AL3">
-        <v>3.198560793470842</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM3">
-        <v>136.5350454544137</v>
+        <v>342.2849025973995</v>
       </c>
       <c r="AN3">
-        <v>0.001365350454544137</v>
+        <v>0.003422849025973995</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ3">
-        <v>388.0228832822809</v>
+        <v>0.01679313873937983</v>
       </c>
       <c r="AR3">
-        <v>122.5489846712669</v>
+        <v>0.002541158608047896</v>
       </c>
       <c r="AS3">
-        <v>166.447380990724</v>
+        <v>0.004951605716327471</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY3" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1103,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,82 +1115,82 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" t="s">
         <v>65</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" t="s">
         <v>67</v>
       </c>
-      <c r="H4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" t="s">
-        <v>69</v>
-      </c>
       <c r="J4" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.5567459216752554</v>
+        <v>0.06525604818593596</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0.705725</v>
+        <v>4.74391</v>
       </c>
       <c r="S4">
-        <v>0.7115063595394642</v>
+        <v>4.751399327901053</v>
       </c>
       <c r="T4">
-        <v>0.7091979286954787</v>
+        <v>4.729077627896135</v>
       </c>
       <c r="U4">
-        <v>0.705725</v>
+        <v>4.74391</v>
       </c>
       <c r="V4">
-        <v>0.7164500000000001</v>
+        <v>4.774819999999999</v>
       </c>
       <c r="W4">
-        <v>0.7115063595394642</v>
+        <v>4.751399327901053</v>
       </c>
       <c r="X4">
-        <v>0.698025</v>
+        <v>4.7090625</v>
       </c>
       <c r="Y4">
-        <v>0.008192085499966879</v>
+        <v>0.001578724701997614</v>
       </c>
       <c r="Z4">
-        <v>0.7508259142161137</v>
+        <v>0.2149172222125982</v>
       </c>
       <c r="AA4">
-        <v>0.008192085499966879</v>
+        <v>0.001578724701997614</v>
       </c>
       <c r="AB4">
-        <v>0.3859091207212976</v>
+        <v>0.3768644105251811</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4140908792787024</v>
+        <v>0.4231355894748189</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1202,58 +1199,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.010910765524815</v>
+        <v>0.007345733793431984</v>
       </c>
       <c r="AJ4">
-        <v>45826.2987012983</v>
+        <v>68066.71927684928</v>
       </c>
       <c r="AK4">
-        <v>34369.72402597372</v>
+        <v>68066.71927684928</v>
       </c>
       <c r="AL4">
-        <v>48701.29870129827</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM4">
-        <v>343.6972402597372</v>
+        <v>680.6671927684928</v>
       </c>
       <c r="AN4">
-        <v>0.003436972402597372</v>
+        <v>0.006806671927684927</v>
       </c>
       <c r="AO4">
-        <v>374.9999999999999</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP4">
-        <v>0.003749999999999999</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.01763968225699579</v>
+        <v>0.05302956846783115</v>
       </c>
       <c r="AR4">
-        <v>0.002899229413044679</v>
+        <v>0.009196851144777574</v>
       </c>
       <c r="AS4">
-        <v>0.004002154579317642</v>
+        <v>0.01106358535704662</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AX4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY4" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1258,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1276,79 +1273,79 @@
         <v>63</v>
       </c>
       <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" t="s">
         <v>67</v>
       </c>
-      <c r="H5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" t="s">
-        <v>70</v>
-      </c>
       <c r="J5" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1729772277224456</v>
       </c>
       <c r="L5">
-        <v>0.04430240762997241</v>
+        <v>1.724392151632915</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.7932443069306114</v>
       </c>
       <c r="R5">
-        <v>4.76213</v>
+        <v>158.517</v>
       </c>
       <c r="S5">
-        <v>4.793264978878625</v>
+        <v>158.3553453867571</v>
       </c>
       <c r="T5">
-        <v>4.788284486143543</v>
+        <v>160.3518610676166</v>
       </c>
       <c r="U5">
-        <v>4.76213</v>
+        <v>158.517</v>
       </c>
       <c r="V5">
-        <v>4.81126</v>
+        <v>155.344</v>
       </c>
       <c r="W5">
-        <v>4.793264978878625</v>
+        <v>158.2792245</v>
       </c>
       <c r="X5">
-        <v>4.7272825</v>
+        <v>160.159</v>
       </c>
       <c r="Y5">
-        <v>0.006538036315393541</v>
+        <v>-0.001019793544180675</v>
       </c>
       <c r="Z5">
-        <v>0.8934637744063452</v>
+        <v>0.1448084652862379</v>
       </c>
       <c r="AA5">
-        <v>0.006538036315393541</v>
+        <v>0.001019793544180675</v>
       </c>
       <c r="AB5">
-        <v>0.3555533587806834</v>
+        <v>0.4746029002534319</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4444466412193167</v>
+        <v>0.3253970997465682</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1357,58 +1354,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>396.6221534653057</v>
       </c>
       <c r="AI5">
-        <v>0.007317628876154141</v>
+        <v>0.0103585104436747</v>
       </c>
       <c r="AJ5">
-        <v>68328.14405624522</v>
+        <v>48269.48842874597</v>
       </c>
       <c r="AK5">
-        <v>68328.14405624522</v>
+        <v>38289.49689455576</v>
       </c>
       <c r="AL5">
-        <v>14348.23158045774</v>
+        <v>241.5482055208953</v>
       </c>
       <c r="AM5">
-        <v>683.2814405624522</v>
+        <v>382.8949689455577</v>
       </c>
       <c r="AN5">
-        <v>0.006832814405624522</v>
+        <v>0.003828949689455577</v>
       </c>
       <c r="AO5">
-        <v>499.9999999999999</v>
+        <v>396.6221534653057</v>
       </c>
       <c r="AP5">
-        <v>0.004999999999999999</v>
+        <v>0.003966221534653057</v>
       </c>
       <c r="AQ5">
-        <v>0.05484312935026162</v>
+        <v>4.280869079203722</v>
       </c>
       <c r="AR5">
-        <v>0.0179985595282394</v>
+        <v>3.2746455770627</v>
       </c>
       <c r="AS5">
-        <v>0.01191892848701538</v>
+        <v>4.57544965190767</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY5" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1413,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,82 +1425,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J6" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.468749840353423</v>
+        <v>0.8444055334790207</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>1.15551</v>
+        <v>1.345145</v>
       </c>
       <c r="S6">
-        <v>1.157452282827527</v>
+        <v>1.343288230207564</v>
       </c>
       <c r="T6">
-        <v>1.146425364745148</v>
+        <v>1.335813427336183</v>
       </c>
       <c r="U6">
-        <v>1.15551</v>
+        <v>1.345145</v>
       </c>
       <c r="V6">
-        <v>1.16972</v>
+        <v>1.34979</v>
       </c>
       <c r="W6">
-        <v>1.157452282827527</v>
+        <v>1.3431272825</v>
       </c>
       <c r="X6">
-        <v>1.14251</v>
+        <v>1.35930125</v>
       </c>
       <c r="Y6">
-        <v>0.001680887943442537</v>
+        <v>-0.001380349176063454</v>
       </c>
       <c r="Z6">
-        <v>0.1494063713482527</v>
+        <v>0.1425319205298015</v>
       </c>
       <c r="AA6">
-        <v>0.001680887943442537</v>
+        <v>0.001380349176063454</v>
       </c>
       <c r="AB6">
-        <v>0.4046303824615381</v>
+        <v>0.3987221993888813</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3953696175384619</v>
+        <v>0.4012778006111187</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,58 +1509,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.0112504435271006</v>
+        <v>0.01052395838366866</v>
       </c>
       <c r="AJ6">
-        <v>44442.69230769228</v>
+        <v>47510.64017660051</v>
       </c>
       <c r="AK6">
-        <v>33332.01923076921</v>
+        <v>47510.64017660051</v>
       </c>
       <c r="AL6">
-        <v>28846.15384615382</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM6">
-        <v>333.320192307692</v>
+        <v>475.1064017660051</v>
       </c>
       <c r="AN6">
-        <v>0.00333320192307692</v>
+        <v>0.004751064017660051</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>0.021719833955678</v>
+        <v>0.01900751894855534</v>
       </c>
       <c r="AR6">
-        <v>0.008021460448215166</v>
+        <v>0.007295565374673613</v>
       </c>
       <c r="AS6">
-        <v>0.008917600017036799</v>
+        <v>0.007388153983550467</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY6" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1568,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,82 +1580,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J7" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K7">
-        <v>0.06640297558107278</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.624084279917644</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="O7" t="s">
+        <v>69</v>
+      </c>
+      <c r="P7" t="s">
         <v>71</v>
       </c>
-      <c r="P7" t="s">
-        <v>74</v>
-      </c>
       <c r="Q7">
-        <v>0.9501977683141954</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>157.669</v>
+        <v>0.812665</v>
       </c>
       <c r="S7">
-        <v>157.8906338727083</v>
+        <v>0.8099574820918927</v>
       </c>
       <c r="T7">
-        <v>160.8963582811799</v>
+        <v>0.8022722374223907</v>
       </c>
       <c r="U7">
-        <v>157.669</v>
+        <v>0.812665</v>
       </c>
       <c r="V7">
-        <v>153.648</v>
+        <v>0.8169299999999999</v>
       </c>
       <c r="W7">
-        <v>157.9055035</v>
+        <v>0.8099574820918927</v>
       </c>
       <c r="X7">
-        <v>156.067</v>
+        <v>0.8221449999999999</v>
       </c>
       <c r="Y7">
-        <v>0.001405690863190216</v>
+        <v>-0.003331653151184442</v>
       </c>
       <c r="Z7">
-        <v>0.1476301498127351</v>
+        <v>0.28560315486364</v>
       </c>
       <c r="AA7">
-        <v>0.001405690863190216</v>
+        <v>0.003331653151184442</v>
       </c>
       <c r="AB7">
-        <v>0.4743741602337886</v>
+        <v>0.4174933163029476</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3256258397662114</v>
+        <v>0.3825066836970525</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,58 +1664,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>475.0988841570977</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01016052616557465</v>
+        <v>0.01166532334971974</v>
       </c>
       <c r="AJ7">
-        <v>49210.04993757835</v>
+        <v>42862.07805907178</v>
       </c>
       <c r="AK7">
-        <v>46759.27962931706</v>
+        <v>42862.07805907178</v>
       </c>
       <c r="AL7">
-        <v>296.5660949794637</v>
+        <v>52742.61603375534</v>
       </c>
       <c r="AM7">
-        <v>467.5927962931706</v>
+        <v>428.6207805907177</v>
       </c>
       <c r="AN7">
-        <v>0.004675927962931706</v>
+        <v>0.004286207805907177</v>
       </c>
       <c r="AO7">
-        <v>475.0988841570978</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.004750988841570978</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>4.187255394617863</v>
+        <v>0.01488205987812656</v>
       </c>
       <c r="AR7">
-        <v>3.169067860778971</v>
+        <v>0.00493814582944648</v>
       </c>
       <c r="AS7">
-        <v>4.458095412923126</v>
+        <v>0.006829982840446672</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY7" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1723,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,82 +1735,82 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>70</v>
-      </c>
       <c r="J8" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.189864250044427</v>
+        <v>0.405796303637743</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>7.7947</v>
+        <v>1.152205</v>
       </c>
       <c r="S8">
-        <v>7.751017249584336</v>
+        <v>1.146655927010239</v>
       </c>
       <c r="T8">
-        <v>7.648737367903129</v>
+        <v>1.127977763191877</v>
       </c>
       <c r="U8">
-        <v>7.7947</v>
+        <v>1.152205</v>
       </c>
       <c r="V8">
-        <v>7.8499</v>
+        <v>1.16311</v>
       </c>
       <c r="W8">
-        <v>7.751017249584336</v>
+        <v>1.146655927010239</v>
       </c>
       <c r="X8">
-        <v>7.857625</v>
+        <v>1.165205</v>
       </c>
       <c r="Y8">
-        <v>-0.005604160572653647</v>
+        <v>-0.004816046614760814</v>
       </c>
       <c r="Z8">
-        <v>0.6942034233716854</v>
+        <v>0.4268517684431138</v>
       </c>
       <c r="AA8">
-        <v>0.005604160572653647</v>
+        <v>0.004816046614760814</v>
       </c>
       <c r="AB8">
-        <v>0.4366752885464417</v>
+        <v>0.4062671291815001</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3633247114535583</v>
+        <v>0.3937328708184999</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,58 +1819,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.008072793051688983</v>
+        <v>0.01128271444751586</v>
       </c>
       <c r="AJ8">
-        <v>61936.43226062762</v>
+        <v>44315.57692307689</v>
       </c>
       <c r="AK8">
-        <v>46452.32419547071</v>
+        <v>44315.57692307689</v>
       </c>
       <c r="AL8">
-        <v>5959.475566150168</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM8">
-        <v>464.5232419547071</v>
+        <v>443.1557692307688</v>
       </c>
       <c r="AN8">
-        <v>0.004645232419547071</v>
+        <v>0.004431557692307688</v>
       </c>
       <c r="AO8">
-        <v>375</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP8">
-        <v>0.00375</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.1033853678495548</v>
+        <v>0.02232993397772965</v>
       </c>
       <c r="AR8">
-        <v>0.04651430074105194</v>
+        <v>0.007922158762517428</v>
       </c>
       <c r="AS8">
-        <v>0.064994795730727</v>
+        <v>0.009212591418826686</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY8" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1878,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,82 +1890,82 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J9" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.007589455652057173</v>
+        <v>0.1963517415702094</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>9.08699</v>
+        <v>7.7765</v>
       </c>
       <c r="S9">
-        <v>9.033570353221139</v>
+        <v>7.734555319021811</v>
       </c>
       <c r="T9">
-        <v>8.95805394890828</v>
+        <v>7.655262878115789</v>
       </c>
       <c r="U9">
-        <v>9.08699</v>
+        <v>7.7765</v>
       </c>
       <c r="V9">
-        <v>9.08365</v>
+        <v>7.813500000000001</v>
       </c>
       <c r="W9">
-        <v>9.033570353221139</v>
+        <v>7.734555319021811</v>
       </c>
       <c r="X9">
-        <v>9.174822499999999</v>
+        <v>7.839425</v>
       </c>
       <c r="Y9">
-        <v>-0.00587869545128381</v>
+        <v>-0.005393773674299412</v>
       </c>
       <c r="Z9">
-        <v>0.6081990923503442</v>
+        <v>0.6665821371186221</v>
       </c>
       <c r="AA9">
-        <v>0.00587869545128381</v>
+        <v>0.005393773674299412</v>
       </c>
       <c r="AB9">
-        <v>0.404054477332267</v>
+        <v>0.4521358839586476</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.395945522667733</v>
+        <v>0.3478641160413524</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1977,58 +1974,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.009665741901333638</v>
+        <v>0.008091686491352166</v>
       </c>
       <c r="AJ9">
-        <v>51729.08661372513</v>
+        <v>61791.8156535557</v>
       </c>
       <c r="AK9">
-        <v>51729.08661372513</v>
+        <v>46343.86174016677</v>
       </c>
       <c r="AL9">
-        <v>5692.653630489868</v>
+        <v>5959.475566150167</v>
       </c>
       <c r="AM9">
-        <v>517.2908661372513</v>
+        <v>463.4386174016677</v>
       </c>
       <c r="AN9">
-        <v>0.005172908661372514</v>
+        <v>0.004634386174016678</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP9">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ9">
-        <v>0.1205436691108248</v>
+        <v>0.08716993882778105</v>
       </c>
       <c r="AR9">
-        <v>0.0400734366610779</v>
+        <v>0.04504504250905235</v>
       </c>
       <c r="AS9">
-        <v>0.04734373094329805</v>
+        <v>0.06758873446495883</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY9" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2033,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,82 +2045,82 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J10" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.3267611576069867</v>
       </c>
       <c r="L10">
-        <v>0.8173047550643496</v>
+        <v>2.726011728951056</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.8316902894017467</v>
       </c>
       <c r="R10">
-        <v>0.8066800000000001</v>
+        <v>6.74783</v>
       </c>
       <c r="S10">
-        <v>0.8003041146654499</v>
+        <v>6.701955186460453</v>
       </c>
       <c r="T10">
-        <v>0.7928026802088131</v>
+        <v>6.659823542736155</v>
       </c>
       <c r="U10">
-        <v>0.8066800000000001</v>
+        <v>6.74783</v>
       </c>
       <c r="V10">
-        <v>0.8049600000000001</v>
+        <v>6.714360000000001</v>
       </c>
       <c r="W10">
-        <v>0.8003041146654499</v>
+        <v>6.701955186460453</v>
       </c>
       <c r="X10">
-        <v>0.81616</v>
+        <v>6.778413209026366</v>
       </c>
       <c r="Y10">
-        <v>-0.007903859441848236</v>
+        <v>-0.006798454249669486</v>
       </c>
       <c r="Z10">
-        <v>0.672561744150859</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>0.007903859441848236</v>
+        <v>0.006798454249669486</v>
       </c>
       <c r="AB10">
-        <v>0.411265428600029</v>
+        <v>0.3502026808809546</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.388734571399971</v>
+        <v>0.4497973191190455</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2132,58 +2129,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>415.8451447008733</v>
       </c>
       <c r="AI10">
-        <v>0.01175187186988643</v>
+        <v>0.004532302833112991</v>
       </c>
       <c r="AJ10">
-        <v>42546.41350210976</v>
+        <v>110319.1949900173</v>
       </c>
       <c r="AK10">
-        <v>42546.41350210976</v>
+        <v>91751.40320781524</v>
       </c>
       <c r="AL10">
-        <v>52742.61603375534</v>
+        <v>13597.17171413851</v>
       </c>
       <c r="AM10">
-        <v>425.4641350210976</v>
+        <v>917.5140320781524</v>
       </c>
       <c r="AN10">
-        <v>0.004254641350210976</v>
+        <v>0.009175140320781523</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>415.8451447008734</v>
       </c>
       <c r="AP10">
-        <v>0.005</v>
+        <v>0.004158451447008733</v>
       </c>
       <c r="AQ10">
-        <v>0.0188382369344123</v>
+        <v>0.06969353820089177</v>
       </c>
       <c r="AR10">
-        <v>0.004833727198490056</v>
+        <v>0.01331742738552463</v>
       </c>
       <c r="AS10">
-        <v>0.007268316473312104</v>
+        <v>0.01083615915409801</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY10" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2188,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,82 +2200,82 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
-      </c>
       <c r="J11" s="2">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K11">
-        <v>0.2588874665877943</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.642373204981608</v>
+        <v>0.006939916177066721</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q11">
-        <v>0.8147218666469486</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>6.74733</v>
+        <v>9.07822</v>
       </c>
       <c r="S11">
-        <v>6.670759159880555</v>
+        <v>9.015184019029054</v>
       </c>
       <c r="T11">
-        <v>6.574913637424834</v>
+        <v>8.937476867689906</v>
       </c>
       <c r="U11">
-        <v>6.74733</v>
+        <v>9.07822</v>
       </c>
       <c r="V11">
-        <v>6.71336</v>
+        <v>9.06611</v>
       </c>
       <c r="W11">
-        <v>6.670759159880555</v>
+        <v>9.015184019029054</v>
       </c>
       <c r="X11">
-        <v>6.798377226746296</v>
+        <v>9.166052499999999</v>
       </c>
       <c r="Y11">
-        <v>-0.01134831705570122</v>
+        <v>-0.0069436498532693</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.7176840118514969</v>
       </c>
       <c r="AA11">
-        <v>0.01134831705570122</v>
+        <v>0.0069436498532693</v>
       </c>
       <c r="AB11">
-        <v>0.3567796163126223</v>
+        <v>0.4147297046482656</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4432203836873777</v>
+        <v>0.3852702953517345</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2287,58 +2284,58 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>407.3609333234743</v>
+        <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.007565544703800811</v>
+        <v>0.009675079475932481</v>
       </c>
       <c r="AJ11">
-        <v>66089.09464890319</v>
+        <v>51679.16204138573</v>
       </c>
       <c r="AK11">
-        <v>53844.23055736127</v>
+        <v>51679.16204138573</v>
       </c>
       <c r="AL11">
-        <v>7980.079610358656</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM11">
-        <v>538.4423055736127</v>
+        <v>516.7916204138573</v>
       </c>
       <c r="AN11">
-        <v>0.005384423055736127</v>
+        <v>0.005167916204138573</v>
       </c>
       <c r="AO11">
-        <v>407.3609333234743</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>0.004073609333234742</v>
+        <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.06804728475470198</v>
+        <v>0.1049437940918561</v>
       </c>
       <c r="AR11">
-        <v>0.01247837149337394</v>
+        <v>0.04212210767873095</v>
       </c>
       <c r="AS11">
-        <v>0.0112953359115846</v>
+        <v>0.04972189952339372</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03910147263564134</v>
+        <v>0.04803577460252564</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AY11" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,6 +169,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -178,37 +181,40 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -217,55 +223,64 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=397.2,naive=103.6,drift4=146.2; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01679,naive=0.002541,drift4=0.004952; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.05303,naive=0.009197,drift4=0.01106; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.281,naive=3.275,drift4=4.575; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01901,naive=0.007296,drift4=0.007388; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01488,naive=0.004938,drift4=0.00683; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02233,naive=0.007922,drift4=0.009213; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.08717,naive=0.04505,drift4=0.06759; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.06969,naive=0.01332,drift4=0.01084; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1049,naive=0.04212,drift4=0.04972; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01627,naive=0.004819,drift4=0.00607; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=351,naive=100.6,drift4=136.2; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01425,naive=0.002056,drift4=0.005166; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.04694,naive=0.01901,drift4=0.01154; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09606,naive=0.04178,drift4=0.05878; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.1253,naive=0.03628,drift4=0.0338; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01789,naive=0.006632,drift4=0.008555; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.0209,naive=0.00635,drift4=0.007539; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.223,naive=2.756,drift4=4.131; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.05421,naive=0.01062,drift4=0.01138; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -793,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -808,13 +823,13 @@
         <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
         <v>46240</v>
@@ -823,64 +838,55 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.02541797099827621</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>4241.799999999999</v>
+        <v>0.812665</v>
       </c>
       <c r="S2">
-        <v>4340.41417539278</v>
+        <v>0.8128482882601045</v>
       </c>
       <c r="T2">
-        <v>4367.531238660604</v>
+        <v>0.8089277019100782</v>
       </c>
       <c r="U2">
-        <v>4241.799999999999</v>
+        <v>0.812665</v>
       </c>
       <c r="V2">
-        <v>4362.519999999999</v>
-      </c>
-      <c r="W2">
-        <v>4340.41417539278</v>
-      </c>
-      <c r="X2">
-        <v>4103.2725</v>
+        <v>0.8169299999999999</v>
       </c>
       <c r="Y2">
-        <v>0.02324819071921837</v>
-      </c>
-      <c r="Z2">
-        <v>0.7118743599125161</v>
+        <v>0.0002255397489795884</v>
       </c>
       <c r="AA2">
-        <v>0.02324819071921837</v>
+        <v>0.0002255397489795884</v>
       </c>
       <c r="AB2">
-        <v>0.4067208789724112</v>
+        <v>0.4034730653138166</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3932791210275888</v>
+        <v>0.3965269346861835</v>
       </c>
       <c r="AE2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -889,58 +895,55 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>500</v>
-      </c>
-      <c r="AI2">
-        <v>0.03265771606393492</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>3.6093916370396</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>153.1031744599457</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.001531031744599457</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>397.1911777113008</v>
+        <v>0.0162662259261182</v>
       </c>
       <c r="AR2">
-        <v>103.6088461173436</v>
+        <v>0.004818996815679723</v>
       </c>
       <c r="AS2">
-        <v>146.1632191822883</v>
+        <v>0.006069971117429406</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -948,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,13 +966,13 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
         <v>46240</v>
@@ -978,64 +981,64 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.4555109864156004</v>
+        <v>0.0244440950116974</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
+        <v>109</v>
+      </c>
+      <c r="O3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3">
         <v>1</v>
       </c>
-      <c r="O3" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q3">
-        <v>0.75</v>
-      </c>
       <c r="R3">
-        <v>0.702825</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="S3">
-        <v>0.7068176889676537</v>
+        <v>4439.608909848444</v>
       </c>
       <c r="T3">
-        <v>0.7051258522573058</v>
+        <v>4610.699150393023</v>
       </c>
       <c r="U3">
-        <v>0.702825</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="V3">
-        <v>0.7106500000000001</v>
+        <v>4362.519999999999</v>
       </c>
       <c r="W3">
-        <v>0.7068176889676537</v>
+        <v>4439.608909848444</v>
       </c>
       <c r="X3">
-        <v>0.695125</v>
+        <v>4103.2725</v>
       </c>
       <c r="Y3">
-        <v>0.005680914833214102</v>
+        <v>0.04663324764214372</v>
       </c>
       <c r="Z3">
-        <v>0.5185310347602163</v>
+        <v>1.427939649877796</v>
       </c>
       <c r="AA3">
-        <v>0.005680914833214102</v>
+        <v>0.04663324764214372</v>
       </c>
       <c r="AB3">
-        <v>0.4104363492712391</v>
+        <v>0.4079025562305689</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3895636507287609</v>
+        <v>0.3920974437694311</v>
       </c>
       <c r="AE3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1044,58 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI3">
-        <v>0.01095578557962518</v>
+        <v>0.03265771606393492</v>
       </c>
       <c r="AJ3">
-        <v>45637.98701298661</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AK3">
-        <v>34228.49025973996</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AL3">
-        <v>48701.29870129827</v>
+        <v>3.6093916370396</v>
       </c>
       <c r="AM3">
-        <v>342.2849025973995</v>
+        <v>153.1031744599457</v>
       </c>
       <c r="AN3">
-        <v>0.003422849025973995</v>
+        <v>0.001531031744599457</v>
       </c>
       <c r="AO3">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.01679313873937983</v>
+        <v>350.9716042667308</v>
       </c>
       <c r="AR3">
-        <v>0.002541158608047896</v>
+        <v>100.6167076492043</v>
       </c>
       <c r="AS3">
-        <v>0.004951605716327471</v>
+        <v>136.1947503332836</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1103,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1115,16 +1118,16 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
         <v>46240</v>
@@ -1133,64 +1136,64 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.06525604818593596</v>
+        <v>0.506860381353027</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4.74391</v>
+        <v>0.702825</v>
       </c>
       <c r="S4">
-        <v>4.751399327901053</v>
+        <v>0.7079610870871413</v>
       </c>
       <c r="T4">
-        <v>4.729077627896135</v>
+        <v>0.7080268223449254</v>
       </c>
       <c r="U4">
-        <v>4.74391</v>
+        <v>0.702825</v>
       </c>
       <c r="V4">
-        <v>4.774819999999999</v>
+        <v>0.7106500000000001</v>
       </c>
       <c r="W4">
-        <v>4.751399327901053</v>
+        <v>0.7079610870871413</v>
       </c>
       <c r="X4">
-        <v>4.7090625</v>
+        <v>0.695125</v>
       </c>
       <c r="Y4">
-        <v>0.001578724701997614</v>
+        <v>0.007307775174675496</v>
       </c>
       <c r="Z4">
-        <v>0.2149172222125982</v>
+        <v>0.6670242970313325</v>
       </c>
       <c r="AA4">
-        <v>0.001578724701997614</v>
+        <v>0.007307775174675496</v>
       </c>
       <c r="AB4">
-        <v>0.3768644105251811</v>
+        <v>0.428454744833826</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4231355894748189</v>
+        <v>0.371545255166174</v>
       </c>
       <c r="AE4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1199,58 +1202,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.007345733793431984</v>
+        <v>0.01095578557962518</v>
       </c>
       <c r="AJ4">
-        <v>68066.71927684928</v>
+        <v>45637.98701298661</v>
       </c>
       <c r="AK4">
-        <v>68066.71927684928</v>
+        <v>34228.49025973996</v>
       </c>
       <c r="AL4">
-        <v>14348.23158045774</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM4">
-        <v>680.6671927684928</v>
+        <v>342.2849025973995</v>
       </c>
       <c r="AN4">
-        <v>0.006806671927684927</v>
+        <v>0.003422849025973995</v>
       </c>
       <c r="AO4">
-        <v>500.0000000000001</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP4">
-        <v>0.005000000000000001</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.05302956846783115</v>
+        <v>0.01425232761761736</v>
       </c>
       <c r="AR4">
-        <v>0.009196851144777574</v>
+        <v>0.002056304187160236</v>
       </c>
       <c r="AS4">
-        <v>0.01106358535704662</v>
+        <v>0.005166355074580426</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1258,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1270,82 +1273,82 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K5">
-        <v>0.1729772277224456</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.724392151632915</v>
+        <v>0.0011224821324551</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q5">
-        <v>0.7932443069306114</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>158.517</v>
+        <v>4.76528</v>
       </c>
       <c r="S5">
-        <v>158.3553453867571</v>
+        <v>4.781387027789476</v>
       </c>
       <c r="T5">
-        <v>160.3518610676166</v>
+        <v>4.745867576179772</v>
       </c>
       <c r="U5">
-        <v>158.517</v>
+        <v>4.76528</v>
       </c>
       <c r="V5">
-        <v>155.344</v>
+        <v>4.817559999999999</v>
       </c>
       <c r="W5">
-        <v>158.2792245</v>
+        <v>4.781387027789476</v>
       </c>
       <c r="X5">
-        <v>160.159</v>
+        <v>4.7304325</v>
       </c>
       <c r="Y5">
-        <v>-0.001019793544180675</v>
+        <v>0.003380080035061186</v>
       </c>
       <c r="Z5">
-        <v>0.1448084652862379</v>
+        <v>0.4622147295925506</v>
       </c>
       <c r="AA5">
-        <v>0.001019793544180675</v>
+        <v>0.003380080035061186</v>
       </c>
       <c r="AB5">
-        <v>0.4746029002534319</v>
+        <v>0.3587125506456568</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3253970997465682</v>
+        <v>0.4412874493543432</v>
       </c>
       <c r="AE5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1354,58 +1357,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>396.6221534653057</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.0103585104436747</v>
+        <v>0.00731279169324781</v>
       </c>
       <c r="AJ5">
-        <v>48269.48842874597</v>
+        <v>68373.34098572365</v>
       </c>
       <c r="AK5">
-        <v>38289.49689455576</v>
+        <v>51280.00573929274</v>
       </c>
       <c r="AL5">
-        <v>241.5482055208953</v>
+        <v>10761.1736853433</v>
       </c>
       <c r="AM5">
-        <v>382.8949689455577</v>
+        <v>512.8000573929274</v>
       </c>
       <c r="AN5">
-        <v>0.003828949689455577</v>
+        <v>0.005128000573929275</v>
       </c>
       <c r="AO5">
-        <v>396.6221534653057</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.003966221534653057</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ5">
-        <v>4.280869079203722</v>
+        <v>0.04694244433687772</v>
       </c>
       <c r="AR5">
-        <v>3.2746455770627</v>
+        <v>0.01901016029710946</v>
       </c>
       <c r="AS5">
-        <v>4.57544965190767</v>
+        <v>0.01153568751042616</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV5" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1413,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1425,82 +1428,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.8444055334790207</v>
+        <v>0.0873260828937016</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="O6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>1.345145</v>
+        <v>7.7936</v>
       </c>
       <c r="S6">
-        <v>1.343288230207564</v>
+        <v>7.778483775693623</v>
       </c>
       <c r="T6">
-        <v>1.335813427336183</v>
+        <v>7.71348829918916</v>
       </c>
       <c r="U6">
-        <v>1.345145</v>
+        <v>7.7936</v>
       </c>
       <c r="V6">
-        <v>1.34979</v>
+        <v>7.8477</v>
       </c>
       <c r="W6">
-        <v>1.3431272825</v>
+        <v>7.778483775693623</v>
       </c>
       <c r="X6">
-        <v>1.35930125</v>
+        <v>7.856525</v>
       </c>
       <c r="Y6">
-        <v>-0.001380349176063454</v>
+        <v>-0.001939568916338654</v>
       </c>
       <c r="Z6">
-        <v>0.1425319205298015</v>
+        <v>0.2402260517501296</v>
       </c>
       <c r="AA6">
-        <v>0.001380349176063454</v>
+        <v>0.001939568916338654</v>
       </c>
       <c r="AB6">
-        <v>0.3987221993888813</v>
+        <v>0.4351053146154676</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.4012778006111187</v>
+        <v>0.3648946853845325</v>
       </c>
       <c r="AE6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1509,58 +1512,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01052395838366866</v>
+        <v>0.00807393245740096</v>
       </c>
       <c r="AJ6">
-        <v>47510.64017660051</v>
+        <v>61927.69169646392</v>
       </c>
       <c r="AK6">
-        <v>47510.64017660051</v>
+        <v>46445.76877234795</v>
       </c>
       <c r="AL6">
-        <v>35320.0883002208</v>
+        <v>5959.475566150168</v>
       </c>
       <c r="AM6">
-        <v>475.1064017660051</v>
+        <v>464.4576877234795</v>
       </c>
       <c r="AN6">
-        <v>0.004751064017660051</v>
+        <v>0.004644576877234795</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.01900751894855534</v>
+        <v>0.09605517607133826</v>
       </c>
       <c r="AR6">
-        <v>0.007295565374673613</v>
+        <v>0.041779463153615</v>
       </c>
       <c r="AS6">
-        <v>0.007388153983550467</v>
+        <v>0.05878122653161438</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV6" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1568,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,79 +1586,79 @@
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1.029249455050077</v>
+        <v>0.00811134348940943</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>0.812665</v>
+        <v>9.09496</v>
       </c>
       <c r="S7">
-        <v>0.8099574820918927</v>
+        <v>9.076217210498575</v>
       </c>
       <c r="T7">
-        <v>0.8022722374223907</v>
+        <v>9.040064246510893</v>
       </c>
       <c r="U7">
-        <v>0.812665</v>
+        <v>9.09496</v>
       </c>
       <c r="V7">
-        <v>0.8169299999999999</v>
+        <v>9.099590000000001</v>
       </c>
       <c r="W7">
-        <v>0.8099574820918927</v>
+        <v>9.076217210498575</v>
       </c>
       <c r="X7">
-        <v>0.8221449999999999</v>
+        <v>9.1827925</v>
       </c>
       <c r="Y7">
-        <v>-0.003331653151184442</v>
+        <v>-0.002060788557775472</v>
       </c>
       <c r="Z7">
-        <v>0.28560315486364</v>
+        <v>0.2133924174015957</v>
       </c>
       <c r="AA7">
-        <v>0.003331653151184442</v>
+        <v>0.002060788557775472</v>
       </c>
       <c r="AB7">
-        <v>0.4174933163029476</v>
+        <v>0.377093748263681</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3825066836970525</v>
+        <v>0.422906251736319</v>
       </c>
       <c r="AE7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,22 +1670,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01166532334971974</v>
+        <v>0.009657271719721664</v>
       </c>
       <c r="AJ7">
-        <v>42862.07805907178</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AK7">
-        <v>42862.07805907178</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AL7">
-        <v>52742.61603375534</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM7">
-        <v>428.6207805907177</v>
+        <v>517.7445706316014</v>
       </c>
       <c r="AN7">
-        <v>0.004286207805907177</v>
+        <v>0.005177445706316014</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1691,31 +1694,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.01488205987812656</v>
+        <v>0.1252864916586665</v>
       </c>
       <c r="AR7">
-        <v>0.00493814582944648</v>
+        <v>0.0362773644852826</v>
       </c>
       <c r="AS7">
-        <v>0.006829982840446672</v>
+        <v>0.03379848244961932</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1723,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1735,16 +1738,16 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
         <v>46240</v>
@@ -1753,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.405796303637743</v>
+        <v>0.4295741562412449</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1762,10 +1765,10 @@
         <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q8">
         <v>1</v>
@@ -1774,10 +1777,10 @@
         <v>1.152205</v>
       </c>
       <c r="S8">
-        <v>1.146655927010239</v>
+        <v>1.149487410616441</v>
       </c>
       <c r="T8">
-        <v>1.127977763191877</v>
+        <v>1.135722416291224</v>
       </c>
       <c r="U8">
         <v>1.152205</v>
@@ -1786,31 +1789,31 @@
         <v>1.16311</v>
       </c>
       <c r="W8">
-        <v>1.146655927010239</v>
+        <v>1.149487410616441</v>
       </c>
       <c r="X8">
         <v>1.165205</v>
       </c>
       <c r="Y8">
-        <v>-0.004816046614760814</v>
+        <v>-0.002358598846176616</v>
       </c>
       <c r="Z8">
-        <v>0.4268517684431138</v>
+        <v>0.2090453371968403</v>
       </c>
       <c r="AA8">
-        <v>0.004816046614760814</v>
+        <v>0.002358598846176616</v>
       </c>
       <c r="AB8">
-        <v>0.4062671291815001</v>
+        <v>0.4177655650539432</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3937328708184999</v>
+        <v>0.3822344349460568</v>
       </c>
       <c r="AE8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1846,31 +1849,31 @@
         <v>0.005000000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.02232993397772965</v>
+        <v>0.01789409651521521</v>
       </c>
       <c r="AR8">
-        <v>0.007922158762517428</v>
+        <v>0.006632066409174154</v>
       </c>
       <c r="AS8">
-        <v>0.009212591418826686</v>
+        <v>0.008555479815543068</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1878,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1890,16 +1893,16 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
         <v>46240</v>
@@ -1908,64 +1911,64 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.1963517415702094</v>
+        <v>0.8642703280274651</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>7.7765</v>
+        <v>1.345145</v>
       </c>
       <c r="S9">
-        <v>7.734555319021811</v>
+        <v>1.340067835602197</v>
       </c>
       <c r="T9">
-        <v>7.655262878115789</v>
+        <v>1.327792918652622</v>
       </c>
       <c r="U9">
-        <v>7.7765</v>
+        <v>1.345145</v>
       </c>
       <c r="V9">
-        <v>7.813500000000001</v>
+        <v>1.34979</v>
       </c>
       <c r="W9">
-        <v>7.734555319021811</v>
+        <v>1.340067835602197</v>
       </c>
       <c r="X9">
-        <v>7.839425</v>
+        <v>1.35930125</v>
       </c>
       <c r="Y9">
-        <v>-0.005393773674299412</v>
+        <v>-0.003774436508929051</v>
       </c>
       <c r="Z9">
-        <v>0.6665821371186221</v>
+        <v>0.3586517896903046</v>
       </c>
       <c r="AA9">
-        <v>0.005393773674299412</v>
+        <v>0.003774436508929051</v>
       </c>
       <c r="AB9">
-        <v>0.4521358839586476</v>
+        <v>0.399742323035582</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3478641160413524</v>
+        <v>0.4002576769644179</v>
       </c>
       <c r="AE9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1974,58 +1977,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.008091686491352166</v>
+        <v>0.01052395838366866</v>
       </c>
       <c r="AJ9">
-        <v>61791.8156535557</v>
+        <v>47510.64017660051</v>
       </c>
       <c r="AK9">
-        <v>46343.86174016677</v>
+        <v>47510.64017660051</v>
       </c>
       <c r="AL9">
-        <v>5959.475566150167</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM9">
-        <v>463.4386174016677</v>
+        <v>475.1064017660051</v>
       </c>
       <c r="AN9">
-        <v>0.004634386174016678</v>
+        <v>0.004751064017660051</v>
       </c>
       <c r="AO9">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.08716993882778105</v>
+        <v>0.02090013896296028</v>
       </c>
       <c r="AR9">
-        <v>0.04504504250905235</v>
+        <v>0.006350008227021008</v>
       </c>
       <c r="AS9">
-        <v>0.06758873446495883</v>
+        <v>0.007539236589116731</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2033,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2045,82 +2048,82 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
         <v>46240</v>
       </c>
       <c r="K10">
-        <v>0.3267611576069867</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2.726011728951056</v>
+        <v>1.496910670713708</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.8316902894017467</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>6.74783</v>
+        <v>158.517</v>
       </c>
       <c r="S10">
-        <v>6.701955186460453</v>
+        <v>157.5346106688172</v>
       </c>
       <c r="T10">
-        <v>6.659823542736155</v>
+        <v>158.6638511547774</v>
       </c>
       <c r="U10">
-        <v>6.74783</v>
+        <v>158.517</v>
       </c>
       <c r="V10">
-        <v>6.714360000000001</v>
+        <v>155.344</v>
       </c>
       <c r="W10">
-        <v>6.701955186460453</v>
+        <v>157.5346106688172</v>
       </c>
       <c r="X10">
-        <v>6.778413209026366</v>
+        <v>160.159</v>
       </c>
       <c r="Y10">
-        <v>-0.006798454249669486</v>
+        <v>-0.00619737524166377</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>0.5982882650321723</v>
       </c>
       <c r="AA10">
-        <v>0.006798454249669486</v>
+        <v>0.00619737524166377</v>
       </c>
       <c r="AB10">
-        <v>0.3502026808809546</v>
+        <v>0.4686989254256231</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4497973191190455</v>
+        <v>0.3313010745743769</v>
       </c>
       <c r="AE10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2129,58 +2132,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>415.8451447008733</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.004532302833112991</v>
+        <v>0.0103585104436747</v>
       </c>
       <c r="AJ10">
-        <v>110319.1949900173</v>
+        <v>48269.48842874597</v>
       </c>
       <c r="AK10">
-        <v>91751.40320781524</v>
+        <v>36202.11632155948</v>
       </c>
       <c r="AL10">
-        <v>13597.17171413851</v>
+        <v>228.3800243605385</v>
       </c>
       <c r="AM10">
-        <v>917.5140320781524</v>
+        <v>362.0211632155948</v>
       </c>
       <c r="AN10">
-        <v>0.009175140320781523</v>
+        <v>0.003620211632155948</v>
       </c>
       <c r="AO10">
-        <v>415.8451447008734</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.004158451447008733</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.06969353820089177</v>
+        <v>4.22318913851516</v>
       </c>
       <c r="AR10">
-        <v>0.01331742738552463</v>
+        <v>2.755984393716529</v>
       </c>
       <c r="AS10">
-        <v>0.01083615915409801</v>
+        <v>4.130636136869751</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2188,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2200,82 +2203,82 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2">
         <v>46240</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.2844424786311258</v>
       </c>
       <c r="L11">
-        <v>0.006939916177066721</v>
+        <v>2.674320367291286</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.8211106196577814</v>
       </c>
       <c r="R11">
-        <v>9.07822</v>
+        <v>6.74783</v>
       </c>
       <c r="S11">
-        <v>9.015184019029054</v>
+        <v>6.675172577865641</v>
       </c>
       <c r="T11">
-        <v>8.937476867689906</v>
+        <v>6.59106509376118</v>
       </c>
       <c r="U11">
-        <v>9.07822</v>
+        <v>6.74783</v>
       </c>
       <c r="V11">
-        <v>9.06611</v>
+        <v>6.714360000000001</v>
       </c>
       <c r="W11">
-        <v>9.015184019029054</v>
+        <v>6.675172577865641</v>
       </c>
       <c r="X11">
-        <v>9.166052499999999</v>
+        <v>6.796268281422907</v>
       </c>
       <c r="Y11">
-        <v>-0.0069436498532693</v>
+        <v>-0.01076752409802247</v>
       </c>
       <c r="Z11">
-        <v>0.7176840118514969</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.0069436498532693</v>
+        <v>0.01076752409802247</v>
       </c>
       <c r="AB11">
-        <v>0.4147297046482656</v>
+        <v>0.3721274749622436</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3852702953517345</v>
+        <v>0.4278725250377564</v>
       </c>
       <c r="AE11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2284,58 +2287,58 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>500</v>
+        <v>410.5553098288907</v>
       </c>
       <c r="AI11">
-        <v>0.009675079475932481</v>
+        <v>0.007178349398681649</v>
       </c>
       <c r="AJ11">
-        <v>51679.16204138573</v>
+        <v>69653.89565626721</v>
       </c>
       <c r="AK11">
-        <v>51679.16204138573</v>
+        <v>57193.55342389602</v>
       </c>
       <c r="AL11">
-        <v>5692.653630489868</v>
+        <v>8475.843852600912</v>
       </c>
       <c r="AM11">
-        <v>516.7916204138573</v>
+        <v>571.9355342389601</v>
       </c>
       <c r="AN11">
-        <v>0.005167916204138573</v>
+        <v>0.005719355342389602</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>410.5553098288908</v>
       </c>
       <c r="AP11">
-        <v>0.005</v>
+        <v>0.004105553098288908</v>
       </c>
       <c r="AQ11">
-        <v>0.1049437940918561</v>
+        <v>0.05421416703208381</v>
       </c>
       <c r="AR11">
-        <v>0.04212210767873095</v>
+        <v>0.01061616474712812</v>
       </c>
       <c r="AS11">
-        <v>0.04972189952339372</v>
+        <v>0.01138305530884299</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04803577460252564</v>
+        <v>0.03842609261256683</v>
       </c>
       <c r="AV11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
   <si>
     <t>Pair</t>
   </si>
@@ -169,18 +169,24 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -190,12 +196,6 @@
     <t>EURUSD</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -205,82 +205,70 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01627,naive=0.004819,drift4=0.00607; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=351,naive=100.6,drift4=136.2; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01425,naive=0.002056,drift4=0.005166; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.04694,naive=0.01901,drift4=0.01154; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.09606,naive=0.04178,drift4=0.05878; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.1253,naive=0.03628,drift4=0.0338; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01789,naive=0.006632,drift4=0.008555; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.0209,naive=0.00635,drift4=0.007539; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.223,naive=2.756,drift4=4.131; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.05421,naive=0.01062,drift4=0.01138; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=389.8,naive=100,drift4=137.4; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01781,naive=0.003155,drift4=0.003404; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.0602,naive=0.01922,drift4=0.01289; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.01717,naive=0.007896,drift4=0.005763; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.457,naive=3.279,drift4=4.543; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01507,naive=0.004836,drift4=0.006677; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.08131,naive=0.0482,drift4=0.06866; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1061,naive=0.04229,drift4=0.04077; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02039,naive=0.008629,drift4=0.009303; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.06109,naive=0.01437,drift4=0.01016; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -808,7 +796,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -829,7 +817,7 @@
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
         <v>46240</v>
@@ -838,55 +826,64 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.00416763117204</v>
+        <v>0.02541797099827621</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>0.812665</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="S2">
-        <v>0.8128482882601045</v>
+        <v>4319.101799672854</v>
       </c>
       <c r="T2">
-        <v>0.8089277019100782</v>
+        <v>4314.778111231457</v>
       </c>
       <c r="U2">
-        <v>0.812665</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="V2">
-        <v>0.8169299999999999</v>
+        <v>4362.519999999999</v>
+      </c>
+      <c r="W2">
+        <v>4319.101799672854</v>
+      </c>
+      <c r="X2">
+        <v>4103.2725</v>
       </c>
       <c r="Y2">
-        <v>0.0002255397489795884</v>
+        <v>0.01822381999925856</v>
+      </c>
+      <c r="Z2">
+        <v>0.5580249385346262</v>
       </c>
       <c r="AA2">
-        <v>0.0002255397489795884</v>
+        <v>0.01822381999925856</v>
       </c>
       <c r="AB2">
-        <v>0.4034730653138166</v>
+        <v>0.4037167532392456</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3965269346861835</v>
+        <v>0.3962832467607544</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -895,55 +892,58 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="AI2">
+        <v>0.03265771606393492</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.6093916370396</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>153.1031744599457</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.001531031744599457</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AQ2">
-        <v>0.0162662259261182</v>
+        <v>389.8302878991883</v>
       </c>
       <c r="AR2">
-        <v>0.004818996815679723</v>
+        <v>100.0087866504446</v>
       </c>
       <c r="AS2">
-        <v>0.006069971117429406</v>
+        <v>137.4096116069606</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AY2" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,82 +963,82 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.0244440950116974</v>
+        <v>0.7295228455748012</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>109</v>
+        <v>2</v>
       </c>
       <c r="O3" t="s">
         <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R3">
-        <v>4241.799999999999</v>
+        <v>0.70652</v>
       </c>
       <c r="S3">
-        <v>4439.608909848444</v>
+        <v>0.7117677207445479</v>
       </c>
       <c r="T3">
-        <v>4610.699150393023</v>
+        <v>0.7072883963104537</v>
       </c>
       <c r="U3">
-        <v>4241.799999999999</v>
+        <v>0.70652</v>
       </c>
       <c r="V3">
-        <v>4362.519999999999</v>
+        <v>0.7180400000000001</v>
       </c>
       <c r="W3">
-        <v>4439.608909848444</v>
+        <v>0.7117677207445479</v>
       </c>
       <c r="X3">
-        <v>4103.2725</v>
+        <v>0.69882</v>
       </c>
       <c r="Y3">
-        <v>0.04663324764214372</v>
+        <v>0.007427561490895973</v>
       </c>
       <c r="Z3">
-        <v>1.427939649877796</v>
+        <v>0.6815221746165945</v>
       </c>
       <c r="AA3">
-        <v>0.04663324764214372</v>
+        <v>0.007427561490895973</v>
       </c>
       <c r="AB3">
-        <v>0.4079025562305689</v>
+        <v>0.3690871957371829</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3920974437694311</v>
+        <v>0.430912804262817</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1047,58 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI3">
-        <v>0.03265771606393492</v>
+        <v>0.01089848836550992</v>
       </c>
       <c r="AJ3">
-        <v>15310.31744599457</v>
+        <v>45877.92207792167</v>
       </c>
       <c r="AK3">
-        <v>15310.31744599457</v>
+        <v>34408.44155844125</v>
       </c>
       <c r="AL3">
-        <v>3.6093916370396</v>
+        <v>48701.29870129826</v>
       </c>
       <c r="AM3">
-        <v>153.1031744599457</v>
+        <v>344.0844155844125</v>
       </c>
       <c r="AN3">
-        <v>0.001531031744599457</v>
+        <v>0.003440844155844125</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ3">
-        <v>350.9716042667308</v>
+        <v>0.01780543112232461</v>
       </c>
       <c r="AR3">
-        <v>100.6167076492043</v>
+        <v>0.003154695189921269</v>
       </c>
       <c r="AS3">
-        <v>136.1947503332836</v>
+        <v>0.00340448045774924</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY3" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1121,79 +1121,79 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.506860381353027</v>
+        <v>0.0011224821324551</v>
       </c>
       <c r="M4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>0.702825</v>
+        <v>4.76528</v>
       </c>
       <c r="S4">
-        <v>0.7079610870871413</v>
+        <v>4.781438601726977</v>
       </c>
       <c r="T4">
-        <v>0.7080268223449254</v>
+        <v>4.745331380627396</v>
       </c>
       <c r="U4">
-        <v>0.702825</v>
+        <v>4.76528</v>
       </c>
       <c r="V4">
-        <v>0.7106500000000001</v>
+        <v>4.817559999999999</v>
       </c>
       <c r="W4">
-        <v>0.7079610870871413</v>
+        <v>4.781438601726977</v>
       </c>
       <c r="X4">
-        <v>0.695125</v>
+        <v>4.7304325</v>
       </c>
       <c r="Y4">
-        <v>0.007307775174675496</v>
+        <v>0.003390902890696344</v>
       </c>
       <c r="Z4">
-        <v>0.6670242970313325</v>
+        <v>0.4636947191901143</v>
       </c>
       <c r="AA4">
-        <v>0.007307775174675496</v>
+        <v>0.003390902890696344</v>
       </c>
       <c r="AB4">
-        <v>0.428454744833826</v>
+        <v>0.3553355788323144</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.371545255166174</v>
+        <v>0.4446644211676857</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1205,22 +1205,22 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.01095578557962518</v>
+        <v>0.00731279169324781</v>
       </c>
       <c r="AJ4">
-        <v>45637.98701298661</v>
+        <v>68373.34098572365</v>
       </c>
       <c r="AK4">
-        <v>34228.49025973996</v>
+        <v>51280.00573929274</v>
       </c>
       <c r="AL4">
-        <v>48701.29870129827</v>
+        <v>10761.1736853433</v>
       </c>
       <c r="AM4">
-        <v>342.2849025973995</v>
+        <v>512.8000573929274</v>
       </c>
       <c r="AN4">
-        <v>0.003422849025973995</v>
+        <v>0.005128000573929275</v>
       </c>
       <c r="AO4">
         <v>374.9999999999999</v>
@@ -1229,31 +1229,31 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.01425232761761736</v>
+        <v>0.06020101928301617</v>
       </c>
       <c r="AR4">
-        <v>0.002056304187160236</v>
+        <v>0.01921599951448615</v>
       </c>
       <c r="AS4">
-        <v>0.005166355074580426</v>
+        <v>0.01289441991380806</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY4" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,13 +1273,13 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
         <v>69</v>
@@ -1291,64 +1291,64 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.0011224821324551</v>
+        <v>0.9941178915224304</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q5">
         <v>0.75</v>
       </c>
       <c r="R5">
-        <v>4.76528</v>
+        <v>1.34987</v>
       </c>
       <c r="S5">
-        <v>4.781387027789476</v>
+        <v>1.352554019293386</v>
       </c>
       <c r="T5">
-        <v>4.745867576179772</v>
+        <v>1.346605000058493</v>
       </c>
       <c r="U5">
-        <v>4.76528</v>
+        <v>1.34987</v>
       </c>
       <c r="V5">
-        <v>4.817559999999999</v>
+        <v>1.35924</v>
       </c>
       <c r="W5">
-        <v>4.781387027789476</v>
+        <v>1.352554019293386</v>
       </c>
       <c r="X5">
-        <v>4.7304325</v>
+        <v>1.33571375</v>
       </c>
       <c r="Y5">
-        <v>0.003380080035061186</v>
+        <v>0.001988353910662605</v>
       </c>
       <c r="Z5">
-        <v>0.4622147295925506</v>
+        <v>0.1895995968837887</v>
       </c>
       <c r="AA5">
-        <v>0.003380080035061186</v>
+        <v>0.001988353910662605</v>
       </c>
       <c r="AB5">
-        <v>0.3587125506456568</v>
+        <v>0.3808453287606064</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4412874493543432</v>
+        <v>0.4191546712393935</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1360,55 +1360,55 @@
         <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.00731279169324781</v>
+        <v>0.01048712098202048</v>
       </c>
       <c r="AJ5">
-        <v>68373.34098572365</v>
+        <v>47677.52759381905</v>
       </c>
       <c r="AK5">
-        <v>51280.00573929274</v>
+        <v>35758.14569536428</v>
       </c>
       <c r="AL5">
-        <v>10761.1736853433</v>
+        <v>26490.0662251656</v>
       </c>
       <c r="AM5">
-        <v>512.8000573929274</v>
+        <v>357.5814569536428</v>
       </c>
       <c r="AN5">
-        <v>0.005128000573929275</v>
+        <v>0.003575814569536428</v>
       </c>
       <c r="AO5">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.04694244433687772</v>
+        <v>0.01717258597711147</v>
       </c>
       <c r="AR5">
-        <v>0.01901016029710946</v>
+        <v>0.00789591650769254</v>
       </c>
       <c r="AS5">
-        <v>0.01153568751042616</v>
+        <v>0.005763103686149383</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY5" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1431,79 +1431,79 @@
         <v>65</v>
       </c>
       <c r="G6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" t="s">
         <v>68</v>
-      </c>
-      <c r="H6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
       </c>
       <c r="J6" s="2">
         <v>46241</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.2546320802678816</v>
       </c>
       <c r="L6">
-        <v>0.0873260828937016</v>
+        <v>1.802033117603085</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>0.8136580200669704</v>
       </c>
       <c r="R6">
-        <v>7.7936</v>
+        <v>157.7145</v>
       </c>
       <c r="S6">
-        <v>7.778483775693623</v>
+        <v>157.361545023825</v>
       </c>
       <c r="T6">
-        <v>7.71348829918916</v>
+        <v>159.7436557675881</v>
       </c>
       <c r="U6">
-        <v>7.7936</v>
+        <v>157.7145</v>
       </c>
       <c r="V6">
-        <v>7.8477</v>
+        <v>153.739</v>
       </c>
       <c r="W6">
-        <v>7.778483775693623</v>
+        <v>157.361545023825</v>
       </c>
       <c r="X6">
-        <v>7.856525</v>
+        <v>159.3165</v>
       </c>
       <c r="Y6">
-        <v>-0.001939568916338654</v>
+        <v>-0.002237936119855449</v>
       </c>
       <c r="Z6">
-        <v>0.2402260517501296</v>
+        <v>0.2203214582864822</v>
       </c>
       <c r="AA6">
-        <v>0.001939568916338654</v>
+        <v>0.002237936119855449</v>
       </c>
       <c r="AB6">
-        <v>0.4351053146154676</v>
+        <v>0.4708754561896867</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3648946853845325</v>
+        <v>0.3291245438103133</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,58 +1512,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>406.8290100334852</v>
       </c>
       <c r="AI6">
-        <v>0.00807393245740096</v>
+        <v>0.01015759489457209</v>
       </c>
       <c r="AJ6">
-        <v>61927.69169646392</v>
+        <v>49224.2509363299</v>
       </c>
       <c r="AK6">
-        <v>46445.76877234795</v>
+        <v>40051.7065561339</v>
       </c>
       <c r="AL6">
-        <v>5959.475566150168</v>
+        <v>253.9506929047989</v>
       </c>
       <c r="AM6">
-        <v>464.4576877234795</v>
+        <v>400.5170655613391</v>
       </c>
       <c r="AN6">
-        <v>0.004644576877234795</v>
+        <v>0.004005170655613391</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>406.8290100334852</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.004068290100334852</v>
       </c>
       <c r="AQ6">
-        <v>0.09605517607133826</v>
+        <v>4.456573953812772</v>
       </c>
       <c r="AR6">
-        <v>0.041779463153615</v>
+        <v>3.278754959089368</v>
       </c>
       <c r="AS6">
-        <v>0.05878122653161438</v>
+        <v>4.543003282566402</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY6" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1586,79 +1586,79 @@
         <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.00811134348940943</v>
+        <v>1.029249455050077</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>9.09496</v>
+        <v>0.812665</v>
       </c>
       <c r="S7">
-        <v>9.076217210498575</v>
+        <v>0.8103614225099802</v>
       </c>
       <c r="T7">
-        <v>9.040064246510893</v>
+        <v>0.803174226232662</v>
       </c>
       <c r="U7">
-        <v>9.09496</v>
+        <v>0.812665</v>
       </c>
       <c r="V7">
-        <v>9.099590000000001</v>
+        <v>0.8169299999999999</v>
       </c>
       <c r="W7">
-        <v>9.076217210498575</v>
+        <v>0.8103614225099802</v>
       </c>
       <c r="X7">
-        <v>9.1827925</v>
+        <v>0.8221449999999999</v>
       </c>
       <c r="Y7">
-        <v>-0.002060788557775472</v>
+        <v>-0.002834596654242213</v>
       </c>
       <c r="Z7">
-        <v>0.2133924174015957</v>
+        <v>0.2429934061202269</v>
       </c>
       <c r="AA7">
-        <v>0.002060788557775472</v>
+        <v>0.002834596654242213</v>
       </c>
       <c r="AB7">
-        <v>0.377093748263681</v>
+        <v>0.4155038885264938</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.422906251736319</v>
+        <v>0.3844961114735062</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1670,22 +1670,22 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.009657271719721664</v>
+        <v>0.01166532334971974</v>
       </c>
       <c r="AJ7">
-        <v>51774.45706316014</v>
+        <v>42862.07805907178</v>
       </c>
       <c r="AK7">
-        <v>51774.45706316014</v>
+        <v>42862.07805907178</v>
       </c>
       <c r="AL7">
-        <v>5692.653630489869</v>
+        <v>52742.61603375534</v>
       </c>
       <c r="AM7">
-        <v>517.7445706316014</v>
+        <v>428.6207805907177</v>
       </c>
       <c r="AN7">
-        <v>0.005177445706316014</v>
+        <v>0.004286207805907177</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -1694,31 +1694,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.1252864916586665</v>
+        <v>0.01507021586503488</v>
       </c>
       <c r="AR7">
-        <v>0.0362773644852826</v>
+        <v>0.004835825912016995</v>
       </c>
       <c r="AS7">
-        <v>0.03379848244961932</v>
+        <v>0.006676646050087449</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY7" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,82 +1738,82 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>69</v>
-      </c>
       <c r="J8" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.4295741562412449</v>
+        <v>0.0873260828937016</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>1.152205</v>
+        <v>7.7936</v>
       </c>
       <c r="S8">
-        <v>1.149487410616441</v>
+        <v>7.761537831520858</v>
       </c>
       <c r="T8">
-        <v>1.135722416291224</v>
+        <v>7.682928024890828</v>
       </c>
       <c r="U8">
-        <v>1.152205</v>
+        <v>7.7936</v>
       </c>
       <c r="V8">
-        <v>1.16311</v>
+        <v>7.8477</v>
       </c>
       <c r="W8">
-        <v>1.149487410616441</v>
+        <v>7.761537831520858</v>
       </c>
       <c r="X8">
-        <v>1.165205</v>
+        <v>7.856525</v>
       </c>
       <c r="Y8">
-        <v>-0.002358598846176616</v>
+        <v>-0.004113909936247891</v>
       </c>
       <c r="Z8">
-        <v>0.2090453371968403</v>
+        <v>0.5095298923979579</v>
       </c>
       <c r="AA8">
-        <v>0.002358598846176616</v>
+        <v>0.004113909936247891</v>
       </c>
       <c r="AB8">
-        <v>0.4177655650539432</v>
+        <v>0.4572511097789738</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3822344349460568</v>
+        <v>0.3427488902210262</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,58 +1822,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.01128271444751586</v>
+        <v>0.00807393245740096</v>
       </c>
       <c r="AJ8">
-        <v>44315.57692307689</v>
+        <v>61927.69169646392</v>
       </c>
       <c r="AK8">
-        <v>44315.57692307689</v>
+        <v>46445.76877234795</v>
       </c>
       <c r="AL8">
-        <v>38461.53846153843</v>
+        <v>5959.475566150168</v>
       </c>
       <c r="AM8">
-        <v>443.1557692307688</v>
+        <v>464.4576877234795</v>
       </c>
       <c r="AN8">
-        <v>0.004431557692307688</v>
+        <v>0.004644576877234795</v>
       </c>
       <c r="AO8">
-        <v>500.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP8">
-        <v>0.005000000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ8">
-        <v>0.01789409651521521</v>
+        <v>0.081311225268774</v>
       </c>
       <c r="AR8">
-        <v>0.006632066409174154</v>
+        <v>0.04820075708843472</v>
       </c>
       <c r="AS8">
-        <v>0.008555479815543068</v>
+        <v>0.06866306171436792</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY8" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,82 +1893,82 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
         <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.8642703280274651</v>
+        <v>0.00811134348940943</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>1.345145</v>
+        <v>9.09496</v>
       </c>
       <c r="S9">
-        <v>1.340067835602197</v>
+        <v>9.049624554261481</v>
       </c>
       <c r="T9">
-        <v>1.327792918652622</v>
+        <v>8.975947411224624</v>
       </c>
       <c r="U9">
-        <v>1.345145</v>
+        <v>9.09496</v>
       </c>
       <c r="V9">
-        <v>1.34979</v>
+        <v>9.099590000000001</v>
       </c>
       <c r="W9">
-        <v>1.340067835602197</v>
+        <v>9.049624554261481</v>
       </c>
       <c r="X9">
-        <v>1.35930125</v>
+        <v>9.1827925</v>
       </c>
       <c r="Y9">
-        <v>-0.003774436508929051</v>
+        <v>-0.004984677858783277</v>
       </c>
       <c r="Z9">
-        <v>0.3586517896903046</v>
+        <v>0.5161579795465195</v>
       </c>
       <c r="AA9">
-        <v>0.003774436508929051</v>
+        <v>0.004984677858783277</v>
       </c>
       <c r="AB9">
-        <v>0.399742323035582</v>
+        <v>0.3966226057237535</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4002576769644179</v>
+        <v>0.4033773942762465</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1980,22 +1980,22 @@
         <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.01052395838366866</v>
+        <v>0.009657271719721664</v>
       </c>
       <c r="AJ9">
-        <v>47510.64017660051</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AK9">
-        <v>47510.64017660051</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AL9">
-        <v>35320.0883002208</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM9">
-        <v>475.1064017660051</v>
+        <v>517.7445706316014</v>
       </c>
       <c r="AN9">
-        <v>0.004751064017660051</v>
+        <v>0.005177445706316014</v>
       </c>
       <c r="AO9">
         <v>500</v>
@@ -2004,31 +2004,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.02090013896296028</v>
+        <v>0.1060862464214886</v>
       </c>
       <c r="AR9">
-        <v>0.006350008227021008</v>
+        <v>0.04229233980205972</v>
       </c>
       <c r="AS9">
-        <v>0.007539236589116731</v>
+        <v>0.04077384803823854</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY9" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2051,79 +2051,79 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.496910670713708</v>
+        <v>0.6714706506544719</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" t="s">
+        <v>70</v>
+      </c>
+      <c r="P10" t="s">
         <v>72</v>
       </c>
-      <c r="P10" t="s">
-        <v>75</v>
-      </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>158.517</v>
+        <v>1.156395</v>
       </c>
       <c r="S10">
-        <v>157.5346106688172</v>
+        <v>1.150586951936813</v>
       </c>
       <c r="T10">
-        <v>158.6638511547774</v>
+        <v>1.127866310711936</v>
       </c>
       <c r="U10">
-        <v>158.517</v>
+        <v>1.156395</v>
       </c>
       <c r="V10">
-        <v>155.344</v>
+        <v>1.17149</v>
       </c>
       <c r="W10">
-        <v>157.5346106688172</v>
+        <v>1.150586951936813</v>
       </c>
       <c r="X10">
-        <v>160.159</v>
+        <v>1.169395</v>
       </c>
       <c r="Y10">
-        <v>-0.00619737524166377</v>
+        <v>-0.005022546848772953</v>
       </c>
       <c r="Z10">
-        <v>0.5982882650321723</v>
+        <v>0.4467729279374457</v>
       </c>
       <c r="AA10">
-        <v>0.00619737524166377</v>
+        <v>0.005022546848772953</v>
       </c>
       <c r="AB10">
-        <v>0.4686989254256231</v>
+        <v>0.4099618430961136</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3313010745743769</v>
+        <v>0.3900381569038864</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2132,58 +2132,58 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.0103585104436747</v>
+        <v>0.01124183345656113</v>
       </c>
       <c r="AJ10">
-        <v>48269.48842874597</v>
+        <v>44476.73076923073</v>
       </c>
       <c r="AK10">
-        <v>36202.11632155948</v>
+        <v>44476.73076923073</v>
       </c>
       <c r="AL10">
-        <v>228.3800243605385</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM10">
-        <v>362.0211632155948</v>
+        <v>444.7673076923073</v>
       </c>
       <c r="AN10">
-        <v>0.003620211632155948</v>
+        <v>0.004447673076923073</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ10">
-        <v>4.22318913851516</v>
+        <v>0.02038852653294506</v>
       </c>
       <c r="AR10">
-        <v>2.755984393716529</v>
+        <v>0.008628950583346404</v>
       </c>
       <c r="AS10">
-        <v>4.130636136869751</v>
+        <v>0.009303379659663994</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY10" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,82 +2203,82 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
-      </c>
       <c r="J11" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K11">
-        <v>0.2844424786311258</v>
+        <v>0.4841155937882756</v>
       </c>
       <c r="L11">
-        <v>2.674320367291286</v>
+        <v>2.918005842436935</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q11">
-        <v>0.8211106196577814</v>
+        <v>0.8710288984470689</v>
       </c>
       <c r="R11">
-        <v>6.74783</v>
+        <v>6.74282</v>
       </c>
       <c r="S11">
-        <v>6.675172577865641</v>
+        <v>6.699353106174017</v>
       </c>
       <c r="T11">
-        <v>6.59106509376118</v>
+        <v>6.667789986037593</v>
       </c>
       <c r="U11">
-        <v>6.74783</v>
+        <v>6.74282</v>
       </c>
       <c r="V11">
-        <v>6.714360000000001</v>
+        <v>6.70434</v>
       </c>
       <c r="W11">
-        <v>6.675172577865641</v>
+        <v>6.699353106174017</v>
       </c>
       <c r="X11">
-        <v>6.796268281422907</v>
+        <v>6.772395</v>
       </c>
       <c r="Y11">
-        <v>-0.01076752409802247</v>
+        <v>-0.006446396882310881</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>1.469717458190474</v>
       </c>
       <c r="AA11">
-        <v>0.01076752409802247</v>
+        <v>0.006446396882310881</v>
       </c>
       <c r="AB11">
-        <v>0.3721274749622436</v>
+        <v>0.3470010665119903</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4278725250377564</v>
+        <v>0.4529989334880097</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2287,58 +2287,58 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>410.5553098288907</v>
+        <v>435.5144492235344</v>
       </c>
       <c r="AI11">
-        <v>0.007178349398681649</v>
+        <v>0.004386147042335422</v>
       </c>
       <c r="AJ11">
-        <v>69653.89565626721</v>
+        <v>113995.2662721889</v>
       </c>
       <c r="AK11">
-        <v>57193.55342389602</v>
+        <v>99293.17120924497</v>
       </c>
       <c r="AL11">
-        <v>8475.843852600912</v>
+        <v>14725.76328735529</v>
       </c>
       <c r="AM11">
-        <v>571.9355342389601</v>
+        <v>992.9317120924497</v>
       </c>
       <c r="AN11">
-        <v>0.005719355342389602</v>
+        <v>0.009929317120924498</v>
       </c>
       <c r="AO11">
-        <v>410.5553098288908</v>
+        <v>435.5144492235345</v>
       </c>
       <c r="AP11">
-        <v>0.004105553098288908</v>
+        <v>0.004355144492235345</v>
       </c>
       <c r="AQ11">
-        <v>0.05421416703208381</v>
+        <v>0.06108616134286088</v>
       </c>
       <c r="AR11">
-        <v>0.01061616474712812</v>
+        <v>0.01436742143228299</v>
       </c>
       <c r="AS11">
-        <v>0.01138305530884299</v>
+        <v>0.01015551979235541</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03842609261256683</v>
+        <v>0.04616608228682823</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY11" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,6 +169,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -178,24 +181,21 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -205,13 +205,16 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>LOW</t>
+    <t>FLAT</t>
   </si>
   <si>
     <t>LONG</t>
@@ -220,55 +223,64 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=389.8,naive=100,drift4=137.4; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.01781,naive=0.003155,drift4=0.003404; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.0602,naive=0.01922,drift4=0.01289; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.01717,naive=0.007896,drift4=0.005763; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=4.457,naive=3.279,drift4=4.543; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01507,naive=0.004836,drift4=0.006677; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.08131,naive=0.0482,drift4=0.06866; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.1061,naive=0.04229,drift4=0.04077; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02039,naive=0.008629,drift4=0.009303; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.06109,naive=0.01437,drift4=0.01016; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01654,naive=0.004666,drift4=0.005684; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=333.1,naive=98.15,drift4=133.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01542,naive=0.002495,drift4=0.003359; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=0.04209,naive=0.01836,drift4=0.01163; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0162,naive=0.006776,drift4=0.007717; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09704,naive=0.03811,drift4=0.05365; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.1272,naive=0.03306,drift4=0.0321; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02028,naive=0.006187,drift4=0.005554; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=4.34,naive=2.569,drift4=3.839; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.04857,naive=0.01154,drift4=0.01025; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -817,7 +829,7 @@
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
         <v>46240</v>
@@ -826,64 +838,55 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.02541797099827621</v>
+        <v>1.00416763117204</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>4241.799999999999</v>
+        <v>0.812665</v>
       </c>
       <c r="S2">
-        <v>4319.101799672854</v>
+        <v>0.8128935875854355</v>
       </c>
       <c r="T2">
-        <v>4314.778111231457</v>
+        <v>0.8089350013142604</v>
       </c>
       <c r="U2">
-        <v>4241.799999999999</v>
+        <v>0.812665</v>
       </c>
       <c r="V2">
-        <v>4362.519999999999</v>
-      </c>
-      <c r="W2">
-        <v>4319.101799672854</v>
-      </c>
-      <c r="X2">
-        <v>4103.2725</v>
+        <v>0.8169299999999999</v>
       </c>
       <c r="Y2">
-        <v>0.01822381999925856</v>
-      </c>
-      <c r="Z2">
-        <v>0.5580249385346262</v>
+        <v>0.0002812814449195372</v>
       </c>
       <c r="AA2">
-        <v>0.01822381999925856</v>
+        <v>0.0002812814449195372</v>
       </c>
       <c r="AB2">
-        <v>0.4037167532392456</v>
+        <v>0.3981754769069263</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3962832467607544</v>
+        <v>0.4018245230930738</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -892,55 +895,52 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>500</v>
-      </c>
-      <c r="AI2">
-        <v>0.03265771606393492</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>3.6093916370396</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>153.1031744599457</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.001531031744599457</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>389.8302878991883</v>
+        <v>0.01654367456609179</v>
       </c>
       <c r="AR2">
-        <v>100.0087866504446</v>
+        <v>0.00466619602509049</v>
       </c>
       <c r="AS2">
-        <v>137.4096116069606</v>
+        <v>0.005683536746422358</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
         <v>46272</v>
@@ -963,82 +963,82 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.7295228455748012</v>
+        <v>0.0244440950116974</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="O3" t="s">
         <v>71</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>0.70652</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="S3">
-        <v>0.7117677207445479</v>
+        <v>4439.503681350399</v>
       </c>
       <c r="T3">
-        <v>0.7072883963104537</v>
+        <v>4609.288414951195</v>
       </c>
       <c r="U3">
-        <v>0.70652</v>
+        <v>4241.799999999999</v>
       </c>
       <c r="V3">
-        <v>0.7180400000000001</v>
+        <v>4362.519999999999</v>
       </c>
       <c r="W3">
-        <v>0.7117677207445479</v>
+        <v>4439.503681350399</v>
       </c>
       <c r="X3">
-        <v>0.69882</v>
+        <v>4103.2725</v>
       </c>
       <c r="Y3">
-        <v>0.007427561490895973</v>
+        <v>0.04660844013164225</v>
       </c>
       <c r="Z3">
-        <v>0.6815221746165945</v>
+        <v>1.427180028156152</v>
       </c>
       <c r="AA3">
-        <v>0.007427561490895973</v>
+        <v>0.04660844013164225</v>
       </c>
       <c r="AB3">
-        <v>0.3690871957371829</v>
+        <v>0.409808043587753</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.430912804262817</v>
+        <v>0.3901919564122471</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1047,55 +1047,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI3">
-        <v>0.01089848836550992</v>
+        <v>0.03265771606393492</v>
       </c>
       <c r="AJ3">
-        <v>45877.92207792167</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AK3">
-        <v>34408.44155844125</v>
+        <v>15310.31744599457</v>
       </c>
       <c r="AL3">
-        <v>48701.29870129826</v>
+        <v>3.6093916370396</v>
       </c>
       <c r="AM3">
-        <v>344.0844155844125</v>
+        <v>153.1031744599457</v>
       </c>
       <c r="AN3">
-        <v>0.003440844155844125</v>
+        <v>0.001531031744599457</v>
       </c>
       <c r="AO3">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ3">
-        <v>0.01780543112232461</v>
+        <v>333.0580242987464</v>
       </c>
       <c r="AR3">
-        <v>0.003154695189921269</v>
+        <v>98.1533697032438</v>
       </c>
       <c r="AS3">
-        <v>0.00340448045774924</v>
+        <v>133.6385426725425</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
         <v>46272</v>
@@ -1118,13 +1118,13 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
@@ -1136,64 +1136,64 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.0011224821324551</v>
+        <v>0.7405895944257652</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4.76528</v>
+        <v>0.70652</v>
       </c>
       <c r="S4">
-        <v>4.781438601726977</v>
+        <v>0.7140368405045054</v>
       </c>
       <c r="T4">
-        <v>4.745331380627396</v>
+        <v>0.7136079475168189</v>
       </c>
       <c r="U4">
-        <v>4.76528</v>
+        <v>0.70652</v>
       </c>
       <c r="V4">
-        <v>4.817559999999999</v>
+        <v>0.7180400000000001</v>
       </c>
       <c r="W4">
-        <v>4.781438601726977</v>
+        <v>0.7140368405045054</v>
       </c>
       <c r="X4">
-        <v>4.7304325</v>
+        <v>0.69882</v>
       </c>
       <c r="Y4">
-        <v>0.003390902890696344</v>
+        <v>0.01063924659529158</v>
       </c>
       <c r="Z4">
-        <v>0.4636947191901143</v>
+        <v>0.976213052533161</v>
       </c>
       <c r="AA4">
-        <v>0.003390902890696344</v>
+        <v>0.01063924659529158</v>
       </c>
       <c r="AB4">
-        <v>0.3553355788323144</v>
+        <v>0.3833798227666965</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4446644211676857</v>
+        <v>0.4166201772333035</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1205,22 +1205,22 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.00731279169324781</v>
+        <v>0.01089848836550992</v>
       </c>
       <c r="AJ4">
-        <v>68373.34098572365</v>
+        <v>45877.92207792167</v>
       </c>
       <c r="AK4">
-        <v>51280.00573929274</v>
+        <v>34408.44155844125</v>
       </c>
       <c r="AL4">
-        <v>10761.1736853433</v>
+        <v>48701.29870129826</v>
       </c>
       <c r="AM4">
-        <v>512.8000573929274</v>
+        <v>344.0844155844125</v>
       </c>
       <c r="AN4">
-        <v>0.005128000573929275</v>
+        <v>0.003440844155844125</v>
       </c>
       <c r="AO4">
         <v>374.9999999999999</v>
@@ -1229,28 +1229,28 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.06020101928301617</v>
+        <v>0.01541773699605002</v>
       </c>
       <c r="AR4">
-        <v>0.01921599951448615</v>
+        <v>0.002494941078237637</v>
       </c>
       <c r="AS4">
-        <v>0.01289441991380806</v>
+        <v>0.00335860998293231</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
         <v>46272</v>
@@ -1273,13 +1273,13 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
         <v>69</v>
@@ -1291,64 +1291,64 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.9941178915224304</v>
+        <v>0.0011224821324551</v>
       </c>
       <c r="M5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q5">
         <v>0.75</v>
       </c>
       <c r="R5">
-        <v>1.34987</v>
+        <v>4.76528</v>
       </c>
       <c r="S5">
-        <v>1.352554019293386</v>
+        <v>4.78081355874455</v>
       </c>
       <c r="T5">
-        <v>1.346605000058493</v>
+        <v>4.745727485636108</v>
       </c>
       <c r="U5">
-        <v>1.34987</v>
+        <v>4.76528</v>
       </c>
       <c r="V5">
-        <v>1.35924</v>
+        <v>4.817559999999999</v>
       </c>
       <c r="W5">
-        <v>1.352554019293386</v>
+        <v>4.78081355874455</v>
       </c>
       <c r="X5">
-        <v>1.33571375</v>
+        <v>4.7304325</v>
       </c>
       <c r="Y5">
-        <v>0.001988353910662605</v>
+        <v>0.003259736834887068</v>
       </c>
       <c r="Z5">
-        <v>0.1895995968837887</v>
+        <v>0.4457581962709142</v>
       </c>
       <c r="AA5">
-        <v>0.001988353910662605</v>
+        <v>0.003259736834887068</v>
       </c>
       <c r="AB5">
-        <v>0.3808453287606064</v>
+        <v>0.3659963943662962</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4191546712393935</v>
+        <v>0.4340036056337038</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1360,52 +1360,52 @@
         <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01048712098202048</v>
+        <v>0.00731279169324781</v>
       </c>
       <c r="AJ5">
-        <v>47677.52759381905</v>
+        <v>68373.34098572365</v>
       </c>
       <c r="AK5">
-        <v>35758.14569536428</v>
+        <v>51280.00573929274</v>
       </c>
       <c r="AL5">
-        <v>26490.0662251656</v>
+        <v>10761.1736853433</v>
       </c>
       <c r="AM5">
-        <v>357.5814569536428</v>
+        <v>512.8000573929274</v>
       </c>
       <c r="AN5">
-        <v>0.003575814569536428</v>
+        <v>0.005128000573929275</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.01717258597711147</v>
+        <v>0.04209278333916979</v>
       </c>
       <c r="AR5">
-        <v>0.00789591650769254</v>
+        <v>0.01835936028567264</v>
       </c>
       <c r="AS5">
-        <v>0.005763103686149383</v>
+        <v>0.0116255810036584</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
         <v>46272</v>
@@ -1431,79 +1431,79 @@
         <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2">
         <v>46241</v>
       </c>
       <c r="K6">
-        <v>0.2546320802678816</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1.802033117603085</v>
+        <v>0.6887771814529435</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q6">
-        <v>0.8136580200669704</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>157.7145</v>
+        <v>1.156395</v>
       </c>
       <c r="S6">
-        <v>157.361545023825</v>
+        <v>1.155141391951658</v>
       </c>
       <c r="T6">
-        <v>159.7436557675881</v>
+        <v>1.139298164454577</v>
       </c>
       <c r="U6">
-        <v>157.7145</v>
+        <v>1.156395</v>
       </c>
       <c r="V6">
-        <v>153.739</v>
+        <v>1.17149</v>
       </c>
       <c r="W6">
-        <v>157.361545023825</v>
+        <v>1.1546604075</v>
       </c>
       <c r="X6">
-        <v>159.3165</v>
+        <v>1.169395</v>
       </c>
       <c r="Y6">
-        <v>-0.002237936119855449</v>
+        <v>-0.001084065607636244</v>
       </c>
       <c r="Z6">
-        <v>0.2203214582864822</v>
+        <v>0.1334301923076922</v>
       </c>
       <c r="AA6">
-        <v>0.002237936119855449</v>
+        <v>0.001084065607636244</v>
       </c>
       <c r="AB6">
-        <v>0.4708754561896867</v>
+        <v>0.4140679716611463</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3291245438103133</v>
+        <v>0.3859320283388538</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,55 +1512,55 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>406.8290100334852</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.01015759489457209</v>
+        <v>0.01124183345656113</v>
       </c>
       <c r="AJ6">
-        <v>49224.2509363299</v>
+        <v>44476.73076923073</v>
       </c>
       <c r="AK6">
-        <v>40051.7065561339</v>
+        <v>44476.73076923073</v>
       </c>
       <c r="AL6">
-        <v>253.9506929047989</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM6">
-        <v>400.5170655613391</v>
+        <v>444.7673076923073</v>
       </c>
       <c r="AN6">
-        <v>0.004005170655613391</v>
+        <v>0.004447673076923073</v>
       </c>
       <c r="AO6">
-        <v>406.8290100334852</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.004068290100334852</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ6">
-        <v>4.456573953812772</v>
+        <v>0.01620175168840787</v>
       </c>
       <c r="AR6">
-        <v>3.278754959089368</v>
+        <v>0.006775866717876774</v>
       </c>
       <c r="AS6">
-        <v>4.543003282566402</v>
+        <v>0.007716949830078606</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
         <v>46272</v>
@@ -1583,82 +1583,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1.029249455050077</v>
+        <v>0.0873260828937016</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>0.812665</v>
+        <v>7.7936</v>
       </c>
       <c r="S7">
-        <v>0.8103614225099802</v>
+        <v>7.779454815065272</v>
       </c>
       <c r="T7">
-        <v>0.803174226232662</v>
+        <v>7.713782011933707</v>
       </c>
       <c r="U7">
-        <v>0.812665</v>
+        <v>7.7936</v>
       </c>
       <c r="V7">
-        <v>0.8169299999999999</v>
+        <v>7.8477</v>
       </c>
       <c r="W7">
-        <v>0.8103614225099802</v>
+        <v>7.779454815065272</v>
       </c>
       <c r="X7">
-        <v>0.8221449999999999</v>
+        <v>7.856525</v>
       </c>
       <c r="Y7">
-        <v>-0.002834596654242213</v>
+        <v>-0.00181497445785363</v>
       </c>
       <c r="Z7">
-        <v>0.2429934061202269</v>
+        <v>0.2247943573258327</v>
       </c>
       <c r="AA7">
-        <v>0.002834596654242213</v>
+        <v>0.00181497445785363</v>
       </c>
       <c r="AB7">
-        <v>0.4155038885264938</v>
+        <v>0.4288085996804423</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3844961114735062</v>
+        <v>0.3711914003195577</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,55 +1667,55 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.01166532334971974</v>
+        <v>0.00807393245740096</v>
       </c>
       <c r="AJ7">
-        <v>42862.07805907178</v>
+        <v>61927.69169646392</v>
       </c>
       <c r="AK7">
-        <v>42862.07805907178</v>
+        <v>46445.76877234795</v>
       </c>
       <c r="AL7">
-        <v>52742.61603375534</v>
+        <v>5959.475566150168</v>
       </c>
       <c r="AM7">
-        <v>428.6207805907177</v>
+        <v>464.4576877234795</v>
       </c>
       <c r="AN7">
-        <v>0.004286207805907177</v>
+        <v>0.004644576877234795</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ7">
-        <v>0.01507021586503488</v>
+        <v>0.09704091895959474</v>
       </c>
       <c r="AR7">
-        <v>0.004835825912016995</v>
+        <v>0.03810707792263828</v>
       </c>
       <c r="AS7">
-        <v>0.006676646050087449</v>
+        <v>0.05365286371443611</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
         <v>46272</v>
@@ -1741,13 +1741,13 @@
         <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
         <v>46241</v>
@@ -1756,64 +1756,64 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.0873260828937016</v>
+        <v>0.00811134348940943</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>7.7936</v>
+        <v>9.09496</v>
       </c>
       <c r="S8">
-        <v>7.761537831520858</v>
+        <v>9.076446546464496</v>
       </c>
       <c r="T8">
-        <v>7.682928024890828</v>
+        <v>9.040431896731027</v>
       </c>
       <c r="U8">
-        <v>7.7936</v>
+        <v>9.09496</v>
       </c>
       <c r="V8">
-        <v>7.8477</v>
+        <v>9.099590000000001</v>
       </c>
       <c r="W8">
-        <v>7.761537831520858</v>
+        <v>9.076446546464496</v>
       </c>
       <c r="X8">
-        <v>7.856525</v>
+        <v>9.1827925</v>
       </c>
       <c r="Y8">
-        <v>-0.004113909936247891</v>
+        <v>-0.002035572837649061</v>
       </c>
       <c r="Z8">
-        <v>0.5095298923979579</v>
+        <v>0.2107813569635927</v>
       </c>
       <c r="AA8">
-        <v>0.004113909936247891</v>
+        <v>0.002035572837649061</v>
       </c>
       <c r="AB8">
-        <v>0.4572511097789738</v>
+        <v>0.3755606131334034</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3427488902210262</v>
+        <v>0.4244393868665965</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,55 +1822,55 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.00807393245740096</v>
+        <v>0.009657271719721664</v>
       </c>
       <c r="AJ8">
-        <v>61927.69169646392</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AK8">
-        <v>46445.76877234795</v>
+        <v>51774.45706316014</v>
       </c>
       <c r="AL8">
-        <v>5959.475566150168</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM8">
-        <v>464.4576877234795</v>
+        <v>517.7445706316014</v>
       </c>
       <c r="AN8">
-        <v>0.004644576877234795</v>
+        <v>0.005177445706316014</v>
       </c>
       <c r="AO8">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ8">
-        <v>0.081311225268774</v>
+        <v>0.1272202985646421</v>
       </c>
       <c r="AR8">
-        <v>0.04820075708843472</v>
+        <v>0.03306487965381423</v>
       </c>
       <c r="AS8">
-        <v>0.06866306171436792</v>
+        <v>0.03209632818862936</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
         <v>46272</v>
@@ -1893,13 +1893,13 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
         <v>69</v>
@@ -1911,64 +1911,64 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.00811134348940943</v>
+        <v>0.999579607254382</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>9.09496</v>
+        <v>1.34987</v>
       </c>
       <c r="S9">
-        <v>9.049624554261481</v>
+        <v>1.346729620505612</v>
       </c>
       <c r="T9">
-        <v>8.975947411224624</v>
+        <v>1.330990297676614</v>
       </c>
       <c r="U9">
-        <v>9.09496</v>
+        <v>1.34987</v>
       </c>
       <c r="V9">
-        <v>9.099590000000001</v>
+        <v>1.35924</v>
       </c>
       <c r="W9">
-        <v>9.049624554261481</v>
+        <v>1.346729620505612</v>
       </c>
       <c r="X9">
-        <v>9.1827925</v>
+        <v>1.36402625</v>
       </c>
       <c r="Y9">
-        <v>-0.004984677858783277</v>
+        <v>-0.002326431059574668</v>
       </c>
       <c r="Z9">
-        <v>0.5161579795465195</v>
+        <v>0.2218369620759778</v>
       </c>
       <c r="AA9">
-        <v>0.004984677858783277</v>
+        <v>0.002326431059574668</v>
       </c>
       <c r="AB9">
-        <v>0.3966226057237535</v>
+        <v>0.3765129760529499</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4033773942762465</v>
+        <v>0.4234870239470501</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1980,22 +1980,22 @@
         <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.009657271719721664</v>
+        <v>0.01048712098202048</v>
       </c>
       <c r="AJ9">
-        <v>51774.45706316014</v>
+        <v>47677.52759381905</v>
       </c>
       <c r="AK9">
-        <v>51774.45706316014</v>
+        <v>47677.52759381905</v>
       </c>
       <c r="AL9">
-        <v>5692.653630489869</v>
+        <v>35320.0883002208</v>
       </c>
       <c r="AM9">
-        <v>517.7445706316014</v>
+        <v>476.7752759381905</v>
       </c>
       <c r="AN9">
-        <v>0.005177445706316014</v>
+        <v>0.004767752759381905</v>
       </c>
       <c r="AO9">
         <v>500</v>
@@ -2004,28 +2004,28 @@
         <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.1060862464214886</v>
+        <v>0.0202753040970711</v>
       </c>
       <c r="AR9">
-        <v>0.04229233980205972</v>
+        <v>0.006187272743404255</v>
       </c>
       <c r="AS9">
-        <v>0.04077384803823854</v>
+        <v>0.005553919851368239</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
         <v>46272</v>
@@ -2051,13 +2051,13 @@
         <v>65</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
         <v>46241</v>
@@ -2066,64 +2066,64 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.6714706506544719</v>
+        <v>1.550379514226834</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>1.156395</v>
+        <v>157.7145</v>
       </c>
       <c r="S10">
-        <v>1.150586951936813</v>
+        <v>156.7270412482461</v>
       </c>
       <c r="T10">
-        <v>1.127866310711936</v>
+        <v>158.4925952069294</v>
       </c>
       <c r="U10">
-        <v>1.156395</v>
+        <v>157.7145</v>
       </c>
       <c r="V10">
-        <v>1.17149</v>
+        <v>153.739</v>
       </c>
       <c r="W10">
-        <v>1.150586951936813</v>
+        <v>156.7270412482461</v>
       </c>
       <c r="X10">
-        <v>1.169395</v>
+        <v>159.3165</v>
       </c>
       <c r="Y10">
-        <v>-0.005022546848772953</v>
+        <v>-0.006261052419110791</v>
       </c>
       <c r="Z10">
-        <v>0.4467729279374457</v>
+        <v>0.6163912308076498</v>
       </c>
       <c r="AA10">
-        <v>0.005022546848772953</v>
+        <v>0.006261052419110791</v>
       </c>
       <c r="AB10">
-        <v>0.4099618430961136</v>
+        <v>0.4613226732157272</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3900381569038864</v>
+        <v>0.3386773267842728</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2132,55 +2132,55 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.01124183345656113</v>
+        <v>0.01015759489457209</v>
       </c>
       <c r="AJ10">
-        <v>44476.73076923073</v>
+        <v>49224.2509363299</v>
       </c>
       <c r="AK10">
-        <v>44476.73076923073</v>
+        <v>36918.18820224743</v>
       </c>
       <c r="AL10">
-        <v>38461.53846153842</v>
+        <v>234.0823970037468</v>
       </c>
       <c r="AM10">
-        <v>444.7673076923073</v>
+        <v>369.1818820224743</v>
       </c>
       <c r="AN10">
-        <v>0.004447673076923073</v>
+        <v>0.003691818820224743</v>
       </c>
       <c r="AO10">
-        <v>499.9999999999999</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP10">
-        <v>0.004999999999999999</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ10">
-        <v>0.02038852653294506</v>
+        <v>4.339886793695866</v>
       </c>
       <c r="AR10">
-        <v>0.008628950583346404</v>
+        <v>2.568890519603397</v>
       </c>
       <c r="AS10">
-        <v>0.009303379659663994</v>
+        <v>3.83864144844791</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
         <v>46272</v>
@@ -2203,25 +2203,25 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J11" s="2">
         <v>46241</v>
       </c>
       <c r="K11">
-        <v>0.4841155937882756</v>
+        <v>0.4274996118397774</v>
       </c>
       <c r="L11">
-        <v>2.918005842436935</v>
+        <v>2.849099356564458</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -2230,22 +2230,22 @@
         <v>17</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.8710288984470689</v>
+        <v>0.8568749029599444</v>
       </c>
       <c r="R11">
         <v>6.74282</v>
       </c>
       <c r="S11">
-        <v>6.699353106174017</v>
+        <v>6.664314415730515</v>
       </c>
       <c r="T11">
-        <v>6.667789986037593</v>
+        <v>6.573510562917879</v>
       </c>
       <c r="U11">
         <v>6.74282</v>
@@ -2254,31 +2254,31 @@
         <v>6.70434</v>
       </c>
       <c r="W11">
-        <v>6.699353106174017</v>
+        <v>6.664314415730515</v>
       </c>
       <c r="X11">
-        <v>6.772395</v>
+        <v>6.795157056179657</v>
       </c>
       <c r="Y11">
-        <v>-0.006446396882310881</v>
+        <v>-0.01164284146239779</v>
       </c>
       <c r="Z11">
-        <v>1.469717458190474</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.006446396882310881</v>
+        <v>0.01164284146239779</v>
       </c>
       <c r="AB11">
-        <v>0.3470010665119903</v>
+        <v>0.3647618252727841</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4529989334880097</v>
+        <v>0.435238174727216</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2287,55 +2287,55 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>435.5144492235344</v>
+        <v>428.4374514799722</v>
       </c>
       <c r="AI11">
-        <v>0.004386147042335422</v>
+        <v>0.007761894308265193</v>
       </c>
       <c r="AJ11">
-        <v>113995.2662721889</v>
+        <v>64417.26467050432</v>
       </c>
       <c r="AK11">
-        <v>99293.17120924497</v>
+        <v>55197.53741348345</v>
       </c>
       <c r="AL11">
-        <v>14725.76328735529</v>
+        <v>8186.120556901037</v>
       </c>
       <c r="AM11">
-        <v>992.9317120924497</v>
+        <v>551.9753741348345</v>
       </c>
       <c r="AN11">
-        <v>0.009929317120924498</v>
+        <v>0.005519753741348345</v>
       </c>
       <c r="AO11">
-        <v>435.5144492235345</v>
+        <v>428.4374514799723</v>
       </c>
       <c r="AP11">
-        <v>0.004355144492235345</v>
+        <v>0.004284374514799723</v>
       </c>
       <c r="AQ11">
-        <v>0.06108616134286088</v>
+        <v>0.04856952994888593</v>
       </c>
       <c r="AR11">
-        <v>0.01436742143228299</v>
+        <v>0.01154045540517659</v>
       </c>
       <c r="AS11">
-        <v>0.01015551979235541</v>
+        <v>0.01025487929226829</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04616608228682823</v>
+        <v>0.03834889745580173</v>
       </c>
       <c r="AV11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
         <v>46272</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -169,6 +169,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
@@ -178,42 +181,39 @@
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -229,49 +229,49 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
+    <t>CONFIRM</t>
+  </si>
+  <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>CONFIRM</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01654,naive=0.004666,drift4=0.005684; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=333.1,naive=98.15,drift4=133.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01542,naive=0.002495,drift4=0.003359; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=0.04209,naive=0.01836,drift4=0.01163; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0162,naive=0.006776,drift4=0.007717; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.09704,naive=0.03811,drift4=0.05365; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.1272,naive=0.03306,drift4=0.0321; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02028,naive=0.006187,drift4=0.005554; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=4.34,naive=2.569,drift4=3.839; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.04857,naive=0.01154,drift4=0.01025; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.28,naive=0.09,drift4=0.63); metric_best=drift4; scores=model=0.1579,naive=0.03871,drift4=0.001277</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02475,naive=0.00695,drift4=0.01504; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1198,naive=408.5,drift4=461.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.04806,naive=0.00649,drift4=0.00598; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.575,naive=5.407,drift4=7.743; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.11,drift4=0.55); metric_best=drift4; scores=model=0.009879,naive=0.01959,drift4=0.001708</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.17,drift4=0.52); metric_best=drift4; scores=model=0.1046,naive=0.03117,drift4=0.008303</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.55,naive=0.20,drift4=0.25); metric_best=model; scores=model=0.06233,naive=0.1095,drift4=0.1692; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.36); metric_best=drift4; scores=model=0.07223,naive=0.1109,drift4=0.06236</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02544,naive=0.0182,drift4=0.01588; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1.00416763117204</v>
+        <v>0.002126301230752134</v>
       </c>
       <c r="M2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0.812665</v>
+        <v>4.75742</v>
       </c>
       <c r="S2">
-        <v>0.8128935875854355</v>
+        <v>4.760940362508544</v>
       </c>
       <c r="T2">
-        <v>0.8089350013142604</v>
+        <v>4.710582426611793</v>
       </c>
       <c r="U2">
-        <v>0.812665</v>
+        <v>4.75742</v>
       </c>
       <c r="V2">
-        <v>0.8169299999999999</v>
+        <v>4.783729999999999</v>
       </c>
       <c r="Y2">
-        <v>0.0002812814449195372</v>
+        <v>0.0007399730333971017</v>
       </c>
       <c r="AA2">
-        <v>0.0002812814449195372</v>
+        <v>0.0007399730333971017</v>
       </c>
       <c r="AB2">
-        <v>0.3981754769069263</v>
+        <v>0.2788836582686398</v>
       </c>
       <c r="AC2">
-        <v>0.2</v>
+        <v>0.09083902058072661</v>
       </c>
       <c r="AD2">
-        <v>0.4018245230930738</v>
+        <v>0.6302773211506336</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01654367456609179</v>
+        <v>0.04698701001632302</v>
       </c>
       <c r="AR2">
-        <v>0.00466619602509049</v>
+        <v>0.01476393936234121</v>
       </c>
       <c r="AS2">
-        <v>0.005683536746422358</v>
+        <v>0.01692915163923248</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,76 +966,67 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.0244440950116974</v>
+        <v>0.9743535519187986</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>4241.799999999999</v>
+        <v>0.8105249999999999</v>
       </c>
       <c r="S3">
-        <v>4439.503681350399</v>
+        <v>0.8110577866881248</v>
       </c>
       <c r="T3">
-        <v>4609.288414951195</v>
+        <v>0.8101466115682419</v>
       </c>
       <c r="U3">
-        <v>4241.799999999999</v>
+        <v>0.8105249999999999</v>
       </c>
       <c r="V3">
-        <v>4362.519999999999</v>
-      </c>
-      <c r="W3">
-        <v>4439.503681350399</v>
-      </c>
-      <c r="X3">
-        <v>4103.2725</v>
+        <v>0.8125049999999998</v>
       </c>
       <c r="Y3">
-        <v>0.04660844013164225</v>
-      </c>
-      <c r="Z3">
-        <v>1.427180028156152</v>
+        <v>0.0006573352927113195</v>
       </c>
       <c r="AA3">
-        <v>0.04660844013164225</v>
+        <v>0.0006573352927113195</v>
       </c>
       <c r="AB3">
-        <v>0.409808043587753</v>
+        <v>0.4457337467057311</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3901919564122471</v>
+        <v>0.3542662532942689</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1047,58 +1038,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>500</v>
-      </c>
-      <c r="AI3">
-        <v>0.03265771606393492</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>15310.31744599457</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>3.6093916370396</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>153.1031744599457</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.001531031744599457</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>333.0580242987464</v>
+        <v>0.01808078097285104</v>
       </c>
       <c r="AR3">
-        <v>98.1533697032438</v>
+        <v>0.003638322517375865</v>
       </c>
       <c r="AS3">
-        <v>133.6385426725425</v>
+        <v>0.004604298557712782</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1130,67 +1118,67 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.7405895944257652</v>
+        <v>0.1815823354572913</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>0.70652</v>
+        <v>4378.51</v>
       </c>
       <c r="S4">
-        <v>0.7140368405045054</v>
+        <v>4688.465304862797</v>
       </c>
       <c r="T4">
-        <v>0.7136079475168189</v>
+        <v>4763.230312129874</v>
       </c>
       <c r="U4">
-        <v>0.70652</v>
+        <v>4378.51</v>
       </c>
       <c r="V4">
-        <v>0.7180400000000001</v>
+        <v>4768.700000000001</v>
       </c>
       <c r="W4">
-        <v>0.7140368405045054</v>
+        <v>4688.465304862797</v>
       </c>
       <c r="X4">
-        <v>0.69882</v>
+        <v>4171.873130091469</v>
       </c>
       <c r="Y4">
-        <v>0.01063924659529158</v>
+        <v>0.07079013291343328</v>
       </c>
       <c r="Z4">
-        <v>0.976213052533161</v>
+        <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.01063924659529158</v>
+        <v>0.07079013291343328</v>
       </c>
       <c r="AB4">
-        <v>0.3833798227666965</v>
+        <v>0.4016125214752247</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4166201772333035</v>
+        <v>0.3983874785247753</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1205,43 +1193,43 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.01089848836550992</v>
+        <v>0.04719342194228885</v>
       </c>
       <c r="AJ4">
-        <v>45877.92207792167</v>
+        <v>10594.6968755822</v>
       </c>
       <c r="AK4">
-        <v>34408.44155844125</v>
+        <v>7946.022656686649</v>
       </c>
       <c r="AL4">
-        <v>48701.29870129826</v>
+        <v>1.814777779812459</v>
       </c>
       <c r="AM4">
-        <v>344.0844155844125</v>
+        <v>79.46022656686648</v>
       </c>
       <c r="AN4">
-        <v>0.003440844155844125</v>
+        <v>0.0007946022656686648</v>
       </c>
       <c r="AO4">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.01541773699605002</v>
+        <v>376.7320788786117</v>
       </c>
       <c r="AR4">
-        <v>0.002494941078237637</v>
+        <v>146.1915630997557</v>
       </c>
       <c r="AS4">
-        <v>0.00335860998293231</v>
+        <v>187.8379939531156</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1253,7 +1241,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,7 +1261,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1285,67 +1273,67 @@
         <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.0011224821324551</v>
+        <v>0.761784839710452</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q5">
         <v>0.75</v>
       </c>
       <c r="R5">
-        <v>4.76528</v>
+        <v>0.70547</v>
       </c>
       <c r="S5">
-        <v>4.78081355874455</v>
+        <v>0.709488337535471</v>
       </c>
       <c r="T5">
-        <v>4.745727485636108</v>
+        <v>0.7056475937264967</v>
       </c>
       <c r="U5">
-        <v>4.76528</v>
+        <v>0.70547</v>
       </c>
       <c r="V5">
-        <v>4.817559999999999</v>
+        <v>0.714245</v>
       </c>
       <c r="W5">
-        <v>4.78081355874455</v>
+        <v>0.709488337535471</v>
       </c>
       <c r="X5">
-        <v>4.7304325</v>
+        <v>0.69777</v>
       </c>
       <c r="Y5">
-        <v>0.003259736834887068</v>
+        <v>0.005695972239033529</v>
       </c>
       <c r="Z5">
-        <v>0.4457581962709142</v>
+        <v>0.5218620175936297</v>
       </c>
       <c r="AA5">
-        <v>0.003259736834887068</v>
+        <v>0.005695972239033529</v>
       </c>
       <c r="AB5">
-        <v>0.3659963943662962</v>
+        <v>0.3491358171335802</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4340036056337038</v>
+        <v>0.4508641828664198</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1360,22 +1348,22 @@
         <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.00731279169324781</v>
+        <v>0.01091470934270779</v>
       </c>
       <c r="AJ5">
-        <v>68373.34098572365</v>
+        <v>45809.74025973985</v>
       </c>
       <c r="AK5">
-        <v>51280.00573929274</v>
+        <v>34357.30519480489</v>
       </c>
       <c r="AL5">
-        <v>10761.1736853433</v>
+        <v>48701.29870129826</v>
       </c>
       <c r="AM5">
-        <v>512.8000573929274</v>
+        <v>343.5730519480489</v>
       </c>
       <c r="AN5">
-        <v>0.005128000573929275</v>
+        <v>0.003435730519480489</v>
       </c>
       <c r="AO5">
         <v>374.9999999999999</v>
@@ -1384,19 +1372,19 @@
         <v>0.003749999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.04209278333916979</v>
+        <v>0.01602548836259331</v>
       </c>
       <c r="AR5">
-        <v>0.01835936028567264</v>
+        <v>0.001824716926400594</v>
       </c>
       <c r="AS5">
-        <v>0.0116255810036584</v>
+        <v>0.005025871961216736</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1408,7 +1396,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,7 +1416,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
         <v>68</v>
@@ -1437,22 +1425,22 @@
         <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.6887771814529435</v>
+        <v>1.266603651507621</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1461,46 +1449,46 @@
         <v>74</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>1.156395</v>
+        <v>159.229</v>
       </c>
       <c r="S6">
-        <v>1.155141391951658</v>
+        <v>158.9457526532241</v>
       </c>
       <c r="T6">
-        <v>1.139298164454577</v>
+        <v>160.4909687247705</v>
       </c>
       <c r="U6">
-        <v>1.156395</v>
+        <v>159.229</v>
       </c>
       <c r="V6">
-        <v>1.17149</v>
+        <v>156.014</v>
       </c>
       <c r="W6">
-        <v>1.1546604075</v>
+        <v>158.9457526532241</v>
       </c>
       <c r="X6">
-        <v>1.169395</v>
+        <v>160.661875</v>
       </c>
       <c r="Y6">
-        <v>-0.001084065607636244</v>
+        <v>-0.001778867836737531</v>
       </c>
       <c r="Z6">
-        <v>0.1334301923076922</v>
+        <v>0.197677638856059</v>
       </c>
       <c r="AA6">
-        <v>0.001084065607636244</v>
+        <v>0.001778867836737531</v>
       </c>
       <c r="AB6">
-        <v>0.4140679716611463</v>
+        <v>0.5112281979011294</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3859320283388538</v>
+        <v>0.2887718020988707</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1512,46 +1500,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01124183345656113</v>
+        <v>0.008998831871078911</v>
       </c>
       <c r="AJ6">
-        <v>44476.73076923073</v>
+        <v>55562.76716391776</v>
       </c>
       <c r="AK6">
-        <v>44476.73076923073</v>
+        <v>41672.07537293832</v>
       </c>
       <c r="AL6">
-        <v>38461.53846153842</v>
+        <v>261.711593823602</v>
       </c>
       <c r="AM6">
-        <v>444.7673076923073</v>
+        <v>416.7207537293832</v>
       </c>
       <c r="AN6">
-        <v>0.004447673076923073</v>
+        <v>0.004167207537293832</v>
       </c>
       <c r="AO6">
-        <v>499.9999999999999</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP6">
-        <v>0.004999999999999999</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ6">
-        <v>0.01620175168840787</v>
+        <v>3.685558316195864</v>
       </c>
       <c r="AR6">
-        <v>0.006775866717876774</v>
+        <v>1.978304711215372</v>
       </c>
       <c r="AS6">
-        <v>0.007716949830078606</v>
+        <v>3.776847194376566</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1563,7 +1551,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,7 +1571,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
         <v>68</v>
@@ -1592,22 +1580,22 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.2657391701112821</v>
       </c>
       <c r="L7">
-        <v>0.0873260828937016</v>
+        <v>1.19749366441393</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="O7" t="s">
         <v>72</v>
@@ -1616,46 +1604,46 @@
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.8006956224165385</v>
       </c>
       <c r="R7">
-        <v>7.7936</v>
+        <v>1.350525</v>
       </c>
       <c r="S7">
-        <v>7.779454815065272</v>
+        <v>1.343772079074953</v>
       </c>
       <c r="T7">
-        <v>7.713782011933707</v>
+        <v>1.32031992344484</v>
       </c>
       <c r="U7">
-        <v>7.7936</v>
+        <v>1.350525</v>
       </c>
       <c r="V7">
-        <v>7.8477</v>
+        <v>1.357155</v>
       </c>
       <c r="W7">
-        <v>7.779454815065272</v>
+        <v>1.343772079074953</v>
       </c>
       <c r="X7">
-        <v>7.856525</v>
+        <v>1.36468125</v>
       </c>
       <c r="Y7">
-        <v>-0.00181497445785363</v>
+        <v>-0.005000219118525743</v>
       </c>
       <c r="Z7">
-        <v>0.2247943573258327</v>
+        <v>0.477027526714136</v>
       </c>
       <c r="AA7">
-        <v>0.00181497445785363</v>
+        <v>0.005000219118525743</v>
       </c>
       <c r="AB7">
-        <v>0.4288085996804423</v>
+        <v>0.3435952010935654</v>
       </c>
       <c r="AC7">
-        <v>0.2</v>
+        <v>0.1095875397858194</v>
       </c>
       <c r="AD7">
-        <v>0.3711914003195577</v>
+        <v>0.5468172591206153</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1667,46 +1655,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>375</v>
+        <v>400.3478112082692</v>
       </c>
       <c r="AI7">
-        <v>0.00807393245740096</v>
+        <v>0.01048203476425833</v>
       </c>
       <c r="AJ7">
-        <v>61927.69169646392</v>
+        <v>47700.6622516557</v>
       </c>
       <c r="AK7">
-        <v>46445.76877234795</v>
+        <v>38193.71145127054</v>
       </c>
       <c r="AL7">
-        <v>5959.475566150168</v>
+        <v>28280.64008535239</v>
       </c>
       <c r="AM7">
-        <v>464.4576877234795</v>
+        <v>381.9371145127054</v>
       </c>
       <c r="AN7">
-        <v>0.004644576877234795</v>
+        <v>0.003819371145127054</v>
       </c>
       <c r="AO7">
-        <v>375</v>
+        <v>400.3478112082693</v>
       </c>
       <c r="AP7">
-        <v>0.00375</v>
+        <v>0.004003478112082693</v>
       </c>
       <c r="AQ7">
-        <v>0.09704091895959474</v>
+        <v>0.02010330860831993</v>
       </c>
       <c r="AR7">
-        <v>0.03810707792263828</v>
+        <v>0.004568937458262513</v>
       </c>
       <c r="AS7">
-        <v>0.05365286371443611</v>
+        <v>0.005578942824751084</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1718,7 +1706,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,7 +1726,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1747,22 +1735,22 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.3076041134461021</v>
       </c>
       <c r="L8">
-        <v>0.00811134348940943</v>
+        <v>2.703799004582577</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1771,46 +1759,46 @@
         <v>74</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.8269010283615255</v>
       </c>
       <c r="R8">
-        <v>9.09496</v>
+        <v>6.74682</v>
       </c>
       <c r="S8">
-        <v>9.076446546464496</v>
+        <v>6.707824862092181</v>
       </c>
       <c r="T8">
-        <v>9.040431896731027</v>
+        <v>6.670651892113909</v>
       </c>
       <c r="U8">
-        <v>9.09496</v>
+        <v>6.74682</v>
       </c>
       <c r="V8">
-        <v>9.099590000000001</v>
+        <v>6.716519999999999</v>
       </c>
       <c r="W8">
-        <v>9.076446546464496</v>
+        <v>6.707824862092181</v>
       </c>
       <c r="X8">
-        <v>9.1827925</v>
+        <v>6.774745</v>
       </c>
       <c r="Y8">
-        <v>-0.002035572837649061</v>
+        <v>-0.005779780386584849</v>
       </c>
       <c r="Z8">
-        <v>0.2107813569635927</v>
+        <v>1.396423917916483</v>
       </c>
       <c r="AA8">
-        <v>0.002035572837649061</v>
+        <v>0.005779780386584849</v>
       </c>
       <c r="AB8">
-        <v>0.3755606131334034</v>
+        <v>0.3044958447301792</v>
       </c>
       <c r="AC8">
-        <v>0.2</v>
+        <v>0.1739772392452882</v>
       </c>
       <c r="AD8">
-        <v>0.4244393868665965</v>
+        <v>0.5215269160245326</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1822,46 +1810,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>413.4505141807628</v>
       </c>
       <c r="AI8">
-        <v>0.009657271719721664</v>
+        <v>0.004138986959782597</v>
       </c>
       <c r="AJ8">
-        <v>51774.45706316014</v>
+        <v>120802.5067144118</v>
       </c>
       <c r="AK8">
-        <v>51774.45706316014</v>
+        <v>99891.71703079718</v>
       </c>
       <c r="AL8">
-        <v>5692.653630489869</v>
+        <v>14805.74804586415</v>
       </c>
       <c r="AM8">
-        <v>517.7445706316014</v>
+        <v>998.9171703079718</v>
       </c>
       <c r="AN8">
-        <v>0.005177445706316014</v>
+        <v>0.009989171703079718</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>413.4505141807627</v>
       </c>
       <c r="AP8">
-        <v>0.005</v>
+        <v>0.004134505141807627</v>
       </c>
       <c r="AQ8">
-        <v>0.1272202985646421</v>
+        <v>0.07680961065158255</v>
       </c>
       <c r="AR8">
-        <v>0.03306487965381423</v>
+        <v>0.008442979746383007</v>
       </c>
       <c r="AS8">
-        <v>0.03209632818862936</v>
+        <v>0.01574726679093924</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1873,7 +1861,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1902,22 +1890,22 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.999579607254382</v>
+        <v>0.06508960673084886</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>124</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
@@ -1926,46 +1914,46 @@
         <v>74</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R9">
-        <v>1.34987</v>
+        <v>7.7865</v>
       </c>
       <c r="S9">
-        <v>1.346729620505612</v>
+        <v>7.729912252962111</v>
       </c>
       <c r="T9">
-        <v>1.330990297676614</v>
+        <v>7.668078369047613</v>
       </c>
       <c r="U9">
-        <v>1.34987</v>
+        <v>7.7865</v>
       </c>
       <c r="V9">
-        <v>1.35924</v>
+        <v>7.819500000000001</v>
       </c>
       <c r="W9">
-        <v>1.346729620505612</v>
+        <v>7.729912252962111</v>
       </c>
       <c r="X9">
-        <v>1.36402625</v>
+        <v>7.849425</v>
       </c>
       <c r="Y9">
-        <v>-0.002326431059574668</v>
+        <v>-0.007267417586577901</v>
       </c>
       <c r="Z9">
-        <v>0.2218369620759778</v>
+        <v>0.8992887888420933</v>
       </c>
       <c r="AA9">
-        <v>0.002326431059574668</v>
+        <v>0.007267417586577901</v>
       </c>
       <c r="AB9">
-        <v>0.3765129760529499</v>
+        <v>0.5480574110576284</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4234870239470501</v>
+        <v>0.2519425889423715</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1977,46 +1965,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI9">
-        <v>0.01048712098202048</v>
+        <v>0.008081294548256613</v>
       </c>
       <c r="AJ9">
-        <v>47677.52759381905</v>
+        <v>61871.27532777104</v>
       </c>
       <c r="AK9">
-        <v>47677.52759381905</v>
+        <v>46403.45649582829</v>
       </c>
       <c r="AL9">
-        <v>35320.0883002208</v>
+        <v>5959.475566150169</v>
       </c>
       <c r="AM9">
-        <v>476.7752759381905</v>
+        <v>464.0345649582829</v>
       </c>
       <c r="AN9">
-        <v>0.004767752759381905</v>
+        <v>0.004640345649582829</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP9">
-        <v>0.005</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ9">
-        <v>0.0202753040970711</v>
+        <v>0.09293715189486755</v>
       </c>
       <c r="AR9">
-        <v>0.006187272743404255</v>
+        <v>0.02730512718684007</v>
       </c>
       <c r="AS9">
-        <v>0.005553919851368239</v>
+        <v>0.04399922571098105</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2028,7 +2016,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,7 +2036,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2057,22 +2045,22 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1.550379514226834</v>
+        <v>0.07621669096916868</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2081,46 +2069,46 @@
         <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>157.7145</v>
+        <v>9.109389999999999</v>
       </c>
       <c r="S10">
-        <v>156.7270412482461</v>
+        <v>9.040006693918514</v>
       </c>
       <c r="T10">
-        <v>158.4925952069294</v>
+        <v>8.963437817549485</v>
       </c>
       <c r="U10">
-        <v>157.7145</v>
+        <v>9.109389999999999</v>
       </c>
       <c r="V10">
-        <v>153.739</v>
+        <v>9.100199999999999</v>
       </c>
       <c r="W10">
-        <v>156.7270412482461</v>
+        <v>9.040006693918514</v>
       </c>
       <c r="X10">
-        <v>159.3165</v>
+        <v>9.197222499999999</v>
       </c>
       <c r="Y10">
-        <v>-0.006261052419110791</v>
+        <v>-0.007616679720759094</v>
       </c>
       <c r="Z10">
-        <v>0.6163912308076498</v>
+        <v>0.7899502585203185</v>
       </c>
       <c r="AA10">
-        <v>0.006261052419110791</v>
+        <v>0.007616679720759094</v>
       </c>
       <c r="AB10">
-        <v>0.4613226732157272</v>
+        <v>0.4529605944769312</v>
       </c>
       <c r="AC10">
-        <v>0.2</v>
+        <v>0.1909220221176282</v>
       </c>
       <c r="AD10">
-        <v>0.3386773267842728</v>
+        <v>0.3561173834054406</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2132,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.01015759489457209</v>
+        <v>0.009641973831398126</v>
       </c>
       <c r="AJ10">
-        <v>49224.2509363299</v>
+        <v>51856.6020550481</v>
       </c>
       <c r="AK10">
-        <v>36918.18820224743</v>
+        <v>51856.6020550481</v>
       </c>
       <c r="AL10">
-        <v>234.0823970037468</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM10">
-        <v>369.1818820224743</v>
+        <v>518.566020550481</v>
       </c>
       <c r="AN10">
-        <v>0.003691818820224743</v>
+        <v>0.00518566020550481</v>
       </c>
       <c r="AO10">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>4.339886793695866</v>
+        <v>0.1001779704000281</v>
       </c>
       <c r="AR10">
-        <v>2.568890519603397</v>
+        <v>0.02578095179864048</v>
       </c>
       <c r="AS10">
-        <v>3.83864144844791</v>
+        <v>0.02479861645312424</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2183,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2212,22 +2200,22 @@
         <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K11">
-        <v>0.4274996118397774</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>2.849099356564458</v>
+        <v>0.734030243305818</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2236,46 +2224,46 @@
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>0.8568749029599444</v>
+        <v>1</v>
       </c>
       <c r="R11">
-        <v>6.74282</v>
+        <v>1.15413</v>
       </c>
       <c r="S11">
-        <v>6.664314415730515</v>
+        <v>1.143433380764401</v>
       </c>
       <c r="T11">
-        <v>6.573510562917879</v>
+        <v>1.11934465431352</v>
       </c>
       <c r="U11">
-        <v>6.74282</v>
+        <v>1.15413</v>
       </c>
       <c r="V11">
-        <v>6.70434</v>
+        <v>1.165215</v>
       </c>
       <c r="W11">
-        <v>6.664314415730515</v>
+        <v>1.143433380764401</v>
       </c>
       <c r="X11">
-        <v>6.795157056179657</v>
+        <v>1.16713</v>
       </c>
       <c r="Y11">
-        <v>-0.01164284146239779</v>
+        <v>-0.009268123379167909</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.82281686427685</v>
       </c>
       <c r="AA11">
-        <v>0.01164284146239779</v>
+        <v>0.009268123379167909</v>
       </c>
       <c r="AB11">
-        <v>0.3647618252727841</v>
+        <v>0.4265199867758034</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.435238174727216</v>
+        <v>0.3734800132241967</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2287,46 +2275,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>428.4374514799722</v>
+        <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.007761894308265193</v>
+        <v>0.01126389574831259</v>
       </c>
       <c r="AJ11">
-        <v>64417.26467050432</v>
+        <v>44389.61538461535</v>
       </c>
       <c r="AK11">
-        <v>55197.53741348345</v>
+        <v>44389.61538461535</v>
       </c>
       <c r="AL11">
-        <v>8186.120556901037</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM11">
-        <v>551.9753741348345</v>
+        <v>443.8961538461535</v>
       </c>
       <c r="AN11">
-        <v>0.005519753741348345</v>
+        <v>0.004438961538461535</v>
       </c>
       <c r="AO11">
-        <v>428.4374514799723</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>0.004284374514799723</v>
+        <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.04856952994888593</v>
+        <v>0.01729555528536116</v>
       </c>
       <c r="AR11">
-        <v>0.01154045540517659</v>
+        <v>0.004832924213043027</v>
       </c>
       <c r="AS11">
-        <v>0.01025487929226829</v>
+        <v>0.008062511876889791</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03834889745580173</v>
+        <v>0.03647105056419893</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2338,7 +2326,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -172,33 +172,33 @@
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>USDCNH</t>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.28,naive=0.09,drift4=0.63); metric_best=drift4; scores=model=0.1579,naive=0.03871,drift4=0.001277</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02475,naive=0.00695,drift4=0.01504; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1198,naive=408.5,drift4=461.7; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.04806,naive=0.00649,drift4=0.00598; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.575,naive=5.407,drift4=7.743; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.11,drift4=0.55); metric_best=drift4; scores=model=0.009879,naive=0.01959,drift4=0.001708</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.17,drift4=0.52); metric_best=drift4; scores=model=0.1046,naive=0.03117,drift4=0.008303</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.55,naive=0.20,drift4=0.25); metric_best=model; scores=model=0.06233,naive=0.1095,drift4=0.1692; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.36); metric_best=drift4; scores=model=0.07223,naive=0.1109,drift4=0.06236</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=drift4; scores=model=0.02544,naive=0.0182,drift4=0.01588; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.12,drift4=0.59); metric_best=drift4; scores=model=0.1694,naive=0.04534,drift4=0.004933</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.18,drift4=0.51); metric_best=drift4; scores=model=0.1202,naive=0.03033,drift4=0.009085</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1173,naive=412.5,drift4=465.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04846,naive=0.007601,drift4=0.004939; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.556,naive=5.253,drift4=7.588; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02406,naive=0.005569,drift4=0.01366; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.11,drift4=0.55); metric_best=drift4; scores=model=0.009796,naive=0.01956,drift4=0.001679</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02972,naive=0.01795,drift4=0.01565; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.36); metric_best=drift4; scores=model=0.07533,naive=0.1117,drift4=0.06315</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.53,naive=0.20,drift4=0.27); metric_best=model; scores=model=0.07357,naive=0.1078,drift4=0.1675; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.002126301230752134</v>
+        <v>0.01736807487827153</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>4.75742</v>
+        <v>4.76282</v>
       </c>
       <c r="S2">
-        <v>4.760940362508544</v>
+        <v>4.767340477839737</v>
       </c>
       <c r="T2">
-        <v>4.710582426611793</v>
+        <v>4.713586512969131</v>
       </c>
       <c r="U2">
-        <v>4.75742</v>
+        <v>4.76282</v>
       </c>
       <c r="V2">
-        <v>4.783729999999999</v>
+        <v>4.794529999999999</v>
       </c>
       <c r="Y2">
-        <v>0.0007399730333971017</v>
+        <v>0.0009491179258794096</v>
       </c>
       <c r="AA2">
-        <v>0.0007399730333971017</v>
+        <v>0.0009491179258794096</v>
       </c>
       <c r="AB2">
-        <v>0.2788836582686398</v>
+        <v>0.2877948358531044</v>
       </c>
       <c r="AC2">
-        <v>0.09083902058072661</v>
+        <v>0.1228131377116539</v>
       </c>
       <c r="AD2">
-        <v>0.6302773211506336</v>
+        <v>0.5893920264352417</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.04698701001632302</v>
+        <v>0.05338439317144019</v>
       </c>
       <c r="AR2">
-        <v>0.01476393936234121</v>
+        <v>0.01620363236140273</v>
       </c>
       <c r="AS2">
-        <v>0.01692915163923248</v>
+        <v>0.01662780376560605</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -972,22 +972,22 @@
         <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J3" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.3937945574816273</v>
       </c>
       <c r="L3">
-        <v>0.9743535519187986</v>
+        <v>2.808759793747735</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.8105249999999999</v>
+        <v>6.7475</v>
       </c>
       <c r="S3">
-        <v>0.8110577866881248</v>
+        <v>6.745190702211145</v>
       </c>
       <c r="T3">
-        <v>0.8101466115682419</v>
+        <v>6.790157616000245</v>
       </c>
       <c r="U3">
-        <v>0.8105249999999999</v>
+        <v>6.7475</v>
       </c>
       <c r="V3">
-        <v>0.8125049999999998</v>
+        <v>6.717879999999999</v>
       </c>
       <c r="Y3">
-        <v>0.0006573352927113195</v>
+        <v>-0.0003422449483296567</v>
       </c>
       <c r="AA3">
-        <v>0.0006573352927113195</v>
+        <v>0.0003422449483296567</v>
       </c>
       <c r="AB3">
-        <v>0.4457337467057311</v>
+        <v>0.302491734479532</v>
       </c>
       <c r="AC3">
-        <v>0.2</v>
+        <v>0.183906846157546</v>
       </c>
       <c r="AD3">
-        <v>0.3542662532942689</v>
+        <v>0.5136014193629219</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.01808078097285104</v>
+        <v>0.06998389308714832</v>
       </c>
       <c r="AR3">
-        <v>0.003638322517375865</v>
+        <v>0.01029880066726979</v>
       </c>
       <c r="AS3">
-        <v>0.004604298557712782</v>
+        <v>0.01616620970931188</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1086,7 +1086,7 @@
         <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,19 +1118,19 @@
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.1815823354572913</v>
+        <v>0.5216109107284753</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
@@ -1142,43 +1142,43 @@
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4378.51</v>
+        <v>4381.79</v>
       </c>
       <c r="S4">
-        <v>4688.465304862797</v>
+        <v>4591.732683522236</v>
       </c>
       <c r="T4">
-        <v>4763.230312129874</v>
+        <v>4515.261925753866</v>
       </c>
       <c r="U4">
-        <v>4378.51</v>
+        <v>4381.79</v>
       </c>
       <c r="V4">
-        <v>4768.700000000001</v>
+        <v>4775.26</v>
       </c>
       <c r="W4">
-        <v>4688.465304862797</v>
+        <v>4591.732683522236</v>
       </c>
       <c r="X4">
-        <v>4171.873130091469</v>
+        <v>4241.455000000001</v>
       </c>
       <c r="Y4">
-        <v>0.07079013291343328</v>
+        <v>0.04791253883053175</v>
       </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>1.496010856324058</v>
       </c>
       <c r="AA4">
-        <v>0.07079013291343328</v>
+        <v>0.04791253883053175</v>
       </c>
       <c r="AB4">
-        <v>0.4016125214752247</v>
+        <v>0.4032080498354822</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3983874785247753</v>
+        <v>0.3967919501645178</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1193,22 +1193,22 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.04719342194228885</v>
+        <v>0.03202686573295373</v>
       </c>
       <c r="AJ4">
-        <v>10594.6968755822</v>
+        <v>15611.89297039235</v>
       </c>
       <c r="AK4">
-        <v>7946.022656686649</v>
+        <v>11708.91972779426</v>
       </c>
       <c r="AL4">
-        <v>1.814777779812459</v>
+        <v>2.67217729005595</v>
       </c>
       <c r="AM4">
-        <v>79.46022656686648</v>
+        <v>117.0891972779426</v>
       </c>
       <c r="AN4">
-        <v>0.0007946022656686648</v>
+        <v>0.001170891972779426</v>
       </c>
       <c r="AO4">
         <v>375</v>
@@ -1217,19 +1217,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>376.7320788786117</v>
+        <v>460.8636246013585</v>
       </c>
       <c r="AR4">
-        <v>146.1915630997557</v>
+        <v>147.3079090225866</v>
       </c>
       <c r="AS4">
-        <v>187.8379939531156</v>
+        <v>181.6655671993815</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1241,7 +1241,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,19 +1273,19 @@
         <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.761784839710452</v>
+        <v>0.8499218835129919</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1297,43 +1297,43 @@
         <v>0.75</v>
       </c>
       <c r="R5">
-        <v>0.70547</v>
+        <v>0.706375</v>
       </c>
       <c r="S5">
-        <v>0.709488337535471</v>
+        <v>0.7114993023291268</v>
       </c>
       <c r="T5">
-        <v>0.7056475937264967</v>
+        <v>0.7080913845611428</v>
       </c>
       <c r="U5">
-        <v>0.70547</v>
+        <v>0.706375</v>
       </c>
       <c r="V5">
-        <v>0.714245</v>
+        <v>0.7160549999999999</v>
       </c>
       <c r="W5">
-        <v>0.709488337535471</v>
+        <v>0.7114993023291268</v>
       </c>
       <c r="X5">
-        <v>0.69777</v>
+        <v>0.6986749999999999</v>
       </c>
       <c r="Y5">
-        <v>0.005695972239033529</v>
+        <v>0.007254365357107573</v>
       </c>
       <c r="Z5">
-        <v>0.5218620175936297</v>
+        <v>0.6654938089775086</v>
       </c>
       <c r="AA5">
-        <v>0.005695972239033529</v>
+        <v>0.007254365357107573</v>
       </c>
       <c r="AB5">
-        <v>0.3491358171335802</v>
+        <v>0.3289583344382415</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4508641828664198</v>
+        <v>0.4710416655617585</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1348,43 +1348,43 @@
         <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01091470934270779</v>
+        <v>0.01090072553530358</v>
       </c>
       <c r="AJ5">
-        <v>45809.74025973985</v>
+        <v>45868.50649350609</v>
       </c>
       <c r="AK5">
-        <v>34357.30519480489</v>
+        <v>34401.37987012957</v>
       </c>
       <c r="AL5">
-        <v>48701.29870129826</v>
+        <v>48701.29870129828</v>
       </c>
       <c r="AM5">
-        <v>343.5730519480489</v>
+        <v>344.0137987012957</v>
       </c>
       <c r="AN5">
-        <v>0.003435730519480489</v>
+        <v>0.003440137987012957</v>
       </c>
       <c r="AO5">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP5">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ5">
-        <v>0.01602548836259331</v>
+        <v>0.01689948069267504</v>
       </c>
       <c r="AR5">
-        <v>0.001824716926400594</v>
+        <v>0.002314413550359111</v>
       </c>
       <c r="AS5">
-        <v>0.005025871961216736</v>
+        <v>0.00458522918392031</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1396,7 +1396,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,25 +1416,25 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
         <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.266603651507621</v>
+        <v>1.308563355560978</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -1443,52 +1443,52 @@
         <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>159.229</v>
+        <v>159.3545</v>
       </c>
       <c r="S6">
-        <v>158.9457526532241</v>
+        <v>160.4766960577176</v>
       </c>
       <c r="T6">
-        <v>160.4909687247705</v>
+        <v>163.3122506912334</v>
       </c>
       <c r="U6">
-        <v>159.229</v>
+        <v>159.3545</v>
       </c>
       <c r="V6">
-        <v>156.014</v>
+        <v>156.265</v>
       </c>
       <c r="W6">
-        <v>158.9457526532241</v>
+        <v>160.4766960577176</v>
       </c>
       <c r="X6">
-        <v>160.661875</v>
+        <v>157.8275</v>
       </c>
       <c r="Y6">
-        <v>-0.001778867836737531</v>
+        <v>0.007042135978071634</v>
       </c>
       <c r="Z6">
-        <v>0.197677638856059</v>
+        <v>0.7349024608497741</v>
       </c>
       <c r="AA6">
-        <v>0.001778867836737531</v>
+        <v>0.007042135978071634</v>
       </c>
       <c r="AB6">
-        <v>0.5112281979011294</v>
+        <v>0.5099571755249422</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.2887718020988707</v>
+        <v>0.2900428244750577</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1500,58 +1500,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.008998831871078911</v>
+        <v>0.009582409031436296</v>
       </c>
       <c r="AJ6">
-        <v>55562.76716391776</v>
+        <v>52178.94564505514</v>
       </c>
       <c r="AK6">
-        <v>41672.07537293832</v>
+        <v>52178.94564505514</v>
       </c>
       <c r="AL6">
-        <v>261.711593823602</v>
+        <v>327.439423706611</v>
       </c>
       <c r="AM6">
-        <v>416.7207537293832</v>
+        <v>521.7894564505515</v>
       </c>
       <c r="AN6">
-        <v>0.004167207537293832</v>
+        <v>0.005217894564505515</v>
       </c>
       <c r="AO6">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ6">
-        <v>3.685558316195864</v>
+        <v>4.222520110880288</v>
       </c>
       <c r="AR6">
-        <v>1.978304711215372</v>
+        <v>2.395596871560259</v>
       </c>
       <c r="AS6">
-        <v>3.776847194376566</v>
+        <v>4.105995184969433</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,19 +1583,19 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K7">
-        <v>0.2657391701112821</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.19749366441393</v>
+        <v>1.04152115130347</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O7" t="s">
         <v>72</v>
@@ -1604,46 +1604,46 @@
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>0.8006956224165385</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>1.350525</v>
+        <v>0.81165</v>
       </c>
       <c r="S7">
-        <v>1.343772079074953</v>
+        <v>0.8071390412476787</v>
       </c>
       <c r="T7">
-        <v>1.32031992344484</v>
+        <v>0.7990689279494918</v>
       </c>
       <c r="U7">
-        <v>1.350525</v>
+        <v>0.81165</v>
       </c>
       <c r="V7">
-        <v>1.357155</v>
+        <v>0.8147549999999999</v>
       </c>
       <c r="W7">
-        <v>1.343772079074953</v>
+        <v>0.8071390412476787</v>
       </c>
       <c r="X7">
-        <v>1.36468125</v>
+        <v>0.8211299999999999</v>
       </c>
       <c r="Y7">
-        <v>-0.005000219118525743</v>
+        <v>-0.005557763509297512</v>
       </c>
       <c r="Z7">
-        <v>0.477027526714136</v>
+        <v>0.4758395308355834</v>
       </c>
       <c r="AA7">
-        <v>0.005000219118525743</v>
+        <v>0.005557763509297512</v>
       </c>
       <c r="AB7">
-        <v>0.3435952010935654</v>
+        <v>0.445934376037415</v>
       </c>
       <c r="AC7">
-        <v>0.1095875397858194</v>
+        <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.5468172591206153</v>
+        <v>0.354065623962585</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,46 +1655,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>400.3478112082692</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01048203476425833</v>
+        <v>0.01167991129181296</v>
       </c>
       <c r="AJ7">
-        <v>47700.6622516557</v>
+        <v>42808.54430379752</v>
       </c>
       <c r="AK7">
-        <v>38193.71145127054</v>
+        <v>42808.54430379752</v>
       </c>
       <c r="AL7">
-        <v>28280.64008535239</v>
+        <v>52742.61603375534</v>
       </c>
       <c r="AM7">
-        <v>381.9371145127054</v>
+        <v>428.0854430379752</v>
       </c>
       <c r="AN7">
-        <v>0.003819371145127054</v>
+        <v>0.004280854430379752</v>
       </c>
       <c r="AO7">
-        <v>400.3478112082693</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP7">
-        <v>0.004003478112082693</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ7">
-        <v>0.02010330860831993</v>
+        <v>0.01942056402251046</v>
       </c>
       <c r="AR7">
-        <v>0.004568937458262513</v>
+        <v>0.003664613049754937</v>
       </c>
       <c r="AS7">
-        <v>0.005578942824751084</v>
+        <v>0.005218673660268351</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1706,7 +1706,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,7 +1726,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1735,70 +1735,70 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K8">
-        <v>0.3076041134461021</v>
+        <v>0.435624528851162</v>
       </c>
       <c r="L8">
-        <v>2.703799004582577</v>
+        <v>1.301850308907033</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>0.8269010283615255</v>
+        <v>0.6732816033616285</v>
       </c>
       <c r="R8">
-        <v>6.74682</v>
+        <v>1.3505</v>
       </c>
       <c r="S8">
-        <v>6.707824862092181</v>
+        <v>1.340729930147171</v>
       </c>
       <c r="T8">
-        <v>6.670651892113909</v>
+        <v>1.311487950013936</v>
       </c>
       <c r="U8">
-        <v>6.74682</v>
+        <v>1.3505</v>
       </c>
       <c r="V8">
-        <v>6.716519999999999</v>
+        <v>1.357105</v>
       </c>
       <c r="W8">
-        <v>6.707824862092181</v>
+        <v>1.340729930147171</v>
       </c>
       <c r="X8">
-        <v>6.774745</v>
+        <v>1.36465625</v>
       </c>
       <c r="Y8">
-        <v>-0.005779780386584849</v>
+        <v>-0.007234409368995697</v>
       </c>
       <c r="Z8">
-        <v>1.396423917916483</v>
+        <v>0.690159459802469</v>
       </c>
       <c r="AA8">
-        <v>0.005779780386584849</v>
+        <v>0.007234409368995697</v>
       </c>
       <c r="AB8">
-        <v>0.3044958447301792</v>
+        <v>0.3431663733404539</v>
       </c>
       <c r="AC8">
-        <v>0.1739772392452882</v>
+        <v>0.1091343295413683</v>
       </c>
       <c r="AD8">
-        <v>0.5215269160245326</v>
+        <v>0.5476992971181778</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1810,46 +1810,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>413.4505141807628</v>
+        <v>336.6408016808142</v>
       </c>
       <c r="AI8">
-        <v>0.004138986959782597</v>
+        <v>0.0104822288041466</v>
       </c>
       <c r="AJ8">
-        <v>120802.5067144118</v>
+        <v>47699.77924944819</v>
       </c>
       <c r="AK8">
-        <v>99891.71703079718</v>
+        <v>32115.38385306421</v>
       </c>
       <c r="AL8">
-        <v>14805.74804586415</v>
+        <v>23780.36568164696</v>
       </c>
       <c r="AM8">
-        <v>998.9171703079718</v>
+        <v>321.1538385306421</v>
       </c>
       <c r="AN8">
-        <v>0.009989171703079718</v>
+        <v>0.003211538385306421</v>
       </c>
       <c r="AO8">
-        <v>413.4505141807627</v>
+        <v>336.6408016808143</v>
       </c>
       <c r="AP8">
-        <v>0.004134505141807627</v>
+        <v>0.003366408016808143</v>
       </c>
       <c r="AQ8">
-        <v>0.07680961065158255</v>
+        <v>0.01932505943579866</v>
       </c>
       <c r="AR8">
-        <v>0.008442979746383007</v>
+        <v>0.005816869159762649</v>
       </c>
       <c r="AS8">
-        <v>0.01574726679093924</v>
+        <v>0.005226354987435744</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1861,7 +1861,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1881,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1890,70 +1890,70 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.06508960673084886</v>
+        <v>0.7870207281778198</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>124</v>
+        <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>7.7865</v>
+        <v>1.153925</v>
       </c>
       <c r="S9">
-        <v>7.729912252962111</v>
+        <v>1.143273518953264</v>
       </c>
       <c r="T9">
-        <v>7.668078369047613</v>
+        <v>1.118068209239886</v>
       </c>
       <c r="U9">
-        <v>7.7865</v>
+        <v>1.153925</v>
       </c>
       <c r="V9">
-        <v>7.819500000000001</v>
+        <v>1.164805</v>
       </c>
       <c r="W9">
-        <v>7.729912252962111</v>
+        <v>1.143273518953264</v>
       </c>
       <c r="X9">
-        <v>7.849425</v>
+        <v>1.166925</v>
       </c>
       <c r="Y9">
-        <v>-0.007267417586577901</v>
+        <v>-0.009230652812562311</v>
       </c>
       <c r="Z9">
-        <v>0.8992887888420933</v>
+        <v>0.8193446959027659</v>
       </c>
       <c r="AA9">
-        <v>0.007267417586577901</v>
+        <v>0.009230652812562311</v>
       </c>
       <c r="AB9">
-        <v>0.5480574110576284</v>
+        <v>0.4141379998913899</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.2519425889423715</v>
+        <v>0.3858620001086101</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1965,46 +1965,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.008081294548256613</v>
+        <v>0.01126589683038327</v>
       </c>
       <c r="AJ9">
-        <v>61871.27532777104</v>
+        <v>44381.73076923073</v>
       </c>
       <c r="AK9">
-        <v>46403.45649582829</v>
+        <v>44381.73076923073</v>
       </c>
       <c r="AL9">
-        <v>5959.475566150169</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM9">
-        <v>464.0345649582829</v>
+        <v>443.8173076923073</v>
       </c>
       <c r="AN9">
-        <v>0.004640345649582829</v>
+        <v>0.004438173076923073</v>
       </c>
       <c r="AO9">
-        <v>375.0000000000001</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP9">
-        <v>0.003750000000000001</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ9">
-        <v>0.09293715189486755</v>
+        <v>0.01810490269536492</v>
       </c>
       <c r="AR9">
-        <v>0.02730512718684007</v>
+        <v>0.006120307498601138</v>
       </c>
       <c r="AS9">
-        <v>0.04399922571098105</v>
+        <v>0.008985542307457588</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2016,7 +2016,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,19 +2048,19 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.07621669096916868</v>
+        <v>0.1432801373781929</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
         <v>72</v>
@@ -2072,43 +2072,43 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>9.109389999999999</v>
+        <v>9.11007</v>
       </c>
       <c r="S10">
-        <v>9.040006693918514</v>
+        <v>9.002973836569677</v>
       </c>
       <c r="T10">
-        <v>8.963437817549485</v>
+        <v>8.878530387622934</v>
       </c>
       <c r="U10">
-        <v>9.109389999999999</v>
+        <v>9.11007</v>
       </c>
       <c r="V10">
-        <v>9.100199999999999</v>
+        <v>9.101560000000001</v>
       </c>
       <c r="W10">
-        <v>9.040006693918514</v>
+        <v>9.002973836569677</v>
       </c>
       <c r="X10">
-        <v>9.197222499999999</v>
+        <v>9.1979025</v>
       </c>
       <c r="Y10">
-        <v>-0.007616679720759094</v>
+        <v>-0.01175580027709159</v>
       </c>
       <c r="Z10">
-        <v>0.7899502585203185</v>
+        <v>1.219322727126338</v>
       </c>
       <c r="AA10">
-        <v>0.007616679720759094</v>
+        <v>0.01175580027709159</v>
       </c>
       <c r="AB10">
-        <v>0.4529605944769312</v>
+        <v>0.4493799958755037</v>
       </c>
       <c r="AC10">
-        <v>0.1909220221176282</v>
+        <v>0.1925831797646148</v>
       </c>
       <c r="AD10">
-        <v>0.3561173834054406</v>
+        <v>0.3580368243598816</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2123,22 +2123,22 @@
         <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.009641973831398126</v>
+        <v>0.009641254128672968</v>
       </c>
       <c r="AJ10">
-        <v>51856.6020550481</v>
+        <v>51860.47305951684</v>
       </c>
       <c r="AK10">
-        <v>51856.6020550481</v>
+        <v>51860.47305951684</v>
       </c>
       <c r="AL10">
-        <v>5692.653630489868</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM10">
-        <v>518.566020550481</v>
+        <v>518.6047305951685</v>
       </c>
       <c r="AN10">
-        <v>0.00518566020550481</v>
+        <v>0.005186047305951685</v>
       </c>
       <c r="AO10">
         <v>500</v>
@@ -2147,19 +2147,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.1001779704000281</v>
+        <v>0.09122487584793544</v>
       </c>
       <c r="AR10">
-        <v>0.02578095179864048</v>
+        <v>0.03272560384090063</v>
       </c>
       <c r="AS10">
-        <v>0.02479861645312424</v>
+        <v>0.02707108109465816</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2171,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2191,7 +2191,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2203,19 +2203,19 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.734030243305818</v>
+        <v>0.05761258491225919</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="O11" t="s">
         <v>72</v>
@@ -2227,43 +2227,43 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1.15413</v>
+        <v>7.7851</v>
       </c>
       <c r="S11">
-        <v>1.143433380764401</v>
+        <v>7.684364014156218</v>
       </c>
       <c r="T11">
-        <v>1.11934465431352</v>
+        <v>7.580984448598004</v>
       </c>
       <c r="U11">
-        <v>1.15413</v>
+        <v>7.7851</v>
       </c>
       <c r="V11">
-        <v>1.165215</v>
+        <v>7.8167</v>
       </c>
       <c r="W11">
-        <v>1.143433380764401</v>
+        <v>7.684364014156218</v>
       </c>
       <c r="X11">
-        <v>1.16713</v>
+        <v>7.852257323895855</v>
       </c>
       <c r="Y11">
-        <v>-0.009268123379167909</v>
+        <v>-0.01293958791072458</v>
       </c>
       <c r="Z11">
-        <v>0.82281686427685</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.009268123379167909</v>
+        <v>0.01293958791072458</v>
       </c>
       <c r="AB11">
-        <v>0.4265199867758034</v>
+        <v>0.534610402641066</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3734800132241967</v>
+        <v>0.265389597358934</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2278,22 +2278,22 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.01126389574831259</v>
+        <v>0.008626391940483057</v>
       </c>
       <c r="AJ11">
-        <v>44389.61538461535</v>
+        <v>57961.66038474728</v>
       </c>
       <c r="AK11">
-        <v>44389.61538461535</v>
+        <v>57961.66038474728</v>
       </c>
       <c r="AL11">
-        <v>38461.53846153843</v>
+        <v>7445.204349943775</v>
       </c>
       <c r="AM11">
-        <v>443.8961538461535</v>
+        <v>579.6166038474728</v>
       </c>
       <c r="AN11">
-        <v>0.004438961538461535</v>
+        <v>0.005796166038474728</v>
       </c>
       <c r="AO11">
         <v>500</v>
@@ -2302,19 +2302,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.01729555528536116</v>
+        <v>0.07179219655383269</v>
       </c>
       <c r="AR11">
-        <v>0.004832924213043027</v>
+        <v>0.03452680272725898</v>
       </c>
       <c r="AS11">
-        <v>0.008062511876889791</v>
+        <v>0.05533514724125275</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03647105056419893</v>
+        <v>0.03274170376133356</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2326,7 +2326,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
   <si>
     <t>Pair</t>
   </si>
@@ -169,22 +169,28 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>GBPUSD</t>
@@ -193,30 +199,21 @@
     <t>EURUSD</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -235,52 +232,43 @@
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.12,drift4=0.59); metric_best=drift4; scores=model=0.1694,naive=0.04534,drift4=0.004933</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.18,drift4=0.51); metric_best=drift4; scores=model=0.1202,naive=0.03033,drift4=0.009085</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1173,naive=412.5,drift4=465.7; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04846,naive=0.007601,drift4=0.004939; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.556,naive=5.253,drift4=7.588; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02406,naive=0.005569,drift4=0.01366; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.11,drift4=0.55); metric_best=drift4; scores=model=0.009796,naive=0.01956,drift4=0.001679</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=drift4; scores=model=0.02972,naive=0.01795,drift4=0.01565; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.36); metric_best=drift4; scores=model=0.07533,naive=0.1117,drift4=0.06315</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.53,naive=0.20,drift4=0.27); metric_best=model; scores=model=0.07357,naive=0.1078,drift4=0.1675; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=352.5,naive=142.5,drift4=183.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01525,naive=0.001661,drift4=0.004667; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01807,naive=0.003513,drift4=0.004016; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.04288,naive=0.01466,drift4=0.01541; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.723,naive=1.767,drift4=3.599; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09418,naive=0.02264,drift4=0.03815; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0768,naive=0.007209,drift4=0.01626; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.1006,naive=0.02185,drift4=0.02266; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02018,naive=0.003773,drift4=0.005517; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01679,naive=0.004057,drift4=0.00775; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -829,7 +817,7 @@
         <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J2" s="2">
         <v>46245</v>
@@ -838,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.01736807487827153</v>
+        <v>0.5282068048872706</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -847,46 +835,55 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R2">
-        <v>4.76282</v>
+        <v>4381.79</v>
       </c>
       <c r="S2">
-        <v>4.767340477839737</v>
+        <v>4691.850842245356</v>
       </c>
       <c r="T2">
-        <v>4.713586512969131</v>
+        <v>4764.109304701087</v>
       </c>
       <c r="U2">
-        <v>4.76282</v>
+        <v>4381.79</v>
       </c>
       <c r="V2">
-        <v>4.794529999999999</v>
+        <v>4775.26</v>
+      </c>
+      <c r="W2">
+        <v>4691.850842245356</v>
+      </c>
+      <c r="X2">
+        <v>4175.082771836429</v>
       </c>
       <c r="Y2">
-        <v>0.0009491179258794096</v>
+        <v>0.07076122822986863</v>
+      </c>
+      <c r="Z2">
+        <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>0.0009491179258794096</v>
+        <v>0.07076122822986863</v>
       </c>
       <c r="AB2">
-        <v>0.2877948358531044</v>
+        <v>0.4228577347194193</v>
       </c>
       <c r="AC2">
-        <v>0.1228131377116539</v>
+        <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.5893920264352417</v>
+        <v>0.3771422652805807</v>
       </c>
       <c r="AE2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -895,52 +892,55 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI2">
+        <v>0.04717415215324575</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>10599.02461788279</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>7949.268463412089</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.814160072347623</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>79.49268463412089</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.0007949268463412089</v>
       </c>
       <c r="AO2">
-        <v>0</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ2">
-        <v>0.05338439317144019</v>
+        <v>352.5109485135201</v>
       </c>
       <c r="AR2">
-        <v>0.01620363236140273</v>
+        <v>142.5293683023909</v>
       </c>
       <c r="AS2">
-        <v>0.01662780376560605</v>
+        <v>183.65683475101</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AY2" s="2">
         <v>46274</v>
@@ -972,64 +972,73 @@
         <v>66</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J3" s="2">
         <v>46245</v>
       </c>
       <c r="K3">
-        <v>0.3937945574816273</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.808759793747735</v>
+        <v>0.8430004673568237</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R3">
-        <v>6.7475</v>
+        <v>0.706375</v>
       </c>
       <c r="S3">
-        <v>6.745190702211145</v>
+        <v>0.7100411976859821</v>
       </c>
       <c r="T3">
-        <v>6.790157616000245</v>
+        <v>0.7065250317093117</v>
       </c>
       <c r="U3">
-        <v>6.7475</v>
+        <v>0.706375</v>
       </c>
       <c r="V3">
-        <v>6.717879999999999</v>
+        <v>0.7160549999999999</v>
+      </c>
+      <c r="W3">
+        <v>0.7100411976859821</v>
+      </c>
+      <c r="X3">
+        <v>0.6986749999999999</v>
       </c>
       <c r="Y3">
-        <v>-0.0003422449483296567</v>
+        <v>0.005190157757539673</v>
+      </c>
+      <c r="Z3">
+        <v>0.476129569608059</v>
       </c>
       <c r="AA3">
-        <v>0.0003422449483296567</v>
+        <v>0.005190157757539673</v>
       </c>
       <c r="AB3">
-        <v>0.302491734479532</v>
+        <v>0.4278925374811863</v>
       </c>
       <c r="AC3">
-        <v>0.183906846157546</v>
+        <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.5136014193629219</v>
+        <v>0.3721074625188138</v>
       </c>
       <c r="AE3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1038,52 +1047,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI3">
+        <v>0.01090072553530358</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>45868.50649350609</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>34401.37987012957</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>48701.29870129828</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>344.0137987012957</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.003440137987012957</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ3">
-        <v>0.06998389308714832</v>
+        <v>0.01524844087415154</v>
       </c>
       <c r="AR3">
-        <v>0.01029880066726979</v>
+        <v>0.001660957664820482</v>
       </c>
       <c r="AS3">
-        <v>0.01616620970931188</v>
+        <v>0.004666961785771238</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AW3" t="s">
         <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AY3" s="2">
         <v>46274</v>
@@ -1109,13 +1121,13 @@
         <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2">
         <v>46245</v>
@@ -1124,64 +1136,64 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.5216109107284753</v>
+        <v>1.045407844964561</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4381.79</v>
+        <v>0.81165</v>
       </c>
       <c r="S4">
-        <v>4591.732683522236</v>
+        <v>0.8131289328454201</v>
       </c>
       <c r="T4">
-        <v>4515.261925753866</v>
+        <v>0.8120885821316038</v>
       </c>
       <c r="U4">
-        <v>4381.79</v>
+        <v>0.81165</v>
       </c>
       <c r="V4">
-        <v>4775.26</v>
+        <v>0.8147549999999999</v>
       </c>
       <c r="W4">
-        <v>4591.732683522236</v>
+        <v>0.8131289328454201</v>
       </c>
       <c r="X4">
-        <v>4241.455000000001</v>
+        <v>0.80217</v>
       </c>
       <c r="Y4">
-        <v>0.04791253883053175</v>
+        <v>0.001822131270153528</v>
       </c>
       <c r="Z4">
-        <v>1.496010856324058</v>
+        <v>0.1560055744114043</v>
       </c>
       <c r="AA4">
-        <v>0.04791253883053175</v>
+        <v>0.001822131270153528</v>
       </c>
       <c r="AB4">
-        <v>0.4032080498354822</v>
+        <v>0.376935350791206</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3967919501645178</v>
+        <v>0.4230646492087941</v>
       </c>
       <c r="AE4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1193,52 +1205,52 @@
         <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.03202686573295373</v>
+        <v>0.01167991129181296</v>
       </c>
       <c r="AJ4">
-        <v>15611.89297039235</v>
+        <v>42808.54430379752</v>
       </c>
       <c r="AK4">
-        <v>11708.91972779426</v>
+        <v>32106.40822784814</v>
       </c>
       <c r="AL4">
-        <v>2.67217729005595</v>
+        <v>39556.9620253165</v>
       </c>
       <c r="AM4">
-        <v>117.0891972779426</v>
+        <v>321.0640822784814</v>
       </c>
       <c r="AN4">
-        <v>0.001170891972779426</v>
+        <v>0.003210640822784814</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ4">
-        <v>460.8636246013585</v>
+        <v>0.01807175545069581</v>
       </c>
       <c r="AR4">
-        <v>147.3079090225866</v>
+        <v>0.003512682333595981</v>
       </c>
       <c r="AS4">
-        <v>181.6655671993815</v>
+        <v>0.004015888786418348</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY4" s="2">
         <v>46274</v>
@@ -1261,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1270,7 +1282,7 @@
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J5" s="2">
         <v>46245</v>
@@ -1279,64 +1291,64 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.8499218835129919</v>
+        <v>0.01736807487827153</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0.706375</v>
+        <v>4.76282</v>
       </c>
       <c r="S5">
-        <v>0.7114993023291268</v>
+        <v>4.75729501047601</v>
       </c>
       <c r="T5">
-        <v>0.7080913845611428</v>
+        <v>4.716430881642689</v>
       </c>
       <c r="U5">
-        <v>0.706375</v>
+        <v>4.76282</v>
       </c>
       <c r="V5">
-        <v>0.7160549999999999</v>
+        <v>4.794529999999999</v>
       </c>
       <c r="W5">
-        <v>0.7114993023291268</v>
+        <v>4.75567577</v>
       </c>
       <c r="X5">
-        <v>0.6986749999999999</v>
+        <v>4.797667499999999</v>
       </c>
       <c r="Y5">
-        <v>0.007254365357107573</v>
+        <v>-0.001160024843262873</v>
       </c>
       <c r="Z5">
-        <v>0.6654938089775086</v>
+        <v>0.2050141330081072</v>
       </c>
       <c r="AA5">
-        <v>0.007254365357107573</v>
+        <v>0.001160024843262873</v>
       </c>
       <c r="AB5">
-        <v>0.3289583344382415</v>
+        <v>0.3955613094459282</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4710416655617585</v>
+        <v>0.4044386905540719</v>
       </c>
       <c r="AE5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1345,55 +1357,55 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI5">
-        <v>0.01090072553530358</v>
+        <v>0.007316568755485179</v>
       </c>
       <c r="AJ5">
-        <v>45868.50649350609</v>
+        <v>68338.04433603573</v>
       </c>
       <c r="AK5">
-        <v>34401.37987012957</v>
+        <v>68338.04433603573</v>
       </c>
       <c r="AL5">
-        <v>48701.29870129828</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM5">
-        <v>344.0137987012957</v>
+        <v>683.3804433603573</v>
       </c>
       <c r="AN5">
-        <v>0.003440137987012957</v>
+        <v>0.006833804433603573</v>
       </c>
       <c r="AO5">
-        <v>375</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.00375</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.01689948069267504</v>
+        <v>0.04288425659186296</v>
       </c>
       <c r="AR5">
-        <v>0.002314413550359111</v>
+        <v>0.01466044020744179</v>
       </c>
       <c r="AS5">
-        <v>0.00458522918392031</v>
+        <v>0.01541472403652306</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY5" s="2">
         <v>46274</v>
@@ -1416,7 +1428,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1425,7 +1437,7 @@
         <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J6" s="2">
         <v>46245</v>
@@ -1434,31 +1446,31 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.308563355560978</v>
+        <v>1.108618118011758</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6" t="s">
+        <v>70</v>
+      </c>
+      <c r="P6" t="s">
         <v>72</v>
       </c>
-      <c r="P6" t="s">
-        <v>75</v>
-      </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
         <v>159.3545</v>
       </c>
       <c r="S6">
-        <v>160.4766960577176</v>
+        <v>158.9298466298336</v>
       </c>
       <c r="T6">
-        <v>163.3122506912334</v>
+        <v>160.6009493766517</v>
       </c>
       <c r="U6">
         <v>159.3545</v>
@@ -1467,31 +1479,31 @@
         <v>156.265</v>
       </c>
       <c r="W6">
-        <v>160.4766960577176</v>
+        <v>158.9298466298336</v>
       </c>
       <c r="X6">
-        <v>157.8275</v>
+        <v>160.8815</v>
       </c>
       <c r="Y6">
-        <v>0.007042135978071634</v>
+        <v>-0.002664834505246905</v>
       </c>
       <c r="Z6">
-        <v>0.7349024608497741</v>
+        <v>0.2780965096046913</v>
       </c>
       <c r="AA6">
-        <v>0.007042135978071634</v>
+        <v>0.002664834505246905</v>
       </c>
       <c r="AB6">
-        <v>0.5099571755249422</v>
+        <v>0.472087299002165</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.2900428244750577</v>
+        <v>0.3279127009978351</v>
       </c>
       <c r="AE6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1500,7 +1512,7 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
         <v>0.009582409031436296</v>
@@ -1509,46 +1521,46 @@
         <v>52178.94564505514</v>
       </c>
       <c r="AK6">
-        <v>52178.94564505514</v>
+        <v>39134.20923379136</v>
       </c>
       <c r="AL6">
-        <v>327.439423706611</v>
+        <v>245.5795677799582</v>
       </c>
       <c r="AM6">
-        <v>521.7894564505515</v>
+        <v>391.3420923379136</v>
       </c>
       <c r="AN6">
-        <v>0.005217894564505515</v>
+        <v>0.003913420923379136</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>4.222520110880288</v>
+        <v>3.722933668067075</v>
       </c>
       <c r="AR6">
-        <v>2.395596871560259</v>
+        <v>1.766595886973183</v>
       </c>
       <c r="AS6">
-        <v>4.105995184969433</v>
+        <v>3.599281919250205</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW6" t="s">
         <v>67</v>
       </c>
       <c r="AX6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY6" s="2">
         <v>46274</v>
@@ -1571,16 +1583,16 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
         <v>68</v>
-      </c>
-      <c r="H7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" t="s">
-        <v>69</v>
       </c>
       <c r="J7" s="2">
         <v>46245</v>
@@ -1589,64 +1601,64 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1.04152115130347</v>
+        <v>0.05761258491225919</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>0.81165</v>
+        <v>7.7851</v>
       </c>
       <c r="S7">
-        <v>0.8071390412476787</v>
+        <v>7.745724668353049</v>
       </c>
       <c r="T7">
-        <v>0.7990689279494918</v>
+        <v>7.661881847682553</v>
       </c>
       <c r="U7">
-        <v>0.81165</v>
+        <v>7.7851</v>
       </c>
       <c r="V7">
-        <v>0.8147549999999999</v>
+        <v>7.8167</v>
       </c>
       <c r="W7">
-        <v>0.8071390412476787</v>
+        <v>7.745724668353049</v>
       </c>
       <c r="X7">
-        <v>0.8211299999999999</v>
+        <v>7.848025</v>
       </c>
       <c r="Y7">
-        <v>-0.005557763509297512</v>
+        <v>-0.005057781100685991</v>
       </c>
       <c r="Z7">
-        <v>0.4758395308355834</v>
+        <v>0.6257502049574959</v>
       </c>
       <c r="AA7">
-        <v>0.005557763509297512</v>
+        <v>0.005057781100685991</v>
       </c>
       <c r="AB7">
-        <v>0.445934376037415</v>
+        <v>0.4176211295583598</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.354065623962585</v>
+        <v>0.3823788704416402</v>
       </c>
       <c r="AE7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1658,52 +1670,52 @@
         <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01167991129181296</v>
+        <v>0.008082747813130226</v>
       </c>
       <c r="AJ7">
-        <v>42808.54430379752</v>
+        <v>61860.15097338089</v>
       </c>
       <c r="AK7">
-        <v>42808.54430379752</v>
+        <v>61860.15097338089</v>
       </c>
       <c r="AL7">
-        <v>52742.61603375534</v>
+        <v>7945.967421533557</v>
       </c>
       <c r="AM7">
-        <v>428.0854430379752</v>
+        <v>618.6015097338089</v>
       </c>
       <c r="AN7">
-        <v>0.004280854430379752</v>
+        <v>0.006186015097338089</v>
       </c>
       <c r="AO7">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.01942056402251046</v>
+        <v>0.09418453126639507</v>
       </c>
       <c r="AR7">
-        <v>0.003664613049754937</v>
+        <v>0.02264209375019527</v>
       </c>
       <c r="AS7">
-        <v>0.005218673660268351</v>
+        <v>0.03815237404529243</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY7" s="2">
         <v>46274</v>
@@ -1726,13 +1738,13 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
@@ -1741,67 +1753,67 @@
         <v>46245</v>
       </c>
       <c r="K8">
-        <v>0.435624528851162</v>
+        <v>0.3266418956129878</v>
       </c>
       <c r="L8">
-        <v>1.301850308907033</v>
+        <v>2.727441907511101</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="O8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P8" t="s">
         <v>72</v>
       </c>
-      <c r="P8" t="s">
-        <v>75</v>
-      </c>
       <c r="Q8">
-        <v>0.6732816033616285</v>
+        <v>0.8316604739032469</v>
       </c>
       <c r="R8">
-        <v>1.3505</v>
+        <v>6.7475</v>
       </c>
       <c r="S8">
-        <v>1.340729930147171</v>
+        <v>6.706425892985083</v>
       </c>
       <c r="T8">
-        <v>1.311487950013936</v>
+        <v>6.675239756782378</v>
       </c>
       <c r="U8">
-        <v>1.3505</v>
+        <v>6.7475</v>
       </c>
       <c r="V8">
-        <v>1.357105</v>
+        <v>6.717879999999999</v>
       </c>
       <c r="W8">
-        <v>1.340729930147171</v>
+        <v>6.706425892985083</v>
       </c>
       <c r="X8">
-        <v>1.36465625</v>
+        <v>6.775425</v>
       </c>
       <c r="Y8">
-        <v>-0.007234409368995697</v>
+        <v>-0.00608730744941341</v>
       </c>
       <c r="Z8">
-        <v>0.690159459802469</v>
+        <v>1.470872229719476</v>
       </c>
       <c r="AA8">
-        <v>0.007234409368995697</v>
+        <v>0.00608730744941341</v>
       </c>
       <c r="AB8">
-        <v>0.3431663733404539</v>
+        <v>0.4075517798110165</v>
       </c>
       <c r="AC8">
-        <v>0.1091343295413683</v>
+        <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.5476992971181778</v>
+        <v>0.3924482201889836</v>
       </c>
       <c r="AE8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1810,55 +1822,55 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>336.6408016808142</v>
+        <v>415.8302369516235</v>
       </c>
       <c r="AI8">
-        <v>0.0104822288041466</v>
+        <v>0.004138569840681797</v>
       </c>
       <c r="AJ8">
-        <v>47699.77924944819</v>
+        <v>120814.6821844207</v>
       </c>
       <c r="AK8">
-        <v>32115.38385306421</v>
+        <v>100476.7958399655</v>
       </c>
       <c r="AL8">
-        <v>23780.36568164696</v>
+        <v>14890.96640829426</v>
       </c>
       <c r="AM8">
-        <v>321.1538385306421</v>
+        <v>1004.767958399655</v>
       </c>
       <c r="AN8">
-        <v>0.003211538385306421</v>
+        <v>0.01004767958399655</v>
       </c>
       <c r="AO8">
-        <v>336.6408016808143</v>
+        <v>415.8302369516234</v>
       </c>
       <c r="AP8">
-        <v>0.003366408016808143</v>
+        <v>0.004158302369516234</v>
       </c>
       <c r="AQ8">
-        <v>0.01932505943579866</v>
+        <v>0.07680050184957016</v>
       </c>
       <c r="AR8">
-        <v>0.005816869159762649</v>
+        <v>0.007208658968011613</v>
       </c>
       <c r="AS8">
-        <v>0.005226354987435744</v>
+        <v>0.01625931445992543</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV8" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY8" s="2">
         <v>46274</v>
@@ -1881,16 +1893,16 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" t="s">
         <v>68</v>
-      </c>
-      <c r="H9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" t="s">
-        <v>69</v>
       </c>
       <c r="J9" s="2">
         <v>46245</v>
@@ -1899,64 +1911,64 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.7870207281778198</v>
+        <v>0.1432801373781929</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
       <c r="R9">
-        <v>1.153925</v>
+        <v>9.11007</v>
       </c>
       <c r="S9">
-        <v>1.143273518953264</v>
+        <v>9.053749977083026</v>
       </c>
       <c r="T9">
-        <v>1.118068209239886</v>
+        <v>8.968972945723523</v>
       </c>
       <c r="U9">
-        <v>1.153925</v>
+        <v>9.11007</v>
       </c>
       <c r="V9">
-        <v>1.164805</v>
+        <v>9.101560000000001</v>
       </c>
       <c r="W9">
-        <v>1.143273518953264</v>
+        <v>9.053749977083026</v>
       </c>
       <c r="X9">
-        <v>1.166925</v>
+        <v>9.1979025</v>
       </c>
       <c r="Y9">
-        <v>-0.009230652812562311</v>
+        <v>-0.006182172356192045</v>
       </c>
       <c r="Z9">
-        <v>0.8193446959027659</v>
+        <v>0.6412207658551746</v>
       </c>
       <c r="AA9">
-        <v>0.009230652812562311</v>
+        <v>0.006182172356192045</v>
       </c>
       <c r="AB9">
-        <v>0.4141379998913899</v>
+        <v>0.3734302959452581</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3858620001086101</v>
+        <v>0.4265697040547419</v>
       </c>
       <c r="AE9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1968,52 +1980,52 @@
         <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.01126589683038327</v>
+        <v>0.009641254128672968</v>
       </c>
       <c r="AJ9">
-        <v>44381.73076923073</v>
+        <v>51860.47305951684</v>
       </c>
       <c r="AK9">
-        <v>44381.73076923073</v>
+        <v>51860.47305951684</v>
       </c>
       <c r="AL9">
-        <v>38461.53846153842</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM9">
-        <v>443.8173076923073</v>
+        <v>518.6047305951685</v>
       </c>
       <c r="AN9">
-        <v>0.004438173076923073</v>
+        <v>0.005186047305951685</v>
       </c>
       <c r="AO9">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.01810490269536492</v>
+        <v>0.1005578380973482</v>
       </c>
       <c r="AR9">
-        <v>0.006120307498601138</v>
+        <v>0.0218498315632536</v>
       </c>
       <c r="AS9">
-        <v>0.008985542307457588</v>
+        <v>0.02265715786483689</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY9" s="2">
         <v>46274</v>
@@ -2036,82 +2048,82 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
         <v>68</v>
-      </c>
-      <c r="H10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>69</v>
       </c>
       <c r="J10" s="2">
         <v>46245</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.4164713617588751</v>
       </c>
       <c r="L10">
-        <v>0.1432801373781929</v>
+        <v>1.290055274739505</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.6876464786808437</v>
       </c>
       <c r="R10">
-        <v>9.11007</v>
+        <v>1.3505</v>
       </c>
       <c r="S10">
-        <v>9.002973836569677</v>
+        <v>1.341823568366699</v>
       </c>
       <c r="T10">
-        <v>8.878530387622934</v>
+        <v>1.321785071496781</v>
       </c>
       <c r="U10">
-        <v>9.11007</v>
+        <v>1.3505</v>
       </c>
       <c r="V10">
-        <v>9.101560000000001</v>
+        <v>1.357105</v>
       </c>
       <c r="W10">
-        <v>9.002973836569677</v>
+        <v>1.341823568366699</v>
       </c>
       <c r="X10">
-        <v>9.1979025</v>
+        <v>1.36465625</v>
       </c>
       <c r="Y10">
-        <v>-0.01175580027709159</v>
+        <v>-0.006424606910996509</v>
       </c>
       <c r="Z10">
-        <v>1.219322727126338</v>
+        <v>0.6129046628380254</v>
       </c>
       <c r="AA10">
-        <v>0.01175580027709159</v>
+        <v>0.006424606910996509</v>
       </c>
       <c r="AB10">
-        <v>0.4493799958755037</v>
+        <v>0.3952565088581216</v>
       </c>
       <c r="AC10">
-        <v>0.1925831797646148</v>
+        <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3580368243598816</v>
+        <v>0.4047434911418784</v>
       </c>
       <c r="AE10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2120,55 +2132,55 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>343.8232393404219</v>
       </c>
       <c r="AI10">
-        <v>0.009641254128672968</v>
+        <v>0.0104822288041466</v>
       </c>
       <c r="AJ10">
-        <v>51860.47305951684</v>
+        <v>47699.77924944819</v>
       </c>
       <c r="AK10">
-        <v>51860.47305951684</v>
+        <v>32800.58523473662</v>
       </c>
       <c r="AL10">
-        <v>5692.653630489869</v>
+        <v>24287.7343463433</v>
       </c>
       <c r="AM10">
-        <v>518.6047305951685</v>
+        <v>328.0058523473662</v>
       </c>
       <c r="AN10">
-        <v>0.005186047305951685</v>
+        <v>0.003280058523473662</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>343.8232393404218</v>
       </c>
       <c r="AP10">
-        <v>0.005</v>
+        <v>0.003438232393404218</v>
       </c>
       <c r="AQ10">
-        <v>0.09122487584793544</v>
+        <v>0.02017903406063495</v>
       </c>
       <c r="AR10">
-        <v>0.03272560384090063</v>
+        <v>0.003772809752475961</v>
       </c>
       <c r="AS10">
-        <v>0.02707108109465816</v>
+        <v>0.005516952866430391</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY10" s="2">
         <v>46274</v>
@@ -2194,13 +2206,13 @@
         <v>63</v>
       </c>
       <c r="G11" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>69</v>
       </c>
       <c r="J11" s="2">
         <v>46245</v>
@@ -2209,64 +2221,64 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.05761258491225919</v>
+        <v>0.7880600803059172</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>7.7851</v>
+        <v>1.153925</v>
       </c>
       <c r="S11">
-        <v>7.684364014156218</v>
+        <v>1.142638646840161</v>
       </c>
       <c r="T11">
-        <v>7.580984448598004</v>
+        <v>1.118113895409617</v>
       </c>
       <c r="U11">
-        <v>7.7851</v>
+        <v>1.153925</v>
       </c>
       <c r="V11">
-        <v>7.8167</v>
+        <v>1.164805</v>
       </c>
       <c r="W11">
-        <v>7.684364014156218</v>
+        <v>1.142638646840161</v>
       </c>
       <c r="X11">
-        <v>7.852257323895855</v>
+        <v>1.166925</v>
       </c>
       <c r="Y11">
-        <v>-0.01293958791072458</v>
+        <v>-0.009780837714617069</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.8681810122953455</v>
       </c>
       <c r="AA11">
-        <v>0.01293958791072458</v>
+        <v>0.009780837714617069</v>
       </c>
       <c r="AB11">
-        <v>0.534610402641066</v>
+        <v>0.428140506317276</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.265389597358934</v>
+        <v>0.371859493682724</v>
       </c>
       <c r="AE11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2278,52 +2290,52 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.008626391940483057</v>
+        <v>0.01126589683038327</v>
       </c>
       <c r="AJ11">
-        <v>57961.66038474728</v>
+        <v>44381.73076923073</v>
       </c>
       <c r="AK11">
-        <v>57961.66038474728</v>
+        <v>44381.73076923073</v>
       </c>
       <c r="AL11">
-        <v>7445.204349943775</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM11">
-        <v>579.6166038474728</v>
+        <v>443.8173076923073</v>
       </c>
       <c r="AN11">
-        <v>0.005796166038474728</v>
+        <v>0.004438173076923073</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>499.9999999999999</v>
       </c>
       <c r="AP11">
-        <v>0.005</v>
+        <v>0.004999999999999999</v>
       </c>
       <c r="AQ11">
-        <v>0.07179219655383269</v>
+        <v>0.01679055826888859</v>
       </c>
       <c r="AR11">
-        <v>0.03452680272725898</v>
+        <v>0.004057330514929258</v>
       </c>
       <c r="AS11">
-        <v>0.05533514724125275</v>
+        <v>0.007749592373065482</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03274170376133356</v>
+        <v>0.04733090460080475</v>
       </c>
       <c r="AV11" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AW11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX11" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="AY11" s="2">
         <v>46274</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -175,30 +175,30 @@
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -238,34 +238,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=352.5,naive=142.5,drift4=183.7; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01525,naive=0.001661,drift4=0.004667; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.01807,naive=0.003513,drift4=0.004016; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.04288,naive=0.01466,drift4=0.01541; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.723,naive=1.767,drift4=3.599; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09418,naive=0.02264,drift4=0.03815; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0768,naive=0.007209,drift4=0.01626; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.1006,naive=0.02185,drift4=0.02266; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.02018,naive=0.003773,drift4=0.005517; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01679,naive=0.004057,drift4=0.00775; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1243,naive=453.3,drift4=506.5; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04917,naive=0.007607,drift4=0.004934; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.612,naive=5.291,drift4=7.626; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.12,drift4=0.59); metric_best=drift4; scores=model=0.1644,naive=0.04525,drift4=0.004853</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.14,drift4=0.57); metric_best=drift4; scores=model=0.1072,naive=0.03473,drift4=0.004968</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02159,naive=0.003739,drift4=0.01183; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.10,drift4=0.59); metric_best=drift4; scores=model=0.01067,naive=0.0187,drift4=0.0008683</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.025,naive=0.01667,drift4=0.01445; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.08074,naive=0.1016,drift4=0.05368</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.55,naive=0.20,drift4=0.25); metric_best=model; scores=model=0.05159,naive=0.09443,drift4=0.1541; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -796,7 +796,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -820,19 +820,19 @@
         <v>68</v>
       </c>
       <c r="J2" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.5282068048872706</v>
+        <v>0.9067916516445035</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="s">
         <v>70</v>
@@ -844,43 +844,43 @@
         <v>0.75</v>
       </c>
       <c r="R2">
-        <v>4381.79</v>
+        <v>4414.99</v>
       </c>
       <c r="S2">
-        <v>4691.850842245356</v>
+        <v>4650.048413108458</v>
       </c>
       <c r="T2">
-        <v>4764.109304701087</v>
+        <v>4578.830891516764</v>
       </c>
       <c r="U2">
-        <v>4381.79</v>
+        <v>4414.99</v>
       </c>
       <c r="V2">
-        <v>4775.26</v>
+        <v>4841.66</v>
       </c>
       <c r="W2">
-        <v>4691.850842245356</v>
+        <v>4650.048413108458</v>
       </c>
       <c r="X2">
-        <v>4175.082771836429</v>
+        <v>4258.284391261028</v>
       </c>
       <c r="Y2">
-        <v>0.07076122822986863</v>
+        <v>0.05324098426235573</v>
       </c>
       <c r="Z2">
         <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>0.07076122822986863</v>
+        <v>0.05324098426235573</v>
       </c>
       <c r="AB2">
-        <v>0.4228577347194193</v>
+        <v>0.404360032664802</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3771422652805807</v>
+        <v>0.395639967335198</v>
       </c>
       <c r="AE2" t="s">
         <v>74</v>
@@ -895,43 +895,43 @@
         <v>375</v>
       </c>
       <c r="AI2">
-        <v>0.04717415215324575</v>
+        <v>0.03549398950823715</v>
       </c>
       <c r="AJ2">
-        <v>10599.02461788279</v>
+        <v>14086.89208870038</v>
       </c>
       <c r="AK2">
-        <v>7949.268463412089</v>
+        <v>10565.16906652528</v>
       </c>
       <c r="AL2">
-        <v>1.814160072347623</v>
+        <v>2.393022196318742</v>
       </c>
       <c r="AM2">
-        <v>79.49268463412089</v>
+        <v>105.6516906652528</v>
       </c>
       <c r="AN2">
-        <v>0.0007949268463412089</v>
+        <v>0.001056516906652528</v>
       </c>
       <c r="AO2">
-        <v>374.9999999999999</v>
+        <v>375</v>
       </c>
       <c r="AP2">
-        <v>0.003749999999999999</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ2">
-        <v>352.5109485135201</v>
+        <v>464.305599110801</v>
       </c>
       <c r="AR2">
-        <v>142.5293683023909</v>
+        <v>158.6503398333342</v>
       </c>
       <c r="AS2">
-        <v>183.65683475101</v>
+        <v>191.4882903559876</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV2" t="s">
         <v>84</v>
@@ -943,7 +943,7 @@
         <v>85</v>
       </c>
       <c r="AY2" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -975,19 +975,19 @@
         <v>68</v>
       </c>
       <c r="J3" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.8430004673568237</v>
+        <v>0.9434522607322694</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O3" t="s">
         <v>70</v>
@@ -999,43 +999,43 @@
         <v>0.75</v>
       </c>
       <c r="R3">
-        <v>0.706375</v>
+        <v>0.70638</v>
       </c>
       <c r="S3">
-        <v>0.7100411976859821</v>
+        <v>0.7114912815908195</v>
       </c>
       <c r="T3">
-        <v>0.7065250317093117</v>
+        <v>0.7080382067801637</v>
       </c>
       <c r="U3">
-        <v>0.706375</v>
+        <v>0.70638</v>
       </c>
       <c r="V3">
-        <v>0.7160549999999999</v>
+        <v>0.716065</v>
       </c>
       <c r="W3">
-        <v>0.7100411976859821</v>
+        <v>0.7114912815908195</v>
       </c>
       <c r="X3">
-        <v>0.6986749999999999</v>
+        <v>0.69868</v>
       </c>
       <c r="Y3">
-        <v>0.005190157757539673</v>
+        <v>0.0072358809575859</v>
       </c>
       <c r="Z3">
-        <v>0.476129569608059</v>
+        <v>0.6638028040025302</v>
       </c>
       <c r="AA3">
-        <v>0.005190157757539673</v>
+        <v>0.0072358809575859</v>
       </c>
       <c r="AB3">
-        <v>0.4278925374811863</v>
+        <v>0.3284896392577361</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3721074625188138</v>
+        <v>0.4715103607422639</v>
       </c>
       <c r="AE3" t="s">
         <v>75</v>
@@ -1050,22 +1050,22 @@
         <v>375</v>
       </c>
       <c r="AI3">
-        <v>0.01090072553530358</v>
+        <v>0.01090064837622819</v>
       </c>
       <c r="AJ3">
-        <v>45868.50649350609</v>
+        <v>45868.83116883077</v>
       </c>
       <c r="AK3">
-        <v>34401.37987012957</v>
+        <v>34401.62337662307</v>
       </c>
       <c r="AL3">
-        <v>48701.29870129828</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM3">
-        <v>344.0137987012957</v>
+        <v>344.0162337662307</v>
       </c>
       <c r="AN3">
-        <v>0.003440137987012957</v>
+        <v>0.003440162337662307</v>
       </c>
       <c r="AO3">
         <v>375</v>
@@ -1074,19 +1074,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ3">
-        <v>0.01524844087415154</v>
+        <v>0.01587465646686066</v>
       </c>
       <c r="AR3">
-        <v>0.001660957664820482</v>
+        <v>0.002049916598005805</v>
       </c>
       <c r="AS3">
-        <v>0.004666961785771238</v>
+        <v>0.00464003341094562</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV3" t="s">
         <v>84</v>
@@ -1098,7 +1098,7 @@
         <v>85</v>
       </c>
       <c r="AY3" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,7 +1118,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>66</v>
@@ -1127,70 +1127,70 @@
         <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.045407844964561</v>
+        <v>1.260122004711455</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>0.81165</v>
+        <v>159.3235</v>
       </c>
       <c r="S4">
-        <v>0.8131289328454201</v>
+        <v>160.357926392579</v>
       </c>
       <c r="T4">
-        <v>0.8120885821316038</v>
+        <v>163.1346889372769</v>
       </c>
       <c r="U4">
-        <v>0.81165</v>
+        <v>159.3235</v>
       </c>
       <c r="V4">
-        <v>0.8147549999999999</v>
+        <v>156.203</v>
       </c>
       <c r="W4">
-        <v>0.8131289328454201</v>
+        <v>160.357926392579</v>
       </c>
       <c r="X4">
-        <v>0.80217</v>
+        <v>157.81975</v>
       </c>
       <c r="Y4">
-        <v>0.001822131270153528</v>
+        <v>0.00649261654796082</v>
       </c>
       <c r="Z4">
-        <v>0.1560055744114043</v>
+        <v>0.687897850426619</v>
       </c>
       <c r="AA4">
-        <v>0.001822131270153528</v>
+        <v>0.00649261654796082</v>
       </c>
       <c r="AB4">
-        <v>0.376935350791206</v>
+        <v>0.5093746162773005</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4230646492087941</v>
+        <v>0.2906253837226995</v>
       </c>
       <c r="AE4" t="s">
         <v>76</v>
@@ -1202,46 +1202,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.01167991129181296</v>
+        <v>0.009438343998217531</v>
       </c>
       <c r="AJ4">
-        <v>42808.54430379752</v>
+        <v>52975.39484621741</v>
       </c>
       <c r="AK4">
-        <v>32106.40822784814</v>
+        <v>52975.39484621741</v>
       </c>
       <c r="AL4">
-        <v>39556.9620253165</v>
+        <v>332.502078137986</v>
       </c>
       <c r="AM4">
-        <v>321.0640822784814</v>
+        <v>529.7539484621741</v>
       </c>
       <c r="AN4">
-        <v>0.003210640822784814</v>
+        <v>0.005297539484621741</v>
       </c>
       <c r="AO4">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>0.01807175545069581</v>
+        <v>4.252864552580693</v>
       </c>
       <c r="AR4">
-        <v>0.003512682333595981</v>
+        <v>2.152318480942192</v>
       </c>
       <c r="AS4">
-        <v>0.004015888786418348</v>
+        <v>3.864898143295614</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV4" t="s">
         <v>84</v>
@@ -1253,7 +1253,7 @@
         <v>85</v>
       </c>
       <c r="AY4" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1276,76 +1276,76 @@
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
         <v>68</v>
       </c>
       <c r="J5" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0.01736807487827153</v>
+        <v>0.04026990801319719</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>4.76282</v>
+        <v>4.76275</v>
       </c>
       <c r="S5">
-        <v>4.75729501047601</v>
+        <v>4.767788442148096</v>
       </c>
       <c r="T5">
-        <v>4.716430881642689</v>
+        <v>4.715441345810354</v>
       </c>
       <c r="U5">
-        <v>4.76282</v>
+        <v>4.76275</v>
       </c>
       <c r="V5">
-        <v>4.794529999999999</v>
+        <v>4.794389999999999</v>
       </c>
       <c r="W5">
-        <v>4.75567577</v>
+        <v>4.769894125</v>
       </c>
       <c r="X5">
-        <v>4.797667499999999</v>
+        <v>4.7279025</v>
       </c>
       <c r="Y5">
-        <v>-0.001160024843262873</v>
+        <v>0.001057885076499224</v>
       </c>
       <c r="Z5">
-        <v>0.2050141330081072</v>
+        <v>0.2050111198794753</v>
       </c>
       <c r="AA5">
-        <v>0.001160024843262873</v>
+        <v>0.001057885076499224</v>
       </c>
       <c r="AB5">
-        <v>0.3955613094459282</v>
+        <v>0.2879855979739051</v>
       </c>
       <c r="AC5">
-        <v>0.2</v>
+        <v>0.1221707479728944</v>
       </c>
       <c r="AD5">
-        <v>0.4044386905540719</v>
+        <v>0.5898436540532004</v>
       </c>
       <c r="AE5" t="s">
         <v>77</v>
@@ -1357,58 +1357,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.007316568755485179</v>
+        <v>0.007316676289958517</v>
       </c>
       <c r="AJ5">
-        <v>68338.04433603573</v>
+        <v>68337.0399598251</v>
       </c>
       <c r="AK5">
-        <v>68338.04433603573</v>
+        <v>51252.77996986882</v>
       </c>
       <c r="AL5">
-        <v>14348.23158045774</v>
+        <v>10761.1736853433</v>
       </c>
       <c r="AM5">
-        <v>683.3804433603573</v>
+        <v>512.5277996986882</v>
       </c>
       <c r="AN5">
-        <v>0.006833804433603573</v>
+        <v>0.005125277996986882</v>
       </c>
       <c r="AO5">
-        <v>499.9999999999999</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>0.004999999999999999</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="AQ5">
-        <v>0.04288425659186296</v>
+        <v>0.04882094002351366</v>
       </c>
       <c r="AR5">
-        <v>0.01466044020744179</v>
+        <v>0.01499500873254836</v>
       </c>
       <c r="AS5">
-        <v>0.01541472403652306</v>
+        <v>0.01703313329349149</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV5" t="s">
         <v>84</v>
       </c>
       <c r="AW5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX5" t="s">
         <v>85</v>
       </c>
       <c r="AY5" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,7 +1428,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1440,19 +1440,19 @@
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.4174537540470262</v>
       </c>
       <c r="L6">
-        <v>1.108618118011758</v>
+        <v>2.837624712178707</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
@@ -1461,46 +1461,46 @@
         <v>72</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>0.8543634385117566</v>
       </c>
       <c r="R6">
-        <v>159.3545</v>
+        <v>6.74392</v>
       </c>
       <c r="S6">
-        <v>158.9298466298336</v>
+        <v>6.723993549396042</v>
       </c>
       <c r="T6">
-        <v>160.6009493766517</v>
+        <v>6.740559390730397</v>
       </c>
       <c r="U6">
-        <v>159.3545</v>
+        <v>6.74392</v>
       </c>
       <c r="V6">
-        <v>156.265</v>
+        <v>6.71072</v>
       </c>
       <c r="W6">
-        <v>158.9298466298336</v>
+        <v>6.723993549396042</v>
       </c>
       <c r="X6">
-        <v>160.8815</v>
+        <v>6.771845000000001</v>
       </c>
       <c r="Y6">
-        <v>-0.002664834505246905</v>
+        <v>-0.002954728200209741</v>
       </c>
       <c r="Z6">
-        <v>0.2780965096046913</v>
+        <v>0.7135702991569625</v>
       </c>
       <c r="AA6">
-        <v>0.002664834505246905</v>
+        <v>0.002954728200209741</v>
       </c>
       <c r="AB6">
-        <v>0.472087299002165</v>
+        <v>0.2944748704450007</v>
       </c>
       <c r="AC6">
-        <v>0.2</v>
+        <v>0.1351385143538878</v>
       </c>
       <c r="AD6">
-        <v>0.3279127009978351</v>
+        <v>0.5703866152011116</v>
       </c>
       <c r="AE6" t="s">
         <v>78</v>
@@ -1512,46 +1512,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>427.1817192558783</v>
       </c>
       <c r="AI6">
-        <v>0.009582409031436296</v>
+        <v>0.00414076679438671</v>
       </c>
       <c r="AJ6">
-        <v>52178.94564505514</v>
+        <v>120750.5819158442</v>
       </c>
       <c r="AK6">
-        <v>39134.20923379136</v>
+        <v>103164.8823679162</v>
       </c>
       <c r="AL6">
-        <v>245.5795677799582</v>
+        <v>15297.4653269784</v>
       </c>
       <c r="AM6">
-        <v>391.3420923379136</v>
+        <v>1031.648823679162</v>
       </c>
       <c r="AN6">
-        <v>0.003913420923379136</v>
+        <v>0.01031648823679162</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>427.1817192558783</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.004271817192558783</v>
       </c>
       <c r="AQ6">
-        <v>3.722933668067075</v>
+        <v>0.06591697664933356</v>
       </c>
       <c r="AR6">
-        <v>1.766595886973183</v>
+        <v>0.009399671781807296</v>
       </c>
       <c r="AS6">
-        <v>3.599281919250205</v>
+        <v>0.01482799723710954</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV6" t="s">
         <v>84</v>
@@ -1563,7 +1563,7 @@
         <v>85</v>
       </c>
       <c r="AY6" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1595,19 +1595,19 @@
         <v>68</v>
       </c>
       <c r="J7" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.05640024919461578</v>
       </c>
       <c r="L7">
-        <v>0.05761258491225919</v>
+        <v>1.115643117315203</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1616,46 +1616,46 @@
         <v>73</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.9576998131040382</v>
       </c>
       <c r="R7">
-        <v>7.7851</v>
+        <v>0.81314</v>
       </c>
       <c r="S7">
-        <v>7.745724668353049</v>
+        <v>0.8094576631845467</v>
       </c>
       <c r="T7">
-        <v>7.661881847682553</v>
+        <v>0.8014648969540474</v>
       </c>
       <c r="U7">
-        <v>7.7851</v>
+        <v>0.81314</v>
       </c>
       <c r="V7">
-        <v>7.8167</v>
+        <v>0.8177349999999999</v>
       </c>
       <c r="W7">
-        <v>7.745724668353049</v>
+        <v>0.8094576631845467</v>
       </c>
       <c r="X7">
-        <v>7.848025</v>
+        <v>0.8226199999999999</v>
       </c>
       <c r="Y7">
-        <v>-0.005057781100685991</v>
+        <v>-0.004528539753859444</v>
       </c>
       <c r="Z7">
-        <v>0.6257502049574959</v>
+        <v>0.3884321535288263</v>
       </c>
       <c r="AA7">
-        <v>0.005057781100685991</v>
+        <v>0.004528539753859444</v>
       </c>
       <c r="AB7">
-        <v>0.4176211295583598</v>
+        <v>0.4522612299793463</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3823788704416402</v>
+        <v>0.3477387700206537</v>
       </c>
       <c r="AE7" t="s">
         <v>79</v>
@@ -1667,46 +1667,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>478.8499065520191</v>
       </c>
       <c r="AI7">
-        <v>0.008082747813130226</v>
+        <v>0.01165850898984183</v>
       </c>
       <c r="AJ7">
-        <v>61860.15097338089</v>
+        <v>42887.13080168782</v>
       </c>
       <c r="AK7">
-        <v>61860.15097338089</v>
+        <v>41072.99715334486</v>
       </c>
       <c r="AL7">
-        <v>7945.967421533557</v>
+        <v>50511.59351814554</v>
       </c>
       <c r="AM7">
-        <v>618.6015097338089</v>
+        <v>410.7299715334486</v>
       </c>
       <c r="AN7">
-        <v>0.006186015097338089</v>
+        <v>0.004107299715334486</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>478.8499065520191</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.004788499065520191</v>
       </c>
       <c r="AQ7">
-        <v>0.09418453126639507</v>
+        <v>0.01897891879164112</v>
       </c>
       <c r="AR7">
-        <v>0.02264209375019527</v>
+        <v>0.003598849442314456</v>
       </c>
       <c r="AS7">
-        <v>0.03815237404529243</v>
+        <v>0.004478939955683554</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV7" t="s">
         <v>84</v>
@@ -1718,7 +1718,7 @@
         <v>85</v>
       </c>
       <c r="AY7" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -1747,70 +1747,70 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J8" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K8">
-        <v>0.3266418956129878</v>
+        <v>0.6399191648840915</v>
       </c>
       <c r="L8">
-        <v>2.727441907511101</v>
+        <v>1.427668953276874</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q8">
-        <v>0.8316604739032469</v>
+        <v>0.5200606263369314</v>
       </c>
       <c r="R8">
-        <v>6.7475</v>
+        <v>1.349795</v>
       </c>
       <c r="S8">
-        <v>6.706425892985083</v>
+        <v>1.341156868505101</v>
       </c>
       <c r="T8">
-        <v>6.675239756782378</v>
+        <v>1.310773211198031</v>
       </c>
       <c r="U8">
-        <v>6.7475</v>
+        <v>1.349795</v>
       </c>
       <c r="V8">
-        <v>6.717879999999999</v>
+        <v>1.355695</v>
       </c>
       <c r="W8">
-        <v>6.706425892985083</v>
+        <v>1.341156868505101</v>
       </c>
       <c r="X8">
-        <v>6.775425</v>
+        <v>1.36395125</v>
       </c>
       <c r="Y8">
-        <v>-0.00608730744941341</v>
+        <v>-0.006399587711392885</v>
       </c>
       <c r="Z8">
-        <v>1.470872229719476</v>
+        <v>0.6101991342975414</v>
       </c>
       <c r="AA8">
-        <v>0.00608730744941341</v>
+        <v>0.006399587711392885</v>
       </c>
       <c r="AB8">
-        <v>0.4075517798110165</v>
+        <v>0.311077562769337</v>
       </c>
       <c r="AC8">
-        <v>0.2</v>
+        <v>0.09558829138035646</v>
       </c>
       <c r="AD8">
-        <v>0.3924482201889836</v>
+        <v>0.5933341458503065</v>
       </c>
       <c r="AE8" t="s">
         <v>80</v>
@@ -1822,46 +1822,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>415.8302369516235</v>
+        <v>260.0303131684657</v>
       </c>
       <c r="AI8">
-        <v>0.004138569840681797</v>
+        <v>0.01048770368833784</v>
       </c>
       <c r="AJ8">
-        <v>120814.6821844207</v>
+        <v>47674.87858719653</v>
       </c>
       <c r="AK8">
-        <v>100476.7958399655</v>
+        <v>24793.82721859459</v>
       </c>
       <c r="AL8">
-        <v>14890.96640829426</v>
+        <v>18368.58724368855</v>
       </c>
       <c r="AM8">
-        <v>1004.767958399655</v>
+        <v>247.9382721859459</v>
       </c>
       <c r="AN8">
-        <v>0.01004767958399655</v>
+        <v>0.002479382721859459</v>
       </c>
       <c r="AO8">
-        <v>415.8302369516234</v>
+        <v>260.0303131684657</v>
       </c>
       <c r="AP8">
-        <v>0.004158302369516234</v>
+        <v>0.002600303131684657</v>
       </c>
       <c r="AQ8">
-        <v>0.07680050184957016</v>
+        <v>0.01991828598504594</v>
       </c>
       <c r="AR8">
-        <v>0.007208658968011613</v>
+        <v>0.004959114959871894</v>
       </c>
       <c r="AS8">
-        <v>0.01625931445992543</v>
+        <v>0.005530499807512544</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV8" t="s">
         <v>84</v>
@@ -1873,7 +1873,7 @@
         <v>85</v>
       </c>
       <c r="AY8" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,7 +1893,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
@@ -1905,19 +1905,19 @@
         <v>68</v>
       </c>
       <c r="J9" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.1432801373781929</v>
+        <v>0.7956531118044045</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
@@ -1929,43 +1929,43 @@
         <v>1</v>
       </c>
       <c r="R9">
-        <v>9.11007</v>
+        <v>1.152885</v>
       </c>
       <c r="S9">
-        <v>9.053749977083026</v>
+        <v>1.141031623345084</v>
       </c>
       <c r="T9">
-        <v>8.968972945723523</v>
+        <v>1.115838092717521</v>
       </c>
       <c r="U9">
-        <v>9.11007</v>
+        <v>1.152885</v>
       </c>
       <c r="V9">
-        <v>9.101560000000001</v>
+        <v>1.162725</v>
       </c>
       <c r="W9">
-        <v>9.053749977083026</v>
+        <v>1.141031623345084</v>
       </c>
       <c r="X9">
-        <v>9.1979025</v>
+        <v>1.165885</v>
       </c>
       <c r="Y9">
-        <v>-0.006182172356192045</v>
+        <v>-0.01028149091619356</v>
       </c>
       <c r="Z9">
-        <v>0.6412207658551746</v>
+        <v>0.9117982042242926</v>
       </c>
       <c r="AA9">
-        <v>0.006182172356192045</v>
+        <v>0.01028149091619356</v>
       </c>
       <c r="AB9">
-        <v>0.3734302959452581</v>
+        <v>0.4207011679417561</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4265697040547419</v>
+        <v>0.3792988320582439</v>
       </c>
       <c r="AE9" t="s">
         <v>81</v>
@@ -1980,43 +1980,43 @@
         <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.009641254128672968</v>
+        <v>0.01127605962433375</v>
       </c>
       <c r="AJ9">
-        <v>51860.47305951684</v>
+        <v>44341.73076923073</v>
       </c>
       <c r="AK9">
-        <v>51860.47305951684</v>
+        <v>44341.73076923073</v>
       </c>
       <c r="AL9">
-        <v>5692.653630489869</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM9">
-        <v>518.6047305951685</v>
+        <v>443.4173076923073</v>
       </c>
       <c r="AN9">
-        <v>0.005186047305951685</v>
+        <v>0.004434173076923073</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP9">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ9">
-        <v>0.1005578380973482</v>
+        <v>0.01755472213306943</v>
       </c>
       <c r="AR9">
-        <v>0.0218498315632536</v>
+        <v>0.005459235683157841</v>
       </c>
       <c r="AS9">
-        <v>0.02265715786483689</v>
+        <v>0.008940364715777596</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV9" t="s">
         <v>84</v>
@@ -2028,7 +2028,7 @@
         <v>85</v>
       </c>
       <c r="AY9" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2060,19 +2060,19 @@
         <v>68</v>
       </c>
       <c r="J10" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K10">
-        <v>0.4164713617588751</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1.290055274739505</v>
+        <v>0.1693278678201049</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
@@ -2081,46 +2081,46 @@
         <v>73</v>
       </c>
       <c r="Q10">
-        <v>0.6876464786808437</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>1.3505</v>
+        <v>9.101839999999999</v>
       </c>
       <c r="S10">
-        <v>1.341823568366699</v>
+        <v>8.992911676451566</v>
       </c>
       <c r="T10">
-        <v>1.321785071496781</v>
+        <v>8.861321971355714</v>
       </c>
       <c r="U10">
-        <v>1.3505</v>
+        <v>9.101839999999999</v>
       </c>
       <c r="V10">
-        <v>1.357105</v>
+        <v>9.085099999999999</v>
       </c>
       <c r="W10">
-        <v>1.341823568366699</v>
+        <v>8.992911676451566</v>
       </c>
       <c r="X10">
-        <v>1.36465625</v>
+        <v>9.189672499999999</v>
       </c>
       <c r="Y10">
-        <v>-0.006424606910996509</v>
+        <v>-0.01196772559706972</v>
       </c>
       <c r="Z10">
-        <v>0.6129046628380254</v>
+        <v>1.240182433022325</v>
       </c>
       <c r="AA10">
-        <v>0.006424606910996509</v>
+        <v>0.01196772559706972</v>
       </c>
       <c r="AB10">
-        <v>0.3952565088581216</v>
+        <v>0.4265831460123769</v>
       </c>
       <c r="AC10">
-        <v>0.2</v>
+        <v>0.1954367932553547</v>
       </c>
       <c r="AD10">
-        <v>0.4047434911418784</v>
+        <v>0.3779800607322683</v>
       </c>
       <c r="AE10" t="s">
         <v>82</v>
@@ -2132,46 +2132,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>343.8232393404219</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.0104822288041466</v>
+        <v>0.009649971873818894</v>
       </c>
       <c r="AJ10">
-        <v>47699.77924944819</v>
+        <v>51813.6225201379</v>
       </c>
       <c r="AK10">
-        <v>32800.58523473662</v>
+        <v>51813.6225201379</v>
       </c>
       <c r="AL10">
-        <v>24287.7343463433</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM10">
-        <v>328.0058523473662</v>
+        <v>518.136225201379</v>
       </c>
       <c r="AN10">
-        <v>0.003280058523473662</v>
+        <v>0.00518136225201379</v>
       </c>
       <c r="AO10">
-        <v>343.8232393404218</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>0.003438232393404218</v>
+        <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.02017903406063495</v>
+        <v>0.09310285597967589</v>
       </c>
       <c r="AR10">
-        <v>0.003772809752475961</v>
+        <v>0.02690906334324671</v>
       </c>
       <c r="AS10">
-        <v>0.005516952866430391</v>
+        <v>0.02486196289279105</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV10" t="s">
         <v>84</v>
@@ -2183,7 +2183,7 @@
         <v>85</v>
       </c>
       <c r="AY10" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,7 +2203,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
         <v>67</v>
@@ -2215,19 +2215,19 @@
         <v>68</v>
       </c>
       <c r="J11" s="2">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.7880600803059172</v>
+        <v>0.1041141052377663</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
@@ -2239,43 +2239,43 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1.153925</v>
+        <v>7.7742</v>
       </c>
       <c r="S11">
-        <v>1.142638646840161</v>
+        <v>7.659342957433165</v>
       </c>
       <c r="T11">
-        <v>1.118113895409617</v>
+        <v>7.558039336754147</v>
       </c>
       <c r="U11">
-        <v>1.153925</v>
+        <v>7.7742</v>
       </c>
       <c r="V11">
-        <v>1.164805</v>
+        <v>7.794900000000001</v>
       </c>
       <c r="W11">
-        <v>1.142638646840161</v>
+        <v>7.659342957433165</v>
       </c>
       <c r="X11">
-        <v>1.166925</v>
+        <v>7.850771361711224</v>
       </c>
       <c r="Y11">
-        <v>-0.009780837714617069</v>
+        <v>-0.0147741301441737</v>
       </c>
       <c r="Z11">
-        <v>0.8681810122953455</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>0.009780837714617069</v>
+        <v>0.0147741301441737</v>
       </c>
       <c r="AB11">
-        <v>0.428140506317276</v>
+        <v>0.5548284834043099</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.371859493682724</v>
+        <v>0.2451715165956901</v>
       </c>
       <c r="AE11" t="s">
         <v>83</v>
@@ -2290,43 +2290,43 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.01126589683038327</v>
+        <v>0.009849420096115797</v>
       </c>
       <c r="AJ11">
-        <v>44381.73076923073</v>
+        <v>50764.40999782101</v>
       </c>
       <c r="AK11">
-        <v>44381.73076923073</v>
+        <v>50764.40999782101</v>
       </c>
       <c r="AL11">
-        <v>38461.53846153842</v>
+        <v>6529.856447971625</v>
       </c>
       <c r="AM11">
-        <v>443.8173076923073</v>
+        <v>507.6440999782101</v>
       </c>
       <c r="AN11">
-        <v>0.004438173076923073</v>
+        <v>0.005076440999782101</v>
       </c>
       <c r="AO11">
-        <v>499.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>0.004999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.01679055826888859</v>
+        <v>0.07524244747300136</v>
       </c>
       <c r="AR11">
-        <v>0.004057330514929258</v>
+        <v>0.03062996388641314</v>
       </c>
       <c r="AS11">
-        <v>0.007749592373065482</v>
+        <v>0.05161681615211205</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04733090460080475</v>
+        <v>0.04651464372862798</v>
       </c>
       <c r="AV11" t="s">
         <v>84</v>
@@ -2338,7 +2338,7 @@
         <v>85</v>
       </c>
       <c r="AY11" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -175,30 +175,30 @@
     <t>AUDUSD</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>AUDCNH</t>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -238,34 +238,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=1243,naive=453.3,drift4=506.5; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04917,naive=0.007607,drift4=0.004934; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=model; scores=model=4.612,naive=5.291,drift4=7.626; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.12,drift4=0.59); metric_best=drift4; scores=model=0.1644,naive=0.04525,drift4=0.004853</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.14,drift4=0.57); metric_best=drift4; scores=model=0.1072,naive=0.03473,drift4=0.004968</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02159,naive=0.003739,drift4=0.01183; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.10,drift4=0.59); metric_best=drift4; scores=model=0.01067,naive=0.0187,drift4=0.0008683</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.025,naive=0.01667,drift4=0.01445; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.08074,naive=0.1016,drift4=0.05368</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.55,naive=0.20,drift4=0.25); metric_best=model; scores=model=0.05159,naive=0.09443,drift4=0.1541; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=335.7,naive=153.1,drift4=193.8; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01419,naive=0.001365,drift4=0.004692; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.01822,naive=0.003598,drift4=0.0035; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03939,naive=0.01348,drift4=0.01576; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.725,naive=1.499,drift4=3.36; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09684,naive=0.01883,drift4=0.03514; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.07459,naive=0.0061,drift4=0.01491; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02045,naive=0.002768,drift4=0.00579; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1042,naive=0.01539,drift4=0.02163; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01711,naive=0.003366,drift4=0.007796; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -826,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.9067916516445035</v>
+        <v>0.9155470572889849</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -847,10 +847,10 @@
         <v>4414.99</v>
       </c>
       <c r="S2">
-        <v>4650.048413108458</v>
+        <v>4741.23920516886</v>
       </c>
       <c r="T2">
-        <v>4578.830891516764</v>
+        <v>4806.478317487463</v>
       </c>
       <c r="U2">
         <v>4414.99</v>
@@ -859,28 +859,28 @@
         <v>4841.66</v>
       </c>
       <c r="W2">
-        <v>4650.048413108458</v>
+        <v>4741.23920516886</v>
       </c>
       <c r="X2">
-        <v>4258.284391261028</v>
+        <v>4197.490529887426</v>
       </c>
       <c r="Y2">
-        <v>0.05324098426235573</v>
+        <v>0.07389579708422002</v>
       </c>
       <c r="Z2">
         <v>1.5</v>
       </c>
       <c r="AA2">
-        <v>0.05324098426235573</v>
+        <v>0.07389579708422002</v>
       </c>
       <c r="AB2">
-        <v>0.404360032664802</v>
+        <v>0.4288252793414246</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.395639967335198</v>
+        <v>0.3711747206585754</v>
       </c>
       <c r="AE2" t="s">
         <v>74</v>
@@ -895,22 +895,22 @@
         <v>375</v>
       </c>
       <c r="AI2">
-        <v>0.03549398950823715</v>
+        <v>0.04926386472281334</v>
       </c>
       <c r="AJ2">
-        <v>14086.89208870038</v>
+        <v>10149.42702553455</v>
       </c>
       <c r="AK2">
-        <v>10565.16906652528</v>
+        <v>7612.070269150914</v>
       </c>
       <c r="AL2">
-        <v>2.393022196318742</v>
+        <v>1.724142131499939</v>
       </c>
       <c r="AM2">
-        <v>105.6516906652528</v>
+        <v>76.12070269150914</v>
       </c>
       <c r="AN2">
-        <v>0.001056516906652528</v>
+        <v>0.0007612070269150913</v>
       </c>
       <c r="AO2">
         <v>375</v>
@@ -919,19 +919,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ2">
-        <v>464.305599110801</v>
+        <v>335.7304625997261</v>
       </c>
       <c r="AR2">
-        <v>158.6503398333342</v>
+        <v>153.122468235517</v>
       </c>
       <c r="AS2">
-        <v>191.4882903559876</v>
+        <v>193.7617359803453</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV2" t="s">
         <v>84</v>
@@ -981,13 +981,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.9434522607322694</v>
+        <v>0.9314110951776342</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O3" t="s">
         <v>70</v>
@@ -1002,10 +1002,10 @@
         <v>0.70638</v>
       </c>
       <c r="S3">
-        <v>0.7114912815908195</v>
+        <v>0.7098977465908642</v>
       </c>
       <c r="T3">
-        <v>0.7080382067801637</v>
+        <v>0.7064252154878075</v>
       </c>
       <c r="U3">
         <v>0.70638</v>
@@ -1014,28 +1014,28 @@
         <v>0.716065</v>
       </c>
       <c r="W3">
-        <v>0.7114912815908195</v>
+        <v>0.7098977465908642</v>
       </c>
       <c r="X3">
         <v>0.69868</v>
       </c>
       <c r="Y3">
-        <v>0.0072358809575859</v>
+        <v>0.00497996346281638</v>
       </c>
       <c r="Z3">
-        <v>0.6638028040025302</v>
+        <v>0.4568502066057407</v>
       </c>
       <c r="AA3">
-        <v>0.0072358809575859</v>
+        <v>0.00497996346281638</v>
       </c>
       <c r="AB3">
-        <v>0.3284896392577361</v>
+        <v>0.4388327772042334</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4715103607422639</v>
+        <v>0.3611672227957666</v>
       </c>
       <c r="AE3" t="s">
         <v>75</v>
@@ -1074,19 +1074,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ3">
-        <v>0.01587465646686066</v>
+        <v>0.01419015996602983</v>
       </c>
       <c r="AR3">
-        <v>0.002049916598005805</v>
+        <v>0.001365070149522031</v>
       </c>
       <c r="AS3">
-        <v>0.00464003341094562</v>
+        <v>0.004692057908554704</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV3" t="s">
         <v>84</v>
@@ -1118,7 +1118,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>66</v>
@@ -1127,70 +1127,70 @@
         <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2">
         <v>46246</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.07942345260201844</v>
       </c>
       <c r="L4">
-        <v>1.260122004711455</v>
+        <v>1.127869704282327</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.7698558631505046</v>
       </c>
       <c r="R4">
-        <v>159.3235</v>
+        <v>0.81314</v>
       </c>
       <c r="S4">
-        <v>160.357926392579</v>
+        <v>0.815665870780931</v>
       </c>
       <c r="T4">
-        <v>163.1346889372769</v>
+        <v>0.8145822599678239</v>
       </c>
       <c r="U4">
-        <v>159.3235</v>
+        <v>0.81314</v>
       </c>
       <c r="V4">
-        <v>156.203</v>
+        <v>0.8177349999999999</v>
       </c>
       <c r="W4">
-        <v>160.357926392579</v>
+        <v>0.815665870780931</v>
       </c>
       <c r="X4">
-        <v>157.81975</v>
+        <v>0.80366</v>
       </c>
       <c r="Y4">
-        <v>0.00649261654796082</v>
+        <v>0.003106317215892746</v>
       </c>
       <c r="Z4">
-        <v>0.687897850426619</v>
+        <v>0.2664420654990539</v>
       </c>
       <c r="AA4">
-        <v>0.00649261654796082</v>
+        <v>0.003106317215892746</v>
       </c>
       <c r="AB4">
-        <v>0.5093746162773005</v>
+        <v>0.3648030625205345</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.2906253837226995</v>
+        <v>0.4351969374794656</v>
       </c>
       <c r="AE4" t="s">
         <v>76</v>
@@ -1202,46 +1202,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>500</v>
+        <v>384.9279315752523</v>
       </c>
       <c r="AI4">
-        <v>0.009438343998217531</v>
+        <v>0.01165850898984183</v>
       </c>
       <c r="AJ4">
-        <v>52975.39484621741</v>
+        <v>42887.13080168782</v>
       </c>
       <c r="AK4">
-        <v>52975.39484621741</v>
+        <v>33016.90910138196</v>
       </c>
       <c r="AL4">
-        <v>332.502078137986</v>
+        <v>40604.21219148236</v>
       </c>
       <c r="AM4">
-        <v>529.7539484621741</v>
+        <v>330.1690910138196</v>
       </c>
       <c r="AN4">
-        <v>0.005297539484621741</v>
+        <v>0.003301690910138196</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>384.9279315752523</v>
       </c>
       <c r="AP4">
-        <v>0.005</v>
+        <v>0.003849279315752523</v>
       </c>
       <c r="AQ4">
-        <v>4.252864552580693</v>
+        <v>0.01822142129768796</v>
       </c>
       <c r="AR4">
-        <v>2.152318480942192</v>
+        <v>0.003598267098710923</v>
       </c>
       <c r="AS4">
-        <v>3.864898143295614</v>
+        <v>0.003499525962822127</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV4" t="s">
         <v>84</v>
@@ -1276,10 +1276,10 @@
         <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
         <v>68</v>
@@ -1300,22 +1300,22 @@
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R5">
         <v>4.76275</v>
       </c>
       <c r="S5">
-        <v>4.767788442148096</v>
+        <v>4.756178956105733</v>
       </c>
       <c r="T5">
-        <v>4.715441345810354</v>
+        <v>4.71561304262475</v>
       </c>
       <c r="U5">
         <v>4.76275</v>
@@ -1324,28 +1324,28 @@
         <v>4.794389999999999</v>
       </c>
       <c r="W5">
-        <v>4.769894125</v>
+        <v>4.755605875</v>
       </c>
       <c r="X5">
-        <v>4.7279025</v>
+        <v>4.797597499999999</v>
       </c>
       <c r="Y5">
-        <v>0.001057885076499224</v>
+        <v>-0.001379674325603087</v>
       </c>
       <c r="Z5">
         <v>0.2050111198794753</v>
       </c>
       <c r="AA5">
-        <v>0.001057885076499224</v>
+        <v>0.001379674325603087</v>
       </c>
       <c r="AB5">
-        <v>0.2879855979739051</v>
+        <v>0.4047255054849662</v>
       </c>
       <c r="AC5">
-        <v>0.1221707479728944</v>
+        <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.5898436540532004</v>
+        <v>0.3952744945150339</v>
       </c>
       <c r="AE5" t="s">
         <v>77</v>
@@ -1357,7 +1357,7 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI5">
         <v>0.007316676289958517</v>
@@ -1366,43 +1366,43 @@
         <v>68337.0399598251</v>
       </c>
       <c r="AK5">
-        <v>51252.77996986882</v>
+        <v>68337.0399598251</v>
       </c>
       <c r="AL5">
-        <v>10761.1736853433</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM5">
-        <v>512.5277996986882</v>
+        <v>683.370399598251</v>
       </c>
       <c r="AN5">
-        <v>0.005125277996986882</v>
+        <v>0.00683370399598251</v>
       </c>
       <c r="AO5">
-        <v>374.9999999999999</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>0.003749999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="AQ5">
-        <v>0.04882094002351366</v>
+        <v>0.03938712279020619</v>
       </c>
       <c r="AR5">
-        <v>0.01499500873254836</v>
+        <v>0.0134846509655139</v>
       </c>
       <c r="AS5">
-        <v>0.01703313329349149</v>
+        <v>0.01575977701159596</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV5" t="s">
         <v>84</v>
       </c>
       <c r="AW5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX5" t="s">
         <v>85</v>
@@ -1428,7 +1428,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1443,16 +1443,16 @@
         <v>46246</v>
       </c>
       <c r="K6">
-        <v>0.4174537540470262</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2.837624712178707</v>
+        <v>1.049236856438738</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O6" t="s">
         <v>70</v>
@@ -1461,46 +1461,46 @@
         <v>72</v>
       </c>
       <c r="Q6">
-        <v>0.8543634385117566</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>6.74392</v>
+        <v>159.3235</v>
       </c>
       <c r="S6">
-        <v>6.723993549396042</v>
+        <v>158.8353996838739</v>
       </c>
       <c r="T6">
-        <v>6.740559390730397</v>
+        <v>160.4836313968502</v>
       </c>
       <c r="U6">
-        <v>6.74392</v>
+        <v>159.3235</v>
       </c>
       <c r="V6">
-        <v>6.71072</v>
+        <v>156.203</v>
       </c>
       <c r="W6">
-        <v>6.723993549396042</v>
+        <v>158.8353996838739</v>
       </c>
       <c r="X6">
-        <v>6.771845000000001</v>
+        <v>160.82725</v>
       </c>
       <c r="Y6">
-        <v>-0.002954728200209741</v>
+        <v>-0.003063580175718723</v>
       </c>
       <c r="Z6">
-        <v>0.7135702991569625</v>
+        <v>0.3245887389034869</v>
       </c>
       <c r="AA6">
-        <v>0.002954728200209741</v>
+        <v>0.003063580175718723</v>
       </c>
       <c r="AB6">
-        <v>0.2944748704450007</v>
+        <v>0.4691596864312148</v>
       </c>
       <c r="AC6">
-        <v>0.1351385143538878</v>
+        <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.5703866152011116</v>
+        <v>0.3308403135687853</v>
       </c>
       <c r="AE6" t="s">
         <v>78</v>
@@ -1512,46 +1512,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>427.1817192558783</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.00414076679438671</v>
+        <v>0.009438343998217531</v>
       </c>
       <c r="AJ6">
-        <v>120750.5819158442</v>
+        <v>52975.39484621741</v>
       </c>
       <c r="AK6">
-        <v>103164.8823679162</v>
+        <v>39731.54613466305</v>
       </c>
       <c r="AL6">
-        <v>15297.4653269784</v>
+        <v>249.3765586034895</v>
       </c>
       <c r="AM6">
-        <v>1031.648823679162</v>
+        <v>397.3154613466306</v>
       </c>
       <c r="AN6">
-        <v>0.01031648823679162</v>
+        <v>0.003973154613466306</v>
       </c>
       <c r="AO6">
-        <v>427.1817192558783</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.004271817192558783</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.06591697664933356</v>
+        <v>3.725225486158831</v>
       </c>
       <c r="AR6">
-        <v>0.009399671781807296</v>
+        <v>1.499353316474598</v>
       </c>
       <c r="AS6">
-        <v>0.01482799723710954</v>
+        <v>3.360060715166471</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV6" t="s">
         <v>84</v>
@@ -1598,16 +1598,16 @@
         <v>46246</v>
       </c>
       <c r="K7">
-        <v>0.05640024919461578</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.115643117315203</v>
+        <v>0.1041141052377663</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="O7" t="s">
         <v>71</v>
@@ -1616,46 +1616,46 @@
         <v>73</v>
       </c>
       <c r="Q7">
-        <v>0.9576998131040382</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>0.81314</v>
+        <v>7.7742</v>
       </c>
       <c r="S7">
-        <v>0.8094576631845467</v>
+        <v>7.732051229556362</v>
       </c>
       <c r="T7">
-        <v>0.8014648969540474</v>
+        <v>7.653959601917407</v>
       </c>
       <c r="U7">
-        <v>0.81314</v>
+        <v>7.7742</v>
       </c>
       <c r="V7">
-        <v>0.8177349999999999</v>
+        <v>7.794900000000001</v>
       </c>
       <c r="W7">
-        <v>0.8094576631845467</v>
+        <v>7.732051229556362</v>
       </c>
       <c r="X7">
-        <v>0.8226199999999999</v>
+        <v>7.837125</v>
       </c>
       <c r="Y7">
-        <v>-0.004528539753859444</v>
+        <v>-0.005421621574392058</v>
       </c>
       <c r="Z7">
-        <v>0.3884321535288263</v>
+        <v>0.6698255136056998</v>
       </c>
       <c r="AA7">
-        <v>0.004528539753859444</v>
+        <v>0.005421621574392058</v>
       </c>
       <c r="AB7">
-        <v>0.4522612299793463</v>
+        <v>0.4165503378898903</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3477387700206537</v>
+        <v>0.3834496621101098</v>
       </c>
       <c r="AE7" t="s">
         <v>79</v>
@@ -1667,46 +1667,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>478.8499065520191</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.01165850898984183</v>
+        <v>0.008094080419850288</v>
       </c>
       <c r="AJ7">
-        <v>42887.13080168782</v>
+        <v>61773.53992848619</v>
       </c>
       <c r="AK7">
-        <v>41072.99715334486</v>
+        <v>61773.53992848619</v>
       </c>
       <c r="AL7">
-        <v>50511.59351814554</v>
+        <v>7945.967421533557</v>
       </c>
       <c r="AM7">
-        <v>410.7299715334486</v>
+        <v>617.7353992848618</v>
       </c>
       <c r="AN7">
-        <v>0.004107299715334486</v>
+        <v>0.006177353992848618</v>
       </c>
       <c r="AO7">
-        <v>478.8499065520191</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.004788499065520191</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>0.01897891879164112</v>
+        <v>0.09683910197488123</v>
       </c>
       <c r="AR7">
-        <v>0.003598849442314456</v>
+        <v>0.01883387534961431</v>
       </c>
       <c r="AS7">
-        <v>0.004478939955683554</v>
+        <v>0.03513599790188422</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV7" t="s">
         <v>84</v>
@@ -1738,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -1747,70 +1747,70 @@
         <v>67</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
         <v>46246</v>
       </c>
       <c r="K8">
-        <v>0.6399191648840915</v>
+        <v>0.345520025502779</v>
       </c>
       <c r="L8">
-        <v>1.427668953276874</v>
+        <v>2.75073626477636</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q8">
-        <v>0.5200606263369314</v>
+        <v>0.8363800063756948</v>
       </c>
       <c r="R8">
-        <v>1.349795</v>
+        <v>6.74392</v>
       </c>
       <c r="S8">
-        <v>1.341156868505101</v>
+        <v>6.701852761949382</v>
       </c>
       <c r="T8">
-        <v>1.310773211198031</v>
+        <v>6.672929188512571</v>
       </c>
       <c r="U8">
-        <v>1.349795</v>
+        <v>6.74392</v>
       </c>
       <c r="V8">
-        <v>1.355695</v>
+        <v>6.71072</v>
       </c>
       <c r="W8">
-        <v>1.341156868505101</v>
+        <v>6.701852761949382</v>
       </c>
       <c r="X8">
-        <v>1.36395125</v>
+        <v>6.771964825367078</v>
       </c>
       <c r="Y8">
-        <v>-0.006399587711392885</v>
+        <v>-0.006237802057352065</v>
       </c>
       <c r="Z8">
-        <v>0.6101991342975414</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>0.006399587711392885</v>
+        <v>0.006237802057352065</v>
       </c>
       <c r="AB8">
-        <v>0.311077562769337</v>
+        <v>0.4103441402885929</v>
       </c>
       <c r="AC8">
-        <v>0.09558829138035646</v>
+        <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.5933341458503065</v>
+        <v>0.3896558597114071</v>
       </c>
       <c r="AE8" t="s">
         <v>80</v>
@@ -1822,46 +1822,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>260.0303131684657</v>
+        <v>418.1900031878474</v>
       </c>
       <c r="AI8">
-        <v>0.01048770368833784</v>
+        <v>0.004158534704901376</v>
       </c>
       <c r="AJ8">
-        <v>47674.87858719653</v>
+        <v>120234.6584749394</v>
       </c>
       <c r="AK8">
-        <v>24793.82721859459</v>
+        <v>100561.8644218493</v>
       </c>
       <c r="AL8">
-        <v>18368.58724368855</v>
+        <v>14911.48537080056</v>
       </c>
       <c r="AM8">
-        <v>247.9382721859459</v>
+        <v>1005.618644218493</v>
       </c>
       <c r="AN8">
-        <v>0.002479382721859459</v>
+        <v>0.01005618644218493</v>
       </c>
       <c r="AO8">
-        <v>260.0303131684657</v>
+        <v>418.1900031878474</v>
       </c>
       <c r="AP8">
-        <v>0.002600303131684657</v>
+        <v>0.004181900031878474</v>
       </c>
       <c r="AQ8">
-        <v>0.01991828598504594</v>
+        <v>0.07459243256710871</v>
       </c>
       <c r="AR8">
-        <v>0.004959114959871894</v>
+        <v>0.006100433688175809</v>
       </c>
       <c r="AS8">
-        <v>0.005530499807512544</v>
+        <v>0.01491465206264271</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV8" t="s">
         <v>84</v>
@@ -1893,7 +1893,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
@@ -1908,16 +1908,16 @@
         <v>46246</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.6097911851613146</v>
       </c>
       <c r="L9">
-        <v>0.7956531118044045</v>
+        <v>1.409173571297483</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
@@ -1926,46 +1926,46 @@
         <v>73</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.5426566111290141</v>
       </c>
       <c r="R9">
-        <v>1.152885</v>
+        <v>1.349795</v>
       </c>
       <c r="S9">
-        <v>1.141031623345084</v>
+        <v>1.341260705178393</v>
       </c>
       <c r="T9">
-        <v>1.115838092717521</v>
+        <v>1.323541701679767</v>
       </c>
       <c r="U9">
-        <v>1.152885</v>
+        <v>1.349795</v>
       </c>
       <c r="V9">
-        <v>1.162725</v>
+        <v>1.355695</v>
       </c>
       <c r="W9">
-        <v>1.141031623345084</v>
+        <v>1.341260705178393</v>
       </c>
       <c r="X9">
-        <v>1.165885</v>
+        <v>1.36395125</v>
       </c>
       <c r="Y9">
-        <v>-0.01028149091619356</v>
+        <v>-0.006322659975483233</v>
       </c>
       <c r="Z9">
-        <v>0.9117982042242926</v>
+        <v>0.6028640933585803</v>
       </c>
       <c r="AA9">
-        <v>0.01028149091619356</v>
+        <v>0.006322659975483233</v>
       </c>
       <c r="AB9">
-        <v>0.4207011679417561</v>
+        <v>0.4122219341107876</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3792988320582439</v>
+        <v>0.3877780658892126</v>
       </c>
       <c r="AE9" t="s">
         <v>81</v>
@@ -1977,46 +1977,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>271.328305564507</v>
       </c>
       <c r="AI9">
-        <v>0.01127605962433375</v>
+        <v>0.01048770368833784</v>
       </c>
       <c r="AJ9">
-        <v>44341.73076923073</v>
+        <v>47674.87858719653</v>
       </c>
       <c r="AK9">
-        <v>44341.73076923073</v>
+        <v>25871.08805011527</v>
       </c>
       <c r="AL9">
-        <v>38461.53846153843</v>
+        <v>19166.67942177536</v>
       </c>
       <c r="AM9">
-        <v>443.4173076923073</v>
+        <v>258.7108805011527</v>
       </c>
       <c r="AN9">
-        <v>0.004434173076923073</v>
+        <v>0.002587108805011527</v>
       </c>
       <c r="AO9">
-        <v>500.0000000000001</v>
+        <v>271.328305564507</v>
       </c>
       <c r="AP9">
-        <v>0.005000000000000001</v>
+        <v>0.00271328305564507</v>
       </c>
       <c r="AQ9">
-        <v>0.01755472213306943</v>
+        <v>0.02045020134324322</v>
       </c>
       <c r="AR9">
-        <v>0.005459235683157841</v>
+        <v>0.002767955668355312</v>
       </c>
       <c r="AS9">
-        <v>0.008940364715777596</v>
+        <v>0.005790002131012603</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV9" t="s">
         <v>84</v>
@@ -2087,10 +2087,10 @@
         <v>9.101839999999999</v>
       </c>
       <c r="S10">
-        <v>8.992911676451566</v>
+        <v>9.040127421538601</v>
       </c>
       <c r="T10">
-        <v>8.861321971355714</v>
+        <v>8.959190982782079</v>
       </c>
       <c r="U10">
         <v>9.101839999999999</v>
@@ -2099,28 +2099,28 @@
         <v>9.085099999999999</v>
       </c>
       <c r="W10">
-        <v>8.992911676451566</v>
+        <v>9.040127421538601</v>
       </c>
       <c r="X10">
         <v>9.189672499999999</v>
       </c>
       <c r="Y10">
-        <v>-0.01196772559706972</v>
+        <v>-0.006780231080902091</v>
       </c>
       <c r="Z10">
-        <v>1.240182433022325</v>
+        <v>0.702616667650335</v>
       </c>
       <c r="AA10">
-        <v>0.01196772559706972</v>
+        <v>0.006780231080902091</v>
       </c>
       <c r="AB10">
-        <v>0.4265831460123769</v>
+        <v>0.383773771959201</v>
       </c>
       <c r="AC10">
-        <v>0.1954367932553547</v>
+        <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3779800607322683</v>
+        <v>0.416226228040799</v>
       </c>
       <c r="AE10" t="s">
         <v>82</v>
@@ -2159,19 +2159,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.09310285597967589</v>
+        <v>0.1041639084790528</v>
       </c>
       <c r="AR10">
-        <v>0.02690906334324671</v>
+        <v>0.01538777208894143</v>
       </c>
       <c r="AS10">
-        <v>0.02486196289279105</v>
+        <v>0.02162742235603577</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV10" t="s">
         <v>84</v>
@@ -2203,7 +2203,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>67</v>
@@ -2221,13 +2221,13 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.1041141052377663</v>
+        <v>0.7896533135781629</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
@@ -2239,43 +2239,43 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>7.7742</v>
+        <v>1.152885</v>
       </c>
       <c r="S11">
-        <v>7.659342957433165</v>
+        <v>1.139967223203121</v>
       </c>
       <c r="T11">
-        <v>7.558039336754147</v>
+        <v>1.114844302776638</v>
       </c>
       <c r="U11">
-        <v>7.7742</v>
+        <v>1.152885</v>
       </c>
       <c r="V11">
-        <v>7.794900000000001</v>
+        <v>1.162725</v>
       </c>
       <c r="W11">
-        <v>7.659342957433165</v>
+        <v>1.139967223203121</v>
       </c>
       <c r="X11">
-        <v>7.850771361711224</v>
+        <v>1.165885</v>
       </c>
       <c r="Y11">
-        <v>-0.0147741301441737</v>
+        <v>-0.01120474010580336</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>0.9936751382214691</v>
       </c>
       <c r="AA11">
-        <v>0.0147741301441737</v>
+        <v>0.01120474010580336</v>
       </c>
       <c r="AB11">
-        <v>0.5548284834043099</v>
+        <v>0.4341995418298861</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.2451715165956901</v>
+        <v>0.3658004581701139</v>
       </c>
       <c r="AE11" t="s">
         <v>83</v>
@@ -2290,43 +2290,43 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.009849420096115797</v>
+        <v>0.01127605962433375</v>
       </c>
       <c r="AJ11">
-        <v>50764.40999782101</v>
+        <v>44341.73076923073</v>
       </c>
       <c r="AK11">
-        <v>50764.40999782101</v>
+        <v>44341.73076923073</v>
       </c>
       <c r="AL11">
-        <v>6529.856447971625</v>
+        <v>38461.53846153843</v>
       </c>
       <c r="AM11">
-        <v>507.6440999782101</v>
+        <v>443.4173076923073</v>
       </c>
       <c r="AN11">
-        <v>0.005076440999782101</v>
+        <v>0.004434173076923073</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP11">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ11">
-        <v>0.07524244747300136</v>
+        <v>0.01710816955796338</v>
       </c>
       <c r="AR11">
-        <v>0.03062996388641314</v>
+        <v>0.003366104147537918</v>
       </c>
       <c r="AS11">
-        <v>0.05161681615211205</v>
+        <v>0.007795546788695359</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04651464372862798</v>
+        <v>0.04674610345314634</v>
       </c>
       <c r="AV11" t="s">
         <v>84</v>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
   <si>
     <t>Pair</t>
   </si>
@@ -169,6 +169,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
@@ -190,9 +193,6 @@
     <t>USDCNH</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
@@ -205,15 +205,18 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -226,10 +229,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -238,37 +244,43 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=335.7,naive=153.1,drift4=193.8; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01419,naive=0.001365,drift4=0.004692; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.01822,naive=0.003598,drift4=0.0035; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03939,naive=0.01348,drift4=0.01576; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.725,naive=1.499,drift4=3.36; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.09684,naive=0.01883,drift4=0.03514; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.07459,naive=0.0061,drift4=0.01491; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02045,naive=0.002768,drift4=0.00579; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1042,naive=0.01539,drift4=0.02163; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01711,naive=0.003366,drift4=0.007796; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01918,naive=0.002967,drift4=0.004363; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=285.7,naive=126.3,drift4=166.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01317,naive=0.00179,drift4=0.003921; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.018,naive=0.003063,drift4=0.003058; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03852,naive=0.01161,drift4=0.01809; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.697,naive=1.129,drift4=3.022; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0988,naive=0.01403,drift4=0.02968; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.07334,naive=0.004951,drift4=0.01408; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1073,naive=0.00973,drift4=0.02191; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01471,naive=0.00213,drift4=0.005719; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -796,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -814,76 +826,67 @@
         <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.7766741168202351</v>
       </c>
       <c r="L2">
-        <v>0.9155470572889849</v>
+        <v>1.512876196419543</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>4414.99</v>
+        <v>1.353755</v>
       </c>
       <c r="S2">
-        <v>4741.23920516886</v>
+        <v>1.348528424697727</v>
       </c>
       <c r="T2">
-        <v>4806.478317487463</v>
+        <v>1.329889967811579</v>
       </c>
       <c r="U2">
-        <v>4414.99</v>
+        <v>1.353755</v>
       </c>
       <c r="V2">
-        <v>4841.66</v>
-      </c>
-      <c r="W2">
-        <v>4741.23920516886</v>
-      </c>
-      <c r="X2">
-        <v>4197.490529887426</v>
+        <v>1.363615</v>
       </c>
       <c r="Y2">
-        <v>0.07389579708422002</v>
-      </c>
-      <c r="Z2">
-        <v>1.5</v>
+        <v>-0.00386079852135217</v>
       </c>
       <c r="AA2">
-        <v>0.07389579708422002</v>
+        <v>0.00386079852135217</v>
       </c>
       <c r="AB2">
-        <v>0.4288252793414246</v>
+        <v>0.3888676882204978</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.3711747206585754</v>
+        <v>0.4111323117795021</v>
       </c>
       <c r="AE2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="AF2">
         <v>100000</v>
@@ -892,58 +895,55 @@
         <v>100</v>
       </c>
       <c r="AH2">
-        <v>375</v>
-      </c>
-      <c r="AI2">
-        <v>0.04926386472281334</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>10149.42702553455</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>7612.070269150914</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>1.724142131499939</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>76.12070269150914</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.0007612070269150913</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>335.7304625997261</v>
+        <v>0.01917569391059237</v>
       </c>
       <c r="AR2">
-        <v>153.122468235517</v>
+        <v>0.002966847433031014</v>
       </c>
       <c r="AS2">
-        <v>193.7617359803453</v>
+        <v>0.004362714611855282</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AW2" t="s">
         <v>66</v>
       </c>
       <c r="AX2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,79 +966,79 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.9314110951776342</v>
+        <v>1.055356092603474</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q3">
         <v>0.75</v>
       </c>
       <c r="R3">
-        <v>0.70638</v>
+        <v>4373.870000000001</v>
       </c>
       <c r="S3">
-        <v>0.7098977465908642</v>
+        <v>4656.713122461769</v>
       </c>
       <c r="T3">
-        <v>0.7064252154878075</v>
+        <v>4699.934082487137</v>
       </c>
       <c r="U3">
-        <v>0.70638</v>
+        <v>4373.870000000001</v>
       </c>
       <c r="V3">
-        <v>0.716065</v>
+        <v>4759.420000000002</v>
       </c>
       <c r="W3">
-        <v>0.7098977465908642</v>
+        <v>4656.713122461769</v>
       </c>
       <c r="X3">
-        <v>0.69868</v>
+        <v>4185.307918358822</v>
       </c>
       <c r="Y3">
-        <v>0.00497996346281638</v>
+        <v>0.06466655901107438</v>
       </c>
       <c r="Z3">
-        <v>0.4568502066057407</v>
+        <v>1.5</v>
       </c>
       <c r="AA3">
-        <v>0.00497996346281638</v>
+        <v>0.06466655901107438</v>
       </c>
       <c r="AB3">
-        <v>0.4388327772042334</v>
+        <v>0.4303014664386313</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3611672227957666</v>
+        <v>0.3696985335613687</v>
       </c>
       <c r="AE3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AF3">
         <v>100000</v>
@@ -1050,22 +1050,22 @@
         <v>375</v>
       </c>
       <c r="AI3">
-        <v>0.01090064837622819</v>
+        <v>0.04311103934071626</v>
       </c>
       <c r="AJ3">
-        <v>45868.83116883077</v>
+        <v>11597.95745234503</v>
       </c>
       <c r="AK3">
-        <v>34401.62337662307</v>
+        <v>8698.468089258775</v>
       </c>
       <c r="AL3">
-        <v>48701.29870129827</v>
+        <v>1.988734939369202</v>
       </c>
       <c r="AM3">
-        <v>344.0162337662307</v>
+        <v>86.98468089258775</v>
       </c>
       <c r="AN3">
-        <v>0.003440162337662307</v>
+        <v>0.0008698468089258774</v>
       </c>
       <c r="AO3">
         <v>375</v>
@@ -1074,31 +1074,31 @@
         <v>0.00375</v>
       </c>
       <c r="AQ3">
-        <v>0.01419015996602983</v>
+        <v>285.7284941047648</v>
       </c>
       <c r="AR3">
-        <v>0.001365070149522031</v>
+        <v>126.3483021341381</v>
       </c>
       <c r="AS3">
-        <v>0.004692057908554704</v>
+        <v>166.2785700074361</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1118,82 +1118,82 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K4">
-        <v>0.07942345260201844</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.127869704282327</v>
+        <v>1.100029119360665</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="O4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="Q4">
-        <v>0.7698558631505046</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>0.81314</v>
+        <v>0.708385</v>
       </c>
       <c r="S4">
-        <v>0.815665870780931</v>
+        <v>0.7116549357076534</v>
       </c>
       <c r="T4">
-        <v>0.8145822599678239</v>
+        <v>0.7054528708016188</v>
       </c>
       <c r="U4">
-        <v>0.81314</v>
+        <v>0.708385</v>
       </c>
       <c r="V4">
-        <v>0.8177349999999999</v>
+        <v>0.720075</v>
       </c>
       <c r="W4">
-        <v>0.815665870780931</v>
+        <v>0.7116549357076534</v>
       </c>
       <c r="X4">
-        <v>0.80366</v>
+        <v>0.700685</v>
       </c>
       <c r="Y4">
-        <v>0.003106317215892746</v>
+        <v>0.004616043122953374</v>
       </c>
       <c r="Z4">
-        <v>0.2664420654990539</v>
+        <v>0.4246669750199088</v>
       </c>
       <c r="AA4">
-        <v>0.003106317215892746</v>
+        <v>0.004616043122953374</v>
       </c>
       <c r="AB4">
-        <v>0.3648030625205345</v>
+        <v>0.4159492923246779</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.4351969374794656</v>
+        <v>0.3840507076753221</v>
       </c>
       <c r="AE4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AF4">
         <v>100000</v>
@@ -1202,58 +1202,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>384.9279315752523</v>
+        <v>375</v>
       </c>
       <c r="AI4">
-        <v>0.01165850898984183</v>
+        <v>0.01086979537963123</v>
       </c>
       <c r="AJ4">
-        <v>42887.13080168782</v>
+        <v>45999.02597402557</v>
       </c>
       <c r="AK4">
-        <v>33016.90910138196</v>
+        <v>34499.26948051918</v>
       </c>
       <c r="AL4">
-        <v>40604.21219148236</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM4">
-        <v>330.1690910138196</v>
+        <v>344.9926948051918</v>
       </c>
       <c r="AN4">
-        <v>0.003301690910138196</v>
+        <v>0.003449926948051918</v>
       </c>
       <c r="AO4">
-        <v>384.9279315752523</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0.003849279315752523</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.01822142129768796</v>
+        <v>0.01316809926535265</v>
       </c>
       <c r="AR4">
-        <v>0.003598267098710923</v>
+        <v>0.001789865698029699</v>
       </c>
       <c r="AS4">
-        <v>0.003499525962822127</v>
+        <v>0.003921493959714081</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1273,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1282,73 +1282,73 @@
         <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.02359176027187941</v>
       </c>
       <c r="L5">
-        <v>0.04026990801319719</v>
+        <v>1.09008008248575</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.7558979400679698</v>
       </c>
       <c r="R5">
-        <v>4.76275</v>
+        <v>0.811605</v>
       </c>
       <c r="S5">
-        <v>4.756178956105733</v>
+        <v>0.8146162461845444</v>
       </c>
       <c r="T5">
-        <v>4.71561304262475</v>
+        <v>0.8162218915689624</v>
       </c>
       <c r="U5">
-        <v>4.76275</v>
+        <v>0.811605</v>
       </c>
       <c r="V5">
-        <v>4.794389999999999</v>
+        <v>0.814665</v>
       </c>
       <c r="W5">
-        <v>4.755605875</v>
+        <v>0.8146162461845444</v>
       </c>
       <c r="X5">
-        <v>4.797597499999999</v>
+        <v>0.802125</v>
       </c>
       <c r="Y5">
-        <v>-0.001379674325603087</v>
+        <v>0.003710236117993855</v>
       </c>
       <c r="Z5">
-        <v>0.2050111198794753</v>
+        <v>0.3176420025890724</v>
       </c>
       <c r="AA5">
-        <v>0.001379674325603087</v>
+        <v>0.003710236117993855</v>
       </c>
       <c r="AB5">
-        <v>0.4047255054849662</v>
+        <v>0.3617761158021388</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3952744945150339</v>
+        <v>0.4382238841978613</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AF5">
         <v>100000</v>
@@ -1357,58 +1357,58 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>500</v>
+        <v>377.9489700339849</v>
       </c>
       <c r="AI5">
-        <v>0.007316676289958517</v>
+        <v>0.01168055889256472</v>
       </c>
       <c r="AJ5">
-        <v>68337.0399598251</v>
+        <v>42806.170886076</v>
       </c>
       <c r="AK5">
-        <v>68337.0399598251</v>
+        <v>32357.09639498235</v>
       </c>
       <c r="AL5">
-        <v>14348.23158045774</v>
+        <v>39868.03481371153</v>
       </c>
       <c r="AM5">
-        <v>683.370399598251</v>
+        <v>323.5709639498235</v>
       </c>
       <c r="AN5">
-        <v>0.00683370399598251</v>
+        <v>0.003235709639498235</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>377.9489700339849</v>
       </c>
       <c r="AP5">
-        <v>0.005</v>
+        <v>0.003779489700339849</v>
       </c>
       <c r="AQ5">
-        <v>0.03938712279020619</v>
+        <v>0.01799703503228851</v>
       </c>
       <c r="AR5">
-        <v>0.0134846509655139</v>
+        <v>0.00306296662314151</v>
       </c>
       <c r="AS5">
-        <v>0.01575977701159596</v>
+        <v>0.003058485201901708</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW5" t="s">
         <v>67</v>
       </c>
       <c r="AX5" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1428,82 +1428,82 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.049236856438738</v>
+        <v>0.03606032892802228</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>159.3235</v>
+        <v>4.75729</v>
       </c>
       <c r="S6">
-        <v>158.8353996838739</v>
+        <v>4.743103154165186</v>
       </c>
       <c r="T6">
-        <v>160.4836313968502</v>
+        <v>4.700306547224801</v>
       </c>
       <c r="U6">
-        <v>159.3235</v>
+        <v>4.75729</v>
       </c>
       <c r="V6">
-        <v>156.203</v>
+        <v>4.78347</v>
       </c>
       <c r="W6">
-        <v>158.8353996838739</v>
+        <v>4.743103154165186</v>
       </c>
       <c r="X6">
-        <v>160.82725</v>
+        <v>4.7921375</v>
       </c>
       <c r="Y6">
-        <v>-0.003063580175718723</v>
+        <v>-0.00298212760517316</v>
       </c>
       <c r="Z6">
-        <v>0.3245887389034869</v>
+        <v>0.4071122988683336</v>
       </c>
       <c r="AA6">
-        <v>0.003063580175718723</v>
+        <v>0.00298212760517316</v>
       </c>
       <c r="AB6">
-        <v>0.4691596864312148</v>
+        <v>0.4224313044069677</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3308403135687853</v>
+        <v>0.3775686955930322</v>
       </c>
       <c r="AE6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AF6">
         <v>100000</v>
@@ -1512,58 +1512,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI6">
-        <v>0.009438343998217531</v>
+        <v>0.007325073728950709</v>
       </c>
       <c r="AJ6">
-        <v>52975.39484621741</v>
+        <v>68258.69861539581</v>
       </c>
       <c r="AK6">
-        <v>39731.54613466305</v>
+        <v>68258.69861539581</v>
       </c>
       <c r="AL6">
-        <v>249.3765586034895</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="AM6">
-        <v>397.3154613466306</v>
+        <v>682.5869861539582</v>
       </c>
       <c r="AN6">
-        <v>0.003973154613466306</v>
+        <v>0.006825869861539582</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="AQ6">
-        <v>3.725225486158831</v>
+        <v>0.03851663027179873</v>
       </c>
       <c r="AR6">
-        <v>1.499353316474598</v>
+        <v>0.01160598318311331</v>
       </c>
       <c r="AS6">
-        <v>3.360060715166471</v>
+        <v>0.01809028262206773</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1583,82 +1583,82 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J7" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.1041141052377663</v>
+        <v>0.9972536718580639</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>7.7742</v>
+        <v>159.0655</v>
       </c>
       <c r="S7">
-        <v>7.732051229556362</v>
+        <v>158.5639807321302</v>
       </c>
       <c r="T7">
-        <v>7.653959601917407</v>
+        <v>160.4030570588963</v>
       </c>
       <c r="U7">
-        <v>7.7742</v>
+        <v>159.0655</v>
       </c>
       <c r="V7">
-        <v>7.794900000000001</v>
+        <v>155.687</v>
       </c>
       <c r="W7">
-        <v>7.732051229556362</v>
+        <v>158.5639807321302</v>
       </c>
       <c r="X7">
-        <v>7.837125</v>
+        <v>160.37575</v>
       </c>
       <c r="Y7">
-        <v>-0.005421621574392058</v>
+        <v>-0.003152910391440967</v>
       </c>
       <c r="Z7">
-        <v>0.6698255136056998</v>
+        <v>0.3827660888149222</v>
       </c>
       <c r="AA7">
-        <v>0.005421621574392058</v>
+        <v>0.003152910391440967</v>
       </c>
       <c r="AB7">
-        <v>0.4165503378898903</v>
+        <v>0.4667629557148317</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3834496621101098</v>
+        <v>0.3332370442851683</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AF7">
         <v>100000</v>
@@ -1667,58 +1667,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.008094080419850288</v>
+        <v>0.008237172737017164</v>
       </c>
       <c r="AJ7">
-        <v>61773.53992848619</v>
+        <v>60700.43884754801</v>
       </c>
       <c r="AK7">
-        <v>61773.53992848619</v>
+        <v>45525.32913566101</v>
       </c>
       <c r="AL7">
-        <v>7945.967421533557</v>
+        <v>286.2049227246701</v>
       </c>
       <c r="AM7">
-        <v>617.7353992848618</v>
+        <v>455.2532913566101</v>
       </c>
       <c r="AN7">
-        <v>0.006177353992848618</v>
+        <v>0.004552532913566101</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ7">
-        <v>0.09683910197488123</v>
+        <v>3.69674520879528</v>
       </c>
       <c r="AR7">
-        <v>0.01883387534961431</v>
+        <v>1.128726678784076</v>
       </c>
       <c r="AS7">
-        <v>0.03513599790188422</v>
+        <v>3.021583832286023</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,82 +1738,82 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
         <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K8">
-        <v>0.345520025502779</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>2.75073626477636</v>
+        <v>0.1340006740962105</v>
       </c>
       <c r="M8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="O8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>0.8363800063756948</v>
+        <v>1</v>
       </c>
       <c r="R8">
-        <v>6.74392</v>
+        <v>7.7739</v>
       </c>
       <c r="S8">
-        <v>6.701852761949382</v>
+        <v>7.729379561797684</v>
       </c>
       <c r="T8">
-        <v>6.672929188512571</v>
+        <v>7.647582205981109</v>
       </c>
       <c r="U8">
-        <v>6.74392</v>
+        <v>7.7739</v>
       </c>
       <c r="V8">
-        <v>6.71072</v>
+        <v>7.794300000000001</v>
       </c>
       <c r="W8">
-        <v>6.701852761949382</v>
+        <v>7.729379561797684</v>
       </c>
       <c r="X8">
-        <v>6.771964825367078</v>
+        <v>7.836825</v>
       </c>
       <c r="Y8">
-        <v>-0.006237802057352065</v>
+        <v>-0.005726911614802936</v>
       </c>
       <c r="Z8">
-        <v>1.5</v>
+        <v>0.7075159030960105</v>
       </c>
       <c r="AA8">
-        <v>0.006237802057352065</v>
+        <v>0.005726911614802936</v>
       </c>
       <c r="AB8">
-        <v>0.4103441402885929</v>
+        <v>0.4146766151246947</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3896558597114071</v>
+        <v>0.3853233848753053</v>
       </c>
       <c r="AE8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AF8">
         <v>100000</v>
@@ -1822,58 +1822,58 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>418.1900031878474</v>
+        <v>500</v>
       </c>
       <c r="AI8">
-        <v>0.004158534704901376</v>
+        <v>0.00809439277582682</v>
       </c>
       <c r="AJ8">
-        <v>120234.6584749394</v>
+        <v>61771.15613825972</v>
       </c>
       <c r="AK8">
-        <v>100561.8644218493</v>
+        <v>61771.15613825972</v>
       </c>
       <c r="AL8">
-        <v>14911.48537080056</v>
+        <v>7945.967421533557</v>
       </c>
       <c r="AM8">
-        <v>1005.618644218493</v>
+        <v>617.7115613825972</v>
       </c>
       <c r="AN8">
-        <v>0.01005618644218493</v>
+        <v>0.006177115613825972</v>
       </c>
       <c r="AO8">
-        <v>418.1900031878474</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>0.004181900031878474</v>
+        <v>0.005</v>
       </c>
       <c r="AQ8">
-        <v>0.07459243256710871</v>
+        <v>0.09879508809217893</v>
       </c>
       <c r="AR8">
-        <v>0.006100433688175809</v>
+        <v>0.01403396472533719</v>
       </c>
       <c r="AS8">
-        <v>0.01491465206264271</v>
+        <v>0.02967955475168191</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX8" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,82 +1893,82 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K9">
-        <v>0.6097911851613146</v>
+        <v>0.443677755568377</v>
       </c>
       <c r="L9">
-        <v>1.409173571297483</v>
+        <v>2.86943970494218</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>0.5426566111290141</v>
+        <v>0.8609194388920942</v>
       </c>
       <c r="R9">
-        <v>1.349795</v>
+        <v>6.74213</v>
       </c>
       <c r="S9">
-        <v>1.341260705178393</v>
+        <v>6.695785984486425</v>
       </c>
       <c r="T9">
-        <v>1.323541701679767</v>
+        <v>6.663173589922606</v>
       </c>
       <c r="U9">
-        <v>1.349795</v>
+        <v>6.74213</v>
       </c>
       <c r="V9">
-        <v>1.355695</v>
+        <v>6.707140000000001</v>
       </c>
       <c r="W9">
-        <v>1.341260705178393</v>
+        <v>6.695785984486425</v>
       </c>
       <c r="X9">
-        <v>1.36395125</v>
+        <v>6.773026010342384</v>
       </c>
       <c r="Y9">
-        <v>-0.006322659975483233</v>
+        <v>-0.006873794411198789</v>
       </c>
       <c r="Z9">
-        <v>0.6028640933585803</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>0.006322659975483233</v>
+        <v>0.006873794411198789</v>
       </c>
       <c r="AB9">
-        <v>0.4122219341107876</v>
+        <v>0.4174099154620866</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3877780658892126</v>
+        <v>0.3825900845379134</v>
       </c>
       <c r="AE9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF9">
         <v>100000</v>
@@ -1977,58 +1977,58 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>271.328305564507</v>
+        <v>430.4597194460471</v>
       </c>
       <c r="AI9">
-        <v>0.01048770368833784</v>
+        <v>0.00458252960746586</v>
       </c>
       <c r="AJ9">
-        <v>47674.87858719653</v>
+        <v>109110.0424502222</v>
       </c>
       <c r="AK9">
-        <v>25871.08805011527</v>
+        <v>93934.95652373787</v>
       </c>
       <c r="AL9">
-        <v>19166.67942177536</v>
+        <v>13932.53415815742</v>
       </c>
       <c r="AM9">
-        <v>258.7108805011527</v>
+        <v>939.3495652373787</v>
       </c>
       <c r="AN9">
-        <v>0.002587108805011527</v>
+        <v>0.009393495652373787</v>
       </c>
       <c r="AO9">
-        <v>271.328305564507</v>
+        <v>430.4597194460471</v>
       </c>
       <c r="AP9">
-        <v>0.00271328305564507</v>
+        <v>0.004304597194460471</v>
       </c>
       <c r="AQ9">
-        <v>0.02045020134324322</v>
+        <v>0.07333624371679121</v>
       </c>
       <c r="AR9">
-        <v>0.002767955668355312</v>
+        <v>0.004950577992601931</v>
       </c>
       <c r="AS9">
-        <v>0.005790002131012603</v>
+        <v>0.01408309749793948</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2048,82 +2048,82 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.1693278678201049</v>
+        <v>0.1591156185073573</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q10">
         <v>1</v>
       </c>
       <c r="R10">
-        <v>9.101839999999999</v>
+        <v>9.09442</v>
       </c>
       <c r="S10">
-        <v>9.040127421538601</v>
+        <v>9.026958368494936</v>
       </c>
       <c r="T10">
-        <v>8.959190982782079</v>
+        <v>8.951875061333071</v>
       </c>
       <c r="U10">
-        <v>9.101839999999999</v>
+        <v>9.09442</v>
       </c>
       <c r="V10">
-        <v>9.085099999999999</v>
+        <v>9.070259999999999</v>
       </c>
       <c r="W10">
-        <v>9.040127421538601</v>
+        <v>9.026958368494936</v>
       </c>
       <c r="X10">
-        <v>9.189672499999999</v>
+        <v>9.182252499999999</v>
       </c>
       <c r="Y10">
-        <v>-0.006780231080902091</v>
+        <v>-0.007417914666912583</v>
       </c>
       <c r="Z10">
-        <v>0.702616667650335</v>
+        <v>0.7680714030121346</v>
       </c>
       <c r="AA10">
-        <v>0.006780231080902091</v>
+        <v>0.007417914666912583</v>
       </c>
       <c r="AB10">
-        <v>0.383773771959201</v>
+        <v>0.4065857705133047</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.416226228040799</v>
+        <v>0.3934142294866952</v>
       </c>
       <c r="AE10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AF10">
         <v>100000</v>
@@ -2135,22 +2135,22 @@
         <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.009649971873818894</v>
+        <v>0.009657845140206825</v>
       </c>
       <c r="AJ10">
-        <v>51813.6225201379</v>
+        <v>51771.38303019967</v>
       </c>
       <c r="AK10">
-        <v>51813.6225201379</v>
+        <v>51771.38303019967</v>
       </c>
       <c r="AL10">
-        <v>5692.653630489868</v>
+        <v>5692.653630489869</v>
       </c>
       <c r="AM10">
-        <v>518.136225201379</v>
+        <v>517.7138303019967</v>
       </c>
       <c r="AN10">
-        <v>0.00518136225201379</v>
+        <v>0.005177138303019967</v>
       </c>
       <c r="AO10">
         <v>500</v>
@@ -2159,31 +2159,31 @@
         <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.1041639084790528</v>
+        <v>0.1073292300372489</v>
       </c>
       <c r="AR10">
-        <v>0.01538777208894143</v>
+        <v>0.009730396063748507</v>
       </c>
       <c r="AS10">
-        <v>0.02162742235603577</v>
+        <v>0.02191251710973816</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,82 +2203,82 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.7896533135781629</v>
+        <v>0.9511767222416696</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" t="s">
         <v>71</v>
       </c>
       <c r="P11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1.152885</v>
+        <v>1.15681</v>
       </c>
       <c r="S11">
-        <v>1.139967223203121</v>
+        <v>1.146857488246976</v>
       </c>
       <c r="T11">
-        <v>1.114844302776638</v>
+        <v>1.122222942576376</v>
       </c>
       <c r="U11">
-        <v>1.152885</v>
+        <v>1.15681</v>
       </c>
       <c r="V11">
-        <v>1.162725</v>
+        <v>1.170575</v>
       </c>
       <c r="W11">
-        <v>1.139967223203121</v>
+        <v>1.146857488246976</v>
       </c>
       <c r="X11">
-        <v>1.165885</v>
+        <v>1.16981</v>
       </c>
       <c r="Y11">
-        <v>-0.01120474010580336</v>
+        <v>-0.008603410891178449</v>
       </c>
       <c r="Z11">
-        <v>0.9936751382214691</v>
+        <v>0.7655778271557024</v>
       </c>
       <c r="AA11">
-        <v>0.01120474010580336</v>
+        <v>0.008603410891178449</v>
       </c>
       <c r="AB11">
-        <v>0.4341995418298861</v>
+        <v>0.4335805521024447</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3658004581701139</v>
+        <v>0.3664194478975553</v>
       </c>
       <c r="AE11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>100000</v>
@@ -2290,55 +2290,55 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.01127605962433375</v>
+        <v>0.0112378005031077</v>
       </c>
       <c r="AJ11">
-        <v>44341.73076923073</v>
+        <v>44492.69230769226</v>
       </c>
       <c r="AK11">
-        <v>44341.73076923073</v>
+        <v>44492.69230769226</v>
       </c>
       <c r="AL11">
-        <v>38461.53846153843</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM11">
-        <v>443.4173076923073</v>
+        <v>444.9269230769226</v>
       </c>
       <c r="AN11">
-        <v>0.004434173076923073</v>
+        <v>0.004449269230769226</v>
       </c>
       <c r="AO11">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="AP11">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.01710816955796338</v>
+        <v>0.01470876843001735</v>
       </c>
       <c r="AR11">
-        <v>0.003366104147537918</v>
+        <v>0.002130088892591291</v>
       </c>
       <c r="AS11">
-        <v>0.007795546788695359</v>
+        <v>0.005719313792567815</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04674610345314634</v>
+        <v>0.04413090497157066</v>
       </c>
       <c r="AV11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AW11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AX11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -172,16 +172,25 @@
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>USDJPY</t>
@@ -190,15 +199,6 @@
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>MEDIUM</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -229,13 +229,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
+    <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -244,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.01918,naive=0.002967,drift4=0.004363; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=285.7,naive=126.3,drift4=166.3; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01317,naive=0.00179,drift4=0.003921; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.018,naive=0.003063,drift4=0.003058; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.03852,naive=0.01161,drift4=0.01809; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.697,naive=1.129,drift4=3.022; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.0988,naive=0.01403,drift4=0.02968; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.07334,naive=0.004951,drift4=0.01408; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1073,naive=0.00973,drift4=0.02191; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01471,naive=0.00213,drift4=0.005719; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01882,naive=0.002232,drift4=0.004188; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.0178,naive=0.00282,drift4=0.002676; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.03269,naive=0.0151,drift4=0.01375; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=254.5,naive=119.3,drift4=158.6; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01196,naive=0.001564,drift4=0.003928; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01488,naive=0.0008904,drift4=0.005408; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.07485,naive=0.003602,drift4=0.01414; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09994,naive=0.01536,drift4=0.01758; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.727,naive=0.8925,drift4=2.821; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.09884,naive=0.008259,drift4=0.01393; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,7 +826,7 @@
         <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
         <v>69</v>
@@ -847,7 +847,7 @@
         <v>9</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P2" t="s">
         <v>73</v>
@@ -859,10 +859,10 @@
         <v>1.353755</v>
       </c>
       <c r="S2">
-        <v>1.348528424697727</v>
+        <v>1.354761248619914</v>
       </c>
       <c r="T2">
-        <v>1.329889967811579</v>
+        <v>1.346398566017191</v>
       </c>
       <c r="U2">
         <v>1.353755</v>
@@ -871,19 +871,19 @@
         <v>1.363615</v>
       </c>
       <c r="Y2">
-        <v>-0.00386079852135217</v>
+        <v>0.0007433018677039846</v>
       </c>
       <c r="AA2">
-        <v>0.00386079852135217</v>
+        <v>0.0007433018677039846</v>
       </c>
       <c r="AB2">
-        <v>0.3888676882204978</v>
+        <v>0.3997199063962878</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4111323117795021</v>
+        <v>0.4002800936037121</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01917569391059237</v>
+        <v>0.01881839671922026</v>
       </c>
       <c r="AR2">
-        <v>0.002966847433031014</v>
+        <v>0.002232289908622685</v>
       </c>
       <c r="AS2">
-        <v>0.004362714611855282</v>
+        <v>0.004188499505885093</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,10 +966,10 @@
         <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
@@ -978,64 +978,55 @@
         <v>46247</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>0.02359176027187941</v>
       </c>
       <c r="L3">
-        <v>1.055356092603474</v>
+        <v>1.09008008248575</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>4373.870000000001</v>
+        <v>0.811605</v>
       </c>
       <c r="S3">
-        <v>4656.713122461769</v>
+        <v>0.8121886625367607</v>
       </c>
       <c r="T3">
-        <v>4699.934082487137</v>
+        <v>0.8094242181930826</v>
       </c>
       <c r="U3">
-        <v>4373.870000000001</v>
+        <v>0.811605</v>
       </c>
       <c r="V3">
-        <v>4759.420000000002</v>
-      </c>
-      <c r="W3">
-        <v>4656.713122461769</v>
-      </c>
-      <c r="X3">
-        <v>4185.307918358822</v>
+        <v>0.814665</v>
       </c>
       <c r="Y3">
-        <v>0.06466655901107438</v>
-      </c>
-      <c r="Z3">
-        <v>1.5</v>
+        <v>0.0007191460584405915</v>
       </c>
       <c r="AA3">
-        <v>0.06466655901107438</v>
+        <v>0.0007191460584405915</v>
       </c>
       <c r="AB3">
-        <v>0.4303014664386313</v>
+        <v>0.3557365164064951</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3696985335613687</v>
+        <v>0.4442634835935049</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1047,58 +1038,55 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>375</v>
-      </c>
-      <c r="AI3">
-        <v>0.04311103934071626</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>11597.95745234503</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>8698.468089258775</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.988734939369202</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>86.98468089258775</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.0008698468089258774</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>285.7284941047648</v>
+        <v>0.0177958735739237</v>
       </c>
       <c r="AR3">
-        <v>126.3483021341381</v>
+        <v>0.002820044300896264</v>
       </c>
       <c r="AS3">
-        <v>166.2785700074361</v>
+        <v>0.002676229565453803</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1106,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1121,76 +1109,67 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
       </c>
       <c r="J4" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.100029119360665</v>
+        <v>0.1333810274471401</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>0.708385</v>
+        <v>4.77564</v>
       </c>
       <c r="S4">
-        <v>0.7116549357076534</v>
+        <v>4.777174113170539</v>
       </c>
       <c r="T4">
-        <v>0.7054528708016188</v>
+        <v>4.735023561957165</v>
       </c>
       <c r="U4">
-        <v>0.708385</v>
+        <v>4.77564</v>
       </c>
       <c r="V4">
-        <v>0.720075</v>
-      </c>
-      <c r="W4">
-        <v>0.7116549357076534</v>
-      </c>
-      <c r="X4">
-        <v>0.700685</v>
+        <v>4.82017</v>
       </c>
       <c r="Y4">
-        <v>0.004616043122953374</v>
-      </c>
-      <c r="Z4">
-        <v>0.4246669750199088</v>
+        <v>0.0003212371892644937</v>
       </c>
       <c r="AA4">
-        <v>0.004616043122953374</v>
+        <v>0.0003212371892644937</v>
       </c>
       <c r="AB4">
-        <v>0.4159492923246779</v>
+        <v>0.4003677383698808</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3840507076753221</v>
+        <v>0.3996322616301193</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1202,58 +1181,55 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
-      </c>
-      <c r="AI4">
-        <v>0.01086979537963123</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>45999.02597402557</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>34499.26948051918</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>48701.29870129827</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>344.9926948051918</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.003449926948051918</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>0.01316809926535265</v>
+        <v>0.03269429669751858</v>
       </c>
       <c r="AR4">
-        <v>0.001789865698029699</v>
+        <v>0.01510131530468636</v>
       </c>
       <c r="AS4">
-        <v>0.003921493959714081</v>
+        <v>0.0137462531598792</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AW4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AX4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AY4" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1261,7 +1237,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1288,64 +1264,64 @@
         <v>46247</v>
       </c>
       <c r="K5">
-        <v>0.02359176027187941</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.09008008248575</v>
+        <v>1.055356092603474</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="s">
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.7558979400679698</v>
+        <v>0.75</v>
       </c>
       <c r="R5">
-        <v>0.811605</v>
+        <v>4373.870000000001</v>
       </c>
       <c r="S5">
-        <v>0.8146162461845444</v>
+        <v>4611.66909420455</v>
       </c>
       <c r="T5">
-        <v>0.8162218915689624</v>
+        <v>4597.004665705038</v>
       </c>
       <c r="U5">
-        <v>0.811605</v>
+        <v>4373.870000000001</v>
       </c>
       <c r="V5">
-        <v>0.814665</v>
+        <v>4759.420000000002</v>
       </c>
       <c r="W5">
-        <v>0.8146162461845444</v>
+        <v>4611.66909420455</v>
       </c>
       <c r="X5">
-        <v>0.802125</v>
+        <v>4215.337270530302</v>
       </c>
       <c r="Y5">
-        <v>0.003710236117993855</v>
+        <v>0.05436812118433994</v>
       </c>
       <c r="Z5">
-        <v>0.3176420025890724</v>
+        <v>1.5</v>
       </c>
       <c r="AA5">
-        <v>0.003710236117993855</v>
+        <v>0.05436812118433994</v>
       </c>
       <c r="AB5">
-        <v>0.3617761158021388</v>
+        <v>0.4349398786887984</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4382238841978613</v>
+        <v>0.3650601213112017</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1357,46 +1333,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>377.9489700339849</v>
+        <v>375</v>
       </c>
       <c r="AI5">
-        <v>0.01168055889256472</v>
+        <v>0.0362454141228933</v>
       </c>
       <c r="AJ5">
-        <v>42806.170886076</v>
+        <v>13794.84859256141</v>
       </c>
       <c r="AK5">
-        <v>32357.09639498235</v>
+        <v>10346.13644442106</v>
       </c>
       <c r="AL5">
-        <v>39868.03481371153</v>
+        <v>2.365442147210835</v>
       </c>
       <c r="AM5">
-        <v>323.5709639498235</v>
+        <v>103.4613644442106</v>
       </c>
       <c r="AN5">
-        <v>0.003235709639498235</v>
+        <v>0.001034613644442106</v>
       </c>
       <c r="AO5">
-        <v>377.9489700339849</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP5">
-        <v>0.003779489700339849</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ5">
-        <v>0.01799703503228851</v>
+        <v>254.4962023971943</v>
       </c>
       <c r="AR5">
-        <v>0.00306296662314151</v>
+        <v>119.3498148437928</v>
       </c>
       <c r="AS5">
-        <v>0.003058485201901708</v>
+        <v>158.5584038513305</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1408,7 +1384,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1416,7 +1392,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1431,10 +1407,10 @@
         <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I6" t="s">
         <v>69</v>
@@ -1446,61 +1422,61 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0.03606032892802228</v>
+        <v>1.100029119360665</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6">
-        <v>4.75729</v>
+        <v>0.708385</v>
       </c>
       <c r="S6">
-        <v>4.743103154165186</v>
+        <v>0.7104688484920432</v>
       </c>
       <c r="T6">
-        <v>4.700306547224801</v>
+        <v>0.7029782978653119</v>
       </c>
       <c r="U6">
-        <v>4.75729</v>
+        <v>0.708385</v>
       </c>
       <c r="V6">
-        <v>4.78347</v>
+        <v>0.720075</v>
       </c>
       <c r="W6">
-        <v>4.743103154165186</v>
+        <v>0.7104688484920432</v>
       </c>
       <c r="X6">
-        <v>4.7921375</v>
+        <v>0.700685</v>
       </c>
       <c r="Y6">
-        <v>-0.00298212760517316</v>
+        <v>0.002941689183202817</v>
       </c>
       <c r="Z6">
-        <v>0.4071122988683336</v>
+        <v>0.2706296742913129</v>
       </c>
       <c r="AA6">
-        <v>0.00298212760517316</v>
+        <v>0.002941689183202817</v>
       </c>
       <c r="AB6">
-        <v>0.4224313044069677</v>
+        <v>0.4251200875290608</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3775686955930322</v>
+        <v>0.3748799124709392</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1512,58 +1488,58 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.007325073728950709</v>
+        <v>0.01086979537963123</v>
       </c>
       <c r="AJ6">
-        <v>68258.69861539581</v>
+        <v>45999.02597402557</v>
       </c>
       <c r="AK6">
-        <v>68258.69861539581</v>
+        <v>34499.26948051918</v>
       </c>
       <c r="AL6">
-        <v>14348.23158045774</v>
+        <v>48701.29870129827</v>
       </c>
       <c r="AM6">
-        <v>682.5869861539582</v>
+        <v>344.9926948051918</v>
       </c>
       <c r="AN6">
-        <v>0.006825869861539582</v>
+        <v>0.003449926948051918</v>
       </c>
       <c r="AO6">
-        <v>500.0000000000001</v>
+        <v>375</v>
       </c>
       <c r="AP6">
-        <v>0.005000000000000001</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.03851663027179873</v>
+        <v>0.01196450047443737</v>
       </c>
       <c r="AR6">
-        <v>0.01160598318311331</v>
+        <v>0.001563561100263482</v>
       </c>
       <c r="AS6">
-        <v>0.01809028262206773</v>
+        <v>0.003927960225024117</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
       </c>
       <c r="AW6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX6" t="s">
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1571,7 +1547,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1592,7 +1568,7 @@
         <v>68</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J7" s="2">
         <v>46247</v>
@@ -1601,61 +1577,61 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.9972536718580639</v>
+        <v>0.9511767222416696</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O7" t="s">
         <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R7">
-        <v>159.0655</v>
+        <v>1.15681</v>
       </c>
       <c r="S7">
-        <v>158.5639807321302</v>
+        <v>1.152100338063596</v>
       </c>
       <c r="T7">
-        <v>160.4030570588963</v>
+        <v>1.136666203526093</v>
       </c>
       <c r="U7">
-        <v>159.0655</v>
+        <v>1.15681</v>
       </c>
       <c r="V7">
-        <v>155.687</v>
+        <v>1.170575</v>
       </c>
       <c r="W7">
-        <v>158.5639807321302</v>
+        <v>1.152100338063596</v>
       </c>
       <c r="X7">
-        <v>160.37575</v>
+        <v>1.16981</v>
       </c>
       <c r="Y7">
-        <v>-0.003152910391440967</v>
+        <v>-0.004071249329106756</v>
       </c>
       <c r="Z7">
-        <v>0.3827660888149222</v>
+        <v>0.3622816874156909</v>
       </c>
       <c r="AA7">
-        <v>0.003152910391440967</v>
+        <v>0.004071249329106756</v>
       </c>
       <c r="AB7">
-        <v>0.4667629557148317</v>
+        <v>0.4636455306959018</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3332370442851683</v>
+        <v>0.3363544693040983</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1667,46 +1643,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI7">
-        <v>0.008237172737017164</v>
+        <v>0.0112378005031077</v>
       </c>
       <c r="AJ7">
-        <v>60700.43884754801</v>
+        <v>44492.69230769226</v>
       </c>
       <c r="AK7">
-        <v>45525.32913566101</v>
+        <v>44492.69230769226</v>
       </c>
       <c r="AL7">
-        <v>286.2049227246701</v>
+        <v>38461.53846153842</v>
       </c>
       <c r="AM7">
-        <v>455.2532913566101</v>
+        <v>444.9269230769226</v>
       </c>
       <c r="AN7">
-        <v>0.004552532913566101</v>
+        <v>0.004449269230769226</v>
       </c>
       <c r="AO7">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP7">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ7">
-        <v>3.69674520879528</v>
+        <v>0.01487582658414505</v>
       </c>
       <c r="AR7">
-        <v>1.128726678784076</v>
+        <v>0.0008903758288682329</v>
       </c>
       <c r="AS7">
-        <v>3.021583832286023</v>
+        <v>0.005407750959507321</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1718,7 +1694,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1726,7 +1702,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1738,7 +1714,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1747,70 +1723,70 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J8" s="2">
         <v>46247</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.443677755568377</v>
       </c>
       <c r="L8">
-        <v>0.1340006740962105</v>
+        <v>2.86943970494218</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.8609194388920942</v>
       </c>
       <c r="R8">
-        <v>7.7739</v>
+        <v>6.74213</v>
       </c>
       <c r="S8">
-        <v>7.729379561797684</v>
+        <v>6.711187661490792</v>
       </c>
       <c r="T8">
-        <v>7.647582205981109</v>
+        <v>6.700338714757544</v>
       </c>
       <c r="U8">
-        <v>7.7739</v>
+        <v>6.74213</v>
       </c>
       <c r="V8">
-        <v>7.794300000000001</v>
+        <v>6.707140000000001</v>
       </c>
       <c r="W8">
-        <v>7.729379561797684</v>
+        <v>6.711187661490792</v>
       </c>
       <c r="X8">
-        <v>7.836825</v>
+        <v>6.770055000000001</v>
       </c>
       <c r="Y8">
-        <v>-0.005726911614802936</v>
+        <v>-0.004589401051182444</v>
       </c>
       <c r="Z8">
-        <v>0.7075159030960105</v>
+        <v>1.108051513310948</v>
       </c>
       <c r="AA8">
-        <v>0.005726911614802936</v>
+        <v>0.004589401051182444</v>
       </c>
       <c r="AB8">
-        <v>0.4146766151246947</v>
+        <v>0.4337913209098045</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3853233848753053</v>
+        <v>0.3662086790901954</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1822,46 +1798,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>500</v>
+        <v>430.4597194460471</v>
       </c>
       <c r="AI8">
-        <v>0.00809439277582682</v>
+        <v>0.004141866146158621</v>
       </c>
       <c r="AJ8">
-        <v>61771.15613825972</v>
+        <v>120718.5317815559</v>
       </c>
       <c r="AK8">
-        <v>61771.15613825972</v>
+        <v>103928.9306452546</v>
       </c>
       <c r="AL8">
-        <v>7945.967421533557</v>
+        <v>15414.85118875705</v>
       </c>
       <c r="AM8">
-        <v>617.7115613825972</v>
+        <v>1039.289306452546</v>
       </c>
       <c r="AN8">
-        <v>0.006177115613825972</v>
+        <v>0.01039289306452546</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>430.4597194460471</v>
       </c>
       <c r="AP8">
-        <v>0.005</v>
+        <v>0.004304597194460471</v>
       </c>
       <c r="AQ8">
-        <v>0.09879508809217893</v>
+        <v>0.07484829024352389</v>
       </c>
       <c r="AR8">
-        <v>0.01403396472533719</v>
+        <v>0.003602111387573889</v>
       </c>
       <c r="AS8">
-        <v>0.02967955475168191</v>
+        <v>0.01414267086542543</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1873,7 +1849,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1881,7 +1857,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1893,7 +1869,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1902,70 +1878,70 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K9">
-        <v>0.443677755568377</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.86943970494218</v>
+        <v>0.2890510674624616</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="O9" t="s">
         <v>72</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.8609194388920942</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>6.74213</v>
+        <v>9.12504</v>
       </c>
       <c r="S9">
-        <v>6.695785984486425</v>
+        <v>9.076229767133603</v>
       </c>
       <c r="T9">
-        <v>6.663173589922606</v>
+        <v>8.985220840995316</v>
       </c>
       <c r="U9">
-        <v>6.74213</v>
+        <v>9.12504</v>
       </c>
       <c r="V9">
-        <v>6.707140000000001</v>
+        <v>9.131500000000001</v>
       </c>
       <c r="W9">
-        <v>6.695785984486425</v>
+        <v>9.076229767133603</v>
       </c>
       <c r="X9">
-        <v>6.773026010342384</v>
+        <v>9.2128725</v>
       </c>
       <c r="Y9">
-        <v>-0.006873794411198789</v>
+        <v>-0.005349043167635182</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>0.55571949866391</v>
       </c>
       <c r="AA9">
-        <v>0.006873794411198789</v>
+        <v>0.005349043167635182</v>
       </c>
       <c r="AB9">
-        <v>0.4174099154620866</v>
+        <v>0.3690083620501937</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.3825900845379134</v>
+        <v>0.4309916379498063</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1977,46 +1953,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>430.4597194460471</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.00458252960746586</v>
+        <v>0.009625437258357197</v>
       </c>
       <c r="AJ9">
-        <v>109110.0424502222</v>
+        <v>51945.69208436527</v>
       </c>
       <c r="AK9">
-        <v>93934.95652373787</v>
+        <v>51945.69208436527</v>
       </c>
       <c r="AL9">
-        <v>13932.53415815742</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM9">
-        <v>939.3495652373787</v>
+        <v>519.4569208436527</v>
       </c>
       <c r="AN9">
-        <v>0.009393495652373787</v>
+        <v>0.005194569208436527</v>
       </c>
       <c r="AO9">
-        <v>430.4597194460471</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>0.004304597194460471</v>
+        <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.07333624371679121</v>
+        <v>0.09993884146371879</v>
       </c>
       <c r="AR9">
-        <v>0.004950577992601931</v>
+        <v>0.01536413929108228</v>
       </c>
       <c r="AS9">
-        <v>0.01408309749793948</v>
+        <v>0.01758446880762395</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2028,7 +2004,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2036,7 +2012,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2057,7 +2033,7 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J10" s="2">
         <v>46247</v>
@@ -2066,61 +2042,61 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.1591156185073573</v>
+        <v>0.9972536718580639</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O10" t="s">
         <v>71</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R10">
-        <v>9.09442</v>
+        <v>159.0655</v>
       </c>
       <c r="S10">
-        <v>9.026958368494936</v>
+        <v>158.1848997636896</v>
       </c>
       <c r="T10">
-        <v>8.951875061333071</v>
+        <v>159.5934940606672</v>
       </c>
       <c r="U10">
-        <v>9.09442</v>
+        <v>159.0655</v>
       </c>
       <c r="V10">
-        <v>9.070259999999999</v>
+        <v>155.687</v>
       </c>
       <c r="W10">
-        <v>9.026958368494936</v>
+        <v>158.1848997636896</v>
       </c>
       <c r="X10">
-        <v>9.182252499999999</v>
+        <v>160.37575</v>
       </c>
       <c r="Y10">
-        <v>-0.007417914666912583</v>
+        <v>-0.005536085677349358</v>
       </c>
       <c r="Z10">
-        <v>0.7680714030121346</v>
+        <v>0.6720856602254622</v>
       </c>
       <c r="AA10">
-        <v>0.007417914666912583</v>
+        <v>0.005536085677349358</v>
       </c>
       <c r="AB10">
-        <v>0.4065857705133047</v>
+        <v>0.4664539956777405</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3934142294866952</v>
+        <v>0.3335460043222595</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2132,46 +2108,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AI10">
-        <v>0.009657845140206825</v>
+        <v>0.008237172737017164</v>
       </c>
       <c r="AJ10">
-        <v>51771.38303019967</v>
+        <v>60700.43884754801</v>
       </c>
       <c r="AK10">
-        <v>51771.38303019967</v>
+        <v>45525.32913566101</v>
       </c>
       <c r="AL10">
-        <v>5692.653630489869</v>
+        <v>286.2049227246701</v>
       </c>
       <c r="AM10">
-        <v>517.7138303019967</v>
+        <v>455.2532913566101</v>
       </c>
       <c r="AN10">
-        <v>0.005177138303019967</v>
+        <v>0.004552532913566101</v>
       </c>
       <c r="AO10">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="AP10">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ10">
-        <v>0.1073292300372489</v>
+        <v>3.727028612183287</v>
       </c>
       <c r="AR10">
-        <v>0.009730396063748507</v>
+        <v>0.8924810351154281</v>
       </c>
       <c r="AS10">
-        <v>0.02191251710973816</v>
+        <v>2.821001726685765</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2183,7 +2159,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2191,7 +2167,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,7 +2179,7 @@
         <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
@@ -2215,22 +2191,22 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.9511767222416696</v>
+        <v>0.006680900891693144</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P11" t="s">
         <v>75</v>
@@ -2239,43 +2215,43 @@
         <v>1</v>
       </c>
       <c r="R11">
-        <v>1.15681</v>
+        <v>7.8025</v>
       </c>
       <c r="S11">
-        <v>1.146857488246976</v>
+        <v>7.742215709944618</v>
       </c>
       <c r="T11">
-        <v>1.122222942576376</v>
+        <v>7.591637235175469</v>
       </c>
       <c r="U11">
-        <v>1.15681</v>
+        <v>7.8025</v>
       </c>
       <c r="V11">
-        <v>1.170575</v>
+        <v>7.851500000000001</v>
       </c>
       <c r="W11">
-        <v>1.146857488246976</v>
+        <v>7.742215709944618</v>
       </c>
       <c r="X11">
-        <v>1.16981</v>
+        <v>7.865425</v>
       </c>
       <c r="Y11">
-        <v>-0.008603410891178449</v>
+        <v>-0.00772627876390666</v>
       </c>
       <c r="Z11">
-        <v>0.7655778271557024</v>
+        <v>0.958034009620685</v>
       </c>
       <c r="AA11">
-        <v>0.008603410891178449</v>
+        <v>0.00772627876390666</v>
       </c>
       <c r="AB11">
-        <v>0.4335805521024447</v>
+        <v>0.3828339551553578</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.3664194478975553</v>
+        <v>0.4171660448446422</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2290,22 +2266,22 @@
         <v>500</v>
       </c>
       <c r="AI11">
-        <v>0.0112378005031077</v>
+        <v>0.008064722845241925</v>
       </c>
       <c r="AJ11">
-        <v>44492.69230769226</v>
+        <v>61998.41080651557</v>
       </c>
       <c r="AK11">
-        <v>44492.69230769226</v>
+        <v>61998.41080651557</v>
       </c>
       <c r="AL11">
-        <v>38461.53846153842</v>
+        <v>7945.967421533556</v>
       </c>
       <c r="AM11">
-        <v>444.9269230769226</v>
+        <v>619.9841080651557</v>
       </c>
       <c r="AN11">
-        <v>0.004449269230769226</v>
+        <v>0.006199841080651558</v>
       </c>
       <c r="AO11">
         <v>500</v>
@@ -2314,19 +2290,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.01470876843001735</v>
+        <v>0.09884048055403342</v>
       </c>
       <c r="AR11">
-        <v>0.002130088892591291</v>
+        <v>0.008258838200342825</v>
       </c>
       <c r="AS11">
-        <v>0.005719313792567815</v>
+        <v>0.01393112821543639</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.04413090497157066</v>
+        <v>0.0352736460904429</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2338,7 +2314,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -172,30 +172,30 @@
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>AUDUSD</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -208,12 +208,12 @@
     <t>MEDIUM</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -244,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01882,naive=0.002232,drift4=0.004188; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.0178,naive=0.00282,drift4=0.002676; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.03269,naive=0.0151,drift4=0.01375; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=254.5,naive=119.3,drift4=158.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01196,naive=0.001564,drift4=0.003928; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01488,naive=0.0008904,drift4=0.005408; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.07485,naive=0.003602,drift4=0.01414; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09994,naive=0.01536,drift4=0.01758; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=3.727,naive=0.8925,drift4=2.821; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.09884,naive=0.008259,drift4=0.01393; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01813,naive=0.002195,drift4=0.003981; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03212,naive=0.01395,drift4=0.01396; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=233.3,naive=113,drift4=151.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.01794,naive=0.002929,drift4=0.00256; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01121,naive=0.001424,drift4=0.003928; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01494,naive=0.0008928,drift4=0.005332; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=3.824,naive=0.9882,drift4=2.823; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07863,naive=0.003107,drift4=0.01462; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09916,naive=0.01521,drift4=0.01708; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09976,naive=0.007746,drift4=0.01437; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -832,19 +832,19 @@
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K2">
-        <v>0.7766741168202351</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1.512876196419543</v>
+        <v>1.764165814666598</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="s">
         <v>66</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.353755</v>
+        <v>1.35379</v>
       </c>
       <c r="S2">
-        <v>1.354761248619914</v>
+        <v>1.354446126401434</v>
       </c>
       <c r="T2">
-        <v>1.346398566017191</v>
+        <v>1.345429519306851</v>
       </c>
       <c r="U2">
-        <v>1.353755</v>
+        <v>1.35379</v>
       </c>
       <c r="V2">
-        <v>1.363615</v>
+        <v>1.363685</v>
       </c>
       <c r="Y2">
-        <v>0.0007433018677039846</v>
+        <v>0.0004846589215712749</v>
       </c>
       <c r="AA2">
-        <v>0.0007433018677039846</v>
+        <v>0.0004846589215712749</v>
       </c>
       <c r="AB2">
-        <v>0.3997199063962878</v>
+        <v>0.3976818644545757</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4002800936037121</v>
+        <v>0.4023181355454243</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01881839671922026</v>
+        <v>0.01813196771044608</v>
       </c>
       <c r="AR2">
-        <v>0.002232289908622685</v>
+        <v>0.002194625450008187</v>
       </c>
       <c r="AS2">
-        <v>0.004188499505885093</v>
+        <v>0.003981261138669483</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -963,7 +963,7 @@
         <v>62</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
         <v>66</v>
@@ -975,19 +975,19 @@
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K3">
-        <v>0.02359176027187941</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>1.09008008248575</v>
+        <v>0.1333810274471401</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="O3" t="s">
         <v>66</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>0.811605</v>
+        <v>4.77564</v>
       </c>
       <c r="S3">
-        <v>0.8121886625367607</v>
+        <v>4.776091833276952</v>
       </c>
       <c r="T3">
-        <v>0.8094242181930826</v>
+        <v>4.733309903615186</v>
       </c>
       <c r="U3">
-        <v>0.811605</v>
+        <v>4.77564</v>
       </c>
       <c r="V3">
-        <v>0.814665</v>
+        <v>4.82017</v>
       </c>
       <c r="Y3">
-        <v>0.0007191460584405915</v>
+        <v>9.461208905032771E-05</v>
       </c>
       <c r="AA3">
-        <v>0.0007191460584405915</v>
+        <v>9.461208905032771E-05</v>
       </c>
       <c r="AB3">
-        <v>0.3557365164064951</v>
+        <v>0.4049289396045029</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.4442634835935049</v>
+        <v>0.3950710603954971</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>0.0177958735739237</v>
+        <v>0.03212356081048925</v>
       </c>
       <c r="AR3">
-        <v>0.002820044300896264</v>
+        <v>0.01394704343464616</v>
       </c>
       <c r="AS3">
-        <v>0.002676229565453803</v>
+        <v>0.01395529553548386</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV3" t="s">
         <v>86</v>
@@ -1086,7 +1086,7 @@
         <v>88</v>
       </c>
       <c r="AY3" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1094,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1106,13 +1106,13 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
         <v>69</v>
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.1333810274471401</v>
+        <v>1.270338028212634</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1133,43 +1133,52 @@
         <v>3</v>
       </c>
       <c r="O4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R4">
-        <v>4.77564</v>
+        <v>4375.73</v>
       </c>
       <c r="S4">
-        <v>4.777174113170539</v>
+        <v>4611.125086679021</v>
       </c>
       <c r="T4">
-        <v>4.735023561957165</v>
+        <v>4592.891674116763</v>
       </c>
       <c r="U4">
-        <v>4.77564</v>
+        <v>4375.73</v>
       </c>
       <c r="V4">
-        <v>4.82017</v>
+        <v>4763.139999999999</v>
+      </c>
+      <c r="W4">
+        <v>4611.125086679021</v>
+      </c>
+      <c r="X4">
+        <v>4218.799942213985</v>
       </c>
       <c r="Y4">
-        <v>0.0003212371892644937</v>
+        <v>0.05379561505829243</v>
+      </c>
+      <c r="Z4">
+        <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.0003212371892644937</v>
+        <v>0.05379561505829243</v>
       </c>
       <c r="AB4">
-        <v>0.4003677383698808</v>
+        <v>0.4377894051780318</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3996322616301193</v>
+        <v>0.3622105948219681</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1181,55 +1190,58 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI4">
+        <v>0.03586374337219495</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>13941.65675375785</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>10456.24256531839</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>2.389599578885897</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>104.5624256531839</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.001045624256531839</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ4">
-        <v>0.03269429669751858</v>
+        <v>233.2694911122572</v>
       </c>
       <c r="AR4">
-        <v>0.01510131530468636</v>
+        <v>112.9706381945564</v>
       </c>
       <c r="AS4">
-        <v>0.0137462531598792</v>
+        <v>151.3172965752368</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1237,7 +1249,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,19 +1273,19 @@
         <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.1290340153162315</v>
       </c>
       <c r="L5">
-        <v>1.055356092603474</v>
+        <v>1.165785178737804</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="O5" t="s">
         <v>71</v>
@@ -1282,46 +1294,46 @@
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>0.7822585038290578</v>
       </c>
       <c r="R5">
-        <v>4373.870000000001</v>
+        <v>0.813375</v>
       </c>
       <c r="S5">
-        <v>4611.66909420455</v>
+        <v>0.8152959144104527</v>
       </c>
       <c r="T5">
-        <v>4597.004665705038</v>
+        <v>0.8126621971306549</v>
       </c>
       <c r="U5">
-        <v>4373.870000000001</v>
+        <v>0.813375</v>
       </c>
       <c r="V5">
-        <v>4759.420000000002</v>
+        <v>0.8182049999999998</v>
       </c>
       <c r="W5">
-        <v>4611.66909420455</v>
+        <v>0.8152959144104527</v>
       </c>
       <c r="X5">
-        <v>4215.337270530302</v>
+        <v>0.803895</v>
       </c>
       <c r="Y5">
-        <v>0.05436812118433994</v>
+        <v>0.002361659026221267</v>
       </c>
       <c r="Z5">
-        <v>1.5</v>
+        <v>0.202628102368431</v>
       </c>
       <c r="AA5">
-        <v>0.05436812118433994</v>
+        <v>0.002361659026221267</v>
       </c>
       <c r="AB5">
-        <v>0.4349398786887984</v>
+        <v>0.3505601110755208</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.3650601213112017</v>
+        <v>0.4494398889244792</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1333,46 +1345,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>375</v>
+        <v>391.1292519145289</v>
       </c>
       <c r="AI5">
-        <v>0.0362454141228933</v>
+        <v>0.01165514061779621</v>
       </c>
       <c r="AJ5">
-        <v>13794.84859256141</v>
+        <v>42899.52531645574</v>
       </c>
       <c r="AK5">
-        <v>10346.13644442106</v>
+        <v>33558.51848902746</v>
       </c>
       <c r="AL5">
-        <v>2.365442147210835</v>
+        <v>41258.35990659593</v>
       </c>
       <c r="AM5">
-        <v>103.4613644442106</v>
+        <v>335.5851848902746</v>
       </c>
       <c r="AN5">
-        <v>0.001034613644442106</v>
+        <v>0.003355851848902746</v>
       </c>
       <c r="AO5">
-        <v>375.0000000000001</v>
+        <v>391.1292519145289</v>
       </c>
       <c r="AP5">
-        <v>0.003750000000000001</v>
+        <v>0.003911292519145289</v>
       </c>
       <c r="AQ5">
-        <v>254.4962023971943</v>
+        <v>0.01794133351795106</v>
       </c>
       <c r="AR5">
-        <v>119.3498148437928</v>
+        <v>0.002928884159287493</v>
       </c>
       <c r="AS5">
-        <v>158.5584038513305</v>
+        <v>0.002560066619181795</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1384,7 +1396,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1392,7 +1404,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,19 +1428,19 @@
         <v>69</v>
       </c>
       <c r="J6" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.100029119360665</v>
+        <v>1.224029802435517</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
@@ -1440,43 +1452,43 @@
         <v>0.75</v>
       </c>
       <c r="R6">
-        <v>0.708385</v>
+        <v>0.70828</v>
       </c>
       <c r="S6">
-        <v>0.7104688484920432</v>
+        <v>0.7095564659469433</v>
       </c>
       <c r="T6">
-        <v>0.7029782978653119</v>
+        <v>0.7013307112264288</v>
       </c>
       <c r="U6">
-        <v>0.708385</v>
+        <v>0.70828</v>
       </c>
       <c r="V6">
-        <v>0.720075</v>
+        <v>0.719865</v>
       </c>
       <c r="W6">
-        <v>0.7104688484920432</v>
+        <v>0.7095564659469433</v>
       </c>
       <c r="X6">
-        <v>0.700685</v>
+        <v>0.70058</v>
       </c>
       <c r="Y6">
-        <v>0.002941689183202817</v>
+        <v>0.001802205267610699</v>
       </c>
       <c r="Z6">
-        <v>0.2706296742913129</v>
+        <v>0.165774798304324</v>
       </c>
       <c r="AA6">
-        <v>0.002941689183202817</v>
+        <v>0.001802205267610699</v>
       </c>
       <c r="AB6">
-        <v>0.4251200875290608</v>
+        <v>0.4311756523645026</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3748799124709392</v>
+        <v>0.3688243476354974</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1491,22 +1503,22 @@
         <v>375</v>
       </c>
       <c r="AI6">
-        <v>0.01086979537963123</v>
+        <v>0.01087140678827592</v>
       </c>
       <c r="AJ6">
-        <v>45999.02597402557</v>
+        <v>45992.20779220739</v>
       </c>
       <c r="AK6">
-        <v>34499.26948051918</v>
+        <v>34494.15584415554</v>
       </c>
       <c r="AL6">
         <v>48701.29870129827</v>
       </c>
       <c r="AM6">
-        <v>344.9926948051918</v>
+        <v>344.9415584415554</v>
       </c>
       <c r="AN6">
-        <v>0.003449926948051918</v>
+        <v>0.003449415584415554</v>
       </c>
       <c r="AO6">
         <v>375</v>
@@ -1515,19 +1527,19 @@
         <v>0.00375</v>
       </c>
       <c r="AQ6">
-        <v>0.01196450047443737</v>
+        <v>0.01120835046085476</v>
       </c>
       <c r="AR6">
-        <v>0.001563561100263482</v>
+        <v>0.001424437759613101</v>
       </c>
       <c r="AS6">
-        <v>0.003927960225024117</v>
+        <v>0.003927745540540827</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1539,7 +1551,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1547,7 +1559,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1571,19 +1583,19 @@
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>0.006484736928676851</v>
       </c>
       <c r="L7">
-        <v>0.9511767222416696</v>
+        <v>1.116455385346934</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
         <v>72</v>
@@ -1592,46 +1604,46 @@
         <v>75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.9951364473034924</v>
       </c>
       <c r="R7">
-        <v>1.15681</v>
+        <v>1.157015</v>
       </c>
       <c r="S7">
-        <v>1.152100338063596</v>
+        <v>1.152021685491978</v>
       </c>
       <c r="T7">
-        <v>1.136666203526093</v>
+        <v>1.136038825119247</v>
       </c>
       <c r="U7">
-        <v>1.15681</v>
+        <v>1.157015</v>
       </c>
       <c r="V7">
-        <v>1.170575</v>
+        <v>1.170985</v>
       </c>
       <c r="W7">
-        <v>1.152100338063596</v>
+        <v>1.152021685491978</v>
       </c>
       <c r="X7">
-        <v>1.16981</v>
+        <v>1.170015</v>
       </c>
       <c r="Y7">
-        <v>-0.004071249329106756</v>
+        <v>-0.004315686925426287</v>
       </c>
       <c r="Z7">
-        <v>0.3622816874156909</v>
+        <v>0.3841011160016993</v>
       </c>
       <c r="AA7">
-        <v>0.004071249329106756</v>
+        <v>0.004315686925426287</v>
       </c>
       <c r="AB7">
-        <v>0.4636455306959018</v>
+        <v>0.4626919702427104</v>
       </c>
       <c r="AC7">
         <v>0.2</v>
       </c>
       <c r="AD7">
-        <v>0.3363544693040983</v>
+        <v>0.3373080297572896</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1643,46 +1655,46 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>500</v>
+        <v>497.5682236517462</v>
       </c>
       <c r="AI7">
-        <v>0.0112378005031077</v>
+        <v>0.01123580938881519</v>
       </c>
       <c r="AJ7">
-        <v>44492.69230769226</v>
+        <v>44500.57692307688</v>
       </c>
       <c r="AK7">
-        <v>44492.69230769226</v>
+        <v>44284.14602218651</v>
       </c>
       <c r="AL7">
-        <v>38461.53846153842</v>
+        <v>38274.47874244198</v>
       </c>
       <c r="AM7">
-        <v>444.9269230769226</v>
+        <v>442.8414602218651</v>
       </c>
       <c r="AN7">
-        <v>0.004449269230769226</v>
+        <v>0.004428414602218651</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>497.5682236517462</v>
       </c>
       <c r="AP7">
-        <v>0.005</v>
+        <v>0.004975682236517462</v>
       </c>
       <c r="AQ7">
-        <v>0.01487582658414505</v>
+        <v>0.01494222642882515</v>
       </c>
       <c r="AR7">
-        <v>0.0008903758288682329</v>
+        <v>0.0008927679322955778</v>
       </c>
       <c r="AS7">
-        <v>0.005407750959507321</v>
+        <v>0.005331521538118108</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
@@ -1694,7 +1706,7 @@
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1702,7 +1714,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1714,7 +1726,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1726,19 +1738,19 @@
         <v>70</v>
       </c>
       <c r="J8" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K8">
-        <v>0.443677755568377</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>2.86943970494218</v>
+        <v>0.9128855372395723</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1747,46 +1759,46 @@
         <v>74</v>
       </c>
       <c r="Q8">
-        <v>0.8609194388920942</v>
+        <v>0.75</v>
       </c>
       <c r="R8">
-        <v>6.74213</v>
+        <v>159.316</v>
       </c>
       <c r="S8">
-        <v>6.711187661490792</v>
+        <v>158.5833228526289</v>
       </c>
       <c r="T8">
-        <v>6.700338714757544</v>
+        <v>160.0115386953985</v>
       </c>
       <c r="U8">
-        <v>6.74213</v>
+        <v>159.316</v>
       </c>
       <c r="V8">
-        <v>6.707140000000001</v>
+        <v>156.188</v>
       </c>
       <c r="W8">
-        <v>6.711187661490792</v>
+        <v>158.5833228526289</v>
       </c>
       <c r="X8">
-        <v>6.770055000000001</v>
+        <v>160.814125</v>
       </c>
       <c r="Y8">
-        <v>-0.004589401051182444</v>
+        <v>-0.004598892436234137</v>
       </c>
       <c r="Z8">
-        <v>1.108051513310948</v>
+        <v>0.4890627600307518</v>
       </c>
       <c r="AA8">
-        <v>0.004589401051182444</v>
+        <v>0.004598892436234137</v>
       </c>
       <c r="AB8">
-        <v>0.4337913209098045</v>
+        <v>0.4628494684148694</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3662086790901954</v>
+        <v>0.3371505315851306</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1798,46 +1810,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>430.4597194460471</v>
+        <v>375</v>
       </c>
       <c r="AI8">
-        <v>0.004141866146158621</v>
+        <v>0.00940348113183871</v>
       </c>
       <c r="AJ8">
-        <v>120718.5317815559</v>
+        <v>53171.79808093394</v>
       </c>
       <c r="AK8">
-        <v>103928.9306452546</v>
+        <v>39878.84856070045</v>
       </c>
       <c r="AL8">
-        <v>15414.85118875705</v>
+        <v>250.3128911138897</v>
       </c>
       <c r="AM8">
-        <v>1039.289306452546</v>
+        <v>398.7884856070045</v>
       </c>
       <c r="AN8">
-        <v>0.01039289306452546</v>
+        <v>0.003987884856070044</v>
       </c>
       <c r="AO8">
-        <v>430.4597194460471</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="AP8">
-        <v>0.004304597194460471</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="AQ8">
-        <v>0.07484829024352389</v>
+        <v>3.823869223422942</v>
       </c>
       <c r="AR8">
-        <v>0.003602111387573889</v>
+        <v>0.988242078866953</v>
       </c>
       <c r="AS8">
-        <v>0.01414267086542543</v>
+        <v>2.822505723365535</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1849,7 +1861,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1857,7 +1869,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1869,7 +1881,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1878,70 +1890,70 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2">
         <v>46248</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.5406137321372756</v>
       </c>
       <c r="L9">
-        <v>0.2890510674624616</v>
+        <v>2.986639488171212</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.8851534330343189</v>
       </c>
       <c r="R9">
-        <v>9.12504</v>
+        <v>6.74283</v>
       </c>
       <c r="S9">
-        <v>9.076229767133603</v>
+        <v>6.709549126017258</v>
       </c>
       <c r="T9">
-        <v>8.985220840995316</v>
+        <v>6.69532435662535</v>
       </c>
       <c r="U9">
-        <v>9.12504</v>
+        <v>6.74283</v>
       </c>
       <c r="V9">
-        <v>9.131500000000001</v>
+        <v>6.708539999999999</v>
       </c>
       <c r="W9">
-        <v>9.076229767133603</v>
+        <v>6.709549126017258</v>
       </c>
       <c r="X9">
-        <v>9.2128725</v>
+        <v>6.770755</v>
       </c>
       <c r="Y9">
-        <v>-0.005349043167635182</v>
+        <v>-0.004935742704879362</v>
       </c>
       <c r="Z9">
-        <v>0.55571949866391</v>
+        <v>1.191794950142926</v>
       </c>
       <c r="AA9">
-        <v>0.005349043167635182</v>
+        <v>0.004935742704879362</v>
       </c>
       <c r="AB9">
-        <v>0.3690083620501937</v>
+        <v>0.4425720199109779</v>
       </c>
       <c r="AC9">
         <v>0.2</v>
       </c>
       <c r="AD9">
-        <v>0.4309916379498063</v>
+        <v>0.3574279800890221</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1953,46 +1965,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>500</v>
+        <v>442.5767165171595</v>
       </c>
       <c r="AI9">
-        <v>0.009625437258357197</v>
+        <v>0.004141436162560887</v>
       </c>
       <c r="AJ9">
-        <v>51945.69208436527</v>
+        <v>120731.065353624</v>
       </c>
       <c r="AK9">
-        <v>51945.69208436527</v>
+        <v>106865.516971651</v>
       </c>
       <c r="AL9">
-        <v>5692.653630489868</v>
+        <v>15848.7633488685</v>
       </c>
       <c r="AM9">
-        <v>519.4569208436527</v>
+        <v>1068.65516971651</v>
       </c>
       <c r="AN9">
-        <v>0.005194569208436527</v>
+        <v>0.0106865516971651</v>
       </c>
       <c r="AO9">
-        <v>500</v>
+        <v>442.5767165171595</v>
       </c>
       <c r="AP9">
-        <v>0.005</v>
+        <v>0.004425767165171595</v>
       </c>
       <c r="AQ9">
-        <v>0.09993884146371879</v>
+        <v>0.07863457666054392</v>
       </c>
       <c r="AR9">
-        <v>0.01536413929108228</v>
+        <v>0.003106643801273546</v>
       </c>
       <c r="AS9">
-        <v>0.01758446880762395</v>
+        <v>0.0146249871311321</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2004,7 +2016,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2012,7 +2024,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2033,70 +2045,70 @@
         <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.9972536718580639</v>
+        <v>0.2890510674624616</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>159.0655</v>
+        <v>9.12504</v>
       </c>
       <c r="S10">
-        <v>158.1848997636896</v>
+        <v>9.074294698805637</v>
       </c>
       <c r="T10">
-        <v>159.5934940606672</v>
+        <v>8.979340003391242</v>
       </c>
       <c r="U10">
-        <v>159.0655</v>
+        <v>9.12504</v>
       </c>
       <c r="V10">
-        <v>155.687</v>
+        <v>9.131500000000001</v>
       </c>
       <c r="W10">
-        <v>158.1848997636896</v>
+        <v>9.074294698805637</v>
       </c>
       <c r="X10">
-        <v>160.37575</v>
+        <v>9.2128725</v>
       </c>
       <c r="Y10">
-        <v>-0.005536085677349358</v>
+        <v>-0.005561104520567891</v>
       </c>
       <c r="Z10">
-        <v>0.6720856602254622</v>
+        <v>0.5777508461487828</v>
       </c>
       <c r="AA10">
-        <v>0.005536085677349358</v>
+        <v>0.005561104520567891</v>
       </c>
       <c r="AB10">
-        <v>0.4664539956777405</v>
+        <v>0.3674638698772487</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.3335460043222595</v>
+        <v>0.4325361301227513</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2108,46 +2120,46 @@
         <v>100</v>
       </c>
       <c r="AH10">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.008237172737017164</v>
+        <v>0.009625437258357197</v>
       </c>
       <c r="AJ10">
-        <v>60700.43884754801</v>
+        <v>51945.69208436527</v>
       </c>
       <c r="AK10">
-        <v>45525.32913566101</v>
+        <v>51945.69208436527</v>
       </c>
       <c r="AL10">
-        <v>286.2049227246701</v>
+        <v>5692.653630489868</v>
       </c>
       <c r="AM10">
-        <v>455.2532913566101</v>
+        <v>519.4569208436527</v>
       </c>
       <c r="AN10">
-        <v>0.004552532913566101</v>
+        <v>0.005194569208436527</v>
       </c>
       <c r="AO10">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP10">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>3.727028612183287</v>
+        <v>0.09915823314272079</v>
       </c>
       <c r="AR10">
-        <v>0.8924810351154281</v>
+        <v>0.01520649956493937</v>
       </c>
       <c r="AS10">
-        <v>2.821001726685765</v>
+        <v>0.01707514047578092</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2159,7 +2171,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2167,7 +2179,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2218,10 +2230,10 @@
         <v>7.8025</v>
       </c>
       <c r="S11">
-        <v>7.742215709944618</v>
+        <v>7.739930980519032</v>
       </c>
       <c r="T11">
-        <v>7.591637235175469</v>
+        <v>7.58953563756701</v>
       </c>
       <c r="U11">
         <v>7.8025</v>
@@ -2230,28 +2242,28 @@
         <v>7.851500000000001</v>
       </c>
       <c r="W11">
-        <v>7.742215709944618</v>
+        <v>7.739930980519032</v>
       </c>
       <c r="X11">
         <v>7.865425</v>
       </c>
       <c r="Y11">
-        <v>-0.00772627876390666</v>
+        <v>-0.008019098940207347</v>
       </c>
       <c r="Z11">
-        <v>0.958034009620685</v>
+        <v>0.9943427807861376</v>
       </c>
       <c r="AA11">
-        <v>0.00772627876390666</v>
+        <v>0.008019098940207347</v>
       </c>
       <c r="AB11">
-        <v>0.3828339551553578</v>
+        <v>0.3884842141724555</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4171660448446422</v>
+        <v>0.4115157858275446</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2290,19 +2302,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ11">
-        <v>0.09884048055403342</v>
+        <v>0.09976110798935797</v>
       </c>
       <c r="AR11">
-        <v>0.008258838200342825</v>
+        <v>0.007746326352123775</v>
       </c>
       <c r="AS11">
-        <v>0.01393112821543639</v>
+        <v>0.01436688009834949</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.0352736460904429</v>
+        <v>0.03834815313439202</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2314,7 +2326,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -172,45 +172,45 @@
     <t>GBPUSD</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>AUDCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>AUDUSD</t>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
@@ -229,13 +229,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>CONFLICT</t>
+  </si>
+  <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
-    <t>NO_SIGNAL</t>
+    <t>BLOCK_STRONG_CONFLICT</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -244,34 +244,34 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01813,naive=0.002195,drift4=0.003981; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03212,naive=0.01395,drift4=0.01396; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=233.3,naive=113,drift4=151.3; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.01794,naive=0.002929,drift4=0.00256; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01121,naive=0.001424,drift4=0.003928; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.01494,naive=0.0008928,drift4=0.005332; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=3.824,naive=0.9882,drift4=2.823; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.07863,naive=0.003107,drift4=0.01462; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.09916,naive=0.01521,drift4=0.01708; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.09976,naive=0.007746,drift4=0.01437; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.0401,naive=0.00935,drift4=0.01187; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=979.9,naive=366.3,drift4=451.8; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.58,naive=0.20,drift4=0.22); metric_best=model; scores=model=1.832,naive=3.473,drift4=8.154; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04386,naive=0.007983,drift4=0.005043; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1362,naive=0.01402,drift4=0.03125; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.18,drift4=0.50); metric_best=drift4; scores=model=0.1231,naive=0.05909,drift4=0.01769</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.02991,naive=0.007195,drift4=0.005234; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.35); metric_best=drift4; scores=model=0.03823,naive=0.05742,drift4=0.03427</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.07669,naive=0.05371,drift4=0.06191; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02535,naive=0.008568,drift4=0.01138; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -808,7 +808,7 @@
         <v>51</v>
       </c>
       <c r="B2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -826,28 +826,28 @@
         <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
         <v>69</v>
       </c>
       <c r="J2" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2">
-        <v>1.764165814666598</v>
+        <v>1.737494928074045</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P2" t="s">
         <v>73</v>
@@ -856,34 +856,34 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1.35379</v>
+        <v>1.35278</v>
       </c>
       <c r="S2">
-        <v>1.354446126401434</v>
+        <v>1.34149626798056</v>
       </c>
       <c r="T2">
-        <v>1.345429519306851</v>
+        <v>1.305172311481587</v>
       </c>
       <c r="U2">
-        <v>1.35379</v>
+        <v>1.35278</v>
       </c>
       <c r="V2">
-        <v>1.363685</v>
+        <v>1.37099</v>
       </c>
       <c r="Y2">
-        <v>0.0004846589215712749</v>
+        <v>-0.008341143437543672</v>
       </c>
       <c r="AA2">
-        <v>0.0004846589215712749</v>
+        <v>0.008341143437543672</v>
       </c>
       <c r="AB2">
-        <v>0.3976818644545757</v>
+        <v>0.3927778778224338</v>
       </c>
       <c r="AC2">
         <v>0.2</v>
       </c>
       <c r="AD2">
-        <v>0.4023181355454243</v>
+        <v>0.4072221221775662</v>
       </c>
       <c r="AE2" t="s">
         <v>76</v>
@@ -919,19 +919,19 @@
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>0.01813196771044608</v>
+        <v>0.0194400831123135</v>
       </c>
       <c r="AR2">
-        <v>0.002194625450008187</v>
+        <v>0.003534007759882105</v>
       </c>
       <c r="AS2">
-        <v>0.003981261138669483</v>
+        <v>0.005491703541461885</v>
       </c>
       <c r="AT2">
         <v>1</v>
       </c>
       <c r="AU2">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV2" t="s">
         <v>86</v>
@@ -943,7 +943,7 @@
         <v>88</v>
       </c>
       <c r="AY2" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="3" spans="1:51">
@@ -951,7 +951,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -966,67 +966,76 @@
         <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
         <v>69</v>
       </c>
       <c r="J3" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0.1333810274471401</v>
+        <v>1.412807215284729</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R3">
-        <v>4.77564</v>
+        <v>4394.049999999999</v>
       </c>
       <c r="S3">
-        <v>4.776091833276952</v>
+        <v>4541.796045950049</v>
       </c>
       <c r="T3">
-        <v>4.733309903615186</v>
+        <v>4426.594967381598</v>
       </c>
       <c r="U3">
-        <v>4.77564</v>
+        <v>4394.049999999999</v>
       </c>
       <c r="V3">
-        <v>4.82017</v>
+        <v>4742.209999999999</v>
+      </c>
+      <c r="W3">
+        <v>4541.796045950049</v>
+      </c>
+      <c r="X3">
+        <v>4255.23</v>
       </c>
       <c r="Y3">
-        <v>9.461208905032771E-05</v>
+        <v>0.03362411578157961</v>
+      </c>
+      <c r="Z3">
+        <v>1.064299423354348</v>
       </c>
       <c r="AA3">
-        <v>9.461208905032771E-05</v>
+        <v>0.03362411578157961</v>
       </c>
       <c r="AB3">
-        <v>0.4049289396045029</v>
+        <v>0.4143717520834128</v>
       </c>
       <c r="AC3">
         <v>0.2</v>
       </c>
       <c r="AD3">
-        <v>0.3950710603954971</v>
+        <v>0.3856282479165873</v>
       </c>
       <c r="AE3" t="s">
         <v>77</v>
@@ -1038,55 +1047,58 @@
         <v>100</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="AI3">
+        <v>0.0315927219763087</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>15826.42990923506</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>11869.8224319263</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.701339864572843</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>118.698224319263</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.00118698224319263</v>
       </c>
       <c r="AO3">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ3">
-        <v>0.03212356081048925</v>
+        <v>410.0278586899465</v>
       </c>
       <c r="AR3">
-        <v>0.01394704343464616</v>
+        <v>125.8248861946142</v>
       </c>
       <c r="AS3">
-        <v>0.01395529553548386</v>
+        <v>170.0538416004675</v>
       </c>
       <c r="AT3">
         <v>1</v>
       </c>
       <c r="AU3">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AW3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AX3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY3" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="4" spans="1:51">
@@ -1094,7 +1106,7 @@
         <v>53</v>
       </c>
       <c r="B4" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1106,7 +1118,7 @@
         <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
         <v>67</v>
@@ -1115,70 +1127,70 @@
         <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J4" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.270338028212634</v>
+        <v>0.9408225092317056</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O4" t="s">
         <v>71</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q4">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R4">
-        <v>4375.73</v>
+        <v>159.676</v>
       </c>
       <c r="S4">
-        <v>4611.125086679021</v>
+        <v>161.8316596777024</v>
       </c>
       <c r="T4">
-        <v>4592.891674116763</v>
+        <v>164.9119908332137</v>
       </c>
       <c r="U4">
-        <v>4375.73</v>
+        <v>159.676</v>
       </c>
       <c r="V4">
-        <v>4763.139999999999</v>
+        <v>155.72</v>
       </c>
       <c r="W4">
-        <v>4611.125086679021</v>
+        <v>161.8316596777024</v>
       </c>
       <c r="X4">
-        <v>4218.799942213985</v>
+        <v>158.2388935481983</v>
       </c>
       <c r="Y4">
-        <v>0.05379561505829243</v>
+        <v>0.01350021091273867</v>
       </c>
       <c r="Z4">
         <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0.05379561505829243</v>
+        <v>0.01350021091273867</v>
       </c>
       <c r="AB4">
-        <v>0.4377894051780318</v>
+        <v>0.5788147284131155</v>
       </c>
       <c r="AC4">
         <v>0.2</v>
       </c>
       <c r="AD4">
-        <v>0.3622105948219681</v>
+        <v>0.2211852715868845</v>
       </c>
       <c r="AE4" t="s">
         <v>78</v>
@@ -1190,46 +1202,46 @@
         <v>100</v>
       </c>
       <c r="AH4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AI4">
-        <v>0.03586374337219495</v>
+        <v>0.009000140608492446</v>
       </c>
       <c r="AJ4">
-        <v>13941.65675375785</v>
+        <v>55554.68761545845</v>
       </c>
       <c r="AK4">
-        <v>10456.24256531839</v>
+        <v>55554.68761545845</v>
       </c>
       <c r="AL4">
-        <v>2.389599578885897</v>
+        <v>347.9213383066864</v>
       </c>
       <c r="AM4">
-        <v>104.5624256531839</v>
+        <v>555.5468761545845</v>
       </c>
       <c r="AN4">
-        <v>0.001045624256531839</v>
+        <v>0.005555468761545846</v>
       </c>
       <c r="AO4">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="AP4">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="AQ4">
-        <v>233.2694911122572</v>
+        <v>3.470121160228256</v>
       </c>
       <c r="AR4">
-        <v>112.9706381945564</v>
+        <v>1.487563435597712</v>
       </c>
       <c r="AS4">
-        <v>151.3172965752368</v>
+        <v>3.658012239705288</v>
       </c>
       <c r="AT4">
         <v>1</v>
       </c>
       <c r="AU4">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV4" t="s">
         <v>87</v>
@@ -1241,7 +1253,7 @@
         <v>89</v>
       </c>
       <c r="AY4" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="5" spans="1:51">
@@ -1249,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="B5" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1261,7 +1273,7 @@
         <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
         <v>67</v>
@@ -1273,67 +1285,67 @@
         <v>69</v>
       </c>
       <c r="J5" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K5">
-        <v>0.1290340153162315</v>
+        <v>0.006645056466970206</v>
       </c>
       <c r="L5">
-        <v>1.165785178737804</v>
+        <v>1.41741649865742</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>0.7822585038290578</v>
+        <v>0.7516612641167425</v>
       </c>
       <c r="R5">
-        <v>0.813375</v>
+        <v>0.711045</v>
       </c>
       <c r="S5">
-        <v>0.8152959144104527</v>
+        <v>0.7163180033516041</v>
       </c>
       <c r="T5">
-        <v>0.8126621971306549</v>
+        <v>0.7115881121532946</v>
       </c>
       <c r="U5">
-        <v>0.813375</v>
+        <v>0.711045</v>
       </c>
       <c r="V5">
-        <v>0.8182049999999998</v>
+        <v>0.721905</v>
       </c>
       <c r="W5">
-        <v>0.8152959144104527</v>
+        <v>0.7163180033516041</v>
       </c>
       <c r="X5">
-        <v>0.803895</v>
+        <v>0.703345</v>
       </c>
       <c r="Y5">
-        <v>0.002361659026221267</v>
+        <v>0.007415850405535623</v>
       </c>
       <c r="Z5">
-        <v>0.202628102368431</v>
+        <v>0.6848056300784456</v>
       </c>
       <c r="AA5">
-        <v>0.002361659026221267</v>
+        <v>0.007415850405535623</v>
       </c>
       <c r="AB5">
-        <v>0.3505601110755208</v>
+        <v>0.3310103491613006</v>
       </c>
       <c r="AC5">
         <v>0.2</v>
       </c>
       <c r="AD5">
-        <v>0.4494398889244792</v>
+        <v>0.4689896508386994</v>
       </c>
       <c r="AE5" t="s">
         <v>79</v>
@@ -1345,46 +1357,46 @@
         <v>100</v>
       </c>
       <c r="AH5">
-        <v>391.1292519145289</v>
+        <v>375.8306320583712</v>
       </c>
       <c r="AI5">
-        <v>0.01165514061779621</v>
+        <v>0.01082913177084441</v>
       </c>
       <c r="AJ5">
-        <v>42899.52531645574</v>
+        <v>46171.75324675284</v>
       </c>
       <c r="AK5">
-        <v>33558.51848902746</v>
+        <v>34705.51841194055</v>
       </c>
       <c r="AL5">
-        <v>41258.35990659593</v>
+        <v>48809.17299459324</v>
       </c>
       <c r="AM5">
-        <v>335.5851848902746</v>
+        <v>347.0551841194055</v>
       </c>
       <c r="AN5">
-        <v>0.003355851848902746</v>
+        <v>0.003470551841194055</v>
       </c>
       <c r="AO5">
-        <v>391.1292519145289</v>
+        <v>375.8306320583712</v>
       </c>
       <c r="AP5">
-        <v>0.003911292519145289</v>
+        <v>0.003758306320583712</v>
       </c>
       <c r="AQ5">
-        <v>0.01794133351795106</v>
+        <v>0.01376090134018822</v>
       </c>
       <c r="AR5">
-        <v>0.002928884159287493</v>
+        <v>0.002950149996103246</v>
       </c>
       <c r="AS5">
-        <v>0.002560066619181795</v>
+        <v>0.003833995718258926</v>
       </c>
       <c r="AT5">
         <v>1</v>
       </c>
       <c r="AU5">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV5" t="s">
         <v>87</v>
@@ -1396,7 +1408,7 @@
         <v>89</v>
       </c>
       <c r="AY5" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="6" spans="1:51">
@@ -1404,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B6" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1416,7 +1428,7 @@
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
@@ -1425,70 +1437,70 @@
         <v>67</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.5259359401337355</v>
       </c>
       <c r="L6">
-        <v>1.224029802435517</v>
+        <v>2.972216273968399</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
         <v>71</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
+        <v>0.6055480448996984</v>
       </c>
       <c r="R6">
-        <v>0.70828</v>
+        <v>6.74544</v>
       </c>
       <c r="S6">
-        <v>0.7095564659469433</v>
+        <v>6.787216888287275</v>
       </c>
       <c r="T6">
-        <v>0.7013307112264288</v>
+        <v>6.873152267607372</v>
       </c>
       <c r="U6">
-        <v>0.70828</v>
+        <v>6.74544</v>
       </c>
       <c r="V6">
-        <v>0.719865</v>
+        <v>6.718680000000001</v>
       </c>
       <c r="W6">
-        <v>0.7095564659469433</v>
+        <v>6.787216888287275</v>
       </c>
       <c r="X6">
-        <v>0.70058</v>
+        <v>6.717515</v>
       </c>
       <c r="Y6">
-        <v>0.001802205267610699</v>
+        <v>0.006193352588900715</v>
       </c>
       <c r="Z6">
-        <v>0.165774798304324</v>
+        <v>1.496038971791363</v>
       </c>
       <c r="AA6">
-        <v>0.001802205267610699</v>
+        <v>0.006193352588900715</v>
       </c>
       <c r="AB6">
-        <v>0.4311756523645026</v>
+        <v>0.4090370994479942</v>
       </c>
       <c r="AC6">
         <v>0.2</v>
       </c>
       <c r="AD6">
-        <v>0.3688243476354974</v>
+        <v>0.3909629005520059</v>
       </c>
       <c r="AE6" t="s">
         <v>80</v>
@@ -1500,46 +1512,46 @@
         <v>100</v>
       </c>
       <c r="AH6">
-        <v>375</v>
+        <v>302.7740224498492</v>
       </c>
       <c r="AI6">
-        <v>0.01087140678827592</v>
+        <v>0.004139833724708903</v>
       </c>
       <c r="AJ6">
-        <v>45992.20779220739</v>
+        <v>120777.7976723348</v>
       </c>
       <c r="AK6">
-        <v>34494.15584415554</v>
+        <v>73136.75924777366</v>
       </c>
       <c r="AL6">
-        <v>48701.29870129827</v>
+        <v>10842.40008772944</v>
       </c>
       <c r="AM6">
-        <v>344.9415584415554</v>
+        <v>731.3675924777366</v>
       </c>
       <c r="AN6">
-        <v>0.003449415584415554</v>
+        <v>0.007313675924777366</v>
       </c>
       <c r="AO6">
-        <v>375</v>
+        <v>302.7740224498492</v>
       </c>
       <c r="AP6">
-        <v>0.00375</v>
+        <v>0.003027740224498492</v>
       </c>
       <c r="AQ6">
-        <v>0.01120835046085476</v>
+        <v>0.08649082966536599</v>
       </c>
       <c r="AR6">
-        <v>0.001424437759613101</v>
+        <v>0.005318272183201098</v>
       </c>
       <c r="AS6">
-        <v>0.003927745540540827</v>
+        <v>0.0202704863066463</v>
       </c>
       <c r="AT6">
         <v>1</v>
       </c>
       <c r="AU6">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV6" t="s">
         <v>87</v>
@@ -1551,7 +1563,7 @@
         <v>89</v>
       </c>
       <c r="AY6" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="7" spans="1:51">
@@ -1559,7 +1571,7 @@
         <v>56</v>
       </c>
       <c r="B7" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1571,79 +1583,79 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
         <v>69</v>
       </c>
       <c r="J7" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K7">
-        <v>0.006484736928676851</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>1.116455385346934</v>
+        <v>0.2815296005162526</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O7" t="s">
         <v>72</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q7">
-        <v>0.9951364473034924</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>1.157015</v>
+        <v>4.78877</v>
       </c>
       <c r="S7">
-        <v>1.152021685491978</v>
+        <v>4.811486426119327</v>
       </c>
       <c r="T7">
-        <v>1.136038825119247</v>
+        <v>4.762614864271115</v>
       </c>
       <c r="U7">
-        <v>1.157015</v>
+        <v>4.78877</v>
       </c>
       <c r="V7">
-        <v>1.170985</v>
+        <v>4.851640000000001</v>
       </c>
       <c r="W7">
-        <v>1.152021685491978</v>
+        <v>4.811486426119327</v>
       </c>
       <c r="X7">
-        <v>1.170015</v>
+        <v>4.753922500000001</v>
       </c>
       <c r="Y7">
-        <v>-0.004315686925426287</v>
+        <v>0.004743687025964172</v>
       </c>
       <c r="Z7">
-        <v>0.3841011160016993</v>
+        <v>0.6518810852809097</v>
       </c>
       <c r="AA7">
-        <v>0.004315686925426287</v>
+        <v>0.004743687025964172</v>
       </c>
       <c r="AB7">
-        <v>0.4626919702427104</v>
+        <v>0.3248113188497139</v>
       </c>
       <c r="AC7">
-        <v>0.2</v>
+        <v>0.1787371104469427</v>
       </c>
       <c r="AD7">
-        <v>0.3373080297572896</v>
+        <v>0.4964515707033433</v>
       </c>
       <c r="AE7" t="s">
         <v>81</v>
@@ -1655,58 +1667,58 @@
         <v>100</v>
       </c>
       <c r="AH7">
-        <v>497.5682236517462</v>
+        <v>375</v>
       </c>
       <c r="AI7">
-        <v>0.01123580938881519</v>
+        <v>0.007276920795945497</v>
       </c>
       <c r="AJ7">
-        <v>44500.57692307688</v>
+        <v>68710.38094554862</v>
       </c>
       <c r="AK7">
-        <v>44284.14602218651</v>
+        <v>51532.78570916146</v>
       </c>
       <c r="AL7">
-        <v>38274.47874244198</v>
+        <v>10761.1736853433</v>
       </c>
       <c r="AM7">
-        <v>442.8414602218651</v>
+        <v>515.3278570916146</v>
       </c>
       <c r="AN7">
-        <v>0.004428414602218651</v>
+        <v>0.005153278570916147</v>
       </c>
       <c r="AO7">
-        <v>497.5682236517462</v>
+        <v>375</v>
       </c>
       <c r="AP7">
-        <v>0.004975682236517462</v>
+        <v>0.00375</v>
       </c>
       <c r="AQ7">
-        <v>0.01494222642882515</v>
+        <v>0.04842918717924546</v>
       </c>
       <c r="AR7">
-        <v>0.0008927679322955778</v>
+        <v>0.01930343713516028</v>
       </c>
       <c r="AS7">
-        <v>0.005331521538118108</v>
+        <v>0.01491546584374072</v>
       </c>
       <c r="AT7">
         <v>1</v>
       </c>
       <c r="AU7">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV7" t="s">
         <v>87</v>
       </c>
       <c r="AW7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AX7" t="s">
         <v>89</v>
       </c>
       <c r="AY7" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="8" spans="1:51">
@@ -1714,7 +1726,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1726,7 +1738,7 @@
         <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>68</v>
@@ -1735,70 +1747,70 @@
         <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>0.0599653482459717</v>
       </c>
       <c r="L8">
-        <v>0.9128855372395723</v>
+        <v>1.12320607582844</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q8">
-        <v>0.75</v>
+        <v>0.9550259888155213</v>
       </c>
       <c r="R8">
-        <v>159.316</v>
+        <v>0.812585</v>
       </c>
       <c r="S8">
-        <v>158.5833228526289</v>
+        <v>0.8109472750776768</v>
       </c>
       <c r="T8">
-        <v>160.0115386953985</v>
+        <v>0.8125349935902897</v>
       </c>
       <c r="U8">
-        <v>159.316</v>
+        <v>0.812585</v>
       </c>
       <c r="V8">
-        <v>156.188</v>
+        <v>0.8089850000000001</v>
       </c>
       <c r="W8">
-        <v>158.5833228526289</v>
+        <v>0.8109472750776768</v>
       </c>
       <c r="X8">
-        <v>160.814125</v>
+        <v>0.8218749999999999</v>
       </c>
       <c r="Y8">
-        <v>-0.004598892436234137</v>
+        <v>-0.002015450595720041</v>
       </c>
       <c r="Z8">
-        <v>0.4890627600307518</v>
+        <v>0.1762890120907621</v>
       </c>
       <c r="AA8">
-        <v>0.004598892436234137</v>
+        <v>0.002015450595720041</v>
       </c>
       <c r="AB8">
-        <v>0.4628494684148694</v>
+        <v>0.3499372734291125</v>
       </c>
       <c r="AC8">
         <v>0.2</v>
       </c>
       <c r="AD8">
-        <v>0.3371505315851306</v>
+        <v>0.4500627265708875</v>
       </c>
       <c r="AE8" t="s">
         <v>82</v>
@@ -1810,46 +1822,46 @@
         <v>100</v>
       </c>
       <c r="AH8">
-        <v>375</v>
+        <v>477.5129944077606</v>
       </c>
       <c r="AI8">
-        <v>0.00940348113183871</v>
+        <v>0.01143265012275631</v>
       </c>
       <c r="AJ8">
-        <v>53171.79808093394</v>
+        <v>43734.39181916069</v>
       </c>
       <c r="AK8">
-        <v>39878.84856070045</v>
+        <v>41767.48079233937</v>
       </c>
       <c r="AL8">
-        <v>250.3128911138897</v>
+        <v>51400.75289642237</v>
       </c>
       <c r="AM8">
-        <v>398.7884856070045</v>
+        <v>417.6748079233938</v>
       </c>
       <c r="AN8">
-        <v>0.003987884856070044</v>
+        <v>0.004176748079233938</v>
       </c>
       <c r="AO8">
-        <v>375.0000000000001</v>
+        <v>477.5129944077606</v>
       </c>
       <c r="AP8">
-        <v>0.003750000000000001</v>
+        <v>0.004775129944077606</v>
       </c>
       <c r="AQ8">
-        <v>3.823869223422942</v>
+        <v>0.0193269055484675</v>
       </c>
       <c r="AR8">
-        <v>0.988242078866953</v>
+        <v>0.002699876450962892</v>
       </c>
       <c r="AS8">
-        <v>2.822505723365535</v>
+        <v>0.003403798390486215</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
       <c r="AU8">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV8" t="s">
         <v>87</v>
@@ -1861,7 +1873,7 @@
         <v>89</v>
       </c>
       <c r="AY8" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="9" spans="1:51">
@@ -1869,7 +1881,7 @@
         <v>58</v>
       </c>
       <c r="B9" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1881,7 +1893,7 @@
         <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>68</v>
@@ -1890,70 +1902,70 @@
         <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K9">
-        <v>0.5406137321372756</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.986639488171212</v>
+        <v>0.3703547186083788</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="O9" t="s">
         <v>71</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q9">
-        <v>0.8851534330343189</v>
+        <v>1</v>
       </c>
       <c r="R9">
-        <v>6.74283</v>
+        <v>9.130549999999999</v>
       </c>
       <c r="S9">
-        <v>6.709549126017258</v>
+        <v>9.109491328372108</v>
       </c>
       <c r="T9">
-        <v>6.69532435662535</v>
+        <v>8.99833753534821</v>
       </c>
       <c r="U9">
-        <v>6.74283</v>
+        <v>9.130549999999999</v>
       </c>
       <c r="V9">
-        <v>6.708539999999999</v>
+        <v>9.242009999999999</v>
       </c>
       <c r="W9">
-        <v>6.709549126017258</v>
+        <v>9.109491328372108</v>
       </c>
       <c r="X9">
-        <v>6.770755</v>
+        <v>9.213339999999999</v>
       </c>
       <c r="Y9">
-        <v>-0.004935742704879362</v>
+        <v>-0.002306396835666099</v>
       </c>
       <c r="Z9">
-        <v>1.191794950142926</v>
+        <v>0.2543625030546088</v>
       </c>
       <c r="AA9">
-        <v>0.004935742704879362</v>
+        <v>0.002306396835666099</v>
       </c>
       <c r="AB9">
-        <v>0.4425720199109779</v>
+        <v>0.4547814825937937</v>
       </c>
       <c r="AC9">
-        <v>0.2</v>
+        <v>0.1946971728536392</v>
       </c>
       <c r="AD9">
-        <v>0.3574279800890221</v>
+        <v>0.3505213445525671</v>
       </c>
       <c r="AE9" t="s">
         <v>83</v>
@@ -1965,46 +1977,46 @@
         <v>100</v>
       </c>
       <c r="AH9">
-        <v>442.5767165171595</v>
+        <v>500</v>
       </c>
       <c r="AI9">
-        <v>0.004141436162560887</v>
+        <v>0.009067361769006264</v>
       </c>
       <c r="AJ9">
-        <v>120731.065353624</v>
+        <v>55142.83125981389</v>
       </c>
       <c r="AK9">
-        <v>106865.516971651</v>
+        <v>55142.83125981389</v>
       </c>
       <c r="AL9">
-        <v>15848.7633488685</v>
+        <v>6039.376736320801</v>
       </c>
       <c r="AM9">
-        <v>1068.65516971651</v>
+        <v>551.4283125981389</v>
       </c>
       <c r="AN9">
-        <v>0.0106865516971651</v>
+        <v>0.005514283125981389</v>
       </c>
       <c r="AO9">
-        <v>442.5767165171595</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>0.004425767165171595</v>
+        <v>0.005</v>
       </c>
       <c r="AQ9">
-        <v>0.07863457666054392</v>
+        <v>0.09265563721517393</v>
       </c>
       <c r="AR9">
-        <v>0.003106643801273546</v>
+        <v>0.02420217711770799</v>
       </c>
       <c r="AS9">
-        <v>0.0146249871311321</v>
+        <v>0.02434479053511114</v>
       </c>
       <c r="AT9">
         <v>1</v>
       </c>
       <c r="AU9">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV9" t="s">
         <v>87</v>
@@ -2016,7 +2028,7 @@
         <v>89</v>
       </c>
       <c r="AY9" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="10" spans="1:51">
@@ -2024,7 +2036,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2036,7 +2048,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" t="s">
         <v>68</v>
@@ -2048,22 +2060,22 @@
         <v>69</v>
       </c>
       <c r="J10" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0.2890510674624616</v>
+        <v>0.03220786753094879</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P10" t="s">
         <v>75</v>
@@ -2072,43 +2084,43 @@
         <v>1</v>
       </c>
       <c r="R10">
-        <v>9.12504</v>
+        <v>7.8064</v>
       </c>
       <c r="S10">
-        <v>9.074294698805637</v>
+        <v>7.784317326789372</v>
       </c>
       <c r="T10">
-        <v>8.979340003391242</v>
+        <v>7.672814980547543</v>
       </c>
       <c r="U10">
-        <v>9.12504</v>
+        <v>7.8064</v>
       </c>
       <c r="V10">
-        <v>9.131500000000001</v>
+        <v>7.9155</v>
       </c>
       <c r="W10">
-        <v>9.074294698805637</v>
+        <v>7.784317326789372</v>
       </c>
       <c r="X10">
-        <v>9.2128725</v>
+        <v>7.867249999999999</v>
       </c>
       <c r="Y10">
-        <v>-0.005561104520567891</v>
+        <v>-0.00282879089088797</v>
       </c>
       <c r="Z10">
-        <v>0.5777508461487828</v>
+        <v>0.3629034217030084</v>
       </c>
       <c r="AA10">
-        <v>0.005561104520567891</v>
+        <v>0.00282879089088797</v>
       </c>
       <c r="AB10">
-        <v>0.3674638698772487</v>
+        <v>0.4506362751906631</v>
       </c>
       <c r="AC10">
         <v>0.2</v>
       </c>
       <c r="AD10">
-        <v>0.4325361301227513</v>
+        <v>0.3493637248093369</v>
       </c>
       <c r="AE10" t="s">
         <v>84</v>
@@ -2123,22 +2135,22 @@
         <v>500</v>
       </c>
       <c r="AI10">
-        <v>0.009625437258357197</v>
+        <v>0.007794886247181723</v>
       </c>
       <c r="AJ10">
-        <v>51945.69208436527</v>
+        <v>64144.6179129012</v>
       </c>
       <c r="AK10">
-        <v>51945.69208436527</v>
+        <v>64144.6179129012</v>
       </c>
       <c r="AL10">
-        <v>5692.653630489868</v>
+        <v>8216.926869350944</v>
       </c>
       <c r="AM10">
-        <v>519.4569208436527</v>
+        <v>641.446179129012</v>
       </c>
       <c r="AN10">
-        <v>0.005194569208436527</v>
+        <v>0.00641446179129012</v>
       </c>
       <c r="AO10">
         <v>500</v>
@@ -2147,19 +2159,19 @@
         <v>0.005</v>
       </c>
       <c r="AQ10">
-        <v>0.09915823314272079</v>
+        <v>0.09451762042150039</v>
       </c>
       <c r="AR10">
-        <v>0.01520649956493937</v>
+        <v>0.0185535982280629</v>
       </c>
       <c r="AS10">
-        <v>0.01707514047578092</v>
+        <v>0.03184693421590027</v>
       </c>
       <c r="AT10">
         <v>1</v>
       </c>
       <c r="AU10">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV10" t="s">
         <v>87</v>
@@ -2171,7 +2183,7 @@
         <v>89</v>
       </c>
       <c r="AY10" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="11" spans="1:51">
@@ -2179,7 +2191,7 @@
         <v>60</v>
       </c>
       <c r="B11" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -2203,67 +2215,67 @@
         <v>69</v>
       </c>
       <c r="J11" s="2">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.2206760510344554</v>
       </c>
       <c r="L11">
-        <v>0.006680900891693144</v>
+        <v>1.257784563326133</v>
       </c>
       <c r="M11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P11" t="s">
         <v>75</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.8344929617241584</v>
       </c>
       <c r="R11">
-        <v>7.8025</v>
+        <v>1.15778</v>
       </c>
       <c r="S11">
-        <v>7.739930980519032</v>
+        <v>1.148981084756681</v>
       </c>
       <c r="T11">
-        <v>7.58953563756701</v>
+        <v>1.119442986245173</v>
       </c>
       <c r="U11">
-        <v>7.8025</v>
+        <v>1.15778</v>
       </c>
       <c r="V11">
-        <v>7.851500000000001</v>
+        <v>1.17625</v>
       </c>
       <c r="W11">
-        <v>7.739930980519032</v>
+        <v>1.148981084756681</v>
       </c>
       <c r="X11">
-        <v>7.865425</v>
+        <v>1.17078</v>
       </c>
       <c r="Y11">
-        <v>-0.008019098940207347</v>
+        <v>-0.007599816237384664</v>
       </c>
       <c r="Z11">
-        <v>0.9943427807861376</v>
+        <v>0.6768396341014776</v>
       </c>
       <c r="AA11">
-        <v>0.008019098940207347</v>
+        <v>0.007599816237384664</v>
       </c>
       <c r="AB11">
-        <v>0.3884842141724555</v>
+        <v>0.4150000798328546</v>
       </c>
       <c r="AC11">
         <v>0.2</v>
       </c>
       <c r="AD11">
-        <v>0.4115157858275446</v>
+        <v>0.3849999201671455</v>
       </c>
       <c r="AE11" t="s">
         <v>85</v>
@@ -2275,46 +2287,46 @@
         <v>100</v>
       </c>
       <c r="AH11">
-        <v>500</v>
+        <v>417.2464808620792</v>
       </c>
       <c r="AI11">
-        <v>0.008064722845241925</v>
+        <v>0.0112283853581855</v>
       </c>
       <c r="AJ11">
-        <v>61998.41080651557</v>
+        <v>44529.99999999996</v>
       </c>
       <c r="AK11">
-        <v>61998.41080651557</v>
+        <v>37159.97158557674</v>
       </c>
       <c r="AL11">
-        <v>7945.967421533556</v>
+        <v>32095.88314323684</v>
       </c>
       <c r="AM11">
-        <v>619.9841080651557</v>
+        <v>371.5997158557674</v>
       </c>
       <c r="AN11">
-        <v>0.006199841080651558</v>
+        <v>0.003715997158557674</v>
       </c>
       <c r="AO11">
-        <v>500</v>
+        <v>417.2464808620792</v>
       </c>
       <c r="AP11">
-        <v>0.005</v>
+        <v>0.004172464808620792</v>
       </c>
       <c r="AQ11">
-        <v>0.09976110798935797</v>
+        <v>0.01371065096530527</v>
       </c>
       <c r="AR11">
-        <v>0.007746326352123775</v>
+        <v>0.00300200900334056</v>
       </c>
       <c r="AS11">
-        <v>0.01436688009834949</v>
+        <v>0.007218716892197261</v>
       </c>
       <c r="AT11">
         <v>1</v>
       </c>
       <c r="AU11">
-        <v>0.03834815313439202</v>
+        <v>0.04250144749668916</v>
       </c>
       <c r="AV11" t="s">
         <v>87</v>
@@ -2326,7 +2338,7 @@
         <v>89</v>
       </c>
       <c r="AY11" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -169,6 +241,15 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
@@ -178,24 +259,15 @@
     <t>USDJPY</t>
   </si>
   <si>
-    <t>AUDUSD</t>
+    <t>AUDCNH</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
     <t>EURUSD</t>
   </si>
   <si>
@@ -205,12 +277,12 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
@@ -229,13 +301,13 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>ALIGNED</t>
+  </si>
+  <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
+    <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -244,34 +316,88 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.0401,naive=0.00935,drift4=0.01187; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=979.9,naive=366.3,drift4=451.8; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.58,naive=0.20,drift4=0.22); metric_best=model; scores=model=1.832,naive=3.473,drift4=8.154; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.04386,naive=0.007983,drift4=0.005043; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1362,naive=0.01402,drift4=0.03125; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.18,drift4=0.50); metric_best=drift4; scores=model=0.1231,naive=0.05909,drift4=0.01769</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.02991,naive=0.007195,drift4=0.005234; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.19,drift4=0.35); metric_best=drift4; scores=model=0.03823,naive=0.05742,drift4=0.03427</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.07669,naive=0.05371,drift4=0.06191; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.02535,naive=0.008568,drift4=0.01138; naive_cap_applied</t>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.1059,naive=0.03461,drift4=0.01925; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.28,naive=0.13,drift4=0.58); metric_best=drift4; scores=model=0.2046,naive=0.028,drift4=0.00368</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.0379,naive=0.007614,drift4=0.005342; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.02602,naive=0.004095,drift4=0.01266; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=657.6,naive=359.4,drift4=450.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.59,naive=0.20,drift4=0.21); metric_best=model; scores=model=1.633,naive=3.079,drift4=8.237; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.18,drift4=0.50); metric_best=drift4; scores=model=0.1235,naive=0.05875,drift4=0.01734</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.102,naive=0.005594,drift4=0.03398; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.20,drift4=0.47); metric_best=drift4; scores=model=0.02184,naive=0.007663,drift4=0.003674; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.02446,naive=0.003666,drift4=0.009557; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -645,10 +771,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,10 +928,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46252</v>
@@ -814,141 +1012,213 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46251</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1.737494928074045</v>
+        <v>0.3703547186083788</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>1.35278</v>
-      </c>
-      <c r="S2">
-        <v>1.34149626798056</v>
+      <c r="R2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" t="s">
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>1.305172311481587</v>
+        <v>0.8731485607573917</v>
       </c>
       <c r="U2">
-        <v>1.35278</v>
-      </c>
-      <c r="V2">
-        <v>1.37099</v>
+        <v>0.7928641254523829</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>95</v>
+      </c>
+      <c r="X2">
+        <v>0.9997890924462272</v>
       </c>
       <c r="Y2">
-        <v>-0.008341143437543672</v>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>51.06378098372646</v>
       </c>
       <c r="AA2">
-        <v>0.008341143437543672</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="AB2">
-        <v>0.3927778778224338</v>
+        <v>0.6284548916177507</v>
       </c>
       <c r="AC2">
+        <v>0.7778460318094585</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>0.3141611728669515</v>
+      </c>
+      <c r="AI2">
+        <v>0.6803251987760545</v>
+      </c>
+      <c r="AJ2">
+        <v>0.2989568369274301</v>
+      </c>
+      <c r="AK2">
+        <v>0.3683537187593863</v>
+      </c>
+      <c r="AL2">
+        <v>0.3782439206868265</v>
+      </c>
+      <c r="AM2">
+        <v>-0.6540304117206963</v>
+      </c>
+      <c r="AN2">
+        <v>0.31255891441515</v>
+      </c>
+      <c r="AO2">
+        <v>0.05424967376966801</v>
+      </c>
+      <c r="AP2">
+        <v>9.130549999999999</v>
+      </c>
+      <c r="AQ2">
+        <v>9.138948235659683</v>
+      </c>
+      <c r="AR2">
+        <v>9.006046534813606</v>
+      </c>
+      <c r="AS2">
+        <v>9.130549999999999</v>
+      </c>
+      <c r="AT2">
+        <v>9.242009999999999</v>
+      </c>
+      <c r="AW2">
+        <v>0.0009197951557883645</v>
+      </c>
+      <c r="AY2">
+        <v>0.0009197951557883645</v>
+      </c>
+      <c r="AZ2">
+        <v>0.3422977547668842</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.4072221221775662</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="BB2">
+        <v>0.4577022452331159</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
+        <v>100000</v>
+      </c>
+      <c r="BE2">
+        <v>100</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0.0893677526326985</v>
+      </c>
+      <c r="BP2">
+        <v>0.01524989365012512</v>
+      </c>
+      <c r="BQ2">
+        <v>0.02257380707097189</v>
+      </c>
+      <c r="BR2">
+        <v>1</v>
+      </c>
+      <c r="BS2">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75">
+      <c r="A3" t="s">
         <v>76</v>
-      </c>
-      <c r="AF2">
-        <v>100000</v>
-      </c>
-      <c r="AG2">
-        <v>100</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0.0194400831123135</v>
-      </c>
-      <c r="AR2">
-        <v>0.003534007759882105</v>
-      </c>
-      <c r="AS2">
-        <v>0.005491703541461885</v>
-      </c>
-      <c r="AT2">
-        <v>1</v>
-      </c>
-      <c r="AU2">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51">
-      <c r="A3" t="s">
-        <v>52</v>
       </c>
       <c r="B3" s="2">
         <v>46252</v>
@@ -957,22 +1227,22 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46251</v>
@@ -981,129 +1251,189 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.412807215284729</v>
+        <v>0.03220786753094879</v>
       </c>
       <c r="M3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O3" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
-      </c>
-      <c r="R3">
-        <v>4394.049999999999</v>
-      </c>
-      <c r="S3">
-        <v>4541.796045950049</v>
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" t="s">
+        <v>104</v>
       </c>
       <c r="T3">
-        <v>4426.594967381598</v>
+        <v>0.7289133392759884</v>
       </c>
       <c r="U3">
-        <v>4394.049999999999</v>
-      </c>
-      <c r="V3">
-        <v>4742.209999999999</v>
-      </c>
-      <c r="W3">
-        <v>4541.796045950049</v>
+        <v>0.7029458061879691</v>
+      </c>
+      <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>4255.23</v>
+        <v>0.999739214055097</v>
       </c>
       <c r="Y3">
-        <v>0.03362411578157961</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>1.064299423354348</v>
+        <v>75.64483922883329</v>
       </c>
       <c r="AA3">
-        <v>0.03362411578157961</v>
+        <v>28.00000000000001</v>
       </c>
       <c r="AB3">
-        <v>0.4143717520834128</v>
+        <v>0.2479318054822442</v>
       </c>
       <c r="AC3">
-        <v>0.2</v>
-      </c>
-      <c r="AD3">
-        <v>0.3856282479165873</v>
+        <v>0.9687774872643948</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>93</v>
       </c>
       <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH3">
+        <v>0.12393357417604</v>
+      </c>
+      <c r="AI3">
+        <v>0.5617788967378223</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1575054069166227</v>
+      </c>
+      <c r="AK3">
+        <v>0.4674529910839584</v>
+      </c>
+      <c r="AL3">
+        <v>-0.1615767030443017</v>
+      </c>
+      <c r="AM3">
+        <v>-0.8461372672257448</v>
+      </c>
+      <c r="AN3">
+        <v>0.2737077062555696</v>
+      </c>
+      <c r="AO3">
+        <v>0.08339579884089887</v>
+      </c>
+      <c r="AP3">
+        <v>7.8064</v>
+      </c>
+      <c r="AQ3">
+        <v>7.810316493620118</v>
+      </c>
+      <c r="AR3">
+        <v>7.594584225819412</v>
+      </c>
+      <c r="AS3">
+        <v>7.8064</v>
+      </c>
+      <c r="AT3">
+        <v>7.9155</v>
+      </c>
+      <c r="AW3">
+        <v>0.0005017029130096289</v>
+      </c>
+      <c r="AY3">
+        <v>0.0005017029130096289</v>
+      </c>
+      <c r="AZ3">
+        <v>0.2828257766303852</v>
+      </c>
+      <c r="BA3">
+        <v>0.1321746408278194</v>
+      </c>
+      <c r="BB3">
+        <v>0.5849995825417953</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
+        <v>100000</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0.1159426554894266</v>
+      </c>
+      <c r="BP3">
+        <v>0.007451440754683148</v>
+      </c>
+      <c r="BQ3">
+        <v>0.02364445582469049</v>
+      </c>
+      <c r="BR3">
+        <v>1</v>
+      </c>
+      <c r="BS3">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:75">
+      <c r="A4" t="s">
         <v>77</v>
-      </c>
-      <c r="AF3">
-        <v>100000</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>375</v>
-      </c>
-      <c r="AI3">
-        <v>0.0315927219763087</v>
-      </c>
-      <c r="AJ3">
-        <v>15826.42990923506</v>
-      </c>
-      <c r="AK3">
-        <v>11869.8224319263</v>
-      </c>
-      <c r="AL3">
-        <v>2.701339864572843</v>
-      </c>
-      <c r="AM3">
-        <v>118.698224319263</v>
-      </c>
-      <c r="AN3">
-        <v>0.00118698224319263</v>
-      </c>
-      <c r="AO3">
-        <v>375</v>
-      </c>
-      <c r="AP3">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ3">
-        <v>410.0278586899465</v>
-      </c>
-      <c r="AR3">
-        <v>125.8248861946142</v>
-      </c>
-      <c r="AS3">
-        <v>170.0538416004675</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51">
-      <c r="A4" t="s">
-        <v>53</v>
       </c>
       <c r="B4" s="2">
         <v>46252</v>
@@ -1112,22 +1442,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
         <v>46251</v>
@@ -1136,129 +1466,189 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0.9408225092317056</v>
+        <v>1.402135618629374</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S4" t="s">
+        <v>104</v>
+      </c>
+      <c r="T4">
+        <v>0.8941983235748435</v>
+      </c>
+      <c r="U4">
+        <v>0.8023856606986273</v>
+      </c>
+      <c r="V4" t="s">
+        <v>93</v>
+      </c>
+      <c r="W4" t="s">
+        <v>95</v>
+      </c>
+      <c r="X4">
+        <v>0.9999856603597906</v>
+      </c>
+      <c r="Y4">
+        <v>0.2774543884003051</v>
+      </c>
+      <c r="Z4">
+        <v>40.57662685848407</v>
+      </c>
+      <c r="AA4">
+        <v>4.000000000000005</v>
+      </c>
+      <c r="AB4">
+        <v>0.7595367198632174</v>
+      </c>
+      <c r="AC4">
+        <v>0.6504644272974691</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH4">
+        <v>0.4851298012836585</v>
+      </c>
+      <c r="AI4">
+        <v>0.7760299076337183</v>
+      </c>
+      <c r="AJ4">
+        <v>1.099228157262111</v>
+      </c>
+      <c r="AK4">
+        <v>0.9258578958991305</v>
+      </c>
+      <c r="AL4">
+        <v>1.567559854865407</v>
+      </c>
+      <c r="AM4">
+        <v>-1.647271930834391</v>
+      </c>
+      <c r="AN4">
+        <v>1.419288914767426</v>
+      </c>
+      <c r="AO4">
+        <v>0.04877978087489713</v>
+      </c>
+      <c r="AP4">
+        <v>0.711045</v>
+      </c>
+      <c r="AQ4">
+        <v>0.7110834754240585</v>
+      </c>
+      <c r="AR4">
+        <v>0.6965497206808055</v>
+      </c>
+      <c r="AS4">
+        <v>0.711045</v>
+      </c>
+      <c r="AT4">
+        <v>0.721905</v>
+      </c>
+      <c r="AW4">
+        <v>5.411109572310795E-05</v>
+      </c>
+      <c r="AY4">
+        <v>5.411109572310795E-05</v>
+      </c>
+      <c r="AZ4">
+        <v>0.3411330818743427</v>
+      </c>
+      <c r="BA4">
+        <v>0.2</v>
+      </c>
+      <c r="BB4">
+        <v>0.4588669181256574</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
+        <v>100000</v>
+      </c>
+      <c r="BE4">
+        <v>100</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0.01098637747502856</v>
+      </c>
+      <c r="BP4">
+        <v>0.002345551734641277</v>
+      </c>
+      <c r="BQ4">
+        <v>0.003726374992324056</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>159.676</v>
-      </c>
-      <c r="S4">
-        <v>161.8316596777024</v>
-      </c>
-      <c r="T4">
-        <v>164.9119908332137</v>
-      </c>
-      <c r="U4">
-        <v>159.676</v>
-      </c>
-      <c r="V4">
-        <v>155.72</v>
-      </c>
-      <c r="W4">
-        <v>161.8316596777024</v>
-      </c>
-      <c r="X4">
-        <v>158.2388935481983</v>
-      </c>
-      <c r="Y4">
-        <v>0.01350021091273867</v>
-      </c>
-      <c r="Z4">
-        <v>1.5</v>
-      </c>
-      <c r="AA4">
-        <v>0.01350021091273867</v>
-      </c>
-      <c r="AB4">
-        <v>0.5788147284131155</v>
-      </c>
-      <c r="AC4">
-        <v>0.2</v>
-      </c>
-      <c r="AD4">
-        <v>0.2211852715868845</v>
-      </c>
-      <c r="AE4" t="s">
+      <c r="BS4">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:75">
+      <c r="A5" t="s">
         <v>78</v>
-      </c>
-      <c r="AF4">
-        <v>100000</v>
-      </c>
-      <c r="AG4">
-        <v>100</v>
-      </c>
-      <c r="AH4">
-        <v>500</v>
-      </c>
-      <c r="AI4">
-        <v>0.009000140608492446</v>
-      </c>
-      <c r="AJ4">
-        <v>55554.68761545845</v>
-      </c>
-      <c r="AK4">
-        <v>55554.68761545845</v>
-      </c>
-      <c r="AL4">
-        <v>347.9213383066864</v>
-      </c>
-      <c r="AM4">
-        <v>555.5468761545845</v>
-      </c>
-      <c r="AN4">
-        <v>0.005555468761545846</v>
-      </c>
-      <c r="AO4">
-        <v>500</v>
-      </c>
-      <c r="AP4">
-        <v>0.005</v>
-      </c>
-      <c r="AQ4">
-        <v>3.470121160228256</v>
-      </c>
-      <c r="AR4">
-        <v>1.487563435597712</v>
-      </c>
-      <c r="AS4">
-        <v>3.658012239705288</v>
-      </c>
-      <c r="AT4">
-        <v>1</v>
-      </c>
-      <c r="AU4">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51">
-      <c r="A5" t="s">
-        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>46252</v>
@@ -1267,153 +1657,213 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
         <v>46251</v>
       </c>
       <c r="K5">
-        <v>0.006645056466970206</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.41741649865742</v>
+        <v>1.71029155165915</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="Q5">
-        <v>0.7516612641167425</v>
-      </c>
-      <c r="R5">
-        <v>0.711045</v>
-      </c>
-      <c r="S5">
-        <v>0.7163180033516041</v>
+        <v>0</v>
+      </c>
+      <c r="R5" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" t="s">
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>0.7115881121532946</v>
+        <v>0.9572648565156808</v>
       </c>
       <c r="U5">
-        <v>0.711045</v>
-      </c>
-      <c r="V5">
-        <v>0.721905</v>
-      </c>
-      <c r="W5">
-        <v>0.7163180033516041</v>
+        <v>0.9807243820935768</v>
+      </c>
+      <c r="V5" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" t="s">
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.703345</v>
+        <v>0.9998207866460816</v>
       </c>
       <c r="Y5">
-        <v>0.007415850405535623</v>
+        <v>0.8346070215056901</v>
       </c>
       <c r="Z5">
-        <v>0.6848056300784456</v>
+        <v>24.58108740811132</v>
       </c>
       <c r="AA5">
-        <v>0.007415850405535623</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB5">
-        <v>0.3310103491613006</v>
+        <v>0.909373468387829</v>
       </c>
       <c r="AC5">
+        <v>0.4159806425692069</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH5">
+        <v>0.8340219804698444</v>
+      </c>
+      <c r="AI5">
+        <v>0.933717606774047</v>
+      </c>
+      <c r="AJ5">
+        <v>1.35560633773079</v>
+      </c>
+      <c r="AK5">
+        <v>0.6492638207534683</v>
+      </c>
+      <c r="AL5">
+        <v>1.878176486453671</v>
+      </c>
+      <c r="AM5">
+        <v>-2.861229809167674</v>
+      </c>
+      <c r="AN5">
+        <v>1.610078382001936</v>
+      </c>
+      <c r="AO5">
+        <v>0.03968742246378829</v>
+      </c>
+      <c r="AP5">
+        <v>1.35278</v>
+      </c>
+      <c r="AQ5">
+        <v>1.351775947525975</v>
+      </c>
+      <c r="AR5">
+        <v>1.336149203501108</v>
+      </c>
+      <c r="AS5">
+        <v>1.35278</v>
+      </c>
+      <c r="AT5">
+        <v>1.37099</v>
+      </c>
+      <c r="AW5">
+        <v>-0.0007422141619665651</v>
+      </c>
+      <c r="AY5">
+        <v>0.0007422141619665651</v>
+      </c>
+      <c r="AZ5">
+        <v>0.4469488082604662</v>
+      </c>
+      <c r="BA5">
         <v>0.2</v>
       </c>
-      <c r="AD5">
-        <v>0.4689896508386994</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="BB5">
+        <v>0.3530511917395338</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
+        <v>100000</v>
+      </c>
+      <c r="BE5">
+        <v>100</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0.01434228429662115</v>
+      </c>
+      <c r="BP5">
+        <v>0.001794025580280825</v>
+      </c>
+      <c r="BQ5">
+        <v>0.00550282774930166</v>
+      </c>
+      <c r="BR5">
+        <v>1</v>
+      </c>
+      <c r="BS5">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:75">
+      <c r="A6" t="s">
         <v>79</v>
-      </c>
-      <c r="AF5">
-        <v>100000</v>
-      </c>
-      <c r="AG5">
-        <v>100</v>
-      </c>
-      <c r="AH5">
-        <v>375.8306320583712</v>
-      </c>
-      <c r="AI5">
-        <v>0.01082913177084441</v>
-      </c>
-      <c r="AJ5">
-        <v>46171.75324675284</v>
-      </c>
-      <c r="AK5">
-        <v>34705.51841194055</v>
-      </c>
-      <c r="AL5">
-        <v>48809.17299459324</v>
-      </c>
-      <c r="AM5">
-        <v>347.0551841194055</v>
-      </c>
-      <c r="AN5">
-        <v>0.003470551841194055</v>
-      </c>
-      <c r="AO5">
-        <v>375.8306320583712</v>
-      </c>
-      <c r="AP5">
-        <v>0.003758306320583712</v>
-      </c>
-      <c r="AQ5">
-        <v>0.01376090134018822</v>
-      </c>
-      <c r="AR5">
-        <v>0.002950149996103246</v>
-      </c>
-      <c r="AS5">
-        <v>0.003833995718258926</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51">
-      <c r="A6" t="s">
-        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>46252</v>
@@ -1422,153 +1872,225 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
         <v>46251</v>
       </c>
       <c r="K6">
-        <v>0.5259359401337355</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2.972216273968399</v>
+        <v>1.420548297286022</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.6055480448996984</v>
-      </c>
-      <c r="R6">
-        <v>6.74544</v>
-      </c>
-      <c r="S6">
-        <v>6.787216888287275</v>
+        <v>0.75</v>
+      </c>
+      <c r="R6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>104</v>
       </c>
       <c r="T6">
-        <v>6.873152267607372</v>
+        <v>0.7527343615871123</v>
       </c>
       <c r="U6">
-        <v>6.74544</v>
-      </c>
-      <c r="V6">
-        <v>6.718680000000001</v>
-      </c>
-      <c r="W6">
-        <v>6.787216888287275</v>
+        <v>0.7385681805198869</v>
+      </c>
+      <c r="V6" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" t="s">
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>6.717515</v>
+        <v>0.9993508712227458</v>
       </c>
       <c r="Y6">
-        <v>0.006193352588900715</v>
+        <v>0.7987276276273882</v>
       </c>
       <c r="Z6">
-        <v>1.496038971791363</v>
+        <v>55.9038704580633</v>
       </c>
       <c r="AA6">
-        <v>0.006193352588900715</v>
+        <v>-12.99999999999999</v>
       </c>
       <c r="AB6">
-        <v>0.4090370994479942</v>
+        <v>0.560583055956321</v>
       </c>
       <c r="AC6">
+        <v>0.8280982051512202</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH6">
+        <v>0.5038408451320852</v>
+      </c>
+      <c r="AI6">
+        <v>0.8199254261792034</v>
+      </c>
+      <c r="AJ6">
+        <v>1.162943351370415</v>
+      </c>
+      <c r="AK6">
+        <v>1.850147974732233</v>
+      </c>
+      <c r="AL6">
+        <v>1.39891718585439</v>
+      </c>
+      <c r="AM6">
+        <v>-3.219612874010256</v>
+      </c>
+      <c r="AN6">
+        <v>1.159805481398617</v>
+      </c>
+      <c r="AO6">
+        <v>0.05178547374087741</v>
+      </c>
+      <c r="AP6">
+        <v>4394.049999999999</v>
+      </c>
+      <c r="AQ6">
+        <v>4476.738452331235</v>
+      </c>
+      <c r="AR6">
+        <v>4297.301254516171</v>
+      </c>
+      <c r="AS6">
+        <v>4394.049999999999</v>
+      </c>
+      <c r="AT6">
+        <v>4742.209999999999</v>
+      </c>
+      <c r="AU6">
+        <v>4476.738452331235</v>
+      </c>
+      <c r="AV6">
+        <v>4255.23</v>
+      </c>
+      <c r="AW6">
+        <v>0.01881827751874366</v>
+      </c>
+      <c r="AX6">
+        <v>0.5956523003258609</v>
+      </c>
+      <c r="AY6">
+        <v>0.01881827751874366</v>
+      </c>
+      <c r="AZ6">
+        <v>0.4401791370852768</v>
+      </c>
+      <c r="BA6">
         <v>0.2</v>
       </c>
-      <c r="AD6">
-        <v>0.3909629005520059</v>
-      </c>
-      <c r="AE6" t="s">
+      <c r="BB6">
+        <v>0.3598208629147232</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
+        <v>100000</v>
+      </c>
+      <c r="BE6">
+        <v>100</v>
+      </c>
+      <c r="BF6">
+        <v>375</v>
+      </c>
+      <c r="BG6">
+        <v>0.0315927219763087</v>
+      </c>
+      <c r="BH6">
+        <v>15826.42990923506</v>
+      </c>
+      <c r="BI6">
+        <v>11869.8224319263</v>
+      </c>
+      <c r="BJ6">
+        <v>2.701339864572843</v>
+      </c>
+      <c r="BK6">
+        <v>118.698224319263</v>
+      </c>
+      <c r="BL6">
+        <v>0.00118698224319263</v>
+      </c>
+      <c r="BM6">
+        <v>375</v>
+      </c>
+      <c r="BN6">
+        <v>0.00375</v>
+      </c>
+      <c r="BO6">
+        <v>330.5540985149648</v>
+      </c>
+      <c r="BP6">
+        <v>96.17042832511125</v>
+      </c>
+      <c r="BQ6">
+        <v>155.9030163635073</v>
+      </c>
+      <c r="BR6">
+        <v>1</v>
+      </c>
+      <c r="BS6">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="7" spans="1:75">
+      <c r="A7" t="s">
         <v>80</v>
-      </c>
-      <c r="AF6">
-        <v>100000</v>
-      </c>
-      <c r="AG6">
-        <v>100</v>
-      </c>
-      <c r="AH6">
-        <v>302.7740224498492</v>
-      </c>
-      <c r="AI6">
-        <v>0.004139833724708903</v>
-      </c>
-      <c r="AJ6">
-        <v>120777.7976723348</v>
-      </c>
-      <c r="AK6">
-        <v>73136.75924777366</v>
-      </c>
-      <c r="AL6">
-        <v>10842.40008772944</v>
-      </c>
-      <c r="AM6">
-        <v>731.3675924777366</v>
-      </c>
-      <c r="AN6">
-        <v>0.007313675924777366</v>
-      </c>
-      <c r="AO6">
-        <v>302.7740224498492</v>
-      </c>
-      <c r="AP6">
-        <v>0.003027740224498492</v>
-      </c>
-      <c r="AQ6">
-        <v>0.08649082966536599</v>
-      </c>
-      <c r="AR6">
-        <v>0.005318272183201098</v>
-      </c>
-      <c r="AS6">
-        <v>0.0202704863066463</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51">
-      <c r="A7" t="s">
-        <v>56</v>
       </c>
       <c r="B7" s="2">
         <v>46252</v>
@@ -1577,22 +2099,22 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
         <v>46251</v>
@@ -1601,129 +2123,201 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.2815296005162526</v>
+        <v>0.768059346761379</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
-      </c>
-      <c r="R7">
-        <v>4.78877</v>
-      </c>
-      <c r="S7">
-        <v>4.811486426119327</v>
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>101</v>
+      </c>
+      <c r="S7" t="s">
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>4.762614864271115</v>
+        <v>-0.8904545610530479</v>
       </c>
       <c r="U7">
-        <v>4.78877</v>
-      </c>
-      <c r="V7">
-        <v>4.851640000000001</v>
-      </c>
-      <c r="W7">
-        <v>4.811486426119327</v>
+        <v>0.8002187525616534</v>
+      </c>
+      <c r="V7" t="s">
+        <v>94</v>
+      </c>
+      <c r="W7" t="s">
+        <v>95</v>
       </c>
       <c r="X7">
-        <v>4.753922500000001</v>
+        <v>0.9980568003511275</v>
       </c>
       <c r="Y7">
-        <v>0.004743687025964172</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>0.6518810852809097</v>
+        <v>132.7481492757411</v>
       </c>
       <c r="AA7">
-        <v>0.004743687025964172</v>
+        <v>-49</v>
       </c>
       <c r="AB7">
-        <v>0.3248113188497139</v>
+        <v>-0.6787770256571848</v>
       </c>
       <c r="AC7">
-        <v>0.1787371104469427</v>
-      </c>
-      <c r="AD7">
-        <v>0.4964515707033433</v>
+        <v>0.7343444351528685</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH7">
+        <v>-0.3387290131896325</v>
+      </c>
+      <c r="AI7">
+        <v>0.6956222769524339</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.7155230982697569</v>
+      </c>
+      <c r="AK7">
+        <v>0.6410500375643496</v>
+      </c>
+      <c r="AL7">
+        <v>-0.3756824104071136</v>
+      </c>
+      <c r="AM7">
+        <v>2.745967919669226</v>
+      </c>
+      <c r="AN7">
+        <v>0.3989677030250876</v>
+      </c>
+      <c r="AO7">
+        <v>0.04887140578410751</v>
+      </c>
+      <c r="AP7">
+        <v>159.676</v>
+      </c>
+      <c r="AQ7">
+        <v>160.3521748809567</v>
+      </c>
+      <c r="AR7">
+        <v>162.2856910118654</v>
+      </c>
+      <c r="AS7">
+        <v>159.676</v>
+      </c>
+      <c r="AT7">
+        <v>155.72</v>
+      </c>
+      <c r="AU7">
+        <v>160.3521748809567</v>
+      </c>
+      <c r="AV7">
+        <v>158.5125</v>
+      </c>
+      <c r="AW7">
+        <v>0.004234668209103126</v>
+      </c>
+      <c r="AX7">
+        <v>0.5811558925283566</v>
+      </c>
+      <c r="AY7">
+        <v>0.004234668209103126</v>
+      </c>
+      <c r="AZ7">
+        <v>0.5850069511366587</v>
+      </c>
+      <c r="BA7">
+        <v>0.2</v>
+      </c>
+      <c r="BB7">
+        <v>0.2149930488633415</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
+        <v>100000</v>
+      </c>
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>500</v>
+      </c>
+      <c r="BG7">
+        <v>0.007286630426613977</v>
+      </c>
+      <c r="BH7">
+        <v>68618.82251826307</v>
+      </c>
+      <c r="BI7">
+        <v>68618.82251826307</v>
+      </c>
+      <c r="BJ7">
+        <v>429.7378599054528</v>
+      </c>
+      <c r="BK7">
+        <v>686.1882251826307</v>
+      </c>
+      <c r="BL7">
+        <v>0.006861882251826307</v>
+      </c>
+      <c r="BM7">
+        <v>500.0000000000001</v>
+      </c>
+      <c r="BN7">
+        <v>0.005000000000000001</v>
+      </c>
+      <c r="BO7">
+        <v>2.762397276157257</v>
+      </c>
+      <c r="BP7">
+        <v>0.9629604675052154</v>
+      </c>
+      <c r="BQ7">
+        <v>2.954874091896178</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
+      <c r="BS7">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:75">
+      <c r="A8" t="s">
         <v>81</v>
-      </c>
-      <c r="AF7">
-        <v>100000</v>
-      </c>
-      <c r="AG7">
-        <v>100</v>
-      </c>
-      <c r="AH7">
-        <v>375</v>
-      </c>
-      <c r="AI7">
-        <v>0.007276920795945497</v>
-      </c>
-      <c r="AJ7">
-        <v>68710.38094554862</v>
-      </c>
-      <c r="AK7">
-        <v>51532.78570916146</v>
-      </c>
-      <c r="AL7">
-        <v>10761.1736853433</v>
-      </c>
-      <c r="AM7">
-        <v>515.3278570916146</v>
-      </c>
-      <c r="AN7">
-        <v>0.005153278570916147</v>
-      </c>
-      <c r="AO7">
-        <v>375</v>
-      </c>
-      <c r="AP7">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ7">
-        <v>0.04842918717924546</v>
-      </c>
-      <c r="AR7">
-        <v>0.01930343713516028</v>
-      </c>
-      <c r="AS7">
-        <v>0.01491546584374072</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51">
-      <c r="A8" t="s">
-        <v>57</v>
       </c>
       <c r="B8" s="2">
         <v>46252</v>
@@ -1732,153 +2326,225 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
         <v>46251</v>
       </c>
       <c r="K8">
-        <v>0.0599653482459717</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.12320607582844</v>
+        <v>0.2815296005162526</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q8">
-        <v>0.9550259888155213</v>
-      </c>
-      <c r="R8">
-        <v>0.812585</v>
-      </c>
-      <c r="S8">
-        <v>0.8109472750776768</v>
+        <v>0.75</v>
+      </c>
+      <c r="R8" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" t="s">
+        <v>104</v>
       </c>
       <c r="T8">
-        <v>0.8125349935902897</v>
+        <v>0.821020732103893</v>
       </c>
       <c r="U8">
-        <v>0.812585</v>
-      </c>
-      <c r="V8">
-        <v>0.8089850000000001</v>
-      </c>
-      <c r="W8">
-        <v>0.8109472750776768</v>
+        <v>0.7694260500042298</v>
+      </c>
+      <c r="V8" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" t="s">
+        <v>95</v>
       </c>
       <c r="X8">
-        <v>0.8218749999999999</v>
+        <v>0.9998668822299118</v>
       </c>
       <c r="Y8">
-        <v>-0.002015450595720041</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>0.1762890120907621</v>
+        <v>61.58851833686625</v>
       </c>
       <c r="AA8">
-        <v>0.002015450595720041</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB8">
-        <v>0.3499372734291125</v>
+        <v>0.4758004747819852</v>
       </c>
       <c r="AC8">
-        <v>0.2</v>
-      </c>
-      <c r="AD8">
-        <v>0.4500627265708875</v>
+        <v>0.8795532435260741</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH8">
+        <v>0.2378685686418877</v>
+      </c>
+      <c r="AI8">
+        <v>0.6325810595956984</v>
+      </c>
+      <c r="AJ8">
+        <v>0.2599542827254005</v>
+      </c>
+      <c r="AK8">
+        <v>0.4686621283756538</v>
+      </c>
+      <c r="AL8">
+        <v>0.3144538402450234</v>
+      </c>
+      <c r="AM8">
+        <v>-0.3663977492770994</v>
+      </c>
+      <c r="AN8">
+        <v>0.280137922763026</v>
+      </c>
+      <c r="AO8">
+        <v>0.06741661079577493</v>
+      </c>
+      <c r="AP8">
+        <v>4.78877</v>
+      </c>
+      <c r="AQ8">
+        <v>4.803774312155674</v>
+      </c>
+      <c r="AR8">
+        <v>4.738376428209267</v>
+      </c>
+      <c r="AS8">
+        <v>4.78877</v>
+      </c>
+      <c r="AT8">
+        <v>4.851640000000001</v>
+      </c>
+      <c r="AU8">
+        <v>4.803774312155674</v>
+      </c>
+      <c r="AV8">
+        <v>4.753922500000001</v>
+      </c>
+      <c r="AW8">
+        <v>0.003133228815682105</v>
+      </c>
+      <c r="AX8">
+        <v>0.4305706910301751</v>
+      </c>
+      <c r="AY8">
+        <v>0.003133228815682105</v>
+      </c>
+      <c r="AZ8">
+        <v>0.3239053220797735</v>
+      </c>
+      <c r="BA8">
+        <v>0.1778115817328445</v>
+      </c>
+      <c r="BB8">
+        <v>0.498283096187382</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
+        <v>100000</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>375</v>
+      </c>
+      <c r="BG8">
+        <v>0.007276920795945497</v>
+      </c>
+      <c r="BH8">
+        <v>68710.38094554862</v>
+      </c>
+      <c r="BI8">
+        <v>51532.78570916146</v>
+      </c>
+      <c r="BJ8">
+        <v>10761.1736853433</v>
+      </c>
+      <c r="BK8">
+        <v>515.3278570916146</v>
+      </c>
+      <c r="BL8">
+        <v>0.005153278570916147</v>
+      </c>
+      <c r="BM8">
+        <v>375</v>
+      </c>
+      <c r="BN8">
+        <v>0.00375</v>
+      </c>
+      <c r="BO8">
+        <v>0.03877691722723194</v>
+      </c>
+      <c r="BP8">
+        <v>0.01510097198732195</v>
+      </c>
+      <c r="BQ8">
+        <v>0.0152465335146067</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:75">
+      <c r="A9" t="s">
         <v>82</v>
-      </c>
-      <c r="AF8">
-        <v>100000</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>477.5129944077606</v>
-      </c>
-      <c r="AI8">
-        <v>0.01143265012275631</v>
-      </c>
-      <c r="AJ8">
-        <v>43734.39181916069</v>
-      </c>
-      <c r="AK8">
-        <v>41767.48079233937</v>
-      </c>
-      <c r="AL8">
-        <v>51400.75289642237</v>
-      </c>
-      <c r="AM8">
-        <v>417.6748079233938</v>
-      </c>
-      <c r="AN8">
-        <v>0.004176748079233938</v>
-      </c>
-      <c r="AO8">
-        <v>477.5129944077606</v>
-      </c>
-      <c r="AP8">
-        <v>0.004775129944077606</v>
-      </c>
-      <c r="AQ8">
-        <v>0.0193269055484675</v>
-      </c>
-      <c r="AR8">
-        <v>0.002699876450962892</v>
-      </c>
-      <c r="AS8">
-        <v>0.003403798390486215</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51">
-      <c r="A9" t="s">
-        <v>58</v>
       </c>
       <c r="B9" s="2">
         <v>46252</v>
@@ -1887,153 +2553,225 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46251</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.4395265256789536</v>
       </c>
       <c r="L9">
-        <v>0.3703547186083788</v>
+        <v>2.865467247385043</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q9">
+        <v>0.6703551057407848</v>
+      </c>
+      <c r="R9" t="s">
+        <v>102</v>
+      </c>
+      <c r="S9" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9">
+        <v>-0.9939397852337705</v>
+      </c>
+      <c r="U9">
+        <v>0.9131616694458771</v>
+      </c>
+      <c r="V9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W9" t="s">
+        <v>95</v>
+      </c>
+      <c r="X9">
+        <v>0.9998391489553492</v>
+      </c>
+      <c r="Y9">
+        <v>0.8084559137929632</v>
+      </c>
+      <c r="Z9">
+        <v>171.2184960870734</v>
+      </c>
+      <c r="AA9">
+        <v>-12</v>
+      </c>
+      <c r="AB9">
+        <v>-0.988277716476738</v>
+      </c>
+      <c r="AC9">
+        <v>0.1526668107858553</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH9">
+        <v>-0.8934845993639957</v>
+      </c>
+      <c r="AI9">
+        <v>0.9532189578065283</v>
+      </c>
+      <c r="AJ9">
+        <v>-2.193405750143193</v>
+      </c>
+      <c r="AK9">
+        <v>0.2873502371253457</v>
+      </c>
+      <c r="AL9">
+        <v>-3.503879798910328</v>
+      </c>
+      <c r="AM9">
+        <v>3.639504824923043</v>
+      </c>
+      <c r="AN9">
+        <v>3.188223828823946</v>
+      </c>
+      <c r="AO9">
+        <v>0.03266161352971927</v>
+      </c>
+      <c r="AP9">
+        <v>6.74544</v>
+      </c>
+      <c r="AQ9">
+        <v>6.763802833960794</v>
+      </c>
+      <c r="AR9">
+        <v>6.804738954981863</v>
+      </c>
+      <c r="AS9">
+        <v>6.74544</v>
+      </c>
+      <c r="AT9">
+        <v>6.718680000000001</v>
+      </c>
+      <c r="AU9">
+        <v>6.763802833960794</v>
+      </c>
+      <c r="AV9">
+        <v>6.717515</v>
+      </c>
+      <c r="AW9">
+        <v>0.002722258883155661</v>
+      </c>
+      <c r="AX9">
+        <v>0.6575768652029811</v>
+      </c>
+      <c r="AY9">
+        <v>0.002722258883155661</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4621347536601463</v>
+      </c>
+      <c r="BA9">
+        <v>0.2</v>
+      </c>
+      <c r="BB9">
+        <v>0.3378652463398537</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
+        <v>100000</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>335.1775528703924</v>
+      </c>
+      <c r="BG9">
+        <v>0.004139833724708903</v>
+      </c>
+      <c r="BH9">
+        <v>120777.7976723348</v>
+      </c>
+      <c r="BI9">
+        <v>80964.0133297771</v>
+      </c>
+      <c r="BJ9">
+        <v>12002.77718425738</v>
+      </c>
+      <c r="BK9">
+        <v>809.6401332977709</v>
+      </c>
+      <c r="BL9">
+        <v>0.008096401332977709</v>
+      </c>
+      <c r="BM9">
+        <v>335.1775528703924</v>
+      </c>
+      <c r="BN9">
+        <v>0.003351775528703924</v>
+      </c>
+      <c r="BO9">
+        <v>0.1014135193494297</v>
+      </c>
+      <c r="BP9">
+        <v>0.002466334229348512</v>
+      </c>
+      <c r="BQ9">
+        <v>0.01869917412824225</v>
+      </c>
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>9.130549999999999</v>
-      </c>
-      <c r="S9">
-        <v>9.109491328372108</v>
-      </c>
-      <c r="T9">
-        <v>8.99833753534821</v>
-      </c>
-      <c r="U9">
-        <v>9.130549999999999</v>
-      </c>
-      <c r="V9">
-        <v>9.242009999999999</v>
-      </c>
-      <c r="W9">
-        <v>9.109491328372108</v>
-      </c>
-      <c r="X9">
-        <v>9.213339999999999</v>
-      </c>
-      <c r="Y9">
-        <v>-0.002306396835666099</v>
-      </c>
-      <c r="Z9">
-        <v>0.2543625030546088</v>
-      </c>
-      <c r="AA9">
-        <v>0.002306396835666099</v>
-      </c>
-      <c r="AB9">
-        <v>0.4547814825937937</v>
-      </c>
-      <c r="AC9">
-        <v>0.1946971728536392</v>
-      </c>
-      <c r="AD9">
-        <v>0.3505213445525671</v>
-      </c>
-      <c r="AE9" t="s">
+      <c r="BS9">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" t="s">
         <v>83</v>
-      </c>
-      <c r="AF9">
-        <v>100000</v>
-      </c>
-      <c r="AG9">
-        <v>100</v>
-      </c>
-      <c r="AH9">
-        <v>500</v>
-      </c>
-      <c r="AI9">
-        <v>0.009067361769006264</v>
-      </c>
-      <c r="AJ9">
-        <v>55142.83125981389</v>
-      </c>
-      <c r="AK9">
-        <v>55142.83125981389</v>
-      </c>
-      <c r="AL9">
-        <v>6039.376736320801</v>
-      </c>
-      <c r="AM9">
-        <v>551.4283125981389</v>
-      </c>
-      <c r="AN9">
-        <v>0.005514283125981389</v>
-      </c>
-      <c r="AO9">
-        <v>500</v>
-      </c>
-      <c r="AP9">
-        <v>0.005</v>
-      </c>
-      <c r="AQ9">
-        <v>0.09265563721517393</v>
-      </c>
-      <c r="AR9">
-        <v>0.02420217711770799</v>
-      </c>
-      <c r="AS9">
-        <v>0.02434479053511114</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" t="s">
-        <v>59</v>
       </c>
       <c r="B10" s="2">
         <v>46252</v>
@@ -2042,153 +2780,225 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J10" s="2">
         <v>46251</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.1050157412859733</v>
       </c>
       <c r="L10">
-        <v>0.03220786753094879</v>
+        <v>1.150148007230601</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q10">
+        <v>0.9212381940355201</v>
+      </c>
+      <c r="R10" t="s">
+        <v>103</v>
+      </c>
+      <c r="S10" t="s">
+        <v>107</v>
+      </c>
+      <c r="T10">
+        <v>0.9937836238698943</v>
+      </c>
+      <c r="U10">
+        <v>0.8626200864699662</v>
+      </c>
+      <c r="V10" t="s">
+        <v>93</v>
+      </c>
+      <c r="W10" t="s">
+        <v>95</v>
+      </c>
+      <c r="X10">
+        <v>0.9986603781424714</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>11.13590782729874</v>
+      </c>
+      <c r="AA10">
+        <v>16</v>
+      </c>
+      <c r="AB10">
+        <v>0.9811718158855942</v>
+      </c>
+      <c r="AC10">
+        <v>0.193136914420226</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH10">
+        <v>0.4899287083375214</v>
+      </c>
+      <c r="AI10">
+        <v>0.7878273821112319</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8213535524512496</v>
+      </c>
+      <c r="AK10">
+        <v>0.1412194746989415</v>
+      </c>
+      <c r="AL10">
+        <v>1.676087523665858</v>
+      </c>
+      <c r="AM10">
+        <v>-0.8608944493337228</v>
+      </c>
+      <c r="AN10">
+        <v>1.575697035069539</v>
+      </c>
+      <c r="AO10">
+        <v>0.04036863336207513</v>
+      </c>
+      <c r="AP10">
+        <v>0.812585</v>
+      </c>
+      <c r="AQ10">
+        <v>0.8114142223622693</v>
+      </c>
+      <c r="AR10">
+        <v>0.8140927522275916</v>
+      </c>
+      <c r="AS10">
+        <v>0.812585</v>
+      </c>
+      <c r="AT10">
+        <v>0.8089850000000001</v>
+      </c>
+      <c r="AU10">
+        <v>0.8113661225</v>
+      </c>
+      <c r="AV10">
+        <v>0.8218749999999999</v>
+      </c>
+      <c r="AW10">
+        <v>-0.001440806362079854</v>
+      </c>
+      <c r="AX10">
+        <v>0.1312031754574821</v>
+      </c>
+      <c r="AY10">
+        <v>0.001440806362079854</v>
+      </c>
+      <c r="AZ10">
+        <v>0.3346329825938251</v>
+      </c>
+      <c r="BA10">
+        <v>0.2</v>
+      </c>
+      <c r="BB10">
+        <v>0.465367017406175</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD10">
+        <v>100000</v>
+      </c>
+      <c r="BE10">
+        <v>100</v>
+      </c>
+      <c r="BF10">
+        <v>460.6190970177601</v>
+      </c>
+      <c r="BG10">
+        <v>0.01143265012275631</v>
+      </c>
+      <c r="BH10">
+        <v>43734.39181916069</v>
+      </c>
+      <c r="BI10">
+        <v>40289.79213672542</v>
+      </c>
+      <c r="BJ10">
+        <v>49582.24940987763</v>
+      </c>
+      <c r="BK10">
+        <v>402.8979213672542</v>
+      </c>
+      <c r="BL10">
+        <v>0.004028979213672542</v>
+      </c>
+      <c r="BM10">
+        <v>460.6190970177601</v>
+      </c>
+      <c r="BN10">
+        <v>0.004606190970177601</v>
+      </c>
+      <c r="BO10">
+        <v>0.01701209962836502</v>
+      </c>
+      <c r="BP10">
+        <v>0.002038744226568694</v>
+      </c>
+      <c r="BQ10">
+        <v>0.002652019595340664</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>7.8064</v>
-      </c>
-      <c r="S10">
-        <v>7.784317326789372</v>
-      </c>
-      <c r="T10">
-        <v>7.672814980547543</v>
-      </c>
-      <c r="U10">
-        <v>7.8064</v>
-      </c>
-      <c r="V10">
-        <v>7.9155</v>
-      </c>
-      <c r="W10">
-        <v>7.784317326789372</v>
-      </c>
-      <c r="X10">
-        <v>7.867249999999999</v>
-      </c>
-      <c r="Y10">
-        <v>-0.00282879089088797</v>
-      </c>
-      <c r="Z10">
-        <v>0.3629034217030084</v>
-      </c>
-      <c r="AA10">
-        <v>0.00282879089088797</v>
-      </c>
-      <c r="AB10">
-        <v>0.4506362751906631</v>
-      </c>
-      <c r="AC10">
-        <v>0.2</v>
-      </c>
-      <c r="AD10">
-        <v>0.3493637248093369</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="BS10">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="AF10">
-        <v>100000</v>
-      </c>
-      <c r="AG10">
-        <v>100</v>
-      </c>
-      <c r="AH10">
-        <v>500</v>
-      </c>
-      <c r="AI10">
-        <v>0.007794886247181723</v>
-      </c>
-      <c r="AJ10">
-        <v>64144.6179129012</v>
-      </c>
-      <c r="AK10">
-        <v>64144.6179129012</v>
-      </c>
-      <c r="AL10">
-        <v>8216.926869350944</v>
-      </c>
-      <c r="AM10">
-        <v>641.446179129012</v>
-      </c>
-      <c r="AN10">
-        <v>0.00641446179129012</v>
-      </c>
-      <c r="AO10">
-        <v>500</v>
-      </c>
-      <c r="AP10">
-        <v>0.005</v>
-      </c>
-      <c r="AQ10">
-        <v>0.09451762042150039</v>
-      </c>
-      <c r="AR10">
-        <v>0.0185535982280629</v>
-      </c>
-      <c r="AS10">
-        <v>0.03184693421590027</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>46252</v>
@@ -2197,31 +3007,31 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
         <v>46251</v>
       </c>
       <c r="K11">
-        <v>0.2206760510344554</v>
+        <v>0.2009038324667773</v>
       </c>
       <c r="L11">
-        <v>1.257784563326133</v>
+        <v>1.234105502156207</v>
       </c>
       <c r="M11">
         <v>6</v>
@@ -2230,114 +3040,186 @@
         <v>8</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q11">
-        <v>0.8344929617241584</v>
-      </c>
-      <c r="R11">
+        <v>0.849322125649917</v>
+      </c>
+      <c r="R11" t="s">
+        <v>100</v>
+      </c>
+      <c r="S11" t="s">
+        <v>104</v>
+      </c>
+      <c r="T11">
+        <v>0.9539800828084271</v>
+      </c>
+      <c r="U11">
+        <v>0.8592457432448537</v>
+      </c>
+      <c r="V11" t="s">
+        <v>93</v>
+      </c>
+      <c r="W11" t="s">
+        <v>95</v>
+      </c>
+      <c r="X11">
+        <v>0.9992765244441797</v>
+      </c>
+      <c r="Y11">
+        <v>0.1653012608324546</v>
+      </c>
+      <c r="Z11">
+        <v>28.42376633486904</v>
+      </c>
+      <c r="AA11">
+        <v>-5.999999999999996</v>
+      </c>
+      <c r="AB11">
+        <v>0.8794512078963892</v>
+      </c>
+      <c r="AC11">
+        <v>0.4759890470689237</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH11">
+        <v>0.5120420825653471</v>
+      </c>
+      <c r="AI11">
+        <v>0.7901629092290927</v>
+      </c>
+      <c r="AJ11">
+        <v>1.040252954443273</v>
+      </c>
+      <c r="AK11">
+        <v>0.5834667613722873</v>
+      </c>
+      <c r="AL11">
+        <v>1.063582433340868</v>
+      </c>
+      <c r="AM11">
+        <v>-2.613558463854223</v>
+      </c>
+      <c r="AN11">
+        <v>0.8433754074825937</v>
+      </c>
+      <c r="AO11">
+        <v>0.04319659241185132</v>
+      </c>
+      <c r="AP11">
         <v>1.15778</v>
       </c>
-      <c r="S11">
-        <v>1.148981084756681</v>
-      </c>
-      <c r="T11">
-        <v>1.119442986245173</v>
-      </c>
-      <c r="U11">
+      <c r="AQ11">
+        <v>1.153414783967473</v>
+      </c>
+      <c r="AR11">
+        <v>1.132001164417092</v>
+      </c>
+      <c r="AS11">
         <v>1.15778</v>
       </c>
-      <c r="V11">
+      <c r="AT11">
         <v>1.17625</v>
       </c>
-      <c r="W11">
-        <v>1.148981084756681</v>
-      </c>
-      <c r="X11">
+      <c r="AU11">
+        <v>1.153414783967473</v>
+      </c>
+      <c r="AV11">
         <v>1.17078</v>
       </c>
-      <c r="Y11">
-        <v>-0.007599816237384664</v>
-      </c>
-      <c r="Z11">
-        <v>0.6768396341014776</v>
-      </c>
-      <c r="AA11">
-        <v>0.007599816237384664</v>
-      </c>
-      <c r="AB11">
-        <v>0.4150000798328546</v>
-      </c>
-      <c r="AC11">
+      <c r="AW11">
+        <v>-0.00377033290653438</v>
+      </c>
+      <c r="AX11">
+        <v>0.3357858486559516</v>
+      </c>
+      <c r="AY11">
+        <v>0.00377033290653438</v>
+      </c>
+      <c r="AZ11">
+        <v>0.4325812370059524</v>
+      </c>
+      <c r="BA11">
         <v>0.2</v>
       </c>
-      <c r="AD11">
-        <v>0.3849999201671455</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF11">
+      <c r="BB11">
+        <v>0.3674187629940476</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD11">
         <v>100000</v>
       </c>
-      <c r="AG11">
+      <c r="BE11">
         <v>100</v>
       </c>
-      <c r="AH11">
-        <v>417.2464808620792</v>
-      </c>
-      <c r="AI11">
+      <c r="BF11">
+        <v>424.6610628249585</v>
+      </c>
+      <c r="BG11">
         <v>0.0112283853581855</v>
       </c>
-      <c r="AJ11">
+      <c r="BH11">
         <v>44529.99999999996</v>
       </c>
-      <c r="AK11">
-        <v>37159.97158557674</v>
-      </c>
-      <c r="AL11">
-        <v>32095.88314323684</v>
-      </c>
-      <c r="AM11">
-        <v>371.5997158557674</v>
-      </c>
-      <c r="AN11">
-        <v>0.003715997158557674</v>
-      </c>
-      <c r="AO11">
-        <v>417.2464808620792</v>
-      </c>
-      <c r="AP11">
-        <v>0.004172464808620792</v>
-      </c>
-      <c r="AQ11">
-        <v>0.01371065096530527</v>
-      </c>
-      <c r="AR11">
-        <v>0.00300200900334056</v>
-      </c>
-      <c r="AS11">
-        <v>0.007218716892197261</v>
-      </c>
-      <c r="AT11">
+      <c r="BI11">
+        <v>37820.31425519077</v>
+      </c>
+      <c r="BJ11">
+        <v>32666.23560191986</v>
+      </c>
+      <c r="BK11">
+        <v>378.2031425519077</v>
+      </c>
+      <c r="BL11">
+        <v>0.003782031425519077</v>
+      </c>
+      <c r="BM11">
+        <v>424.6610628249585</v>
+      </c>
+      <c r="BN11">
+        <v>0.004246610628249585</v>
+      </c>
+      <c r="BO11">
+        <v>0.01491577822475181</v>
+      </c>
+      <c r="BP11">
+        <v>0.0009274116185603584</v>
+      </c>
+      <c r="BQ11">
+        <v>0.006461974999220072</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="AU11">
-        <v>0.04250144749668916</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY11" s="2">
+      <c r="BS11">
+        <v>0.02910955503810441</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW11" s="2">
         <v>46280</v>
       </c>
     </row>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -169,22 +241,28 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>EURUSD</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
-    <t>XAUUSD</t>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>GBPCNH</t>
   </si>
   <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
-    <t>AUDCNH</t>
+    <t>USDCHF</t>
   </si>
   <si>
     <t>AUDUSD</t>
@@ -193,27 +271,21 @@
     <t>EURCNH</t>
   </si>
   <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -223,12 +295,12 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>CONFLICT</t>
   </si>
   <si>
@@ -244,34 +316,88 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.02366,naive=0.008653,drift4=0.0079; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.03885,naive=0.009151,drift4=0.009497; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=912.4,naive=328.2,drift4=416.6; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.60,naive=0.20,drift4=0.20); metric_best=model; scores=model=1.152,naive=2.667,drift4=7.55; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1354,naive=0.01522,drift4=0.02638; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.14,drift4=0.55); metric_best=drift4; scores=model=0.108,naive=0.04895,drift4=0.008583</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.03882,naive=0.003883,drift4=0.009267; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=drift4; scores=model=0.08029,naive=0.04283,drift4=0.04159; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=drift4; scores=model=0.03579,naive=0.04299,drift4=0.03082; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.48); metric_best=drift4; scores=model=0.03359,naive=0.004559,drift4=0.00272; naive_cap_applied</t>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_STEADY</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>多头稳态</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>UP_SLOPE</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>上升坡延续</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.45,naive=0.20,drift4=0.35); metric_best=naive; scores=model=0.09499,naive=0.002772,drift4=0.01537; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01642,naive=0.002252,drift4=0.005647; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=351,naive=78.73,drift4=157.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.01486,naive=0.002332,drift4=0.004599; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.03293,naive=0.01015,drift4=0.01736; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.08539,naive=0.01323,drift4=0.02169; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.873,naive=0.7501,drift4=2.504; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01653,naive=0.002323,drift4=0.003888; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=0.009198,naive=0.0009901,drift4=0.00525; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.116,naive=0.007144,drift4=0.02405; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -645,10 +771,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,10 +928,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46253</v>
@@ -814,141 +1012,213 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46252</v>
       </c>
       <c r="K2">
-        <v>0.8552766994279543</v>
+        <v>0.9712887148124082</v>
       </c>
       <c r="L2">
-        <v>1.639723445230607</v>
+        <v>3.505577569841422</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>1.160455</v>
-      </c>
-      <c r="S2">
-        <v>1.154336423108373</v>
+      <c r="R2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" t="s">
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>1.122096938046343</v>
+        <v>-0.9986248315635631</v>
       </c>
       <c r="U2">
-        <v>1.160455</v>
-      </c>
-      <c r="V2">
-        <v>1.1816</v>
+        <v>0.9950363712852694</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>96</v>
+      </c>
+      <c r="X2">
+        <v>0.9998475594392194</v>
       </c>
       <c r="Y2">
-        <v>-0.005272567132397861</v>
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>175.7593669605106</v>
       </c>
       <c r="AA2">
-        <v>0.005272567132397861</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB2">
-        <v>0.3871158245531414</v>
+        <v>-0.9972622873473986</v>
       </c>
       <c r="AC2">
+        <v>0.07394545445552796</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>-0.9971102641250701</v>
+      </c>
+      <c r="AI2">
+        <v>0.9940172618120188</v>
+      </c>
+      <c r="AJ2">
+        <v>-2.663763578722742</v>
+      </c>
+      <c r="AK2">
+        <v>0.1821231615291742</v>
+      </c>
+      <c r="AL2">
+        <v>-4.362469652293859</v>
+      </c>
+      <c r="AM2">
+        <v>3.935603322726354</v>
+      </c>
+      <c r="AN2">
+        <v>4.026433105590166</v>
+      </c>
+      <c r="AO2">
+        <v>0.03405380130618409</v>
+      </c>
+      <c r="AP2">
+        <v>6.739695</v>
+      </c>
+      <c r="AQ2">
+        <v>6.748432845269706</v>
+      </c>
+      <c r="AR2">
+        <v>6.784586324081888</v>
+      </c>
+      <c r="AS2">
+        <v>6.739695</v>
+      </c>
+      <c r="AT2">
+        <v>6.707190000000001</v>
+      </c>
+      <c r="AW2">
+        <v>0.001296474880496192</v>
+      </c>
+      <c r="AY2">
+        <v>0.001296474880496192</v>
+      </c>
+      <c r="AZ2">
+        <v>0.4488823685340356</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.4128841754468586</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="BB2">
+        <v>0.3511176314659644</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
+        <v>100000</v>
+      </c>
+      <c r="BE2">
+        <v>100</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0.09499283793953767</v>
+      </c>
+      <c r="BP2">
+        <v>0.002771568051790289</v>
+      </c>
+      <c r="BQ2">
+        <v>0.01537092808990672</v>
+      </c>
+      <c r="BR2">
+        <v>1</v>
+      </c>
+      <c r="BS2">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75">
+      <c r="A3" t="s">
         <v>76</v>
-      </c>
-      <c r="AF2">
-        <v>100000</v>
-      </c>
-      <c r="AG2">
-        <v>100</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0.01433894382857525</v>
-      </c>
-      <c r="AR2">
-        <v>0.003085652446782065</v>
-      </c>
-      <c r="AS2">
-        <v>0.005995276653577342</v>
-      </c>
-      <c r="AT2">
-        <v>1</v>
-      </c>
-      <c r="AU2">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51">
-      <c r="A3" t="s">
-        <v>52</v>
       </c>
       <c r="B3" s="2">
         <v>46253</v>
@@ -957,22 +1227,22 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
         <v>46252</v>
@@ -981,117 +1251,189 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>2.004240521415301</v>
+        <v>1.877847691186643</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q3">
         <v>0</v>
       </c>
-      <c r="R3">
-        <v>1.35533</v>
-      </c>
-      <c r="S3">
-        <v>1.346125378661115</v>
+      <c r="R3" t="s">
+        <v>101</v>
+      </c>
+      <c r="S3" t="s">
+        <v>105</v>
       </c>
       <c r="T3">
-        <v>1.307578150224325</v>
+        <v>0.9038501979646764</v>
       </c>
       <c r="U3">
-        <v>1.35533</v>
-      </c>
-      <c r="V3">
-        <v>1.37609</v>
+        <v>0.9566417049698011</v>
+      </c>
+      <c r="V3" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" t="s">
+        <v>96</v>
+      </c>
+      <c r="X3">
+        <v>0.999636463542787</v>
       </c>
       <c r="Y3">
-        <v>-0.006791424478824509</v>
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>36.13153934722025</v>
       </c>
       <c r="AA3">
-        <v>0.006791424478824509</v>
+        <v>9</v>
       </c>
       <c r="AB3">
-        <v>0.3767614131482682</v>
+        <v>0.8076654292592997</v>
       </c>
       <c r="AC3">
+        <v>0.5896410385814331</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH3">
+        <v>0.8073718134305334</v>
+      </c>
+      <c r="AI3">
+        <v>0.9353814439616006</v>
+      </c>
+      <c r="AJ3">
+        <v>1.539942938701542</v>
+      </c>
+      <c r="AK3">
+        <v>1.078235688508524</v>
+      </c>
+      <c r="AL3">
+        <v>1.803327626737504</v>
+      </c>
+      <c r="AM3">
+        <v>-3.260640591164396</v>
+      </c>
+      <c r="AN3">
+        <v>1.525280467253671</v>
+      </c>
+      <c r="AO3">
+        <v>0.04527298037443184</v>
+      </c>
+      <c r="AP3">
+        <v>1.160455</v>
+      </c>
+      <c r="AQ3">
+        <v>1.15749920552575</v>
+      </c>
+      <c r="AR3">
+        <v>1.135015150499668</v>
+      </c>
+      <c r="AS3">
+        <v>1.160455</v>
+      </c>
+      <c r="AT3">
+        <v>1.1816</v>
+      </c>
+      <c r="AW3">
+        <v>-0.002547099606835428</v>
+      </c>
+      <c r="AY3">
+        <v>0.002547099606835428</v>
+      </c>
+      <c r="AZ3">
+        <v>0.4265720440742983</v>
+      </c>
+      <c r="BA3">
         <v>0.2</v>
       </c>
-      <c r="AD3">
-        <v>0.4232385868517318</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="BB3">
+        <v>0.3734279559257017</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
+        <v>100000</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0.01642049063283507</v>
+      </c>
+      <c r="BP3">
+        <v>0.002252389449551994</v>
+      </c>
+      <c r="BQ3">
+        <v>0.005647465381999003</v>
+      </c>
+      <c r="BR3">
+        <v>1</v>
+      </c>
+      <c r="BS3">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:75">
+      <c r="A4" t="s">
         <v>77</v>
-      </c>
-      <c r="AF3">
-        <v>100000</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0.01964523977254359</v>
-      </c>
-      <c r="AR3">
-        <v>0.003420163516987608</v>
-      </c>
-      <c r="AS3">
-        <v>0.004461831024590966</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51">
-      <c r="A4" t="s">
-        <v>53</v>
       </c>
       <c r="B4" s="2">
         <v>46253</v>
@@ -1100,22 +1442,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
         <v>46252</v>
@@ -1124,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1.330725565828205</v>
+        <v>1.336874444188156</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -1133,120 +1475,192 @@
         <v>5</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>0.75</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="s">
+        <v>101</v>
+      </c>
+      <c r="S4" t="s">
+        <v>105</v>
+      </c>
+      <c r="T4">
+        <v>0.8880681771351673</v>
+      </c>
+      <c r="U4">
+        <v>0.7989147895991404</v>
+      </c>
+      <c r="V4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W4" t="s">
+        <v>96</v>
+      </c>
+      <c r="X4">
+        <v>0.9971364395532607</v>
+      </c>
+      <c r="Y4">
+        <v>0.2583244267815755</v>
+      </c>
+      <c r="Z4">
+        <v>42.11784220552273</v>
+      </c>
+      <c r="AA4">
+        <v>-30</v>
+      </c>
+      <c r="AB4">
+        <v>0.7417670306461555</v>
+      </c>
+      <c r="AC4">
+        <v>0.6706576416073893</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH4">
+        <v>0.4653553866800869</v>
+      </c>
+      <c r="AI4">
+        <v>0.7668314562053249</v>
+      </c>
+      <c r="AJ4">
+        <v>1.134248265310175</v>
+      </c>
+      <c r="AK4">
+        <v>1.219731614639799</v>
+      </c>
+      <c r="AL4">
+        <v>1.144886056015245</v>
+      </c>
+      <c r="AM4">
+        <v>-3.613848854316405</v>
+      </c>
+      <c r="AN4">
+        <v>0.9875081275617564</v>
+      </c>
+      <c r="AO4">
+        <v>0.04240861458985336</v>
+      </c>
+      <c r="AP4">
         <v>4363.68</v>
       </c>
-      <c r="S4">
-        <v>4483.615250684331</v>
-      </c>
-      <c r="T4">
-        <v>4357.56985798385</v>
-      </c>
-      <c r="U4">
+      <c r="AQ4">
+        <v>4430.324183392777</v>
+      </c>
+      <c r="AR4">
+        <v>4243.462606517724</v>
+      </c>
+      <c r="AS4">
         <v>4363.68</v>
       </c>
-      <c r="V4">
+      <c r="AT4">
         <v>4681.470000000001</v>
       </c>
-      <c r="W4">
-        <v>4483.615250684331</v>
-      </c>
-      <c r="X4">
+      <c r="AU4">
+        <v>4430.324183392777</v>
+      </c>
+      <c r="AV4">
         <v>4224.860000000001</v>
       </c>
-      <c r="Y4">
-        <v>0.02748488676629144</v>
-      </c>
-      <c r="Z4">
-        <v>0.8639623302429857</v>
-      </c>
-      <c r="AA4">
-        <v>0.02748488676629144</v>
-      </c>
-      <c r="AB4">
-        <v>0.4146239284729106</v>
-      </c>
-      <c r="AC4">
+      <c r="AW4">
+        <v>0.01527247263611826</v>
+      </c>
+      <c r="AX4">
+        <v>0.4800762382421618</v>
+      </c>
+      <c r="AY4">
+        <v>0.01527247263611826</v>
+      </c>
+      <c r="AZ4">
+        <v>0.4282754569868101</v>
+      </c>
+      <c r="BA4">
         <v>0.2</v>
       </c>
-      <c r="AD4">
-        <v>0.3853760715270894</v>
-      </c>
-      <c r="AE4" t="s">
+      <c r="BB4">
+        <v>0.37172454301319</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
+        <v>100000</v>
+      </c>
+      <c r="BE4">
+        <v>100</v>
+      </c>
+      <c r="BF4">
+        <v>375</v>
+      </c>
+      <c r="BG4">
+        <v>0.03181259854068109</v>
+      </c>
+      <c r="BH4">
+        <v>15717.0436536523</v>
+      </c>
+      <c r="BI4">
+        <v>11787.78274023922</v>
+      </c>
+      <c r="BJ4">
+        <v>2.701339864572842</v>
+      </c>
+      <c r="BK4">
+        <v>117.8778274023922</v>
+      </c>
+      <c r="BL4">
+        <v>0.001178778274023922</v>
+      </c>
+      <c r="BM4">
+        <v>374.9999999999999</v>
+      </c>
+      <c r="BN4">
+        <v>0.003749999999999999</v>
+      </c>
+      <c r="BO4">
+        <v>350.995418625476</v>
+      </c>
+      <c r="BP4">
+        <v>78.73115690666117</v>
+      </c>
+      <c r="BQ4">
+        <v>157.2554718121795</v>
+      </c>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+      <c r="BS4">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:75">
+      <c r="A5" t="s">
         <v>78</v>
-      </c>
-      <c r="AF4">
-        <v>100000</v>
-      </c>
-      <c r="AG4">
-        <v>100</v>
-      </c>
-      <c r="AH4">
-        <v>375</v>
-      </c>
-      <c r="AI4">
-        <v>0.03181259854068109</v>
-      </c>
-      <c r="AJ4">
-        <v>15717.0436536523</v>
-      </c>
-      <c r="AK4">
-        <v>11787.78274023922</v>
-      </c>
-      <c r="AL4">
-        <v>2.701339864572842</v>
-      </c>
-      <c r="AM4">
-        <v>117.8778274023922</v>
-      </c>
-      <c r="AN4">
-        <v>0.001178778274023922</v>
-      </c>
-      <c r="AO4">
-        <v>374.9999999999999</v>
-      </c>
-      <c r="AP4">
-        <v>0.003749999999999999</v>
-      </c>
-      <c r="AQ4">
-        <v>381.7463564987442</v>
-      </c>
-      <c r="AR4">
-        <v>108.8191222854915</v>
-      </c>
-      <c r="AS4">
-        <v>168.1776038235682</v>
-      </c>
-      <c r="AT4">
-        <v>1</v>
-      </c>
-      <c r="AU4">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51">
-      <c r="A5" t="s">
-        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>46253</v>
@@ -1255,153 +1669,225 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
         <v>46252</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0.9513880630347501</v>
+        <v>2.393967128640724</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
-      <c r="R5">
-        <v>159.111</v>
-      </c>
-      <c r="S5">
-        <v>161.424468827666</v>
+      <c r="R5" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" t="s">
+        <v>105</v>
       </c>
       <c r="T5">
-        <v>164.4900654122559</v>
+        <v>0.9566516313483018</v>
       </c>
       <c r="U5">
-        <v>159.111</v>
-      </c>
-      <c r="V5">
-        <v>154.59</v>
-      </c>
-      <c r="W5">
-        <v>161.424468827666</v>
+        <v>0.9804757572401196</v>
+      </c>
+      <c r="V5" t="s">
+        <v>94</v>
+      </c>
+      <c r="W5" t="s">
+        <v>96</v>
       </c>
       <c r="X5">
-        <v>157.5686874482227</v>
+        <v>0.9999300925335349</v>
       </c>
       <c r="Y5">
-        <v>0.01453996786938669</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>1.5</v>
+        <v>24.03452083496258</v>
       </c>
       <c r="AA5">
-        <v>0.01453996786938669</v>
+        <v>-3.999999999999993</v>
       </c>
       <c r="AB5">
-        <v>0.5990130954412235</v>
+        <v>0.9133002321101152</v>
       </c>
       <c r="AC5">
+        <v>0.407286982393999</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH5">
+        <v>0.9132363856047665</v>
+      </c>
+      <c r="AI5">
+        <v>0.9679745031472357</v>
+      </c>
+      <c r="AJ5">
+        <v>1.888659480193469</v>
+      </c>
+      <c r="AK5">
+        <v>0.861808934316782</v>
+      </c>
+      <c r="AL5">
+        <v>2.664250041100024</v>
+      </c>
+      <c r="AM5">
+        <v>-3.775343999220554</v>
+      </c>
+      <c r="AN5">
+        <v>2.314975851877224</v>
+      </c>
+      <c r="AO5">
+        <v>0.03994065915024112</v>
+      </c>
+      <c r="AP5">
+        <v>1.35533</v>
+      </c>
+      <c r="AQ5">
+        <v>1.357927751796845</v>
+      </c>
+      <c r="AR5">
+        <v>1.34214032833947</v>
+      </c>
+      <c r="AS5">
+        <v>1.35533</v>
+      </c>
+      <c r="AT5">
+        <v>1.37609</v>
+      </c>
+      <c r="AU5">
+        <v>1.357927751796845</v>
+      </c>
+      <c r="AV5">
+        <v>1.343405</v>
+      </c>
+      <c r="AW5">
+        <v>0.001916693201541621</v>
+      </c>
+      <c r="AX5">
+        <v>0.2178408215383983</v>
+      </c>
+      <c r="AY5">
+        <v>0.001916693201541621</v>
+      </c>
+      <c r="AZ5">
+        <v>0.4126769867834441</v>
+      </c>
+      <c r="BA5">
         <v>0.2</v>
       </c>
-      <c r="AD5">
-        <v>0.2009869045587765</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="BB5">
+        <v>0.387323013216556</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
+        <v>100000</v>
+      </c>
+      <c r="BE5">
+        <v>100</v>
+      </c>
+      <c r="BF5">
+        <v>500</v>
+      </c>
+      <c r="BG5">
+        <v>0.008798595176082592</v>
+      </c>
+      <c r="BH5">
+        <v>56827.25366876301</v>
+      </c>
+      <c r="BI5">
+        <v>56827.25366876301</v>
+      </c>
+      <c r="BJ5">
+        <v>41928.72117400412</v>
+      </c>
+      <c r="BK5">
+        <v>568.27253668763</v>
+      </c>
+      <c r="BL5">
+        <v>0.0056827253668763</v>
+      </c>
+      <c r="BM5">
+        <v>500</v>
+      </c>
+      <c r="BN5">
+        <v>0.005</v>
+      </c>
+      <c r="BO5">
+        <v>0.01486063623128037</v>
+      </c>
+      <c r="BP5">
+        <v>0.002331835650838522</v>
+      </c>
+      <c r="BQ5">
+        <v>0.004598973773382313</v>
+      </c>
+      <c r="BR5">
+        <v>1</v>
+      </c>
+      <c r="BS5">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:75">
+      <c r="A6" t="s">
         <v>79</v>
-      </c>
-      <c r="AF5">
-        <v>100000</v>
-      </c>
-      <c r="AG5">
-        <v>100</v>
-      </c>
-      <c r="AH5">
-        <v>500</v>
-      </c>
-      <c r="AI5">
-        <v>0.009693311912924461</v>
-      </c>
-      <c r="AJ5">
-        <v>51581.95717743602</v>
-      </c>
-      <c r="AK5">
-        <v>51581.95717743602</v>
-      </c>
-      <c r="AL5">
-        <v>324.188504738428</v>
-      </c>
-      <c r="AM5">
-        <v>515.8195717743603</v>
-      </c>
-      <c r="AN5">
-        <v>0.005158195717743602</v>
-      </c>
-      <c r="AO5">
-        <v>500</v>
-      </c>
-      <c r="AP5">
-        <v>0.005</v>
-      </c>
-      <c r="AQ5">
-        <v>3.607996468534737</v>
-      </c>
-      <c r="AR5">
-        <v>1.127428771670176</v>
-      </c>
-      <c r="AS5">
-        <v>3.163768024238871</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51">
-      <c r="A6" t="s">
-        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>46253</v>
@@ -1410,153 +1896,225 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
         <v>46252</v>
       </c>
       <c r="K6">
-        <v>0.6172540645551702</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>3.084531080095666</v>
+        <v>0.3537659909936395</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q6">
-        <v>0.5370594515836223</v>
-      </c>
-      <c r="R6">
-        <v>6.739695</v>
-      </c>
-      <c r="S6">
-        <v>6.772883720492086</v>
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>101</v>
+      </c>
+      <c r="S6" t="s">
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>6.858173106634791</v>
+        <v>0.8423878998878066</v>
       </c>
       <c r="U6">
-        <v>6.739695</v>
-      </c>
-      <c r="V6">
-        <v>6.707190000000001</v>
-      </c>
-      <c r="W6">
-        <v>6.772883720492086</v>
+        <v>0.7790499211257802</v>
+      </c>
+      <c r="V6" t="s">
+        <v>94</v>
+      </c>
+      <c r="W6" t="s">
+        <v>96</v>
       </c>
       <c r="X6">
-        <v>6.71177</v>
+        <v>0.9999014647050692</v>
       </c>
       <c r="Y6">
-        <v>0.004924365344735265</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.188494914667325</v>
+        <v>57.4257745628755</v>
       </c>
       <c r="AA6">
-        <v>0.004924365344735265</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AB6">
-        <v>0.392048632535195</v>
+        <v>0.5383917524642465</v>
       </c>
       <c r="AC6">
+        <v>0.8426946783257133</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH6">
+        <v>0.2691693509370646</v>
+      </c>
+      <c r="AI6">
+        <v>0.6527833795694323</v>
+      </c>
+      <c r="AJ6">
+        <v>0.3076008003248081</v>
+      </c>
+      <c r="AK6">
+        <v>0.4676126510565853</v>
+      </c>
+      <c r="AL6">
+        <v>0.3342931389128422</v>
+      </c>
+      <c r="AM6">
+        <v>-0.6319870952416665</v>
+      </c>
+      <c r="AN6">
+        <v>0.2748281582593743</v>
+      </c>
+      <c r="AO6">
+        <v>0.05799772544410547</v>
+      </c>
+      <c r="AP6">
+        <v>4.78</v>
+      </c>
+      <c r="AQ6">
+        <v>4.775052611559333</v>
+      </c>
+      <c r="AR6">
+        <v>4.722330291888193</v>
+      </c>
+      <c r="AS6">
+        <v>4.78</v>
+      </c>
+      <c r="AT6">
+        <v>4.8341</v>
+      </c>
+      <c r="AU6">
+        <v>4.77283</v>
+      </c>
+      <c r="AV6">
+        <v>4.8148475</v>
+      </c>
+      <c r="AW6">
+        <v>-0.001035018502231543</v>
+      </c>
+      <c r="AX6">
+        <v>0.205753640863764</v>
+      </c>
+      <c r="AY6">
+        <v>0.001035018502231543</v>
+      </c>
+      <c r="AZ6">
+        <v>0.431488900305828</v>
+      </c>
+      <c r="BA6">
         <v>0.2</v>
       </c>
-      <c r="AD6">
-        <v>0.407951367464805</v>
-      </c>
-      <c r="AE6" t="s">
+      <c r="BB6">
+        <v>0.368511099694172</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
+        <v>100000</v>
+      </c>
+      <c r="BE6">
+        <v>100</v>
+      </c>
+      <c r="BF6">
+        <v>500</v>
+      </c>
+      <c r="BG6">
+        <v>0.00729027196652718</v>
+      </c>
+      <c r="BH6">
+        <v>68584.546954588</v>
+      </c>
+      <c r="BI6">
+        <v>68584.546954588</v>
+      </c>
+      <c r="BJ6">
+        <v>14348.23158045774</v>
+      </c>
+      <c r="BK6">
+        <v>685.8454695458801</v>
+      </c>
+      <c r="BL6">
+        <v>0.006858454695458801</v>
+      </c>
+      <c r="BM6">
+        <v>500</v>
+      </c>
+      <c r="BN6">
+        <v>0.005</v>
+      </c>
+      <c r="BO6">
+        <v>0.03292710828397369</v>
+      </c>
+      <c r="BP6">
+        <v>0.01014748819104095</v>
+      </c>
+      <c r="BQ6">
+        <v>0.01736329393332179</v>
+      </c>
+      <c r="BR6">
+        <v>1</v>
+      </c>
+      <c r="BS6">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:75">
+      <c r="A7" t="s">
         <v>80</v>
-      </c>
-      <c r="AF6">
-        <v>100000</v>
-      </c>
-      <c r="AG6">
-        <v>100</v>
-      </c>
-      <c r="AH6">
-        <v>268.5297257918112</v>
-      </c>
-      <c r="AI6">
-        <v>0.00414336257056149</v>
-      </c>
-      <c r="AJ6">
-        <v>120674.9328558621</v>
-      </c>
-      <c r="AK6">
-        <v>64809.61325945975</v>
-      </c>
-      <c r="AL6">
-        <v>9616.104773207058</v>
-      </c>
-      <c r="AM6">
-        <v>648.0961325945975</v>
-      </c>
-      <c r="AN6">
-        <v>0.006480961325945975</v>
-      </c>
-      <c r="AO6">
-        <v>268.5297257918112</v>
-      </c>
-      <c r="AP6">
-        <v>0.002685297257918112</v>
-      </c>
-      <c r="AQ6">
-        <v>0.08039134114286102</v>
-      </c>
-      <c r="AR6">
-        <v>0.004513726780550246</v>
-      </c>
-      <c r="AS6">
-        <v>0.01700022082592868</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51">
-      <c r="A7" t="s">
-        <v>56</v>
       </c>
       <c r="B7" s="2">
         <v>46253</v>
@@ -1565,22 +2123,22 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
         <v>46252</v>
@@ -1589,129 +2147,201 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.3537659909936395</v>
+        <v>0.4332062325661995</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
-      </c>
-      <c r="R7">
-        <v>4.78</v>
-      </c>
-      <c r="S7">
-        <v>4.802519797109076</v>
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>101</v>
+      </c>
+      <c r="S7" t="s">
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>4.756680831279233</v>
+        <v>0.9012782753710262</v>
       </c>
       <c r="U7">
-        <v>4.78</v>
-      </c>
-      <c r="V7">
-        <v>4.8341</v>
-      </c>
-      <c r="W7">
-        <v>4.802519797109076</v>
+        <v>0.805515143226235</v>
+      </c>
+      <c r="V7" t="s">
+        <v>94</v>
+      </c>
+      <c r="W7" t="s">
+        <v>96</v>
       </c>
       <c r="X7">
-        <v>4.745152500000001</v>
+        <v>0.9997596772370927</v>
       </c>
       <c r="Y7">
-        <v>0.004711254625329621</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>0.6462385281318787</v>
+        <v>44.69664900174041</v>
       </c>
       <c r="AA7">
-        <v>0.004711254625329621</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.3066781589330014</v>
+        <v>0.7108406113667157</v>
       </c>
       <c r="AC7">
-        <v>0.1448694040945606</v>
-      </c>
-      <c r="AD7">
-        <v>0.548452436972438</v>
+        <v>0.7033531298229886</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH7">
+        <v>0.3553348900935027</v>
+      </c>
+      <c r="AI7">
+        <v>0.7058015494446936</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3539453759008871</v>
+      </c>
+      <c r="AK7">
+        <v>0.3518354544801641</v>
+      </c>
+      <c r="AL7">
+        <v>0.4262722105653874</v>
+      </c>
+      <c r="AM7">
+        <v>-0.8737501050199816</v>
+      </c>
+      <c r="AN7">
+        <v>0.3413524275817372</v>
+      </c>
+      <c r="AO7">
+        <v>0.0491101399886893</v>
+      </c>
+      <c r="AP7">
+        <v>9.12626</v>
+      </c>
+      <c r="AQ7">
+        <v>9.115686151473991</v>
+      </c>
+      <c r="AR7">
+        <v>8.991183486240537</v>
+      </c>
+      <c r="AS7">
+        <v>9.12626</v>
+      </c>
+      <c r="AT7">
+        <v>9.23343</v>
+      </c>
+      <c r="AU7">
+        <v>9.112570610000001</v>
+      </c>
+      <c r="AV7">
+        <v>9.209050000000001</v>
+      </c>
+      <c r="AW7">
+        <v>-0.001158617936154504</v>
+      </c>
+      <c r="AX7">
+        <v>0.1653507670008453</v>
+      </c>
+      <c r="AY7">
+        <v>0.001158617936154504</v>
+      </c>
+      <c r="AZ7">
+        <v>0.3975695956625422</v>
+      </c>
+      <c r="BA7">
+        <v>0.2</v>
+      </c>
+      <c r="BB7">
+        <v>0.4024304043374577</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
+        <v>100000</v>
+      </c>
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>500</v>
+      </c>
+      <c r="BG7">
+        <v>0.009071624082592447</v>
+      </c>
+      <c r="BH7">
+        <v>55116.92233361508</v>
+      </c>
+      <c r="BI7">
+        <v>55116.92233361508</v>
+      </c>
+      <c r="BJ7">
+        <v>6039.376736320801</v>
+      </c>
+      <c r="BK7">
+        <v>551.1692233361507</v>
+      </c>
+      <c r="BL7">
+        <v>0.005511692233361507</v>
+      </c>
+      <c r="BM7">
+        <v>500</v>
+      </c>
+      <c r="BN7">
+        <v>0.005</v>
+      </c>
+      <c r="BO7">
+        <v>0.08539165250102503</v>
+      </c>
+      <c r="BP7">
+        <v>0.013228157100338</v>
+      </c>
+      <c r="BQ7">
+        <v>0.02169021150232337</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
+      <c r="BS7">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="8" spans="1:75">
+      <c r="A8" t="s">
         <v>81</v>
-      </c>
-      <c r="AF7">
-        <v>100000</v>
-      </c>
-      <c r="AG7">
-        <v>100</v>
-      </c>
-      <c r="AH7">
-        <v>375</v>
-      </c>
-      <c r="AI7">
-        <v>0.00729027196652718</v>
-      </c>
-      <c r="AJ7">
-        <v>68584.546954588</v>
-      </c>
-      <c r="AK7">
-        <v>51438.410215941</v>
-      </c>
-      <c r="AL7">
-        <v>10761.1736853433</v>
-      </c>
-      <c r="AM7">
-        <v>514.3841021594101</v>
-      </c>
-      <c r="AN7">
-        <v>0.005143841021594101</v>
-      </c>
-      <c r="AO7">
-        <v>375</v>
-      </c>
-      <c r="AP7">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ7">
-        <v>0.04056294429608506</v>
-      </c>
-      <c r="AR7">
-        <v>0.01435639670211202</v>
-      </c>
-      <c r="AS7">
-        <v>0.01732048332774807</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51">
-      <c r="A8" t="s">
-        <v>57</v>
       </c>
       <c r="B8" s="2">
         <v>46253</v>
@@ -1720,22 +2350,22 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
         <v>46252</v>
@@ -1744,129 +2374,201 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1.253548991734727</v>
+        <v>1.14038771988262</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q8">
         <v>0.75</v>
       </c>
-      <c r="R8">
-        <v>0.707355</v>
-      </c>
-      <c r="S8">
-        <v>0.7097417734392341</v>
+      <c r="R8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S8" t="s">
+        <v>106</v>
       </c>
       <c r="T8">
-        <v>0.7064237405100262</v>
+        <v>-0.9196294928912929</v>
       </c>
       <c r="U8">
-        <v>0.707355</v>
-      </c>
-      <c r="V8">
-        <v>0.7145249999999999</v>
-      </c>
-      <c r="W8">
-        <v>0.7097417734392341</v>
+        <v>0.8132973957830469</v>
+      </c>
+      <c r="V8" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" t="s">
+        <v>96</v>
       </c>
       <c r="X8">
-        <v>0.6996549999999999</v>
+        <v>0.9978564959278607</v>
       </c>
       <c r="Y8">
-        <v>0.003374222899723763</v>
+        <v>0.02617288771994366</v>
       </c>
       <c r="Z8">
-        <v>0.3099705765239066</v>
+        <v>140.4884676350799</v>
       </c>
       <c r="AA8">
-        <v>0.003374222899723763</v>
+        <v>-31.99999999999999</v>
       </c>
       <c r="AB8">
-        <v>0.4134204767679452</v>
+        <v>-0.7714965393726552</v>
       </c>
       <c r="AC8">
+        <v>0.6362335182431189</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH8">
+        <v>-0.3949959217197102</v>
+      </c>
+      <c r="AI8">
+        <v>0.7286974106680848</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.034821703662467</v>
+      </c>
+      <c r="AK8">
+        <v>0.7289239759964443</v>
+      </c>
+      <c r="AL8">
+        <v>-0.6652119309142848</v>
+      </c>
+      <c r="AM8">
+        <v>3.364540723262911</v>
+      </c>
+      <c r="AN8">
+        <v>0.5719917185265165</v>
+      </c>
+      <c r="AO8">
+        <v>0.04823934841634513</v>
+      </c>
+      <c r="AP8">
+        <v>159.111</v>
+      </c>
+      <c r="AQ8">
+        <v>158.8976868153578</v>
+      </c>
+      <c r="AR8">
+        <v>161.7620918338071</v>
+      </c>
+      <c r="AS8">
+        <v>159.111</v>
+      </c>
+      <c r="AT8">
+        <v>154.59</v>
+      </c>
+      <c r="AU8">
+        <v>158.8723335</v>
+      </c>
+      <c r="AV8">
+        <v>160.2745</v>
+      </c>
+      <c r="AW8">
+        <v>-0.001340656426282122</v>
+      </c>
+      <c r="AX8">
+        <v>0.2051280618822495</v>
+      </c>
+      <c r="AY8">
+        <v>0.001340656426282122</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4745459057446484</v>
+      </c>
+      <c r="BA8">
         <v>0.2</v>
       </c>
-      <c r="AD8">
-        <v>0.3865795232320547</v>
-      </c>
-      <c r="AE8" t="s">
+      <c r="BB8">
+        <v>0.3254540942553517</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
+        <v>100000</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>375</v>
+      </c>
+      <c r="BG8">
+        <v>0.007312505106498063</v>
+      </c>
+      <c r="BH8">
+        <v>68376.0206274165</v>
+      </c>
+      <c r="BI8">
+        <v>51282.01547056237</v>
+      </c>
+      <c r="BJ8">
+        <v>322.3033949290896</v>
+      </c>
+      <c r="BK8">
+        <v>512.8201547056237</v>
+      </c>
+      <c r="BL8">
+        <v>0.005128201547056238</v>
+      </c>
+      <c r="BM8">
+        <v>375.0000000000001</v>
+      </c>
+      <c r="BN8">
+        <v>0.003750000000000001</v>
+      </c>
+      <c r="BO8">
+        <v>2.873362164760643</v>
+      </c>
+      <c r="BP8">
+        <v>0.7501165232665784</v>
+      </c>
+      <c r="BQ8">
+        <v>2.504395345894933</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:75">
+      <c r="A9" t="s">
         <v>82</v>
-      </c>
-      <c r="AF8">
-        <v>100000</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>375</v>
-      </c>
-      <c r="AI8">
-        <v>0.01088562320192841</v>
-      </c>
-      <c r="AJ8">
-        <v>45932.14285714245</v>
-      </c>
-      <c r="AK8">
-        <v>34449.10714285684</v>
-      </c>
-      <c r="AL8">
-        <v>48701.29870129828</v>
-      </c>
-      <c r="AM8">
-        <v>344.4910714285684</v>
-      </c>
-      <c r="AN8">
-        <v>0.003444910714285684</v>
-      </c>
-      <c r="AO8">
-        <v>375</v>
-      </c>
-      <c r="AP8">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ8">
-        <v>0.01184220944847617</v>
-      </c>
-      <c r="AR8">
-        <v>0.001429859699966422</v>
-      </c>
-      <c r="AS8">
-        <v>0.005564338405102013</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51">
-      <c r="A9" t="s">
-        <v>58</v>
       </c>
       <c r="B9" s="2">
         <v>46253</v>
@@ -1875,22 +2577,22 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46252</v>
@@ -1899,129 +2601,201 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0.07086701662554831</v>
+        <v>0.9633919720979356</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="O9" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>7.8075</v>
-      </c>
-      <c r="S9">
-        <v>7.796140265336246</v>
+      <c r="R9" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" t="s">
+        <v>107</v>
       </c>
       <c r="T9">
-        <v>7.678155499477644</v>
+        <v>0.9978251093858237</v>
       </c>
       <c r="U9">
-        <v>7.8075</v>
-      </c>
-      <c r="V9">
-        <v>7.9177</v>
-      </c>
-      <c r="W9">
-        <v>7.79578875</v>
+        <v>0.8485278928039384</v>
+      </c>
+      <c r="V9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W9" t="s">
+        <v>96</v>
       </c>
       <c r="X9">
-        <v>7.86835</v>
+        <v>0.9980263743212707</v>
       </c>
       <c r="Y9">
-        <v>-0.001454977222382888</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>0.1924609695973725</v>
+        <v>-6.474376271949135</v>
       </c>
       <c r="AA9">
-        <v>0.001454977222382888</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="AB9">
-        <v>0.4154540573744712</v>
+        <v>0.9936223828780991</v>
       </c>
       <c r="AC9">
+        <v>-0.1127588588255848</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH9">
+        <v>0.4958306721141454</v>
+      </c>
+      <c r="AI9">
+        <v>0.7927347424177903</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7046525863479556</v>
+      </c>
+      <c r="AK9">
+        <v>-0.07877474972109345</v>
+      </c>
+      <c r="AL9">
+        <v>1.341511126839038</v>
+      </c>
+      <c r="AM9">
+        <v>-1.173495820312121</v>
+      </c>
+      <c r="AN9">
+        <v>1.216869280342908</v>
+      </c>
+      <c r="AO9">
+        <v>0.03107468972056124</v>
+      </c>
+      <c r="AP9">
+        <v>0.810115</v>
+      </c>
+      <c r="AQ9">
+        <v>0.8089575027810496</v>
+      </c>
+      <c r="AR9">
+        <v>0.8133859561880754</v>
+      </c>
+      <c r="AS9">
+        <v>0.810115</v>
+      </c>
+      <c r="AT9">
+        <v>0.8040450000000001</v>
+      </c>
+      <c r="AU9">
+        <v>0.8088998275</v>
+      </c>
+      <c r="AV9">
+        <v>0.8194049999999999</v>
+      </c>
+      <c r="AW9">
+        <v>-0.001428806057103523</v>
+      </c>
+      <c r="AX9">
+        <v>0.1308043595263733</v>
+      </c>
+      <c r="AY9">
+        <v>0.001428806057103523</v>
+      </c>
+      <c r="AZ9">
+        <v>0.3959447733810169</v>
+      </c>
+      <c r="BA9">
         <v>0.2</v>
       </c>
-      <c r="AD9">
-        <v>0.3845459426255288</v>
-      </c>
-      <c r="AE9" t="s">
+      <c r="BB9">
+        <v>0.404055226618983</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
+        <v>100000</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>500</v>
+      </c>
+      <c r="BG9">
+        <v>0.01146750769952406</v>
+      </c>
+      <c r="BH9">
+        <v>43601.45317545778</v>
+      </c>
+      <c r="BI9">
+        <v>43601.45317545778</v>
+      </c>
+      <c r="BJ9">
+        <v>53821.31324004342</v>
+      </c>
+      <c r="BK9">
+        <v>436.0145317545778</v>
+      </c>
+      <c r="BL9">
+        <v>0.004360145317545778</v>
+      </c>
+      <c r="BM9">
+        <v>500</v>
+      </c>
+      <c r="BN9">
+        <v>0.005</v>
+      </c>
+      <c r="BO9">
+        <v>0.01653145112279913</v>
+      </c>
+      <c r="BP9">
+        <v>0.002322769988777568</v>
+      </c>
+      <c r="BQ9">
+        <v>0.003887778187125053</v>
+      </c>
+      <c r="BR9">
+        <v>1</v>
+      </c>
+      <c r="BS9">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" t="s">
         <v>83</v>
-      </c>
-      <c r="AF9">
-        <v>100000</v>
-      </c>
-      <c r="AG9">
-        <v>100</v>
-      </c>
-      <c r="AH9">
-        <v>500</v>
-      </c>
-      <c r="AI9">
-        <v>0.007793788024335498</v>
-      </c>
-      <c r="AJ9">
-        <v>64153.65653245749</v>
-      </c>
-      <c r="AK9">
-        <v>64153.65653245749</v>
-      </c>
-      <c r="AL9">
-        <v>8216.926869350944</v>
-      </c>
-      <c r="AM9">
-        <v>641.5365653245749</v>
-      </c>
-      <c r="AN9">
-        <v>0.006415365653245749</v>
-      </c>
-      <c r="AO9">
-        <v>500</v>
-      </c>
-      <c r="AP9">
-        <v>0.005</v>
-      </c>
-      <c r="AQ9">
-        <v>0.09659844491165079</v>
-      </c>
-      <c r="AR9">
-        <v>0.01359212335736655</v>
-      </c>
-      <c r="AS9">
-        <v>0.02610163156644305</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" t="s">
-        <v>59</v>
       </c>
       <c r="B10" s="2">
         <v>46253</v>
@@ -2030,153 +2804,225 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2">
         <v>46252</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.02427946824172759</v>
       </c>
       <c r="L10">
-        <v>0.4332062325661995</v>
+        <v>1.432562669526511</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O10" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q10">
+        <v>0.9817903988187043</v>
+      </c>
+      <c r="R10" t="s">
+        <v>101</v>
+      </c>
+      <c r="S10" t="s">
+        <v>105</v>
+      </c>
+      <c r="T10">
+        <v>0.933315875994664</v>
+      </c>
+      <c r="U10">
+        <v>0.823612586994795</v>
+      </c>
+      <c r="V10" t="s">
+        <v>94</v>
+      </c>
+      <c r="W10" t="s">
+        <v>96</v>
+      </c>
+      <c r="X10">
+        <v>0.9999140902437478</v>
+      </c>
+      <c r="Y10">
+        <v>0.2197037257474797</v>
+      </c>
+      <c r="Z10">
+        <v>32.76443224784209</v>
+      </c>
+      <c r="AA10">
+        <v>-3.000000000000004</v>
+      </c>
+      <c r="AB10">
+        <v>0.8409027200932033</v>
+      </c>
+      <c r="AC10">
+        <v>0.5411863037252992</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH10">
+        <v>0.5127820335800138</v>
+      </c>
+      <c r="AI10">
+        <v>0.7900816218130932</v>
+      </c>
+      <c r="AJ10">
+        <v>1.172045796002494</v>
+      </c>
+      <c r="AK10">
+        <v>0.7660031978631556</v>
+      </c>
+      <c r="AL10">
+        <v>1.398291002628391</v>
+      </c>
+      <c r="AM10">
+        <v>-2.637059647908032</v>
+      </c>
+      <c r="AN10">
+        <v>1.164209014676019</v>
+      </c>
+      <c r="AO10">
+        <v>0.04066580633117039</v>
+      </c>
+      <c r="AP10">
+        <v>0.707355</v>
+      </c>
+      <c r="AQ10">
+        <v>0.7032781486468448</v>
+      </c>
+      <c r="AR10">
+        <v>0.6936267132876414</v>
+      </c>
+      <c r="AS10">
+        <v>0.707355</v>
+      </c>
+      <c r="AT10">
+        <v>0.7145249999999999</v>
+      </c>
+      <c r="AU10">
+        <v>0.7032781486468448</v>
+      </c>
+      <c r="AV10">
+        <v>0.715055</v>
+      </c>
+      <c r="AW10">
+        <v>-0.005763515283210219</v>
+      </c>
+      <c r="AX10">
+        <v>0.5294612146954712</v>
+      </c>
+      <c r="AY10">
+        <v>0.005763515283210219</v>
+      </c>
+      <c r="AZ10">
+        <v>0.4695529106389434</v>
+      </c>
+      <c r="BA10">
+        <v>0.2</v>
+      </c>
+      <c r="BB10">
+        <v>0.3304470893610566</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD10">
+        <v>100000</v>
+      </c>
+      <c r="BE10">
+        <v>100</v>
+      </c>
+      <c r="BF10">
+        <v>490.8951994093522</v>
+      </c>
+      <c r="BG10">
+        <v>0.01088562320192841</v>
+      </c>
+      <c r="BH10">
+        <v>45932.14285714245</v>
+      </c>
+      <c r="BI10">
+        <v>45095.73685431159</v>
+      </c>
+      <c r="BJ10">
+        <v>63752.62329991531</v>
+      </c>
+      <c r="BK10">
+        <v>450.9573685431159</v>
+      </c>
+      <c r="BL10">
+        <v>0.004509573685431159</v>
+      </c>
+      <c r="BM10">
+        <v>490.8951994093522</v>
+      </c>
+      <c r="BN10">
+        <v>0.004908951994093522</v>
+      </c>
+      <c r="BO10">
+        <v>0.00919809849144352</v>
+      </c>
+      <c r="BP10">
+        <v>0.0009901347101195673</v>
+      </c>
+      <c r="BQ10">
+        <v>0.005249656267135857</v>
+      </c>
+      <c r="BR10">
         <v>1</v>
       </c>
-      <c r="R10">
-        <v>9.12626</v>
-      </c>
-      <c r="S10">
-        <v>9.102126592571794</v>
-      </c>
-      <c r="T10">
-        <v>8.989214972588059</v>
-      </c>
-      <c r="U10">
-        <v>9.12626</v>
-      </c>
-      <c r="V10">
-        <v>9.23343</v>
-      </c>
-      <c r="W10">
-        <v>9.102126592571794</v>
-      </c>
-      <c r="X10">
-        <v>9.209050000000001</v>
-      </c>
-      <c r="Y10">
-        <v>-0.002644391835013006</v>
-      </c>
-      <c r="Z10">
-        <v>0.2915014787801155</v>
-      </c>
-      <c r="AA10">
-        <v>0.002644391835013006</v>
-      </c>
-      <c r="AB10">
-        <v>0.4498879884360194</v>
-      </c>
-      <c r="AC10">
-        <v>0.2</v>
-      </c>
-      <c r="AD10">
-        <v>0.3501120115639806</v>
-      </c>
-      <c r="AE10" t="s">
+      <c r="BS10">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="AF10">
-        <v>100000</v>
-      </c>
-      <c r="AG10">
-        <v>100</v>
-      </c>
-      <c r="AH10">
-        <v>500</v>
-      </c>
-      <c r="AI10">
-        <v>0.009071624082592447</v>
-      </c>
-      <c r="AJ10">
-        <v>55116.92233361508</v>
-      </c>
-      <c r="AK10">
-        <v>55116.92233361508</v>
-      </c>
-      <c r="AL10">
-        <v>6039.376736320801</v>
-      </c>
-      <c r="AM10">
-        <v>551.1692233361507</v>
-      </c>
-      <c r="AN10">
-        <v>0.005511692233361507</v>
-      </c>
-      <c r="AO10">
-        <v>500</v>
-      </c>
-      <c r="AP10">
-        <v>0.005</v>
-      </c>
-      <c r="AQ10">
-        <v>0.09114280687534651</v>
-      </c>
-      <c r="AR10">
-        <v>0.01931721177399911</v>
-      </c>
-      <c r="AS10">
-        <v>0.02212244137492236</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>46253</v>
@@ -2185,22 +3031,22 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2">
         <v>46252</v>
@@ -2209,123 +3055,195 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.9338423918927403</v>
+        <v>0.07086701662554831</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
-      <c r="R11">
-        <v>0.810115</v>
-      </c>
-      <c r="S11">
-        <v>0.8075181930208151</v>
+      <c r="R11" t="s">
+        <v>101</v>
+      </c>
+      <c r="S11" t="s">
+        <v>105</v>
       </c>
       <c r="T11">
-        <v>0.8110987186855383</v>
+        <v>0.7764485855780732</v>
       </c>
       <c r="U11">
-        <v>0.810115</v>
-      </c>
-      <c r="V11">
-        <v>0.8040450000000001</v>
-      </c>
-      <c r="W11">
-        <v>0.8075181930208151</v>
+        <v>0.749368987564258</v>
+      </c>
+      <c r="V11" t="s">
+        <v>94</v>
+      </c>
+      <c r="W11" t="s">
+        <v>96</v>
       </c>
       <c r="X11">
-        <v>0.8194049999999999</v>
+        <v>0.9998684962165003</v>
       </c>
       <c r="Y11">
-        <v>-0.003205479443270353</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>0.2795271237012896</v>
+        <v>69.80251450562062</v>
       </c>
       <c r="AA11">
-        <v>0.003205479443270353</v>
+        <v>25</v>
       </c>
       <c r="AB11">
-        <v>0.3202839695672591</v>
+        <v>0.3452570115838208</v>
       </c>
       <c r="AC11">
+        <v>0.938508175751394</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH11">
+        <v>0.1726058044902589</v>
+      </c>
+      <c r="AI11">
+        <v>0.5930772642404968</v>
+      </c>
+      <c r="AJ11">
+        <v>0.2530756250093301</v>
+      </c>
+      <c r="AK11">
+        <v>0.580131888621675</v>
+      </c>
+      <c r="AL11">
+        <v>-0.05836330496217956</v>
+      </c>
+      <c r="AM11">
+        <v>-1.093069637526959</v>
+      </c>
+      <c r="AN11">
+        <v>0.2226812473251264</v>
+      </c>
+      <c r="AO11">
+        <v>0.06969208606949671</v>
+      </c>
+      <c r="AP11">
+        <v>7.8075</v>
+      </c>
+      <c r="AQ11">
+        <v>7.748514487180444</v>
+      </c>
+      <c r="AR11">
+        <v>7.573525580830044</v>
+      </c>
+      <c r="AS11">
+        <v>7.8075</v>
+      </c>
+      <c r="AT11">
+        <v>7.9177</v>
+      </c>
+      <c r="AU11">
+        <v>7.748514487180444</v>
+      </c>
+      <c r="AV11">
+        <v>7.86835</v>
+      </c>
+      <c r="AW11">
+        <v>-0.00755498082863355</v>
+      </c>
+      <c r="AX11">
+        <v>0.9693592903789157</v>
+      </c>
+      <c r="AY11">
+        <v>0.00755498082863355</v>
+      </c>
+      <c r="AZ11">
+        <v>0.4275318112671654</v>
+      </c>
+      <c r="BA11">
         <v>0.2</v>
       </c>
-      <c r="AD11">
-        <v>0.4797160304327409</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF11">
+      <c r="BB11">
+        <v>0.3724681887328345</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD11">
         <v>100000</v>
       </c>
-      <c r="AG11">
+      <c r="BE11">
         <v>100</v>
       </c>
-      <c r="AH11">
+      <c r="BF11">
         <v>500</v>
       </c>
-      <c r="AI11">
-        <v>0.01146750769952406</v>
-      </c>
-      <c r="AJ11">
-        <v>43601.45317545778</v>
-      </c>
-      <c r="AK11">
-        <v>43601.45317545778</v>
-      </c>
-      <c r="AL11">
-        <v>53821.31324004342</v>
-      </c>
-      <c r="AM11">
-        <v>436.0145317545778</v>
-      </c>
-      <c r="AN11">
-        <v>0.004360145317545778</v>
-      </c>
-      <c r="AO11">
+      <c r="BG11">
+        <v>0.007793788024335498</v>
+      </c>
+      <c r="BH11">
+        <v>64153.65653245749</v>
+      </c>
+      <c r="BI11">
+        <v>64153.65653245749</v>
+      </c>
+      <c r="BJ11">
+        <v>8216.926869350944</v>
+      </c>
+      <c r="BK11">
+        <v>641.5365653245749</v>
+      </c>
+      <c r="BL11">
+        <v>0.006415365653245749</v>
+      </c>
+      <c r="BM11">
         <v>500</v>
       </c>
-      <c r="AP11">
+      <c r="BN11">
         <v>0.005</v>
       </c>
-      <c r="AQ11">
-        <v>0.01898690559685134</v>
-      </c>
-      <c r="AR11">
-        <v>0.002837173800501619</v>
-      </c>
-      <c r="AS11">
-        <v>0.004172558780877277</v>
-      </c>
-      <c r="AT11">
+      <c r="BO11">
+        <v>0.1159615444415966</v>
+      </c>
+      <c r="BP11">
+        <v>0.007143888050169083</v>
+      </c>
+      <c r="BQ11">
+        <v>0.02404527632224423</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="AU11">
-        <v>0.03769389025774632</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY11" s="2">
+      <c r="BS11">
+        <v>0.03964493677299945</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW11" s="2">
         <v>46281</v>
       </c>
     </row>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -169,42 +241,39 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPCNH</t>
+  </si>
+  <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
+  </si>
+  <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
     <t>AUDUSD</t>
   </si>
   <si>
-    <t>AUDCNH</t>
-  </si>
-  <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>GBPCNH</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
     <t>ensemble</t>
   </si>
   <si>
-    <t>model</t>
-  </si>
-  <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
@@ -214,6 +283,9 @@
     <t>LOW</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -223,19 +295,19 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
+    <t>ALIGNED</t>
   </si>
   <si>
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>ALIGNED</t>
-  </si>
-  <si>
-    <t>BLOCK_STRONG_CONFLICT</t>
+    <t>NO_SIGNAL</t>
   </si>
   <si>
     <t>CONFIRM</t>
@@ -244,34 +316,88 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.20,drift4=0.49); metric_best=drift4; scores=model=0.124,naive=0.02922,drift4=0.01186; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=989.9,naive=440.2,drift4=531.5; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.65,naive=0.17,drift4=0.18); metric_best=model; scores=model=0.4817,naive=1.908,drift4=7.067</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.20,drift4=0.46); metric_best=drift4; scores=model=0.04179,naive=0.007454,drift4=0.005491; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.19,drift4=0.47); metric_best=drift4; scores=model=0.1196,naive=0.06594,drift4=0.02408</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.1451,naive=0.09382,drift4=0.05796; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.33,naive=0.13,drift4=0.53); metric_best=drift4; scores=model=0.01589,naive=0.01648,drift4=0.002444</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.28,naive=0.09,drift4=0.62); metric_best=drift4; scores=model=0.03066,naive=0.017,drift4=0.0005807</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.34,naive=0.13,drift4=0.52); metric_best=drift4; scores=model=0.05856,naive=0.06641,drift4=0.01053</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.05123,naive=0.009756,drift4=0.0135; naive_cap_applied</t>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
+    <t>UP_DECELERATING</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>空头减速</t>
+  </si>
+  <si>
+    <t>多头减速</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>UP_CREST_FLATTENING</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>上升坡顶钝化</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1011,naive=0.02555,drift4=0.03357; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=276.8,naive=98.21,drift4=133.7; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.01929,naive=0.006332,drift4=0.006052; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02232,naive=0.006625,drift4=0.006242; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03925,naive=0.01498,drift4=0.01512; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.1566,naive=0.03521,drift4=0.03531; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.08922,naive=0.009875,drift4=0.01206; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.966,naive=0.676,drift4=2.202; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.008955,naive=0.002031,drift4=0.003663; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01922,naive=0.008523,drift4=0.01127; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -645,10 +771,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,10 +928,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46254</v>
@@ -814,141 +1012,213 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46253</v>
       </c>
       <c r="K2">
-        <v>0.8544308170286511</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>3.373012898437886</v>
+        <v>0.5781780700216143</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
-        <v>6.7262</v>
-      </c>
-      <c r="S2">
-        <v>6.733304942846981</v>
+      <c r="R2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S2" t="s">
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>6.821474636375678</v>
+        <v>0.8843281615246334</v>
       </c>
       <c r="U2">
-        <v>6.7262</v>
-      </c>
-      <c r="V2">
-        <v>6.680200000000001</v>
+        <v>0.7979403523348219</v>
+      </c>
+      <c r="V2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W2" t="s">
+        <v>95</v>
+      </c>
+      <c r="X2">
+        <v>0.9999707185949473</v>
       </c>
       <c r="Y2">
-        <v>0.001056308591326593</v>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>48.6054717682086</v>
       </c>
       <c r="AA2">
-        <v>0.001056308591326593</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB2">
-        <v>0.3107772490047508</v>
+        <v>0.6612402264225222</v>
       </c>
       <c r="AC2">
+        <v>0.7501742217383183</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>0.3306104321898076</v>
+      </c>
+      <c r="AI2">
+        <v>0.6903604912104218</v>
+      </c>
+      <c r="AJ2">
+        <v>0.4542375573949776</v>
+      </c>
+      <c r="AK2">
+        <v>0.5013875605815916</v>
+      </c>
+      <c r="AL2">
+        <v>0.6464621698535724</v>
+      </c>
+      <c r="AM2">
+        <v>-0.836181056609497</v>
+      </c>
+      <c r="AN2">
+        <v>0.5620402351596001</v>
+      </c>
+      <c r="AO2">
+        <v>0.05334218816377579</v>
+      </c>
+      <c r="AP2">
+        <v>9.15645</v>
+      </c>
+      <c r="AQ2">
+        <v>9.163802224345721</v>
+      </c>
+      <c r="AR2">
+        <v>9.036997556714635</v>
+      </c>
+      <c r="AS2">
+        <v>9.15645</v>
+      </c>
+      <c r="AT2">
+        <v>9.293809999999999</v>
+      </c>
+      <c r="AW2">
+        <v>0.0008029557684169718</v>
+      </c>
+      <c r="AY2">
+        <v>0.0008029557684169718</v>
+      </c>
+      <c r="AZ2">
+        <v>0.3992632691101521</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.4892227509952493</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="BB2">
+        <v>0.400736730889848</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
+        <v>100000</v>
+      </c>
+      <c r="BE2">
+        <v>100</v>
+      </c>
+      <c r="BF2">
+        <v>0</v>
+      </c>
+      <c r="BH2">
+        <v>0</v>
+      </c>
+      <c r="BI2">
+        <v>0</v>
+      </c>
+      <c r="BJ2">
+        <v>0</v>
+      </c>
+      <c r="BK2">
+        <v>0</v>
+      </c>
+      <c r="BL2">
+        <v>0</v>
+      </c>
+      <c r="BM2">
+        <v>0</v>
+      </c>
+      <c r="BN2">
+        <v>0</v>
+      </c>
+      <c r="BO2">
+        <v>0.1011178684330099</v>
+      </c>
+      <c r="BP2">
+        <v>0.02555118686527646</v>
+      </c>
+      <c r="BQ2">
+        <v>0.03356821077507182</v>
+      </c>
+      <c r="BR2">
+        <v>1</v>
+      </c>
+      <c r="BS2">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW2" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="3" spans="1:75">
+      <c r="A3" t="s">
         <v>76</v>
-      </c>
-      <c r="AF2">
-        <v>100000</v>
-      </c>
-      <c r="AG2">
-        <v>100</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>0</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>0</v>
-      </c>
-      <c r="AO2">
-        <v>0</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0.07349335688046871</v>
-      </c>
-      <c r="AR2">
-        <v>0.0108713637128573</v>
-      </c>
-      <c r="AS2">
-        <v>0.01279087660342946</v>
-      </c>
-      <c r="AT2">
-        <v>1</v>
-      </c>
-      <c r="AU2">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY2" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="3" spans="1:51">
-      <c r="A3" t="s">
-        <v>52</v>
       </c>
       <c r="B3" s="2">
         <v>46254</v>
@@ -957,22 +1227,22 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46253</v>
@@ -981,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1.419803310739046</v>
+        <v>1.425699501519865</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -990,120 +1260,192 @@
         <v>6</v>
       </c>
       <c r="O3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q3">
         <v>0.75</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" t="s">
+        <v>104</v>
+      </c>
+      <c r="T3">
+        <v>0.9387787232160607</v>
+      </c>
+      <c r="U3">
+        <v>0.8220264675511796</v>
+      </c>
+      <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X3">
+        <v>0.9983041684158089</v>
+      </c>
+      <c r="Y3">
+        <v>0.06825432873385694</v>
+      </c>
+      <c r="Z3">
+        <v>33.50748502364006</v>
+      </c>
+      <c r="AA3">
+        <v>-28</v>
+      </c>
+      <c r="AB3">
+        <v>0.8338137108382806</v>
+      </c>
+      <c r="AC3">
+        <v>0.5520459180340854</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH3">
+        <v>0.4446072930965568</v>
+      </c>
+      <c r="AI3">
+        <v>0.7564924193643786</v>
+      </c>
+      <c r="AJ3">
+        <v>1.173589067040108</v>
+      </c>
+      <c r="AK3">
+        <v>0.90980182733142</v>
+      </c>
+      <c r="AL3">
+        <v>1.36601229944368</v>
+      </c>
+      <c r="AM3">
+        <v>-2.966708736995491</v>
+      </c>
+      <c r="AN3">
+        <v>1.09181223998737</v>
+      </c>
+      <c r="AO3">
+        <v>0.04472679052940127</v>
+      </c>
+      <c r="AP3">
         <v>4459.799999999999</v>
       </c>
-      <c r="S3">
-        <v>4654.629514776308</v>
-      </c>
-      <c r="T3">
-        <v>4551.531010633514</v>
-      </c>
-      <c r="U3">
+      <c r="AQ3">
+        <v>4571.029223550129</v>
+      </c>
+      <c r="AR3">
+        <v>4349.981174304025</v>
+      </c>
+      <c r="AS3">
         <v>4459.799999999999</v>
       </c>
-      <c r="V3">
+      <c r="AT3">
         <v>4873.709999999999</v>
       </c>
-      <c r="W3">
-        <v>4654.629514776308</v>
-      </c>
-      <c r="X3">
+      <c r="AU3">
+        <v>4571.029223550129</v>
+      </c>
+      <c r="AV3">
         <v>4320.98</v>
       </c>
-      <c r="Y3">
-        <v>0.04368570670799347</v>
-      </c>
-      <c r="Z3">
-        <v>1.403468626828341</v>
-      </c>
-      <c r="AA3">
-        <v>0.04368570670799347</v>
-      </c>
-      <c r="AB3">
-        <v>0.4230520602591145</v>
-      </c>
-      <c r="AC3">
+      <c r="AW3">
+        <v>0.02494040619537423</v>
+      </c>
+      <c r="AX3">
+        <v>0.8012478284838681</v>
+      </c>
+      <c r="AY3">
+        <v>0.02494040619537423</v>
+      </c>
+      <c r="AZ3">
+        <v>0.419871440449453</v>
+      </c>
+      <c r="BA3">
         <v>0.2</v>
       </c>
-      <c r="AD3">
-        <v>0.3769479397408855</v>
-      </c>
-      <c r="AE3" t="s">
+      <c r="BB3">
+        <v>0.380128559550547</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
+        <v>100000</v>
+      </c>
+      <c r="BE3">
+        <v>100</v>
+      </c>
+      <c r="BF3">
+        <v>375</v>
+      </c>
+      <c r="BG3">
+        <v>0.03112695636575615</v>
+      </c>
+      <c r="BH3">
+        <v>16063.24737069595</v>
+      </c>
+      <c r="BI3">
+        <v>12047.43552802196</v>
+      </c>
+      <c r="BJ3">
+        <v>2.701339864572843</v>
+      </c>
+      <c r="BK3">
+        <v>120.4743552802196</v>
+      </c>
+      <c r="BL3">
+        <v>0.001204743552802196</v>
+      </c>
+      <c r="BM3">
+        <v>375</v>
+      </c>
+      <c r="BN3">
+        <v>0.00375</v>
+      </c>
+      <c r="BO3">
+        <v>276.8197345618283</v>
+      </c>
+      <c r="BP3">
+        <v>98.20575709988094</v>
+      </c>
+      <c r="BQ3">
+        <v>133.6514356744719</v>
+      </c>
+      <c r="BR3">
+        <v>1</v>
+      </c>
+      <c r="BS3">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW3" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:75">
+      <c r="A4" t="s">
         <v>77</v>
-      </c>
-      <c r="AF3">
-        <v>100000</v>
-      </c>
-      <c r="AG3">
-        <v>100</v>
-      </c>
-      <c r="AH3">
-        <v>375</v>
-      </c>
-      <c r="AI3">
-        <v>0.03112695636575615</v>
-      </c>
-      <c r="AJ3">
-        <v>16063.24737069595</v>
-      </c>
-      <c r="AK3">
-        <v>12047.43552802196</v>
-      </c>
-      <c r="AL3">
-        <v>2.701339864572843</v>
-      </c>
-      <c r="AM3">
-        <v>120.4743552802196</v>
-      </c>
-      <c r="AN3">
-        <v>0.001204743552802196</v>
-      </c>
-      <c r="AO3">
-        <v>375</v>
-      </c>
-      <c r="AP3">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ3">
-        <v>378.1553170065869</v>
-      </c>
-      <c r="AR3">
-        <v>133.7257779252185</v>
-      </c>
-      <c r="AS3">
-        <v>154.6443837832282</v>
-      </c>
-      <c r="AT3">
-        <v>1</v>
-      </c>
-      <c r="AU3">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY3" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:51">
-      <c r="A4" t="s">
-        <v>53</v>
       </c>
       <c r="B4" s="2">
         <v>46254</v>
@@ -1112,153 +1454,225 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
         <v>46253</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1.298314982471483</v>
+        <v>2.476432103856031</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>158.7225</v>
-      </c>
-      <c r="S4">
-        <v>161.0386381299522</v>
+      <c r="R4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S4" t="s">
+        <v>104</v>
       </c>
       <c r="T4">
-        <v>163.5867128900194</v>
+        <v>0.911331543491438</v>
       </c>
       <c r="U4">
-        <v>158.7225</v>
-      </c>
-      <c r="V4">
-        <v>153.813</v>
-      </c>
-      <c r="W4">
-        <v>161.0386381299522</v>
+        <v>0.9600891646449576</v>
+      </c>
+      <c r="V4" t="s">
+        <v>93</v>
+      </c>
+      <c r="W4" t="s">
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>157.1784079133652</v>
+        <v>0.9999598802952427</v>
       </c>
       <c r="Y4">
-        <v>0.0145923743007591</v>
+        <v>1</v>
       </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>34.64808410787485</v>
       </c>
       <c r="AA4">
-        <v>0.0145923743007591</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB4">
-        <v>0.653601907163825</v>
+        <v>0.8226595294878541</v>
       </c>
       <c r="AC4">
-        <v>0.1705918616893499</v>
-      </c>
-      <c r="AD4">
-        <v>0.175806231146825</v>
+        <v>0.5685343424480375</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH4">
+        <v>0.8226265246304153</v>
+      </c>
+      <c r="AI4">
+        <v>0.9397469757820209</v>
+      </c>
+      <c r="AJ4">
+        <v>1.886753805740311</v>
+      </c>
+      <c r="AK4">
+        <v>1.268310300213958</v>
+      </c>
+      <c r="AL4">
+        <v>3.034765938404792</v>
+      </c>
+      <c r="AM4">
+        <v>-2.617596247757652</v>
+      </c>
+      <c r="AN4">
+        <v>2.782946818459877</v>
+      </c>
+      <c r="AO4">
+        <v>0.04691227445113542</v>
+      </c>
+      <c r="AP4">
+        <v>1.363285</v>
+      </c>
+      <c r="AQ4">
+        <v>1.369985825518027</v>
+      </c>
+      <c r="AR4">
+        <v>1.349773617780689</v>
+      </c>
+      <c r="AS4">
+        <v>1.363285</v>
+      </c>
+      <c r="AT4">
+        <v>1.392</v>
+      </c>
+      <c r="AU4">
+        <v>1.369985825518027</v>
+      </c>
+      <c r="AV4">
+        <v>1.35136</v>
+      </c>
+      <c r="AW4">
+        <v>0.004915205197758909</v>
+      </c>
+      <c r="AX4">
+        <v>0.5619140895619911</v>
+      </c>
+      <c r="AY4">
+        <v>0.004915205197758909</v>
+      </c>
+      <c r="AZ4">
+        <v>0.3853319566299963</v>
+      </c>
+      <c r="BA4">
+        <v>0.2</v>
+      </c>
+      <c r="BB4">
+        <v>0.4146680433700037</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
+        <v>100000</v>
+      </c>
+      <c r="BE4">
+        <v>100</v>
+      </c>
+      <c r="BF4">
+        <v>500</v>
+      </c>
+      <c r="BG4">
+        <v>0.008747253875748665</v>
+      </c>
+      <c r="BH4">
+        <v>57160.79664570222</v>
+      </c>
+      <c r="BI4">
+        <v>57160.79664570222</v>
+      </c>
+      <c r="BJ4">
+        <v>41928.72117400412</v>
+      </c>
+      <c r="BK4">
+        <v>571.6079664570221</v>
+      </c>
+      <c r="BL4">
+        <v>0.005716079664570222</v>
+      </c>
+      <c r="BM4">
+        <v>500</v>
+      </c>
+      <c r="BN4">
+        <v>0.005</v>
+      </c>
+      <c r="BO4">
+        <v>0.01929412441718169</v>
+      </c>
+      <c r="BP4">
+        <v>0.006331878104713164</v>
+      </c>
+      <c r="BQ4">
+        <v>0.006052454349751199</v>
+      </c>
+      <c r="BR4">
+        <v>1</v>
+      </c>
+      <c r="BS4">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW4" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="5" spans="1:75">
+      <c r="A5" t="s">
         <v>78</v>
-      </c>
-      <c r="AF4">
-        <v>100000</v>
-      </c>
-      <c r="AG4">
-        <v>100</v>
-      </c>
-      <c r="AH4">
-        <v>500</v>
-      </c>
-      <c r="AI4">
-        <v>0.009728249533839399</v>
-      </c>
-      <c r="AJ4">
-        <v>51396.70793401899</v>
-      </c>
-      <c r="AK4">
-        <v>51396.70793401899</v>
-      </c>
-      <c r="AL4">
-        <v>323.8148840524752</v>
-      </c>
-      <c r="AM4">
-        <v>513.9670793401899</v>
-      </c>
-      <c r="AN4">
-        <v>0.005139670793401899</v>
-      </c>
-      <c r="AO4">
-        <v>500</v>
-      </c>
-      <c r="AP4">
-        <v>0.005</v>
-      </c>
-      <c r="AQ4">
-        <v>3.690935444663191</v>
-      </c>
-      <c r="AR4">
-        <v>0.8918330746389613</v>
-      </c>
-      <c r="AS4">
-        <v>2.823281972119873</v>
-      </c>
-      <c r="AT4">
-        <v>1</v>
-      </c>
-      <c r="AU4">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY4" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="5" spans="1:51">
-      <c r="A5" t="s">
-        <v>54</v>
       </c>
       <c r="B5" s="2">
         <v>46254</v>
@@ -1267,31 +1681,31 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
         <v>46253</v>
       </c>
       <c r="K5">
-        <v>0.05736538233206671</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>1.462360520978653</v>
+        <v>2.098247299854969</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1300,120 +1714,192 @@
         <v>10</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P5" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.7643413455830167</v>
-      </c>
-      <c r="R5">
-        <v>0.710915</v>
-      </c>
-      <c r="S5">
-        <v>0.7160642116735914</v>
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" t="s">
+        <v>104</v>
       </c>
       <c r="T5">
-        <v>0.711570215142442</v>
+        <v>0.8372223440523791</v>
       </c>
       <c r="U5">
-        <v>0.710915</v>
-      </c>
-      <c r="V5">
-        <v>0.7216449999999999</v>
-      </c>
-      <c r="W5">
-        <v>0.7160642116735914</v>
+        <v>0.926727600597396</v>
+      </c>
+      <c r="V5" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" t="s">
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.7032149999999999</v>
+        <v>0.9999101830953019</v>
       </c>
       <c r="Y5">
-        <v>0.007243076420657029</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>0.6687287887780969</v>
+        <v>47.59009277023014</v>
       </c>
       <c r="AA5">
-        <v>0.007243076420657029</v>
+        <v>14.00000000000001</v>
       </c>
       <c r="AB5">
-        <v>0.3409291984862462</v>
+        <v>0.6744300666062889</v>
       </c>
       <c r="AC5">
+        <v>0.7383387334126774</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH5">
+        <v>0.674369491385271</v>
+      </c>
+      <c r="AI5">
+        <v>0.8942277757563757</v>
+      </c>
+      <c r="AJ5">
+        <v>1.620148793511938</v>
+      </c>
+      <c r="AK5">
+        <v>1.691258887943281</v>
+      </c>
+      <c r="AL5">
+        <v>2.448955539854732</v>
+      </c>
+      <c r="AM5">
+        <v>-2.030293092778862</v>
+      </c>
+      <c r="AN5">
+        <v>2.26216891955886</v>
+      </c>
+      <c r="AO5">
+        <v>0.05379872205911085</v>
+      </c>
+      <c r="AP5">
+        <v>1.168215</v>
+      </c>
+      <c r="AQ5">
+        <v>1.172691649512342</v>
+      </c>
+      <c r="AR5">
+        <v>1.14794271536709</v>
+      </c>
+      <c r="AS5">
+        <v>1.168215</v>
+      </c>
+      <c r="AT5">
+        <v>1.19712</v>
+      </c>
+      <c r="AU5">
+        <v>1.172691649512342</v>
+      </c>
+      <c r="AV5">
+        <v>1.154915</v>
+      </c>
+      <c r="AW5">
+        <v>0.003832042485622986</v>
+      </c>
+      <c r="AX5">
+        <v>0.3365901888978982</v>
+      </c>
+      <c r="AY5">
+        <v>0.003832042485622986</v>
+      </c>
+      <c r="AZ5">
+        <v>0.3791862569650508</v>
+      </c>
+      <c r="BA5">
         <v>0.2</v>
       </c>
-      <c r="AD5">
-        <v>0.4590708015137539</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="BB5">
+        <v>0.4208137430349492</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
+        <v>100000</v>
+      </c>
+      <c r="BE5">
+        <v>100</v>
+      </c>
+      <c r="BF5">
+        <v>500</v>
+      </c>
+      <c r="BG5">
+        <v>0.01138489062372939</v>
+      </c>
+      <c r="BH5">
+        <v>43917.85714285703</v>
+      </c>
+      <c r="BI5">
+        <v>43917.85714285703</v>
+      </c>
+      <c r="BJ5">
+        <v>37593.98496240592</v>
+      </c>
+      <c r="BK5">
+        <v>439.1785714285703</v>
+      </c>
+      <c r="BL5">
+        <v>0.004391785714285703</v>
+      </c>
+      <c r="BM5">
+        <v>500</v>
+      </c>
+      <c r="BN5">
+        <v>0.005</v>
+      </c>
+      <c r="BO5">
+        <v>0.02231554613837267</v>
+      </c>
+      <c r="BP5">
+        <v>0.006625069795342857</v>
+      </c>
+      <c r="BQ5">
+        <v>0.006241516887333231</v>
+      </c>
+      <c r="BR5">
+        <v>1</v>
+      </c>
+      <c r="BS5">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW5" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:75">
+      <c r="A6" t="s">
         <v>79</v>
-      </c>
-      <c r="AF5">
-        <v>100000</v>
-      </c>
-      <c r="AG5">
-        <v>100</v>
-      </c>
-      <c r="AH5">
-        <v>382.1706727915084</v>
-      </c>
-      <c r="AI5">
-        <v>0.0108311120176112</v>
-      </c>
-      <c r="AJ5">
-        <v>46163.31168831128</v>
-      </c>
-      <c r="AK5">
-        <v>35284.52777241205</v>
-      </c>
-      <c r="AL5">
-        <v>49632.55490798766</v>
-      </c>
-      <c r="AM5">
-        <v>352.8452777241205</v>
-      </c>
-      <c r="AN5">
-        <v>0.003528452777241205</v>
-      </c>
-      <c r="AO5">
-        <v>382.1706727915084</v>
-      </c>
-      <c r="AP5">
-        <v>0.003821706727915084</v>
-      </c>
-      <c r="AQ5">
-        <v>0.01083393097625526</v>
-      </c>
-      <c r="AR5">
-        <v>0.002497708205639136</v>
-      </c>
-      <c r="AS5">
-        <v>0.003864383335192844</v>
-      </c>
-      <c r="AT5">
-        <v>1</v>
-      </c>
-      <c r="AU5">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY5" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="6" spans="1:51">
-      <c r="A6" t="s">
-        <v>55</v>
       </c>
       <c r="B6" s="2">
         <v>46254</v>
@@ -1422,22 +1908,22 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
         <v>46253</v>
@@ -1455,120 +1941,192 @@
         <v>6</v>
       </c>
       <c r="O6" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>0.75</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>104</v>
+      </c>
+      <c r="T6">
+        <v>0.8497579668037913</v>
+      </c>
+      <c r="U6">
+        <v>0.7823822726760881</v>
+      </c>
+      <c r="V6" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" t="s">
+        <v>95</v>
+      </c>
+      <c r="X6">
+        <v>0.9999647504575279</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>55.94453004495183</v>
+      </c>
+      <c r="AA6">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AB6">
+        <v>0.5599952602082706</v>
+      </c>
+      <c r="AC6">
+        <v>0.8284958108187822</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH6">
+        <v>0.2799877603157809</v>
+      </c>
+      <c r="AI6">
+        <v>0.6594540373169837</v>
+      </c>
+      <c r="AJ6">
+        <v>0.3913817078300837</v>
+      </c>
+      <c r="AK6">
+        <v>0.5590562862638696</v>
+      </c>
+      <c r="AL6">
+        <v>0.4842945765041812</v>
+      </c>
+      <c r="AM6">
+        <v>-0.6991426692546785</v>
+      </c>
+      <c r="AN6">
+        <v>0.4179375416273116</v>
+      </c>
+      <c r="AO6">
+        <v>0.05688135603754795</v>
+      </c>
+      <c r="AP6">
         <v>4.79463</v>
       </c>
-      <c r="S6">
-        <v>4.819683433022941</v>
-      </c>
-      <c r="T6">
-        <v>4.773429669737864</v>
-      </c>
-      <c r="U6">
+      <c r="AQ6">
+        <v>4.80105757886611</v>
+      </c>
+      <c r="AR6">
+        <v>4.741396593121281</v>
+      </c>
+      <c r="AS6">
         <v>4.79463</v>
       </c>
-      <c r="V6">
+      <c r="AT6">
         <v>4.863359999999999</v>
       </c>
-      <c r="W6">
-        <v>4.819683433022941</v>
-      </c>
-      <c r="X6">
+      <c r="AU6">
+        <v>4.801821944999999</v>
+      </c>
+      <c r="AV6">
         <v>4.7597825</v>
       </c>
-      <c r="Y6">
-        <v>0.005225311029827292</v>
-      </c>
-      <c r="Z6">
-        <v>0.718944917797285</v>
-      </c>
-      <c r="AA6">
-        <v>0.005225311029827292</v>
-      </c>
-      <c r="AB6">
-        <v>0.3392746273114318</v>
-      </c>
-      <c r="AC6">
-        <v>0.1915537275335136</v>
-      </c>
-      <c r="AD6">
-        <v>0.4691716451550546</v>
-      </c>
-      <c r="AE6" t="s">
+      <c r="AW6">
+        <v>0.001340578702863436</v>
+      </c>
+      <c r="AX6">
+        <v>0.2063833847478303</v>
+      </c>
+      <c r="AY6">
+        <v>0.001340578702863436</v>
+      </c>
+      <c r="AZ6">
+        <v>0.3981228663296886</v>
+      </c>
+      <c r="BA6">
+        <v>0.2</v>
+      </c>
+      <c r="BB6">
+        <v>0.4018771336703114</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
+        <v>100000</v>
+      </c>
+      <c r="BE6">
+        <v>100</v>
+      </c>
+      <c r="BF6">
+        <v>375</v>
+      </c>
+      <c r="BG6">
+        <v>0.007268026938470731</v>
+      </c>
+      <c r="BH6">
+        <v>68794.46158261009</v>
+      </c>
+      <c r="BI6">
+        <v>51595.84618695757</v>
+      </c>
+      <c r="BJ6">
+        <v>10761.1736853433</v>
+      </c>
+      <c r="BK6">
+        <v>515.9584618695757</v>
+      </c>
+      <c r="BL6">
+        <v>0.005159584618695757</v>
+      </c>
+      <c r="BM6">
+        <v>375</v>
+      </c>
+      <c r="BN6">
+        <v>0.00375</v>
+      </c>
+      <c r="BO6">
+        <v>0.03924837962525179</v>
+      </c>
+      <c r="BP6">
+        <v>0.01497957627324833</v>
+      </c>
+      <c r="BQ6">
+        <v>0.01512112759770574</v>
+      </c>
+      <c r="BR6">
+        <v>1</v>
+      </c>
+      <c r="BS6">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW6" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:75">
+      <c r="A7" t="s">
         <v>80</v>
-      </c>
-      <c r="AF6">
-        <v>100000</v>
-      </c>
-      <c r="AG6">
-        <v>100</v>
-      </c>
-      <c r="AH6">
-        <v>375</v>
-      </c>
-      <c r="AI6">
-        <v>0.007268026938470731</v>
-      </c>
-      <c r="AJ6">
-        <v>68794.46158261009</v>
-      </c>
-      <c r="AK6">
-        <v>51595.84618695757</v>
-      </c>
-      <c r="AL6">
-        <v>10761.1736853433</v>
-      </c>
-      <c r="AM6">
-        <v>515.9584618695757</v>
-      </c>
-      <c r="AN6">
-        <v>0.005159584618695757</v>
-      </c>
-      <c r="AO6">
-        <v>375</v>
-      </c>
-      <c r="AP6">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ6">
-        <v>0.04648578062612102</v>
-      </c>
-      <c r="AR6">
-        <v>0.01925124810247776</v>
-      </c>
-      <c r="AS6">
-        <v>0.01438259946121461</v>
-      </c>
-      <c r="AT6">
-        <v>1</v>
-      </c>
-      <c r="AU6">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY6" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="7" spans="1:51">
-      <c r="A7" t="s">
-        <v>56</v>
       </c>
       <c r="B7" s="2">
         <v>46254</v>
@@ -1577,22 +2135,22 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2">
         <v>46253</v>
@@ -1610,120 +2168,192 @@
         <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
-      </c>
-      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>100</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
+      </c>
+      <c r="T7">
+        <v>0.7948947594915265</v>
+      </c>
+      <c r="U7">
+        <v>0.7576991604779089</v>
+      </c>
+      <c r="V7" t="s">
+        <v>93</v>
+      </c>
+      <c r="W7" t="s">
+        <v>95</v>
+      </c>
+      <c r="X7">
+        <v>0.9999860748268876</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>66.46375324164961</v>
+      </c>
+      <c r="AA7">
+        <v>13.00000000000001</v>
+      </c>
+      <c r="AB7">
+        <v>0.3993291444769469</v>
+      </c>
+      <c r="AC7">
+        <v>0.9168076321515379</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH7">
+        <v>0.1996617918747406</v>
+      </c>
+      <c r="AI7">
+        <v>0.608347542252906</v>
+      </c>
+      <c r="AJ7">
+        <v>0.5353949232934802</v>
+      </c>
+      <c r="AK7">
+        <v>1.162963241903283</v>
+      </c>
+      <c r="AL7">
+        <v>0.6691324286627586</v>
+      </c>
+      <c r="AM7">
+        <v>-0.6677289918141179</v>
+      </c>
+      <c r="AN7">
+        <v>0.6048684398241793</v>
+      </c>
+      <c r="AO7">
+        <v>0.07630884853059125</v>
+      </c>
+      <c r="AP7">
         <v>7.86</v>
       </c>
-      <c r="S7">
-        <v>7.897871097294477</v>
-      </c>
-      <c r="T7">
-        <v>7.784608293362252</v>
-      </c>
-      <c r="U7">
+      <c r="AQ7">
+        <v>7.849252726758345</v>
+      </c>
+      <c r="AR7">
+        <v>7.644023815283218</v>
+      </c>
+      <c r="AS7">
         <v>7.86</v>
       </c>
-      <c r="V7">
+      <c r="AT7">
         <v>8.0227</v>
       </c>
-      <c r="W7">
-        <v>7.897871097294477</v>
-      </c>
-      <c r="X7">
-        <v>7.798825000000001</v>
-      </c>
-      <c r="Y7">
-        <v>0.004818205762656038</v>
-      </c>
-      <c r="Z7">
-        <v>0.6190616639881774</v>
-      </c>
-      <c r="AA7">
-        <v>0.004818205762656038</v>
-      </c>
-      <c r="AB7">
-        <v>0.3876191405773744</v>
-      </c>
-      <c r="AC7">
+      <c r="AU7">
+        <v>7.84821</v>
+      </c>
+      <c r="AV7">
+        <v>7.921175</v>
+      </c>
+      <c r="AW7">
+        <v>-0.001367337562551573</v>
+      </c>
+      <c r="AX7">
+        <v>0.1927257866775658</v>
+      </c>
+      <c r="AY7">
+        <v>0.001367337562551573</v>
+      </c>
+      <c r="AZ7">
+        <v>0.3721049248107365</v>
+      </c>
+      <c r="BA7">
         <v>0.2</v>
       </c>
-      <c r="AD7">
-        <v>0.4123808594226257</v>
-      </c>
-      <c r="AE7" t="s">
+      <c r="BB7">
+        <v>0.4278950751892635</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
+        <v>100000</v>
+      </c>
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>500</v>
+      </c>
+      <c r="BG7">
+        <v>0.007783078880407066</v>
+      </c>
+      <c r="BH7">
+        <v>64241.92889252194</v>
+      </c>
+      <c r="BI7">
+        <v>64241.92889252194</v>
+      </c>
+      <c r="BJ7">
+        <v>8173.273395995158</v>
+      </c>
+      <c r="BK7">
+        <v>642.4192889252195</v>
+      </c>
+      <c r="BL7">
+        <v>0.006424192889252195</v>
+      </c>
+      <c r="BM7">
+        <v>500</v>
+      </c>
+      <c r="BN7">
+        <v>0.005</v>
+      </c>
+      <c r="BO7">
+        <v>0.1566289190579347</v>
+      </c>
+      <c r="BP7">
+        <v>0.03520613265407405</v>
+      </c>
+      <c r="BQ7">
+        <v>0.0353051358246164</v>
+      </c>
+      <c r="BR7">
+        <v>1</v>
+      </c>
+      <c r="BS7">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW7" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:75">
+      <c r="A8" t="s">
         <v>81</v>
-      </c>
-      <c r="AF7">
-        <v>100000</v>
-      </c>
-      <c r="AG7">
-        <v>100</v>
-      </c>
-      <c r="AH7">
-        <v>375</v>
-      </c>
-      <c r="AI7">
-        <v>0.007783078880407066</v>
-      </c>
-      <c r="AJ7">
-        <v>64241.92889252194</v>
-      </c>
-      <c r="AK7">
-        <v>48181.44666939146</v>
-      </c>
-      <c r="AL7">
-        <v>6129.955046996369</v>
-      </c>
-      <c r="AM7">
-        <v>481.8144666939146</v>
-      </c>
-      <c r="AN7">
-        <v>0.004818144666939146</v>
-      </c>
-      <c r="AO7">
-        <v>375</v>
-      </c>
-      <c r="AP7">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ7">
-        <v>0.1372038539960127</v>
-      </c>
-      <c r="AR7">
-        <v>0.03880658517066761</v>
-      </c>
-      <c r="AS7">
-        <v>0.03130686654020728</v>
-      </c>
-      <c r="AT7">
-        <v>1</v>
-      </c>
-      <c r="AU7">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY7" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="8" spans="1:51">
-      <c r="A8" t="s">
-        <v>57</v>
       </c>
       <c r="B8" s="2">
         <v>46254</v>
@@ -1732,153 +2362,225 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
         <v>46253</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.8346552579069189</v>
       </c>
       <c r="L8">
-        <v>2.129642440989339</v>
+        <v>3.344028327709457</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="O8" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q8">
+        <v>0.9586638144767297</v>
+      </c>
+      <c r="R8" t="s">
+        <v>101</v>
+      </c>
+      <c r="S8" t="s">
+        <v>105</v>
+      </c>
+      <c r="T8">
+        <v>-0.9954595725036556</v>
+      </c>
+      <c r="U8">
+        <v>0.9730946571918411</v>
+      </c>
+      <c r="V8" t="s">
+        <v>94</v>
+      </c>
+      <c r="W8" t="s">
+        <v>95</v>
+      </c>
+      <c r="X8">
+        <v>0.9997582435166329</v>
+      </c>
+      <c r="Y8">
         <v>1</v>
       </c>
-      <c r="R8">
-        <v>1.168215</v>
-      </c>
-      <c r="S8">
-        <v>1.1737119429846</v>
-      </c>
-      <c r="T8">
-        <v>1.138465874244325</v>
-      </c>
-      <c r="U8">
-        <v>1.168215</v>
-      </c>
-      <c r="V8">
-        <v>1.19712</v>
-      </c>
-      <c r="W8">
-        <v>1.1737119429846</v>
-      </c>
-      <c r="X8">
-        <v>1.154915</v>
-      </c>
-      <c r="Y8">
-        <v>0.004705420649966084</v>
-      </c>
       <c r="Z8">
-        <v>0.4133039838045199</v>
+        <v>-172.3768816259754</v>
       </c>
       <c r="AA8">
-        <v>0.004705420649966084</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB8">
-        <v>0.3340649015651971</v>
+        <v>-0.9911620952036588</v>
       </c>
       <c r="AC8">
-        <v>0.1319416110858937</v>
-      </c>
-      <c r="AD8">
-        <v>0.5339934873489092</v>
+        <v>-0.1326563267676789</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>94</v>
       </c>
       <c r="AE8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH8">
+        <v>-0.9909224753410756</v>
+      </c>
+      <c r="AI8">
+        <v>0.9912305746941298</v>
+      </c>
+      <c r="AJ8">
+        <v>-2.479793160044495</v>
+      </c>
+      <c r="AK8">
+        <v>-0.3004458313453518</v>
+      </c>
+      <c r="AL8">
+        <v>-4.410775866295087</v>
+      </c>
+      <c r="AM8">
+        <v>2.520525211740795</v>
+      </c>
+      <c r="AN8">
+        <v>4.188109640161673</v>
+      </c>
+      <c r="AO8">
+        <v>0.04022292731859602</v>
+      </c>
+      <c r="AP8">
+        <v>6.7262</v>
+      </c>
+      <c r="AQ8">
+        <v>6.714035850780595</v>
+      </c>
+      <c r="AR8">
+        <v>6.747721135191535</v>
+      </c>
+      <c r="AS8">
+        <v>6.7262</v>
+      </c>
+      <c r="AT8">
+        <v>6.680200000000001</v>
+      </c>
+      <c r="AU8">
+        <v>6.714035850780595</v>
+      </c>
+      <c r="AV8">
+        <v>6.754125000000001</v>
+      </c>
+      <c r="AW8">
+        <v>-0.001808472721507704</v>
+      </c>
+      <c r="AX8">
+        <v>0.4356006882508481</v>
+      </c>
+      <c r="AY8">
+        <v>0.001808472721507704</v>
+      </c>
+      <c r="AZ8">
+        <v>0.3648613239500608</v>
+      </c>
+      <c r="BA8">
+        <v>0.2</v>
+      </c>
+      <c r="BB8">
+        <v>0.4351386760499392</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
+        <v>100000</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>479.3319072383648</v>
+      </c>
+      <c r="BG8">
+        <v>0.004151675537450629</v>
+      </c>
+      <c r="BH8">
+        <v>120433.3034914933</v>
+      </c>
+      <c r="BI8">
+        <v>115455.0501151886</v>
+      </c>
+      <c r="BJ8">
+        <v>17164.97429680779</v>
+      </c>
+      <c r="BK8">
+        <v>1154.550501151886</v>
+      </c>
+      <c r="BL8">
+        <v>0.01154550501151886</v>
+      </c>
+      <c r="BM8">
+        <v>479.3319072383649</v>
+      </c>
+      <c r="BN8">
+        <v>0.004793319072383649</v>
+      </c>
+      <c r="BO8">
+        <v>0.08922169778185285</v>
+      </c>
+      <c r="BP8">
+        <v>0.009875435536450216</v>
+      </c>
+      <c r="BQ8">
+        <v>0.01206133065912319</v>
+      </c>
+      <c r="BR8">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW8" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:75">
+      <c r="A9" t="s">
         <v>82</v>
-      </c>
-      <c r="AF8">
-        <v>100000</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>500</v>
-      </c>
-      <c r="AI8">
-        <v>0.01138489062372939</v>
-      </c>
-      <c r="AJ8">
-        <v>43917.85714285703</v>
-      </c>
-      <c r="AK8">
-        <v>43917.85714285703</v>
-      </c>
-      <c r="AL8">
-        <v>37593.98496240592</v>
-      </c>
-      <c r="AM8">
-        <v>439.1785714285703</v>
-      </c>
-      <c r="AN8">
-        <v>0.004391785714285703</v>
-      </c>
-      <c r="AO8">
-        <v>500</v>
-      </c>
-      <c r="AP8">
-        <v>0.005</v>
-      </c>
-      <c r="AQ8">
-        <v>0.01792201523889069</v>
-      </c>
-      <c r="AR8">
-        <v>0.007157456204189467</v>
-      </c>
-      <c r="AS8">
-        <v>0.005649702838520291</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY8" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="9" spans="1:51">
-      <c r="A9" t="s">
-        <v>58</v>
       </c>
       <c r="B9" s="2">
         <v>46254</v>
@@ -1887,153 +2589,225 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46253</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.518479144418527</v>
+        <v>1.224522360957086</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q9">
+        <v>0.75</v>
+      </c>
+      <c r="R9" t="s">
+        <v>102</v>
+      </c>
+      <c r="S9" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9">
+        <v>-0.9712772551812577</v>
+      </c>
+      <c r="U9">
+        <v>0.8358987908355353</v>
+      </c>
+      <c r="V9" t="s">
+        <v>94</v>
+      </c>
+      <c r="W9" t="s">
+        <v>95</v>
+      </c>
+      <c r="X9">
+        <v>0.9952961040158775</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>156.2941560896775</v>
+      </c>
+      <c r="AA9">
+        <v>-2.000000000000003</v>
+      </c>
+      <c r="AB9">
+        <v>-0.9156215917218425</v>
+      </c>
+      <c r="AC9">
+        <v>0.4020411680074063</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH9">
+        <v>-0.4556573014967832</v>
+      </c>
+      <c r="AI9">
+        <v>0.7664129892859401</v>
+      </c>
+      <c r="AJ9">
+        <v>-1.068051724138155</v>
+      </c>
+      <c r="AK9">
+        <v>0.4623541320830815</v>
+      </c>
+      <c r="AL9">
+        <v>-0.893938406614134</v>
+      </c>
+      <c r="AM9">
+        <v>2.801726646986756</v>
+      </c>
+      <c r="AN9">
+        <v>0.7061852967172343</v>
+      </c>
+      <c r="AO9">
+        <v>0.0441808309077974</v>
+      </c>
+      <c r="AP9">
+        <v>158.7225</v>
+      </c>
+      <c r="AQ9">
+        <v>158.3963731009328</v>
+      </c>
+      <c r="AR9">
+        <v>161.5372384049711</v>
+      </c>
+      <c r="AS9">
+        <v>158.7225</v>
+      </c>
+      <c r="AT9">
+        <v>153.813</v>
+      </c>
+      <c r="AU9">
+        <v>158.3963731009328</v>
+      </c>
+      <c r="AV9">
+        <v>159.886</v>
+      </c>
+      <c r="AW9">
+        <v>-0.002054698603331092</v>
+      </c>
+      <c r="AX9">
+        <v>0.2802981513254968</v>
+      </c>
+      <c r="AY9">
+        <v>0.002054698603331092</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4662560775719941</v>
+      </c>
+      <c r="BA9">
+        <v>0.2</v>
+      </c>
+      <c r="BB9">
+        <v>0.333743922428006</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
+        <v>100000</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>375</v>
+      </c>
+      <c r="BG9">
+        <v>0.007330403691978222</v>
+      </c>
+      <c r="BH9">
+        <v>68209.06746884322</v>
+      </c>
+      <c r="BI9">
+        <v>51156.80060163241</v>
+      </c>
+      <c r="BJ9">
+        <v>322.3033949290896</v>
+      </c>
+      <c r="BK9">
+        <v>511.5680060163241</v>
+      </c>
+      <c r="BL9">
+        <v>0.005115680060163241</v>
+      </c>
+      <c r="BM9">
+        <v>375</v>
+      </c>
+      <c r="BN9">
+        <v>0.00375</v>
+      </c>
+      <c r="BO9">
+        <v>2.966035496536826</v>
+      </c>
+      <c r="BP9">
+        <v>0.6759679685511583</v>
+      </c>
+      <c r="BQ9">
+        <v>2.202381130375768</v>
+      </c>
+      <c r="BR9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>1.363285</v>
-      </c>
-      <c r="S9">
-        <v>1.369292934845553</v>
-      </c>
-      <c r="T9">
-        <v>1.321267568602516</v>
-      </c>
-      <c r="U9">
-        <v>1.363285</v>
-      </c>
-      <c r="V9">
-        <v>1.392</v>
-      </c>
-      <c r="W9">
-        <v>1.369292934845553</v>
-      </c>
-      <c r="X9">
-        <v>1.35136</v>
-      </c>
-      <c r="Y9">
-        <v>0.004406954411992078</v>
-      </c>
-      <c r="Z9">
-        <v>0.5038100499415188</v>
-      </c>
-      <c r="AA9">
-        <v>0.004406954411992078</v>
-      </c>
-      <c r="AB9">
-        <v>0.2839938729703027</v>
-      </c>
-      <c r="AC9">
-        <v>0.09122368160437243</v>
-      </c>
-      <c r="AD9">
-        <v>0.6247824454253249</v>
-      </c>
-      <c r="AE9" t="s">
+      <c r="BS9">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW9" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:75">
+      <c r="A10" t="s">
         <v>83</v>
-      </c>
-      <c r="AF9">
-        <v>100000</v>
-      </c>
-      <c r="AG9">
-        <v>100</v>
-      </c>
-      <c r="AH9">
-        <v>500</v>
-      </c>
-      <c r="AI9">
-        <v>0.008747253875748665</v>
-      </c>
-      <c r="AJ9">
-        <v>57160.79664570222</v>
-      </c>
-      <c r="AK9">
-        <v>57160.79664570222</v>
-      </c>
-      <c r="AL9">
-        <v>41928.72117400412</v>
-      </c>
-      <c r="AM9">
-        <v>571.6079664570221</v>
-      </c>
-      <c r="AN9">
-        <v>0.005716079664570222</v>
-      </c>
-      <c r="AO9">
-        <v>500</v>
-      </c>
-      <c r="AP9">
-        <v>0.005</v>
-      </c>
-      <c r="AQ9">
-        <v>0.02115109639962907</v>
-      </c>
-      <c r="AR9">
-        <v>0.007205561859685078</v>
-      </c>
-      <c r="AS9">
-        <v>0.005467518014274479</v>
-      </c>
-      <c r="AT9">
-        <v>1</v>
-      </c>
-      <c r="AU9">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY9" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="10" spans="1:51">
-      <c r="A10" t="s">
-        <v>59</v>
       </c>
       <c r="B10" s="2">
         <v>46254</v>
@@ -2042,153 +2816,225 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J10" s="2">
         <v>46253</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.01636935260508167</v>
       </c>
       <c r="L10">
-        <v>0.5781780700216143</v>
+        <v>1.426871435149012</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O10" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
-      </c>
-      <c r="R10">
-        <v>9.15645</v>
-      </c>
-      <c r="S10">
-        <v>9.187163541207818</v>
+        <v>0.9877229855461888</v>
+      </c>
+      <c r="R10" t="s">
+        <v>100</v>
+      </c>
+      <c r="S10" t="s">
+        <v>104</v>
       </c>
       <c r="T10">
-        <v>9.036043410356791</v>
+        <v>0.9252029799917924</v>
       </c>
       <c r="U10">
-        <v>9.15645</v>
-      </c>
-      <c r="V10">
-        <v>9.293809999999999</v>
-      </c>
-      <c r="W10">
-        <v>9.187163541207818</v>
+        <v>0.8187948620166103</v>
+      </c>
+      <c r="V10" t="s">
+        <v>93</v>
+      </c>
+      <c r="W10" t="s">
+        <v>95</v>
       </c>
       <c r="X10">
-        <v>9.07366</v>
+        <v>0.999992472518166</v>
       </c>
       <c r="Y10">
-        <v>0.003354306659001966</v>
+        <v>0.2038960067893222</v>
       </c>
       <c r="Z10">
-        <v>0.3709812925210593</v>
+        <v>34.9406006058263</v>
       </c>
       <c r="AA10">
-        <v>0.003354306659001966</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB10">
-        <v>0.3421910033802746</v>
+        <v>0.8197462392755892</v>
       </c>
       <c r="AC10">
-        <v>0.1342534278120276</v>
-      </c>
-      <c r="AD10">
-        <v>0.5235555688076977</v>
+        <v>0.5727269010562788</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>93</v>
       </c>
       <c r="AE10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH10">
+        <v>0.49344089762687</v>
+      </c>
+      <c r="AI10">
+        <v>0.7803073031970221</v>
+      </c>
+      <c r="AJ10">
+        <v>1.145284586633104</v>
+      </c>
+      <c r="AK10">
+        <v>0.789098290569426</v>
+      </c>
+      <c r="AL10">
+        <v>1.484843873573096</v>
+      </c>
+      <c r="AM10">
+        <v>-2.174224443684099</v>
+      </c>
+      <c r="AN10">
+        <v>1.295532618310246</v>
+      </c>
+      <c r="AO10">
+        <v>0.04262090216584771</v>
+      </c>
+      <c r="AP10">
+        <v>0.710915</v>
+      </c>
+      <c r="AQ10">
+        <v>0.7086330635653748</v>
+      </c>
+      <c r="AR10">
+        <v>0.6958042435032287</v>
+      </c>
+      <c r="AS10">
+        <v>0.710915</v>
+      </c>
+      <c r="AT10">
+        <v>0.7216449999999999</v>
+      </c>
+      <c r="AU10">
+        <v>0.7086330635653748</v>
+      </c>
+      <c r="AV10">
+        <v>0.718615</v>
+      </c>
+      <c r="AW10">
+        <v>-0.003209858329934174</v>
+      </c>
+      <c r="AX10">
+        <v>0.2963553811201472</v>
+      </c>
+      <c r="AY10">
+        <v>0.003209858329934174</v>
+      </c>
+      <c r="AZ10">
+        <v>0.4204960654299259</v>
+      </c>
+      <c r="BA10">
+        <v>0.2</v>
+      </c>
+      <c r="BB10">
+        <v>0.3795039345700741</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>126</v>
+      </c>
+      <c r="BD10">
+        <v>100000</v>
+      </c>
+      <c r="BE10">
+        <v>100</v>
+      </c>
+      <c r="BF10">
+        <v>493.8614927730944</v>
+      </c>
+      <c r="BG10">
+        <v>0.0108311120176112</v>
+      </c>
+      <c r="BH10">
+        <v>46163.31168831128</v>
+      </c>
+      <c r="BI10">
+        <v>45596.56404347809</v>
+      </c>
+      <c r="BJ10">
+        <v>64137.85620429741</v>
+      </c>
+      <c r="BK10">
+        <v>455.9656404347809</v>
+      </c>
+      <c r="BL10">
+        <v>0.004559656404347809</v>
+      </c>
+      <c r="BM10">
+        <v>493.8614927730944</v>
+      </c>
+      <c r="BN10">
+        <v>0.004938614927730944</v>
+      </c>
+      <c r="BO10">
+        <v>0.008955484327776788</v>
+      </c>
+      <c r="BP10">
+        <v>0.002030753790924494</v>
+      </c>
+      <c r="BQ10">
+        <v>0.003662605163050011</v>
+      </c>
+      <c r="BR10">
+        <v>1</v>
+      </c>
+      <c r="BS10">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW10" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="11" spans="1:75">
+      <c r="A11" t="s">
         <v>84</v>
-      </c>
-      <c r="AF10">
-        <v>100000</v>
-      </c>
-      <c r="AG10">
-        <v>100</v>
-      </c>
-      <c r="AH10">
-        <v>375</v>
-      </c>
-      <c r="AI10">
-        <v>0.009041713764614032</v>
-      </c>
-      <c r="AJ10">
-        <v>55299.2511172846</v>
-      </c>
-      <c r="AK10">
-        <v>41474.43833796345</v>
-      </c>
-      <c r="AL10">
-        <v>4529.532552240601</v>
-      </c>
-      <c r="AM10">
-        <v>414.7443833796345</v>
-      </c>
-      <c r="AN10">
-        <v>0.004147443833796345</v>
-      </c>
-      <c r="AO10">
-        <v>375.0000000000001</v>
-      </c>
-      <c r="AP10">
-        <v>0.003750000000000001</v>
-      </c>
-      <c r="AQ10">
-        <v>0.1083867444862362</v>
-      </c>
-      <c r="AR10">
-        <v>0.03062800077863456</v>
-      </c>
-      <c r="AS10">
-        <v>0.03301192115657233</v>
-      </c>
-      <c r="AT10">
-        <v>1</v>
-      </c>
-      <c r="AU10">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY10" s="2">
-        <v>46282</v>
-      </c>
-    </row>
-    <row r="11" spans="1:51">
-      <c r="A11" t="s">
-        <v>60</v>
       </c>
       <c r="B11" s="2">
         <v>46254</v>
@@ -2197,22 +3043,22 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
         <v>46253</v>
@@ -2221,123 +3067,195 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.02812122986921546</v>
+        <v>0.03701447009399642</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>54</v>
       </c>
       <c r="O11" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" t="s">
+        <v>107</v>
+      </c>
+      <c r="T11">
+        <v>0.6853787671500985</v>
+      </c>
+      <c r="U11">
+        <v>0.70811771335306</v>
+      </c>
+      <c r="V11" t="s">
+        <v>93</v>
+      </c>
+      <c r="W11" t="s">
+        <v>95</v>
+      </c>
+      <c r="X11">
+        <v>0.9987890725420626</v>
+      </c>
+      <c r="Y11">
+        <v>0.1539430924141814</v>
+      </c>
+      <c r="Z11">
+        <v>-77.70524749282117</v>
+      </c>
+      <c r="AA11">
+        <v>-18</v>
+      </c>
+      <c r="AB11">
+        <v>0.2129409016590923</v>
+      </c>
+      <c r="AC11">
+        <v>-0.9770650809442597</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>113</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH11">
+        <v>0.1227120657147661</v>
+      </c>
+      <c r="AI11">
+        <v>0.576325034692154</v>
+      </c>
+      <c r="AJ11">
+        <v>0.257825198952521</v>
+      </c>
+      <c r="AK11">
+        <v>-1.092074321074909</v>
+      </c>
+      <c r="AL11">
+        <v>0.04268234739644627</v>
+      </c>
+      <c r="AM11">
+        <v>-2.283244132581187</v>
+      </c>
+      <c r="AN11">
+        <v>0.4092268280514446</v>
+      </c>
+      <c r="AO11">
+        <v>0.1194801978542123</v>
+      </c>
+      <c r="AP11">
         <v>0.7984</v>
       </c>
-      <c r="S11">
-        <v>0.7897649806250115</v>
-      </c>
-      <c r="T11">
-        <v>0.7949019740383687</v>
-      </c>
-      <c r="U11">
+      <c r="AQ11">
+        <v>0.7896262800223005</v>
+      </c>
+      <c r="AR11">
+        <v>0.7932723671265853</v>
+      </c>
+      <c r="AS11">
         <v>0.7984</v>
       </c>
-      <c r="V11">
+      <c r="AT11">
         <v>0.7806150000000001</v>
       </c>
-      <c r="W11">
-        <v>0.7897649806250115</v>
-      </c>
-      <c r="X11">
+      <c r="AU11">
+        <v>0.7896262800223005</v>
+      </c>
+      <c r="AV11">
         <v>0.808435</v>
       </c>
-      <c r="Y11">
-        <v>-0.01081540502879315</v>
-      </c>
-      <c r="Z11">
-        <v>0.8604902217228162</v>
-      </c>
-      <c r="AA11">
-        <v>0.01081540502879315</v>
-      </c>
-      <c r="AB11">
-        <v>0.3914741225112592</v>
-      </c>
-      <c r="AC11">
+      <c r="AW11">
+        <v>-0.01098912822858153</v>
+      </c>
+      <c r="AX11">
+        <v>0.8743119060986049</v>
+      </c>
+      <c r="AY11">
+        <v>0.01098912822858153</v>
+      </c>
+      <c r="AZ11">
+        <v>0.4309174228536322</v>
+      </c>
+      <c r="BA11">
         <v>0.2</v>
       </c>
-      <c r="AD11">
-        <v>0.4085258774887408</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>85</v>
-      </c>
-      <c r="AF11">
+      <c r="BB11">
+        <v>0.3690825771463678</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>127</v>
+      </c>
+      <c r="BD11">
         <v>100000</v>
       </c>
-      <c r="AG11">
+      <c r="BE11">
         <v>100</v>
       </c>
-      <c r="AH11">
+      <c r="BF11">
         <v>500</v>
       </c>
-      <c r="AI11">
+      <c r="BG11">
         <v>0.01256888777555109</v>
       </c>
-      <c r="AJ11">
+      <c r="BH11">
         <v>39780.76731439965</v>
       </c>
-      <c r="AK11">
+      <c r="BI11">
         <v>39780.76731439965</v>
       </c>
-      <c r="AL11">
+      <c r="BJ11">
         <v>49825.61036372702</v>
       </c>
-      <c r="AM11">
+      <c r="BK11">
         <v>397.8076731439965</v>
       </c>
-      <c r="AN11">
+      <c r="BL11">
         <v>0.003978076731439965</v>
       </c>
-      <c r="AO11">
+      <c r="BM11">
         <v>500.0000000000001</v>
       </c>
-      <c r="AP11">
+      <c r="BN11">
         <v>0.005000000000000001</v>
       </c>
-      <c r="AQ11">
-        <v>0.02034943100360603</v>
-      </c>
-      <c r="AR11">
-        <v>0.008920118098905066</v>
-      </c>
-      <c r="AS11">
-        <v>0.01140446538860507</v>
-      </c>
-      <c r="AT11">
+      <c r="BO11">
+        <v>0.0192237000735142</v>
+      </c>
+      <c r="BP11">
+        <v>0.008522870882223466</v>
+      </c>
+      <c r="BQ11">
+        <v>0.01127377687915577</v>
+      </c>
+      <c r="BR11">
         <v>1</v>
       </c>
-      <c r="AU11">
-        <v>0.03808398235317244</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>87</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>89</v>
-      </c>
-      <c r="AY11" s="2">
+      <c r="BS11">
+        <v>0.04809530464707595</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW11" s="2">
         <v>46282</v>
       </c>
     </row>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="129">
   <si>
     <t>Pair</t>
   </si>
@@ -241,33 +241,33 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>XAUUSD</t>
+  </si>
+  <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>XAUUSD</t>
-  </si>
-  <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>AUDCNH</t>
   </si>
   <si>
+    <t>USDCNH</t>
+  </si>
+  <si>
     <t>EURCNH</t>
   </si>
   <si>
-    <t>USDCNH</t>
-  </si>
-  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>USDCHF</t>
   </si>
   <si>
@@ -277,18 +277,15 @@
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>FLAT</t>
-  </si>
-  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -307,9 +304,6 @@
     <t>CONFLICT</t>
   </si>
   <si>
-    <t>NO_SIGNAL</t>
-  </si>
-  <si>
     <t>CONFIRM</t>
   </si>
   <si>
@@ -319,25 +313,25 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_STEADY</t>
+    <t>DOWN_ACCELERATING</t>
   </si>
   <si>
     <t>DOWN_DECELERATING</t>
   </si>
   <si>
-    <t>UP_DECELERATING</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头稳态</t>
+    <t>空头加速</t>
   </si>
   <si>
     <t>空头减速</t>
   </si>
   <si>
-    <t>多头减速</t>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
   </si>
   <si>
     <t>上涨</t>
@@ -346,67 +340,64 @@
     <t>下跌</t>
   </si>
   <si>
+    <t>转换</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_SLOPE</t>
+    <t>DOWN_STEEPENING</t>
   </si>
   <si>
     <t>DOWN_VALLEY_FLATTENING</t>
   </si>
   <si>
-    <t>UP_CREST_FLATTENING</t>
+    <t>TRANSITION_ZONE</t>
   </si>
   <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降坡延续</t>
+    <t>下降陡坡形成</t>
   </si>
   <si>
     <t>下降谷底收敛</t>
   </si>
   <si>
-    <t>上升坡顶钝化</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.1011,naive=0.02555,drift4=0.03357; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=276.8,naive=98.21,drift4=133.7; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.01929,naive=0.006332,drift4=0.006052; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02232,naive=0.006625,drift4=0.006242; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.03925,naive=0.01498,drift4=0.01512; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=naive; scores=model=0.1566,naive=0.03521,drift4=0.03531; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.08922,naive=0.009875,drift4=0.01206; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.966,naive=0.676,drift4=2.202; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.008955,naive=0.002031,drift4=0.003663; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01922,naive=0.008523,drift4=0.01127; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>SKIP</t>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=185.7,naive=145.2,drift4=135.5; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.02071,naive=0.007171,drift4=0.007376; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02451,naive=0.007486,drift4=0.007284; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0109,naive=0.004963,drift4=0.004; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1029,naive=0.0272,drift4=0.038; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.02792,naive=0.005542,drift4=0.01716; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.08478,naive=0.01319,drift4=0.0129; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1458,naive=0.02932,drift4=0.03361; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=2.796,naive=0.5569,drift4=1.816; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0189,naive=0.007966,drift4=0.0108; naive_cap_applied</t>
   </si>
   <si>
     <t>OPEN</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -1006,7 +997,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1027,136 +1018,145 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0.5781780700216143</v>
+        <v>1.842550331079064</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T2">
-        <v>0.8843281615246334</v>
+        <v>0.8739244504506468</v>
       </c>
       <c r="U2">
-        <v>0.7979403523348219</v>
+        <v>0.7932067133357139</v>
       </c>
       <c r="V2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X2">
-        <v>0.9999707185949473</v>
+        <v>0.9997628425316913</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>0.5359779605829512</v>
       </c>
       <c r="Z2">
-        <v>48.6054717682086</v>
+        <v>41.2324549124319</v>
       </c>
       <c r="AA2">
-        <v>6.999999999999997</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB2">
-        <v>0.6612402264225222</v>
+        <v>0.7520416768015612</v>
       </c>
       <c r="AC2">
-        <v>0.7501742217383183</v>
+        <v>0.6591155561458827</v>
       </c>
       <c r="AD2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH2">
-        <v>0.3306104321898076</v>
+        <v>0.5774227479024108</v>
       </c>
       <c r="AI2">
-        <v>0.6903604912104218</v>
+        <v>0.824966669233184</v>
       </c>
       <c r="AJ2">
-        <v>0.4542375573949776</v>
+        <v>1.441282703672705</v>
       </c>
       <c r="AK2">
-        <v>0.5013875605815916</v>
+        <v>1.279701112861722</v>
       </c>
       <c r="AL2">
-        <v>0.6464621698535724</v>
+        <v>2.082580962013676</v>
       </c>
       <c r="AM2">
-        <v>-0.836181056609497</v>
+        <v>-2.390018558409804</v>
       </c>
       <c r="AN2">
-        <v>0.5620402351596001</v>
+        <v>1.855837817997649</v>
       </c>
       <c r="AO2">
-        <v>0.05334218816377579</v>
+        <v>0.0517228053997773</v>
       </c>
       <c r="AP2">
-        <v>9.15645</v>
+        <v>4595.98</v>
       </c>
       <c r="AQ2">
-        <v>9.163802224345721</v>
+        <v>4759.194340854186</v>
       </c>
       <c r="AR2">
-        <v>9.036997556714635</v>
+        <v>4516.303669825544</v>
       </c>
       <c r="AS2">
-        <v>9.15645</v>
+        <v>4595.98</v>
       </c>
       <c r="AT2">
-        <v>9.293809999999999</v>
+        <v>5146.07</v>
+      </c>
+      <c r="AU2">
+        <v>4759.194340854186</v>
+      </c>
+      <c r="AV2">
+        <v>4446.965</v>
       </c>
       <c r="AW2">
-        <v>0.0008029557684169718</v>
+        <v>0.03551241320766976</v>
+      </c>
+      <c r="AX2">
+        <v>1.095287996874049</v>
       </c>
       <c r="AY2">
-        <v>0.0008029557684169718</v>
+        <v>0.03551241320766976</v>
       </c>
       <c r="AZ2">
-        <v>0.3992632691101521</v>
+        <v>0.4396196587218628</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.400736730889848</v>
+        <v>0.3603803412781372</v>
       </c>
       <c r="BC2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1165,55 +1165,58 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>375</v>
+      </c>
+      <c r="BG2">
+        <v>0.03242290001261965</v>
       </c>
       <c r="BH2">
-        <v>0</v>
+        <v>15421.19920813344</v>
       </c>
       <c r="BI2">
-        <v>0</v>
+        <v>11565.89940610008</v>
       </c>
       <c r="BJ2">
-        <v>0</v>
+        <v>2.51652518202866</v>
       </c>
       <c r="BK2">
-        <v>0</v>
+        <v>115.6589940610008</v>
       </c>
       <c r="BL2">
-        <v>0</v>
+        <v>0.001156589940610008</v>
       </c>
       <c r="BM2">
-        <v>0</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN2">
-        <v>0</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO2">
-        <v>0.1011178684330099</v>
+        <v>185.6517557047789</v>
       </c>
       <c r="BP2">
-        <v>0.02555118686527646</v>
+        <v>145.180152494632</v>
       </c>
       <c r="BQ2">
-        <v>0.03356821077507182</v>
+        <v>135.4858129633054</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="BW2" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1221,7 +1224,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1236,151 +1239,151 @@
         <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J3" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1.425699501519865</v>
+        <v>2.799788928978186</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P3" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
         <v>98</v>
       </c>
-      <c r="Q3">
-        <v>0.75</v>
-      </c>
-      <c r="R3" t="s">
-        <v>100</v>
-      </c>
       <c r="S3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T3">
-        <v>0.9387787232160607</v>
+        <v>0.9038103801512347</v>
       </c>
       <c r="U3">
-        <v>0.8220264675511796</v>
+        <v>0.9567110974963017</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X3">
-        <v>0.9983041684158089</v>
+        <v>0.9999857057129841</v>
       </c>
       <c r="Y3">
-        <v>0.06825432873385694</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>33.50748502364006</v>
+        <v>36.13601322557214</v>
       </c>
       <c r="AA3">
-        <v>-28</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AB3">
-        <v>0.8338137108382806</v>
+        <v>0.807619385320781</v>
       </c>
       <c r="AC3">
-        <v>0.5520459180340854</v>
+        <v>0.5897041024565488</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH3">
-        <v>0.4446072930965568</v>
+        <v>0.8076078409774876</v>
       </c>
       <c r="AI3">
-        <v>0.7564924193643786</v>
+        <v>0.9348738201194033</v>
       </c>
       <c r="AJ3">
-        <v>1.173589067040108</v>
+        <v>2.113288595471767</v>
       </c>
       <c r="AK3">
-        <v>0.90980182733142</v>
+        <v>1.508310092799069</v>
       </c>
       <c r="AL3">
-        <v>1.36601229944368</v>
+        <v>3.519860679519747</v>
       </c>
       <c r="AM3">
-        <v>-2.966708736995491</v>
+        <v>-2.75011321001353</v>
       </c>
       <c r="AN3">
-        <v>1.09181223998737</v>
+        <v>3.240920255412093</v>
       </c>
       <c r="AO3">
-        <v>0.04472679052940127</v>
+        <v>0.04937994984250294</v>
       </c>
       <c r="AP3">
-        <v>4459.799999999999</v>
+        <v>1.36555</v>
       </c>
       <c r="AQ3">
-        <v>4571.029223550129</v>
+        <v>1.372678466015573</v>
       </c>
       <c r="AR3">
-        <v>4349.981174304025</v>
+        <v>1.351760380768147</v>
       </c>
       <c r="AS3">
-        <v>4459.799999999999</v>
+        <v>1.36555</v>
       </c>
       <c r="AT3">
-        <v>4873.709999999999</v>
+        <v>1.39653</v>
       </c>
       <c r="AU3">
-        <v>4571.029223550129</v>
+        <v>1.372678466015573</v>
       </c>
       <c r="AV3">
-        <v>4320.98</v>
+        <v>1.35361</v>
       </c>
       <c r="AW3">
-        <v>0.02494040619537423</v>
+        <v>0.005220216041574895</v>
       </c>
       <c r="AX3">
-        <v>0.8012478284838681</v>
+        <v>0.5970239544030649</v>
       </c>
       <c r="AY3">
-        <v>0.02494040619537423</v>
+        <v>0.005220216041574895</v>
       </c>
       <c r="AZ3">
-        <v>0.419871440449453</v>
+        <v>0.3943641756922918</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.380128559550547</v>
+        <v>0.4056358243077082</v>
       </c>
       <c r="BC3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1389,58 +1392,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG3">
-        <v>0.03112695636575615</v>
+        <v>0.008743729632748713</v>
       </c>
       <c r="BH3">
-        <v>16063.24737069595</v>
+        <v>57183.83584589612</v>
       </c>
       <c r="BI3">
-        <v>12047.43552802196</v>
+        <v>57183.83584589612</v>
       </c>
       <c r="BJ3">
-        <v>2.701339864572843</v>
+        <v>41876.04690117251</v>
       </c>
       <c r="BK3">
-        <v>120.4743552802196</v>
+        <v>571.8383584589612</v>
       </c>
       <c r="BL3">
-        <v>0.001204743552802196</v>
+        <v>0.005718383584589612</v>
       </c>
       <c r="BM3">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN3">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO3">
-        <v>276.8197345618283</v>
+        <v>0.02070822257070009</v>
       </c>
       <c r="BP3">
-        <v>98.20575709988094</v>
+        <v>0.007171322759006341</v>
       </c>
       <c r="BQ3">
-        <v>133.6514356744719</v>
+        <v>0.007375623821229548</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW3" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1448,7 +1451,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1463,151 +1466,151 @@
         <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J4" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.476432103856031</v>
+        <v>2.559319104838145</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T4">
-        <v>0.911331543491438</v>
+        <v>0.8318112568274303</v>
       </c>
       <c r="U4">
-        <v>0.9600891646449576</v>
+        <v>0.9243073098068914</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X4">
-        <v>0.9999598802952427</v>
+        <v>0.9999689769381911</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>34.64808410787485</v>
+        <v>48.42366466301528</v>
       </c>
       <c r="AA4">
-        <v>6.999999999999997</v>
+        <v>11</v>
       </c>
       <c r="AB4">
-        <v>0.8226595294878541</v>
+        <v>0.6636172957632107</v>
       </c>
       <c r="AC4">
-        <v>0.5685343424480375</v>
+        <v>0.7480722456848158</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH4">
-        <v>0.8226265246304153</v>
+        <v>0.6635967083228268</v>
       </c>
       <c r="AI4">
-        <v>0.9397469757820209</v>
+        <v>0.8907372185570044</v>
       </c>
       <c r="AJ4">
-        <v>1.886753805740311</v>
+        <v>1.950892777410652</v>
       </c>
       <c r="AK4">
-        <v>1.268310300213958</v>
+        <v>2.118073102677476</v>
       </c>
       <c r="AL4">
-        <v>3.034765938404792</v>
+        <v>3.108834761886927</v>
       </c>
       <c r="AM4">
-        <v>-2.617596247757652</v>
+        <v>-2.378758064309582</v>
       </c>
       <c r="AN4">
-        <v>2.782946818459877</v>
+        <v>2.868011158736149</v>
       </c>
       <c r="AO4">
-        <v>0.04691227445113542</v>
+        <v>0.05558074733550537</v>
       </c>
       <c r="AP4">
-        <v>1.363285</v>
+        <v>1.17016</v>
       </c>
       <c r="AQ4">
-        <v>1.369985825518027</v>
+        <v>1.176214495402759</v>
       </c>
       <c r="AR4">
-        <v>1.349773617780689</v>
+        <v>1.152408785740714</v>
       </c>
       <c r="AS4">
-        <v>1.363285</v>
+        <v>1.17016</v>
       </c>
       <c r="AT4">
-        <v>1.392</v>
+        <v>1.20101</v>
       </c>
       <c r="AU4">
-        <v>1.369985825518027</v>
+        <v>1.176214495402759</v>
       </c>
       <c r="AV4">
-        <v>1.35136</v>
+        <v>1.15637375</v>
       </c>
       <c r="AW4">
-        <v>0.004915205197758909</v>
+        <v>0.005174074829731866</v>
       </c>
       <c r="AX4">
-        <v>0.5619140895619911</v>
+        <v>0.4391691288609315</v>
       </c>
       <c r="AY4">
-        <v>0.004915205197758909</v>
+        <v>0.005174074829731866</v>
       </c>
       <c r="AZ4">
-        <v>0.3853319566299963</v>
+        <v>0.3832312603935049</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4146680433700037</v>
+        <v>0.4167687396064951</v>
       </c>
       <c r="BC4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1619,22 +1622,22 @@
         <v>500</v>
       </c>
       <c r="BG4">
-        <v>0.008747253875748665</v>
+        <v>0.01178150851165657</v>
       </c>
       <c r="BH4">
-        <v>57160.79664570222</v>
+        <v>42439.38707045046</v>
       </c>
       <c r="BI4">
-        <v>57160.79664570222</v>
+        <v>42439.38707045046</v>
       </c>
       <c r="BJ4">
-        <v>41928.72117400412</v>
+        <v>36268.02067277164</v>
       </c>
       <c r="BK4">
-        <v>571.6079664570221</v>
+        <v>424.3938707045046</v>
       </c>
       <c r="BL4">
-        <v>0.005716079664570222</v>
+        <v>0.004243938707045046</v>
       </c>
       <c r="BM4">
         <v>500</v>
@@ -1643,31 +1646,31 @@
         <v>0.005</v>
       </c>
       <c r="BO4">
-        <v>0.01929412441718169</v>
+        <v>0.02450828036901452</v>
       </c>
       <c r="BP4">
-        <v>0.006331878104713164</v>
+        <v>0.00748638850717295</v>
       </c>
       <c r="BQ4">
-        <v>0.006052454349751199</v>
+        <v>0.00728373871436286</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW4" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1675,7 +1678,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1687,154 +1690,154 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.4236656675179737</v>
       </c>
       <c r="L5">
-        <v>2.098247299854969</v>
+        <v>1.77162634908774</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q5">
+        <v>0.8559164168794934</v>
+      </c>
+      <c r="R5" t="s">
         <v>98</v>
       </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5" t="s">
-        <v>100</v>
-      </c>
       <c r="S5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T5">
-        <v>0.8372223440523791</v>
+        <v>0.8848405598661534</v>
       </c>
       <c r="U5">
-        <v>0.926727600597396</v>
+        <v>0.8617267344551464</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X5">
-        <v>0.9999101830953019</v>
+        <v>0.9999945295507252</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.728906953090797</v>
       </c>
       <c r="Z5">
-        <v>47.59009277023014</v>
+        <v>39.53535493000027</v>
       </c>
       <c r="AA5">
-        <v>14.00000000000001</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB5">
-        <v>0.6744300666062889</v>
+        <v>0.77123193812414</v>
       </c>
       <c r="AC5">
-        <v>0.7383387334126774</v>
+        <v>0.6365542377655518</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH5">
-        <v>0.674369491385271</v>
+        <v>0.6666904830178377</v>
       </c>
       <c r="AI5">
-        <v>0.8942277757563757</v>
+        <v>0.8695223443438814</v>
       </c>
       <c r="AJ5">
-        <v>1.620148793511938</v>
+        <v>1.354231212924323</v>
       </c>
       <c r="AK5">
-        <v>1.691258887943281</v>
+        <v>1.088437348502598</v>
       </c>
       <c r="AL5">
-        <v>2.448955539854732</v>
+        <v>2.132516225977054</v>
       </c>
       <c r="AM5">
-        <v>-2.030293092778862</v>
+        <v>-1.543205890574448</v>
       </c>
       <c r="AN5">
-        <v>2.26216891955886</v>
+        <v>1.990644408001752</v>
       </c>
       <c r="AO5">
-        <v>0.05379872205911085</v>
+        <v>0.05084475369515897</v>
       </c>
       <c r="AP5">
-        <v>1.168215</v>
+        <v>0.71668</v>
       </c>
       <c r="AQ5">
-        <v>1.172691649512342</v>
+        <v>0.717928094540049</v>
       </c>
       <c r="AR5">
-        <v>1.14794271536709</v>
+        <v>0.7024454720028523</v>
       </c>
       <c r="AS5">
-        <v>1.168215</v>
+        <v>0.71668</v>
       </c>
       <c r="AT5">
-        <v>1.19712</v>
+        <v>0.7331749999999999</v>
       </c>
       <c r="AU5">
-        <v>1.172691649512342</v>
+        <v>0.717928094540049</v>
       </c>
       <c r="AV5">
-        <v>1.154915</v>
+        <v>0.708305</v>
       </c>
       <c r="AW5">
-        <v>0.003832042485622986</v>
+        <v>0.001741494865280235</v>
       </c>
       <c r="AX5">
-        <v>0.3365901888978982</v>
+        <v>0.1490262137371987</v>
       </c>
       <c r="AY5">
-        <v>0.003832042485622986</v>
+        <v>0.001741494865280235</v>
       </c>
       <c r="AZ5">
-        <v>0.3791862569650508</v>
+        <v>0.388808622802798</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.4208137430349492</v>
+        <v>0.411191377197202</v>
       </c>
       <c r="BC5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1843,58 +1846,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>500</v>
+        <v>427.9582084397467</v>
       </c>
       <c r="BG5">
-        <v>0.01138489062372939</v>
+        <v>0.01168582910085393</v>
       </c>
       <c r="BH5">
-        <v>43917.85714285703</v>
+        <v>42786.86567164182</v>
       </c>
       <c r="BI5">
-        <v>43917.85714285703</v>
+        <v>36621.98075517586</v>
       </c>
       <c r="BJ5">
-        <v>37593.98496240592</v>
+        <v>51099.48757489516</v>
       </c>
       <c r="BK5">
-        <v>439.1785714285703</v>
+        <v>366.2198075517587</v>
       </c>
       <c r="BL5">
-        <v>0.004391785714285703</v>
+        <v>0.003662198075517587</v>
       </c>
       <c r="BM5">
-        <v>500</v>
+        <v>427.9582084397467</v>
       </c>
       <c r="BN5">
-        <v>0.005</v>
+        <v>0.004279582084397467</v>
       </c>
       <c r="BO5">
-        <v>0.02231554613837267</v>
+        <v>0.01090118721268276</v>
       </c>
       <c r="BP5">
-        <v>0.006625069795342857</v>
+        <v>0.004963073343992102</v>
       </c>
       <c r="BQ5">
-        <v>0.006241516887333231</v>
+        <v>0.003999580815931342</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW5" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1902,7 +1905,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1914,154 +1917,154 @@
         <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>0.03993506226774555</v>
       </c>
       <c r="L6">
-        <v>0.4840309185698284</v>
+        <v>0.705768003120097</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q6">
+        <v>0.7599837655669364</v>
+      </c>
+      <c r="R6" t="s">
         <v>98</v>
       </c>
-      <c r="Q6">
-        <v>0.75</v>
-      </c>
-      <c r="R6" t="s">
-        <v>100</v>
-      </c>
       <c r="S6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T6">
-        <v>0.8497579668037913</v>
+        <v>0.8135047667508462</v>
       </c>
       <c r="U6">
-        <v>0.7823822726760881</v>
+        <v>0.7720649420737459</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X6">
-        <v>0.9999647504575279</v>
+        <v>0.9999901507828128</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>0.4420779968234593</v>
       </c>
       <c r="Z6">
-        <v>55.94453004495183</v>
+        <v>52.25174269577867</v>
       </c>
       <c r="AA6">
-        <v>7.999999999999998</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>0.5599952602082706</v>
+        <v>0.6121932303117764</v>
       </c>
       <c r="AC6">
-        <v>0.8284958108187822</v>
+        <v>0.7907081944437102</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH6">
-        <v>0.2799877603157809</v>
+        <v>0.441410846024333</v>
       </c>
       <c r="AI6">
-        <v>0.6594540373169837</v>
+        <v>0.7640742648544088</v>
       </c>
       <c r="AJ6">
-        <v>0.3913817078300837</v>
+        <v>0.5492305659924983</v>
       </c>
       <c r="AK6">
-        <v>0.5590562862638696</v>
+        <v>0.6861654558813107</v>
       </c>
       <c r="AL6">
-        <v>0.4842945765041812</v>
+        <v>0.8136425168908916</v>
       </c>
       <c r="AM6">
-        <v>-0.6991426692546785</v>
+        <v>-0.9698468574691853</v>
       </c>
       <c r="AN6">
-        <v>0.4179375416273116</v>
+        <v>0.7139352009881679</v>
       </c>
       <c r="AO6">
-        <v>0.05688135603754795</v>
+        <v>0.05330570918533644</v>
       </c>
       <c r="AP6">
-        <v>4.79463</v>
+        <v>9.16441</v>
       </c>
       <c r="AQ6">
-        <v>4.80105757886611</v>
+        <v>9.173646254099516</v>
       </c>
       <c r="AR6">
-        <v>4.741396593121281</v>
+        <v>9.046500198557935</v>
       </c>
       <c r="AS6">
-        <v>4.79463</v>
+        <v>9.16441</v>
       </c>
       <c r="AT6">
-        <v>4.863359999999999</v>
+        <v>9.30973</v>
       </c>
       <c r="AU6">
-        <v>4.801821944999999</v>
+        <v>9.178156615000001</v>
       </c>
       <c r="AV6">
-        <v>4.7597825</v>
+        <v>9.081620000000001</v>
       </c>
       <c r="AW6">
-        <v>0.001340578702863436</v>
+        <v>0.001007839468063532</v>
       </c>
       <c r="AX6">
-        <v>0.2063833847478303</v>
+        <v>0.1660419736683172</v>
       </c>
       <c r="AY6">
-        <v>0.001340578702863436</v>
+        <v>0.001007839468063532</v>
       </c>
       <c r="AZ6">
-        <v>0.3981228663296886</v>
+        <v>0.4065639426622356</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.4018771336703114</v>
+        <v>0.3934360573377645</v>
       </c>
       <c r="BC6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2070,58 +2073,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>375</v>
+        <v>379.9918827834682</v>
       </c>
       <c r="BG6">
-        <v>0.007268026938470731</v>
+        <v>0.009033860335799046</v>
       </c>
       <c r="BH6">
-        <v>68794.46158261009</v>
+        <v>55347.32455610572</v>
       </c>
       <c r="BI6">
-        <v>51595.84618695757</v>
+        <v>42063.06813020459</v>
       </c>
       <c r="BJ6">
-        <v>10761.1736853433</v>
+        <v>4589.828273746438</v>
       </c>
       <c r="BK6">
-        <v>515.9584618695757</v>
+        <v>420.6306813020459</v>
       </c>
       <c r="BL6">
-        <v>0.005159584618695757</v>
+        <v>0.004206306813020459</v>
       </c>
       <c r="BM6">
-        <v>375</v>
+        <v>379.9918827834682</v>
       </c>
       <c r="BN6">
-        <v>0.00375</v>
+        <v>0.003799918827834682</v>
       </c>
       <c r="BO6">
-        <v>0.03924837962525179</v>
+        <v>0.1028598876385414</v>
       </c>
       <c r="BP6">
-        <v>0.01497957627324833</v>
+        <v>0.02720439429255812</v>
       </c>
       <c r="BQ6">
-        <v>0.01512112759770574</v>
+        <v>0.03800271019137067</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW6" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2129,7 +2132,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2144,151 +2147,151 @@
         <v>88</v>
       </c>
       <c r="G7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" t="s">
         <v>92</v>
       </c>
-      <c r="H7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" t="s">
-        <v>93</v>
-      </c>
       <c r="J7" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.5165323702993595</v>
+        <v>0.4901354772408594</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="S7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T7">
-        <v>0.7948947594915265</v>
+        <v>0.8504698565259804</v>
       </c>
       <c r="U7">
-        <v>0.7576991604779089</v>
+        <v>0.7827089691119478</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>0.9999860748268876</v>
+        <v>0.999990134701026</v>
       </c>
       <c r="Y7">
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>66.46375324164961</v>
+        <v>55.79971796265564</v>
       </c>
       <c r="AA7">
-        <v>13.00000000000001</v>
+        <v>11</v>
       </c>
       <c r="AB7">
-        <v>0.3993291444769469</v>
+        <v>0.5620874491331316</v>
       </c>
       <c r="AC7">
-        <v>0.9168076321515379</v>
+        <v>0.8270778074202023</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH7">
-        <v>0.1996617918747406</v>
+        <v>0.2810409519861982</v>
       </c>
       <c r="AI7">
-        <v>0.608347542252906</v>
+        <v>0.6614995998291965</v>
       </c>
       <c r="AJ7">
-        <v>0.5353949232934802</v>
+        <v>0.4126282140054479</v>
       </c>
       <c r="AK7">
-        <v>1.162963241903283</v>
+        <v>0.5773075844022497</v>
       </c>
       <c r="AL7">
-        <v>0.6691324286627586</v>
+        <v>0.4232373049617013</v>
       </c>
       <c r="AM7">
-        <v>-0.6677289918141179</v>
+        <v>-1.03499428405337</v>
       </c>
       <c r="AN7">
-        <v>0.6048684398241793</v>
+        <v>0.3494276594209536</v>
       </c>
       <c r="AO7">
-        <v>0.07630884853059125</v>
+        <v>0.04748788037401379</v>
       </c>
       <c r="AP7">
-        <v>7.86</v>
+        <v>4.78158</v>
       </c>
       <c r="AQ7">
-        <v>7.849252726758345</v>
+        <v>4.776577545454366</v>
       </c>
       <c r="AR7">
-        <v>7.644023815283218</v>
+        <v>4.728700072013886</v>
       </c>
       <c r="AS7">
-        <v>7.86</v>
+        <v>4.78158</v>
       </c>
       <c r="AT7">
-        <v>8.0227</v>
+        <v>4.83726</v>
       </c>
       <c r="AU7">
-        <v>7.84821</v>
+        <v>4.77440763</v>
       </c>
       <c r="AV7">
-        <v>7.921175</v>
+        <v>4.8164275</v>
       </c>
       <c r="AW7">
-        <v>-0.001367337562551573</v>
+        <v>-0.001046192795192006</v>
       </c>
       <c r="AX7">
-        <v>0.1927257866775658</v>
+        <v>0.2058216514814554</v>
       </c>
       <c r="AY7">
-        <v>0.001367337562551573</v>
+        <v>0.001046192795192006</v>
       </c>
       <c r="AZ7">
-        <v>0.3721049248107365</v>
+        <v>0.4563972679861426</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.4278950751892635</v>
+        <v>0.3436027320138575</v>
       </c>
       <c r="BC7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2300,55 +2303,55 @@
         <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.007783078880407066</v>
+        <v>0.007287863007625078</v>
       </c>
       <c r="BH7">
-        <v>64241.92889252194</v>
+        <v>68607.21716048513</v>
       </c>
       <c r="BI7">
-        <v>64241.92889252194</v>
+        <v>68607.21716048513</v>
       </c>
       <c r="BJ7">
-        <v>8173.273395995158</v>
+        <v>14348.23158045774</v>
       </c>
       <c r="BK7">
-        <v>642.4192889252195</v>
+        <v>686.0721716048513</v>
       </c>
       <c r="BL7">
-        <v>0.006424192889252195</v>
+        <v>0.006860721716048513</v>
       </c>
       <c r="BM7">
-        <v>500</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN7">
-        <v>0.005</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO7">
-        <v>0.1566289190579347</v>
+        <v>0.02791706782303844</v>
       </c>
       <c r="BP7">
-        <v>0.03520613265407405</v>
+        <v>0.005542118526797983</v>
       </c>
       <c r="BQ7">
-        <v>0.0353051358246164</v>
+        <v>0.01715696424868714</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW7" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2356,7 +2359,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2371,151 +2374,151 @@
         <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K8">
-        <v>0.8346552579069189</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>3.344028327709457</v>
+        <v>3.672976609750829</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q8">
-        <v>0.9586638144767297</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T8">
-        <v>-0.9954595725036556</v>
+        <v>-0.9773777765031695</v>
       </c>
       <c r="U8">
-        <v>0.9730946571918411</v>
+        <v>0.9897677588998222</v>
       </c>
       <c r="V8" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" t="s">
         <v>94</v>
       </c>
-      <c r="W8" t="s">
-        <v>95</v>
-      </c>
       <c r="X8">
-        <v>0.9997582435166329</v>
+        <v>0.9997910378935834</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>-172.3768816259754</v>
+        <v>-162.6980782645607</v>
       </c>
       <c r="AA8">
-        <v>6.999999999999997</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>-0.9911620952036588</v>
+        <v>-0.9547508248308558</v>
       </c>
       <c r="AC8">
-        <v>-0.1326563267676789</v>
+        <v>-0.2974068971708632</v>
       </c>
       <c r="AD8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AH8">
-        <v>-0.9909224753410756</v>
+        <v>-0.9545513180873961</v>
       </c>
       <c r="AI8">
-        <v>0.9912305746941298</v>
+        <v>0.9796547909557933</v>
       </c>
       <c r="AJ8">
-        <v>-2.479793160044495</v>
+        <v>-2.692407542451325</v>
       </c>
       <c r="AK8">
-        <v>-0.3004458313453518</v>
+        <v>-0.7894845107283921</v>
       </c>
       <c r="AL8">
-        <v>-4.410775866295087</v>
+        <v>-4.97731983308966</v>
       </c>
       <c r="AM8">
-        <v>2.520525211740795</v>
+        <v>2.311647954026918</v>
       </c>
       <c r="AN8">
-        <v>4.188109640161673</v>
+        <v>4.75185668384593</v>
       </c>
       <c r="AO8">
-        <v>0.04022292731859602</v>
+        <v>0.04464879837478363</v>
       </c>
       <c r="AP8">
-        <v>6.7262</v>
+        <v>6.71944</v>
       </c>
       <c r="AQ8">
-        <v>6.714035850780595</v>
+        <v>6.704341462783908</v>
       </c>
       <c r="AR8">
-        <v>6.747721135191535</v>
+        <v>6.742525149058838</v>
       </c>
       <c r="AS8">
-        <v>6.7262</v>
+        <v>6.71944</v>
       </c>
       <c r="AT8">
-        <v>6.680200000000001</v>
+        <v>6.666679999999999</v>
       </c>
       <c r="AU8">
-        <v>6.714035850780595</v>
+        <v>6.704341462783908</v>
       </c>
       <c r="AV8">
-        <v>6.754125000000001</v>
+        <v>6.747365</v>
       </c>
       <c r="AW8">
-        <v>-0.001808472721507704</v>
+        <v>-0.002246993382795475</v>
       </c>
       <c r="AX8">
-        <v>0.4356006882508481</v>
+        <v>0.5406817266281466</v>
       </c>
       <c r="AY8">
-        <v>0.001808472721507704</v>
+        <v>0.002246993382795475</v>
       </c>
       <c r="AZ8">
-        <v>0.3648613239500608</v>
+        <v>0.3574317292577109</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.4351386760499392</v>
+        <v>0.442568270742289</v>
       </c>
       <c r="BC8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2524,58 +2527,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>479.3319072383648</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.004151675537450629</v>
+        <v>0.004155852273403799</v>
       </c>
       <c r="BH8">
-        <v>120433.3034914933</v>
+        <v>120312.2649955219</v>
       </c>
       <c r="BI8">
-        <v>115455.0501151886</v>
+        <v>120312.2649955219</v>
       </c>
       <c r="BJ8">
-        <v>17164.97429680779</v>
+        <v>17905.10295434172</v>
       </c>
       <c r="BK8">
-        <v>1154.550501151886</v>
+        <v>1203.122649955219</v>
       </c>
       <c r="BL8">
-        <v>0.01154550501151886</v>
+        <v>0.01203122649955219</v>
       </c>
       <c r="BM8">
-        <v>479.3319072383649</v>
+        <v>500</v>
       </c>
       <c r="BN8">
-        <v>0.004793319072383649</v>
+        <v>0.005</v>
       </c>
       <c r="BO8">
-        <v>0.08922169778185285</v>
+        <v>0.08477888734106553</v>
       </c>
       <c r="BP8">
-        <v>0.009875435536450216</v>
+        <v>0.01319435604094559</v>
       </c>
       <c r="BQ8">
-        <v>0.01206133065912319</v>
+        <v>0.01290237387631207</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW8" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2583,7 +2586,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2595,154 +2598,154 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" t="s">
         <v>92</v>
       </c>
-      <c r="H9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" t="s">
-        <v>94</v>
-      </c>
       <c r="J9" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>1.224522360957086</v>
+        <v>0.8685446894451283</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
       </c>
       <c r="P9" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9" t="s">
         <v>98</v>
       </c>
-      <c r="Q9">
-        <v>0.75</v>
-      </c>
-      <c r="R9" t="s">
-        <v>102</v>
-      </c>
       <c r="S9" t="s">
+        <v>101</v>
+      </c>
+      <c r="T9">
+        <v>0.6831823310055514</v>
+      </c>
+      <c r="U9">
+        <v>0.7074302466322477</v>
+      </c>
+      <c r="V9" t="s">
+        <v>92</v>
+      </c>
+      <c r="W9" t="s">
+        <v>94</v>
+      </c>
+      <c r="X9">
+        <v>0.9999927907189984</v>
+      </c>
+      <c r="Y9">
+        <v>0.6442016024401184</v>
+      </c>
+      <c r="Z9">
+        <v>66.10936809713229</v>
+      </c>
+      <c r="AA9">
+        <v>12</v>
+      </c>
+      <c r="AB9">
+        <v>0.4049920970587502</v>
+      </c>
+      <c r="AC9">
+        <v>0.9143201853398818</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE9" t="s">
         <v>106</v>
       </c>
-      <c r="T9">
-        <v>-0.9712772551812577</v>
-      </c>
-      <c r="U9">
-        <v>0.8358987908355353</v>
-      </c>
-      <c r="V9" t="s">
-        <v>94</v>
-      </c>
-      <c r="W9" t="s">
-        <v>95</v>
-      </c>
-      <c r="X9">
-        <v>0.9952961040158775</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>156.2941560896775</v>
-      </c>
-      <c r="AA9">
-        <v>-2.000000000000003</v>
-      </c>
-      <c r="AB9">
-        <v>-0.9156215917218425</v>
-      </c>
-      <c r="AC9">
-        <v>0.4020411680074063</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>94</v>
-      </c>
-      <c r="AE9" t="s">
+      <c r="AF9" t="s">
         <v>109</v>
       </c>
-      <c r="AF9" t="s">
-        <v>112</v>
-      </c>
       <c r="AG9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AH9">
-        <v>-0.4556573014967832</v>
+        <v>0.3329419271905759</v>
       </c>
       <c r="AI9">
-        <v>0.7664129892859401</v>
+        <v>0.7400069032371405</v>
       </c>
       <c r="AJ9">
-        <v>-1.068051724138155</v>
+        <v>0.7661801512332116</v>
       </c>
       <c r="AK9">
-        <v>0.4623541320830815</v>
+        <v>1.64323692369165</v>
       </c>
       <c r="AL9">
-        <v>-0.893938406614134</v>
+        <v>1.00420965457867</v>
       </c>
       <c r="AM9">
-        <v>2.801726646986756</v>
+        <v>-1.246062843434765</v>
       </c>
       <c r="AN9">
-        <v>0.7061852967172343</v>
+        <v>0.8743558278062863</v>
       </c>
       <c r="AO9">
-        <v>0.0441808309077974</v>
+        <v>0.06885682080105154</v>
       </c>
       <c r="AP9">
-        <v>158.7225</v>
+        <v>7.8525</v>
       </c>
       <c r="AQ9">
-        <v>158.3963731009328</v>
+        <v>7.8329110413689</v>
       </c>
       <c r="AR9">
-        <v>161.5372384049711</v>
+        <v>7.627851628018186</v>
       </c>
       <c r="AS9">
-        <v>158.7225</v>
+        <v>7.8525</v>
       </c>
       <c r="AT9">
-        <v>153.813</v>
+        <v>8.0077</v>
       </c>
       <c r="AU9">
-        <v>158.3963731009328</v>
+        <v>7.8329110413689</v>
       </c>
       <c r="AV9">
-        <v>159.886</v>
+        <v>7.913349999999999</v>
       </c>
       <c r="AW9">
-        <v>-0.002054698603331092</v>
+        <v>-0.002494614279668838</v>
       </c>
       <c r="AX9">
-        <v>0.2802981513254968</v>
+        <v>0.321922081036972</v>
       </c>
       <c r="AY9">
-        <v>0.002054698603331092</v>
+        <v>0.002494614279668838</v>
       </c>
       <c r="AZ9">
-        <v>0.4662560775719941</v>
+        <v>0.3784377378823732</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.333743922428006</v>
+        <v>0.4215622621176268</v>
       </c>
       <c r="BC9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2751,58 +2754,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG9">
-        <v>0.007330403691978222</v>
+        <v>0.007749124482648762</v>
       </c>
       <c r="BH9">
-        <v>68209.06746884322</v>
+        <v>64523.41824157829</v>
       </c>
       <c r="BI9">
-        <v>51156.80060163241</v>
+        <v>64523.41824157829</v>
       </c>
       <c r="BJ9">
-        <v>322.3033949290896</v>
+        <v>8216.926869350944</v>
       </c>
       <c r="BK9">
-        <v>511.5680060163241</v>
+        <v>645.2341824157828</v>
       </c>
       <c r="BL9">
-        <v>0.005115680060163241</v>
+        <v>0.006452341824157828</v>
       </c>
       <c r="BM9">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BN9">
-        <v>0.00375</v>
+        <v>0.005</v>
       </c>
       <c r="BO9">
-        <v>2.966035496536826</v>
+        <v>0.1457973570517644</v>
       </c>
       <c r="BP9">
-        <v>0.6759679685511583</v>
+        <v>0.02931881379040566</v>
       </c>
       <c r="BQ9">
-        <v>2.202381130375768</v>
+        <v>0.03361060126143285</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW9" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2810,7 +2813,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2825,151 +2828,151 @@
         <v>87</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" t="s">
         <v>93</v>
       </c>
       <c r="J10" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K10">
-        <v>0.01636935260508167</v>
+        <v>0.06621278626437836</v>
       </c>
       <c r="L10">
-        <v>1.426871435149012</v>
+        <v>1.637136906626681</v>
       </c>
       <c r="M10">
         <v>6</v>
       </c>
       <c r="N10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O10" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" t="s">
         <v>96</v>
       </c>
-      <c r="P10" t="s">
-        <v>99</v>
-      </c>
       <c r="Q10">
-        <v>0.9877229855461888</v>
+        <v>0.7665531965660946</v>
       </c>
       <c r="R10" t="s">
         <v>100</v>
       </c>
       <c r="S10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T10">
-        <v>0.9252029799917924</v>
+        <v>-0.9844460133251428</v>
       </c>
       <c r="U10">
-        <v>0.8187948620166103</v>
+        <v>0.8520339916907844</v>
       </c>
       <c r="V10" t="s">
         <v>93</v>
       </c>
       <c r="W10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="X10">
-        <v>0.999992472518166</v>
+        <v>0.9964054710192536</v>
       </c>
       <c r="Y10">
-        <v>0.2038960067893222</v>
+        <v>0.2791157243714534</v>
       </c>
       <c r="Z10">
-        <v>34.9406006058263</v>
+        <v>164.5765081209393</v>
       </c>
       <c r="AA10">
-        <v>3.000000000000004</v>
+        <v>11</v>
       </c>
       <c r="AB10">
-        <v>0.8197462392755892</v>
+        <v>-0.9639864423678249</v>
       </c>
       <c r="AC10">
-        <v>0.5727269010562788</v>
+        <v>0.2659513845254884</v>
       </c>
       <c r="AD10" t="s">
         <v>93</v>
       </c>
       <c r="AE10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AH10">
-        <v>0.49344089762687</v>
+        <v>-0.6143089908878036</v>
       </c>
       <c r="AI10">
-        <v>0.7803073031970221</v>
+        <v>0.8375106535875269</v>
       </c>
       <c r="AJ10">
-        <v>1.145284586633104</v>
+        <v>-1.400465121071157</v>
       </c>
       <c r="AK10">
-        <v>0.789098290569426</v>
+        <v>0.4294431392108509</v>
       </c>
       <c r="AL10">
-        <v>1.484843873573096</v>
+        <v>-1.313231770328659</v>
       </c>
       <c r="AM10">
-        <v>-2.174224443684099</v>
+        <v>3.33070689379288</v>
       </c>
       <c r="AN10">
-        <v>1.295532618310246</v>
+        <v>1.084636112146913</v>
       </c>
       <c r="AO10">
-        <v>0.04262090216584771</v>
+        <v>0.04166892569233371</v>
       </c>
       <c r="AP10">
-        <v>0.710915</v>
+        <v>158.6705</v>
       </c>
       <c r="AQ10">
-        <v>0.7086330635653748</v>
+        <v>158.2067588046467</v>
       </c>
       <c r="AR10">
-        <v>0.6958042435032287</v>
+        <v>161.3252435451827</v>
       </c>
       <c r="AS10">
-        <v>0.710915</v>
+        <v>158.6705</v>
       </c>
       <c r="AT10">
-        <v>0.7216449999999999</v>
+        <v>153.709</v>
       </c>
       <c r="AU10">
-        <v>0.7086330635653748</v>
+        <v>158.2067588046467</v>
       </c>
       <c r="AV10">
-        <v>0.718615</v>
+        <v>159.834</v>
       </c>
       <c r="AW10">
-        <v>-0.003209858329934174</v>
+        <v>-0.002922668015499373</v>
       </c>
       <c r="AX10">
-        <v>0.2963553811201472</v>
+        <v>0.3985742976822415</v>
       </c>
       <c r="AY10">
-        <v>0.003209858329934174</v>
+        <v>0.002922668015499373</v>
       </c>
       <c r="AZ10">
-        <v>0.4204960654299259</v>
+        <v>0.4602608600750335</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3795039345700741</v>
+        <v>0.3397391399249665</v>
       </c>
       <c r="BC10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2978,58 +2981,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>493.8614927730944</v>
+        <v>383.2765982830473</v>
       </c>
       <c r="BG10">
-        <v>0.0108311120176112</v>
+        <v>0.007332806035148394</v>
       </c>
       <c r="BH10">
-        <v>46163.31168831128</v>
+        <v>68186.72110012814</v>
       </c>
       <c r="BI10">
-        <v>45596.56404347809</v>
+        <v>52268.74902266399</v>
       </c>
       <c r="BJ10">
-        <v>64137.85620429741</v>
+        <v>329.4169301959973</v>
       </c>
       <c r="BK10">
-        <v>455.9656404347809</v>
+        <v>522.68749022664</v>
       </c>
       <c r="BL10">
-        <v>0.004559656404347809</v>
+        <v>0.0052268749022664</v>
       </c>
       <c r="BM10">
-        <v>493.8614927730944</v>
+        <v>383.2765982830473</v>
       </c>
       <c r="BN10">
-        <v>0.004938614927730944</v>
+        <v>0.003832765982830473</v>
       </c>
       <c r="BO10">
-        <v>0.008955484327776788</v>
+        <v>2.795547701258807</v>
       </c>
       <c r="BP10">
-        <v>0.002030753790924494</v>
+        <v>0.5568598907852828</v>
       </c>
       <c r="BQ10">
-        <v>0.003662605163050011</v>
+        <v>1.816119394291128</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW10" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3037,7 +3040,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3049,154 +3052,154 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s">
         <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0.03701447009399642</v>
+        <v>0.07591293037768411</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O11" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" t="s">
         <v>96</v>
       </c>
-      <c r="P11" t="s">
+      <c r="Q11">
+        <v>0.75</v>
+      </c>
+      <c r="R11" t="s">
         <v>99</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11" t="s">
-        <v>103</v>
-      </c>
       <c r="S11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="T11">
-        <v>0.6853787671500985</v>
+        <v>-0.4092036361630399</v>
       </c>
       <c r="U11">
-        <v>0.70811771335306</v>
+        <v>0.5590639223686202</v>
       </c>
       <c r="V11" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="X11">
-        <v>0.9987890725420626</v>
+        <v>0.9996891443810091</v>
       </c>
       <c r="Y11">
-        <v>0.1539430924141814</v>
+        <v>0.9943494743949133</v>
       </c>
       <c r="Z11">
-        <v>-77.70524749282117</v>
+        <v>-92.34697423853162</v>
       </c>
       <c r="AA11">
-        <v>-18</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB11">
-        <v>0.2129409016590923</v>
+        <v>-0.04095097359994582</v>
       </c>
       <c r="AC11">
-        <v>-0.9770650809442597</v>
+        <v>-0.9991611570518625</v>
       </c>
       <c r="AD11" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="AE11" t="s">
         <v>108</v>
       </c>
       <c r="AF11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AH11">
-        <v>0.1227120657147661</v>
+        <v>-0.04082258246240339</v>
       </c>
       <c r="AI11">
-        <v>0.576325034692154</v>
+        <v>0.6547500567402622</v>
       </c>
       <c r="AJ11">
-        <v>0.257825198952521</v>
+        <v>-0.05214664521845188</v>
       </c>
       <c r="AK11">
-        <v>-1.092074321074909</v>
+        <v>-1.643112663229438</v>
       </c>
       <c r="AL11">
-        <v>0.04268234739644627</v>
+        <v>-0.5445606754256364</v>
       </c>
       <c r="AM11">
-        <v>-2.283244132581187</v>
+        <v>-1.72515865826341</v>
       </c>
       <c r="AN11">
-        <v>0.4092268280514446</v>
+        <v>0.6707493927570177</v>
       </c>
       <c r="AO11">
-        <v>0.1194801978542123</v>
+        <v>0.3753088716803816</v>
       </c>
       <c r="AP11">
-        <v>0.7984</v>
+        <v>0.79914</v>
       </c>
       <c r="AQ11">
-        <v>0.7896262800223005</v>
+        <v>0.7893697760435053</v>
       </c>
       <c r="AR11">
-        <v>0.7932723671265853</v>
+        <v>0.7910878802046709</v>
       </c>
       <c r="AS11">
-        <v>0.7984</v>
+        <v>0.79914</v>
       </c>
       <c r="AT11">
-        <v>0.7806150000000001</v>
+        <v>0.782095</v>
       </c>
       <c r="AU11">
-        <v>0.7896262800223005</v>
+        <v>0.7893697760435053</v>
       </c>
       <c r="AV11">
-        <v>0.808435</v>
+        <v>0.809175</v>
       </c>
       <c r="AW11">
-        <v>-0.01098912822858153</v>
+        <v>-0.01222592281264188</v>
       </c>
       <c r="AX11">
-        <v>0.8743119060986049</v>
+        <v>0.9736147440453053</v>
       </c>
       <c r="AY11">
-        <v>0.01098912822858153</v>
+        <v>0.01222592281264188</v>
       </c>
       <c r="AZ11">
-        <v>0.4309174228536322</v>
+        <v>0.4298707372413849</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3690825771463678</v>
+        <v>0.3701292627586151</v>
       </c>
       <c r="BC11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3205,58 +3208,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG11">
-        <v>0.01256888777555109</v>
+        <v>0.01255724904272091</v>
       </c>
       <c r="BH11">
-        <v>39780.76731439965</v>
+        <v>39817.6382660688</v>
       </c>
       <c r="BI11">
-        <v>39780.76731439965</v>
+        <v>29863.2286995516</v>
       </c>
       <c r="BJ11">
-        <v>49825.61036372702</v>
+        <v>37369.20777279526</v>
       </c>
       <c r="BK11">
-        <v>397.8076731439965</v>
+        <v>298.632286995516</v>
       </c>
       <c r="BL11">
-        <v>0.003978076731439965</v>
+        <v>0.00298632286995516</v>
       </c>
       <c r="BM11">
-        <v>500.0000000000001</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN11">
-        <v>0.005000000000000001</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO11">
-        <v>0.0192237000735142</v>
+        <v>0.01890071132597321</v>
       </c>
       <c r="BP11">
-        <v>0.008522870882223466</v>
+        <v>0.007966138826463194</v>
       </c>
       <c r="BQ11">
-        <v>0.01127377687915577</v>
+        <v>0.01079946229767044</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04809530464707595</v>
+        <v>0.0525449049327628</v>
       </c>
       <c r="BT11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BU11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BW11" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
   <si>
     <t>Pair</t>
   </si>
@@ -241,36 +241,36 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
-    <t>GBPUSD</t>
+    <t>AUDUSD</t>
+  </si>
+  <si>
+    <t>AUDCNH</t>
+  </si>
+  <si>
+    <t>EURCNH</t>
   </si>
   <si>
     <t>EURUSD</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>AUDCNH</t>
+    <t>USDJPY</t>
+  </si>
+  <si>
+    <t>USDCHF</t>
   </si>
   <si>
     <t>USDCNH</t>
   </si>
   <si>
-    <t>EURCNH</t>
-  </si>
-  <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
@@ -286,6 +286,9 @@
     <t>HIGH</t>
   </si>
   <si>
+    <t>FLAT</t>
+  </si>
+  <si>
     <t>LONG</t>
   </si>
   <si>
@@ -304,6 +307,9 @@
     <t>CONFLICT</t>
   </si>
   <si>
+    <t>NO_SIGNAL</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
@@ -313,21 +319,21 @@
     <t>UP_ACCELERATING</t>
   </si>
   <si>
+    <t>DOWN_DECELERATING</t>
+  </si>
+  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>多头加速</t>
   </si>
   <si>
+    <t>空头减速</t>
+  </si>
+  <si>
     <t>空头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>NEUTRAL</t>
   </si>
   <si>
@@ -346,58 +352,64 @@
     <t>UP_STEEPENING</t>
   </si>
   <si>
+    <t>DOWN_VALLEY_FLATTENING</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
-    <t>TRANSITION_ZONE</t>
-  </si>
-  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
+    <t>下降谷底收敛</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
-    <t>地形转换区</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.02071,naive=0.007171,drift4=0.007376; naive_cap_applied</t>
   </si>
   <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=185.7,naive=145.2,drift4=135.5; naive_cap_applied</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.02071,naive=0.007171,drift4=0.007376; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0109,naive=0.004963,drift4=0.004; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.05464,naive=0.02473,drift4=0.02191; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1412,naive=0.02646,drift4=0.03148; naive_cap_applied</t>
   </si>
   <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02451,naive=0.007486,drift4=0.007284; naive_cap_applied</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0109,naive=0.004963,drift4=0.004; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.1029,naive=0.0272,drift4=0.038; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=0.02792,naive=0.005542,drift4=0.01716; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.09977,naive=0.02511,drift4=0.03592; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=2.796,naive=0.5569,drift4=1.816; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0189,naive=0.007966,drift4=0.0108; naive_cap_applied</t>
   </si>
   <si>
     <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.08478,naive=0.01319,drift4=0.0129; naive_cap_applied</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1458,naive=0.02932,drift4=0.03361; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=2.796,naive=0.5569,drift4=1.816; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0189,naive=0.007966,drift4=0.0108; naive_cap_applied</t>
+    <t>SKIP</t>
   </si>
   <si>
     <t>OPEN</t>
+  </si>
+  <si>
+    <t>NONE</t>
   </si>
   <si>
     <t>MARKET</t>
@@ -997,7 +1009,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1018,145 +1030,136 @@
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2">
         <v>46254</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1.842550331079064</v>
+        <v>2.799788928978186</v>
       </c>
       <c r="M2">
         <v>6</v>
       </c>
       <c r="N2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q2">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T2">
-        <v>0.8739244504506468</v>
+        <v>0.9038103801512347</v>
       </c>
       <c r="U2">
-        <v>0.7932067133357139</v>
+        <v>0.9567110974963017</v>
       </c>
       <c r="V2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X2">
-        <v>0.9997628425316913</v>
+        <v>0.9999857057129841</v>
       </c>
       <c r="Y2">
-        <v>0.5359779605829512</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>41.2324549124319</v>
+        <v>36.13601322557214</v>
       </c>
       <c r="AA2">
-        <v>-3.000000000000004</v>
+        <v>6.000000000000009</v>
       </c>
       <c r="AB2">
-        <v>0.7520416768015612</v>
+        <v>0.807619385320781</v>
       </c>
       <c r="AC2">
-        <v>0.6591155561458827</v>
+        <v>0.5897041024565488</v>
       </c>
       <c r="AD2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH2">
-        <v>0.5774227479024108</v>
+        <v>0.8076078409774876</v>
       </c>
       <c r="AI2">
-        <v>0.824966669233184</v>
+        <v>0.9348738201194033</v>
       </c>
       <c r="AJ2">
-        <v>1.441282703672705</v>
+        <v>2.113288595471767</v>
       </c>
       <c r="AK2">
-        <v>1.279701112861722</v>
+        <v>1.508310092799069</v>
       </c>
       <c r="AL2">
-        <v>2.082580962013676</v>
+        <v>3.519860679519747</v>
       </c>
       <c r="AM2">
-        <v>-2.390018558409804</v>
+        <v>-2.75011321001353</v>
       </c>
       <c r="AN2">
-        <v>1.855837817997649</v>
+        <v>3.240920255412093</v>
       </c>
       <c r="AO2">
-        <v>0.0517228053997773</v>
+        <v>0.04937994984250294</v>
       </c>
       <c r="AP2">
-        <v>4595.98</v>
+        <v>1.36555</v>
       </c>
       <c r="AQ2">
-        <v>4759.194340854186</v>
+        <v>1.366496174145982</v>
       </c>
       <c r="AR2">
-        <v>4516.303669825544</v>
+        <v>1.336083774598892</v>
       </c>
       <c r="AS2">
-        <v>4595.98</v>
+        <v>1.36555</v>
       </c>
       <c r="AT2">
-        <v>5146.07</v>
-      </c>
-      <c r="AU2">
-        <v>4759.194340854186</v>
-      </c>
-      <c r="AV2">
-        <v>4446.965</v>
+        <v>1.39653</v>
       </c>
       <c r="AW2">
-        <v>0.03551241320766976</v>
-      </c>
-      <c r="AX2">
-        <v>1.095287996874049</v>
+        <v>0.0006928886865964252</v>
       </c>
       <c r="AY2">
-        <v>0.03551241320766976</v>
+        <v>0.0006928886865964252</v>
       </c>
       <c r="AZ2">
-        <v>0.4396196587218628</v>
+        <v>0.3943641756922918</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.3603803412781372</v>
+        <v>0.4056358243077082</v>
       </c>
       <c r="BC2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1165,58 +1168,55 @@
         <v>100</v>
       </c>
       <c r="BF2">
-        <v>375</v>
-      </c>
-      <c r="BG2">
-        <v>0.03242290001261965</v>
+        <v>0</v>
       </c>
       <c r="BH2">
-        <v>15421.19920813344</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>11565.89940610008</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>2.51652518202866</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>115.6589940610008</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>0.001156589940610008</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>374.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>0.003749999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>185.6517557047789</v>
+        <v>0.02070822257070009</v>
       </c>
       <c r="BP2">
-        <v>145.180152494632</v>
+        <v>0.007171322759006341</v>
       </c>
       <c r="BQ2">
-        <v>135.4858129633054</v>
+        <v>0.007375623821229548</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="BW2" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1224,7 +1224,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1236,154 +1236,154 @@
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46254</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>2.799788928978186</v>
+        <v>1.842550331079064</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T3">
-        <v>0.9038103801512347</v>
+        <v>0.8739244504506468</v>
       </c>
       <c r="U3">
-        <v>0.9567110974963017</v>
+        <v>0.7932067133357139</v>
       </c>
       <c r="V3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X3">
-        <v>0.9999857057129841</v>
+        <v>0.9997628425316913</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0.5359779605829512</v>
       </c>
       <c r="Z3">
-        <v>36.13601322557214</v>
+        <v>41.2324549124319</v>
       </c>
       <c r="AA3">
-        <v>6.000000000000009</v>
+        <v>-3.000000000000004</v>
       </c>
       <c r="AB3">
-        <v>0.807619385320781</v>
+        <v>0.7520416768015612</v>
       </c>
       <c r="AC3">
-        <v>0.5897041024565488</v>
+        <v>0.6591155561458827</v>
       </c>
       <c r="AD3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH3">
-        <v>0.8076078409774876</v>
+        <v>0.5774227479024108</v>
       </c>
       <c r="AI3">
-        <v>0.9348738201194033</v>
+        <v>0.824966669233184</v>
       </c>
       <c r="AJ3">
-        <v>2.113288595471767</v>
+        <v>1.441282703672705</v>
       </c>
       <c r="AK3">
-        <v>1.508310092799069</v>
+        <v>1.279701112861722</v>
       </c>
       <c r="AL3">
-        <v>3.519860679519747</v>
+        <v>2.082580962013676</v>
       </c>
       <c r="AM3">
-        <v>-2.75011321001353</v>
+        <v>-2.390018558409804</v>
       </c>
       <c r="AN3">
-        <v>3.240920255412093</v>
+        <v>1.855837817997649</v>
       </c>
       <c r="AO3">
-        <v>0.04937994984250294</v>
+        <v>0.0517228053997773</v>
       </c>
       <c r="AP3">
-        <v>1.36555</v>
+        <v>4595.98</v>
       </c>
       <c r="AQ3">
-        <v>1.372678466015573</v>
+        <v>4758.902063072866</v>
       </c>
       <c r="AR3">
-        <v>1.351760380768147</v>
+        <v>4515.638827442995</v>
       </c>
       <c r="AS3">
-        <v>1.36555</v>
+        <v>4595.98</v>
       </c>
       <c r="AT3">
-        <v>1.39653</v>
+        <v>5146.07</v>
       </c>
       <c r="AU3">
-        <v>1.372678466015573</v>
+        <v>4758.902063072866</v>
       </c>
       <c r="AV3">
-        <v>1.35361</v>
+        <v>4446.965</v>
       </c>
       <c r="AW3">
-        <v>0.005220216041574895</v>
+        <v>0.03544881898373491</v>
       </c>
       <c r="AX3">
-        <v>0.5970239544030649</v>
+        <v>1.093326598482477</v>
       </c>
       <c r="AY3">
-        <v>0.005220216041574895</v>
+        <v>0.03544881898373491</v>
       </c>
       <c r="AZ3">
-        <v>0.3943641756922918</v>
+        <v>0.4396196587218628</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.4056358243077082</v>
+        <v>0.3603803412781372</v>
       </c>
       <c r="BC3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1392,58 +1392,58 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG3">
-        <v>0.008743729632748713</v>
+        <v>0.03242290001261965</v>
       </c>
       <c r="BH3">
-        <v>57183.83584589612</v>
+        <v>15421.19920813344</v>
       </c>
       <c r="BI3">
-        <v>57183.83584589612</v>
+        <v>11565.89940610008</v>
       </c>
       <c r="BJ3">
-        <v>41876.04690117251</v>
+        <v>2.51652518202866</v>
       </c>
       <c r="BK3">
-        <v>571.8383584589612</v>
+        <v>115.6589940610008</v>
       </c>
       <c r="BL3">
-        <v>0.005718383584589612</v>
+        <v>0.001156589940610008</v>
       </c>
       <c r="BM3">
-        <v>500</v>
+        <v>374.9999999999999</v>
       </c>
       <c r="BN3">
-        <v>0.005</v>
+        <v>0.003749999999999999</v>
       </c>
       <c r="BO3">
-        <v>0.02070822257070009</v>
+        <v>185.6517557047789</v>
       </c>
       <c r="BP3">
-        <v>0.007171322759006341</v>
+        <v>145.180152494632</v>
       </c>
       <c r="BQ3">
-        <v>0.007375623821229548</v>
+        <v>135.4858129633054</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW3" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1451,7 +1451,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1463,154 +1463,154 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
         <v>46254</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0.4236656675179737</v>
       </c>
       <c r="L4">
-        <v>2.559319104838145</v>
+        <v>1.77162634908774</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q4">
-        <v>1</v>
+        <v>0.8559164168794934</v>
       </c>
       <c r="R4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T4">
-        <v>0.8318112568274303</v>
+        <v>0.8848405598661534</v>
       </c>
       <c r="U4">
-        <v>0.9243073098068914</v>
+        <v>0.8617267344551464</v>
       </c>
       <c r="V4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X4">
-        <v>0.9999689769381911</v>
+        <v>0.9999945295507252</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>0.728906953090797</v>
       </c>
       <c r="Z4">
-        <v>48.42366466301528</v>
+        <v>39.53535493000027</v>
       </c>
       <c r="AA4">
-        <v>11</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB4">
-        <v>0.6636172957632107</v>
+        <v>0.77123193812414</v>
       </c>
       <c r="AC4">
-        <v>0.7480722456848158</v>
+        <v>0.6365542377655518</v>
       </c>
       <c r="AD4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH4">
-        <v>0.6635967083228268</v>
+        <v>0.6666904830178377</v>
       </c>
       <c r="AI4">
-        <v>0.8907372185570044</v>
+        <v>0.8695223443438814</v>
       </c>
       <c r="AJ4">
-        <v>1.950892777410652</v>
+        <v>1.354231212924323</v>
       </c>
       <c r="AK4">
-        <v>2.118073102677476</v>
+        <v>1.088437348502598</v>
       </c>
       <c r="AL4">
-        <v>3.108834761886927</v>
+        <v>2.132516225977054</v>
       </c>
       <c r="AM4">
-        <v>-2.378758064309582</v>
+        <v>-1.543205890574448</v>
       </c>
       <c r="AN4">
-        <v>2.868011158736149</v>
+        <v>1.990644408001752</v>
       </c>
       <c r="AO4">
-        <v>0.05558074733550537</v>
+        <v>0.05084475369515897</v>
       </c>
       <c r="AP4">
-        <v>1.17016</v>
+        <v>0.71668</v>
       </c>
       <c r="AQ4">
-        <v>1.176214495402759</v>
+        <v>0.7232428738892167</v>
       </c>
       <c r="AR4">
-        <v>1.152408785740714</v>
+        <v>0.7161148688152355</v>
       </c>
       <c r="AS4">
-        <v>1.17016</v>
+        <v>0.71668</v>
       </c>
       <c r="AT4">
-        <v>1.20101</v>
+        <v>0.7331749999999999</v>
       </c>
       <c r="AU4">
-        <v>1.176214495402759</v>
+        <v>0.7232428738892167</v>
       </c>
       <c r="AV4">
-        <v>1.15637375</v>
+        <v>0.708305</v>
       </c>
       <c r="AW4">
-        <v>0.005174074829731866</v>
+        <v>0.009157328081175316</v>
       </c>
       <c r="AX4">
-        <v>0.4391691288609315</v>
+        <v>0.7836267330408035</v>
       </c>
       <c r="AY4">
-        <v>0.005174074829731866</v>
+        <v>0.009157328081175316</v>
       </c>
       <c r="AZ4">
-        <v>0.3832312603935049</v>
+        <v>0.388808622802798</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.4167687396064951</v>
+        <v>0.411191377197202</v>
       </c>
       <c r="BC4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1619,58 +1619,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>500</v>
+        <v>427.9582084397467</v>
       </c>
       <c r="BG4">
-        <v>0.01178150851165657</v>
+        <v>0.01168582910085393</v>
       </c>
       <c r="BH4">
-        <v>42439.38707045046</v>
+        <v>42786.86567164182</v>
       </c>
       <c r="BI4">
-        <v>42439.38707045046</v>
+        <v>36621.98075517586</v>
       </c>
       <c r="BJ4">
-        <v>36268.02067277164</v>
+        <v>51099.48757489516</v>
       </c>
       <c r="BK4">
-        <v>424.3938707045046</v>
+        <v>366.2198075517587</v>
       </c>
       <c r="BL4">
-        <v>0.004243938707045046</v>
+        <v>0.003662198075517587</v>
       </c>
       <c r="BM4">
-        <v>500</v>
+        <v>427.9582084397467</v>
       </c>
       <c r="BN4">
-        <v>0.005</v>
+        <v>0.004279582084397467</v>
       </c>
       <c r="BO4">
-        <v>0.02450828036901452</v>
+        <v>0.01090118721268276</v>
       </c>
       <c r="BP4">
-        <v>0.00748638850717295</v>
+        <v>0.004963073343992102</v>
       </c>
       <c r="BQ4">
-        <v>0.00728373871436286</v>
+        <v>0.003999580815931342</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW4" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1678,7 +1678,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1690,154 +1690,154 @@
         <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K5">
-        <v>0.4236656675179737</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.77162634908774</v>
+        <v>0.6856766544182692</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q5">
-        <v>0.8559164168794934</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T5">
-        <v>0.8848405598661534</v>
+        <v>0.8229077268110704</v>
       </c>
       <c r="U5">
-        <v>0.8617267344551464</v>
+        <v>0.7703033444583698</v>
       </c>
       <c r="V5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X5">
-        <v>0.9999945295507252</v>
+        <v>0.9999794695735529</v>
       </c>
       <c r="Y5">
-        <v>0.728906953090797</v>
+        <v>0.3037884302855449</v>
       </c>
       <c r="Z5">
-        <v>39.53535493000027</v>
+        <v>52.80314866724348</v>
       </c>
       <c r="AA5">
         <v>6.999999999999997</v>
       </c>
       <c r="AB5">
-        <v>0.77123193812414</v>
+        <v>0.6045553409580938</v>
       </c>
       <c r="AC5">
-        <v>0.6365542377655518</v>
+        <v>0.7965631423302505</v>
       </c>
       <c r="AD5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH5">
-        <v>0.6666904830178377</v>
+        <v>0.3940980383373436</v>
       </c>
       <c r="AI5">
-        <v>0.8695223443438814</v>
+        <v>0.7339695153069584</v>
       </c>
       <c r="AJ5">
-        <v>1.354231212924323</v>
+        <v>0.5415463540732421</v>
       </c>
       <c r="AK5">
-        <v>1.088437348502598</v>
+        <v>0.6936543499988544</v>
       </c>
       <c r="AL5">
-        <v>2.132516225977054</v>
+        <v>0.7457365964217691</v>
       </c>
       <c r="AM5">
-        <v>-1.543205890574448</v>
+        <v>-0.8341788638886329</v>
       </c>
       <c r="AN5">
-        <v>1.990644408001752</v>
+        <v>0.6672754744244622</v>
       </c>
       <c r="AO5">
-        <v>0.05084475369515897</v>
+        <v>0.05431724925548111</v>
       </c>
       <c r="AP5">
-        <v>0.71668</v>
+        <v>4.81707</v>
       </c>
       <c r="AQ5">
-        <v>0.717928094540049</v>
+        <v>4.852868531473597</v>
       </c>
       <c r="AR5">
-        <v>0.7024454720028523</v>
+        <v>4.814635544571294</v>
       </c>
       <c r="AS5">
-        <v>0.71668</v>
+        <v>4.81707</v>
       </c>
       <c r="AT5">
-        <v>0.7331749999999999</v>
+        <v>4.90824</v>
       </c>
       <c r="AU5">
-        <v>0.717928094540049</v>
+        <v>4.852868531473597</v>
       </c>
       <c r="AV5">
-        <v>0.708305</v>
+        <v>4.77727</v>
       </c>
       <c r="AW5">
-        <v>0.001741494865280235</v>
+        <v>0.007431598767216682</v>
       </c>
       <c r="AX5">
-        <v>0.1490262137371987</v>
+        <v>0.8994605897888546</v>
       </c>
       <c r="AY5">
-        <v>0.001741494865280235</v>
+        <v>0.007431598767216682</v>
       </c>
       <c r="AZ5">
-        <v>0.388808622802798</v>
+        <v>0.3967489405959904</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.411191377197202</v>
+        <v>0.4032510594040097</v>
       </c>
       <c r="BC5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1846,58 +1846,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>427.9582084397467</v>
+        <v>375</v>
       </c>
       <c r="BG5">
-        <v>0.01168582910085393</v>
+        <v>0.008262283919478034</v>
       </c>
       <c r="BH5">
-        <v>42786.86567164182</v>
+        <v>60515.95477386926</v>
       </c>
       <c r="BI5">
-        <v>36621.98075517586</v>
+        <v>45386.96608040195</v>
       </c>
       <c r="BJ5">
-        <v>51099.48757489516</v>
+        <v>9422.110552763806</v>
       </c>
       <c r="BK5">
-        <v>366.2198075517587</v>
+        <v>453.8696608040195</v>
       </c>
       <c r="BL5">
-        <v>0.003662198075517587</v>
+        <v>0.004538696608040195</v>
       </c>
       <c r="BM5">
-        <v>427.9582084397467</v>
+        <v>375</v>
       </c>
       <c r="BN5">
-        <v>0.004279582084397467</v>
+        <v>0.00375</v>
       </c>
       <c r="BO5">
-        <v>0.01090118721268276</v>
+        <v>0.05464128401302773</v>
       </c>
       <c r="BP5">
-        <v>0.004963073343992102</v>
+        <v>0.02472564932138134</v>
       </c>
       <c r="BQ5">
-        <v>0.003999580815931342</v>
+        <v>0.02191173550814567</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW5" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1905,7 +1905,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1920,151 +1920,151 @@
         <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K6">
-        <v>0.03993506226774555</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>0.705768003120097</v>
+        <v>1.063070255311046</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q6">
-        <v>0.7599837655669364</v>
+        <v>0.75</v>
       </c>
       <c r="R6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T6">
-        <v>0.8135047667508462</v>
+        <v>0.7103445297546604</v>
       </c>
       <c r="U6">
-        <v>0.7720649420737459</v>
+        <v>0.7196531592295451</v>
       </c>
       <c r="V6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X6">
-        <v>0.9999901507828128</v>
+        <v>0.9999924833597915</v>
       </c>
       <c r="Y6">
-        <v>0.4420779968234593</v>
+        <v>0.6711414810589248</v>
       </c>
       <c r="Z6">
-        <v>52.25174269577867</v>
+        <v>62.50512399006986</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AB6">
-        <v>0.6121932303117764</v>
+        <v>0.461669285568499</v>
       </c>
       <c r="AC6">
-        <v>0.7907081944437102</v>
+        <v>0.8870521240393214</v>
       </c>
       <c r="AD6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH6">
-        <v>0.441410846024333</v>
+        <v>0.3857544472229946</v>
       </c>
       <c r="AI6">
-        <v>0.7640742648544088</v>
+        <v>0.7638367478449776</v>
       </c>
       <c r="AJ6">
-        <v>0.5492305659924983</v>
+        <v>0.8802517176106891</v>
       </c>
       <c r="AK6">
-        <v>0.6861654558813107</v>
+        <v>1.60961567707343</v>
       </c>
       <c r="AL6">
-        <v>0.8136425168908916</v>
+        <v>1.052695289542354</v>
       </c>
       <c r="AM6">
-        <v>-0.9698468574691853</v>
+        <v>-1.963087461817747</v>
       </c>
       <c r="AN6">
-        <v>0.7139352009881679</v>
+        <v>0.8613929497502741</v>
       </c>
       <c r="AO6">
-        <v>0.05330570918533644</v>
+        <v>0.05926468808856026</v>
       </c>
       <c r="AP6">
-        <v>9.16441</v>
+        <v>7.8474</v>
       </c>
       <c r="AQ6">
-        <v>9.173646254099516</v>
+        <v>7.898880647833577</v>
       </c>
       <c r="AR6">
-        <v>9.046500198557935</v>
+        <v>7.816395365733179</v>
       </c>
       <c r="AS6">
-        <v>9.16441</v>
+        <v>7.8474</v>
       </c>
       <c r="AT6">
-        <v>9.30973</v>
+        <v>7.9975</v>
       </c>
       <c r="AU6">
-        <v>9.178156615000001</v>
+        <v>7.898880647833577</v>
       </c>
       <c r="AV6">
-        <v>9.081620000000001</v>
+        <v>7.786550000000001</v>
       </c>
       <c r="AW6">
-        <v>0.001007839468063532</v>
+        <v>0.006560217120775894</v>
       </c>
       <c r="AX6">
-        <v>0.1660419736683172</v>
+        <v>0.8460254368706205</v>
       </c>
       <c r="AY6">
-        <v>0.001007839468063532</v>
+        <v>0.006560217120775894</v>
       </c>
       <c r="AZ6">
-        <v>0.4065639426622356</v>
+        <v>0.3787829750692961</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.3934360573377645</v>
+        <v>0.421217024930704</v>
       </c>
       <c r="BC6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2073,58 +2073,58 @@
         <v>100</v>
       </c>
       <c r="BF6">
-        <v>379.9918827834682</v>
+        <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.009033860335799046</v>
+        <v>0.007754160613706374</v>
       </c>
       <c r="BH6">
-        <v>55347.32455610572</v>
+        <v>64481.51191454459</v>
       </c>
       <c r="BI6">
-        <v>42063.06813020459</v>
+        <v>48361.13393590844</v>
       </c>
       <c r="BJ6">
-        <v>4589.828273746438</v>
+        <v>6162.695152013207</v>
       </c>
       <c r="BK6">
-        <v>420.6306813020459</v>
+        <v>483.6113393590845</v>
       </c>
       <c r="BL6">
-        <v>0.004206306813020459</v>
+        <v>0.004836113393590845</v>
       </c>
       <c r="BM6">
-        <v>379.9918827834682</v>
+        <v>375</v>
       </c>
       <c r="BN6">
-        <v>0.003799918827834682</v>
+        <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.1028598876385414</v>
+        <v>0.1411587024259356</v>
       </c>
       <c r="BP6">
-        <v>0.02720439429255812</v>
+        <v>0.02645611204324677</v>
       </c>
       <c r="BQ6">
-        <v>0.03800271019137067</v>
+        <v>0.03148490536551985</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW6" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2132,7 +2132,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2144,7 +2144,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2153,145 +2153,145 @@
         <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7" s="2">
         <v>46254</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0.4901354772408594</v>
+        <v>2.559319104838145</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O7" t="s">
         <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="T7">
-        <v>0.8504698565259804</v>
+        <v>0.8318112568274303</v>
       </c>
       <c r="U7">
-        <v>0.7827089691119478</v>
+        <v>0.9243073098068914</v>
       </c>
       <c r="V7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X7">
-        <v>0.999990134701026</v>
+        <v>0.9999689769381911</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7">
-        <v>55.79971796265564</v>
+        <v>48.42366466301528</v>
       </c>
       <c r="AA7">
         <v>11</v>
       </c>
       <c r="AB7">
-        <v>0.5620874491331316</v>
+        <v>0.6636172957632107</v>
       </c>
       <c r="AC7">
-        <v>0.8270778074202023</v>
+        <v>0.7480722456848158</v>
       </c>
       <c r="AD7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AE7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AF7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AH7">
-        <v>0.2810409519861982</v>
+        <v>0.6635967083228268</v>
       </c>
       <c r="AI7">
-        <v>0.6614995998291965</v>
+        <v>0.8907372185570044</v>
       </c>
       <c r="AJ7">
-        <v>0.4126282140054479</v>
+        <v>1.950892777410652</v>
       </c>
       <c r="AK7">
-        <v>0.5773075844022497</v>
+        <v>2.118073102677476</v>
       </c>
       <c r="AL7">
-        <v>0.4232373049617013</v>
+        <v>3.108834761886927</v>
       </c>
       <c r="AM7">
-        <v>-1.03499428405337</v>
+        <v>-2.378758064309582</v>
       </c>
       <c r="AN7">
-        <v>0.3494276594209536</v>
+        <v>2.868011158736149</v>
       </c>
       <c r="AO7">
-        <v>0.04748788037401379</v>
+        <v>0.05558074733550537</v>
       </c>
       <c r="AP7">
-        <v>4.78158</v>
+        <v>1.17016</v>
       </c>
       <c r="AQ7">
-        <v>4.776577545454366</v>
+        <v>1.174049752683845</v>
       </c>
       <c r="AR7">
-        <v>4.728700072013886</v>
+        <v>1.146760126712504</v>
       </c>
       <c r="AS7">
-        <v>4.78158</v>
+        <v>1.17016</v>
       </c>
       <c r="AT7">
-        <v>4.83726</v>
+        <v>1.20101</v>
       </c>
       <c r="AU7">
-        <v>4.77440763</v>
+        <v>1.174049752683845</v>
       </c>
       <c r="AV7">
-        <v>4.8164275</v>
+        <v>1.15637375</v>
       </c>
       <c r="AW7">
-        <v>-0.001046192795192006</v>
+        <v>0.003324120362895059</v>
       </c>
       <c r="AX7">
-        <v>0.2058216514814554</v>
+        <v>0.2821472614993393</v>
       </c>
       <c r="AY7">
-        <v>0.001046192795192006</v>
+        <v>0.003324120362895059</v>
       </c>
       <c r="AZ7">
-        <v>0.4563972679861426</v>
+        <v>0.3832312603935049</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.3436027320138575</v>
+        <v>0.4167687396064951</v>
       </c>
       <c r="BC7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2303,55 +2303,55 @@
         <v>500</v>
       </c>
       <c r="BG7">
-        <v>0.007287863007625078</v>
+        <v>0.01178150851165657</v>
       </c>
       <c r="BH7">
-        <v>68607.21716048513</v>
+        <v>42439.38707045046</v>
       </c>
       <c r="BI7">
-        <v>68607.21716048513</v>
+        <v>42439.38707045046</v>
       </c>
       <c r="BJ7">
-        <v>14348.23158045774</v>
+        <v>36268.02067277164</v>
       </c>
       <c r="BK7">
-        <v>686.0721716048513</v>
+        <v>424.3938707045046</v>
       </c>
       <c r="BL7">
-        <v>0.006860721716048513</v>
+        <v>0.004243938707045046</v>
       </c>
       <c r="BM7">
-        <v>500.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN7">
-        <v>0.005000000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO7">
-        <v>0.02791706782303844</v>
+        <v>0.02450828036901452</v>
       </c>
       <c r="BP7">
-        <v>0.005542118526797983</v>
+        <v>0.00748638850717295</v>
       </c>
       <c r="BQ7">
-        <v>0.01715696424868714</v>
+        <v>0.00728373871436286</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU7" t="s">
         <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW7" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2359,7 +2359,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2371,154 +2371,154 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I8" t="s">
         <v>93</v>
       </c>
       <c r="J8" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.1984309268304248</v>
       </c>
       <c r="L8">
-        <v>3.672976609750829</v>
+        <v>0.7875694870461764</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0.8511768048771814</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T8">
-        <v>-0.9773777765031695</v>
+        <v>0.8428938372814724</v>
       </c>
       <c r="U8">
-        <v>0.9897677588998222</v>
+        <v>0.8090656441841318</v>
       </c>
       <c r="V8" t="s">
         <v>93</v>
       </c>
       <c r="W8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="X8">
-        <v>0.9997910378935834</v>
+        <v>0.9999951135316221</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0.5210408549913357</v>
       </c>
       <c r="Z8">
-        <v>-162.6980782645607</v>
+        <v>47.60834027287718</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB8">
-        <v>-0.9547508248308558</v>
+        <v>0.6741948870243686</v>
       </c>
       <c r="AC8">
-        <v>-0.2974068971708632</v>
+        <v>0.7385534877787788</v>
       </c>
       <c r="AD8" t="s">
         <v>93</v>
       </c>
       <c r="AE8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AH8">
-        <v>-0.9545513180873961</v>
+        <v>0.5127364782123364</v>
       </c>
       <c r="AI8">
-        <v>0.9796547909557933</v>
+        <v>0.7991032687435249</v>
       </c>
       <c r="AJ8">
-        <v>-2.692407542451325</v>
+        <v>0.6208640918820814</v>
       </c>
       <c r="AK8">
-        <v>-0.7894845107283921</v>
+        <v>0.6666871392583099</v>
       </c>
       <c r="AL8">
-        <v>-4.97731983308966</v>
+        <v>0.8769229157207086</v>
       </c>
       <c r="AM8">
-        <v>2.311647954026918</v>
+        <v>-1.279075352466956</v>
       </c>
       <c r="AN8">
-        <v>4.75185668384593</v>
+        <v>0.7477836088508186</v>
       </c>
       <c r="AO8">
-        <v>0.04464879837478363</v>
+        <v>0.04907772065413754</v>
       </c>
       <c r="AP8">
-        <v>6.71944</v>
+        <v>9.16042</v>
       </c>
       <c r="AQ8">
-        <v>6.704341462783908</v>
+        <v>9.145792457271199</v>
       </c>
       <c r="AR8">
-        <v>6.742525149058838</v>
+        <v>8.987387874896811</v>
       </c>
       <c r="AS8">
-        <v>6.71944</v>
+        <v>9.16042</v>
       </c>
       <c r="AT8">
-        <v>6.666679999999999</v>
+        <v>9.30175</v>
       </c>
       <c r="AU8">
-        <v>6.704341462783908</v>
+        <v>9.145792457271199</v>
       </c>
       <c r="AV8">
-        <v>6.747365</v>
+        <v>9.243210000000001</v>
       </c>
       <c r="AW8">
-        <v>-0.002246993382795475</v>
+        <v>-0.001596820094362638</v>
       </c>
       <c r="AX8">
-        <v>0.5406817266281466</v>
+        <v>0.1766824825317234</v>
       </c>
       <c r="AY8">
-        <v>0.002246993382795475</v>
+        <v>0.001596820094362638</v>
       </c>
       <c r="AZ8">
-        <v>0.3574317292577109</v>
+        <v>0.4061925166299428</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.442568270742289</v>
+        <v>0.3938074833700572</v>
       </c>
       <c r="BC8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2527,58 +2527,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>500</v>
+        <v>425.5884024385907</v>
       </c>
       <c r="BG8">
-        <v>0.004155852273403799</v>
+        <v>0.009037795210263299</v>
       </c>
       <c r="BH8">
-        <v>120312.2649955219</v>
+        <v>55323.2274429278</v>
       </c>
       <c r="BI8">
-        <v>120312.2649955219</v>
+        <v>47089.84797036488</v>
       </c>
       <c r="BJ8">
-        <v>17905.10295434172</v>
+        <v>5140.57739387112</v>
       </c>
       <c r="BK8">
-        <v>1203.122649955219</v>
+        <v>470.8984797036488</v>
       </c>
       <c r="BL8">
-        <v>0.01203122649955219</v>
+        <v>0.004708984797036487</v>
       </c>
       <c r="BM8">
-        <v>500</v>
+        <v>425.5884024385907</v>
       </c>
       <c r="BN8">
-        <v>0.005</v>
+        <v>0.004255884024385907</v>
       </c>
       <c r="BO8">
-        <v>0.08477888734106553</v>
+        <v>0.09977306775028287</v>
       </c>
       <c r="BP8">
-        <v>0.01319435604094559</v>
+        <v>0.02510545486167899</v>
       </c>
       <c r="BQ8">
-        <v>0.01290237387631207</v>
+        <v>0.03592307066841621</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV8" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW8" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2586,7 +2586,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2601,151 +2601,151 @@
         <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J9" s="2">
         <v>46254</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.06621278626437836</v>
       </c>
       <c r="L9">
-        <v>0.8685446894451283</v>
+        <v>1.637136906626681</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O9" t="s">
         <v>95</v>
       </c>
       <c r="P9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.7665531965660946</v>
       </c>
       <c r="R9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="S9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="T9">
-        <v>0.6831823310055514</v>
+        <v>-0.9844460133251428</v>
       </c>
       <c r="U9">
-        <v>0.7074302466322477</v>
+        <v>0.8520339916907844</v>
       </c>
       <c r="V9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="W9" t="s">
+        <v>95</v>
+      </c>
+      <c r="X9">
+        <v>0.9964054710192536</v>
+      </c>
+      <c r="Y9">
+        <v>0.2791157243714534</v>
+      </c>
+      <c r="Z9">
+        <v>164.5765081209393</v>
+      </c>
+      <c r="AA9">
+        <v>11</v>
+      </c>
+      <c r="AB9">
+        <v>-0.9639864423678249</v>
+      </c>
+      <c r="AC9">
+        <v>0.2659513845254884</v>
+      </c>
+      <c r="AD9" t="s">
         <v>94</v>
       </c>
-      <c r="X9">
-        <v>0.9999927907189984</v>
-      </c>
-      <c r="Y9">
-        <v>0.6442016024401184</v>
-      </c>
-      <c r="Z9">
-        <v>66.10936809713229</v>
-      </c>
-      <c r="AA9">
-        <v>12</v>
-      </c>
-      <c r="AB9">
-        <v>0.4049920970587502</v>
-      </c>
-      <c r="AC9">
-        <v>0.9143201853398818</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>92</v>
-      </c>
       <c r="AE9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="AF9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AG9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AH9">
-        <v>0.3329419271905759</v>
+        <v>-0.6143089908878036</v>
       </c>
       <c r="AI9">
-        <v>0.7400069032371405</v>
+        <v>0.8375106535875269</v>
       </c>
       <c r="AJ9">
-        <v>0.7661801512332116</v>
+        <v>-1.400465121071157</v>
       </c>
       <c r="AK9">
-        <v>1.64323692369165</v>
+        <v>0.4294431392108509</v>
       </c>
       <c r="AL9">
-        <v>1.00420965457867</v>
+        <v>-1.313231770328659</v>
       </c>
       <c r="AM9">
-        <v>-1.246062843434765</v>
+        <v>3.33070689379288</v>
       </c>
       <c r="AN9">
-        <v>0.8743558278062863</v>
+        <v>1.084636112146913</v>
       </c>
       <c r="AO9">
-        <v>0.06885682080105154</v>
+        <v>0.04166892569233371</v>
       </c>
       <c r="AP9">
-        <v>7.8525</v>
+        <v>158.6705</v>
       </c>
       <c r="AQ9">
-        <v>7.8329110413689</v>
+        <v>158.4034210938131</v>
       </c>
       <c r="AR9">
-        <v>7.627851628018186</v>
+        <v>161.7525279532776</v>
       </c>
       <c r="AS9">
-        <v>7.8525</v>
+        <v>158.6705</v>
       </c>
       <c r="AT9">
-        <v>8.0077</v>
+        <v>153.709</v>
       </c>
       <c r="AU9">
-        <v>7.8329110413689</v>
+        <v>158.4034210938131</v>
       </c>
       <c r="AV9">
-        <v>7.913349999999999</v>
+        <v>159.834</v>
       </c>
       <c r="AW9">
-        <v>-0.002494614279668838</v>
+        <v>-0.001683229750879312</v>
       </c>
       <c r="AX9">
-        <v>0.321922081036972</v>
+        <v>0.2295478351412917</v>
       </c>
       <c r="AY9">
-        <v>0.002494614279668838</v>
+        <v>0.001683229750879312</v>
       </c>
       <c r="AZ9">
-        <v>0.3784377378823732</v>
+        <v>0.4602608600750335</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.4215622621176268</v>
+        <v>0.3397391399249665</v>
       </c>
       <c r="BC9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2754,58 +2754,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>500</v>
+        <v>383.2765982830473</v>
       </c>
       <c r="BG9">
-        <v>0.007749124482648762</v>
+        <v>0.007332806035148394</v>
       </c>
       <c r="BH9">
-        <v>64523.41824157829</v>
+        <v>68186.72110012814</v>
       </c>
       <c r="BI9">
-        <v>64523.41824157829</v>
+        <v>52268.74902266399</v>
       </c>
       <c r="BJ9">
-        <v>8216.926869350944</v>
+        <v>329.4169301959973</v>
       </c>
       <c r="BK9">
-        <v>645.2341824157828</v>
+        <v>522.68749022664</v>
       </c>
       <c r="BL9">
-        <v>0.006452341824157828</v>
+        <v>0.0052268749022664</v>
       </c>
       <c r="BM9">
-        <v>500</v>
+        <v>383.2765982830473</v>
       </c>
       <c r="BN9">
-        <v>0.005</v>
+        <v>0.003832765982830473</v>
       </c>
       <c r="BO9">
-        <v>0.1457973570517644</v>
+        <v>2.795547701258807</v>
       </c>
       <c r="BP9">
-        <v>0.02931881379040566</v>
+        <v>0.5568598907852828</v>
       </c>
       <c r="BQ9">
-        <v>0.03361060126143285</v>
+        <v>1.816119394291128</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW9" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2813,7 +2813,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2825,154 +2825,154 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="2">
         <v>46254</v>
       </c>
       <c r="K10">
-        <v>0.06621278626437836</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>1.637136906626681</v>
+        <v>0.07591293037768411</v>
       </c>
       <c r="M10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q10">
-        <v>0.7665531965660946</v>
+        <v>0.75</v>
       </c>
       <c r="R10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.9844460133251428</v>
+        <v>-0.4092036361630399</v>
       </c>
       <c r="U10">
-        <v>0.8520339916907844</v>
+        <v>0.5590639223686202</v>
       </c>
       <c r="V10" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="W10" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="X10">
-        <v>0.9964054710192536</v>
+        <v>0.9996891443810091</v>
       </c>
       <c r="Y10">
-        <v>0.2791157243714534</v>
+        <v>0.9943494743949133</v>
       </c>
       <c r="Z10">
-        <v>164.5765081209393</v>
+        <v>-92.34697423853162</v>
       </c>
       <c r="AA10">
-        <v>11</v>
+        <v>-7.999999999999998</v>
       </c>
       <c r="AB10">
-        <v>-0.9639864423678249</v>
+        <v>-0.04095097359994582</v>
       </c>
       <c r="AC10">
-        <v>0.2659513845254884</v>
+        <v>-0.9991611570518625</v>
       </c>
       <c r="AD10" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="AE10" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH10">
-        <v>-0.6143089908878036</v>
+        <v>-0.04082258246240339</v>
       </c>
       <c r="AI10">
-        <v>0.8375106535875269</v>
+        <v>0.6547500567402622</v>
       </c>
       <c r="AJ10">
-        <v>-1.400465121071157</v>
+        <v>-0.05214664521845188</v>
       </c>
       <c r="AK10">
-        <v>0.4294431392108509</v>
+        <v>-1.643112663229438</v>
       </c>
       <c r="AL10">
-        <v>-1.313231770328659</v>
+        <v>-0.5445606754256364</v>
       </c>
       <c r="AM10">
-        <v>3.33070689379288</v>
+        <v>-1.72515865826341</v>
       </c>
       <c r="AN10">
-        <v>1.084636112146913</v>
+        <v>0.6707493927570177</v>
       </c>
       <c r="AO10">
-        <v>0.04166892569233371</v>
+        <v>0.3753088716803816</v>
       </c>
       <c r="AP10">
-        <v>158.6705</v>
+        <v>0.79914</v>
       </c>
       <c r="AQ10">
-        <v>158.2067588046467</v>
+        <v>0.7968270912239529</v>
       </c>
       <c r="AR10">
-        <v>161.3252435451827</v>
+        <v>0.8084356885907533</v>
       </c>
       <c r="AS10">
-        <v>158.6705</v>
+        <v>0.79914</v>
       </c>
       <c r="AT10">
-        <v>153.709</v>
+        <v>0.782095</v>
       </c>
       <c r="AU10">
-        <v>158.2067588046467</v>
+        <v>0.7968270912239529</v>
       </c>
       <c r="AV10">
-        <v>159.834</v>
+        <v>0.809175</v>
       </c>
       <c r="AW10">
-        <v>-0.002922668015499373</v>
+        <v>-0.002894247285891161</v>
       </c>
       <c r="AX10">
-        <v>0.3985742976822415</v>
+        <v>0.2304841829643313</v>
       </c>
       <c r="AY10">
-        <v>0.002922668015499373</v>
+        <v>0.002894247285891161</v>
       </c>
       <c r="AZ10">
-        <v>0.4602608600750335</v>
+        <v>0.4298707372413849</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3397391399249665</v>
+        <v>0.3701292627586151</v>
       </c>
       <c r="BC10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2981,58 +2981,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>383.2765982830473</v>
+        <v>375</v>
       </c>
       <c r="BG10">
-        <v>0.007332806035148394</v>
+        <v>0.01255724904272091</v>
       </c>
       <c r="BH10">
-        <v>68186.72110012814</v>
+        <v>39817.6382660688</v>
       </c>
       <c r="BI10">
-        <v>52268.74902266399</v>
+        <v>29863.2286995516</v>
       </c>
       <c r="BJ10">
-        <v>329.4169301959973</v>
+        <v>37369.20777279526</v>
       </c>
       <c r="BK10">
-        <v>522.68749022664</v>
+        <v>298.632286995516</v>
       </c>
       <c r="BL10">
-        <v>0.0052268749022664</v>
+        <v>0.00298632286995516</v>
       </c>
       <c r="BM10">
-        <v>383.2765982830473</v>
+        <v>375.0000000000001</v>
       </c>
       <c r="BN10">
-        <v>0.003832765982830473</v>
+        <v>0.003750000000000001</v>
       </c>
       <c r="BO10">
-        <v>2.795547701258807</v>
+        <v>0.01890071132597321</v>
       </c>
       <c r="BP10">
-        <v>0.5568598907852828</v>
+        <v>0.007966138826463194</v>
       </c>
       <c r="BQ10">
-        <v>1.816119394291128</v>
+        <v>0.01079946229767044</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW10" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3040,7 +3040,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3052,154 +3052,154 @@
         <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="2">
         <v>46254</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0.07591293037768411</v>
+        <v>3.672976609750829</v>
       </c>
       <c r="M11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
+        <v>95</v>
+      </c>
+      <c r="P11" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>102</v>
+      </c>
+      <c r="S11" t="s">
+        <v>105</v>
+      </c>
+      <c r="T11">
+        <v>-0.9773777765031695</v>
+      </c>
+      <c r="U11">
+        <v>0.9897677588998222</v>
+      </c>
+      <c r="V11" t="s">
         <v>94</v>
       </c>
-      <c r="P11" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q11">
-        <v>0.75</v>
-      </c>
-      <c r="R11" t="s">
-        <v>99</v>
-      </c>
-      <c r="S11" t="s">
-        <v>102</v>
-      </c>
-      <c r="T11">
-        <v>-0.4092036361630399</v>
-      </c>
-      <c r="U11">
-        <v>0.5590639223686202</v>
-      </c>
-      <c r="V11" t="s">
-        <v>104</v>
-      </c>
       <c r="W11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="X11">
-        <v>0.9996891443810091</v>
+        <v>0.9997910378935834</v>
       </c>
       <c r="Y11">
-        <v>0.9943494743949133</v>
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>-92.34697423853162</v>
+        <v>-162.6980782645607</v>
       </c>
       <c r="AA11">
-        <v>-7.999999999999998</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>-0.04095097359994582</v>
+        <v>-0.9547508248308558</v>
       </c>
       <c r="AC11">
-        <v>-0.9991611570518625</v>
+        <v>-0.2974068971708632</v>
       </c>
       <c r="AD11" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="AE11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AH11">
-        <v>-0.04082258246240339</v>
+        <v>-0.9545513180873961</v>
       </c>
       <c r="AI11">
-        <v>0.6547500567402622</v>
+        <v>0.9796547909557933</v>
       </c>
       <c r="AJ11">
-        <v>-0.05214664521845188</v>
+        <v>-2.692407542451325</v>
       </c>
       <c r="AK11">
-        <v>-1.643112663229438</v>
+        <v>-0.7894845107283921</v>
       </c>
       <c r="AL11">
-        <v>-0.5445606754256364</v>
+        <v>-4.97731983308966</v>
       </c>
       <c r="AM11">
-        <v>-1.72515865826341</v>
+        <v>2.311647954026918</v>
       </c>
       <c r="AN11">
-        <v>0.6707493927570177</v>
+        <v>4.75185668384593</v>
       </c>
       <c r="AO11">
-        <v>0.3753088716803816</v>
+        <v>0.04464879837478363</v>
       </c>
       <c r="AP11">
-        <v>0.79914</v>
+        <v>6.71944</v>
       </c>
       <c r="AQ11">
-        <v>0.7893697760435053</v>
+        <v>6.684035560918689</v>
       </c>
       <c r="AR11">
-        <v>0.7910878802046709</v>
+        <v>6.685714574610426</v>
       </c>
       <c r="AS11">
-        <v>0.79914</v>
+        <v>6.71944</v>
       </c>
       <c r="AT11">
-        <v>0.782095</v>
+        <v>6.666679999999999</v>
       </c>
       <c r="AU11">
-        <v>0.7893697760435053</v>
+        <v>6.684035560918689</v>
       </c>
       <c r="AV11">
-        <v>0.809175</v>
+        <v>6.747365</v>
       </c>
       <c r="AW11">
-        <v>-0.01222592281264188</v>
+        <v>-0.005268956800166477</v>
       </c>
       <c r="AX11">
-        <v>0.9736147440453053</v>
+        <v>1.267840253583173</v>
       </c>
       <c r="AY11">
-        <v>0.01222592281264188</v>
+        <v>0.005268956800166477</v>
       </c>
       <c r="AZ11">
-        <v>0.4298707372413849</v>
+        <v>0.3574317292577109</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.3701292627586151</v>
+        <v>0.442568270742289</v>
       </c>
       <c r="BC11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3208,58 +3208,58 @@
         <v>100</v>
       </c>
       <c r="BF11">
-        <v>375</v>
+        <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.01255724904272091</v>
+        <v>0.004155852273403799</v>
       </c>
       <c r="BH11">
-        <v>39817.6382660688</v>
+        <v>120312.2649955219</v>
       </c>
       <c r="BI11">
-        <v>29863.2286995516</v>
+        <v>120312.2649955219</v>
       </c>
       <c r="BJ11">
-        <v>37369.20777279526</v>
+        <v>17905.10295434172</v>
       </c>
       <c r="BK11">
-        <v>298.632286995516</v>
+        <v>1203.122649955219</v>
       </c>
       <c r="BL11">
-        <v>0.00298632286995516</v>
+        <v>0.01203122649955219</v>
       </c>
       <c r="BM11">
-        <v>375.0000000000001</v>
+        <v>500</v>
       </c>
       <c r="BN11">
-        <v>0.003750000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.01890071132597321</v>
+        <v>0.08477888734106553</v>
       </c>
       <c r="BP11">
-        <v>0.007966138826463194</v>
+        <v>0.01319435604094559</v>
       </c>
       <c r="BQ11">
-        <v>0.01079946229767044</v>
+        <v>0.01290237387631207</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.0525449049327628</v>
+        <v>0.04339094579361392</v>
       </c>
       <c r="BT11" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="BU11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BW11" s="2">
-        <v>46283</v>
+        <v>46284</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="134">
   <si>
     <t>Pair</t>
   </si>
@@ -241,6 +241,9 @@
     <t>ValidUntil</t>
   </si>
   <si>
+    <t>USDJPY</t>
+  </si>
+  <si>
     <t>GBPUSD</t>
   </si>
   <si>
@@ -259,15 +262,12 @@
     <t>EURUSD</t>
   </si>
   <si>
+    <t>USDCHF</t>
+  </si>
+  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>USDJPY</t>
-  </si>
-  <si>
-    <t>USDCHF</t>
-  </si>
-  <si>
     <t>USDCNH</t>
   </si>
   <si>
@@ -295,42 +295,45 @@
     <t>SHORT</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
+    <t>CONFLICT</t>
   </si>
   <si>
     <t>ALIGNED</t>
   </si>
   <si>
-    <t>CONFLICT</t>
-  </si>
-  <si>
     <t>NO_SIGNAL</t>
   </si>
   <si>
+    <t>BLOCK_STRONG_CONFLICT</t>
+  </si>
+  <si>
     <t>CONFIRM</t>
   </si>
   <si>
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
     <t>UP_ACCELERATING</t>
   </si>
   <si>
-    <t>DOWN_DECELERATING</t>
-  </si>
-  <si>
     <t>DOWN_ACCELERATING</t>
   </si>
   <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
     <t>多头加速</t>
   </si>
   <si>
-    <t>空头减速</t>
-  </si>
-  <si>
     <t>空头加速</t>
   </si>
   <si>
@@ -340,67 +343,67 @@
     <t>TRANSITION</t>
   </si>
   <si>
+    <t>下跌</t>
+  </si>
+  <si>
     <t>上涨</t>
   </si>
   <si>
-    <t>下跌</t>
-  </si>
-  <si>
     <t>转换</t>
   </si>
   <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
     <t>UP_STEEPENING</t>
   </si>
   <si>
-    <t>DOWN_VALLEY_FLATTENING</t>
-  </si>
-  <si>
     <t>TRANSITION_ZONE</t>
   </si>
   <si>
     <t>DOWN_STEEPENING</t>
   </si>
   <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
     <t>上升陡坡形成</t>
   </si>
   <si>
-    <t>下降谷底收敛</t>
-  </si>
-  <si>
     <t>地形转换区</t>
   </si>
   <si>
     <t>下降陡坡形成</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.02071,naive=0.007171,drift4=0.007376; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=drift4; scores=model=185.7,naive=145.2,drift4=135.5; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=drift4; scores=model=0.0109,naive=0.004963,drift4=0.004; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.05464,naive=0.02473,drift4=0.02191; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1412,naive=0.02646,drift4=0.03148; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=0.02451,naive=0.007486,drift4=0.007284; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.09977,naive=0.02511,drift4=0.03592; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=2.796,naive=0.5569,drift4=1.816; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.0189,naive=0.007966,drift4=0.0108; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=drift4; scores=model=0.08478,naive=0.01319,drift4=0.0129; naive_cap_applied</t>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.47,naive=0.20,drift4=0.33); metric_best=naive; scores=model=2.29,naive=0.3508,drift4=1.586; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=naive; scores=model=0.01794,naive=0.00504,drift4=0.006389; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.46,naive=0.20,drift4=0.34); metric_best=naive; scores=model=144.2,naive=134.3,drift4=137.3; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.009901,naive=0.004209,drift4=0.003855; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.40,naive=0.20,drift4=0.40); metric_best=drift4; scores=model=0.05476,naive=0.02287,drift4=0.02286; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.1386,naive=0.02463,drift4=0.03364; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.39,naive=0.20,drift4=0.41); metric_best=naive; scores=model=0.02268,naive=0.005664,drift4=0.006527; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.01809,naive=0.006239,drift4=0.008898; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.09802,naive=0.02139,drift4=0.03565; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.20,drift4=0.44); metric_best=naive; scores=model=0.07718,naive=0.01184,drift4=0.01251; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -1009,7 +1012,7 @@
         <v>75</v>
       </c>
       <c r="B2" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1033,13 +1036,13 @@
         <v>93</v>
       </c>
       <c r="J2" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>2.799788928978186</v>
+        <v>1.573807635651196</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -1057,109 +1060,109 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T2">
-        <v>0.9038103801512347</v>
+        <v>-0.9908003157508283</v>
       </c>
       <c r="U2">
-        <v>0.9567110974963017</v>
+        <v>0.8452581329310004</v>
       </c>
       <c r="V2" t="s">
         <v>93</v>
       </c>
       <c r="W2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X2">
-        <v>0.9999857057129841</v>
+        <v>0.9975919633725104</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0.2007326519985159</v>
       </c>
       <c r="Z2">
-        <v>36.13601322557214</v>
+        <v>167.9168621547007</v>
       </c>
       <c r="AA2">
-        <v>6.000000000000009</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="AB2">
-        <v>0.807619385320781</v>
+        <v>-0.9778448851814655</v>
       </c>
       <c r="AC2">
-        <v>0.5897041024565488</v>
+        <v>0.2093307921077227</v>
       </c>
       <c r="AD2" t="s">
         <v>93</v>
       </c>
       <c r="AE2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AH2">
-        <v>0.8076078409774876</v>
+        <v>-0.585651466751039</v>
       </c>
       <c r="AI2">
-        <v>0.9348738201194033</v>
+        <v>0.8265887448728856</v>
       </c>
       <c r="AJ2">
-        <v>2.113288595471767</v>
+        <v>-1.363355026066289</v>
       </c>
       <c r="AK2">
-        <v>1.508310092799069</v>
+        <v>0.3486837527031618</v>
       </c>
       <c r="AL2">
-        <v>3.519860679519747</v>
+        <v>-1.191627563071416</v>
       </c>
       <c r="AM2">
-        <v>-2.75011321001353</v>
+        <v>3.547809695379906</v>
       </c>
       <c r="AN2">
-        <v>3.240920255412093</v>
+        <v>0.9370187811729748</v>
       </c>
       <c r="AO2">
-        <v>0.04937994984250294</v>
+        <v>0.0404562550775729</v>
       </c>
       <c r="AP2">
-        <v>1.36555</v>
+        <v>159.0115</v>
       </c>
       <c r="AQ2">
-        <v>1.366496174145982</v>
+        <v>158.9054197671131</v>
       </c>
       <c r="AR2">
-        <v>1.336083774598892</v>
+        <v>162.0060370312414</v>
       </c>
       <c r="AS2">
-        <v>1.36555</v>
+        <v>159.0115</v>
       </c>
       <c r="AT2">
-        <v>1.39653</v>
+        <v>154.391</v>
       </c>
       <c r="AW2">
-        <v>0.0006928886865964252</v>
+        <v>-0.000667123024981726</v>
       </c>
       <c r="AY2">
-        <v>0.0006928886865964252</v>
+        <v>0.000667123024981726</v>
       </c>
       <c r="AZ2">
-        <v>0.3943641756922918</v>
+        <v>0.4714776503887586</v>
       </c>
       <c r="BA2">
         <v>0.2</v>
       </c>
       <c r="BB2">
-        <v>0.4056358243077082</v>
+        <v>0.3285223496112414</v>
       </c>
       <c r="BC2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BD2">
         <v>100000</v>
@@ -1192,31 +1195,31 @@
         <v>0</v>
       </c>
       <c r="BO2">
-        <v>0.02070822257070009</v>
+        <v>2.289837561270624</v>
       </c>
       <c r="BP2">
-        <v>0.007171322759006341</v>
+        <v>0.3507768553407175</v>
       </c>
       <c r="BQ2">
-        <v>0.007375623821229548</v>
+        <v>1.586263327863231</v>
       </c>
       <c r="BR2">
         <v>1</v>
       </c>
       <c r="BS2">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BU2" t="s">
         <v>90</v>
       </c>
       <c r="BV2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="BW2" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1224,7 +1227,7 @@
         <v>76</v>
       </c>
       <c r="B3" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1239,28 +1242,28 @@
         <v>87</v>
       </c>
       <c r="G3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>1.842550331079064</v>
+        <v>3.10617716041243</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O3" t="s">
         <v>95</v>
@@ -1269,121 +1272,112 @@
         <v>98</v>
       </c>
       <c r="Q3">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T3">
-        <v>0.8739244504506468</v>
+        <v>0.9099541647101644</v>
       </c>
       <c r="U3">
-        <v>0.7932067133357139</v>
+        <v>0.9594784291707591</v>
       </c>
       <c r="V3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X3">
-        <v>0.9997628425316913</v>
+        <v>0.9999962202047404</v>
       </c>
       <c r="Y3">
-        <v>0.5359779605829512</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>41.2324549124319</v>
+        <v>34.92441583398459</v>
       </c>
       <c r="AA3">
-        <v>-3.000000000000004</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AB3">
-        <v>0.7520416768015612</v>
+        <v>0.8199079890642212</v>
       </c>
       <c r="AC3">
-        <v>0.6591155561458827</v>
+        <v>0.5724953182941017</v>
       </c>
       <c r="AD3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH3">
-        <v>0.5774227479024108</v>
+        <v>0.8199048899798909</v>
       </c>
       <c r="AI3">
-        <v>0.824966669233184</v>
+        <v>0.9391305050586733</v>
       </c>
       <c r="AJ3">
-        <v>1.441282703672705</v>
+        <v>2.384313109767851</v>
       </c>
       <c r="AK3">
-        <v>1.279701112861722</v>
+        <v>1.637783569956673</v>
       </c>
       <c r="AL3">
-        <v>2.082580962013676</v>
+        <v>3.747594584664606</v>
       </c>
       <c r="AM3">
-        <v>-2.390018558409804</v>
+        <v>-4.01477573440989</v>
       </c>
       <c r="AN3">
-        <v>1.855837817997649</v>
+        <v>3.344969589891187</v>
       </c>
       <c r="AO3">
-        <v>0.0517228053997773</v>
+        <v>0.0456037915483485</v>
       </c>
       <c r="AP3">
-        <v>4595.98</v>
+        <v>1.362695</v>
       </c>
       <c r="AQ3">
-        <v>4758.902063072866</v>
+        <v>1.361274060729326</v>
       </c>
       <c r="AR3">
-        <v>4515.638827442995</v>
+        <v>1.331217628946483</v>
       </c>
       <c r="AS3">
-        <v>4595.98</v>
+        <v>1.362695</v>
       </c>
       <c r="AT3">
-        <v>5146.07</v>
-      </c>
-      <c r="AU3">
-        <v>4758.902063072866</v>
-      </c>
-      <c r="AV3">
-        <v>4446.965</v>
+        <v>1.39082</v>
       </c>
       <c r="AW3">
-        <v>0.03544881898373491</v>
-      </c>
-      <c r="AX3">
-        <v>1.093326598482477</v>
+        <v>-0.001042741971368252</v>
       </c>
       <c r="AY3">
-        <v>0.03544881898373491</v>
+        <v>0.001042741971368252</v>
       </c>
       <c r="AZ3">
-        <v>0.4396196587218628</v>
+        <v>0.4013420749519329</v>
       </c>
       <c r="BA3">
         <v>0.2</v>
       </c>
       <c r="BB3">
-        <v>0.3603803412781372</v>
+        <v>0.3986579250480671</v>
       </c>
       <c r="BC3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BD3">
         <v>100000</v>
@@ -1392,58 +1386,55 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>375</v>
-      </c>
-      <c r="BG3">
-        <v>0.03242290001261965</v>
+        <v>0</v>
       </c>
       <c r="BH3">
-        <v>15421.19920813344</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>11565.89940610008</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>2.51652518202866</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>115.6589940610008</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>0.001156589940610008</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>374.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>0.003749999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>185.6517557047789</v>
+        <v>0.01794303975491077</v>
       </c>
       <c r="BP3">
-        <v>145.180152494632</v>
+        <v>0.005040264734104203</v>
       </c>
       <c r="BQ3">
-        <v>135.4858129633054</v>
+        <v>0.006389382454054583</v>
       </c>
       <c r="BR3">
         <v>1</v>
       </c>
       <c r="BS3">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT3" t="s">
         <v>130</v>
       </c>
       <c r="BU3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BV3" t="s">
         <v>132</v>
       </c>
       <c r="BW3" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1451,7 +1442,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1463,7 +1454,7 @@
         <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
         <v>91</v>
@@ -1472,145 +1463,145 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J4" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K4">
-        <v>0.4236656675179737</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.77162634908774</v>
+        <v>2.154523023899989</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q4">
-        <v>0.8559164168794934</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T4">
-        <v>0.8848405598661534</v>
+        <v>0.836488345692881</v>
       </c>
       <c r="U4">
-        <v>0.8617267344551464</v>
+        <v>0.7763963424495952</v>
       </c>
       <c r="V4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X4">
-        <v>0.9999945295507252</v>
+        <v>0.9999063475511949</v>
       </c>
       <c r="Y4">
-        <v>0.728906953090797</v>
+        <v>0.9489870167833568</v>
       </c>
       <c r="Z4">
-        <v>39.53535493000027</v>
+        <v>43.75347121801627</v>
       </c>
       <c r="AA4">
-        <v>6.999999999999997</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB4">
-        <v>0.77123193812414</v>
+        <v>0.7223220659802616</v>
       </c>
       <c r="AC4">
-        <v>0.6365542377655518</v>
+        <v>0.6915568183439497</v>
       </c>
       <c r="AD4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH4">
-        <v>0.6666904830178377</v>
+        <v>0.7038322424790375</v>
       </c>
       <c r="AI4">
-        <v>0.8695223443438814</v>
+        <v>0.8986964526771742</v>
       </c>
       <c r="AJ4">
-        <v>1.354231212924323</v>
+        <v>1.67578244994257</v>
       </c>
       <c r="AK4">
-        <v>1.088437348502598</v>
+        <v>1.585326491145277</v>
       </c>
       <c r="AL4">
-        <v>2.132516225977054</v>
+        <v>2.481956224500641</v>
       </c>
       <c r="AM4">
-        <v>-1.543205890574448</v>
+        <v>-2.763643596638051</v>
       </c>
       <c r="AN4">
-        <v>1.990644408001752</v>
+        <v>2.211343105636636</v>
       </c>
       <c r="AO4">
-        <v>0.05084475369515897</v>
+        <v>0.05176528077662528</v>
       </c>
       <c r="AP4">
-        <v>0.71668</v>
+        <v>4608.219999999999</v>
       </c>
       <c r="AQ4">
-        <v>0.7232428738892167</v>
+        <v>4760.530292443389</v>
       </c>
       <c r="AR4">
-        <v>0.7161148688152355</v>
+        <v>4526.63647771073</v>
       </c>
       <c r="AS4">
-        <v>0.71668</v>
+        <v>4608.219999999999</v>
       </c>
       <c r="AT4">
-        <v>0.7331749999999999</v>
+        <v>5170.549999999999</v>
       </c>
       <c r="AU4">
-        <v>0.7232428738892167</v>
+        <v>4760.530292443389</v>
       </c>
       <c r="AV4">
-        <v>0.708305</v>
+        <v>4459.205</v>
       </c>
       <c r="AW4">
-        <v>0.009157328081175316</v>
+        <v>0.03305187088363614</v>
       </c>
       <c r="AX4">
-        <v>0.7836267330408035</v>
+        <v>1.022113830442506</v>
       </c>
       <c r="AY4">
-        <v>0.009157328081175316</v>
+        <v>0.03305187088363614</v>
       </c>
       <c r="AZ4">
-        <v>0.388808622802798</v>
+        <v>0.4621019706166982</v>
       </c>
       <c r="BA4">
         <v>0.2</v>
       </c>
       <c r="BB4">
-        <v>0.411191377197202</v>
+        <v>0.3378980293833018</v>
       </c>
       <c r="BC4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BD4">
         <v>100000</v>
@@ -1619,58 +1610,58 @@
         <v>100</v>
       </c>
       <c r="BF4">
-        <v>427.9582084397467</v>
+        <v>375</v>
       </c>
       <c r="BG4">
-        <v>0.01168582910085393</v>
+        <v>0.03233678079605567</v>
       </c>
       <c r="BH4">
-        <v>42786.86567164182</v>
+        <v>15462.26889910415</v>
       </c>
       <c r="BI4">
-        <v>36621.98075517586</v>
+        <v>11596.70167432811</v>
       </c>
       <c r="BJ4">
-        <v>51099.48757489516</v>
+        <v>2.516525182028661</v>
       </c>
       <c r="BK4">
-        <v>366.2198075517587</v>
+        <v>115.9670167432811</v>
       </c>
       <c r="BL4">
-        <v>0.003662198075517587</v>
+        <v>0.001159670167432811</v>
       </c>
       <c r="BM4">
-        <v>427.9582084397467</v>
+        <v>375</v>
       </c>
       <c r="BN4">
-        <v>0.004279582084397467</v>
+        <v>0.00375</v>
       </c>
       <c r="BO4">
-        <v>0.01090118721268276</v>
+        <v>144.2196092804531</v>
       </c>
       <c r="BP4">
-        <v>0.004963073343992102</v>
+        <v>134.2858519946211</v>
       </c>
       <c r="BQ4">
-        <v>0.003999580815931342</v>
+        <v>137.2939584678612</v>
       </c>
       <c r="BR4">
         <v>1</v>
       </c>
       <c r="BS4">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU4" t="s">
         <v>91</v>
       </c>
       <c r="BV4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW4" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1678,7 +1669,7 @@
         <v>78</v>
       </c>
       <c r="B5" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -1699,145 +1690,145 @@
         <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2">
         <v>46255</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>0.87856591911644</v>
       </c>
       <c r="L5">
-        <v>0.6856766544182692</v>
+        <v>2.15866004106353</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q5">
-        <v>0.75</v>
+        <v>0.96964147977911</v>
       </c>
       <c r="R5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T5">
-        <v>0.8229077268110704</v>
+        <v>0.8752482801329587</v>
       </c>
       <c r="U5">
-        <v>0.7703033444583698</v>
+        <v>0.9256442855531559</v>
       </c>
       <c r="V5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X5">
-        <v>0.9999794695735529</v>
+        <v>0.9999906865034341</v>
       </c>
       <c r="Y5">
-        <v>0.3037884302855449</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>52.80314866724348</v>
+        <v>40.93801375300145</v>
       </c>
       <c r="AA5">
         <v>6.999999999999997</v>
       </c>
       <c r="AB5">
-        <v>0.6045553409580938</v>
+        <v>0.7554189051286716</v>
       </c>
       <c r="AC5">
-        <v>0.7965631423302505</v>
+        <v>0.6552421520126731</v>
       </c>
       <c r="AD5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH5">
-        <v>0.3940980383373436</v>
+        <v>0.7554118695372929</v>
       </c>
       <c r="AI5">
-        <v>0.7339695153069584</v>
+        <v>0.9190808892033182</v>
       </c>
       <c r="AJ5">
-        <v>0.5415463540732421</v>
+        <v>1.653227085011985</v>
       </c>
       <c r="AK5">
-        <v>0.6936543499988544</v>
+        <v>1.396831106070048</v>
       </c>
       <c r="AL5">
-        <v>0.7457365964217691</v>
+        <v>2.594682880768611</v>
       </c>
       <c r="AM5">
-        <v>-0.8341788638886329</v>
+        <v>-2.176128171011526</v>
       </c>
       <c r="AN5">
-        <v>0.6672754744244622</v>
+        <v>2.382795644339242</v>
       </c>
       <c r="AO5">
-        <v>0.05431724925548111</v>
+        <v>0.05027681740990086</v>
       </c>
       <c r="AP5">
-        <v>4.81707</v>
+        <v>0.7159249999999999</v>
       </c>
       <c r="AQ5">
-        <v>4.852868531473597</v>
+        <v>0.7216130710944829</v>
       </c>
       <c r="AR5">
-        <v>4.814635544571294</v>
+        <v>0.7142262237544867</v>
       </c>
       <c r="AS5">
-        <v>4.81707</v>
+        <v>0.7159249999999999</v>
       </c>
       <c r="AT5">
-        <v>4.90824</v>
+        <v>0.7316649999999998</v>
       </c>
       <c r="AU5">
-        <v>4.852868531473597</v>
+        <v>0.7216130710944829</v>
       </c>
       <c r="AV5">
-        <v>4.77727</v>
+        <v>0.7077887499999999</v>
       </c>
       <c r="AW5">
-        <v>0.007431598767216682</v>
+        <v>0.007945065606708795</v>
       </c>
       <c r="AX5">
-        <v>0.8994605897888546</v>
+        <v>0.6991023007507102</v>
       </c>
       <c r="AY5">
-        <v>0.007431598767216682</v>
+        <v>0.007945065606708795</v>
       </c>
       <c r="AZ5">
-        <v>0.3967489405959904</v>
+        <v>0.3958952628509871</v>
       </c>
       <c r="BA5">
         <v>0.2</v>
       </c>
       <c r="BB5">
-        <v>0.4032510594040097</v>
+        <v>0.404104737149013</v>
       </c>
       <c r="BC5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BD5">
         <v>100000</v>
@@ -1846,58 +1837,58 @@
         <v>100</v>
       </c>
       <c r="BF5">
-        <v>375</v>
+        <v>484.820739889555</v>
       </c>
       <c r="BG5">
-        <v>0.008262283919478034</v>
+        <v>0.01136466808674099</v>
       </c>
       <c r="BH5">
-        <v>60515.95477386926</v>
+        <v>43996.00553080328</v>
       </c>
       <c r="BI5">
-        <v>45386.96608040195</v>
+        <v>42660.351907258</v>
       </c>
       <c r="BJ5">
-        <v>9422.110552763806</v>
+        <v>59587.7388095932</v>
       </c>
       <c r="BK5">
-        <v>453.8696608040195</v>
+        <v>426.60351907258</v>
       </c>
       <c r="BL5">
-        <v>0.004538696608040195</v>
+        <v>0.0042660351907258</v>
       </c>
       <c r="BM5">
-        <v>375</v>
+        <v>484.8207398895549</v>
       </c>
       <c r="BN5">
-        <v>0.00375</v>
+        <v>0.004848207398895549</v>
       </c>
       <c r="BO5">
-        <v>0.05464128401302773</v>
+        <v>0.009900553367894502</v>
       </c>
       <c r="BP5">
-        <v>0.02472564932138134</v>
+        <v>0.00420936313200217</v>
       </c>
       <c r="BQ5">
-        <v>0.02191173550814567</v>
+        <v>0.003854821946595356</v>
       </c>
       <c r="BR5">
         <v>1</v>
       </c>
       <c r="BS5">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU5" t="s">
         <v>91</v>
       </c>
       <c r="BV5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW5" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1905,7 +1896,7 @@
         <v>79</v>
       </c>
       <c r="B6" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -1926,7 +1917,7 @@
         <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J6" s="2">
         <v>46255</v>
@@ -1935,136 +1926,136 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1.063070255311046</v>
+        <v>0.6856766544182692</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q6">
         <v>0.75</v>
       </c>
       <c r="R6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T6">
-        <v>0.7103445297546604</v>
+        <v>0.8229077268110704</v>
       </c>
       <c r="U6">
-        <v>0.7196531592295451</v>
+        <v>0.7703033444583698</v>
       </c>
       <c r="V6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X6">
-        <v>0.9999924833597915</v>
+        <v>0.9999794695735529</v>
       </c>
       <c r="Y6">
-        <v>0.6711414810589248</v>
+        <v>0.3037884302855449</v>
       </c>
       <c r="Z6">
-        <v>62.50512399006986</v>
+        <v>52.80314866724348</v>
       </c>
       <c r="AA6">
-        <v>11</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB6">
-        <v>0.461669285568499</v>
+        <v>0.6045553409580938</v>
       </c>
       <c r="AC6">
-        <v>0.8870521240393214</v>
+        <v>0.7965631423302505</v>
       </c>
       <c r="AD6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH6">
-        <v>0.3857544472229946</v>
+        <v>0.3940980383373436</v>
       </c>
       <c r="AI6">
-        <v>0.7638367478449776</v>
+        <v>0.7339695153069584</v>
       </c>
       <c r="AJ6">
-        <v>0.8802517176106891</v>
+        <v>0.5415463540732421</v>
       </c>
       <c r="AK6">
-        <v>1.60961567707343</v>
+        <v>0.6936543499988544</v>
       </c>
       <c r="AL6">
-        <v>1.052695289542354</v>
+        <v>0.7457365964217691</v>
       </c>
       <c r="AM6">
-        <v>-1.963087461817747</v>
+        <v>-0.8341788638886329</v>
       </c>
       <c r="AN6">
-        <v>0.8613929497502741</v>
+        <v>0.6672754744244622</v>
       </c>
       <c r="AO6">
-        <v>0.05926468808856026</v>
+        <v>0.05431724925548111</v>
       </c>
       <c r="AP6">
-        <v>7.8474</v>
+        <v>4.81707</v>
       </c>
       <c r="AQ6">
-        <v>7.898880647833577</v>
+        <v>4.852391262210171</v>
       </c>
       <c r="AR6">
-        <v>7.816395365733179</v>
+        <v>4.814788231867039</v>
       </c>
       <c r="AS6">
-        <v>7.8474</v>
+        <v>4.81707</v>
       </c>
       <c r="AT6">
-        <v>7.9975</v>
+        <v>4.90824</v>
       </c>
       <c r="AU6">
-        <v>7.898880647833577</v>
+        <v>4.852391262210171</v>
       </c>
       <c r="AV6">
-        <v>7.786550000000001</v>
+        <v>4.77727</v>
       </c>
       <c r="AW6">
-        <v>0.006560217120775894</v>
+        <v>0.007332520019466319</v>
       </c>
       <c r="AX6">
-        <v>0.8460254368706205</v>
+        <v>0.8874688997530294</v>
       </c>
       <c r="AY6">
-        <v>0.006560217120775894</v>
+        <v>0.007332520019466319</v>
       </c>
       <c r="AZ6">
-        <v>0.3787829750692961</v>
+        <v>0.4025042922281774</v>
       </c>
       <c r="BA6">
         <v>0.2</v>
       </c>
       <c r="BB6">
-        <v>0.421217024930704</v>
+        <v>0.3974957077718226</v>
       </c>
       <c r="BC6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BD6">
         <v>100000</v>
@@ -2076,22 +2067,22 @@
         <v>375</v>
       </c>
       <c r="BG6">
-        <v>0.007754160613706374</v>
+        <v>0.008262283919478034</v>
       </c>
       <c r="BH6">
-        <v>64481.51191454459</v>
+        <v>60515.95477386926</v>
       </c>
       <c r="BI6">
-        <v>48361.13393590844</v>
+        <v>45386.96608040195</v>
       </c>
       <c r="BJ6">
-        <v>6162.695152013207</v>
+        <v>9422.110552763806</v>
       </c>
       <c r="BK6">
-        <v>483.6113393590845</v>
+        <v>453.8696608040195</v>
       </c>
       <c r="BL6">
-        <v>0.004836113393590845</v>
+        <v>0.004538696608040195</v>
       </c>
       <c r="BM6">
         <v>375</v>
@@ -2100,31 +2091,31 @@
         <v>0.00375</v>
       </c>
       <c r="BO6">
-        <v>0.1411587024259356</v>
+        <v>0.05475756753976965</v>
       </c>
       <c r="BP6">
-        <v>0.02645611204324677</v>
+        <v>0.02286613350923267</v>
       </c>
       <c r="BQ6">
-        <v>0.03148490536551985</v>
+        <v>0.02285877795451473</v>
       </c>
       <c r="BR6">
         <v>1</v>
       </c>
       <c r="BS6">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU6" t="s">
         <v>91</v>
       </c>
       <c r="BV6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW6" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2132,7 +2123,7 @@
         <v>80</v>
       </c>
       <c r="B7" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -2144,7 +2135,7 @@
         <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
         <v>91</v>
@@ -2153,145 +2144,145 @@
         <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J7" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>2.559319104838145</v>
+        <v>1.063070255311046</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T7">
-        <v>0.8318112568274303</v>
+        <v>0.7103445297546604</v>
       </c>
       <c r="U7">
-        <v>0.9243073098068914</v>
+        <v>0.7196531592295451</v>
       </c>
       <c r="V7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X7">
-        <v>0.9999689769381911</v>
+        <v>0.9999924833597915</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.6711414810589248</v>
       </c>
       <c r="Z7">
-        <v>48.42366466301528</v>
+        <v>62.50512399006986</v>
       </c>
       <c r="AA7">
         <v>11</v>
       </c>
       <c r="AB7">
-        <v>0.6636172957632107</v>
+        <v>0.461669285568499</v>
       </c>
       <c r="AC7">
-        <v>0.7480722456848158</v>
+        <v>0.8870521240393214</v>
       </c>
       <c r="AD7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH7">
-        <v>0.6635967083228268</v>
+        <v>0.3857544472229946</v>
       </c>
       <c r="AI7">
-        <v>0.8907372185570044</v>
+        <v>0.7638367478449776</v>
       </c>
       <c r="AJ7">
-        <v>1.950892777410652</v>
+        <v>0.8802517176106891</v>
       </c>
       <c r="AK7">
-        <v>2.118073102677476</v>
+        <v>1.60961567707343</v>
       </c>
       <c r="AL7">
-        <v>3.108834761886927</v>
+        <v>1.052695289542354</v>
       </c>
       <c r="AM7">
-        <v>-2.378758064309582</v>
+        <v>-1.963087461817747</v>
       </c>
       <c r="AN7">
-        <v>2.868011158736149</v>
+        <v>0.8613929497502741</v>
       </c>
       <c r="AO7">
-        <v>0.05558074733550537</v>
+        <v>0.05926468808856026</v>
       </c>
       <c r="AP7">
-        <v>1.17016</v>
+        <v>7.8474</v>
       </c>
       <c r="AQ7">
-        <v>1.174049752683845</v>
+        <v>7.89663424660774</v>
       </c>
       <c r="AR7">
-        <v>1.146760126712504</v>
+        <v>7.814837626631428</v>
       </c>
       <c r="AS7">
-        <v>1.17016</v>
+        <v>7.8474</v>
       </c>
       <c r="AT7">
-        <v>1.20101</v>
+        <v>7.9975</v>
       </c>
       <c r="AU7">
-        <v>1.174049752683845</v>
+        <v>7.89663424660774</v>
       </c>
       <c r="AV7">
-        <v>1.15637375</v>
+        <v>7.786550000000001</v>
       </c>
       <c r="AW7">
-        <v>0.003324120362895059</v>
+        <v>0.006273956547103472</v>
       </c>
       <c r="AX7">
-        <v>0.2821472614993393</v>
+        <v>0.8091084076867752</v>
       </c>
       <c r="AY7">
-        <v>0.003324120362895059</v>
+        <v>0.006273956547103472</v>
       </c>
       <c r="AZ7">
-        <v>0.3832312603935049</v>
+        <v>0.3878508314862915</v>
       </c>
       <c r="BA7">
         <v>0.2</v>
       </c>
       <c r="BB7">
-        <v>0.4167687396064951</v>
+        <v>0.4121491685137084</v>
       </c>
       <c r="BC7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BD7">
         <v>100000</v>
@@ -2300,58 +2291,58 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BG7">
-        <v>0.01178150851165657</v>
+        <v>0.007754160613706374</v>
       </c>
       <c r="BH7">
-        <v>42439.38707045046</v>
+        <v>64481.51191454459</v>
       </c>
       <c r="BI7">
-        <v>42439.38707045046</v>
+        <v>48361.13393590844</v>
       </c>
       <c r="BJ7">
-        <v>36268.02067277164</v>
+        <v>6162.695152013207</v>
       </c>
       <c r="BK7">
-        <v>424.3938707045046</v>
+        <v>483.6113393590845</v>
       </c>
       <c r="BL7">
-        <v>0.004243938707045046</v>
+        <v>0.004836113393590845</v>
       </c>
       <c r="BM7">
-        <v>500</v>
+        <v>375</v>
       </c>
       <c r="BN7">
-        <v>0.005</v>
+        <v>0.00375</v>
       </c>
       <c r="BO7">
-        <v>0.02450828036901452</v>
+        <v>0.1386109871117193</v>
       </c>
       <c r="BP7">
-        <v>0.00748638850717295</v>
+        <v>0.02462940194042405</v>
       </c>
       <c r="BQ7">
-        <v>0.00728373871436286</v>
+        <v>0.03364399099312401</v>
       </c>
       <c r="BR7">
         <v>1</v>
       </c>
       <c r="BS7">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU7" t="s">
         <v>91</v>
       </c>
       <c r="BV7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW7" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2359,7 +2350,7 @@
         <v>81</v>
       </c>
       <c r="B8" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -2371,31 +2362,31 @@
         <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J8" s="2">
         <v>46255</v>
       </c>
       <c r="K8">
-        <v>0.1984309268304248</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0.7875694870461764</v>
+        <v>2.759804263225185</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O8" t="s">
         <v>96</v>
@@ -2404,121 +2395,121 @@
         <v>99</v>
       </c>
       <c r="Q8">
-        <v>0.8511768048771814</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="T8">
-        <v>0.8428938372814724</v>
+        <v>0.836991584791107</v>
       </c>
       <c r="U8">
-        <v>0.8090656441841318</v>
+        <v>0.9266418306489912</v>
       </c>
       <c r="V8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="W8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X8">
-        <v>0.9999951135316221</v>
+        <v>0.9999824699719719</v>
       </c>
       <c r="Y8">
-        <v>0.5210408549913357</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>47.60834027287718</v>
+        <v>47.62498444875057</v>
       </c>
       <c r="AA8">
-        <v>5.000000000000007</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>0.6741948870243686</v>
+        <v>0.6739803119900329</v>
       </c>
       <c r="AC8">
-        <v>0.7385534877787788</v>
+        <v>0.7387493073091966</v>
       </c>
       <c r="AD8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH8">
-        <v>0.5127364782123364</v>
+        <v>0.6739684970962734</v>
       </c>
       <c r="AI8">
-        <v>0.7991032687435249</v>
+        <v>0.894632281288783</v>
       </c>
       <c r="AJ8">
-        <v>0.6208640918820814</v>
+        <v>2.148241999209514</v>
       </c>
       <c r="AK8">
-        <v>0.6666871392583099</v>
+        <v>2.277277787354816</v>
       </c>
       <c r="AL8">
-        <v>0.8769229157207086</v>
+        <v>3.178570750260458</v>
       </c>
       <c r="AM8">
-        <v>-1.279075352466956</v>
+        <v>-3.697301711279223</v>
       </c>
       <c r="AN8">
-        <v>0.7477836088508186</v>
+        <v>2.80742433655606</v>
       </c>
       <c r="AO8">
-        <v>0.04907772065413754</v>
+        <v>0.05037117865611267</v>
       </c>
       <c r="AP8">
-        <v>9.16042</v>
+        <v>1.167495</v>
       </c>
       <c r="AQ8">
-        <v>9.145792457271199</v>
+        <v>1.169060410219256</v>
       </c>
       <c r="AR8">
-        <v>8.987387874896811</v>
+        <v>1.141578758664465</v>
       </c>
       <c r="AS8">
-        <v>9.16042</v>
+        <v>1.167495</v>
       </c>
       <c r="AT8">
-        <v>9.30175</v>
+        <v>1.19568</v>
       </c>
       <c r="AU8">
-        <v>9.145792457271199</v>
+        <v>1.1692462425</v>
       </c>
       <c r="AV8">
-        <v>9.243210000000001</v>
+        <v>1.154375</v>
       </c>
       <c r="AW8">
-        <v>-0.001596820094362638</v>
+        <v>0.001340828199911532</v>
       </c>
       <c r="AX8">
-        <v>0.1766824825317234</v>
+        <v>0.1334788490853656</v>
       </c>
       <c r="AY8">
-        <v>0.001596820094362638</v>
+        <v>0.001340828199911532</v>
       </c>
       <c r="AZ8">
-        <v>0.4061925166299428</v>
+        <v>0.3878393408870359</v>
       </c>
       <c r="BA8">
         <v>0.2</v>
       </c>
       <c r="BB8">
-        <v>0.3938074833700572</v>
+        <v>0.4121606591129641</v>
       </c>
       <c r="BC8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BD8">
         <v>100000</v>
@@ -2527,58 +2518,58 @@
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>425.5884024385907</v>
+        <v>500</v>
       </c>
       <c r="BG8">
-        <v>0.009037795210263299</v>
+        <v>0.01123773549351391</v>
       </c>
       <c r="BH8">
-        <v>55323.2274429278</v>
+        <v>44492.94969512188</v>
       </c>
       <c r="BI8">
-        <v>47089.84797036488</v>
+        <v>44492.94969512188</v>
       </c>
       <c r="BJ8">
-        <v>5140.57739387112</v>
+        <v>38109.75609756092</v>
       </c>
       <c r="BK8">
-        <v>470.8984797036488</v>
+        <v>444.9294969512188</v>
       </c>
       <c r="BL8">
-        <v>0.004708984797036487</v>
+        <v>0.004449294969512188</v>
       </c>
       <c r="BM8">
-        <v>425.5884024385907</v>
+        <v>500.0000000000001</v>
       </c>
       <c r="BN8">
-        <v>0.004255884024385907</v>
+        <v>0.005000000000000001</v>
       </c>
       <c r="BO8">
-        <v>0.09977306775028287</v>
+        <v>0.02268129541736496</v>
       </c>
       <c r="BP8">
-        <v>0.02510545486167899</v>
+        <v>0.005664165574859163</v>
       </c>
       <c r="BQ8">
-        <v>0.03592307066841621</v>
+        <v>0.006526983738951008</v>
       </c>
       <c r="BR8">
         <v>1</v>
       </c>
       <c r="BS8">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="BV8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW8" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2586,7 +2577,7 @@
         <v>82</v>
       </c>
       <c r="B9" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -2598,7 +2589,7 @@
         <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
         <v>92</v>
@@ -2607,145 +2598,145 @@
         <v>92</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K9">
-        <v>0.06621278626437836</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1.637136906626681</v>
+        <v>0.1631055640919626</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q9">
-        <v>0.7665531965660946</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="S9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="T9">
-        <v>-0.9844460133251428</v>
+        <v>-0.4632662556503959</v>
       </c>
       <c r="U9">
-        <v>0.8520339916907844</v>
+        <v>0.6084426051572448</v>
       </c>
       <c r="V9" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="W9" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="X9">
-        <v>0.9964054710192536</v>
+        <v>0.9998911604582666</v>
       </c>
       <c r="Y9">
-        <v>0.2791157243714534</v>
+        <v>1</v>
       </c>
       <c r="Z9">
-        <v>164.5765081209393</v>
+        <v>-95.79281531210295</v>
       </c>
       <c r="AA9">
-        <v>11</v>
+        <v>-2.000000000000003</v>
       </c>
       <c r="AB9">
-        <v>-0.9639864423678249</v>
+        <v>-0.1009315418702112</v>
       </c>
       <c r="AC9">
-        <v>0.2659513845254884</v>
+        <v>-0.9948933731087477</v>
       </c>
       <c r="AD9" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AF9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AH9">
-        <v>-0.6143089908878036</v>
+        <v>-0.1009205565274476</v>
       </c>
       <c r="AI9">
-        <v>0.8375106535875269</v>
+        <v>0.6958281889274697</v>
       </c>
       <c r="AJ9">
-        <v>-1.400465121071157</v>
+        <v>-0.1932666252708736</v>
       </c>
       <c r="AK9">
-        <v>0.4294431392108509</v>
+        <v>-1.959874900696018</v>
       </c>
       <c r="AL9">
-        <v>-1.313231770328659</v>
+        <v>-0.56557184200474</v>
       </c>
       <c r="AM9">
-        <v>3.33070689379288</v>
+        <v>-0.5547588968345553</v>
       </c>
       <c r="AN9">
-        <v>1.084636112146913</v>
+        <v>0.5673804568283902</v>
       </c>
       <c r="AO9">
-        <v>0.04166892569233371</v>
+        <v>0.22942119862658</v>
       </c>
       <c r="AP9">
-        <v>158.6705</v>
+        <v>0.801715</v>
       </c>
       <c r="AQ9">
-        <v>158.4034210938131</v>
+        <v>0.8006537172065967</v>
       </c>
       <c r="AR9">
-        <v>161.7525279532776</v>
+        <v>0.8121437163541148</v>
       </c>
       <c r="AS9">
-        <v>158.6705</v>
+        <v>0.801715</v>
       </c>
       <c r="AT9">
-        <v>153.709</v>
+        <v>0.787245</v>
       </c>
       <c r="AU9">
-        <v>158.4034210938131</v>
+        <v>0.8005124275</v>
       </c>
       <c r="AV9">
-        <v>159.834</v>
+        <v>0.81175</v>
       </c>
       <c r="AW9">
-        <v>-0.001683229750879312</v>
+        <v>-0.001323765669100901</v>
       </c>
       <c r="AX9">
-        <v>0.2295478351412917</v>
+        <v>0.1198378176382662</v>
       </c>
       <c r="AY9">
-        <v>0.001683229750879312</v>
+        <v>0.001323765669100901</v>
       </c>
       <c r="AZ9">
-        <v>0.4602608600750335</v>
+        <v>0.4222995698675491</v>
       </c>
       <c r="BA9">
         <v>0.2</v>
       </c>
       <c r="BB9">
-        <v>0.3397391399249665</v>
+        <v>0.3777004301324509</v>
       </c>
       <c r="BC9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BD9">
         <v>100000</v>
@@ -2754,58 +2745,58 @@
         <v>100</v>
       </c>
       <c r="BF9">
-        <v>383.2765982830473</v>
+        <v>375</v>
       </c>
       <c r="BG9">
-        <v>0.007332806035148394</v>
+        <v>0.01251691685948247</v>
       </c>
       <c r="BH9">
-        <v>68186.72110012814</v>
+        <v>39945.9392127554</v>
       </c>
       <c r="BI9">
-        <v>52268.74902266399</v>
+        <v>29959.45440956655</v>
       </c>
       <c r="BJ9">
-        <v>329.4169301959973</v>
+        <v>37369.20777279526</v>
       </c>
       <c r="BK9">
-        <v>522.68749022664</v>
+        <v>299.5945440956655</v>
       </c>
       <c r="BL9">
-        <v>0.0052268749022664</v>
+        <v>0.002995945440956655</v>
       </c>
       <c r="BM9">
-        <v>383.2765982830473</v>
+        <v>375</v>
       </c>
       <c r="BN9">
-        <v>0.003832765982830473</v>
+        <v>0.00375</v>
       </c>
       <c r="BO9">
-        <v>2.795547701258807</v>
+        <v>0.01808817939016196</v>
       </c>
       <c r="BP9">
-        <v>0.5568598907852828</v>
+        <v>0.006239401540592509</v>
       </c>
       <c r="BQ9">
-        <v>1.816119394291128</v>
+        <v>0.008898201320130458</v>
       </c>
       <c r="BR9">
         <v>1</v>
       </c>
       <c r="BS9">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU9" t="s">
         <v>92</v>
       </c>
       <c r="BV9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW9" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2813,7 +2804,7 @@
         <v>83</v>
       </c>
       <c r="B10" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -2837,28 +2828,28 @@
         <v>94</v>
       </c>
       <c r="J10" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>0.1984309268304248</v>
       </c>
       <c r="L10">
-        <v>0.07591293037768411</v>
+        <v>0.7875694870461764</v>
       </c>
       <c r="M10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="O10" t="s">
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0.75</v>
+        <v>0.8511768048771814</v>
       </c>
       <c r="R10" t="s">
         <v>102</v>
@@ -2867,37 +2858,37 @@
         <v>105</v>
       </c>
       <c r="T10">
-        <v>-0.4092036361630399</v>
+        <v>0.8428938372814724</v>
       </c>
       <c r="U10">
-        <v>0.5590639223686202</v>
+        <v>0.8090656441841318</v>
       </c>
       <c r="V10" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="W10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="X10">
-        <v>0.9996891443810091</v>
+        <v>0.9999951135316221</v>
       </c>
       <c r="Y10">
-        <v>0.9943494743949133</v>
+        <v>0.5210408549913357</v>
       </c>
       <c r="Z10">
-        <v>-92.34697423853162</v>
+        <v>47.60834027287718</v>
       </c>
       <c r="AA10">
-        <v>-7.999999999999998</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB10">
-        <v>-0.04095097359994582</v>
+        <v>0.6741948870243686</v>
       </c>
       <c r="AC10">
-        <v>-0.9991611570518625</v>
+        <v>0.7385534877787788</v>
       </c>
       <c r="AD10" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="AE10" t="s">
         <v>110</v>
@@ -2909,70 +2900,70 @@
         <v>117</v>
       </c>
       <c r="AH10">
-        <v>-0.04082258246240339</v>
+        <v>0.5127364782123364</v>
       </c>
       <c r="AI10">
-        <v>0.6547500567402622</v>
+        <v>0.7991032687435249</v>
       </c>
       <c r="AJ10">
-        <v>-0.05214664521845188</v>
+        <v>0.6208640918820814</v>
       </c>
       <c r="AK10">
-        <v>-1.643112663229438</v>
+        <v>0.6666871392583099</v>
       </c>
       <c r="AL10">
-        <v>-0.5445606754256364</v>
+        <v>0.8769229157207086</v>
       </c>
       <c r="AM10">
-        <v>-1.72515865826341</v>
+        <v>-1.279075352466956</v>
       </c>
       <c r="AN10">
-        <v>0.6707493927570177</v>
+        <v>0.7477836088508186</v>
       </c>
       <c r="AO10">
-        <v>0.3753088716803816</v>
+        <v>0.04907772065413754</v>
       </c>
       <c r="AP10">
-        <v>0.79914</v>
+        <v>9.16042</v>
       </c>
       <c r="AQ10">
-        <v>0.7968270912239529</v>
+        <v>9.143525298158536</v>
       </c>
       <c r="AR10">
-        <v>0.8084356885907533</v>
+        <v>8.986558372163172</v>
       </c>
       <c r="AS10">
-        <v>0.79914</v>
+        <v>9.16042</v>
       </c>
       <c r="AT10">
-        <v>0.782095</v>
+        <v>9.30175</v>
       </c>
       <c r="AU10">
-        <v>0.7968270912239529</v>
+        <v>9.143525298158536</v>
       </c>
       <c r="AV10">
-        <v>0.809175</v>
+        <v>9.243210000000001</v>
       </c>
       <c r="AW10">
-        <v>-0.002894247285891161</v>
+        <v>-0.001844315199681215</v>
       </c>
       <c r="AX10">
-        <v>0.2304841829643313</v>
+        <v>0.2040669385368253</v>
       </c>
       <c r="AY10">
-        <v>0.002894247285891161</v>
+        <v>0.001844315199681215</v>
       </c>
       <c r="AZ10">
-        <v>0.4298707372413849</v>
+        <v>0.4123164778626114</v>
       </c>
       <c r="BA10">
         <v>0.2</v>
       </c>
       <c r="BB10">
-        <v>0.3701292627586151</v>
+        <v>0.3876835221373887</v>
       </c>
       <c r="BC10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BD10">
         <v>100000</v>
@@ -2981,58 +2972,58 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>375</v>
+        <v>425.5884024385907</v>
       </c>
       <c r="BG10">
-        <v>0.01255724904272091</v>
+        <v>0.009037795210263299</v>
       </c>
       <c r="BH10">
-        <v>39817.6382660688</v>
+        <v>55323.2274429278</v>
       </c>
       <c r="BI10">
-        <v>29863.2286995516</v>
+        <v>47089.84797036488</v>
       </c>
       <c r="BJ10">
-        <v>37369.20777279526</v>
+        <v>5140.57739387112</v>
       </c>
       <c r="BK10">
-        <v>298.632286995516</v>
+        <v>470.8984797036488</v>
       </c>
       <c r="BL10">
-        <v>0.00298632286995516</v>
+        <v>0.004708984797036487</v>
       </c>
       <c r="BM10">
-        <v>375.0000000000001</v>
+        <v>425.5884024385907</v>
       </c>
       <c r="BN10">
-        <v>0.003750000000000001</v>
+        <v>0.004255884024385907</v>
       </c>
       <c r="BO10">
-        <v>0.01890071132597321</v>
+        <v>0.09802491818546012</v>
       </c>
       <c r="BP10">
-        <v>0.007966138826463194</v>
+        <v>0.02138883614251228</v>
       </c>
       <c r="BQ10">
-        <v>0.01079946229767044</v>
+        <v>0.03565046571848309</v>
       </c>
       <c r="BR10">
         <v>1</v>
       </c>
       <c r="BS10">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU10" t="s">
         <v>92</v>
       </c>
       <c r="BV10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW10" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3040,7 +3031,7 @@
         <v>84</v>
       </c>
       <c r="B11" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -3061,145 +3052,145 @@
         <v>92</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
       <c r="L11">
-        <v>3.672976609750829</v>
+        <v>4.113377338486962</v>
       </c>
       <c r="M11">
         <v>6</v>
       </c>
       <c r="N11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q11">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T11">
-        <v>-0.9773777765031695</v>
+        <v>-0.9620218799730507</v>
       </c>
       <c r="U11">
-        <v>0.9897677588998222</v>
+        <v>0.9828746937730799</v>
       </c>
       <c r="V11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="X11">
-        <v>0.9997910378935834</v>
+        <v>0.9998593911408282</v>
       </c>
       <c r="Y11">
         <v>1</v>
       </c>
       <c r="Z11">
-        <v>-162.6980782645607</v>
+        <v>-157.5238006130807</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>-0.9547508248308558</v>
+        <v>-0.9240384191350055</v>
       </c>
       <c r="AC11">
-        <v>-0.2974068971708632</v>
+        <v>-0.382299620667455</v>
       </c>
       <c r="AD11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE11" t="s">
         <v>109</v>
       </c>
       <c r="AF11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AH11">
-        <v>-0.9545513180873961</v>
+        <v>-0.9239084911470601</v>
       </c>
       <c r="AI11">
-        <v>0.9796547909557933</v>
+        <v>0.9704855814292279</v>
       </c>
       <c r="AJ11">
-        <v>-2.692407542451325</v>
+        <v>-3.032250883123614</v>
       </c>
       <c r="AK11">
-        <v>-0.7894845107283921</v>
+        <v>-1.200880076249634</v>
       </c>
       <c r="AL11">
-        <v>-4.97731983308966</v>
+        <v>-5.511255125741923</v>
       </c>
       <c r="AM11">
-        <v>2.311647954026918</v>
+        <v>3.161310104484486</v>
       </c>
       <c r="AN11">
-        <v>4.75185668384593</v>
+        <v>5.189729054617612</v>
       </c>
       <c r="AO11">
-        <v>0.04464879837478363</v>
+        <v>0.04451154140375793</v>
       </c>
       <c r="AP11">
-        <v>6.71944</v>
+        <v>6.720800000000001</v>
       </c>
       <c r="AQ11">
-        <v>6.684035560918689</v>
+        <v>6.684047466734482</v>
       </c>
       <c r="AR11">
-        <v>6.685714574610426</v>
+        <v>6.681436933071859</v>
       </c>
       <c r="AS11">
-        <v>6.71944</v>
+        <v>6.720800000000001</v>
       </c>
       <c r="AT11">
-        <v>6.666679999999999</v>
+        <v>6.669400000000003</v>
       </c>
       <c r="AU11">
-        <v>6.684035560918689</v>
+        <v>6.684047466734482</v>
       </c>
       <c r="AV11">
-        <v>6.747365</v>
+        <v>6.748725000000002</v>
       </c>
       <c r="AW11">
-        <v>-0.005268956800166477</v>
+        <v>-0.005468475964992208</v>
       </c>
       <c r="AX11">
-        <v>1.267840253583173</v>
+        <v>1.316115783903996</v>
       </c>
       <c r="AY11">
-        <v>0.005268956800166477</v>
+        <v>0.005468475964992208</v>
       </c>
       <c r="AZ11">
-        <v>0.3574317292577109</v>
+        <v>0.3628388318193</v>
       </c>
       <c r="BA11">
         <v>0.2</v>
       </c>
       <c r="BB11">
-        <v>0.442568270742289</v>
+        <v>0.4371611681807</v>
       </c>
       <c r="BC11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BD11">
         <v>100000</v>
@@ -3211,22 +3202,22 @@
         <v>500</v>
       </c>
       <c r="BG11">
-        <v>0.004155852273403799</v>
+        <v>0.00415501130817766</v>
       </c>
       <c r="BH11">
-        <v>120312.2649955219</v>
+        <v>120336.6159355398</v>
       </c>
       <c r="BI11">
-        <v>120312.2649955219</v>
+        <v>120336.6159355398</v>
       </c>
       <c r="BJ11">
         <v>17905.10295434172</v>
       </c>
       <c r="BK11">
-        <v>1203.122649955219</v>
+        <v>1203.366159355398</v>
       </c>
       <c r="BL11">
-        <v>0.01203122649955219</v>
+        <v>0.01203366159355398</v>
       </c>
       <c r="BM11">
         <v>500</v>
@@ -3235,31 +3226,31 @@
         <v>0.005</v>
       </c>
       <c r="BO11">
-        <v>0.08477888734106553</v>
+        <v>0.0771786124335779</v>
       </c>
       <c r="BP11">
-        <v>0.01319435604094559</v>
+        <v>0.0118407085145946</v>
       </c>
       <c r="BQ11">
-        <v>0.01290237387631207</v>
+        <v>0.01251203857240322</v>
       </c>
       <c r="BR11">
         <v>1</v>
       </c>
       <c r="BS11">
-        <v>0.04339094579361392</v>
+        <v>0.03898840216084896</v>
       </c>
       <c r="BT11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BU11" t="s">
         <v>92</v>
       </c>
       <c r="BV11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BW11" s="2">
-        <v>46284</v>
+        <v>46286</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/latest_trade_signals.xlsx
+++ b/public/data/files/latest_trade_signals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="132">
   <si>
     <t>Pair</t>
   </si>
@@ -67,6 +67,78 @@
     <t>TerrainSizeMultiplier</t>
   </si>
   <si>
+    <t>MarketPosture</t>
+  </si>
+  <si>
+    <t>MarketPostureCN</t>
+  </si>
+  <si>
+    <t>MarketPostureScore</t>
+  </si>
+  <si>
+    <t>MarketPostureConfidence</t>
+  </si>
+  <si>
+    <t>PhasedDirection</t>
+  </si>
+  <si>
+    <t>PhasedAlignment</t>
+  </si>
+  <si>
+    <t>PhasedCoherence</t>
+  </si>
+  <si>
+    <t>PhasedGate</t>
+  </si>
+  <si>
+    <t>PhasedBeamPhaseDeg</t>
+  </si>
+  <si>
+    <t>PhasedGradientDeg</t>
+  </si>
+  <si>
+    <t>PhasedDirectionScore</t>
+  </si>
+  <si>
+    <t>PhasedImpulseScore</t>
+  </si>
+  <si>
+    <t>SurveyTrend</t>
+  </si>
+  <si>
+    <t>SurveyTrendCN</t>
+  </si>
+  <si>
+    <t>TerrainPattern</t>
+  </si>
+  <si>
+    <t>TerrainPatternCN</t>
+  </si>
+  <si>
+    <t>SurveyDirectionScore</t>
+  </si>
+  <si>
+    <t>SurveyConfidence</t>
+  </si>
+  <si>
+    <t>ContourElevation</t>
+  </si>
+  <si>
+    <t>ContourTemporalSlope</t>
+  </si>
+  <si>
+    <t>ContourScaleSlope</t>
+  </si>
+  <si>
+    <t>ContourCurvature</t>
+  </si>
+  <si>
+    <t>ContourRelief</t>
+  </si>
+  <si>
+    <t>ContourRoughness</t>
+  </si>
+  <si>
     <t>EntryPrice</t>
   </si>
   <si>
@@ -172,15 +244,21 @@
     <t>USDCNH</t>
   </si>
   <si>
+    <t>GBPUSD</t>
+  </si>
+  <si>
+    <t>EURUSD</t>
+  </si>
+  <si>
     <t>XAUUSD</t>
   </si>
   <si>
+    <t>AUDUSD</t>
+  </si>
+  <si>
     <t>USDJPY</t>
   </si>
   <si>
-    <t>AUDUSD</t>
-  </si>
-  <si>
     <t>EURCNH</t>
   </si>
   <si>
@@ -190,30 +268,24 @@
     <t>USDCHF</t>
   </si>
   <si>
-    <t>EURUSD</t>
-  </si>
-  <si>
     <t>GBPCNH</t>
   </si>
   <si>
-    <t>GBPUSD</t>
-  </si>
-  <si>
     <t>ensemble</t>
   </si>
   <si>
     <t>horizon_ensemble_terrain_v1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>MEDIUM</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>FLAT</t>
   </si>
   <si>
@@ -241,34 +313,91 @@
     <t>REDUCE_CONFLICT</t>
   </si>
   <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.48); metric_best=drift4; scores=model=0.2065,naive=0.02884,drift4=0.0172; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=drift4; scores=model=920.8,naive=491.2,drift4=338.5; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.51,naive=0.20,drift4=0.29); metric_best=naive; scores=model=3.97,naive=1.871,drift4=6.766; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.31,naive=0.17,drift4=0.51); metric_best=drift4; scores=model=0.02855,naive=0.01105,drift4=0.00295</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.29,naive=0.18,drift4=0.53); metric_best=drift4; scores=model=0.33,naive=0.05506,drift4=0.01483</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.32,naive=0.20,drift4=0.49); metric_best=drift4; scores=model=0.148,naive=0.05103,drift4=0.01814</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.02609,naive=0.01205,drift4=0.01722; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.35,naive=0.20,drift4=0.45); metric_best=drift4; scores=model=0.02299,naive=0.01227,drift4=0.005904; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.37,naive=0.20,drift4=0.43); metric_best=drift4; scores=model=0.2724,naive=0.07937,drift4=0.06765; naive_cap_applied</t>
-  </si>
-  <si>
-    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.36,naive=0.17,drift4=0.48); metric_best=drift4; scores=model=0.01938,naive=0.01667,drift4=0.004741</t>
+    <t>DOWN_ACCELERATING</t>
+  </si>
+  <si>
+    <t>UP_ACCELERATING</t>
+  </si>
+  <si>
+    <t>DOWN_STEADY</t>
+  </si>
+  <si>
+    <t>空头加速</t>
+  </si>
+  <si>
+    <t>多头加速</t>
+  </si>
+  <si>
+    <t>空头稳态</t>
+  </si>
+  <si>
+    <t>NEUTRAL</t>
+  </si>
+  <si>
+    <t>TRANSITION</t>
+  </si>
+  <si>
+    <t>下跌</t>
+  </si>
+  <si>
+    <t>上涨</t>
+  </si>
+  <si>
+    <t>转换</t>
+  </si>
+  <si>
+    <t>DOWN_STEEPENING</t>
+  </si>
+  <si>
+    <t>UP_STEEPENING</t>
+  </si>
+  <si>
+    <t>DOWN_SLOPE</t>
+  </si>
+  <si>
+    <t>TRANSITION_ZONE</t>
+  </si>
+  <si>
+    <t>下降陡坡形成</t>
+  </si>
+  <si>
+    <t>上升陡坡形成</t>
+  </si>
+  <si>
+    <t>下降坡延续</t>
+  </si>
+  <si>
+    <t>地形转换区</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.38,naive=0.20,drift4=0.42); metric_best=naive; scores=model=0.1007,naive=0.01093,drift4=0.01548; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.02205,naive=0.004717,drift4=0.00813; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.41,naive=0.20,drift4=0.39); metric_best=naive; scores=model=0.03087,naive=0.004849,drift4=0.009107; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.30,naive=0.30,drift4=0.40); metric_best=naive; scores=model=223.5,naive=127.6,drift4=178.5; naive_cap_applied; model_divergence_guard(abs=479.9,thr=416.5)</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.43,naive=0.20,drift4=0.37); metric_best=naive; scores=model=0.01003,naive=0.003665,drift4=0.005305; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.49,naive=0.20,drift4=0.31); metric_best=naive; scores=model=2.34,naive=0.2879,drift4=1.959; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1676,naive=0.02057,drift4=0.04914; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.06358,naive=0.01895,drift4=0.03487; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.44,naive=0.20,drift4=0.36); metric_best=naive; scores=model=0.01537,naive=0.005411,drift4=0.008973; naive_cap_applied</t>
+  </si>
+  <si>
+    <t>horizon=4; policy=horizon_ensemble_terrain_v1; weights(model=0.42,naive=0.20,drift4=0.38); metric_best=naive; scores=model=0.1366,naive=0.0188,drift4=0.04593; naive_cap_applied</t>
   </si>
   <si>
     <t>SKIP</t>
@@ -642,10 +771,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:BW11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:51">
+    <row r="1" spans="1:75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -799,10 +928,82 @@
       <c r="AY1" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:75">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="B2" s="2">
         <v>46259</v>
@@ -811,22 +1012,22 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2">
         <v>46258</v>
@@ -835,7 +1036,7 @@
         <v>1</v>
       </c>
       <c r="L2">
-        <v>4.490804287764481</v>
+        <v>4.458899308317085</v>
       </c>
       <c r="M2">
         <v>6</v>
@@ -844,108 +1045,180 @@
         <v>28</v>
       </c>
       <c r="O2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="P2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S2" t="s">
+        <v>102</v>
+      </c>
+      <c r="T2">
+        <v>-0.9424296120656104</v>
+      </c>
+      <c r="U2">
+        <v>0.9740642884105478</v>
+      </c>
+      <c r="V2" t="s">
+        <v>92</v>
+      </c>
+      <c r="W2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X2">
+        <v>0.9998838519240926</v>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>-152.2333798732249</v>
+      </c>
+      <c r="AA2">
+        <v>7.999999999999998</v>
+      </c>
+      <c r="AB2">
+        <v>-0.8848525366646968</v>
+      </c>
+      <c r="AC2">
+        <v>-0.4658712143479693</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AH2">
+        <v>-0.8847497627451013</v>
+      </c>
+      <c r="AI2">
+        <v>0.9589348227309553</v>
+      </c>
+      <c r="AJ2">
+        <v>-3.311549434642514</v>
+      </c>
+      <c r="AK2">
+        <v>-1.686046025948992</v>
+      </c>
+      <c r="AL2">
+        <v>-5.87752958986212</v>
+      </c>
+      <c r="AM2">
+        <v>4.054848521620608</v>
+      </c>
+      <c r="AN2">
+        <v>5.465289041106415</v>
+      </c>
+      <c r="AO2">
+        <v>0.04320190961257366</v>
+      </c>
+      <c r="AP2">
         <v>6.71965</v>
       </c>
-      <c r="S2">
-        <v>6.725555618739609</v>
-      </c>
-      <c r="T2">
-        <v>6.783369356682931</v>
-      </c>
-      <c r="U2">
+      <c r="AQ2">
+        <v>6.721243384162189</v>
+      </c>
+      <c r="AR2">
+        <v>6.758181972602392</v>
+      </c>
+      <c r="AS2">
         <v>6.71965</v>
       </c>
-      <c r="V2">
+      <c r="AT2">
         <v>6.689304999999999</v>
       </c>
-      <c r="Y2">
-        <v>0.0008788580863004998</v>
-      </c>
-      <c r="AA2">
-        <v>0.0008788580863004998</v>
-      </c>
-      <c r="AB2">
-        <v>0.3208613741052144</v>
-      </c>
-      <c r="AC2">
+      <c r="AW2">
+        <v>0.0002371230885819638</v>
+      </c>
+      <c r="AY2">
+        <v>0.0002371230885819638</v>
+      </c>
+      <c r="AZ2">
+        <v>0.3755882871264846</v>
+      </c>
+      <c r="BA2">
         <v>0.2</v>
       </c>
-      <c r="AD2">
-        <v>0.4791386258947857</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF2">
+      <c r="BB2">
+        <v>0.4244117128735155</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BD2">
         <v>100000</v>
       </c>
-      <c r="AG2">
+      <c r="BE2">
         <v>100</v>
       </c>
-      <c r="AH2">
+      <c r="BF2">
         <v>0</v>
       </c>
-      <c r="AJ2">
+      <c r="BH2">
         <v>0</v>
       </c>
-      <c r="AK2">
+      <c r="BI2">
         <v>0</v>
       </c>
-      <c r="AL2">
+      <c r="BJ2">
         <v>0</v>
       </c>
-      <c r="AM2">
+      <c r="BK2">
         <v>0</v>
       </c>
-      <c r="AN2">
+      <c r="BL2">
         <v>0</v>
       </c>
-      <c r="AO2">
+      <c r="BM2">
         <v>0</v>
       </c>
-      <c r="AP2">
+      <c r="BN2">
         <v>0</v>
       </c>
-      <c r="AQ2">
-        <v>0.08525548435744139</v>
-      </c>
-      <c r="AR2">
-        <v>0.01388827048500356</v>
-      </c>
-      <c r="AS2">
-        <v>0.01439765753955598</v>
-      </c>
-      <c r="AT2">
+      <c r="BO2">
+        <v>0.1006832097601681</v>
+      </c>
+      <c r="BP2">
+        <v>0.0109333826416664</v>
+      </c>
+      <c r="BQ2">
+        <v>0.01548343064880831</v>
+      </c>
+      <c r="BR2">
         <v>1</v>
       </c>
-      <c r="AU2">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AY2" s="2">
+      <c r="BS2">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW2" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:75">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
         <v>46259</v>
@@ -954,153 +1227,213 @@
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J3" s="2">
         <v>46258</v>
       </c>
       <c r="K3">
-        <v>0.1601536574253007</v>
+        <v>1</v>
       </c>
       <c r="L3">
-        <v>2.338976754730542</v>
+        <v>3.376630418212414</v>
       </c>
       <c r="M3">
         <v>6</v>
       </c>
       <c r="N3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="P3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="Q3">
-        <v>0.7900384143563252</v>
-      </c>
-      <c r="R3">
-        <v>4635.809999999999</v>
-      </c>
-      <c r="S3">
-        <v>4808.304484772529</v>
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
+        <v>100</v>
+      </c>
+      <c r="S3" t="s">
+        <v>103</v>
       </c>
       <c r="T3">
-        <v>4507.443384040592</v>
+        <v>0.9052059991432598</v>
       </c>
       <c r="U3">
-        <v>4635.809999999999</v>
-      </c>
-      <c r="V3">
-        <v>5170.269999999997</v>
-      </c>
-      <c r="W3">
-        <v>4808.304484772529</v>
+        <v>0.9573412545182542</v>
+      </c>
+      <c r="V3" t="s">
+        <v>93</v>
+      </c>
+      <c r="W3" t="s">
+        <v>94</v>
       </c>
       <c r="X3">
-        <v>4496.99</v>
+        <v>0.999994219615149</v>
       </c>
       <c r="Y3">
-        <v>0.03720913600266839</v>
+        <v>1</v>
       </c>
       <c r="Z3">
-        <v>1.24257660835997</v>
+        <v>35.86384927527484</v>
       </c>
       <c r="AA3">
-        <v>0.03720913600266839</v>
+        <v>4.000000000000005</v>
       </c>
       <c r="AB3">
-        <v>0.3848269050847682</v>
+        <v>0.8104114503375457</v>
       </c>
       <c r="AC3">
+        <v>0.5858611449497191</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH3">
+        <v>0.8104067658474751</v>
+      </c>
+      <c r="AI3">
+        <v>0.9367543457803579</v>
+      </c>
+      <c r="AJ3">
+        <v>2.621397111205324</v>
+      </c>
+      <c r="AK3">
+        <v>1.863913365961104</v>
+      </c>
+      <c r="AL3">
+        <v>3.953780588612692</v>
+      </c>
+      <c r="AM3">
+        <v>-4.968332378490205</v>
+      </c>
+      <c r="AN3">
+        <v>3.466742252617929</v>
+      </c>
+      <c r="AO3">
+        <v>0.04244710790805367</v>
+      </c>
+      <c r="AP3">
+        <v>1.363465</v>
+      </c>
+      <c r="AQ3">
+        <v>1.363756210140485</v>
+      </c>
+      <c r="AR3">
+        <v>1.351109021907149</v>
+      </c>
+      <c r="AS3">
+        <v>1.363465</v>
+      </c>
+      <c r="AT3">
+        <v>1.377485</v>
+      </c>
+      <c r="AW3">
+        <v>0.0002135809430272212</v>
+      </c>
+      <c r="AY3">
+        <v>0.0002135809430272212</v>
+      </c>
+      <c r="AZ3">
+        <v>0.4141946820344204</v>
+      </c>
+      <c r="BA3">
         <v>0.2</v>
       </c>
-      <c r="AD3">
-        <v>0.4151730949152317</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF3">
+      <c r="BB3">
+        <v>0.3858053179655795</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD3">
         <v>100000</v>
       </c>
-      <c r="AG3">
+      <c r="BE3">
         <v>100</v>
       </c>
-      <c r="AH3">
-        <v>395.0192071781626</v>
-      </c>
-      <c r="AI3">
-        <v>0.02994514442999159</v>
-      </c>
-      <c r="AJ3">
-        <v>16697.1978101139</v>
-      </c>
-      <c r="AK3">
-        <v>13191.42768209629</v>
-      </c>
-      <c r="AL3">
-        <v>2.845549684326211</v>
-      </c>
-      <c r="AM3">
-        <v>131.9142768209629</v>
-      </c>
-      <c r="AN3">
-        <v>0.001319142768209629</v>
-      </c>
-      <c r="AO3">
-        <v>395.0192071781626</v>
-      </c>
-      <c r="AP3">
-        <v>0.003950192071781627</v>
-      </c>
-      <c r="AQ3">
-        <v>375.0129746039156</v>
-      </c>
-      <c r="AR3">
-        <v>186.4573571983389</v>
-      </c>
-      <c r="AS3">
-        <v>179.1563094023557</v>
-      </c>
-      <c r="AT3">
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0.02204921517530336</v>
+      </c>
+      <c r="BP3">
+        <v>0.004716818709875022</v>
+      </c>
+      <c r="BQ3">
+        <v>0.008130420661116074</v>
+      </c>
+      <c r="BR3">
         <v>1</v>
       </c>
-      <c r="AU3">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY3" s="2">
+      <c r="BS3">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW3" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:75">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2">
         <v>46259</v>
@@ -1109,153 +1442,213 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="J4" s="2">
         <v>46258</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>1.537751271770883</v>
+        <v>2.900632541281531</v>
       </c>
       <c r="M4">
         <v>6</v>
       </c>
       <c r="N4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>100</v>
+      </c>
+      <c r="S4" t="s">
+        <v>103</v>
+      </c>
+      <c r="T4">
+        <v>0.8490697911334227</v>
+      </c>
+      <c r="U4">
+        <v>0.9320778333059989</v>
+      </c>
+      <c r="V4" t="s">
+        <v>93</v>
+      </c>
+      <c r="W4" t="s">
+        <v>94</v>
+      </c>
+      <c r="X4">
+        <v>0.9999857091838348</v>
+      </c>
+      <c r="Y4">
         <v>1</v>
       </c>
-      <c r="R4">
-        <v>159.2205</v>
-      </c>
-      <c r="S4">
-        <v>161.8620797171961</v>
-      </c>
-      <c r="T4">
-        <v>163.2215376779572</v>
-      </c>
-      <c r="U4">
-        <v>159.2205</v>
-      </c>
-      <c r="V4">
-        <v>161.272</v>
-      </c>
-      <c r="W4">
-        <v>161.8620797171961</v>
-      </c>
-      <c r="X4">
-        <v>157.4594468552026</v>
-      </c>
-      <c r="Y4">
-        <v>0.01659070105417372</v>
-      </c>
       <c r="Z4">
-        <v>1.5</v>
+        <v>45.72224026683239</v>
       </c>
       <c r="AA4">
-        <v>0.01659070105417372</v>
+        <v>6.999999999999997</v>
       </c>
       <c r="AB4">
-        <v>0.5131368983051977</v>
+        <v>0.6981374253201522</v>
       </c>
       <c r="AC4">
+        <v>0.7159637807650251</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH4">
+        <v>0.6981274483665489</v>
+      </c>
+      <c r="AI4">
+        <v>0.9028232642579117</v>
+      </c>
+      <c r="AJ4">
+        <v>2.312721927774895</v>
+      </c>
+      <c r="AK4">
+        <v>2.305627588470507</v>
+      </c>
+      <c r="AL4">
+        <v>3.116674231579814</v>
+      </c>
+      <c r="AM4">
+        <v>-5.011885829396338</v>
+      </c>
+      <c r="AN4">
+        <v>2.631330194211097</v>
+      </c>
+      <c r="AO4">
+        <v>0.04408641034984021</v>
+      </c>
+      <c r="AP4">
+        <v>1.16623</v>
+      </c>
+      <c r="AQ4">
+        <v>1.165798488903975</v>
+      </c>
+      <c r="AR4">
+        <v>1.154234260231938</v>
+      </c>
+      <c r="AS4">
+        <v>1.16623</v>
+      </c>
+      <c r="AT4">
+        <v>1.177665</v>
+      </c>
+      <c r="AW4">
+        <v>-0.0003700051413746429</v>
+      </c>
+      <c r="AY4">
+        <v>0.0003700051413746429</v>
+      </c>
+      <c r="AZ4">
+        <v>0.4088437322445551</v>
+      </c>
+      <c r="BA4">
         <v>0.2</v>
       </c>
-      <c r="AD4">
-        <v>0.2868631016948024</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF4">
+      <c r="BB4">
+        <v>0.391156267755445</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD4">
         <v>100000</v>
       </c>
-      <c r="AG4">
+      <c r="BE4">
         <v>100</v>
       </c>
-      <c r="AH4">
-        <v>500</v>
-      </c>
-      <c r="AI4">
-        <v>0.01106046736944914</v>
-      </c>
-      <c r="AJ4">
-        <v>45206.04629973263</v>
-      </c>
-      <c r="AK4">
-        <v>45206.04629973263</v>
-      </c>
-      <c r="AL4">
-        <v>283.9210170784078</v>
-      </c>
-      <c r="AM4">
-        <v>452.0604629973263</v>
-      </c>
-      <c r="AN4">
-        <v>0.004520604629973263</v>
-      </c>
-      <c r="AO4">
-        <v>500</v>
-      </c>
-      <c r="AP4">
-        <v>0.005</v>
-      </c>
-      <c r="AQ4">
-        <v>3.984261955618841</v>
-      </c>
-      <c r="AR4">
-        <v>0.6403706188702041</v>
-      </c>
-      <c r="AS4">
-        <v>2.617286218588576</v>
-      </c>
-      <c r="AT4">
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0.03087036451860621</v>
+      </c>
+      <c r="BP4">
+        <v>0.004849037491668432</v>
+      </c>
+      <c r="BQ4">
+        <v>0.009106745004209013</v>
+      </c>
+      <c r="BR4">
         <v>1</v>
       </c>
-      <c r="AU4">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY4" s="2">
+      <c r="BS4">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>128</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>90</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>130</v>
+      </c>
+      <c r="BW4" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:75">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2">
         <v>46259</v>
@@ -1264,153 +1657,225 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J5" s="2">
         <v>46258</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.1558771339693187</v>
       </c>
       <c r="L5">
-        <v>2.538324649084723</v>
+        <v>2.333259364297918</v>
       </c>
       <c r="M5">
         <v>6</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O5" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q5">
+        <v>0.7889692834923296</v>
+      </c>
+      <c r="R5" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" t="s">
+        <v>103</v>
+      </c>
+      <c r="T5">
+        <v>0.8326459262956046</v>
+      </c>
+      <c r="U5">
+        <v>0.7980625052793621</v>
+      </c>
+      <c r="V5" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" t="s">
+        <v>94</v>
+      </c>
+      <c r="X5">
+        <v>0.9999610734037686</v>
+      </c>
+      <c r="Y5">
         <v>1</v>
       </c>
-      <c r="R5">
-        <v>0.715405</v>
-      </c>
-      <c r="S5">
-        <v>0.721466738994615</v>
-      </c>
-      <c r="T5">
-        <v>0.7174018303940544</v>
-      </c>
-      <c r="U5">
-        <v>0.715405</v>
-      </c>
-      <c r="V5">
-        <v>0.725965</v>
-      </c>
-      <c r="W5">
-        <v>0.721466738994615</v>
-      </c>
-      <c r="X5">
-        <v>0.7072687499999999</v>
-      </c>
-      <c r="Y5">
-        <v>0.008473157155198861</v>
-      </c>
       <c r="Z5">
-        <v>0.7450286058829326</v>
+        <v>44.667444358273</v>
       </c>
       <c r="AA5">
-        <v>0.008473157155198861</v>
+        <v>5.000000000000007</v>
       </c>
       <c r="AB5">
-        <v>0.312700994459592</v>
+        <v>0.7111990301865317</v>
       </c>
       <c r="AC5">
-        <v>0.1724005069961753</v>
-      </c>
-      <c r="AD5">
-        <v>0.5148984985442326</v>
+        <v>0.7029907107933481</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>93</v>
       </c>
       <c r="AE5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF5">
+        <v>108</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH5">
+        <v>0.7111713456290435</v>
+      </c>
+      <c r="AI5">
+        <v>0.9058400495282899</v>
+      </c>
+      <c r="AJ5">
+        <v>1.820105687051705</v>
+      </c>
+      <c r="AK5">
+        <v>1.76423491000674</v>
+      </c>
+      <c r="AL5">
+        <v>2.671512049342179</v>
+      </c>
+      <c r="AM5">
+        <v>-3.212159978830436</v>
+      </c>
+      <c r="AN5">
+        <v>2.35473461935825</v>
+      </c>
+      <c r="AO5">
+        <v>0.05004023479325828</v>
+      </c>
+      <c r="AP5">
+        <v>4635.809999999999</v>
+      </c>
+      <c r="AQ5">
+        <v>4785.806171472148</v>
+      </c>
+      <c r="AR5">
+        <v>4423.183904907169</v>
+      </c>
+      <c r="AS5">
+        <v>4635.809999999999</v>
+      </c>
+      <c r="AT5">
+        <v>5170.269999999997</v>
+      </c>
+      <c r="AU5">
+        <v>4785.806171472148</v>
+      </c>
+      <c r="AV5">
+        <v>4496.99</v>
+      </c>
+      <c r="AW5">
+        <v>0.03235597910012478</v>
+      </c>
+      <c r="AX5">
+        <v>1.080508366749389</v>
+      </c>
+      <c r="AY5">
+        <v>0.03235597910012478</v>
+      </c>
+      <c r="AZ5">
+        <v>0.3</v>
+      </c>
+      <c r="BA5">
+        <v>0.3</v>
+      </c>
+      <c r="BB5">
+        <v>0.4</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>121</v>
+      </c>
+      <c r="BD5">
         <v>100000</v>
       </c>
-      <c r="AG5">
+      <c r="BE5">
         <v>100</v>
       </c>
-      <c r="AH5">
-        <v>500</v>
-      </c>
-      <c r="AI5">
-        <v>0.01137292862085118</v>
-      </c>
-      <c r="AJ5">
-        <v>43964.04977723131</v>
-      </c>
-      <c r="AK5">
-        <v>43964.04977723131</v>
-      </c>
-      <c r="AL5">
-        <v>61453.37225380213</v>
-      </c>
-      <c r="AM5">
-        <v>439.6404977723131</v>
-      </c>
-      <c r="AN5">
-        <v>0.004396404977723131</v>
-      </c>
-      <c r="AO5">
-        <v>500</v>
-      </c>
-      <c r="AP5">
-        <v>0.005</v>
-      </c>
-      <c r="AQ5">
-        <v>0.01015374352877074</v>
-      </c>
-      <c r="AR5">
-        <v>0.004932853835718002</v>
-      </c>
-      <c r="AS5">
-        <v>0.004569097085417728</v>
-      </c>
-      <c r="AT5">
+      <c r="BF5">
+        <v>394.4846417461648</v>
+      </c>
+      <c r="BG5">
+        <v>0.02994514442999159</v>
+      </c>
+      <c r="BH5">
+        <v>16697.1978101139</v>
+      </c>
+      <c r="BI5">
+        <v>13173.57619257526</v>
+      </c>
+      <c r="BJ5">
+        <v>2.841698903228403</v>
+      </c>
+      <c r="BK5">
+        <v>131.7357619257526</v>
+      </c>
+      <c r="BL5">
+        <v>0.001317357619257526</v>
+      </c>
+      <c r="BM5">
+        <v>394.4846417461648</v>
+      </c>
+      <c r="BN5">
+        <v>0.003944846417461648</v>
+      </c>
+      <c r="BO5">
+        <v>223.5127567301772</v>
+      </c>
+      <c r="BP5">
+        <v>127.5666779433151</v>
+      </c>
+      <c r="BQ5">
+        <v>178.543941721783</v>
+      </c>
+      <c r="BR5">
         <v>1</v>
       </c>
-      <c r="AU5">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY5" s="2">
+      <c r="BS5">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW5" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:75">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2">
         <v>46259</v>
@@ -1419,153 +1884,225 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2">
         <v>46258</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>1.056134761727802</v>
+        <v>2.498181505869455</v>
       </c>
       <c r="M6">
         <v>6</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O6" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P6" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q6">
-        <v>0.75</v>
-      </c>
-      <c r="R6">
-        <v>7.8373</v>
-      </c>
-      <c r="S6">
-        <v>7.891144032616348</v>
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S6" t="s">
+        <v>103</v>
       </c>
       <c r="T6">
-        <v>7.924123373828378</v>
+        <v>0.9025922180602828</v>
       </c>
       <c r="U6">
-        <v>7.8373</v>
-      </c>
-      <c r="V6">
-        <v>7.891</v>
-      </c>
-      <c r="W6">
-        <v>7.891144032616348</v>
+        <v>0.956158207845921</v>
+      </c>
+      <c r="V6" t="s">
+        <v>93</v>
+      </c>
+      <c r="W6" t="s">
+        <v>94</v>
       </c>
       <c r="X6">
-        <v>7.776450000000001</v>
+        <v>0.9999668388751755</v>
       </c>
       <c r="Y6">
-        <v>0.006870227325271155</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>0.8848649567189507</v>
+        <v>36.37224101247428</v>
       </c>
       <c r="AA6">
-        <v>0.006870227325271155</v>
+        <v>3.000000000000004</v>
       </c>
       <c r="AB6">
-        <v>0.2920989383978017</v>
+        <v>0.8051812058618306</v>
       </c>
       <c r="AC6">
-        <v>0.1774910561466491</v>
-      </c>
-      <c r="AD6">
-        <v>0.5304100054555492</v>
+        <v>0.593028857414956</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>93</v>
       </c>
       <c r="AE6" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF6">
+        <v>108</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH6">
+        <v>0.8051545051473566</v>
+      </c>
+      <c r="AI6">
+        <v>0.934530340741347</v>
+      </c>
+      <c r="AJ6">
+        <v>1.93989071029883</v>
+      </c>
+      <c r="AK6">
+        <v>1.410828488305417</v>
+      </c>
+      <c r="AL6">
+        <v>2.898749912023796</v>
+      </c>
+      <c r="AM6">
+        <v>-3.189108757480399</v>
+      </c>
+      <c r="AN6">
+        <v>2.589023724384023</v>
+      </c>
+      <c r="AO6">
+        <v>0.04674943082342426</v>
+      </c>
+      <c r="AP6">
+        <v>0.715405</v>
+      </c>
+      <c r="AQ6">
+        <v>0.7267736953333398</v>
+      </c>
+      <c r="AR6">
+        <v>0.7328068864149425</v>
+      </c>
+      <c r="AS6">
+        <v>0.715405</v>
+      </c>
+      <c r="AT6">
+        <v>0.725965</v>
+      </c>
+      <c r="AU6">
+        <v>0.7267736953333398</v>
+      </c>
+      <c r="AV6">
+        <v>0.7072687499999999</v>
+      </c>
+      <c r="AW6">
+        <v>0.0158912718436967</v>
+      </c>
+      <c r="AX6">
+        <v>1.397289332719593</v>
+      </c>
+      <c r="AY6">
+        <v>0.0158912718436967</v>
+      </c>
+      <c r="AZ6">
+        <v>0.4268845105293013</v>
+      </c>
+      <c r="BA6">
+        <v>0.2</v>
+      </c>
+      <c r="BB6">
+        <v>0.3731154894706987</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD6">
         <v>100000</v>
       </c>
-      <c r="AG6">
+      <c r="BE6">
         <v>100</v>
       </c>
-      <c r="AH6">
-        <v>375</v>
-      </c>
-      <c r="AI6">
-        <v>0.00776415347122088</v>
-      </c>
-      <c r="AJ6">
-        <v>64398.52095316414</v>
-      </c>
-      <c r="AK6">
-        <v>48298.89071487311</v>
-      </c>
-      <c r="AL6">
-        <v>6162.695152013207</v>
-      </c>
-      <c r="AM6">
-        <v>482.9889071487311</v>
-      </c>
-      <c r="AN6">
-        <v>0.00482988907148731</v>
-      </c>
-      <c r="AO6">
-        <v>375</v>
-      </c>
-      <c r="AP6">
-        <v>0.00375</v>
-      </c>
-      <c r="AQ6">
-        <v>0.1981942207121046</v>
-      </c>
-      <c r="AR6">
-        <v>0.0270379820686291</v>
-      </c>
-      <c r="AS6">
-        <v>0.04013408196648214</v>
-      </c>
-      <c r="AT6">
+      <c r="BF6">
+        <v>500</v>
+      </c>
+      <c r="BG6">
+        <v>0.01137292862085118</v>
+      </c>
+      <c r="BH6">
+        <v>43964.04977723131</v>
+      </c>
+      <c r="BI6">
+        <v>43964.04977723131</v>
+      </c>
+      <c r="BJ6">
+        <v>61453.37225380213</v>
+      </c>
+      <c r="BK6">
+        <v>439.6404977723131</v>
+      </c>
+      <c r="BL6">
+        <v>0.004396404977723131</v>
+      </c>
+      <c r="BM6">
+        <v>500</v>
+      </c>
+      <c r="BN6">
+        <v>0.005</v>
+      </c>
+      <c r="BO6">
+        <v>0.01003453770955882</v>
+      </c>
+      <c r="BP6">
+        <v>0.003664576587432029</v>
+      </c>
+      <c r="BQ6">
+        <v>0.005305160627820868</v>
+      </c>
+      <c r="BR6">
         <v>1</v>
       </c>
-      <c r="AU6">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY6" s="2">
+      <c r="BS6">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW6" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:75">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="B7" s="2">
         <v>46259</v>
@@ -1574,22 +2111,22 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I7" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J7" s="2">
         <v>46258</v>
@@ -1598,129 +2135,201 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0.7544249014873886</v>
+        <v>1.440812448376137</v>
       </c>
       <c r="M7">
         <v>6</v>
       </c>
       <c r="N7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="P7" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
-      </c>
-      <c r="R7">
-        <v>4.80441</v>
-      </c>
-      <c r="S7">
-        <v>4.832245008414006</v>
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>101</v>
+      </c>
+      <c r="S7" t="s">
+        <v>104</v>
       </c>
       <c r="T7">
-        <v>4.794416980220809</v>
+        <v>-0.9979897629802601</v>
       </c>
       <c r="U7">
-        <v>4.80441</v>
-      </c>
-      <c r="V7">
-        <v>4.86789</v>
-      </c>
-      <c r="W7">
-        <v>4.832245008414006</v>
+        <v>0.848502317540091</v>
+      </c>
+      <c r="V7" t="s">
+        <v>92</v>
+      </c>
+      <c r="W7" t="s">
+        <v>94</v>
       </c>
       <c r="X7">
-        <v>4.764609999999999</v>
+        <v>0.9976276967958955</v>
       </c>
       <c r="Y7">
-        <v>0.005793637182090203</v>
+        <v>0.04922462486363275</v>
       </c>
       <c r="Z7">
-        <v>0.6993720707036671</v>
+        <v>173.9493804213141</v>
       </c>
       <c r="AA7">
-        <v>0.005793637182090203</v>
+        <v>24.00000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.3164640584622161</v>
+        <v>-0.9944291586207727</v>
       </c>
       <c r="AC7">
-        <v>0.1952334839192866</v>
-      </c>
-      <c r="AD7">
-        <v>0.4883024576184973</v>
+        <v>0.1054070608867452</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>92</v>
       </c>
       <c r="AE7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF7">
+        <v>107</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH7">
+        <v>-0.5204521741159502</v>
+      </c>
+      <c r="AI7">
+        <v>0.8012011517805757</v>
+      </c>
+      <c r="AJ7">
+        <v>-1.274209289886901</v>
+      </c>
+      <c r="AK7">
+        <v>0.2195193766033079</v>
+      </c>
+      <c r="AL7">
+        <v>-0.9792225666673142</v>
+      </c>
+      <c r="AM7">
+        <v>3.667075126397408</v>
+      </c>
+      <c r="AN7">
+        <v>0.7680871446875039</v>
+      </c>
+      <c r="AO7">
+        <v>0.04094809771297364</v>
+      </c>
+      <c r="AP7">
+        <v>159.2205</v>
+      </c>
+      <c r="AQ7">
+        <v>161.7497644636774</v>
+      </c>
+      <c r="AR7">
+        <v>163.0954935730301</v>
+      </c>
+      <c r="AS7">
+        <v>159.2205</v>
+      </c>
+      <c r="AT7">
+        <v>161.272</v>
+      </c>
+      <c r="AU7">
+        <v>161.7497644636774</v>
+      </c>
+      <c r="AV7">
+        <v>157.5343236908817</v>
+      </c>
+      <c r="AW7">
+        <v>0.01588529406500693</v>
+      </c>
+      <c r="AX7">
+        <v>1.5</v>
+      </c>
+      <c r="AY7">
+        <v>0.01588529406500693</v>
+      </c>
+      <c r="AZ7">
+        <v>0.4870126644876198</v>
+      </c>
+      <c r="BA7">
+        <v>0.2</v>
+      </c>
+      <c r="BB7">
+        <v>0.3129873355123802</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>123</v>
+      </c>
+      <c r="BD7">
         <v>100000</v>
       </c>
-      <c r="AG7">
+      <c r="BE7">
         <v>100</v>
       </c>
-      <c r="AH7">
-        <v>375</v>
-      </c>
-      <c r="AI7">
-        <v>0.008284055690501032</v>
-      </c>
-      <c r="AJ7">
-        <v>60356.9095477386</v>
-      </c>
-      <c r="AK7">
-        <v>45267.68216080395</v>
-      </c>
-      <c r="AL7">
-        <v>9422.110552763805</v>
-      </c>
-      <c r="AM7">
-        <v>452.6768216080395</v>
-      </c>
-      <c r="AN7">
-        <v>0.004526768216080395</v>
-      </c>
-      <c r="AO7">
-        <v>374.9999999999999</v>
-      </c>
-      <c r="AP7">
-        <v>0.003749999999999999</v>
-      </c>
-      <c r="AQ7">
-        <v>0.0698956334999188</v>
-      </c>
-      <c r="AR7">
-        <v>0.02513851040307176</v>
-      </c>
-      <c r="AS7">
-        <v>0.02929259479525299</v>
-      </c>
-      <c r="AT7">
+      <c r="BF7">
+        <v>500</v>
+      </c>
+      <c r="BG7">
+        <v>0.01059019604333795</v>
+      </c>
+      <c r="BH7">
+        <v>47213.47914182745</v>
+      </c>
+      <c r="BI7">
+        <v>47213.47914182745</v>
+      </c>
+      <c r="BJ7">
+        <v>296.528896353343</v>
+      </c>
+      <c r="BK7">
+        <v>472.1347914182745</v>
+      </c>
+      <c r="BL7">
+        <v>0.004721347914182745</v>
+      </c>
+      <c r="BM7">
+        <v>500</v>
+      </c>
+      <c r="BN7">
+        <v>0.005</v>
+      </c>
+      <c r="BO7">
+        <v>2.340499296274656</v>
+      </c>
+      <c r="BP7">
+        <v>0.2878946313937342</v>
+      </c>
+      <c r="BQ7">
+        <v>1.959093555582671</v>
+      </c>
+      <c r="BR7">
         <v>1</v>
       </c>
-      <c r="AU7">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY7" s="2">
+      <c r="BS7">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW7" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:75">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B8" s="2">
         <v>46259</v>
@@ -1729,22 +2338,22 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="J8" s="2">
         <v>46258</v>
@@ -1753,129 +2362,201 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0.2424267865881329</v>
+        <v>1.056134761727802</v>
       </c>
       <c r="M8">
         <v>6</v>
       </c>
       <c r="N8">
+        <v>8</v>
+      </c>
+      <c r="O8" t="s">
+        <v>94</v>
+      </c>
+      <c r="P8" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8">
+        <v>0.75</v>
+      </c>
+      <c r="R8" t="s">
+        <v>100</v>
+      </c>
+      <c r="S8" t="s">
+        <v>103</v>
+      </c>
+      <c r="T8">
+        <v>0.7615799839236796</v>
+      </c>
+      <c r="U8">
+        <v>0.7427087014364006</v>
+      </c>
+      <c r="V8" t="s">
+        <v>93</v>
+      </c>
+      <c r="W8" t="s">
+        <v>94</v>
+      </c>
+      <c r="X8">
+        <v>0.9999908346829788</v>
+      </c>
+      <c r="Y8">
+        <v>0.4615302609136551</v>
+      </c>
+      <c r="Z8">
+        <v>59.07032033352175</v>
+      </c>
+      <c r="AA8">
+        <v>11</v>
+      </c>
+      <c r="AB8">
+        <v>0.5139856675391538</v>
+      </c>
+      <c r="AC8">
+        <v>0.857798772186304</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH8">
+        <v>0.3755993608734222</v>
+      </c>
+      <c r="AI8">
+        <v>0.7392270011824164</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8966434547389286</v>
+      </c>
+      <c r="AK8">
+        <v>1.41977643485972</v>
+      </c>
+      <c r="AL8">
+        <v>0.888488091291638</v>
+      </c>
+      <c r="AM8">
+        <v>-2.616449941642473</v>
+      </c>
+      <c r="AN8">
+        <v>0.7766054254501199</v>
+      </c>
+      <c r="AO8">
+        <v>0.04847695600735568</v>
+      </c>
+      <c r="AP8">
+        <v>7.8373</v>
+      </c>
+      <c r="AQ8">
+        <v>7.887934517690176</v>
+      </c>
+      <c r="AR8">
+        <v>7.909302772205145</v>
+      </c>
+      <c r="AS8">
+        <v>7.8373</v>
+      </c>
+      <c r="AT8">
+        <v>7.891</v>
+      </c>
+      <c r="AU8">
+        <v>7.887934517690176</v>
+      </c>
+      <c r="AV8">
+        <v>7.776450000000001</v>
+      </c>
+      <c r="AW8">
+        <v>0.006460709388459761</v>
+      </c>
+      <c r="AX8">
+        <v>0.8321202578500605</v>
+      </c>
+      <c r="AY8">
+        <v>0.006460709388459761</v>
+      </c>
+      <c r="AZ8">
+        <v>0.4193090316677708</v>
+      </c>
+      <c r="BA8">
+        <v>0.2</v>
+      </c>
+      <c r="BB8">
+        <v>0.3806909683322292</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>124</v>
+      </c>
+      <c r="BD8">
+        <v>100000</v>
+      </c>
+      <c r="BE8">
+        <v>100</v>
+      </c>
+      <c r="BF8">
+        <v>375</v>
+      </c>
+      <c r="BG8">
+        <v>0.00776415347122088</v>
+      </c>
+      <c r="BH8">
+        <v>64398.52095316414</v>
+      </c>
+      <c r="BI8">
+        <v>48298.89071487311</v>
+      </c>
+      <c r="BJ8">
+        <v>6162.695152013207</v>
+      </c>
+      <c r="BK8">
+        <v>482.9889071487311</v>
+      </c>
+      <c r="BL8">
+        <v>0.00482988907148731</v>
+      </c>
+      <c r="BM8">
+        <v>375</v>
+      </c>
+      <c r="BN8">
+        <v>0.00375</v>
+      </c>
+      <c r="BO8">
+        <v>0.1676474057603191</v>
+      </c>
+      <c r="BP8">
+        <v>0.02057377393023887</v>
+      </c>
+      <c r="BQ8">
+        <v>0.04913827815876589</v>
+      </c>
+      <c r="BR8">
         <v>1</v>
       </c>
-      <c r="O8" t="s">
-        <v>71</v>
-      </c>
-      <c r="P8" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>0.802655</v>
-      </c>
-      <c r="S8">
-        <v>0.8067437347357025</v>
-      </c>
-      <c r="T8">
-        <v>0.8149541158397413</v>
-      </c>
-      <c r="U8">
-        <v>0.802655</v>
-      </c>
-      <c r="V8">
-        <v>0.798965</v>
-      </c>
-      <c r="W8">
-        <v>0.8067437347357025</v>
-      </c>
-      <c r="X8">
-        <v>0.79262</v>
-      </c>
-      <c r="Y8">
-        <v>0.005094012665095815</v>
-      </c>
-      <c r="Z8">
-        <v>0.4074474076434964</v>
-      </c>
-      <c r="AA8">
-        <v>0.005094012665095815</v>
-      </c>
-      <c r="AB8">
-        <v>0.4403454703982151</v>
-      </c>
-      <c r="AC8">
-        <v>0.2</v>
-      </c>
-      <c r="AD8">
-        <v>0.3596545296017849</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>81</v>
-      </c>
-      <c r="AF8">
-        <v>100000</v>
-      </c>
-      <c r="AG8">
-        <v>100</v>
-      </c>
-      <c r="AH8">
-        <v>500</v>
-      </c>
-      <c r="AI8">
-        <v>0.0125022581308283</v>
-      </c>
-      <c r="AJ8">
-        <v>39992.77528649731</v>
-      </c>
-      <c r="AK8">
-        <v>39992.77528649731</v>
-      </c>
-      <c r="AL8">
-        <v>49825.61036372701</v>
-      </c>
-      <c r="AM8">
-        <v>399.9277528649731</v>
-      </c>
-      <c r="AN8">
-        <v>0.003999277528649731</v>
-      </c>
-      <c r="AO8">
-        <v>500</v>
-      </c>
-      <c r="AP8">
-        <v>0.005</v>
-      </c>
-      <c r="AQ8">
-        <v>0.01571701446863262</v>
-      </c>
-      <c r="AR8">
-        <v>0.00672339156689989</v>
-      </c>
-      <c r="AS8">
-        <v>0.01017430234174833</v>
-      </c>
-      <c r="AT8">
-        <v>1</v>
-      </c>
-      <c r="AU8">
-        <v>0.03825409026847387</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>86</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>67</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY8" s="2">
+      <c r="BS8">
+        <v>0.02829173993681405</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>129</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>91</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>131</v>
+      </c>
+      <c r="BW8" s="2">
         <v>46287</v>
       </c>
     </row>
-    <row r="9" spans="1:51">
+    <row r="9" spans="1:75">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B9" s="2">
         <v>46259</v>
@@ -1884,153 +2565,225 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="J9" s="2">
         <v>46258</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>2.934327230362023</v>
+        <v>0.7544249014873886</v>
       </c>
       <c r="M9">
         <v>6</v>
       </c>
       <c r="N9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O9" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P9" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="Q9">
+        <v>0.75</v>
+      </c>
+      <c r="R9" t="s">
+        <v>100</v>
+      </c>
+      <c r="S9" t="s">
+        <v>103</v>
+      </c>
+      <c r="T9">
+        <v>0.8704251670624802</v>
+      </c>
+      <c r="U9">
+        <v>0.7916658304811172</v>
+      </c>
+      <c r="V9" t="s">
+        <v>93</v>
+      </c>
+      <c r="W9" t="s">
+        <v>94</v>
+      </c>
+      <c r="X9">
+        <v>0.9998980212120042</v>
+      </c>
+      <c r="Y9">
+        <v>0.2572137202752759</v>
+      </c>
+      <c r="Z9">
+        <v>45.46895636211881</v>
+      </c>
+      <c r="AA9">
+        <v>2.000000000000003</v>
+      </c>
+      <c r="AB9">
+        <v>0.70129561026052</v>
+      </c>
+      <c r="AC9">
+        <v>0.7128705822442983</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AH9">
+        <v>0.4407942753436352</v>
+      </c>
+      <c r="AI9">
+        <v>0.7543727577699688</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6054687129152738</v>
+      </c>
+      <c r="AK9">
+        <v>0.6101302909640854</v>
+      </c>
+      <c r="AL9">
+        <v>0.7835889176812064</v>
+      </c>
+      <c r="AM9">
+        <v>-1.17141656044948</v>
+      </c>
+      <c r="AN9">
+        <v>0.6729008517865356</v>
+      </c>
+      <c r="AO9">
+        <v>0.04948651191629264</v>
+      </c>
+      <c r="AP9">
+        <v>4.80441</v>
+      </c>
+      <c r="AQ9">
+        <v>4.833251306552598</v>
+      </c>
+      <c r="AR9">
+        <v>4.817532009625882</v>
+      </c>
+      <c r="AS9">
+        <v>4.80441</v>
+      </c>
+      <c r="AT9">
+        <v>4.86789</v>
+      </c>
+      <c r="AU9">
+        <v>4.833251306552598</v>
+      </c>
+      <c r="AV9">
+        <v>4.764609999999999</v>
+      </c>
+      <c r="AW9">
+        <v>0.006003090192676793</v>
+      </c>
+      <c r="AX9">
+        <v>0.7246559435326199</v>
+      </c>
+      <c r="AY9">
+        <v>0.006003090192676793</v>
+      </c>
+      <c r="AZ9">
+        <v>0.4357340967021426</v>
+      </c>
+      <c r="BA9">
+        <v>0.2</v>
+      </c>
+      <c r="BB9">
+        <v>0.3642659032978574</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>125</v>
+      </c>
+      <c r="BD9">
+        <v>100000</v>
+      </c>
+      <c r="BE9">
+        <v>100</v>
+      </c>
+      <c r="BF9">
+        <v>375</v>
+      </c>
+      <c r="BG9">
+        <v>0.008284055690501032</v>
+      </c>
+      <c r="BH9">
+        <v>60356.9095477386</v>
+      </c>
+      <c r="BI9">
+        <v>45267.68216080395</v>
+      </c>
+      <c r="BJ9">
+        <v>9422.110552763805</v>
+      </c>
+      <c r="BK9">
+        <v>452.6768216080395</v>
+      </c>
+      <c r="BL9">
+        <v>0.004526768216080395</v>
+      </c>
+      <c r="BM9">
+        <v>374.9999999999999</v>
+      </c>
+      <c r="BN9">
+        <v>0.003749999999999999</v>
+      </c>
+      <c r="BO9">
+        <v>0.06357835849285487</v>
+      </c>
+      <c r="BP9">
+        <v>0.0189454200942434</v>
+      </c>
+      <c r="BQ9">
+        <v>0.0348687423964861</v>
+      </